--- a/MC3020_E24.xlsx
+++ b/MC3020_E24.xlsx
@@ -1756,7 +1756,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1939,7 +1939,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
   </cellXfs>
   <cellStyles count="11">
@@ -2230,7 +2229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K226"/>
+  <dimension ref="A1:J226"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -2240,7 +2239,7 @@
     <col min="8" max="8" width="15.5703125" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1">
+    <row r="1" spans="1:10" ht="18.75" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2266,7 +2265,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:10">
       <c r="A2" s="28" t="s">
         <v>9</v>
       </c>
@@ -2281,12 +2280,11 @@
       <c r="F2" s="39"/>
       <c r="G2" s="51"/>
       <c r="H2" s="61">
-        <v>60</v>
-      </c>
-      <c r="J2" s="69"/>
-      <c r="K2" s="68"/>
-    </row>
-    <row r="3" spans="1:11">
+        <v>65.22</v>
+      </c>
+      <c r="J2" s="68"/>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="28" t="s">
         <v>11</v>
       </c>
@@ -2301,12 +2299,11 @@
       <c r="F3" s="40"/>
       <c r="G3" s="52"/>
       <c r="H3" s="61">
-        <v>85</v>
-      </c>
-      <c r="J3" s="69"/>
-      <c r="K3" s="68"/>
-    </row>
-    <row r="4" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J3" s="68"/>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="28" t="s">
         <v>13</v>
       </c>
@@ -2321,12 +2318,11 @@
       <c r="F4" s="40"/>
       <c r="G4" s="53"/>
       <c r="H4" s="61">
-        <v>70</v>
-      </c>
-      <c r="J4" s="69"/>
-      <c r="K4" s="68"/>
-    </row>
-    <row r="5" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J4" s="68"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="28" t="s">
         <v>15</v>
       </c>
@@ -2341,12 +2337,11 @@
       <c r="F5" s="40"/>
       <c r="G5" s="53"/>
       <c r="H5" s="61">
-        <v>25</v>
-      </c>
-      <c r="J5" s="69"/>
-      <c r="K5" s="68"/>
-    </row>
-    <row r="6" spans="1:11">
+        <v>30.43</v>
+      </c>
+      <c r="J5" s="68"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="28" t="s">
         <v>17</v>
       </c>
@@ -2361,12 +2356,11 @@
       <c r="F6" s="40"/>
       <c r="G6" s="53"/>
       <c r="H6" s="61">
-        <v>40</v>
-      </c>
-      <c r="J6" s="69"/>
-      <c r="K6" s="68"/>
-    </row>
-    <row r="7" spans="1:11">
+        <v>43.480000000000004</v>
+      </c>
+      <c r="J6" s="68"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="28" t="s">
         <v>19</v>
       </c>
@@ -2381,12 +2375,11 @@
       <c r="F7" s="40"/>
       <c r="G7" s="53"/>
       <c r="H7" s="61">
-        <v>80</v>
-      </c>
-      <c r="J7" s="69"/>
-      <c r="K7" s="68"/>
-    </row>
-    <row r="8" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J7" s="68"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="28" t="s">
         <v>21</v>
       </c>
@@ -2401,12 +2394,11 @@
       <c r="F8" s="40"/>
       <c r="G8" s="53"/>
       <c r="H8" s="61">
-        <v>85</v>
-      </c>
-      <c r="J8" s="69"/>
-      <c r="K8" s="68"/>
-    </row>
-    <row r="9" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J8" s="68"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="28" t="s">
         <v>23</v>
       </c>
@@ -2421,12 +2413,11 @@
       <c r="F9" s="40"/>
       <c r="G9" s="53"/>
       <c r="H9" s="61">
-        <v>75</v>
-      </c>
-      <c r="J9" s="69"/>
-      <c r="K9" s="68"/>
-    </row>
-    <row r="10" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J9" s="68"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="28" t="s">
         <v>25</v>
       </c>
@@ -2441,12 +2432,11 @@
       <c r="F10" s="40"/>
       <c r="G10" s="53"/>
       <c r="H10" s="61">
-        <v>90</v>
-      </c>
-      <c r="J10" s="69"/>
-      <c r="K10" s="68"/>
-    </row>
-    <row r="11" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J10" s="68"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="28" t="s">
         <v>27</v>
       </c>
@@ -2461,12 +2451,11 @@
       <c r="F11" s="40"/>
       <c r="G11" s="53"/>
       <c r="H11" s="61">
-        <v>80</v>
-      </c>
-      <c r="J11" s="69"/>
-      <c r="K11" s="68"/>
-    </row>
-    <row r="12" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J11" s="68"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="28" t="s">
         <v>29</v>
       </c>
@@ -2481,12 +2470,11 @@
       <c r="F12" s="40"/>
       <c r="G12" s="53"/>
       <c r="H12" s="61">
-        <v>60</v>
-      </c>
-      <c r="J12" s="69"/>
-      <c r="K12" s="68"/>
-    </row>
-    <row r="13" spans="1:11">
+        <v>60.870000000000005</v>
+      </c>
+      <c r="J12" s="68"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="28" t="s">
         <v>31</v>
       </c>
@@ -2501,12 +2489,11 @@
       <c r="F13" s="40"/>
       <c r="G13" s="53"/>
       <c r="H13" s="61">
-        <v>89.47</v>
-      </c>
-      <c r="J13" s="69"/>
-      <c r="K13" s="68"/>
-    </row>
-    <row r="14" spans="1:11">
+        <v>90.91</v>
+      </c>
+      <c r="J13" s="68"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="28" t="s">
         <v>33</v>
       </c>
@@ -2521,12 +2508,11 @@
       <c r="F14" s="40"/>
       <c r="G14" s="53"/>
       <c r="H14" s="61">
-        <v>75</v>
-      </c>
-      <c r="J14" s="69"/>
-      <c r="K14" s="68"/>
-    </row>
-    <row r="15" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J14" s="68"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="28" t="s">
         <v>35</v>
       </c>
@@ -2541,12 +2527,11 @@
       <c r="F15" s="40"/>
       <c r="G15" s="53"/>
       <c r="H15" s="61">
-        <v>80</v>
-      </c>
-      <c r="J15" s="69"/>
-      <c r="K15" s="68"/>
-    </row>
-    <row r="16" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J15" s="68"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="28" t="s">
         <v>37</v>
       </c>
@@ -2563,10 +2548,9 @@
       <c r="H16" s="61">
         <v>0</v>
       </c>
-      <c r="J16" s="69"/>
-      <c r="K16" s="68"/>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="J16" s="68"/>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="28" t="s">
         <v>39</v>
       </c>
@@ -2581,12 +2565,11 @@
       <c r="F17" s="38"/>
       <c r="G17" s="54"/>
       <c r="H17" s="61">
-        <v>80</v>
-      </c>
-      <c r="J17" s="69"/>
-      <c r="K17" s="68"/>
-    </row>
-    <row r="18" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J17" s="68"/>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="28" t="s">
         <v>41</v>
       </c>
@@ -2601,12 +2584,11 @@
       <c r="F18" s="40"/>
       <c r="G18" s="53"/>
       <c r="H18" s="61">
-        <v>90</v>
-      </c>
-      <c r="J18" s="69"/>
-      <c r="K18" s="68"/>
-    </row>
-    <row r="19" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J18" s="68"/>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="28" t="s">
         <v>43</v>
       </c>
@@ -2621,12 +2603,11 @@
       <c r="F19" s="40"/>
       <c r="G19" s="53"/>
       <c r="H19" s="61">
-        <v>75</v>
-      </c>
-      <c r="J19" s="69"/>
-      <c r="K19" s="68"/>
-    </row>
-    <row r="20" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J19" s="68"/>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="28" t="s">
         <v>45</v>
       </c>
@@ -2641,12 +2622,11 @@
       <c r="F20" s="40"/>
       <c r="G20" s="53"/>
       <c r="H20" s="61">
-        <v>75</v>
-      </c>
-      <c r="J20" s="69"/>
-      <c r="K20" s="68"/>
-    </row>
-    <row r="21" spans="1:11">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="J20" s="68"/>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="28" t="s">
         <v>47</v>
       </c>
@@ -2661,12 +2641,11 @@
       <c r="F21" s="40"/>
       <c r="G21" s="53"/>
       <c r="H21" s="61">
-        <v>80</v>
-      </c>
-      <c r="J21" s="69"/>
-      <c r="K21" s="68"/>
-    </row>
-    <row r="22" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J21" s="68"/>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="28" t="s">
         <v>49</v>
       </c>
@@ -2681,12 +2660,11 @@
       <c r="F22" s="40"/>
       <c r="G22" s="53"/>
       <c r="H22" s="61">
-        <v>80</v>
-      </c>
-      <c r="J22" s="69"/>
-      <c r="K22" s="68"/>
-    </row>
-    <row r="23" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J22" s="68"/>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="28" t="s">
         <v>51</v>
       </c>
@@ -2701,12 +2679,11 @@
       <c r="F23" s="40"/>
       <c r="G23" s="53"/>
       <c r="H23" s="61">
-        <v>90</v>
-      </c>
-      <c r="J23" s="69"/>
-      <c r="K23" s="68"/>
-    </row>
-    <row r="24" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J23" s="68"/>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="28" t="s">
         <v>53</v>
       </c>
@@ -2721,12 +2698,11 @@
       <c r="F24" s="40"/>
       <c r="G24" s="53"/>
       <c r="H24" s="61">
-        <v>85</v>
-      </c>
-      <c r="J24" s="69"/>
-      <c r="K24" s="68"/>
-    </row>
-    <row r="25" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J24" s="68"/>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="28" t="s">
         <v>55</v>
       </c>
@@ -2741,12 +2717,11 @@
       <c r="F25" s="40"/>
       <c r="G25" s="53"/>
       <c r="H25" s="61">
-        <v>85</v>
-      </c>
-      <c r="J25" s="69"/>
-      <c r="K25" s="68"/>
-    </row>
-    <row r="26" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J25" s="68"/>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="28" t="s">
         <v>57</v>
       </c>
@@ -2761,12 +2736,11 @@
       <c r="F26" s="40"/>
       <c r="G26" s="53"/>
       <c r="H26" s="61">
-        <v>90</v>
-      </c>
-      <c r="J26" s="69"/>
-      <c r="K26" s="68"/>
-    </row>
-    <row r="27" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J26" s="68"/>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="28" t="s">
         <v>59</v>
       </c>
@@ -2781,12 +2755,11 @@
       <c r="F27" s="40"/>
       <c r="G27" s="53"/>
       <c r="H27" s="61">
-        <v>85</v>
-      </c>
-      <c r="J27" s="69"/>
-      <c r="K27" s="68"/>
-    </row>
-    <row r="28" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J27" s="68"/>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="28" t="s">
         <v>61</v>
       </c>
@@ -2801,12 +2774,11 @@
       <c r="F28" s="40"/>
       <c r="G28" s="53"/>
       <c r="H28" s="61">
-        <v>90</v>
-      </c>
-      <c r="J28" s="69"/>
-      <c r="K28" s="68"/>
-    </row>
-    <row r="29" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J28" s="68"/>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="28" t="s">
         <v>63</v>
       </c>
@@ -2821,12 +2793,11 @@
       <c r="F29" s="40"/>
       <c r="G29" s="53"/>
       <c r="H29" s="61">
-        <v>100</v>
-      </c>
-      <c r="J29" s="69"/>
-      <c r="K29" s="68"/>
-    </row>
-    <row r="30" spans="1:11">
+        <v>95.65</v>
+      </c>
+      <c r="J29" s="68"/>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="28" t="s">
         <v>65</v>
       </c>
@@ -2841,12 +2812,11 @@
       <c r="F30" s="40"/>
       <c r="G30" s="53"/>
       <c r="H30" s="61">
-        <v>70</v>
-      </c>
-      <c r="J30" s="69"/>
-      <c r="K30" s="68"/>
-    </row>
-    <row r="31" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J30" s="68"/>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="28" t="s">
         <v>67</v>
       </c>
@@ -2861,12 +2831,11 @@
       <c r="F31" s="40"/>
       <c r="G31" s="53"/>
       <c r="H31" s="61">
-        <v>90</v>
-      </c>
-      <c r="J31" s="69"/>
-      <c r="K31" s="68"/>
-    </row>
-    <row r="32" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J31" s="68"/>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="28" t="s">
         <v>69</v>
       </c>
@@ -2881,12 +2850,11 @@
       <c r="F32" s="40"/>
       <c r="G32" s="55"/>
       <c r="H32" s="61">
-        <v>45</v>
-      </c>
-      <c r="J32" s="69"/>
-      <c r="K32" s="68"/>
-    </row>
-    <row r="33" spans="1:11">
+        <v>47.83</v>
+      </c>
+      <c r="J32" s="68"/>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="28" t="s">
         <v>71</v>
       </c>
@@ -2901,12 +2869,11 @@
       <c r="F33" s="40"/>
       <c r="G33" s="53"/>
       <c r="H33" s="61">
-        <v>75</v>
-      </c>
-      <c r="J33" s="69"/>
-      <c r="K33" s="68"/>
-    </row>
-    <row r="34" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J33" s="68"/>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="28" t="s">
         <v>73</v>
       </c>
@@ -2921,12 +2888,11 @@
       <c r="F34" s="40"/>
       <c r="G34" s="53"/>
       <c r="H34" s="61">
-        <v>95</v>
-      </c>
-      <c r="J34" s="69"/>
-      <c r="K34" s="68"/>
-    </row>
-    <row r="35" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J34" s="68"/>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="28" t="s">
         <v>75</v>
       </c>
@@ -2941,12 +2907,11 @@
       <c r="F35" s="40"/>
       <c r="G35" s="53"/>
       <c r="H35" s="61">
-        <v>80</v>
-      </c>
-      <c r="J35" s="69"/>
-      <c r="K35" s="68"/>
-    </row>
-    <row r="36" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J35" s="68"/>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="28" t="s">
         <v>77</v>
       </c>
@@ -2961,12 +2926,11 @@
       <c r="F36" s="40"/>
       <c r="G36" s="53"/>
       <c r="H36" s="61">
-        <v>85</v>
-      </c>
-      <c r="J36" s="69"/>
-      <c r="K36" s="68"/>
-    </row>
-    <row r="37" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J36" s="68"/>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="28" t="s">
         <v>79</v>
       </c>
@@ -2981,12 +2945,11 @@
       <c r="F37" s="40"/>
       <c r="G37" s="53"/>
       <c r="H37" s="61">
-        <v>85</v>
-      </c>
-      <c r="J37" s="69"/>
-      <c r="K37" s="68"/>
-    </row>
-    <row r="38" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J37" s="68"/>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="28" t="s">
         <v>81</v>
       </c>
@@ -3001,12 +2964,11 @@
       <c r="F38" s="40"/>
       <c r="G38" s="53"/>
       <c r="H38" s="61">
-        <v>70</v>
-      </c>
-      <c r="J38" s="69"/>
-      <c r="K38" s="68"/>
-    </row>
-    <row r="39" spans="1:11">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="J38" s="68"/>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="28" t="s">
         <v>83</v>
       </c>
@@ -3021,12 +2983,11 @@
       <c r="F39" s="40"/>
       <c r="G39" s="53"/>
       <c r="H39" s="61">
-        <v>80</v>
-      </c>
-      <c r="J39" s="69"/>
-      <c r="K39" s="68"/>
-    </row>
-    <row r="40" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J39" s="68"/>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="28" t="s">
         <v>85</v>
       </c>
@@ -3041,12 +3002,11 @@
       <c r="F40" s="40"/>
       <c r="G40" s="53"/>
       <c r="H40" s="61">
-        <v>90</v>
-      </c>
-      <c r="J40" s="69"/>
-      <c r="K40" s="68"/>
-    </row>
-    <row r="41" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J40" s="68"/>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="28" t="s">
         <v>87</v>
       </c>
@@ -3061,12 +3021,11 @@
       <c r="F41" s="40"/>
       <c r="G41" s="53"/>
       <c r="H41" s="61">
-        <v>45</v>
-      </c>
-      <c r="J41" s="69"/>
-      <c r="K41" s="68"/>
-    </row>
-    <row r="42" spans="1:11">
+        <v>52.17</v>
+      </c>
+      <c r="J41" s="68"/>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="28" t="s">
         <v>89</v>
       </c>
@@ -3081,12 +3040,11 @@
       <c r="F42" s="40"/>
       <c r="G42" s="53"/>
       <c r="H42" s="61">
-        <v>70</v>
-      </c>
-      <c r="J42" s="69"/>
-      <c r="K42" s="68"/>
-    </row>
-    <row r="43" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J42" s="68"/>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="28" t="s">
         <v>91</v>
       </c>
@@ -3101,12 +3059,11 @@
       <c r="F43" s="40"/>
       <c r="G43" s="53"/>
       <c r="H43" s="61">
-        <v>55.000000000000007</v>
-      </c>
-      <c r="J43" s="69"/>
-      <c r="K43" s="68"/>
-    </row>
-    <row r="44" spans="1:11">
+        <v>56.52</v>
+      </c>
+      <c r="J43" s="68"/>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="28" t="s">
         <v>93</v>
       </c>
@@ -3121,12 +3078,11 @@
       <c r="F44" s="40"/>
       <c r="G44" s="53"/>
       <c r="H44" s="61">
-        <v>65</v>
-      </c>
-      <c r="J44" s="69"/>
-      <c r="K44" s="68"/>
-    </row>
-    <row r="45" spans="1:11">
+        <v>60.870000000000005</v>
+      </c>
+      <c r="J44" s="68"/>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="28" t="s">
         <v>95</v>
       </c>
@@ -3141,12 +3097,11 @@
       <c r="F45" s="40"/>
       <c r="G45" s="53"/>
       <c r="H45" s="61">
-        <v>80</v>
-      </c>
-      <c r="J45" s="69"/>
-      <c r="K45" s="68"/>
-    </row>
-    <row r="46" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J45" s="68"/>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="28" t="s">
         <v>97</v>
       </c>
@@ -3161,12 +3116,11 @@
       <c r="F46" s="40"/>
       <c r="G46" s="53"/>
       <c r="H46" s="61">
-        <v>50</v>
-      </c>
-      <c r="J46" s="69"/>
-      <c r="K46" s="68"/>
-    </row>
-    <row r="47" spans="1:11">
+        <v>56.52</v>
+      </c>
+      <c r="J46" s="68"/>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="28" t="s">
         <v>99</v>
       </c>
@@ -3181,12 +3135,11 @@
       <c r="F47" s="40"/>
       <c r="G47" s="53"/>
       <c r="H47" s="61">
-        <v>80</v>
-      </c>
-      <c r="J47" s="69"/>
-      <c r="K47" s="68"/>
-    </row>
-    <row r="48" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J47" s="68"/>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="28" t="s">
         <v>101</v>
       </c>
@@ -3201,12 +3154,11 @@
       <c r="F48" s="40"/>
       <c r="G48" s="53"/>
       <c r="H48" s="61">
-        <v>90</v>
-      </c>
-      <c r="J48" s="69"/>
-      <c r="K48" s="68"/>
-    </row>
-    <row r="49" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J48" s="68"/>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="28" t="s">
         <v>103</v>
       </c>
@@ -3221,12 +3173,11 @@
       <c r="F49" s="40"/>
       <c r="G49" s="55"/>
       <c r="H49" s="61">
-        <v>15</v>
-      </c>
-      <c r="J49" s="69"/>
-      <c r="K49" s="68"/>
-    </row>
-    <row r="50" spans="1:11">
+        <v>21.740000000000002</v>
+      </c>
+      <c r="J49" s="68"/>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="28" t="s">
         <v>105</v>
       </c>
@@ -3241,12 +3192,11 @@
       <c r="F50" s="40"/>
       <c r="G50" s="53"/>
       <c r="H50" s="61">
-        <v>90</v>
-      </c>
-      <c r="J50" s="69"/>
-      <c r="K50" s="68"/>
-    </row>
-    <row r="51" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J50" s="68"/>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="28" t="s">
         <v>107</v>
       </c>
@@ -3261,12 +3211,11 @@
       <c r="F51" s="40"/>
       <c r="G51" s="53"/>
       <c r="H51" s="61">
-        <v>80</v>
-      </c>
-      <c r="J51" s="69"/>
-      <c r="K51" s="68"/>
-    </row>
-    <row r="52" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J51" s="68"/>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="28" t="s">
         <v>109</v>
       </c>
@@ -3281,12 +3230,11 @@
       <c r="F52" s="40"/>
       <c r="G52" s="53"/>
       <c r="H52" s="61">
-        <v>80</v>
-      </c>
-      <c r="J52" s="69"/>
-      <c r="K52" s="68"/>
-    </row>
-    <row r="53" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J52" s="68"/>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="28" t="s">
         <v>111</v>
       </c>
@@ -3301,12 +3249,11 @@
       <c r="F53" s="40"/>
       <c r="G53" s="53"/>
       <c r="H53" s="61">
-        <v>50</v>
-      </c>
-      <c r="J53" s="69"/>
-      <c r="K53" s="68"/>
-    </row>
-    <row r="54" spans="1:11">
+        <v>47.83</v>
+      </c>
+      <c r="J53" s="68"/>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="28" t="s">
         <v>113</v>
       </c>
@@ -3321,12 +3268,11 @@
       <c r="F54" s="40"/>
       <c r="G54" s="53"/>
       <c r="H54" s="61">
-        <v>75</v>
-      </c>
-      <c r="J54" s="69"/>
-      <c r="K54" s="68"/>
-    </row>
-    <row r="55" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J54" s="68"/>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" s="28" t="s">
         <v>115</v>
       </c>
@@ -3341,12 +3287,11 @@
       <c r="F55" s="40"/>
       <c r="G55" s="53"/>
       <c r="H55" s="61">
-        <v>90</v>
-      </c>
-      <c r="J55" s="69"/>
-      <c r="K55" s="68"/>
-    </row>
-    <row r="56" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J55" s="68"/>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" s="28" t="s">
         <v>117</v>
       </c>
@@ -3363,10 +3308,9 @@
       <c r="H56" s="61">
         <v>100</v>
       </c>
-      <c r="J56" s="69"/>
-      <c r="K56" s="68"/>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="J56" s="68"/>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" s="28" t="s">
         <v>119</v>
       </c>
@@ -3381,12 +3325,11 @@
       <c r="F57" s="40"/>
       <c r="G57" s="53"/>
       <c r="H57" s="61">
-        <v>90</v>
-      </c>
-      <c r="J57" s="69"/>
-      <c r="K57" s="68"/>
-    </row>
-    <row r="58" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J57" s="68"/>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" s="28" t="s">
         <v>121</v>
       </c>
@@ -3401,12 +3344,11 @@
       <c r="F58" s="40"/>
       <c r="G58" s="53"/>
       <c r="H58" s="61">
-        <v>60</v>
-      </c>
-      <c r="J58" s="69"/>
-      <c r="K58" s="68"/>
-    </row>
-    <row r="59" spans="1:11">
+        <v>60.870000000000005</v>
+      </c>
+      <c r="J58" s="68"/>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" s="28" t="s">
         <v>123</v>
       </c>
@@ -3421,12 +3363,11 @@
       <c r="F59" s="40"/>
       <c r="G59" s="53"/>
       <c r="H59" s="61">
-        <v>85</v>
-      </c>
-      <c r="J59" s="69"/>
-      <c r="K59" s="68"/>
-    </row>
-    <row r="60" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J59" s="68"/>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" s="28" t="s">
         <v>125</v>
       </c>
@@ -3441,12 +3382,11 @@
       <c r="F60" s="40"/>
       <c r="G60" s="53"/>
       <c r="H60" s="61">
-        <v>80</v>
-      </c>
-      <c r="J60" s="69"/>
-      <c r="K60" s="68"/>
-    </row>
-    <row r="61" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J60" s="68"/>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" s="28" t="s">
         <v>127</v>
       </c>
@@ -3461,12 +3401,11 @@
       <c r="F61" s="41"/>
       <c r="G61" s="54"/>
       <c r="H61" s="61">
-        <v>70</v>
-      </c>
-      <c r="J61" s="69"/>
-      <c r="K61" s="68"/>
-    </row>
-    <row r="62" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J61" s="68"/>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" s="28" t="s">
         <v>129</v>
       </c>
@@ -3481,12 +3420,11 @@
       <c r="F62" s="40"/>
       <c r="G62" s="53"/>
       <c r="H62" s="61">
-        <v>90</v>
-      </c>
-      <c r="J62" s="69"/>
-      <c r="K62" s="68"/>
-    </row>
-    <row r="63" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J62" s="68"/>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="28" t="s">
         <v>131</v>
       </c>
@@ -3501,12 +3439,11 @@
       <c r="F63" s="40"/>
       <c r="G63" s="53"/>
       <c r="H63" s="61">
-        <v>75</v>
-      </c>
-      <c r="J63" s="69"/>
-      <c r="K63" s="68"/>
-    </row>
-    <row r="64" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J63" s="68"/>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" s="28" t="s">
         <v>133</v>
       </c>
@@ -3523,10 +3460,9 @@
       <c r="H64" s="61">
         <v>100</v>
       </c>
-      <c r="J64" s="69"/>
-      <c r="K64" s="68"/>
-    </row>
-    <row r="65" spans="1:11">
+      <c r="J64" s="68"/>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" s="28" t="s">
         <v>135</v>
       </c>
@@ -3541,12 +3477,11 @@
       <c r="F65" s="40"/>
       <c r="G65" s="53"/>
       <c r="H65" s="61">
-        <v>95</v>
-      </c>
-      <c r="J65" s="69"/>
-      <c r="K65" s="68"/>
-    </row>
-    <row r="66" spans="1:11">
+        <v>95.65</v>
+      </c>
+      <c r="J65" s="68"/>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" s="28" t="s">
         <v>137</v>
       </c>
@@ -3561,12 +3496,11 @@
       <c r="F66" s="40"/>
       <c r="G66" s="53"/>
       <c r="H66" s="61">
-        <v>85</v>
-      </c>
-      <c r="J66" s="69"/>
-      <c r="K66" s="68"/>
-    </row>
-    <row r="67" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J66" s="68"/>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" s="28" t="s">
         <v>139</v>
       </c>
@@ -3581,12 +3515,11 @@
       <c r="F67" s="40"/>
       <c r="G67" s="53"/>
       <c r="H67" s="61">
-        <v>90</v>
-      </c>
-      <c r="J67" s="69"/>
-      <c r="K67" s="68"/>
-    </row>
-    <row r="68" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J67" s="68"/>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" s="28" t="s">
         <v>141</v>
       </c>
@@ -3601,12 +3534,11 @@
       <c r="F68" s="40"/>
       <c r="G68" s="53"/>
       <c r="H68" s="61">
-        <v>60</v>
-      </c>
-      <c r="J68" s="69"/>
-      <c r="K68" s="68"/>
-    </row>
-    <row r="69" spans="1:11">
+        <v>60.870000000000005</v>
+      </c>
+      <c r="J68" s="68"/>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" s="28" t="s">
         <v>143</v>
       </c>
@@ -3621,12 +3553,11 @@
       <c r="F69" s="40"/>
       <c r="G69" s="55"/>
       <c r="H69" s="61">
-        <v>50</v>
-      </c>
-      <c r="J69" s="69"/>
-      <c r="K69" s="68"/>
-    </row>
-    <row r="70" spans="1:11">
+        <v>52.17</v>
+      </c>
+      <c r="J69" s="68"/>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" s="28" t="s">
         <v>145</v>
       </c>
@@ -3641,12 +3572,11 @@
       <c r="F70" s="40"/>
       <c r="G70" s="53"/>
       <c r="H70" s="61">
-        <v>75</v>
-      </c>
-      <c r="J70" s="69"/>
-      <c r="K70" s="68"/>
-    </row>
-    <row r="71" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J70" s="68"/>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" s="28" t="s">
         <v>147</v>
       </c>
@@ -3661,12 +3591,11 @@
       <c r="F71" s="40"/>
       <c r="G71" s="53"/>
       <c r="H71" s="61">
-        <v>65</v>
-      </c>
-      <c r="J71" s="69"/>
-      <c r="K71" s="68"/>
-    </row>
-    <row r="72" spans="1:11">
+        <v>60.870000000000005</v>
+      </c>
+      <c r="J71" s="68"/>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" s="28" t="s">
         <v>149</v>
       </c>
@@ -3681,12 +3610,11 @@
       <c r="F72" s="40"/>
       <c r="G72" s="53"/>
       <c r="H72" s="61">
-        <v>70</v>
-      </c>
-      <c r="J72" s="69"/>
-      <c r="K72" s="68"/>
-    </row>
-    <row r="73" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J72" s="68"/>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" s="28" t="s">
         <v>151</v>
       </c>
@@ -3701,12 +3629,11 @@
       <c r="F73" s="40"/>
       <c r="G73" s="53"/>
       <c r="H73" s="61">
-        <v>85</v>
-      </c>
-      <c r="J73" s="69"/>
-      <c r="K73" s="68"/>
-    </row>
-    <row r="74" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J73" s="68"/>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" s="28" t="s">
         <v>153</v>
       </c>
@@ -3721,12 +3648,11 @@
       <c r="F74" s="40"/>
       <c r="G74" s="55"/>
       <c r="H74" s="61">
-        <v>100</v>
-      </c>
-      <c r="J74" s="69"/>
-      <c r="K74" s="68"/>
-    </row>
-    <row r="75" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J74" s="68"/>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" s="28" t="s">
         <v>155</v>
       </c>
@@ -3743,10 +3669,9 @@
       <c r="H75" s="61">
         <v>0</v>
       </c>
-      <c r="J75" s="69"/>
-      <c r="K75" s="68"/>
-    </row>
-    <row r="76" spans="1:11">
+      <c r="J75" s="68"/>
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76" s="28" t="s">
         <v>157</v>
       </c>
@@ -3761,12 +3686,11 @@
       <c r="F76" s="40"/>
       <c r="G76" s="53"/>
       <c r="H76" s="61">
-        <v>50</v>
-      </c>
-      <c r="J76" s="69"/>
-      <c r="K76" s="68"/>
-    </row>
-    <row r="77" spans="1:11">
+        <v>52.17</v>
+      </c>
+      <c r="J76" s="68"/>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77" s="28" t="s">
         <v>159</v>
       </c>
@@ -3781,12 +3705,11 @@
       <c r="F77" s="40"/>
       <c r="G77" s="53"/>
       <c r="H77" s="61">
-        <v>50</v>
-      </c>
-      <c r="J77" s="69"/>
-      <c r="K77" s="68"/>
-    </row>
-    <row r="78" spans="1:11">
+        <v>52.17</v>
+      </c>
+      <c r="J77" s="68"/>
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78" s="28" t="s">
         <v>161</v>
       </c>
@@ -3801,12 +3724,11 @@
       <c r="F78" s="40"/>
       <c r="G78" s="53"/>
       <c r="H78" s="61">
-        <v>85</v>
-      </c>
-      <c r="J78" s="69"/>
-      <c r="K78" s="68"/>
-    </row>
-    <row r="79" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J78" s="68"/>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" s="28" t="s">
         <v>163</v>
       </c>
@@ -3823,10 +3745,9 @@
       <c r="H79" s="61">
         <v>0</v>
       </c>
-      <c r="J79" s="69"/>
-      <c r="K79" s="68"/>
-    </row>
-    <row r="80" spans="1:11">
+      <c r="J79" s="68"/>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80" s="28" t="s">
         <v>165</v>
       </c>
@@ -3841,12 +3762,11 @@
       <c r="F80" s="40"/>
       <c r="G80" s="53"/>
       <c r="H80" s="61">
-        <v>85</v>
-      </c>
-      <c r="J80" s="69"/>
-      <c r="K80" s="68"/>
-    </row>
-    <row r="81" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J80" s="68"/>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" s="28" t="s">
         <v>167</v>
       </c>
@@ -3861,12 +3781,11 @@
       <c r="F81" s="40"/>
       <c r="G81" s="53"/>
       <c r="H81" s="61">
-        <v>45</v>
-      </c>
-      <c r="J81" s="69"/>
-      <c r="K81" s="68"/>
-    </row>
-    <row r="82" spans="1:11">
+        <v>43.480000000000004</v>
+      </c>
+      <c r="J81" s="68"/>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" s="28" t="s">
         <v>169</v>
       </c>
@@ -3881,12 +3800,11 @@
       <c r="F82" s="40"/>
       <c r="G82" s="53"/>
       <c r="H82" s="61">
-        <v>70</v>
-      </c>
-      <c r="J82" s="69"/>
-      <c r="K82" s="68"/>
-    </row>
-    <row r="83" spans="1:11">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="J82" s="68"/>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83" s="28" t="s">
         <v>171</v>
       </c>
@@ -3901,12 +3819,11 @@
       <c r="F83" s="40"/>
       <c r="G83" s="53"/>
       <c r="H83" s="61">
-        <v>80</v>
-      </c>
-      <c r="J83" s="69"/>
-      <c r="K83" s="68"/>
-    </row>
-    <row r="84" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J83" s="68"/>
+    </row>
+    <row r="84" spans="1:10">
       <c r="A84" s="28" t="s">
         <v>173</v>
       </c>
@@ -3921,12 +3838,11 @@
       <c r="F84" s="40"/>
       <c r="G84" s="53"/>
       <c r="H84" s="61">
-        <v>95</v>
-      </c>
-      <c r="J84" s="69"/>
-      <c r="K84" s="68"/>
-    </row>
-    <row r="85" spans="1:11">
+        <v>95.65</v>
+      </c>
+      <c r="J84" s="68"/>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85" s="28" t="s">
         <v>175</v>
       </c>
@@ -3941,12 +3857,11 @@
       <c r="F85" s="40"/>
       <c r="G85" s="53"/>
       <c r="H85" s="61">
-        <v>80</v>
-      </c>
-      <c r="J85" s="69"/>
-      <c r="K85" s="68"/>
-    </row>
-    <row r="86" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J85" s="68"/>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86" s="28" t="s">
         <v>177</v>
       </c>
@@ -3961,12 +3876,11 @@
       <c r="F86" s="40"/>
       <c r="G86" s="55"/>
       <c r="H86" s="61">
-        <v>90</v>
-      </c>
-      <c r="J86" s="69"/>
-      <c r="K86" s="68"/>
-    </row>
-    <row r="87" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J86" s="68"/>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" s="28" t="s">
         <v>179</v>
       </c>
@@ -3981,12 +3895,11 @@
       <c r="F87" s="40"/>
       <c r="G87" s="53"/>
       <c r="H87" s="61">
-        <v>80</v>
-      </c>
-      <c r="J87" s="69"/>
-      <c r="K87" s="68"/>
-    </row>
-    <row r="88" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J87" s="68"/>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88" s="28" t="s">
         <v>181</v>
       </c>
@@ -4001,12 +3914,11 @@
       <c r="F88" s="41"/>
       <c r="G88" s="54"/>
       <c r="H88" s="61">
-        <v>75</v>
-      </c>
-      <c r="J88" s="69"/>
-      <c r="K88" s="68"/>
-    </row>
-    <row r="89" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J88" s="68"/>
+    </row>
+    <row r="89" spans="1:10">
       <c r="A89" s="28" t="s">
         <v>183</v>
       </c>
@@ -4021,12 +3933,11 @@
       <c r="F89" s="40"/>
       <c r="G89" s="53"/>
       <c r="H89" s="61">
-        <v>75</v>
-      </c>
-      <c r="J89" s="69"/>
-      <c r="K89" s="68"/>
-    </row>
-    <row r="90" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J89" s="68"/>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90" s="28" t="s">
         <v>185</v>
       </c>
@@ -4041,12 +3952,11 @@
       <c r="F90" s="40"/>
       <c r="G90" s="53"/>
       <c r="H90" s="61">
-        <v>50</v>
-      </c>
-      <c r="J90" s="69"/>
-      <c r="K90" s="68"/>
-    </row>
-    <row r="91" spans="1:11">
+        <v>56.52</v>
+      </c>
+      <c r="J90" s="68"/>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91" s="28" t="s">
         <v>187</v>
       </c>
@@ -4061,12 +3971,11 @@
       <c r="F91" s="40"/>
       <c r="G91" s="53"/>
       <c r="H91" s="61">
-        <v>85</v>
-      </c>
-      <c r="J91" s="69"/>
-      <c r="K91" s="68"/>
-    </row>
-    <row r="92" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J91" s="68"/>
+    </row>
+    <row r="92" spans="1:10">
       <c r="A92" s="28" t="s">
         <v>189</v>
       </c>
@@ -4081,12 +3990,11 @@
       <c r="F92" s="40"/>
       <c r="G92" s="53"/>
       <c r="H92" s="61">
-        <v>65</v>
-      </c>
-      <c r="J92" s="69"/>
-      <c r="K92" s="68"/>
-    </row>
-    <row r="93" spans="1:11">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="J92" s="68"/>
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93" s="28" t="s">
         <v>191</v>
       </c>
@@ -4101,12 +4009,11 @@
       <c r="F93" s="40"/>
       <c r="G93" s="55"/>
       <c r="H93" s="61">
-        <v>55.000000000000007</v>
-      </c>
-      <c r="J93" s="69"/>
-      <c r="K93" s="68"/>
-    </row>
-    <row r="94" spans="1:11">
+        <v>52.17</v>
+      </c>
+      <c r="J93" s="68"/>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" s="28" t="s">
         <v>193</v>
       </c>
@@ -4121,12 +4028,11 @@
       <c r="F94" s="40"/>
       <c r="G94" s="53"/>
       <c r="H94" s="61">
-        <v>80</v>
-      </c>
-      <c r="J94" s="69"/>
-      <c r="K94" s="68"/>
-    </row>
-    <row r="95" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J94" s="68"/>
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95" s="28" t="s">
         <v>195</v>
       </c>
@@ -4141,12 +4047,11 @@
       <c r="F95" s="40"/>
       <c r="G95" s="53"/>
       <c r="H95" s="61">
-        <v>10</v>
-      </c>
-      <c r="J95" s="69"/>
-      <c r="K95" s="68"/>
-    </row>
-    <row r="96" spans="1:11">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="J95" s="68"/>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96" s="28" t="s">
         <v>197</v>
       </c>
@@ -4161,12 +4066,11 @@
       <c r="F96" s="40"/>
       <c r="G96" s="53"/>
       <c r="H96" s="61">
-        <v>85</v>
-      </c>
-      <c r="J96" s="69"/>
-      <c r="K96" s="68"/>
-    </row>
-    <row r="97" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J96" s="68"/>
+    </row>
+    <row r="97" spans="1:10">
       <c r="A97" s="28" t="s">
         <v>199</v>
       </c>
@@ -4181,12 +4085,11 @@
       <c r="F97" s="40"/>
       <c r="G97" s="53"/>
       <c r="H97" s="61">
-        <v>90</v>
-      </c>
-      <c r="J97" s="69"/>
-      <c r="K97" s="68"/>
-    </row>
-    <row r="98" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J97" s="68"/>
+    </row>
+    <row r="98" spans="1:10">
       <c r="A98" s="28" t="s">
         <v>201</v>
       </c>
@@ -4201,12 +4104,11 @@
       <c r="F98" s="40"/>
       <c r="G98" s="53"/>
       <c r="H98" s="61">
-        <v>75</v>
-      </c>
-      <c r="J98" s="69"/>
-      <c r="K98" s="68"/>
-    </row>
-    <row r="99" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J98" s="68"/>
+    </row>
+    <row r="99" spans="1:10">
       <c r="A99" s="28" t="s">
         <v>203</v>
       </c>
@@ -4221,12 +4123,11 @@
       <c r="F99" s="40"/>
       <c r="G99" s="53"/>
       <c r="H99" s="61">
-        <v>80</v>
-      </c>
-      <c r="J99" s="69"/>
-      <c r="K99" s="68"/>
-    </row>
-    <row r="100" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J99" s="68"/>
+    </row>
+    <row r="100" spans="1:10">
       <c r="A100" s="28" t="s">
         <v>205</v>
       </c>
@@ -4241,12 +4142,11 @@
       <c r="F100" s="41"/>
       <c r="G100" s="54"/>
       <c r="H100" s="61">
-        <v>60</v>
-      </c>
-      <c r="J100" s="69"/>
-      <c r="K100" s="68"/>
-    </row>
-    <row r="101" spans="1:11">
+        <v>65.22</v>
+      </c>
+      <c r="J100" s="68"/>
+    </row>
+    <row r="101" spans="1:10">
       <c r="A101" s="28" t="s">
         <v>207</v>
       </c>
@@ -4261,12 +4161,11 @@
       <c r="F101" s="40"/>
       <c r="G101" s="53"/>
       <c r="H101" s="61">
-        <v>50</v>
-      </c>
-      <c r="J101" s="69"/>
-      <c r="K101" s="68"/>
-    </row>
-    <row r="102" spans="1:11">
+        <v>56.52</v>
+      </c>
+      <c r="J101" s="68"/>
+    </row>
+    <row r="102" spans="1:10">
       <c r="A102" s="28" t="s">
         <v>209</v>
       </c>
@@ -4283,10 +4182,9 @@
       <c r="H102" s="61">
         <v>0</v>
       </c>
-      <c r="J102" s="69"/>
-      <c r="K102" s="68"/>
-    </row>
-    <row r="103" spans="1:11">
+      <c r="J102" s="68"/>
+    </row>
+    <row r="103" spans="1:10">
       <c r="A103" s="28" t="s">
         <v>211</v>
       </c>
@@ -4301,12 +4199,11 @@
       <c r="F103" s="40"/>
       <c r="G103" s="53"/>
       <c r="H103" s="61">
-        <v>80</v>
-      </c>
-      <c r="J103" s="69"/>
-      <c r="K103" s="68"/>
-    </row>
-    <row r="104" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J103" s="68"/>
+    </row>
+    <row r="104" spans="1:10">
       <c r="A104" s="28" t="s">
         <v>213</v>
       </c>
@@ -4321,12 +4218,11 @@
       <c r="F104" s="40"/>
       <c r="G104" s="55"/>
       <c r="H104" s="61">
-        <v>90</v>
-      </c>
-      <c r="J104" s="69"/>
-      <c r="K104" s="68"/>
-    </row>
-    <row r="105" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J104" s="68"/>
+    </row>
+    <row r="105" spans="1:10">
       <c r="A105" s="28" t="s">
         <v>215</v>
       </c>
@@ -4341,12 +4237,11 @@
       <c r="F105" s="40"/>
       <c r="G105" s="53"/>
       <c r="H105" s="61">
-        <v>95</v>
-      </c>
-      <c r="J105" s="69"/>
-      <c r="K105" s="68"/>
-    </row>
-    <row r="106" spans="1:11">
+        <v>95.65</v>
+      </c>
+      <c r="J105" s="68"/>
+    </row>
+    <row r="106" spans="1:10">
       <c r="A106" s="28" t="s">
         <v>217</v>
       </c>
@@ -4361,12 +4256,11 @@
       <c r="F106" s="40"/>
       <c r="G106" s="53"/>
       <c r="H106" s="61">
-        <v>80</v>
-      </c>
-      <c r="J106" s="69"/>
-      <c r="K106" s="68"/>
-    </row>
-    <row r="107" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J106" s="68"/>
+    </row>
+    <row r="107" spans="1:10">
       <c r="A107" s="28" t="s">
         <v>219</v>
       </c>
@@ -4381,12 +4275,11 @@
       <c r="F107" s="40"/>
       <c r="G107" s="53"/>
       <c r="H107" s="61">
-        <v>95</v>
-      </c>
-      <c r="J107" s="69"/>
-      <c r="K107" s="68"/>
-    </row>
-    <row r="108" spans="1:11">
+        <v>95.65</v>
+      </c>
+      <c r="J107" s="68"/>
+    </row>
+    <row r="108" spans="1:10">
       <c r="A108" s="28" t="s">
         <v>221</v>
       </c>
@@ -4401,12 +4294,11 @@
       <c r="F108" s="40"/>
       <c r="G108" s="53"/>
       <c r="H108" s="61">
-        <v>80</v>
-      </c>
-      <c r="J108" s="69"/>
-      <c r="K108" s="68"/>
-    </row>
-    <row r="109" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J108" s="68"/>
+    </row>
+    <row r="109" spans="1:10">
       <c r="A109" s="28" t="s">
         <v>223</v>
       </c>
@@ -4421,12 +4313,11 @@
       <c r="F109" s="40"/>
       <c r="G109" s="53"/>
       <c r="H109" s="61">
-        <v>85</v>
-      </c>
-      <c r="J109" s="69"/>
-      <c r="K109" s="68"/>
-    </row>
-    <row r="110" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J109" s="68"/>
+    </row>
+    <row r="110" spans="1:10">
       <c r="A110" s="28" t="s">
         <v>225</v>
       </c>
@@ -4443,10 +4334,9 @@
       <c r="H110" s="61">
         <v>100</v>
       </c>
-      <c r="J110" s="69"/>
-      <c r="K110" s="68"/>
-    </row>
-    <row r="111" spans="1:11">
+      <c r="J110" s="68"/>
+    </row>
+    <row r="111" spans="1:10">
       <c r="A111" s="28" t="s">
         <v>227</v>
       </c>
@@ -4463,10 +4353,9 @@
       <c r="H111" s="61">
         <v>100</v>
       </c>
-      <c r="J111" s="69"/>
-      <c r="K111" s="68"/>
-    </row>
-    <row r="112" spans="1:11">
+      <c r="J111" s="68"/>
+    </row>
+    <row r="112" spans="1:10">
       <c r="A112" s="28" t="s">
         <v>229</v>
       </c>
@@ -4481,12 +4370,11 @@
       <c r="F112" s="40"/>
       <c r="G112" s="53"/>
       <c r="H112" s="61">
-        <v>70</v>
-      </c>
-      <c r="J112" s="69"/>
-      <c r="K112" s="68"/>
-    </row>
-    <row r="113" spans="1:11">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="J112" s="68"/>
+    </row>
+    <row r="113" spans="1:10">
       <c r="A113" s="28" t="s">
         <v>231</v>
       </c>
@@ -4501,12 +4389,11 @@
       <c r="F113" s="40"/>
       <c r="G113" s="53"/>
       <c r="H113" s="61">
-        <v>85</v>
-      </c>
-      <c r="J113" s="69"/>
-      <c r="K113" s="68"/>
-    </row>
-    <row r="114" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J113" s="68"/>
+    </row>
+    <row r="114" spans="1:10">
       <c r="A114" s="28" t="s">
         <v>233</v>
       </c>
@@ -4521,12 +4408,11 @@
       <c r="F114" s="40"/>
       <c r="G114" s="53"/>
       <c r="H114" s="61">
-        <v>75</v>
-      </c>
-      <c r="J114" s="69"/>
-      <c r="K114" s="68"/>
-    </row>
-    <row r="115" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J114" s="68"/>
+    </row>
+    <row r="115" spans="1:10">
       <c r="A115" s="28" t="s">
         <v>234</v>
       </c>
@@ -4541,12 +4427,11 @@
       <c r="F115" s="40"/>
       <c r="G115" s="53"/>
       <c r="H115" s="61">
-        <v>75</v>
-      </c>
-      <c r="J115" s="69"/>
-      <c r="K115" s="68"/>
-    </row>
-    <row r="116" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J115" s="68"/>
+    </row>
+    <row r="116" spans="1:10">
       <c r="A116" s="28" t="s">
         <v>236</v>
       </c>
@@ -4561,12 +4446,11 @@
       <c r="F116" s="40"/>
       <c r="G116" s="53"/>
       <c r="H116" s="61">
-        <v>90</v>
-      </c>
-      <c r="J116" s="69"/>
-      <c r="K116" s="68"/>
-    </row>
-    <row r="117" spans="1:11" ht="17.25" customHeight="1">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J116" s="68"/>
+    </row>
+    <row r="117" spans="1:10" ht="17.25" customHeight="1">
       <c r="A117" s="28" t="s">
         <v>238</v>
       </c>
@@ -4581,12 +4465,11 @@
       <c r="F117" s="40"/>
       <c r="G117" s="53"/>
       <c r="H117" s="61">
-        <v>65</v>
-      </c>
-      <c r="J117" s="69"/>
-      <c r="K117" s="68"/>
-    </row>
-    <row r="118" spans="1:11">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="J117" s="68"/>
+    </row>
+    <row r="118" spans="1:10">
       <c r="A118" s="28" t="s">
         <v>240</v>
       </c>
@@ -4601,12 +4484,11 @@
       <c r="F118" s="40"/>
       <c r="G118" s="53"/>
       <c r="H118" s="61">
-        <v>90</v>
-      </c>
-      <c r="J118" s="69"/>
-      <c r="K118" s="68"/>
-    </row>
-    <row r="119" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J118" s="68"/>
+    </row>
+    <row r="119" spans="1:10">
       <c r="A119" s="28" t="s">
         <v>242</v>
       </c>
@@ -4621,12 +4503,11 @@
       <c r="F119" s="40"/>
       <c r="G119" s="53"/>
       <c r="H119" s="61">
-        <v>85</v>
-      </c>
-      <c r="J119" s="69"/>
-      <c r="K119" s="68"/>
-    </row>
-    <row r="120" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J119" s="68"/>
+    </row>
+    <row r="120" spans="1:10">
       <c r="A120" s="28" t="s">
         <v>244</v>
       </c>
@@ -4641,12 +4522,11 @@
       <c r="F120" s="40"/>
       <c r="G120" s="53"/>
       <c r="H120" s="61">
-        <v>85</v>
-      </c>
-      <c r="J120" s="69"/>
-      <c r="K120" s="68"/>
-    </row>
-    <row r="121" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J120" s="68"/>
+    </row>
+    <row r="121" spans="1:10">
       <c r="A121" s="28" t="s">
         <v>246</v>
       </c>
@@ -4661,12 +4541,11 @@
       <c r="F121" s="40"/>
       <c r="G121" s="53"/>
       <c r="H121" s="61">
-        <v>75</v>
-      </c>
-      <c r="J121" s="69"/>
-      <c r="K121" s="68"/>
-    </row>
-    <row r="122" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J121" s="68"/>
+    </row>
+    <row r="122" spans="1:10">
       <c r="A122" s="28" t="s">
         <v>248</v>
       </c>
@@ -4681,12 +4560,11 @@
       <c r="F122" s="40"/>
       <c r="G122" s="53"/>
       <c r="H122" s="61">
-        <v>75</v>
-      </c>
-      <c r="J122" s="69"/>
-      <c r="K122" s="68"/>
-    </row>
-    <row r="123" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J122" s="68"/>
+    </row>
+    <row r="123" spans="1:10">
       <c r="A123" s="28" t="s">
         <v>250</v>
       </c>
@@ -4701,12 +4579,11 @@
       <c r="F123" s="40"/>
       <c r="G123" s="53"/>
       <c r="H123" s="61">
-        <v>100</v>
-      </c>
-      <c r="J123" s="69"/>
-      <c r="K123" s="68"/>
-    </row>
-    <row r="124" spans="1:11">
+        <v>95.65</v>
+      </c>
+      <c r="J123" s="68"/>
+    </row>
+    <row r="124" spans="1:10">
       <c r="A124" s="28" t="s">
         <v>252</v>
       </c>
@@ -4721,12 +4598,11 @@
       <c r="F124" s="40"/>
       <c r="G124" s="53"/>
       <c r="H124" s="61">
-        <v>85</v>
-      </c>
-      <c r="J124" s="69"/>
-      <c r="K124" s="68"/>
-    </row>
-    <row r="125" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J124" s="68"/>
+    </row>
+    <row r="125" spans="1:10">
       <c r="A125" s="28" t="s">
         <v>254</v>
       </c>
@@ -4743,10 +4619,9 @@
       <c r="H125" s="61">
         <v>0</v>
       </c>
-      <c r="J125" s="69"/>
-      <c r="K125" s="68"/>
-    </row>
-    <row r="126" spans="1:11">
+      <c r="J125" s="68"/>
+    </row>
+    <row r="126" spans="1:10">
       <c r="A126" s="28" t="s">
         <v>256</v>
       </c>
@@ -4761,12 +4636,11 @@
       <c r="F126" s="40"/>
       <c r="G126" s="53"/>
       <c r="H126" s="61">
-        <v>80</v>
-      </c>
-      <c r="J126" s="69"/>
-      <c r="K126" s="68"/>
-    </row>
-    <row r="127" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J126" s="68"/>
+    </row>
+    <row r="127" spans="1:10">
       <c r="A127" s="28" t="s">
         <v>258</v>
       </c>
@@ -4781,12 +4655,11 @@
       <c r="F127" s="40"/>
       <c r="G127" s="53"/>
       <c r="H127" s="61">
-        <v>70</v>
-      </c>
-      <c r="J127" s="69"/>
-      <c r="K127" s="68"/>
-    </row>
-    <row r="128" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J127" s="68"/>
+    </row>
+    <row r="128" spans="1:10">
       <c r="A128" s="28" t="s">
         <v>260</v>
       </c>
@@ -4801,12 +4674,11 @@
       <c r="F128" s="40"/>
       <c r="G128" s="53"/>
       <c r="H128" s="61">
-        <v>85</v>
-      </c>
-      <c r="J128" s="69"/>
-      <c r="K128" s="68"/>
-    </row>
-    <row r="129" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J128" s="68"/>
+    </row>
+    <row r="129" spans="1:10">
       <c r="A129" s="28" t="s">
         <v>262</v>
       </c>
@@ -4823,10 +4695,9 @@
       <c r="H129" s="61">
         <v>0</v>
       </c>
-      <c r="J129" s="69"/>
-      <c r="K129" s="68"/>
-    </row>
-    <row r="130" spans="1:11">
+      <c r="J129" s="68"/>
+    </row>
+    <row r="130" spans="1:10">
       <c r="A130" s="28" t="s">
         <v>264</v>
       </c>
@@ -4841,12 +4712,11 @@
       <c r="F130" s="40"/>
       <c r="G130" s="53"/>
       <c r="H130" s="61">
-        <v>90</v>
-      </c>
-      <c r="J130" s="69"/>
-      <c r="K130" s="68"/>
-    </row>
-    <row r="131" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J130" s="68"/>
+    </row>
+    <row r="131" spans="1:10">
       <c r="A131" s="28" t="s">
         <v>266</v>
       </c>
@@ -4861,12 +4731,11 @@
       <c r="F131" s="40"/>
       <c r="G131" s="53"/>
       <c r="H131" s="61">
-        <v>85</v>
-      </c>
-      <c r="J131" s="69"/>
-      <c r="K131" s="68"/>
-    </row>
-    <row r="132" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J131" s="68"/>
+    </row>
+    <row r="132" spans="1:10">
       <c r="A132" s="28" t="s">
         <v>268</v>
       </c>
@@ -4881,12 +4750,11 @@
       <c r="F132" s="40"/>
       <c r="G132" s="53"/>
       <c r="H132" s="61">
-        <v>85</v>
-      </c>
-      <c r="J132" s="69"/>
-      <c r="K132" s="68"/>
-    </row>
-    <row r="133" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J132" s="68"/>
+    </row>
+    <row r="133" spans="1:10">
       <c r="A133" s="28" t="s">
         <v>270</v>
       </c>
@@ -4901,12 +4769,11 @@
       <c r="F133" s="40"/>
       <c r="G133" s="53"/>
       <c r="H133" s="61">
-        <v>75</v>
-      </c>
-      <c r="J133" s="69"/>
-      <c r="K133" s="68"/>
-    </row>
-    <row r="134" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J133" s="68"/>
+    </row>
+    <row r="134" spans="1:10">
       <c r="A134" s="28" t="s">
         <v>272</v>
       </c>
@@ -4921,12 +4788,11 @@
       <c r="F134" s="40"/>
       <c r="G134" s="53"/>
       <c r="H134" s="61">
-        <v>80</v>
-      </c>
-      <c r="J134" s="69"/>
-      <c r="K134" s="68"/>
-    </row>
-    <row r="135" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J134" s="68"/>
+    </row>
+    <row r="135" spans="1:10">
       <c r="A135" s="28" t="s">
         <v>274</v>
       </c>
@@ -4941,12 +4807,11 @@
       <c r="F135" s="40"/>
       <c r="G135" s="53"/>
       <c r="H135" s="61">
-        <v>85</v>
-      </c>
-      <c r="J135" s="69"/>
-      <c r="K135" s="68"/>
-    </row>
-    <row r="136" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J135" s="68"/>
+    </row>
+    <row r="136" spans="1:10">
       <c r="A136" s="28" t="s">
         <v>276</v>
       </c>
@@ -4961,12 +4826,11 @@
       <c r="F136" s="40"/>
       <c r="G136" s="53"/>
       <c r="H136" s="61">
-        <v>80</v>
-      </c>
-      <c r="J136" s="69"/>
-      <c r="K136" s="68"/>
-    </row>
-    <row r="137" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J136" s="68"/>
+    </row>
+    <row r="137" spans="1:10">
       <c r="A137" s="28" t="s">
         <v>278</v>
       </c>
@@ -4981,12 +4845,11 @@
       <c r="F137" s="40"/>
       <c r="G137" s="53"/>
       <c r="H137" s="61">
-        <v>90</v>
-      </c>
-      <c r="J137" s="69"/>
-      <c r="K137" s="68"/>
-    </row>
-    <row r="138" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J137" s="68"/>
+    </row>
+    <row r="138" spans="1:10">
       <c r="A138" s="28" t="s">
         <v>280</v>
       </c>
@@ -5001,12 +4864,11 @@
       <c r="F138" s="41"/>
       <c r="G138" s="54"/>
       <c r="H138" s="61">
-        <v>85</v>
-      </c>
-      <c r="J138" s="69"/>
-      <c r="K138" s="68"/>
-    </row>
-    <row r="139" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J138" s="68"/>
+    </row>
+    <row r="139" spans="1:10">
       <c r="A139" s="28" t="s">
         <v>282</v>
       </c>
@@ -5021,12 +4883,11 @@
       <c r="F139" s="40"/>
       <c r="G139" s="53"/>
       <c r="H139" s="61">
-        <v>85</v>
-      </c>
-      <c r="J139" s="69"/>
-      <c r="K139" s="68"/>
-    </row>
-    <row r="140" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J139" s="68"/>
+    </row>
+    <row r="140" spans="1:10">
       <c r="A140" s="28" t="s">
         <v>284</v>
       </c>
@@ -5043,10 +4904,9 @@
       <c r="H140" s="61">
         <v>100</v>
       </c>
-      <c r="J140" s="69"/>
-      <c r="K140" s="68"/>
-    </row>
-    <row r="141" spans="1:11">
+      <c r="J140" s="68"/>
+    </row>
+    <row r="141" spans="1:10">
       <c r="A141" s="28" t="s">
         <v>286</v>
       </c>
@@ -5061,12 +4921,11 @@
       <c r="F141" s="40"/>
       <c r="G141" s="57"/>
       <c r="H141" s="61">
-        <v>90</v>
-      </c>
-      <c r="J141" s="69"/>
-      <c r="K141" s="68"/>
-    </row>
-    <row r="142" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J141" s="68"/>
+    </row>
+    <row r="142" spans="1:10">
       <c r="A142" s="28" t="s">
         <v>288</v>
       </c>
@@ -5083,10 +4942,9 @@
       <c r="H142" s="61">
         <v>100</v>
       </c>
-      <c r="J142" s="69"/>
-      <c r="K142" s="68"/>
-    </row>
-    <row r="143" spans="1:11">
+      <c r="J142" s="68"/>
+    </row>
+    <row r="143" spans="1:10">
       <c r="A143" s="28" t="s">
         <v>290</v>
       </c>
@@ -5101,12 +4959,11 @@
       <c r="F143" s="41"/>
       <c r="G143" s="54"/>
       <c r="H143" s="61">
-        <v>90</v>
-      </c>
-      <c r="J143" s="69"/>
-      <c r="K143" s="68"/>
-    </row>
-    <row r="144" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J143" s="68"/>
+    </row>
+    <row r="144" spans="1:10">
       <c r="A144" s="28" t="s">
         <v>292</v>
       </c>
@@ -5121,12 +4978,11 @@
       <c r="F144" s="40"/>
       <c r="G144" s="53"/>
       <c r="H144" s="61">
-        <v>85</v>
-      </c>
-      <c r="J144" s="69"/>
-      <c r="K144" s="68"/>
-    </row>
-    <row r="145" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J144" s="68"/>
+    </row>
+    <row r="145" spans="1:10">
       <c r="A145" s="28" t="s">
         <v>294</v>
       </c>
@@ -5141,12 +4997,11 @@
       <c r="F145" s="40"/>
       <c r="G145" s="53"/>
       <c r="H145" s="61">
-        <v>90</v>
-      </c>
-      <c r="J145" s="69"/>
-      <c r="K145" s="68"/>
-    </row>
-    <row r="146" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J145" s="68"/>
+    </row>
+    <row r="146" spans="1:10">
       <c r="A146" s="28" t="s">
         <v>296</v>
       </c>
@@ -5161,12 +5016,11 @@
       <c r="F146" s="40"/>
       <c r="G146" s="53"/>
       <c r="H146" s="61">
-        <v>90</v>
-      </c>
-      <c r="J146" s="69"/>
-      <c r="K146" s="68"/>
-    </row>
-    <row r="147" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J146" s="68"/>
+    </row>
+    <row r="147" spans="1:10">
       <c r="A147" s="28" t="s">
         <v>298</v>
       </c>
@@ -5181,12 +5035,11 @@
       <c r="F147" s="40"/>
       <c r="G147" s="53"/>
       <c r="H147" s="61">
-        <v>85</v>
-      </c>
-      <c r="J147" s="69"/>
-      <c r="K147" s="68"/>
-    </row>
-    <row r="148" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J147" s="68"/>
+    </row>
+    <row r="148" spans="1:10">
       <c r="A148" s="28" t="s">
         <v>300</v>
       </c>
@@ -5201,12 +5054,11 @@
       <c r="F148" s="40"/>
       <c r="G148" s="53"/>
       <c r="H148" s="61">
-        <v>95</v>
-      </c>
-      <c r="J148" s="69"/>
-      <c r="K148" s="68"/>
-    </row>
-    <row r="149" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J148" s="68"/>
+    </row>
+    <row r="149" spans="1:10">
       <c r="A149" s="28" t="s">
         <v>302</v>
       </c>
@@ -5221,12 +5073,11 @@
       <c r="F149" s="40"/>
       <c r="G149" s="53"/>
       <c r="H149" s="61">
-        <v>75</v>
-      </c>
-      <c r="J149" s="69"/>
-      <c r="K149" s="68"/>
-    </row>
-    <row r="150" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J149" s="68"/>
+    </row>
+    <row r="150" spans="1:10">
       <c r="A150" s="28" t="s">
         <v>304</v>
       </c>
@@ -5241,12 +5092,11 @@
       <c r="F150" s="40"/>
       <c r="G150" s="53"/>
       <c r="H150" s="61">
-        <v>90</v>
-      </c>
-      <c r="J150" s="69"/>
-      <c r="K150" s="68"/>
-    </row>
-    <row r="151" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J150" s="68"/>
+    </row>
+    <row r="151" spans="1:10">
       <c r="A151" s="28" t="s">
         <v>306</v>
       </c>
@@ -5261,12 +5111,11 @@
       <c r="F151" s="40"/>
       <c r="G151" s="53"/>
       <c r="H151" s="61">
-        <v>85</v>
-      </c>
-      <c r="J151" s="69"/>
-      <c r="K151" s="68"/>
-    </row>
-    <row r="152" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J151" s="68"/>
+    </row>
+    <row r="152" spans="1:10">
       <c r="A152" s="28" t="s">
         <v>308</v>
       </c>
@@ -5281,12 +5130,11 @@
       <c r="F152" s="40"/>
       <c r="G152" s="53"/>
       <c r="H152" s="61">
-        <v>85</v>
-      </c>
-      <c r="J152" s="69"/>
-      <c r="K152" s="68"/>
-    </row>
-    <row r="153" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J152" s="68"/>
+    </row>
+    <row r="153" spans="1:10">
       <c r="A153" s="28" t="s">
         <v>310</v>
       </c>
@@ -5303,10 +5151,9 @@
       <c r="H153" s="61">
         <v>0</v>
       </c>
-      <c r="J153" s="69"/>
-      <c r="K153" s="68"/>
-    </row>
-    <row r="154" spans="1:11">
+      <c r="J153" s="68"/>
+    </row>
+    <row r="154" spans="1:10">
       <c r="A154" s="28" t="s">
         <v>312</v>
       </c>
@@ -5321,12 +5168,11 @@
       <c r="F154" s="40"/>
       <c r="G154" s="53"/>
       <c r="H154" s="61">
-        <v>85</v>
-      </c>
-      <c r="J154" s="69"/>
-      <c r="K154" s="68"/>
-    </row>
-    <row r="155" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J154" s="68"/>
+    </row>
+    <row r="155" spans="1:10">
       <c r="A155" s="28" t="s">
         <v>314</v>
       </c>
@@ -5341,12 +5187,11 @@
       <c r="F155" s="40"/>
       <c r="G155" s="53"/>
       <c r="H155" s="61">
-        <v>65</v>
-      </c>
-      <c r="J155" s="69"/>
-      <c r="K155" s="68"/>
-    </row>
-    <row r="156" spans="1:11">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="J155" s="68"/>
+    </row>
+    <row r="156" spans="1:10">
       <c r="A156" s="28" t="s">
         <v>316</v>
       </c>
@@ -5361,12 +5206,11 @@
       <c r="F156" s="40"/>
       <c r="G156" s="53"/>
       <c r="H156" s="61">
-        <v>80</v>
-      </c>
-      <c r="J156" s="69"/>
-      <c r="K156" s="68"/>
-    </row>
-    <row r="157" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J156" s="68"/>
+    </row>
+    <row r="157" spans="1:10">
       <c r="A157" s="28" t="s">
         <v>318</v>
       </c>
@@ -5381,12 +5225,11 @@
       <c r="F157" s="42"/>
       <c r="G157" s="54"/>
       <c r="H157" s="61">
-        <v>75</v>
-      </c>
-      <c r="J157" s="69"/>
-      <c r="K157" s="68"/>
-    </row>
-    <row r="158" spans="1:11">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="J157" s="68"/>
+    </row>
+    <row r="158" spans="1:10">
       <c r="A158" s="28" t="s">
         <v>320</v>
       </c>
@@ -5401,12 +5244,11 @@
       <c r="F158" s="40"/>
       <c r="G158" s="53"/>
       <c r="H158" s="61">
-        <v>80</v>
-      </c>
-      <c r="J158" s="69"/>
-      <c r="K158" s="68"/>
-    </row>
-    <row r="159" spans="1:11">
+        <v>82.61</v>
+      </c>
+      <c r="J158" s="68"/>
+    </row>
+    <row r="159" spans="1:10">
       <c r="A159" s="28" t="s">
         <v>322</v>
       </c>
@@ -5421,12 +5263,11 @@
       <c r="F159" s="40"/>
       <c r="G159" s="53"/>
       <c r="H159" s="61">
-        <v>80</v>
-      </c>
-      <c r="J159" s="69"/>
-      <c r="K159" s="68"/>
-    </row>
-    <row r="160" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J159" s="68"/>
+    </row>
+    <row r="160" spans="1:10">
       <c r="A160" s="28" t="s">
         <v>324</v>
       </c>
@@ -5441,12 +5282,11 @@
       <c r="F160" s="40"/>
       <c r="G160" s="53"/>
       <c r="H160" s="61">
-        <v>85</v>
-      </c>
-      <c r="J160" s="69"/>
-      <c r="K160" s="68"/>
-    </row>
-    <row r="161" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J160" s="68"/>
+    </row>
+    <row r="161" spans="1:10">
       <c r="A161" s="28" t="s">
         <v>326</v>
       </c>
@@ -5463,10 +5303,9 @@
       <c r="H161" s="61">
         <v>0</v>
       </c>
-      <c r="J161" s="69"/>
-      <c r="K161" s="68"/>
-    </row>
-    <row r="162" spans="1:11">
+      <c r="J161" s="68"/>
+    </row>
+    <row r="162" spans="1:10">
       <c r="A162" s="28" t="s">
         <v>328</v>
       </c>
@@ -5481,12 +5320,11 @@
       <c r="F162" s="40"/>
       <c r="G162" s="53"/>
       <c r="H162" s="61">
-        <v>50</v>
-      </c>
-      <c r="J162" s="69"/>
-      <c r="K162" s="68"/>
-    </row>
-    <row r="163" spans="1:11">
+        <v>43.480000000000004</v>
+      </c>
+      <c r="J162" s="68"/>
+    </row>
+    <row r="163" spans="1:10">
       <c r="A163" s="28" t="s">
         <v>330</v>
       </c>
@@ -5501,12 +5339,11 @@
       <c r="F163" s="40"/>
       <c r="G163" s="53"/>
       <c r="H163" s="61">
-        <v>85</v>
-      </c>
-      <c r="J163" s="69"/>
-      <c r="K163" s="68"/>
-    </row>
-    <row r="164" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J163" s="68"/>
+    </row>
+    <row r="164" spans="1:10">
       <c r="A164" s="28" t="s">
         <v>332</v>
       </c>
@@ -5521,12 +5358,11 @@
       <c r="F164" s="42"/>
       <c r="G164" s="54"/>
       <c r="H164" s="61">
-        <v>100</v>
-      </c>
-      <c r="J164" s="69"/>
-      <c r="K164" s="68"/>
-    </row>
-    <row r="165" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J164" s="68"/>
+    </row>
+    <row r="165" spans="1:10">
       <c r="A165" s="28" t="s">
         <v>334</v>
       </c>
@@ -5541,12 +5377,11 @@
       <c r="F165" s="40"/>
       <c r="G165" s="53"/>
       <c r="H165" s="61">
-        <v>70</v>
-      </c>
-      <c r="J165" s="69"/>
-      <c r="K165" s="68"/>
-    </row>
-    <row r="166" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J165" s="68"/>
+    </row>
+    <row r="166" spans="1:10">
       <c r="A166" s="28" t="s">
         <v>336</v>
       </c>
@@ -5561,12 +5396,11 @@
       <c r="F166" s="40"/>
       <c r="G166" s="53"/>
       <c r="H166" s="61">
-        <v>65</v>
-      </c>
-      <c r="J166" s="69"/>
-      <c r="K166" s="68"/>
-    </row>
-    <row r="167" spans="1:11">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="J166" s="68"/>
+    </row>
+    <row r="167" spans="1:10">
       <c r="A167" s="28" t="s">
         <v>338</v>
       </c>
@@ -5581,12 +5415,11 @@
       <c r="F167" s="40"/>
       <c r="G167" s="53"/>
       <c r="H167" s="61">
-        <v>95</v>
-      </c>
-      <c r="J167" s="69"/>
-      <c r="K167" s="68"/>
-    </row>
-    <row r="168" spans="1:11">
+        <v>95.65</v>
+      </c>
+      <c r="J167" s="68"/>
+    </row>
+    <row r="168" spans="1:10">
       <c r="A168" s="28" t="s">
         <v>340</v>
       </c>
@@ -5601,12 +5434,11 @@
       <c r="F168" s="40"/>
       <c r="G168" s="53"/>
       <c r="H168" s="61">
-        <v>80</v>
-      </c>
-      <c r="J168" s="69"/>
-      <c r="K168" s="68"/>
-    </row>
-    <row r="169" spans="1:11">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="J168" s="68"/>
+    </row>
+    <row r="169" spans="1:10">
       <c r="A169" s="28" t="s">
         <v>342</v>
       </c>
@@ -5621,12 +5453,11 @@
       <c r="F169" s="40"/>
       <c r="G169" s="53"/>
       <c r="H169" s="61">
-        <v>80</v>
-      </c>
-      <c r="J169" s="69"/>
-      <c r="K169" s="68"/>
-    </row>
-    <row r="170" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J169" s="68"/>
+    </row>
+    <row r="170" spans="1:10">
       <c r="A170" s="28" t="s">
         <v>344</v>
       </c>
@@ -5641,12 +5472,11 @@
       <c r="F170" s="40"/>
       <c r="G170" s="53"/>
       <c r="H170" s="61">
-        <v>80</v>
-      </c>
-      <c r="J170" s="69"/>
-      <c r="K170" s="68"/>
-    </row>
-    <row r="171" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J170" s="68"/>
+    </row>
+    <row r="171" spans="1:10">
       <c r="A171" s="28" t="s">
         <v>346</v>
       </c>
@@ -5661,12 +5491,11 @@
       <c r="F171" s="40"/>
       <c r="G171" s="53"/>
       <c r="H171" s="61">
-        <v>65</v>
-      </c>
-      <c r="J171" s="69"/>
-      <c r="K171" s="68"/>
-    </row>
-    <row r="172" spans="1:11">
+        <v>69.569999999999993</v>
+      </c>
+      <c r="J171" s="68"/>
+    </row>
+    <row r="172" spans="1:10">
       <c r="A172" s="28" t="s">
         <v>348</v>
       </c>
@@ -5681,12 +5510,11 @@
       <c r="F172" s="40"/>
       <c r="G172" s="53"/>
       <c r="H172" s="61">
-        <v>5</v>
-      </c>
-      <c r="J172" s="69"/>
-      <c r="K172" s="68"/>
-    </row>
-    <row r="173" spans="1:11">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="J172" s="68"/>
+    </row>
+    <row r="173" spans="1:10">
       <c r="A173" s="28" t="s">
         <v>350</v>
       </c>
@@ -5701,12 +5529,11 @@
       <c r="F173" s="40"/>
       <c r="G173" s="56"/>
       <c r="H173" s="61">
-        <v>45</v>
-      </c>
-      <c r="J173" s="69"/>
-      <c r="K173" s="68"/>
-    </row>
-    <row r="174" spans="1:11">
+        <v>47.83</v>
+      </c>
+      <c r="J173" s="68"/>
+    </row>
+    <row r="174" spans="1:10">
       <c r="A174" s="28" t="s">
         <v>352</v>
       </c>
@@ -5721,12 +5548,11 @@
       <c r="F174" s="40"/>
       <c r="G174" s="51"/>
       <c r="H174" s="61">
-        <v>70</v>
-      </c>
-      <c r="J174" s="69"/>
-      <c r="K174" s="68"/>
-    </row>
-    <row r="175" spans="1:11">
+        <v>65.22</v>
+      </c>
+      <c r="J174" s="68"/>
+    </row>
+    <row r="175" spans="1:10">
       <c r="A175" s="28" t="s">
         <v>354</v>
       </c>
@@ -5741,12 +5567,11 @@
       <c r="F175" s="40"/>
       <c r="G175" s="51"/>
       <c r="H175" s="61">
-        <v>40</v>
-      </c>
-      <c r="J175" s="69"/>
-      <c r="K175" s="68"/>
-    </row>
-    <row r="176" spans="1:11">
+        <v>43.480000000000004</v>
+      </c>
+      <c r="J175" s="68"/>
+    </row>
+    <row r="176" spans="1:10">
       <c r="A176" s="28" t="s">
         <v>356</v>
       </c>
@@ -5761,12 +5586,11 @@
       <c r="F176" s="40"/>
       <c r="G176" s="51"/>
       <c r="H176" s="61">
-        <v>90</v>
-      </c>
-      <c r="J176" s="69"/>
-      <c r="K176" s="68"/>
-    </row>
-    <row r="177" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J176" s="68"/>
+    </row>
+    <row r="177" spans="1:10">
       <c r="A177" s="28" t="s">
         <v>358</v>
       </c>
@@ -5781,12 +5605,11 @@
       <c r="F177" s="40"/>
       <c r="G177" s="51"/>
       <c r="H177" s="61">
-        <v>80</v>
-      </c>
-      <c r="J177" s="69"/>
-      <c r="K177" s="68"/>
-    </row>
-    <row r="178" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J177" s="68"/>
+    </row>
+    <row r="178" spans="1:10">
       <c r="A178" s="28" t="s">
         <v>360</v>
       </c>
@@ -5801,12 +5624,11 @@
       <c r="F178" s="40"/>
       <c r="G178" s="51"/>
       <c r="H178" s="61">
-        <v>90</v>
-      </c>
-      <c r="J178" s="69"/>
-      <c r="K178" s="68"/>
-    </row>
-    <row r="179" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J178" s="68"/>
+    </row>
+    <row r="179" spans="1:10">
       <c r="A179" s="28" t="s">
         <v>362</v>
       </c>
@@ -5821,12 +5643,11 @@
       <c r="F179" s="43"/>
       <c r="G179" s="58"/>
       <c r="H179" s="61">
-        <v>45</v>
-      </c>
-      <c r="J179" s="69"/>
-      <c r="K179" s="68"/>
-    </row>
-    <row r="180" spans="1:11">
+        <v>47.83</v>
+      </c>
+      <c r="J179" s="68"/>
+    </row>
+    <row r="180" spans="1:10">
       <c r="A180" s="28" t="s">
         <v>364</v>
       </c>
@@ -5843,10 +5664,9 @@
       <c r="H180" s="61">
         <v>0</v>
       </c>
-      <c r="J180" s="69"/>
-      <c r="K180" s="68"/>
-    </row>
-    <row r="181" spans="1:11">
+      <c r="J180" s="68"/>
+    </row>
+    <row r="181" spans="1:10">
       <c r="A181" s="28" t="s">
         <v>366</v>
       </c>
@@ -5861,12 +5681,11 @@
       <c r="F181" s="44"/>
       <c r="G181" s="59"/>
       <c r="H181" s="61">
-        <v>70</v>
-      </c>
-      <c r="J181" s="69"/>
-      <c r="K181" s="68"/>
-    </row>
-    <row r="182" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J181" s="68"/>
+    </row>
+    <row r="182" spans="1:10">
       <c r="A182" s="28" t="s">
         <v>368</v>
       </c>
@@ -5881,12 +5700,11 @@
       <c r="F182" s="44"/>
       <c r="G182" s="59"/>
       <c r="H182" s="61">
-        <v>45</v>
-      </c>
-      <c r="J182" s="69"/>
-      <c r="K182" s="68"/>
-    </row>
-    <row r="183" spans="1:11">
+        <v>43.480000000000004</v>
+      </c>
+      <c r="J182" s="68"/>
+    </row>
+    <row r="183" spans="1:10">
       <c r="A183" s="28" t="s">
         <v>370</v>
       </c>
@@ -5901,12 +5719,11 @@
       <c r="F183" s="44"/>
       <c r="G183" s="59"/>
       <c r="H183" s="61">
-        <v>40</v>
-      </c>
-      <c r="J183" s="69"/>
-      <c r="K183" s="68"/>
-    </row>
-    <row r="184" spans="1:11">
+        <v>43.480000000000004</v>
+      </c>
+      <c r="J183" s="68"/>
+    </row>
+    <row r="184" spans="1:10">
       <c r="A184" s="28" t="s">
         <v>372</v>
       </c>
@@ -5921,12 +5738,11 @@
       <c r="F184" s="44"/>
       <c r="G184" s="59"/>
       <c r="H184" s="61">
-        <v>75</v>
-      </c>
-      <c r="J184" s="69"/>
-      <c r="K184" s="68"/>
-    </row>
-    <row r="185" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J184" s="68"/>
+    </row>
+    <row r="185" spans="1:10">
       <c r="A185" s="28" t="s">
         <v>374</v>
       </c>
@@ -5941,12 +5757,11 @@
       <c r="F185" s="44"/>
       <c r="G185" s="59"/>
       <c r="H185" s="61">
-        <v>30</v>
-      </c>
-      <c r="J185" s="69"/>
-      <c r="K185" s="68"/>
-    </row>
-    <row r="186" spans="1:11">
+        <v>30.43</v>
+      </c>
+      <c r="J185" s="68"/>
+    </row>
+    <row r="186" spans="1:10">
       <c r="A186" s="28" t="s">
         <v>376</v>
       </c>
@@ -5961,12 +5776,11 @@
       <c r="F186" s="44"/>
       <c r="G186" s="59"/>
       <c r="H186" s="61">
-        <v>85</v>
-      </c>
-      <c r="J186" s="69"/>
-      <c r="K186" s="68"/>
-    </row>
-    <row r="187" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J186" s="68"/>
+    </row>
+    <row r="187" spans="1:10">
       <c r="A187" s="28" t="s">
         <v>378</v>
       </c>
@@ -5981,12 +5795,11 @@
       <c r="F187" s="44"/>
       <c r="G187" s="59"/>
       <c r="H187" s="61">
-        <v>85</v>
-      </c>
-      <c r="J187" s="69"/>
-      <c r="K187" s="68"/>
-    </row>
-    <row r="188" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J187" s="68"/>
+    </row>
+    <row r="188" spans="1:10">
       <c r="A188" s="28" t="s">
         <v>380</v>
       </c>
@@ -6003,10 +5816,9 @@
       <c r="H188" s="61">
         <v>0</v>
       </c>
-      <c r="J188" s="69"/>
-      <c r="K188" s="68"/>
-    </row>
-    <row r="189" spans="1:11">
+      <c r="J188" s="68"/>
+    </row>
+    <row r="189" spans="1:10">
       <c r="A189" s="28" t="s">
         <v>382</v>
       </c>
@@ -6023,10 +5835,9 @@
       <c r="H189" s="61">
         <v>100</v>
       </c>
-      <c r="J189" s="69"/>
-      <c r="K189" s="68"/>
-    </row>
-    <row r="190" spans="1:11">
+      <c r="J189" s="68"/>
+    </row>
+    <row r="190" spans="1:10">
       <c r="A190" s="28" t="s">
         <v>384</v>
       </c>
@@ -6041,12 +5852,11 @@
       <c r="F190" s="44"/>
       <c r="G190" s="59"/>
       <c r="H190" s="61">
-        <v>95</v>
-      </c>
-      <c r="J190" s="69"/>
-      <c r="K190" s="68"/>
-    </row>
-    <row r="191" spans="1:11">
+        <v>95.65</v>
+      </c>
+      <c r="J190" s="68"/>
+    </row>
+    <row r="191" spans="1:10">
       <c r="A191" s="28" t="s">
         <v>386</v>
       </c>
@@ -6061,12 +5871,11 @@
       <c r="F191" s="44"/>
       <c r="G191" s="59"/>
       <c r="H191" s="61">
-        <v>75</v>
-      </c>
-      <c r="J191" s="69"/>
-      <c r="K191" s="68"/>
-    </row>
-    <row r="192" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J191" s="68"/>
+    </row>
+    <row r="192" spans="1:10">
       <c r="A192" s="28" t="s">
         <v>388</v>
       </c>
@@ -6083,10 +5892,9 @@
       <c r="H192" s="61">
         <v>0</v>
       </c>
-      <c r="J192" s="69"/>
-      <c r="K192" s="68"/>
-    </row>
-    <row r="193" spans="1:11">
+      <c r="J192" s="68"/>
+    </row>
+    <row r="193" spans="1:10">
       <c r="A193" s="28" t="s">
         <v>390</v>
       </c>
@@ -6101,12 +5909,11 @@
       <c r="F193" s="44"/>
       <c r="G193" s="59"/>
       <c r="H193" s="61">
-        <v>90</v>
-      </c>
-      <c r="J193" s="69"/>
-      <c r="K193" s="68"/>
-    </row>
-    <row r="194" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J193" s="68"/>
+    </row>
+    <row r="194" spans="1:10">
       <c r="A194" s="28" t="s">
         <v>392</v>
       </c>
@@ -6121,12 +5928,11 @@
       <c r="F194" s="44"/>
       <c r="G194" s="59"/>
       <c r="H194" s="61">
-        <v>90</v>
-      </c>
-      <c r="J194" s="69"/>
-      <c r="K194" s="68"/>
-    </row>
-    <row r="195" spans="1:11">
+        <v>86.960000000000008</v>
+      </c>
+      <c r="J194" s="68"/>
+    </row>
+    <row r="195" spans="1:10">
       <c r="A195" s="28" t="s">
         <v>394</v>
       </c>
@@ -6141,12 +5947,11 @@
       <c r="F195" s="44"/>
       <c r="G195" s="59"/>
       <c r="H195" s="61">
-        <v>75</v>
-      </c>
-      <c r="J195" s="69"/>
-      <c r="K195" s="68"/>
-    </row>
-    <row r="196" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J195" s="68"/>
+    </row>
+    <row r="196" spans="1:10">
       <c r="A196" s="28" t="s">
         <v>396</v>
       </c>
@@ -6161,12 +5966,11 @@
       <c r="F196" s="44"/>
       <c r="G196" s="59"/>
       <c r="H196" s="61">
-        <v>100</v>
-      </c>
-      <c r="J196" s="69"/>
-      <c r="K196" s="68"/>
-    </row>
-    <row r="197" spans="1:11">
+        <v>95.65</v>
+      </c>
+      <c r="J196" s="68"/>
+    </row>
+    <row r="197" spans="1:10">
       <c r="A197" s="28" t="s">
         <v>398</v>
       </c>
@@ -6181,12 +5985,11 @@
       <c r="F197" s="44"/>
       <c r="G197" s="59"/>
       <c r="H197" s="61">
-        <v>75</v>
-      </c>
-      <c r="J197" s="69"/>
-      <c r="K197" s="68"/>
-    </row>
-    <row r="198" spans="1:11">
+        <v>78.259999999999991</v>
+      </c>
+      <c r="J197" s="68"/>
+    </row>
+    <row r="198" spans="1:10">
       <c r="A198" s="28" t="s">
         <v>400</v>
       </c>
@@ -6201,12 +6004,11 @@
       <c r="F198" s="44"/>
       <c r="G198" s="59"/>
       <c r="H198" s="61">
-        <v>95</v>
-      </c>
-      <c r="J198" s="69"/>
-      <c r="K198" s="68"/>
-    </row>
-    <row r="199" spans="1:11">
+        <v>91.3</v>
+      </c>
+      <c r="J198" s="68"/>
+    </row>
+    <row r="199" spans="1:10">
       <c r="A199" s="62" t="s">
         <v>404</v>
       </c>
@@ -6221,12 +6023,11 @@
       <c r="F199" s="44"/>
       <c r="G199" s="60"/>
       <c r="H199" s="61">
-        <v>70</v>
-      </c>
-      <c r="J199" s="69"/>
-      <c r="K199" s="68"/>
-    </row>
-    <row r="200" spans="1:11">
+        <v>73.91</v>
+      </c>
+      <c r="J199" s="68"/>
+    </row>
+    <row r="200" spans="1:10">
       <c r="A200" s="49" t="s">
         <v>402</v>
       </c>
@@ -6241,12 +6042,11 @@
       <c r="F200" s="44"/>
       <c r="G200" s="24"/>
       <c r="H200" s="61">
-        <v>55.000000000000007</v>
-      </c>
-      <c r="J200" s="69"/>
-      <c r="K200" s="68"/>
-    </row>
-    <row r="201" spans="1:11" ht="15.75">
+        <v>60.870000000000005</v>
+      </c>
+      <c r="J200" s="68"/>
+    </row>
+    <row r="201" spans="1:10" ht="15.75">
       <c r="A201" s="66" t="s">
         <v>407</v>
       </c>
@@ -6260,7 +6060,7 @@
       <c r="G201" s="24"/>
       <c r="H201" s="13"/>
     </row>
-    <row r="202" spans="1:11" ht="15.75">
+    <row r="202" spans="1:10" ht="15.75">
       <c r="A202" s="67" t="s">
         <v>408</v>
       </c>
@@ -6274,7 +6074,7 @@
       <c r="G202" s="25"/>
       <c r="H202" s="13"/>
     </row>
-    <row r="203" spans="1:11" ht="15.75">
+    <row r="203" spans="1:10" ht="15.75">
       <c r="A203" s="67" t="s">
         <v>409</v>
       </c>
@@ -6288,7 +6088,7 @@
       <c r="G203" s="27"/>
       <c r="H203" s="13"/>
     </row>
-    <row r="204" spans="1:11" ht="15.75">
+    <row r="204" spans="1:10" ht="15.75">
       <c r="A204" s="67" t="s">
         <v>410</v>
       </c>
@@ -6302,7 +6102,7 @@
       <c r="G204" s="27"/>
       <c r="H204" s="13"/>
     </row>
-    <row r="205" spans="1:11" ht="15.75">
+    <row r="205" spans="1:10" ht="15.75">
       <c r="A205" s="67" t="s">
         <v>411</v>
       </c>
@@ -6316,7 +6116,7 @@
       <c r="G205" s="27"/>
       <c r="H205" s="13"/>
     </row>
-    <row r="206" spans="1:11" ht="15.75">
+    <row r="206" spans="1:10" ht="15.75">
       <c r="A206" s="67" t="s">
         <v>412</v>
       </c>
@@ -6330,7 +6130,7 @@
       <c r="G206" s="27"/>
       <c r="H206" s="13"/>
     </row>
-    <row r="207" spans="1:11" ht="15.75">
+    <row r="207" spans="1:10" ht="15.75">
       <c r="A207" s="67" t="s">
         <v>413</v>
       </c>
@@ -6344,7 +6144,7 @@
       <c r="G207" s="27"/>
       <c r="H207" s="14"/>
     </row>
-    <row r="208" spans="1:11" ht="15.75">
+    <row r="208" spans="1:10" ht="15.75">
       <c r="A208" s="67" t="s">
         <v>414</v>
       </c>
@@ -6545,6 +6345,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -6688,7 +6494,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6697,25 +6503,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -6729,4 +6517,16 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>
--- a/MC3020_E24.xlsx
+++ b/MC3020_E24.xlsx
@@ -2230,7 +2230,6 @@
     <col min="7" max="7" width="15.5703125" customWidth="1"/>
     <col min="8" max="8" width="15.5703125" style="9" customWidth="1"/>
     <col min="10" max="10" width="12.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" customHeight="1">
@@ -2276,7 +2275,7 @@
       <c r="F2" s="26"/>
       <c r="G2" s="38"/>
       <c r="H2" s="48">
-        <v>65.22</v>
+        <v>65.217391300000003</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2296,7 +2295,7 @@
       <c r="F3" s="27"/>
       <c r="G3" s="39"/>
       <c r="H3" s="48">
-        <v>86.960000000000008</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2316,7 +2315,7 @@
       <c r="F4" s="27"/>
       <c r="G4" s="40"/>
       <c r="H4" s="48">
-        <v>73.91</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2336,7 +2335,7 @@
       <c r="F5" s="27"/>
       <c r="G5" s="40"/>
       <c r="H5" s="48">
-        <v>30.43</v>
+        <v>30.434782599999998</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2356,7 +2355,7 @@
       <c r="F6" s="27"/>
       <c r="G6" s="40"/>
       <c r="H6" s="48">
-        <v>43.480000000000004</v>
+        <v>43.478260899999995</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2376,7 +2375,7 @@
       <c r="F7" s="27"/>
       <c r="G7" s="40"/>
       <c r="H7" s="48">
-        <v>82.61</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2396,7 +2395,7 @@
       <c r="F8" s="27"/>
       <c r="G8" s="40"/>
       <c r="H8" s="48">
-        <v>86.960000000000008</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2416,7 +2415,7 @@
       <c r="F9" s="27"/>
       <c r="G9" s="40"/>
       <c r="H9" s="48">
-        <v>78.259999999999991</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2436,7 +2435,7 @@
       <c r="F10" s="27"/>
       <c r="G10" s="40"/>
       <c r="H10" s="48">
-        <v>91.3</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2456,7 +2455,7 @@
       <c r="F11" s="27"/>
       <c r="G11" s="40"/>
       <c r="H11" s="48">
-        <v>82.61</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2476,7 +2475,7 @@
       <c r="F12" s="27"/>
       <c r="G12" s="40"/>
       <c r="H12" s="48">
-        <v>60.870000000000005</v>
+        <v>60.869565199999997</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2496,7 +2495,7 @@
       <c r="F13" s="27"/>
       <c r="G13" s="40"/>
       <c r="H13" s="48">
-        <v>90.91</v>
+        <v>90.909090899999995</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2516,7 +2515,7 @@
       <c r="F14" s="27"/>
       <c r="G14" s="40"/>
       <c r="H14" s="48">
-        <v>73.91</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2536,7 +2535,7 @@
       <c r="F15" s="27"/>
       <c r="G15" s="40"/>
       <c r="H15" s="48">
-        <v>78.259999999999991</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2556,7 +2555,7 @@
       <c r="F16" s="25"/>
       <c r="G16" s="41"/>
       <c r="H16" s="48">
-        <v>0</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2576,7 +2575,7 @@
       <c r="F17" s="27"/>
       <c r="G17" s="40"/>
       <c r="H17" s="48">
-        <v>82.61</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2596,7 +2595,7 @@
       <c r="F18" s="27"/>
       <c r="G18" s="40"/>
       <c r="H18" s="48">
-        <v>86.960000000000008</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2616,7 +2615,7 @@
       <c r="F19" s="27"/>
       <c r="G19" s="40"/>
       <c r="H19" s="48">
-        <v>78.259999999999991</v>
+        <v>69.565217399999995</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2636,7 +2635,7 @@
       <c r="F20" s="27"/>
       <c r="G20" s="40"/>
       <c r="H20" s="48">
-        <v>69.569999999999993</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2656,7 +2655,7 @@
       <c r="F21" s="27"/>
       <c r="G21" s="40"/>
       <c r="H21" s="48">
-        <v>82.61</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2676,7 +2675,7 @@
       <c r="F22" s="27"/>
       <c r="G22" s="40"/>
       <c r="H22" s="48">
-        <v>82.61</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2696,7 +2695,7 @@
       <c r="F23" s="27"/>
       <c r="G23" s="40"/>
       <c r="H23" s="48">
-        <v>86.960000000000008</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2716,7 +2715,7 @@
       <c r="F24" s="27"/>
       <c r="G24" s="40"/>
       <c r="H24" s="48">
-        <v>82.61</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2736,7 +2735,7 @@
       <c r="F25" s="27"/>
       <c r="G25" s="40"/>
       <c r="H25" s="48">
-        <v>82.61</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2756,7 +2755,7 @@
       <c r="F26" s="27"/>
       <c r="G26" s="40"/>
       <c r="H26" s="48">
-        <v>91.3</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2776,7 +2775,7 @@
       <c r="F27" s="27"/>
       <c r="G27" s="40"/>
       <c r="H27" s="48">
-        <v>82.61</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2796,7 +2795,7 @@
       <c r="F28" s="27"/>
       <c r="G28" s="40"/>
       <c r="H28" s="48">
-        <v>91.3</v>
+        <v>95.652173900000008</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2816,7 +2815,7 @@
       <c r="F29" s="27"/>
       <c r="G29" s="40"/>
       <c r="H29" s="48">
-        <v>95.65</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2836,7 +2835,7 @@
       <c r="F30" s="27"/>
       <c r="G30" s="40"/>
       <c r="H30" s="48">
-        <v>73.91</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2856,7 +2855,7 @@
       <c r="F31" s="27"/>
       <c r="G31" s="42"/>
       <c r="H31" s="48">
-        <v>86.960000000000008</v>
+        <v>47.826087000000001</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2876,7 +2875,7 @@
       <c r="F32" s="27"/>
       <c r="G32" s="40"/>
       <c r="H32" s="48">
-        <v>47.83</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2896,7 +2895,7 @@
       <c r="F33" s="27"/>
       <c r="G33" s="40"/>
       <c r="H33" s="48">
-        <v>73.91</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2916,7 +2915,7 @@
       <c r="F34" s="27"/>
       <c r="G34" s="40"/>
       <c r="H34" s="48">
-        <v>91.3</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2936,7 +2935,7 @@
       <c r="F35" s="27"/>
       <c r="G35" s="40"/>
       <c r="H35" s="48">
-        <v>82.61</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2956,7 +2955,7 @@
       <c r="F36" s="27"/>
       <c r="G36" s="40"/>
       <c r="H36" s="48">
-        <v>86.960000000000008</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2976,7 +2975,7 @@
       <c r="F37" s="27"/>
       <c r="G37" s="40"/>
       <c r="H37" s="48">
-        <v>86.960000000000008</v>
+        <v>69.565217399999995</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2996,7 +2995,7 @@
       <c r="F38" s="27"/>
       <c r="G38" s="40"/>
       <c r="H38" s="48">
-        <v>69.569999999999993</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -3016,7 +3015,7 @@
       <c r="F39" s="27"/>
       <c r="G39" s="40"/>
       <c r="H39" s="48">
-        <v>82.61</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -3036,7 +3035,7 @@
       <c r="F40" s="27"/>
       <c r="G40" s="40"/>
       <c r="H40" s="48">
-        <v>86.960000000000008</v>
+        <v>52.173913000000006</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -3056,7 +3055,7 @@
       <c r="F41" s="27"/>
       <c r="G41" s="40"/>
       <c r="H41" s="48">
-        <v>52.17</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -3076,7 +3075,7 @@
       <c r="F42" s="27"/>
       <c r="G42" s="40"/>
       <c r="H42" s="48">
-        <v>73.91</v>
+        <v>56.521739100000005</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -3096,7 +3095,7 @@
       <c r="F43" s="27"/>
       <c r="G43" s="40"/>
       <c r="H43" s="48">
-        <v>56.52</v>
+        <v>60.869565199999997</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -3116,7 +3115,7 @@
       <c r="F44" s="27"/>
       <c r="G44" s="40"/>
       <c r="H44" s="48">
-        <v>60.870000000000005</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -3136,7 +3135,7 @@
       <c r="F45" s="27"/>
       <c r="G45" s="40"/>
       <c r="H45" s="48">
-        <v>82.61</v>
+        <v>56.521739100000005</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -3156,7 +3155,7 @@
       <c r="F46" s="27"/>
       <c r="G46" s="40"/>
       <c r="H46" s="48">
-        <v>56.52</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -3176,7 +3175,7 @@
       <c r="F47" s="27"/>
       <c r="G47" s="40"/>
       <c r="H47" s="48">
-        <v>78.259999999999991</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -3196,7 +3195,7 @@
       <c r="F48" s="27"/>
       <c r="G48" s="42"/>
       <c r="H48" s="48">
-        <v>86.960000000000008</v>
+        <v>21.739130400000001</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -3216,7 +3215,7 @@
       <c r="F49" s="27"/>
       <c r="G49" s="40"/>
       <c r="H49" s="48">
-        <v>21.740000000000002</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -3236,7 +3235,7 @@
       <c r="F50" s="27"/>
       <c r="G50" s="40"/>
       <c r="H50" s="48">
-        <v>86.960000000000008</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -3256,7 +3255,7 @@
       <c r="F51" s="27"/>
       <c r="G51" s="40"/>
       <c r="H51" s="48">
-        <v>82.61</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -3276,7 +3275,7 @@
       <c r="F52" s="27"/>
       <c r="G52" s="40"/>
       <c r="H52" s="48">
-        <v>78.259999999999991</v>
+        <v>47.826087000000001</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -3296,7 +3295,7 @@
       <c r="F53" s="27"/>
       <c r="G53" s="40"/>
       <c r="H53" s="48">
-        <v>47.83</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -3316,7 +3315,7 @@
       <c r="F54" s="27"/>
       <c r="G54" s="40"/>
       <c r="H54" s="48">
-        <v>73.91</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -3336,7 +3335,7 @@
       <c r="F55" s="27"/>
       <c r="G55" s="42"/>
       <c r="H55" s="48">
-        <v>91.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -3356,7 +3355,7 @@
       <c r="F56" s="27"/>
       <c r="G56" s="40"/>
       <c r="H56" s="48">
-        <v>100</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -3376,7 +3375,7 @@
       <c r="F57" s="27"/>
       <c r="G57" s="40"/>
       <c r="H57" s="48">
-        <v>91.3</v>
+        <v>60.869565199999997</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -3396,7 +3395,7 @@
       <c r="F58" s="27"/>
       <c r="G58" s="40"/>
       <c r="H58" s="48">
-        <v>60.870000000000005</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -3416,10 +3415,10 @@
       <c r="F59" s="27"/>
       <c r="G59" s="40"/>
       <c r="H59" s="48">
-        <v>86.960000000000008</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>82.608695699999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="14.25" customHeight="1">
       <c r="A60" s="16" t="s">
         <v>125</v>
       </c>
@@ -3436,7 +3435,7 @@
       <c r="F60" s="28"/>
       <c r="G60" s="41"/>
       <c r="H60" s="48">
-        <v>82.61</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -3456,7 +3455,7 @@
       <c r="F61" s="27"/>
       <c r="G61" s="40"/>
       <c r="H61" s="48">
-        <v>73.91</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -3476,7 +3475,7 @@
       <c r="F62" s="27"/>
       <c r="G62" s="40"/>
       <c r="H62" s="48">
-        <v>91.3</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -3496,7 +3495,7 @@
       <c r="F63" s="27"/>
       <c r="G63" s="40"/>
       <c r="H63" s="48">
-        <v>78.259999999999991</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -3516,7 +3515,7 @@
       <c r="F64" s="27"/>
       <c r="G64" s="40"/>
       <c r="H64" s="48">
-        <v>100</v>
+        <v>95.652173900000008</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -3536,7 +3535,7 @@
       <c r="F65" s="27"/>
       <c r="G65" s="40"/>
       <c r="H65" s="48">
-        <v>95.65</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -3556,7 +3555,7 @@
       <c r="F66" s="27"/>
       <c r="G66" s="40"/>
       <c r="H66" s="48">
-        <v>82.61</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -3576,7 +3575,7 @@
       <c r="F67" s="27"/>
       <c r="G67" s="40"/>
       <c r="H67" s="48">
-        <v>86.960000000000008</v>
+        <v>60.869565199999997</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -3596,7 +3595,7 @@
       <c r="F68" s="27"/>
       <c r="G68" s="42"/>
       <c r="H68" s="48">
-        <v>60.870000000000005</v>
+        <v>52.173913000000006</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -3616,7 +3615,7 @@
       <c r="F69" s="27"/>
       <c r="G69" s="40"/>
       <c r="H69" s="48">
-        <v>52.17</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -3636,7 +3635,7 @@
       <c r="F70" s="27"/>
       <c r="G70" s="40"/>
       <c r="H70" s="48">
-        <v>73.91</v>
+        <v>60.869565199999997</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -3656,7 +3655,7 @@
       <c r="F71" s="27"/>
       <c r="G71" s="40"/>
       <c r="H71" s="48">
-        <v>60.870000000000005</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -3676,7 +3675,7 @@
       <c r="F72" s="27"/>
       <c r="G72" s="40"/>
       <c r="H72" s="48">
-        <v>73.91</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -3696,7 +3695,7 @@
       <c r="F73" s="27"/>
       <c r="G73" s="42"/>
       <c r="H73" s="48">
-        <v>86.960000000000008</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -3716,7 +3715,7 @@
       <c r="F74" s="27"/>
       <c r="G74" s="40"/>
       <c r="H74" s="48">
-        <v>91.3</v>
+        <v>52.173913000000006</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -3736,7 +3735,7 @@
       <c r="F75" s="27"/>
       <c r="G75" s="40"/>
       <c r="H75" s="48">
-        <v>0</v>
+        <v>52.173913000000006</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -3756,7 +3755,7 @@
       <c r="F76" s="27"/>
       <c r="G76" s="40"/>
       <c r="H76" s="48">
-        <v>52.17</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -3776,7 +3775,7 @@
       <c r="F77" s="27"/>
       <c r="G77" s="40"/>
       <c r="H77" s="48">
-        <v>52.17</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -3796,7 +3795,7 @@
       <c r="F78" s="27"/>
       <c r="G78" s="40"/>
       <c r="H78" s="48">
-        <v>78.259999999999991</v>
+        <v>43.478260899999995</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -3816,7 +3815,7 @@
       <c r="F79" s="27"/>
       <c r="G79" s="40"/>
       <c r="H79" s="48">
-        <v>0</v>
+        <v>69.565217399999995</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -3836,7 +3835,7 @@
       <c r="F80" s="27"/>
       <c r="G80" s="40"/>
       <c r="H80" s="48">
-        <v>86.960000000000008</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -3856,7 +3855,7 @@
       <c r="F81" s="27"/>
       <c r="G81" s="40"/>
       <c r="H81" s="48">
-        <v>43.480000000000004</v>
+        <v>95.652173900000008</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -3876,7 +3875,7 @@
       <c r="F82" s="27"/>
       <c r="G82" s="40"/>
       <c r="H82" s="48">
-        <v>69.569999999999993</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -3896,7 +3895,7 @@
       <c r="F83" s="27"/>
       <c r="G83" s="42"/>
       <c r="H83" s="48">
-        <v>82.61</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -3916,7 +3915,7 @@
       <c r="F84" s="27"/>
       <c r="G84" s="40"/>
       <c r="H84" s="48">
-        <v>95.65</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -3936,7 +3935,7 @@
       <c r="F85" s="28"/>
       <c r="G85" s="41"/>
       <c r="H85" s="48">
-        <v>82.61</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -3956,7 +3955,7 @@
       <c r="F86" s="27"/>
       <c r="G86" s="40"/>
       <c r="H86" s="48">
-        <v>86.960000000000008</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -3976,7 +3975,7 @@
       <c r="F87" s="27"/>
       <c r="G87" s="40"/>
       <c r="H87" s="48">
-        <v>78.259999999999991</v>
+        <v>56.521739100000005</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -3996,7 +3995,7 @@
       <c r="F88" s="27"/>
       <c r="G88" s="40"/>
       <c r="H88" s="48">
-        <v>78.259999999999991</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -4016,7 +4015,7 @@
       <c r="F89" s="27"/>
       <c r="G89" s="40"/>
       <c r="H89" s="48">
-        <v>78.259999999999991</v>
+        <v>69.565217399999995</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -4036,7 +4035,7 @@
       <c r="F90" s="27"/>
       <c r="G90" s="42"/>
       <c r="H90" s="48">
-        <v>56.52</v>
+        <v>52.173913000000006</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -4056,7 +4055,7 @@
       <c r="F91" s="27"/>
       <c r="G91" s="40"/>
       <c r="H91" s="48">
-        <v>86.960000000000008</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -4076,7 +4075,7 @@
       <c r="F92" s="27"/>
       <c r="G92" s="40"/>
       <c r="H92" s="48">
-        <v>69.569999999999993</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -4096,7 +4095,7 @@
       <c r="F93" s="27"/>
       <c r="G93" s="40"/>
       <c r="H93" s="48">
-        <v>52.17</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -4116,7 +4115,7 @@
       <c r="F94" s="27"/>
       <c r="G94" s="40"/>
       <c r="H94" s="48">
-        <v>82.61</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -4136,7 +4135,7 @@
       <c r="F95" s="27"/>
       <c r="G95" s="40"/>
       <c r="H95" s="48">
-        <v>8.6999999999999993</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -4156,7 +4155,7 @@
       <c r="F96" s="28"/>
       <c r="G96" s="41"/>
       <c r="H96" s="48">
-        <v>86.960000000000008</v>
+        <v>65.217391300000003</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -4176,7 +4175,7 @@
       <c r="F97" s="27"/>
       <c r="G97" s="40"/>
       <c r="H97" s="48">
-        <v>91.3</v>
+        <v>56.521739100000005</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -4196,7 +4195,7 @@
       <c r="F98" s="27"/>
       <c r="G98" s="40"/>
       <c r="H98" s="48">
-        <v>73.91</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -4216,7 +4215,7 @@
       <c r="F99" s="27"/>
       <c r="G99" s="42"/>
       <c r="H99" s="48">
-        <v>82.61</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -4236,7 +4235,7 @@
       <c r="F100" s="27"/>
       <c r="G100" s="40"/>
       <c r="H100" s="48">
-        <v>65.22</v>
+        <v>95.652173900000008</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -4256,7 +4255,7 @@
       <c r="F101" s="27"/>
       <c r="G101" s="40"/>
       <c r="H101" s="48">
-        <v>56.52</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -4276,7 +4275,7 @@
       <c r="F102" s="27"/>
       <c r="G102" s="40"/>
       <c r="H102" s="48">
-        <v>0</v>
+        <v>95.652173900000008</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -4296,7 +4295,7 @@
       <c r="F103" s="27"/>
       <c r="G103" s="40"/>
       <c r="H103" s="48">
-        <v>82.61</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -4316,7 +4315,7 @@
       <c r="F104" s="27"/>
       <c r="G104" s="40"/>
       <c r="H104" s="48">
-        <v>86.960000000000008</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -4336,7 +4335,7 @@
       <c r="F105" s="27"/>
       <c r="G105" s="40"/>
       <c r="H105" s="48">
-        <v>95.65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -4356,7 +4355,7 @@
       <c r="F106" s="27"/>
       <c r="G106" s="40"/>
       <c r="H106" s="48">
-        <v>82.61</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -4376,7 +4375,7 @@
       <c r="F107" s="27"/>
       <c r="G107" s="40"/>
       <c r="H107" s="48">
-        <v>95.65</v>
+        <v>69.565217399999995</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -4396,7 +4395,7 @@
       <c r="F108" s="27"/>
       <c r="G108" s="40"/>
       <c r="H108" s="48">
-        <v>82.61</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -4416,7 +4415,7 @@
       <c r="F109" s="27"/>
       <c r="G109" s="40"/>
       <c r="H109" s="48">
-        <v>82.61</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -4436,7 +4435,7 @@
       <c r="F110" s="27"/>
       <c r="G110" s="40"/>
       <c r="H110" s="48">
-        <v>100</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -4456,7 +4455,7 @@
       <c r="F111" s="27"/>
       <c r="G111" s="40"/>
       <c r="H111" s="48">
-        <v>100</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -4476,7 +4475,7 @@
       <c r="F112" s="27"/>
       <c r="G112" s="40"/>
       <c r="H112" s="48">
-        <v>69.569999999999993</v>
+        <v>69.565217399999995</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -4496,7 +4495,7 @@
       <c r="F113" s="27"/>
       <c r="G113" s="40"/>
       <c r="H113" s="48">
-        <v>86.960000000000008</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -4516,7 +4515,7 @@
       <c r="F114" s="27"/>
       <c r="G114" s="40"/>
       <c r="H114" s="48">
-        <v>78.259999999999991</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -4536,7 +4535,7 @@
       <c r="F115" s="27"/>
       <c r="G115" s="40"/>
       <c r="H115" s="48">
-        <v>73.91</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -4556,7 +4555,7 @@
       <c r="F116" s="27"/>
       <c r="G116" s="40"/>
       <c r="H116" s="48">
-        <v>86.960000000000008</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.25" customHeight="1">
@@ -4576,7 +4575,7 @@
       <c r="F117" s="27"/>
       <c r="G117" s="40"/>
       <c r="H117" s="48">
-        <v>69.569999999999993</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -4596,7 +4595,7 @@
       <c r="F118" s="27"/>
       <c r="G118" s="40"/>
       <c r="H118" s="48">
-        <v>91.3</v>
+        <v>95.652173900000008</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -4616,7 +4615,7 @@
       <c r="F119" s="27"/>
       <c r="G119" s="40"/>
       <c r="H119" s="48">
-        <v>82.61</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -4636,7 +4635,7 @@
       <c r="F120" s="27"/>
       <c r="G120" s="40"/>
       <c r="H120" s="48">
-        <v>86.960000000000008</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -4656,7 +4655,7 @@
       <c r="F121" s="27"/>
       <c r="G121" s="40"/>
       <c r="H121" s="48">
-        <v>78.259999999999991</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -4676,7 +4675,7 @@
       <c r="F122" s="27"/>
       <c r="G122" s="40"/>
       <c r="H122" s="48">
-        <v>78.259999999999991</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -4696,7 +4695,7 @@
       <c r="F123" s="27"/>
       <c r="G123" s="40"/>
       <c r="H123" s="48">
-        <v>95.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -4716,7 +4715,7 @@
       <c r="F124" s="27"/>
       <c r="G124" s="40"/>
       <c r="H124" s="48">
-        <v>86.960000000000008</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -4736,7 +4735,7 @@
       <c r="F125" s="27"/>
       <c r="G125" s="40"/>
       <c r="H125" s="48">
-        <v>0</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -4756,7 +4755,7 @@
       <c r="F126" s="27"/>
       <c r="G126" s="40"/>
       <c r="H126" s="48">
-        <v>78.259999999999991</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -4776,7 +4775,7 @@
       <c r="F127" s="27"/>
       <c r="G127" s="40"/>
       <c r="H127" s="48">
-        <v>73.91</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -4796,7 +4795,7 @@
       <c r="F128" s="27"/>
       <c r="G128" s="40"/>
       <c r="H128" s="48">
-        <v>82.61</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -4816,7 +4815,7 @@
       <c r="F129" s="27"/>
       <c r="G129" s="40"/>
       <c r="H129" s="48">
-        <v>0</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -4836,7 +4835,7 @@
       <c r="F130" s="27"/>
       <c r="G130" s="40"/>
       <c r="H130" s="48">
-        <v>91.3</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -4856,7 +4855,7 @@
       <c r="F131" s="27"/>
       <c r="G131" s="40"/>
       <c r="H131" s="48">
-        <v>86.960000000000008</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4876,7 +4875,7 @@
       <c r="F132" s="28"/>
       <c r="G132" s="41"/>
       <c r="H132" s="48">
-        <v>86.960000000000008</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -4896,7 +4895,7 @@
       <c r="F133" s="27"/>
       <c r="G133" s="40"/>
       <c r="H133" s="48">
-        <v>78.259999999999991</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4916,7 +4915,7 @@
       <c r="F134" s="27"/>
       <c r="G134" s="43"/>
       <c r="H134" s="48">
-        <v>73.91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -4936,7 +4935,7 @@
       <c r="F135" s="27"/>
       <c r="G135" s="44"/>
       <c r="H135" s="48">
-        <v>86.960000000000008</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -4956,7 +4955,7 @@
       <c r="F136" s="27"/>
       <c r="G136" s="39"/>
       <c r="H136" s="48">
-        <v>82.61</v>
+        <v>100</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -4976,7 +4975,7 @@
       <c r="F137" s="28"/>
       <c r="G137" s="41"/>
       <c r="H137" s="48">
-        <v>91.3</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -4996,7 +4995,7 @@
       <c r="F138" s="27"/>
       <c r="G138" s="40"/>
       <c r="H138" s="48">
-        <v>86.960000000000008</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -5016,7 +5015,7 @@
       <c r="F139" s="27"/>
       <c r="G139" s="40"/>
       <c r="H139" s="48">
-        <v>86.960000000000008</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -5036,7 +5035,7 @@
       <c r="F140" s="27"/>
       <c r="G140" s="40"/>
       <c r="H140" s="48">
-        <v>100</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -5056,7 +5055,7 @@
       <c r="F141" s="27"/>
       <c r="G141" s="40"/>
       <c r="H141" s="48">
-        <v>91.3</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -5076,7 +5075,7 @@
       <c r="F142" s="27"/>
       <c r="G142" s="40"/>
       <c r="H142" s="48">
-        <v>100</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -5096,7 +5095,7 @@
       <c r="F143" s="27"/>
       <c r="G143" s="40"/>
       <c r="H143" s="48">
-        <v>86.960000000000008</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -5116,7 +5115,7 @@
       <c r="F144" s="27"/>
       <c r="G144" s="40"/>
       <c r="H144" s="48">
-        <v>86.960000000000008</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -5136,7 +5135,7 @@
       <c r="F145" s="27"/>
       <c r="G145" s="40"/>
       <c r="H145" s="48">
-        <v>91.3</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -5156,7 +5155,7 @@
       <c r="F146" s="27"/>
       <c r="G146" s="40"/>
       <c r="H146" s="48">
-        <v>91.3</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -5176,7 +5175,7 @@
       <c r="F147" s="27"/>
       <c r="G147" s="40"/>
       <c r="H147" s="48">
-        <v>82.61</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -5196,7 +5195,7 @@
       <c r="F148" s="27"/>
       <c r="G148" s="40"/>
       <c r="H148" s="48">
-        <v>91.3</v>
+        <v>69.565217399999995</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -5216,7 +5215,7 @@
       <c r="F149" s="27"/>
       <c r="G149" s="40"/>
       <c r="H149" s="48">
-        <v>73.91</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -5236,7 +5235,7 @@
       <c r="F150" s="29"/>
       <c r="G150" s="41"/>
       <c r="H150" s="48">
-        <v>86.960000000000008</v>
+        <v>69.565217399999995</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -5256,7 +5255,7 @@
       <c r="F151" s="27"/>
       <c r="G151" s="40"/>
       <c r="H151" s="48">
-        <v>86.960000000000008</v>
+        <v>82.608695699999998</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -5276,7 +5275,7 @@
       <c r="F152" s="27"/>
       <c r="G152" s="40"/>
       <c r="H152" s="48">
-        <v>86.960000000000008</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -5296,7 +5295,7 @@
       <c r="F153" s="27"/>
       <c r="G153" s="40"/>
       <c r="H153" s="48">
-        <v>0</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -5316,7 +5315,7 @@
       <c r="F154" s="27"/>
       <c r="G154" s="40"/>
       <c r="H154" s="48">
-        <v>82.61</v>
+        <v>43.478260899999995</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -5336,7 +5335,7 @@
       <c r="F155" s="27"/>
       <c r="G155" s="40"/>
       <c r="H155" s="48">
-        <v>69.569999999999993</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -5356,7 +5355,7 @@
       <c r="F156" s="29"/>
       <c r="G156" s="41"/>
       <c r="H156" s="48">
-        <v>82.61</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -5376,7 +5375,7 @@
       <c r="F157" s="27"/>
       <c r="G157" s="40"/>
       <c r="H157" s="48">
-        <v>69.569999999999993</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -5396,7 +5395,7 @@
       <c r="F158" s="27"/>
       <c r="G158" s="40"/>
       <c r="H158" s="48">
-        <v>82.61</v>
+        <v>69.565217399999995</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -5416,7 +5415,7 @@
       <c r="F159" s="27"/>
       <c r="G159" s="40"/>
       <c r="H159" s="48">
-        <v>78.259999999999991</v>
+        <v>95.652173900000008</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -5436,7 +5435,7 @@
       <c r="F160" s="27"/>
       <c r="G160" s="40"/>
       <c r="H160" s="48">
-        <v>78.259999999999991</v>
+        <v>69.565217399999995</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -5456,7 +5455,7 @@
       <c r="F161" s="27"/>
       <c r="G161" s="40"/>
       <c r="H161" s="48">
-        <v>0</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -5476,7 +5475,7 @@
       <c r="F162" s="27"/>
       <c r="G162" s="40"/>
       <c r="H162" s="48">
-        <v>43.480000000000004</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -5496,7 +5495,7 @@
       <c r="F163" s="27"/>
       <c r="G163" s="40"/>
       <c r="H163" s="48">
-        <v>73.91</v>
+        <v>69.565217399999995</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -5516,7 +5515,7 @@
       <c r="F164" s="27"/>
       <c r="G164" s="43"/>
       <c r="H164" s="48">
-        <v>91.3</v>
+        <v>47.826087000000001</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -5536,7 +5535,7 @@
       <c r="F165" s="27"/>
       <c r="G165" s="38"/>
       <c r="H165" s="48">
-        <v>73.91</v>
+        <v>65.217391300000003</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -5556,7 +5555,7 @@
       <c r="F166" s="27"/>
       <c r="G166" s="38"/>
       <c r="H166" s="48">
-        <v>69.569999999999993</v>
+        <v>43.478260899999995</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -5576,7 +5575,7 @@
       <c r="F167" s="27"/>
       <c r="G167" s="38"/>
       <c r="H167" s="48">
-        <v>95.65</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -5596,7 +5595,7 @@
       <c r="F168" s="27"/>
       <c r="G168" s="38"/>
       <c r="H168" s="48">
-        <v>69.569999999999993</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -5616,7 +5615,7 @@
       <c r="F169" s="27"/>
       <c r="G169" s="38"/>
       <c r="H169" s="48">
-        <v>78.259999999999991</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -5636,7 +5635,7 @@
       <c r="F170" s="30"/>
       <c r="G170" s="45"/>
       <c r="H170" s="48">
-        <v>78.259999999999991</v>
+        <v>47.826087000000001</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -5656,7 +5655,7 @@
       <c r="F171" s="31"/>
       <c r="G171" s="46"/>
       <c r="H171" s="48">
-        <v>69.569999999999993</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -5676,7 +5675,7 @@
       <c r="F172" s="31"/>
       <c r="G172" s="46"/>
       <c r="H172" s="48">
-        <v>4.3499999999999996</v>
+        <v>43.478260899999995</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -5696,7 +5695,7 @@
       <c r="F173" s="31"/>
       <c r="G173" s="46"/>
       <c r="H173" s="48">
-        <v>47.83</v>
+        <v>43.478260899999995</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -5716,7 +5715,7 @@
       <c r="F174" s="31"/>
       <c r="G174" s="46"/>
       <c r="H174" s="48">
-        <v>65.22</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -5736,7 +5735,7 @@
       <c r="F175" s="31"/>
       <c r="G175" s="46"/>
       <c r="H175" s="48">
-        <v>43.480000000000004</v>
+        <v>30.434782599999998</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -5756,7 +5755,7 @@
       <c r="F176" s="31"/>
       <c r="G176" s="46"/>
       <c r="H176" s="48">
-        <v>86.960000000000008</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -5776,7 +5775,7 @@
       <c r="F177" s="31"/>
       <c r="G177" s="46"/>
       <c r="H177" s="48">
-        <v>78.259999999999991</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -5796,7 +5795,7 @@
       <c r="F178" s="31"/>
       <c r="G178" s="46"/>
       <c r="H178" s="48">
-        <v>91.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -5816,7 +5815,7 @@
       <c r="F179" s="31"/>
       <c r="G179" s="46"/>
       <c r="H179" s="48">
-        <v>47.83</v>
+        <v>95.652173900000008</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -5836,7 +5835,7 @@
       <c r="F180" s="31"/>
       <c r="G180" s="46"/>
       <c r="H180" s="48">
-        <v>0</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -5856,7 +5855,7 @@
       <c r="F181" s="31"/>
       <c r="G181" s="46"/>
       <c r="H181" s="48">
-        <v>73.91</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -5876,7 +5875,7 @@
       <c r="F182" s="31"/>
       <c r="G182" s="46"/>
       <c r="H182" s="48">
-        <v>43.480000000000004</v>
+        <v>86.956521699999996</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -5896,7 +5895,7 @@
       <c r="F183" s="31"/>
       <c r="G183" s="46"/>
       <c r="H183" s="48">
-        <v>43.480000000000004</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -5916,7 +5915,7 @@
       <c r="F184" s="31"/>
       <c r="G184" s="46"/>
       <c r="H184" s="48">
-        <v>78.259999999999991</v>
+        <v>95.652173900000008</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -5936,7 +5935,7 @@
       <c r="F185" s="31"/>
       <c r="G185" s="46"/>
       <c r="H185" s="48">
-        <v>30.43</v>
+        <v>78.260869600000007</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -5956,7 +5955,7 @@
       <c r="F186" s="31"/>
       <c r="G186" s="46"/>
       <c r="H186" s="48">
-        <v>86.960000000000008</v>
+        <v>91.304347800000002</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -5976,7 +5975,7 @@
       <c r="F187" s="31"/>
       <c r="G187" s="47"/>
       <c r="H187" s="48">
-        <v>86.960000000000008</v>
+        <v>73.913043500000001</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -5996,7 +5995,7 @@
       <c r="F188" s="31"/>
       <c r="G188" s="13"/>
       <c r="H188" s="48">
-        <v>0</v>
+        <v>60.869565199999997</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="15.75">
@@ -6015,9 +6014,7 @@
       <c r="E189" s="20"/>
       <c r="F189" s="31"/>
       <c r="G189" s="13"/>
-      <c r="H189" s="48">
-        <v>100</v>
-      </c>
+      <c r="H189" s="48"/>
     </row>
     <row r="190" spans="1:8" ht="15.75">
       <c r="A190" s="61" t="s">
@@ -6035,9 +6032,7 @@
       <c r="E190" s="11"/>
       <c r="F190" s="32"/>
       <c r="G190" s="14"/>
-      <c r="H190" s="48">
-        <v>95.65</v>
-      </c>
+      <c r="H190" s="48"/>
     </row>
     <row r="191" spans="1:8" ht="15.75">
       <c r="A191" s="61" t="s">
@@ -6055,9 +6050,7 @@
       <c r="E191" s="59"/>
       <c r="F191" s="32"/>
       <c r="G191" s="15"/>
-      <c r="H191" s="48">
-        <v>78.259999999999991</v>
-      </c>
+      <c r="H191" s="48"/>
     </row>
     <row r="192" spans="1:8" ht="15.75">
       <c r="A192" s="62" t="s">
@@ -6075,9 +6068,7 @@
       <c r="E192" s="10"/>
       <c r="F192" s="34"/>
       <c r="G192" s="15"/>
-      <c r="H192" s="48">
-        <v>0</v>
-      </c>
+      <c r="H192" s="48"/>
     </row>
     <row r="193" spans="1:8" ht="15.75">
       <c r="A193" s="61" t="s">
@@ -6095,9 +6086,7 @@
       <c r="E193" s="22"/>
       <c r="F193" s="33"/>
       <c r="G193" s="15"/>
-      <c r="H193" s="48">
-        <v>86.960000000000008</v>
-      </c>
+      <c r="H193" s="48"/>
     </row>
     <row r="194" spans="1:8" ht="15.75">
       <c r="A194" s="61" t="s">
@@ -6115,9 +6104,7 @@
       <c r="E194" s="11"/>
       <c r="F194" s="32"/>
       <c r="G194" s="15"/>
-      <c r="H194" s="48">
-        <v>86.960000000000008</v>
-      </c>
+      <c r="H194" s="48"/>
     </row>
     <row r="195" spans="1:8" ht="15.75">
       <c r="A195" s="61" t="s">
@@ -6135,9 +6122,7 @@
       <c r="E195" s="24"/>
       <c r="F195" s="34"/>
       <c r="G195" s="15"/>
-      <c r="H195" s="48">
-        <v>78.259999999999991</v>
-      </c>
+      <c r="H195" s="48"/>
     </row>
     <row r="196" spans="1:8" ht="15.75">
       <c r="A196" s="61" t="s">
@@ -6155,9 +6140,7 @@
       <c r="E196" s="59"/>
       <c r="F196" s="35"/>
       <c r="G196" s="15"/>
-      <c r="H196" s="48">
-        <v>95.65</v>
-      </c>
+      <c r="H196" s="48"/>
     </row>
     <row r="197" spans="1:8" ht="15.75">
       <c r="A197" s="62" t="s">
@@ -6175,9 +6158,7 @@
       <c r="E197" s="10"/>
       <c r="F197" s="35"/>
       <c r="G197" s="15"/>
-      <c r="H197" s="48">
-        <v>78.259999999999991</v>
-      </c>
+      <c r="H197" s="48"/>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="62" t="s">
@@ -6195,9 +6176,7 @@
       <c r="E198" s="10"/>
       <c r="F198" s="35"/>
       <c r="G198" s="15"/>
-      <c r="H198" s="48">
-        <v>91.3</v>
-      </c>
+      <c r="H198" s="48"/>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="61" t="s">
@@ -6215,9 +6194,7 @@
       <c r="E199" s="10"/>
       <c r="F199" s="55"/>
       <c r="G199" s="56"/>
-      <c r="H199" s="48">
-        <v>73.91</v>
-      </c>
+      <c r="H199" s="48"/>
     </row>
     <row r="200" spans="1:8" ht="15.75">
       <c r="A200" s="62" t="s">
@@ -6235,9 +6212,7 @@
       <c r="E200" s="10"/>
       <c r="F200" s="58"/>
       <c r="G200" s="15"/>
-      <c r="H200" s="48">
-        <v>60.870000000000005</v>
-      </c>
+      <c r="H200" s="48"/>
     </row>
     <row r="201" spans="1:8" ht="15.75">
       <c r="A201" s="62" t="s">
@@ -6264,21 +6239,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -6422,7 +6382,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -6436,16 +6423,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
 </file>
--- a/MC3020_E24.xlsx
+++ b/MC3020_E24.xlsx
@@ -6239,6 +6239,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -6382,15 +6391,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -6398,13 +6398,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>

--- a/MC3020_E24.xlsx
+++ b/MC3020_E24.xlsx
@@ -6239,15 +6239,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -6391,6 +6382,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -6398,13 +6398,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>

--- a/MC3020_E24.xlsx
+++ b/MC3020_E24.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0750CB54-5456-40D3-B875-49C42517A11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1251,9 +1252,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1754,7 +1755,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1772,9 +1773,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="10" borderId="10" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="10" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1782,15 +1783,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1859,36 +1851,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1911,9 +1873,6 @@
     <xf numFmtId="2" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1932,19 +1891,61 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
-    <cellStyle name="60% - Accent1 2" xfId="1"/>
-    <cellStyle name="60% - Accent2 2" xfId="2"/>
-    <cellStyle name="60% - Accent3 2" xfId="3"/>
-    <cellStyle name="60% - Accent4 2" xfId="4"/>
-    <cellStyle name="60% - Accent5 2" xfId="5"/>
-    <cellStyle name="60% - Accent6 2" xfId="6"/>
+    <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="60% - Accent2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="60% - Accent3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="60% - Accent4 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="60% - Accent5 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="60% - Accent6 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Comma" xfId="10" builtinId="3"/>
-    <cellStyle name="Neutral 2" xfId="7"/>
+    <cellStyle name="Neutral 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="8"/>
-    <cellStyle name="Title 2" xfId="9"/>
+    <cellStyle name="Normal 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Title 2" xfId="9" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2220,7 +2221,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -2259,3948 +2260,3966 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="51">
+      <c r="C2" s="38">
         <v>24</v>
       </c>
-      <c r="D2" s="52">
+      <c r="D2" s="39">
         <v>54</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="48">
+      <c r="E2" s="14"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="35">
         <v>65.217391300000003</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="51">
+      <c r="C3" s="38">
         <v>39</v>
       </c>
-      <c r="D3" s="52">
+      <c r="D3" s="39">
         <v>75</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="48">
+      <c r="E3" s="15"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="13" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="51">
+      <c r="C4" s="38">
         <v>43</v>
       </c>
-      <c r="D4" s="51">
+      <c r="D4" s="38">
         <v>71</v>
       </c>
       <c r="E4" s="11"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="48">
+      <c r="F4" s="24"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="51">
+      <c r="C5" s="38">
         <v>30</v>
       </c>
-      <c r="D5" s="51">
+      <c r="D5" s="38">
         <v>38</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="48">
+      <c r="E5" s="15"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="35">
         <v>30.434782599999998</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="13" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="51">
+      <c r="C6" s="38">
         <v>18</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="38">
         <v>37</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="48">
+      <c r="E6" s="15"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="35">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="13" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="38">
         <v>12</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="39">
         <v>34</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="48">
+      <c r="E7" s="15"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="13" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="38">
         <v>69</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="39">
         <v>83</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="48">
+      <c r="E8" s="15"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="13" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="38">
         <v>43</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="39">
         <v>68</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="48">
+      <c r="E9" s="15"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="13" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="38">
         <v>38</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="38">
         <v>55</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="48">
+      <c r="E10" s="15"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="51">
+      <c r="C11" s="38">
         <v>16</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="39">
         <v>28</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="48">
+      <c r="E11" s="15"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="13" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="38">
         <v>84</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="38">
         <v>59</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="48">
+      <c r="E12" s="15"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="35">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="13" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="51">
+      <c r="C13" s="38">
         <v>39</v>
       </c>
-      <c r="D13" s="52">
+      <c r="D13" s="39">
         <v>43</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="48">
+      <c r="E13" s="15"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="35">
         <v>90.909090899999995</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="51">
+      <c r="C14" s="38">
         <v>61</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="38">
         <v>89</v>
       </c>
-      <c r="E14" s="18"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="48">
+      <c r="E14" s="15"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="51">
+      <c r="C15" s="38">
         <v>80</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="39">
         <v>42</v>
       </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="48">
+      <c r="E15" s="15"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="13" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="51">
+      <c r="C16" s="38">
         <v>33</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="38">
         <v>46</v>
       </c>
-      <c r="E16" s="19"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="48">
+      <c r="E16" s="16"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="13" t="s">
         <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="38">
         <v>45</v>
       </c>
-      <c r="D17" s="52">
+      <c r="D17" s="39">
         <v>68</v>
       </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="48">
+      <c r="E17" s="15"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="13" t="s">
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="51">
+      <c r="C18" s="38">
         <v>52</v>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="38">
         <v>54</v>
       </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="48">
+      <c r="E18" s="15"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="51">
+      <c r="C19" s="38">
         <v>86</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="38">
         <v>94</v>
       </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="48">
+      <c r="E19" s="15"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="35">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="51">
+      <c r="C20" s="38">
         <v>76</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="38">
         <v>78</v>
       </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="48">
+      <c r="E20" s="15"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="13" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="51">
+      <c r="C21" s="38">
         <v>99</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="38">
         <v>84</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="48">
+      <c r="E21" s="15"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="13" t="s">
         <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="51">
+      <c r="C22" s="38">
         <v>34</v>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="39">
         <v>51</v>
       </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="48">
+      <c r="E22" s="15"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="13" t="s">
         <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="51">
+      <c r="C23" s="38">
         <v>71</v>
       </c>
-      <c r="D23" s="52">
+      <c r="D23" s="39">
         <v>87</v>
       </c>
-      <c r="E23" s="18"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="48">
+      <c r="E23" s="15"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="13" t="s">
         <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="51">
+      <c r="C24" s="38">
         <v>64</v>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="39">
         <v>40</v>
       </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="48">
+      <c r="E24" s="15"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="13" t="s">
         <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="38" t="s">
         <v>382</v>
       </c>
-      <c r="D25" s="52">
+      <c r="D25" s="39">
         <v>63</v>
       </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="48">
+      <c r="E25" s="15"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="13" t="s">
         <v>57</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="51">
+      <c r="C26" s="38">
         <v>68</v>
       </c>
-      <c r="D26" s="52">
+      <c r="D26" s="39">
         <v>73</v>
       </c>
-      <c r="E26" s="18"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="48">
+      <c r="E26" s="15"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="51">
+      <c r="C27" s="38">
         <v>43</v>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="38">
         <v>72</v>
       </c>
-      <c r="E27" s="18"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="48">
+      <c r="E27" s="15"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="13" t="s">
         <v>61</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="51">
+      <c r="C28" s="38">
         <v>30</v>
       </c>
-      <c r="D28" s="52">
+      <c r="D28" s="39">
         <v>85</v>
       </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="48">
+      <c r="E28" s="15"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="35">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="13" t="s">
         <v>63</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="51">
+      <c r="C29" s="38">
         <v>65</v>
       </c>
-      <c r="D29" s="52">
+      <c r="D29" s="39">
         <v>84</v>
       </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="48">
+      <c r="E29" s="15"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="38">
         <v>69</v>
       </c>
-      <c r="D30" s="52">
+      <c r="D30" s="39">
         <v>25</v>
       </c>
-      <c r="E30" s="18"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="48">
+      <c r="E30" s="15"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="13" t="s">
         <v>67</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="51">
+      <c r="C31" s="38">
         <v>44</v>
       </c>
-      <c r="D31" s="52">
+      <c r="D31" s="39">
         <v>34</v>
       </c>
-      <c r="E31" s="18"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="48">
+      <c r="E31" s="15"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="35">
         <v>47.826087000000001</v>
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="51">
+      <c r="C32" s="38">
         <v>61</v>
       </c>
-      <c r="D32" s="52">
+      <c r="D32" s="39">
         <v>85</v>
       </c>
-      <c r="E32" s="18"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="48">
+      <c r="E32" s="15"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="13" t="s">
         <v>71</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="51">
+      <c r="C33" s="38">
         <v>49</v>
       </c>
-      <c r="D33" s="52">
+      <c r="D33" s="39">
         <v>67</v>
       </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="48">
+      <c r="E33" s="15"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="13" t="s">
         <v>73</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="51">
+      <c r="C34" s="38">
         <v>50</v>
       </c>
-      <c r="D34" s="52">
+      <c r="D34" s="39">
         <v>45</v>
       </c>
-      <c r="E34" s="18"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="48">
+      <c r="E34" s="15"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="13" t="s">
         <v>75</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="51">
+      <c r="C35" s="38">
         <v>48</v>
       </c>
-      <c r="D35" s="51">
+      <c r="D35" s="38">
         <v>55</v>
       </c>
-      <c r="E35" s="18"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="48">
+      <c r="E35" s="15"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="13" t="s">
         <v>77</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="51">
+      <c r="C36" s="38">
         <v>49</v>
       </c>
-      <c r="D36" s="52">
+      <c r="D36" s="39">
         <v>57</v>
       </c>
-      <c r="E36" s="18"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="48">
+      <c r="E36" s="15"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="13" t="s">
         <v>79</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="51">
+      <c r="C37" s="38">
         <v>58</v>
       </c>
-      <c r="D37" s="52">
+      <c r="D37" s="39">
         <v>41</v>
       </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="48">
+      <c r="E37" s="15"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="35">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="13" t="s">
         <v>81</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="51">
+      <c r="C38" s="38">
         <v>81</v>
       </c>
-      <c r="D38" s="52">
+      <c r="D38" s="39">
         <v>84</v>
       </c>
-      <c r="E38" s="18"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="48">
+      <c r="E38" s="15"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="13" t="s">
         <v>83</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="51">
+      <c r="C39" s="38">
         <v>23</v>
       </c>
-      <c r="D39" s="52">
+      <c r="D39" s="39">
         <v>61</v>
       </c>
-      <c r="E39" s="18"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="48">
+      <c r="E39" s="15"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="13" t="s">
         <v>85</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="51">
+      <c r="C40" s="38">
         <v>32</v>
       </c>
-      <c r="D40" s="51">
+      <c r="D40" s="38">
         <v>37</v>
       </c>
-      <c r="E40" s="18"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="48">
+      <c r="E40" s="15"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="35">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="13" t="s">
         <v>87</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="51">
+      <c r="C41" s="38">
         <v>18</v>
       </c>
-      <c r="D41" s="51">
+      <c r="D41" s="38">
         <v>52</v>
       </c>
-      <c r="E41" s="18"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="48">
+      <c r="E41" s="15"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="51">
+      <c r="C42" s="38">
         <v>46</v>
       </c>
-      <c r="D42" s="52">
+      <c r="D42" s="39">
         <v>75</v>
       </c>
-      <c r="E42" s="18"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="48">
+      <c r="E42" s="15"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="35">
         <v>56.521739100000005</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="13" t="s">
         <v>91</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="51">
+      <c r="C43" s="38">
         <v>53</v>
       </c>
-      <c r="D43" s="51">
+      <c r="D43" s="38">
         <v>50</v>
       </c>
-      <c r="E43" s="18"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="48">
+      <c r="E43" s="15"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="35">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="13" t="s">
         <v>93</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="51">
+      <c r="C44" s="38">
         <v>60</v>
       </c>
-      <c r="D44" s="51">
+      <c r="D44" s="38">
         <v>39</v>
       </c>
-      <c r="E44" s="18"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="48">
+      <c r="E44" s="15"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="13" t="s">
         <v>95</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C45" s="51">
+      <c r="C45" s="38">
         <v>58</v>
       </c>
-      <c r="D45" s="52">
+      <c r="D45" s="39">
         <v>79</v>
       </c>
-      <c r="E45" s="18"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="48">
+      <c r="E45" s="15"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="35">
         <v>56.521739100000005</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="13" t="s">
         <v>97</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C46" s="51">
+      <c r="C46" s="38">
         <v>60</v>
       </c>
-      <c r="D46" s="51">
+      <c r="D46" s="38">
         <v>70</v>
       </c>
-      <c r="E46" s="18"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="48">
+      <c r="E46" s="15"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="13" t="s">
         <v>99</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="51">
+      <c r="C47" s="38">
         <v>18</v>
       </c>
-      <c r="D47" s="52">
+      <c r="D47" s="39">
         <v>64</v>
       </c>
-      <c r="E47" s="18"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="40"/>
-      <c r="H47" s="48">
+      <c r="E47" s="15"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="53"/>
+      <c r="H47" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="13" t="s">
         <v>101</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="51">
+      <c r="C48" s="38">
         <v>77</v>
       </c>
-      <c r="D48" s="52">
+      <c r="D48" s="39">
         <v>64</v>
       </c>
-      <c r="E48" s="18"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="42"/>
-      <c r="H48" s="48">
+      <c r="E48" s="15"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="55"/>
+      <c r="H48" s="35">
         <v>21.739130400000001</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="13" t="s">
         <v>103</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="51">
+      <c r="C49" s="38">
         <v>36</v>
       </c>
-      <c r="D49" s="52">
+      <c r="D49" s="39">
         <v>81</v>
       </c>
-      <c r="E49" s="18"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="48">
+      <c r="E49" s="15"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="53"/>
+      <c r="H49" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="13" t="s">
         <v>105</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="51">
+      <c r="C50" s="38">
         <v>47</v>
       </c>
-      <c r="D50" s="52">
+      <c r="D50" s="39">
         <v>63</v>
       </c>
-      <c r="E50" s="18"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="48">
+      <c r="E50" s="15"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="13" t="s">
         <v>107</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="51">
+      <c r="C51" s="38">
         <v>59</v>
       </c>
-      <c r="D51" s="51">
+      <c r="D51" s="38">
         <v>90</v>
       </c>
-      <c r="E51" s="18"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="48">
+      <c r="E51" s="15"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="13" t="s">
         <v>109</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="51">
+      <c r="C52" s="38">
         <v>68</v>
       </c>
-      <c r="D52" s="51">
+      <c r="D52" s="38">
         <v>42</v>
       </c>
-      <c r="E52" s="18"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="48">
+      <c r="E52" s="15"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="53"/>
+      <c r="H52" s="35">
         <v>47.826087000000001</v>
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="13" t="s">
         <v>111</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C53" s="51">
+      <c r="C53" s="38">
         <v>41</v>
       </c>
-      <c r="D53" s="52">
+      <c r="D53" s="39">
         <v>60</v>
       </c>
-      <c r="E53" s="18"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="48">
+      <c r="E53" s="15"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="53"/>
+      <c r="H53" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="13" t="s">
         <v>113</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="51">
+      <c r="C54" s="38">
         <v>54</v>
       </c>
-      <c r="D54" s="51">
+      <c r="D54" s="38">
         <v>76</v>
       </c>
-      <c r="E54" s="18"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="48">
+      <c r="E54" s="15"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="53"/>
+      <c r="H54" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="13" t="s">
         <v>115</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="51">
+      <c r="C55" s="38">
         <v>51</v>
       </c>
-      <c r="D55" s="52">
+      <c r="D55" s="39">
         <v>89</v>
       </c>
-      <c r="E55" s="18"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="42"/>
-      <c r="H55" s="48">
+      <c r="E55" s="15"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="55"/>
+      <c r="H55" s="35">
         <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="13" t="s">
         <v>117</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C56" s="51">
+      <c r="C56" s="38">
         <v>100</v>
       </c>
-      <c r="D56" s="52">
+      <c r="D56" s="39">
         <v>96</v>
       </c>
-      <c r="E56" s="18"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="48">
+      <c r="E56" s="15"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="53"/>
+      <c r="H56" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="13" t="s">
         <v>119</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="51">
+      <c r="C57" s="38">
         <v>21</v>
       </c>
-      <c r="D57" s="52">
+      <c r="D57" s="39">
         <v>37</v>
       </c>
-      <c r="E57" s="18"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="48">
+      <c r="E57" s="15"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="53"/>
+      <c r="H57" s="35">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="13" t="s">
         <v>121</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C58" s="51">
+      <c r="C58" s="38">
         <v>32</v>
       </c>
-      <c r="D58" s="51">
+      <c r="D58" s="38">
         <v>20</v>
       </c>
-      <c r="E58" s="18"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="48">
+      <c r="E58" s="15"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="13" t="s">
         <v>123</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="51">
+      <c r="C59" s="38">
         <v>23</v>
       </c>
-      <c r="D59" s="52">
+      <c r="D59" s="39">
         <v>36</v>
       </c>
-      <c r="E59" s="18"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="40"/>
-      <c r="H59" s="48">
+      <c r="E59" s="15"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="53"/>
+      <c r="H59" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A60" s="16" t="s">
+      <c r="A60" s="13" t="s">
         <v>125</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C60" s="51">
+      <c r="C60" s="38">
         <v>42</v>
       </c>
-      <c r="D60" s="52">
+      <c r="D60" s="39">
         <v>28</v>
       </c>
-      <c r="E60" s="19"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="41"/>
-      <c r="H60" s="48">
+      <c r="E60" s="16"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="16" t="s">
+      <c r="A61" s="13" t="s">
         <v>127</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="51">
+      <c r="C61" s="38">
         <v>58</v>
       </c>
-      <c r="D61" s="52">
+      <c r="D61" s="39">
         <v>68</v>
       </c>
-      <c r="E61" s="18"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="40"/>
-      <c r="H61" s="48">
+      <c r="E61" s="15"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="53"/>
+      <c r="H61" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="13" t="s">
         <v>129</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C62" s="51">
+      <c r="C62" s="38">
         <v>64</v>
       </c>
-      <c r="D62" s="52" t="s">
+      <c r="D62" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="E62" s="18"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="40"/>
-      <c r="H62" s="48">
+      <c r="E62" s="15"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="53"/>
+      <c r="H62" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="13" t="s">
         <v>131</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C63" s="51">
+      <c r="C63" s="38">
         <v>54</v>
       </c>
-      <c r="D63" s="52">
+      <c r="D63" s="39">
         <v>57</v>
       </c>
-      <c r="E63" s="18"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="40"/>
-      <c r="H63" s="48">
+      <c r="E63" s="15"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="53"/>
+      <c r="H63" s="35">
         <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="13" t="s">
         <v>133</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C64" s="51">
+      <c r="C64" s="38">
         <v>30</v>
       </c>
-      <c r="D64" s="52">
+      <c r="D64" s="39">
         <v>40</v>
       </c>
-      <c r="E64" s="18"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="40"/>
-      <c r="H64" s="48">
+      <c r="E64" s="15"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="53"/>
+      <c r="H64" s="35">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="16" t="s">
+      <c r="A65" s="13" t="s">
         <v>135</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="51">
+      <c r="C65" s="38">
         <v>30</v>
       </c>
-      <c r="D65" s="52">
+      <c r="D65" s="39">
         <v>48</v>
       </c>
-      <c r="E65" s="18"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="40"/>
-      <c r="H65" s="48">
+      <c r="E65" s="15"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="53"/>
+      <c r="H65" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="16" t="s">
+      <c r="A66" s="13" t="s">
         <v>137</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C66" s="51">
+      <c r="C66" s="38">
         <v>47</v>
       </c>
-      <c r="D66" s="52">
+      <c r="D66" s="39">
         <v>84</v>
       </c>
-      <c r="E66" s="18"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="48">
+      <c r="E66" s="15"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="13" t="s">
         <v>139</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C67" s="51">
+      <c r="C67" s="38">
         <v>38</v>
       </c>
-      <c r="D67" s="52">
+      <c r="D67" s="39">
         <v>50</v>
       </c>
-      <c r="E67" s="18"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="40"/>
-      <c r="H67" s="48">
+      <c r="E67" s="15"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="53"/>
+      <c r="H67" s="35">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="13" t="s">
         <v>141</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C68" s="51">
+      <c r="C68" s="38">
         <v>47</v>
       </c>
-      <c r="D68" s="52">
+      <c r="D68" s="39">
         <v>73</v>
       </c>
-      <c r="E68" s="18"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="42"/>
-      <c r="H68" s="48">
+      <c r="E68" s="15"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="55"/>
+      <c r="H68" s="35">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="13" t="s">
         <v>143</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C69" s="51">
+      <c r="C69" s="38">
         <v>36</v>
       </c>
-      <c r="D69" s="51">
+      <c r="D69" s="38">
         <v>17</v>
       </c>
-      <c r="E69" s="18"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="40"/>
-      <c r="H69" s="48">
+      <c r="E69" s="15"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="53"/>
+      <c r="H69" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="13" t="s">
         <v>145</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C70" s="51">
+      <c r="C70" s="38">
         <v>47</v>
       </c>
-      <c r="D70" s="52">
+      <c r="D70" s="39">
         <v>60</v>
       </c>
-      <c r="E70" s="18"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="40"/>
-      <c r="H70" s="48">
+      <c r="E70" s="15"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="53"/>
+      <c r="H70" s="35">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="13" t="s">
         <v>147</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C71" s="51">
+      <c r="C71" s="38">
         <v>43</v>
       </c>
-      <c r="D71" s="51">
+      <c r="D71" s="38">
         <v>74</v>
       </c>
-      <c r="E71" s="18"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="40"/>
-      <c r="H71" s="48">
+      <c r="E71" s="15"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="53"/>
+      <c r="H71" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="13" t="s">
         <v>149</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C72" s="51">
+      <c r="C72" s="38">
         <v>46</v>
       </c>
-      <c r="D72" s="51">
+      <c r="D72" s="38">
         <v>68</v>
       </c>
-      <c r="E72" s="18"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="40"/>
-      <c r="H72" s="48">
+      <c r="E72" s="15"/>
+      <c r="F72" s="24"/>
+      <c r="G72" s="53"/>
+      <c r="H72" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="13" t="s">
         <v>151</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C73" s="51">
+      <c r="C73" s="38">
         <v>51</v>
       </c>
-      <c r="D73" s="52">
+      <c r="D73" s="39">
         <v>80</v>
       </c>
-      <c r="E73" s="18"/>
-      <c r="F73" s="27"/>
-      <c r="G73" s="42"/>
-      <c r="H73" s="48">
+      <c r="E73" s="15"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="55"/>
+      <c r="H73" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="13" t="s">
         <v>153</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C74" s="51">
+      <c r="C74" s="38">
         <v>73</v>
       </c>
-      <c r="D74" s="52">
+      <c r="D74" s="39">
         <v>58</v>
       </c>
-      <c r="E74" s="18"/>
-      <c r="F74" s="27"/>
-      <c r="G74" s="40"/>
-      <c r="H74" s="48">
+      <c r="E74" s="15"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="35">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="13" t="s">
         <v>155</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C75" s="51">
+      <c r="C75" s="38">
         <v>0</v>
       </c>
-      <c r="D75" s="51">
+      <c r="D75" s="38">
         <v>60</v>
       </c>
-      <c r="E75" s="18"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="40"/>
-      <c r="H75" s="48">
+      <c r="E75" s="15"/>
+      <c r="F75" s="24"/>
+      <c r="G75" s="53"/>
+      <c r="H75" s="35">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="13" t="s">
         <v>157</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C76" s="51">
+      <c r="C76" s="38">
         <v>55</v>
       </c>
-      <c r="D76" s="52">
+      <c r="D76" s="39">
         <v>44</v>
       </c>
-      <c r="E76" s="18"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="40"/>
-      <c r="H76" s="48">
+      <c r="E76" s="15"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="13" t="s">
         <v>159</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C77" s="51">
+      <c r="C77" s="38">
         <v>56</v>
       </c>
-      <c r="D77" s="52">
+      <c r="D77" s="39">
         <v>48</v>
       </c>
-      <c r="E77" s="18"/>
-      <c r="F77" s="27"/>
-      <c r="G77" s="40"/>
-      <c r="H77" s="48">
+      <c r="E77" s="15"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="53"/>
+      <c r="H77" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="16" t="s">
+      <c r="A78" s="13" t="s">
         <v>161</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C78" s="51">
+      <c r="C78" s="38">
         <v>35</v>
       </c>
-      <c r="D78" s="51">
+      <c r="D78" s="38">
         <v>68</v>
       </c>
-      <c r="E78" s="18"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="40"/>
-      <c r="H78" s="48">
+      <c r="E78" s="15"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="53"/>
+      <c r="H78" s="35">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="13" t="s">
         <v>163</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C79" s="51">
+      <c r="C79" s="38">
         <v>32</v>
       </c>
-      <c r="D79" s="52">
+      <c r="D79" s="39">
         <v>41</v>
       </c>
-      <c r="E79" s="18"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="40"/>
-      <c r="H79" s="48">
+      <c r="E79" s="15"/>
+      <c r="F79" s="24"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="35">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="16" t="s">
+      <c r="A80" s="13" t="s">
         <v>165</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C80" s="51">
+      <c r="C80" s="38">
         <v>71</v>
       </c>
-      <c r="D80" s="52">
+      <c r="D80" s="39">
         <v>56</v>
       </c>
-      <c r="E80" s="18"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="40"/>
-      <c r="H80" s="48">
+      <c r="E80" s="15"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="16" t="s">
+      <c r="A81" s="13" t="s">
         <v>167</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C81" s="51">
+      <c r="C81" s="38">
         <v>56</v>
       </c>
-      <c r="D81" s="52">
+      <c r="D81" s="39">
         <v>63</v>
       </c>
-      <c r="E81" s="18"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="40"/>
-      <c r="H81" s="48">
+      <c r="E81" s="15"/>
+      <c r="F81" s="24"/>
+      <c r="G81" s="53"/>
+      <c r="H81" s="35">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="16" t="s">
+      <c r="A82" s="13" t="s">
         <v>169</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C82" s="51">
+      <c r="C82" s="38">
         <v>52</v>
       </c>
-      <c r="D82" s="52">
+      <c r="D82" s="39">
         <v>30</v>
       </c>
-      <c r="E82" s="18"/>
-      <c r="F82" s="27"/>
-      <c r="G82" s="40"/>
-      <c r="H82" s="48">
+      <c r="E82" s="15"/>
+      <c r="F82" s="24"/>
+      <c r="G82" s="53"/>
+      <c r="H82" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="13" t="s">
         <v>171</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C83" s="51">
+      <c r="C83" s="38">
         <v>34</v>
       </c>
-      <c r="D83" s="52">
+      <c r="D83" s="39">
         <v>85</v>
       </c>
-      <c r="E83" s="18"/>
-      <c r="F83" s="27"/>
-      <c r="G83" s="42"/>
-      <c r="H83" s="48">
+      <c r="E83" s="15"/>
+      <c r="F83" s="24"/>
+      <c r="G83" s="55"/>
+      <c r="H83" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="16" t="s">
+      <c r="A84" s="13" t="s">
         <v>173</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C84" s="51">
+      <c r="C84" s="38">
         <v>42</v>
       </c>
-      <c r="D84" s="51">
+      <c r="D84" s="38">
         <v>34</v>
       </c>
-      <c r="E84" s="18"/>
-      <c r="F84" s="27"/>
-      <c r="G84" s="40"/>
-      <c r="H84" s="48">
+      <c r="E84" s="15"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="53"/>
+      <c r="H84" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="16" t="s">
+      <c r="A85" s="13" t="s">
         <v>175</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C85" s="51">
+      <c r="C85" s="38">
         <v>51</v>
       </c>
-      <c r="D85" s="51">
+      <c r="D85" s="38">
         <v>67</v>
       </c>
-      <c r="E85" s="19"/>
-      <c r="F85" s="28"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="48">
+      <c r="E85" s="16"/>
+      <c r="F85" s="25"/>
+      <c r="G85" s="54"/>
+      <c r="H85" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="16" t="s">
+      <c r="A86" s="13" t="s">
         <v>177</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C86" s="51">
+      <c r="C86" s="38">
         <v>17</v>
       </c>
-      <c r="D86" s="52">
+      <c r="D86" s="39">
         <v>49</v>
       </c>
-      <c r="E86" s="18"/>
-      <c r="F86" s="27"/>
-      <c r="G86" s="40"/>
-      <c r="H86" s="48">
+      <c r="E86" s="15"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="53"/>
+      <c r="H86" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="16" t="s">
+      <c r="A87" s="13" t="s">
         <v>179</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C87" s="51">
+      <c r="C87" s="38">
         <v>34</v>
       </c>
-      <c r="D87" s="52">
+      <c r="D87" s="39">
         <v>58</v>
       </c>
-      <c r="E87" s="18"/>
-      <c r="F87" s="27"/>
-      <c r="G87" s="40"/>
-      <c r="H87" s="48">
+      <c r="E87" s="15"/>
+      <c r="F87" s="24"/>
+      <c r="G87" s="53"/>
+      <c r="H87" s="35">
         <v>56.521739100000005</v>
       </c>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="16" t="s">
+      <c r="A88" s="13" t="s">
         <v>181</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="51">
+      <c r="C88" s="38">
         <v>60</v>
       </c>
-      <c r="D88" s="52">
+      <c r="D88" s="39">
         <v>47</v>
       </c>
-      <c r="E88" s="18"/>
-      <c r="F88" s="27"/>
-      <c r="G88" s="40"/>
-      <c r="H88" s="48">
+      <c r="E88" s="15"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="16" t="s">
+      <c r="A89" s="13" t="s">
         <v>183</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C89" s="51">
+      <c r="C89" s="38">
         <v>29</v>
       </c>
-      <c r="D89" s="52">
+      <c r="D89" s="39">
         <v>58</v>
       </c>
-      <c r="E89" s="18"/>
-      <c r="F89" s="27"/>
-      <c r="G89" s="40"/>
-      <c r="H89" s="48">
+      <c r="E89" s="15"/>
+      <c r="F89" s="24"/>
+      <c r="G89" s="53"/>
+      <c r="H89" s="35">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="16" t="s">
+      <c r="A90" s="13" t="s">
         <v>185</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C90" s="51">
+      <c r="C90" s="38">
         <v>25</v>
       </c>
-      <c r="D90" s="52">
+      <c r="D90" s="39">
         <v>84</v>
       </c>
-      <c r="E90" s="18"/>
-      <c r="F90" s="27"/>
-      <c r="G90" s="42"/>
-      <c r="H90" s="48">
+      <c r="E90" s="15"/>
+      <c r="F90" s="24"/>
+      <c r="G90" s="55"/>
+      <c r="H90" s="35">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="13" t="s">
         <v>187</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C91" s="51">
+      <c r="C91" s="38">
         <v>33</v>
       </c>
-      <c r="D91" s="51">
+      <c r="D91" s="38">
         <v>66</v>
       </c>
-      <c r="E91" s="18"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="40"/>
-      <c r="H91" s="48">
+      <c r="E91" s="15"/>
+      <c r="F91" s="24"/>
+      <c r="G91" s="53"/>
+      <c r="H91" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="16" t="s">
+      <c r="A92" s="13" t="s">
         <v>189</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="51">
+      <c r="C92" s="38">
         <v>43</v>
       </c>
-      <c r="D92" s="51">
+      <c r="D92" s="38">
         <v>48</v>
       </c>
-      <c r="E92" s="18"/>
-      <c r="F92" s="27"/>
-      <c r="G92" s="40"/>
-      <c r="H92" s="48">
+      <c r="E92" s="15"/>
+      <c r="F92" s="24"/>
+      <c r="G92" s="53"/>
+      <c r="H92" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="16" t="s">
+      <c r="A93" s="13" t="s">
         <v>191</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C93" s="51">
+      <c r="C93" s="38">
         <v>24</v>
       </c>
-      <c r="D93" s="52" t="s">
+      <c r="D93" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="E93" s="18"/>
-      <c r="F93" s="27"/>
-      <c r="G93" s="40"/>
-      <c r="H93" s="48">
+      <c r="E93" s="15"/>
+      <c r="F93" s="24"/>
+      <c r="G93" s="53"/>
+      <c r="H93" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="16" t="s">
+      <c r="A94" s="13" t="s">
         <v>193</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C94" s="51">
+      <c r="C94" s="38">
         <v>57</v>
       </c>
-      <c r="D94" s="51">
+      <c r="D94" s="38">
         <v>55</v>
       </c>
-      <c r="E94" s="18"/>
-      <c r="F94" s="27"/>
-      <c r="G94" s="40"/>
-      <c r="H94" s="48">
+      <c r="E94" s="15"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="53"/>
+      <c r="H94" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="16" t="s">
+      <c r="A95" s="13" t="s">
         <v>195</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C95" s="51">
+      <c r="C95" s="38">
         <v>93</v>
       </c>
-      <c r="D95" s="52">
+      <c r="D95" s="39">
         <v>87</v>
       </c>
-      <c r="E95" s="18"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="40"/>
-      <c r="H95" s="48">
+      <c r="E95" s="15"/>
+      <c r="F95" s="24"/>
+      <c r="G95" s="53"/>
+      <c r="H95" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="16" t="s">
+      <c r="A96" s="13" t="s">
         <v>197</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="51">
+      <c r="C96" s="38">
         <v>65</v>
       </c>
-      <c r="D96" s="52">
+      <c r="D96" s="39">
         <v>79</v>
       </c>
-      <c r="E96" s="19"/>
-      <c r="F96" s="28"/>
-      <c r="G96" s="41"/>
-      <c r="H96" s="48">
+      <c r="E96" s="16"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="54"/>
+      <c r="H96" s="35">
         <v>65.217391300000003</v>
       </c>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="13" t="s">
         <v>199</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="51">
+      <c r="C97" s="38">
         <v>26</v>
       </c>
-      <c r="D97" s="52">
+      <c r="D97" s="39">
         <v>63</v>
       </c>
-      <c r="E97" s="18"/>
-      <c r="F97" s="27"/>
-      <c r="G97" s="40"/>
-      <c r="H97" s="48">
+      <c r="E97" s="15"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="53"/>
+      <c r="H97" s="35">
         <v>56.521739100000005</v>
       </c>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="16" t="s">
+      <c r="A98" s="13" t="s">
         <v>201</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="51">
+      <c r="C98" s="38">
         <v>13</v>
       </c>
-      <c r="D98" s="53">
+      <c r="D98" s="40">
         <v>52</v>
       </c>
-      <c r="E98" s="18"/>
-      <c r="F98" s="27"/>
-      <c r="G98" s="40"/>
-      <c r="H98" s="48">
+      <c r="E98" s="15"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="53"/>
+      <c r="H98" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="16" t="s">
+      <c r="A99" s="13" t="s">
         <v>203</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C99" s="51">
+      <c r="C99" s="38">
         <v>60</v>
       </c>
-      <c r="D99" s="53">
+      <c r="D99" s="40">
         <v>83</v>
       </c>
-      <c r="E99" s="18"/>
-      <c r="F99" s="27"/>
-      <c r="G99" s="42"/>
-      <c r="H99" s="48">
+      <c r="E99" s="15"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="55"/>
+      <c r="H99" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="16" t="s">
+      <c r="A100" s="13" t="s">
         <v>205</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="51">
+      <c r="C100" s="38">
         <v>42</v>
       </c>
-      <c r="D100" s="53">
+      <c r="D100" s="40">
         <v>48</v>
       </c>
-      <c r="E100" s="18"/>
-      <c r="F100" s="27"/>
-      <c r="G100" s="40"/>
-      <c r="H100" s="48">
+      <c r="E100" s="15"/>
+      <c r="F100" s="24"/>
+      <c r="G100" s="53"/>
+      <c r="H100" s="35">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="16" t="s">
+      <c r="A101" s="13" t="s">
         <v>207</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="51">
+      <c r="C101" s="38">
         <v>52</v>
       </c>
-      <c r="D101" s="53">
+      <c r="D101" s="40">
         <v>79</v>
       </c>
-      <c r="E101" s="18"/>
-      <c r="F101" s="27"/>
-      <c r="G101" s="40"/>
-      <c r="H101" s="48">
+      <c r="E101" s="15"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="53"/>
+      <c r="H101" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="16" t="s">
+      <c r="A102" s="13" t="s">
         <v>209</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="51">
+      <c r="C102" s="38">
         <v>60</v>
       </c>
-      <c r="D102" s="51">
+      <c r="D102" s="38">
         <v>85</v>
       </c>
-      <c r="E102" s="18"/>
-      <c r="F102" s="27"/>
-      <c r="G102" s="40"/>
-      <c r="H102" s="48">
+      <c r="E102" s="15"/>
+      <c r="F102" s="24"/>
+      <c r="G102" s="53"/>
+      <c r="H102" s="35">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="13" t="s">
         <v>211</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="51">
+      <c r="C103" s="38">
         <v>28</v>
       </c>
-      <c r="D103" s="53">
+      <c r="D103" s="40">
         <v>41</v>
       </c>
-      <c r="E103" s="18"/>
-      <c r="F103" s="27"/>
-      <c r="G103" s="40"/>
-      <c r="H103" s="48">
+      <c r="E103" s="15"/>
+      <c r="F103" s="24"/>
+      <c r="G103" s="53"/>
+      <c r="H103" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="16" t="s">
+      <c r="A104" s="13" t="s">
         <v>213</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C104" s="51">
+      <c r="C104" s="38">
         <v>27</v>
       </c>
-      <c r="D104" s="53">
+      <c r="D104" s="40">
         <v>74</v>
       </c>
-      <c r="E104" s="18"/>
-      <c r="F104" s="27"/>
-      <c r="G104" s="40"/>
-      <c r="H104" s="48">
+      <c r="E104" s="15"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="53"/>
+      <c r="H104" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="16" t="s">
+      <c r="A105" s="13" t="s">
         <v>215</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="51">
+      <c r="C105" s="38">
         <v>36</v>
       </c>
-      <c r="D105" s="53">
+      <c r="D105" s="40">
         <v>60</v>
       </c>
-      <c r="E105" s="18"/>
-      <c r="F105" s="27"/>
-      <c r="G105" s="40"/>
-      <c r="H105" s="48">
+      <c r="E105" s="15"/>
+      <c r="F105" s="24"/>
+      <c r="G105" s="53"/>
+      <c r="H105" s="35">
         <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="16" t="s">
+      <c r="A106" s="13" t="s">
         <v>217</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="51">
+      <c r="C106" s="38">
         <v>19</v>
       </c>
-      <c r="D106" s="53">
+      <c r="D106" s="40">
         <v>43</v>
       </c>
-      <c r="E106" s="18"/>
-      <c r="F106" s="27"/>
-      <c r="G106" s="40"/>
-      <c r="H106" s="48">
+      <c r="E106" s="15"/>
+      <c r="F106" s="24"/>
+      <c r="G106" s="53"/>
+      <c r="H106" s="35">
         <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="16" t="s">
+      <c r="A107" s="13" t="s">
         <v>219</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="51">
+      <c r="C107" s="38">
         <v>54</v>
       </c>
-      <c r="D107" s="53">
+      <c r="D107" s="40">
         <v>47</v>
       </c>
-      <c r="E107" s="18"/>
-      <c r="F107" s="27"/>
-      <c r="G107" s="40"/>
-      <c r="H107" s="48">
+      <c r="E107" s="15"/>
+      <c r="F107" s="24"/>
+      <c r="G107" s="53"/>
+      <c r="H107" s="35">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="16" t="s">
+      <c r="A108" s="13" t="s">
         <v>221</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C108" s="51">
+      <c r="C108" s="38">
         <v>46</v>
       </c>
-      <c r="D108" s="53">
+      <c r="D108" s="40">
         <v>12</v>
       </c>
-      <c r="E108" s="18"/>
-      <c r="F108" s="27"/>
-      <c r="G108" s="40"/>
-      <c r="H108" s="48">
+      <c r="E108" s="15"/>
+      <c r="F108" s="24"/>
+      <c r="G108" s="53"/>
+      <c r="H108" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="16" t="s">
+      <c r="A109" s="13" t="s">
         <v>223</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C109" s="51" t="s">
+      <c r="C109" s="38" t="s">
         <v>382</v>
       </c>
-      <c r="D109" s="51">
+      <c r="D109" s="38">
         <v>35</v>
       </c>
-      <c r="E109" s="18"/>
-      <c r="F109" s="27"/>
-      <c r="G109" s="40"/>
-      <c r="H109" s="48">
+      <c r="E109" s="15"/>
+      <c r="F109" s="24"/>
+      <c r="G109" s="53"/>
+      <c r="H109" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="16" t="s">
+      <c r="A110" s="13" t="s">
         <v>224</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C110" s="51">
+      <c r="C110" s="38">
         <v>53</v>
       </c>
-      <c r="D110" s="51" t="s">
+      <c r="D110" s="38" t="s">
         <v>382</v>
       </c>
-      <c r="E110" s="18"/>
-      <c r="F110" s="27"/>
-      <c r="G110" s="40"/>
-      <c r="H110" s="48">
+      <c r="E110" s="15"/>
+      <c r="F110" s="24"/>
+      <c r="G110" s="53"/>
+      <c r="H110" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="16" t="s">
+      <c r="A111" s="13" t="s">
         <v>226</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C111" s="51">
+      <c r="C111" s="38">
         <v>4</v>
       </c>
-      <c r="D111" s="51">
+      <c r="D111" s="38">
         <v>12</v>
       </c>
-      <c r="E111" s="18"/>
-      <c r="F111" s="27"/>
-      <c r="G111" s="40"/>
-      <c r="H111" s="48">
+      <c r="E111" s="15"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="53"/>
+      <c r="H111" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="16" t="s">
+      <c r="A112" s="13" t="s">
         <v>228</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C112" s="51">
+      <c r="C112" s="38">
         <v>71</v>
       </c>
-      <c r="D112" s="53">
+      <c r="D112" s="40">
         <v>85</v>
       </c>
-      <c r="E112" s="18"/>
-      <c r="F112" s="27"/>
-      <c r="G112" s="40"/>
-      <c r="H112" s="48">
+      <c r="E112" s="15"/>
+      <c r="F112" s="24"/>
+      <c r="G112" s="53"/>
+      <c r="H112" s="35">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="16" t="s">
+      <c r="A113" s="13" t="s">
         <v>230</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C113" s="51">
+      <c r="C113" s="38">
         <v>29</v>
       </c>
-      <c r="D113" s="53">
+      <c r="D113" s="40">
         <v>19</v>
       </c>
-      <c r="E113" s="18"/>
-      <c r="F113" s="27"/>
-      <c r="G113" s="40"/>
-      <c r="H113" s="48">
+      <c r="E113" s="15"/>
+      <c r="F113" s="24"/>
+      <c r="G113" s="53"/>
+      <c r="H113" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="16" t="s">
+      <c r="A114" s="13" t="s">
         <v>232</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C114" s="51">
+      <c r="C114" s="38">
         <v>45</v>
       </c>
-      <c r="D114" s="51">
+      <c r="D114" s="38">
         <v>75</v>
       </c>
-      <c r="E114" s="18"/>
-      <c r="F114" s="27"/>
-      <c r="G114" s="40"/>
-      <c r="H114" s="48">
+      <c r="E114" s="15"/>
+      <c r="F114" s="24"/>
+      <c r="G114" s="53"/>
+      <c r="H114" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="16" t="s">
+      <c r="A115" s="13" t="s">
         <v>234</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C115" s="51">
+      <c r="C115" s="38">
         <v>75</v>
       </c>
-      <c r="D115" s="51">
+      <c r="D115" s="38">
         <v>79</v>
       </c>
-      <c r="E115" s="18"/>
-      <c r="F115" s="27"/>
-      <c r="G115" s="40"/>
-      <c r="H115" s="48">
+      <c r="E115" s="15"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="53"/>
+      <c r="H115" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="16" t="s">
+      <c r="A116" s="13" t="s">
         <v>236</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C116" s="51">
+      <c r="C116" s="38">
         <v>53</v>
       </c>
-      <c r="D116" s="53">
+      <c r="D116" s="40">
         <v>47</v>
       </c>
-      <c r="E116" s="18"/>
-      <c r="F116" s="27"/>
-      <c r="G116" s="40"/>
-      <c r="H116" s="48">
+      <c r="E116" s="15"/>
+      <c r="F116" s="24"/>
+      <c r="G116" s="53"/>
+      <c r="H116" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.25" customHeight="1">
-      <c r="A117" s="16" t="s">
+      <c r="A117" s="13" t="s">
         <v>238</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C117" s="51">
+      <c r="C117" s="38">
         <v>44</v>
       </c>
-      <c r="D117" s="53">
+      <c r="D117" s="40">
         <v>60</v>
       </c>
-      <c r="E117" s="18"/>
-      <c r="F117" s="27"/>
-      <c r="G117" s="40"/>
-      <c r="H117" s="48">
+      <c r="E117" s="15"/>
+      <c r="F117" s="24"/>
+      <c r="G117" s="53"/>
+      <c r="H117" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="16" t="s">
+      <c r="A118" s="13" t="s">
         <v>240</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C118" s="51">
+      <c r="C118" s="38">
         <v>64</v>
       </c>
-      <c r="D118" s="51">
+      <c r="D118" s="38">
         <v>57</v>
       </c>
-      <c r="E118" s="18"/>
-      <c r="F118" s="27"/>
-      <c r="G118" s="40"/>
-      <c r="H118" s="48">
+      <c r="E118" s="15"/>
+      <c r="F118" s="24"/>
+      <c r="G118" s="53"/>
+      <c r="H118" s="35">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="16" t="s">
+      <c r="A119" s="13" t="s">
         <v>242</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C119" s="51">
+      <c r="C119" s="38">
         <v>83</v>
       </c>
-      <c r="D119" s="51">
+      <c r="D119" s="38">
         <v>52</v>
       </c>
-      <c r="E119" s="18"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="40"/>
-      <c r="H119" s="48">
+      <c r="E119" s="15"/>
+      <c r="F119" s="24"/>
+      <c r="G119" s="53"/>
+      <c r="H119" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="16" t="s">
+      <c r="A120" s="13" t="s">
         <v>244</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C120" s="51">
+      <c r="C120" s="38">
         <v>17</v>
       </c>
-      <c r="D120" s="53">
+      <c r="D120" s="40">
         <v>31</v>
       </c>
-      <c r="E120" s="18"/>
-      <c r="F120" s="27"/>
-      <c r="G120" s="40"/>
-      <c r="H120" s="48">
+      <c r="E120" s="15"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="53"/>
+      <c r="H120" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="16" t="s">
+      <c r="A121" s="13" t="s">
         <v>246</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C121" s="51" t="s">
+      <c r="C121" s="38" t="s">
         <v>382</v>
       </c>
-      <c r="D121" s="51">
+      <c r="D121" s="38">
         <v>16</v>
       </c>
-      <c r="E121" s="18"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="40"/>
-      <c r="H121" s="48">
+      <c r="E121" s="15"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="53"/>
+      <c r="H121" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="16" t="s">
+      <c r="A122" s="13" t="s">
         <v>248</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C122" s="51">
+      <c r="C122" s="38">
         <v>25</v>
       </c>
-      <c r="D122" s="51">
+      <c r="D122" s="38">
         <v>36</v>
       </c>
-      <c r="E122" s="18"/>
-      <c r="F122" s="27"/>
-      <c r="G122" s="40"/>
-      <c r="H122" s="48">
+      <c r="E122" s="15"/>
+      <c r="F122" s="24"/>
+      <c r="G122" s="53"/>
+      <c r="H122" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="16" t="s">
+      <c r="A123" s="13" t="s">
         <v>250</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C123" s="51" t="s">
+      <c r="C123" s="38" t="s">
         <v>382</v>
       </c>
-      <c r="D123" s="53" t="s">
+      <c r="D123" s="40" t="s">
         <v>382</v>
       </c>
-      <c r="E123" s="18"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="40"/>
-      <c r="H123" s="48">
+      <c r="E123" s="15"/>
+      <c r="F123" s="24"/>
+      <c r="G123" s="53"/>
+      <c r="H123" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="16" t="s">
+      <c r="A124" s="13" t="s">
         <v>252</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C124" s="51">
+      <c r="C124" s="38">
         <v>58</v>
       </c>
-      <c r="D124" s="51">
+      <c r="D124" s="38">
         <v>72</v>
       </c>
-      <c r="E124" s="18"/>
-      <c r="F124" s="27"/>
-      <c r="G124" s="40"/>
-      <c r="H124" s="48">
+      <c r="E124" s="15"/>
+      <c r="F124" s="24"/>
+      <c r="G124" s="53"/>
+      <c r="H124" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="16" t="s">
+      <c r="A125" s="13" t="s">
         <v>254</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C125" s="51">
+      <c r="C125" s="38">
         <v>28</v>
       </c>
-      <c r="D125" s="53">
+      <c r="D125" s="40">
         <v>41</v>
       </c>
-      <c r="E125" s="18"/>
-      <c r="F125" s="27"/>
-      <c r="G125" s="40"/>
-      <c r="H125" s="48">
+      <c r="E125" s="15"/>
+      <c r="F125" s="24"/>
+      <c r="G125" s="53"/>
+      <c r="H125" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="16" t="s">
+      <c r="A126" s="13" t="s">
         <v>256</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C126" s="51">
+      <c r="C126" s="38">
         <v>44</v>
       </c>
-      <c r="D126" s="51">
+      <c r="D126" s="38">
         <v>53</v>
       </c>
-      <c r="E126" s="18"/>
-      <c r="F126" s="27"/>
-      <c r="G126" s="40"/>
-      <c r="H126" s="48">
+      <c r="E126" s="15"/>
+      <c r="F126" s="24"/>
+      <c r="G126" s="53"/>
+      <c r="H126" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="16" t="s">
+      <c r="A127" s="13" t="s">
         <v>258</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C127" s="51">
+      <c r="C127" s="38">
         <v>54</v>
       </c>
-      <c r="D127" s="53">
+      <c r="D127" s="40">
         <v>32</v>
       </c>
-      <c r="E127" s="18"/>
-      <c r="F127" s="27"/>
-      <c r="G127" s="40"/>
-      <c r="H127" s="48">
+      <c r="E127" s="15"/>
+      <c r="F127" s="24"/>
+      <c r="G127" s="53"/>
+      <c r="H127" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="16" t="s">
+      <c r="A128" s="13" t="s">
         <v>260</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C128" s="51">
+      <c r="C128" s="38">
         <v>21</v>
       </c>
-      <c r="D128" s="53">
+      <c r="D128" s="40">
         <v>56</v>
       </c>
-      <c r="E128" s="18"/>
-      <c r="F128" s="27"/>
-      <c r="G128" s="40"/>
-      <c r="H128" s="48">
+      <c r="E128" s="15"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="53"/>
+      <c r="H128" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="16" t="s">
+      <c r="A129" s="13" t="s">
         <v>262</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C129" s="51">
+      <c r="C129" s="38">
         <v>26</v>
       </c>
-      <c r="D129" s="53">
+      <c r="D129" s="40">
         <v>49</v>
       </c>
-      <c r="E129" s="18"/>
-      <c r="F129" s="27"/>
-      <c r="G129" s="40"/>
-      <c r="H129" s="48">
+      <c r="E129" s="15"/>
+      <c r="F129" s="24"/>
+      <c r="G129" s="53"/>
+      <c r="H129" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="16" t="s">
+      <c r="A130" s="13" t="s">
         <v>264</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C130" s="51">
+      <c r="C130" s="38">
         <v>15</v>
       </c>
-      <c r="D130" s="53">
+      <c r="D130" s="40">
         <v>26</v>
       </c>
-      <c r="E130" s="18"/>
-      <c r="F130" s="27"/>
-      <c r="G130" s="40"/>
-      <c r="H130" s="48">
+      <c r="E130" s="15"/>
+      <c r="F130" s="24"/>
+      <c r="G130" s="53"/>
+      <c r="H130" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="16" t="s">
+      <c r="A131" s="13" t="s">
         <v>266</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C131" s="51">
+      <c r="C131" s="38">
         <v>51</v>
       </c>
-      <c r="D131" s="53">
+      <c r="D131" s="40">
         <v>23</v>
       </c>
-      <c r="E131" s="18"/>
-      <c r="F131" s="27"/>
-      <c r="G131" s="40"/>
-      <c r="H131" s="48">
+      <c r="E131" s="15"/>
+      <c r="F131" s="24"/>
+      <c r="G131" s="53"/>
+      <c r="H131" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="16" t="s">
+      <c r="A132" s="13" t="s">
         <v>268</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C132" s="51">
+      <c r="C132" s="38">
         <v>50</v>
       </c>
-      <c r="D132" s="53">
+      <c r="D132" s="40">
         <v>81</v>
       </c>
-      <c r="E132" s="19"/>
-      <c r="F132" s="28"/>
-      <c r="G132" s="41"/>
-      <c r="H132" s="48">
+      <c r="E132" s="16"/>
+      <c r="F132" s="25"/>
+      <c r="G132" s="54"/>
+      <c r="H132" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="16" t="s">
+      <c r="A133" s="13" t="s">
         <v>270</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C133" s="51">
+      <c r="C133" s="38">
         <v>18</v>
       </c>
-      <c r="D133" s="53">
+      <c r="D133" s="40">
         <v>13</v>
       </c>
-      <c r="E133" s="18"/>
-      <c r="F133" s="27"/>
-      <c r="G133" s="40"/>
-      <c r="H133" s="48">
+      <c r="E133" s="15"/>
+      <c r="F133" s="24"/>
+      <c r="G133" s="53"/>
+      <c r="H133" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="16" t="s">
+      <c r="A134" s="13" t="s">
         <v>272</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C134" s="51">
+      <c r="C134" s="38">
         <v>53</v>
       </c>
-      <c r="D134" s="53">
+      <c r="D134" s="40">
         <v>49</v>
       </c>
-      <c r="E134" s="18"/>
-      <c r="F134" s="27"/>
-      <c r="G134" s="43"/>
-      <c r="H134" s="48">
+      <c r="E134" s="15"/>
+      <c r="F134" s="24"/>
+      <c r="G134" s="56"/>
+      <c r="H134" s="35">
         <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="16" t="s">
+      <c r="A135" s="13" t="s">
         <v>274</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C135" s="51">
+      <c r="C135" s="38">
         <v>8</v>
       </c>
-      <c r="D135" s="53">
+      <c r="D135" s="40">
         <v>42</v>
       </c>
-      <c r="E135" s="18"/>
-      <c r="F135" s="27"/>
-      <c r="G135" s="44"/>
-      <c r="H135" s="48">
+      <c r="E135" s="15"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="57"/>
+      <c r="H135" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="16" t="s">
+      <c r="A136" s="13" t="s">
         <v>276</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C136" s="51">
+      <c r="C136" s="38">
         <v>42</v>
       </c>
-      <c r="D136" s="51">
+      <c r="D136" s="38">
         <v>58</v>
       </c>
-      <c r="E136" s="18"/>
-      <c r="F136" s="27"/>
-      <c r="G136" s="39"/>
-      <c r="H136" s="48">
+      <c r="E136" s="15"/>
+      <c r="F136" s="24"/>
+      <c r="G136" s="52"/>
+      <c r="H136" s="35">
         <v>100</v>
       </c>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="16" t="s">
+      <c r="A137" s="13" t="s">
         <v>278</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C137" s="51">
+      <c r="C137" s="38">
         <v>37</v>
       </c>
-      <c r="D137" s="51">
+      <c r="D137" s="38">
         <v>45</v>
       </c>
-      <c r="E137" s="19"/>
-      <c r="F137" s="28"/>
-      <c r="G137" s="41"/>
-      <c r="H137" s="48">
+      <c r="E137" s="16"/>
+      <c r="F137" s="25"/>
+      <c r="G137" s="54"/>
+      <c r="H137" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="16" t="s">
+      <c r="A138" s="13" t="s">
         <v>280</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C138" s="51">
+      <c r="C138" s="38">
         <v>46</v>
       </c>
-      <c r="D138" s="51">
+      <c r="D138" s="38">
         <v>29</v>
       </c>
-      <c r="E138" s="18"/>
-      <c r="F138" s="27"/>
-      <c r="G138" s="40"/>
-      <c r="H138" s="48">
+      <c r="E138" s="15"/>
+      <c r="F138" s="24"/>
+      <c r="G138" s="53"/>
+      <c r="H138" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="16" t="s">
+      <c r="A139" s="13" t="s">
         <v>282</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C139" s="51">
+      <c r="C139" s="38">
         <v>43</v>
       </c>
-      <c r="D139" s="53">
+      <c r="D139" s="40">
         <v>38</v>
       </c>
-      <c r="E139" s="18"/>
-      <c r="F139" s="27"/>
-      <c r="G139" s="40"/>
-      <c r="H139" s="48">
+      <c r="E139" s="15"/>
+      <c r="F139" s="24"/>
+      <c r="G139" s="53"/>
+      <c r="H139" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="16" t="s">
+      <c r="A140" s="13" t="s">
         <v>284</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C140" s="51">
+      <c r="C140" s="38">
         <v>40</v>
       </c>
-      <c r="D140" s="51">
+      <c r="D140" s="38">
         <v>66</v>
       </c>
-      <c r="E140" s="18"/>
-      <c r="F140" s="27"/>
-      <c r="G140" s="40"/>
-      <c r="H140" s="48">
+      <c r="E140" s="15"/>
+      <c r="F140" s="24"/>
+      <c r="G140" s="53"/>
+      <c r="H140" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="16" t="s">
+      <c r="A141" s="13" t="s">
         <v>286</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C141" s="51">
+      <c r="C141" s="38">
         <v>32</v>
       </c>
-      <c r="D141" s="51">
+      <c r="D141" s="38">
         <v>17</v>
       </c>
-      <c r="E141" s="18"/>
-      <c r="F141" s="27"/>
-      <c r="G141" s="40"/>
-      <c r="H141" s="48">
+      <c r="E141" s="15"/>
+      <c r="F141" s="24"/>
+      <c r="G141" s="53"/>
+      <c r="H141" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="16" t="s">
+      <c r="A142" s="13" t="s">
         <v>288</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C142" s="51">
+      <c r="C142" s="38">
         <v>32</v>
       </c>
-      <c r="D142" s="51">
+      <c r="D142" s="38">
         <v>45</v>
       </c>
-      <c r="E142" s="18"/>
-      <c r="F142" s="27"/>
-      <c r="G142" s="40"/>
-      <c r="H142" s="48">
+      <c r="E142" s="15"/>
+      <c r="F142" s="24"/>
+      <c r="G142" s="53"/>
+      <c r="H142" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="143" spans="1:8">
-      <c r="A143" s="16" t="s">
+      <c r="A143" s="13" t="s">
         <v>290</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C143" s="51">
+      <c r="C143" s="38">
         <v>67</v>
       </c>
-      <c r="D143" s="53">
+      <c r="D143" s="40">
         <v>89</v>
       </c>
-      <c r="E143" s="18"/>
-      <c r="F143" s="27"/>
-      <c r="G143" s="40"/>
-      <c r="H143" s="48">
+      <c r="E143" s="15"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="53"/>
+      <c r="H143" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="16" t="s">
+      <c r="A144" s="13" t="s">
         <v>292</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C144" s="51">
+      <c r="C144" s="38">
         <v>61</v>
       </c>
-      <c r="D144" s="53">
+      <c r="D144" s="40">
         <v>76</v>
       </c>
-      <c r="E144" s="18"/>
-      <c r="F144" s="27"/>
-      <c r="G144" s="40"/>
-      <c r="H144" s="48">
+      <c r="E144" s="15"/>
+      <c r="F144" s="24"/>
+      <c r="G144" s="53"/>
+      <c r="H144" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="145" spans="1:8">
-      <c r="A145" s="16" t="s">
+      <c r="A145" s="13" t="s">
         <v>294</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C145" s="51">
+      <c r="C145" s="38">
         <v>71</v>
       </c>
-      <c r="D145" s="53">
+      <c r="D145" s="40">
         <v>76</v>
       </c>
-      <c r="E145" s="18"/>
-      <c r="F145" s="27"/>
-      <c r="G145" s="40"/>
-      <c r="H145" s="48">
+      <c r="E145" s="15"/>
+      <c r="F145" s="24"/>
+      <c r="G145" s="53"/>
+      <c r="H145" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="146" spans="1:8">
-      <c r="A146" s="16" t="s">
+      <c r="A146" s="13" t="s">
         <v>296</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C146" s="51">
+      <c r="C146" s="38">
         <v>96</v>
       </c>
-      <c r="D146" s="53">
+      <c r="D146" s="40">
         <v>86</v>
       </c>
-      <c r="E146" s="18"/>
-      <c r="F146" s="27"/>
-      <c r="G146" s="40"/>
-      <c r="H146" s="48">
+      <c r="E146" s="15"/>
+      <c r="F146" s="24"/>
+      <c r="G146" s="53"/>
+      <c r="H146" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" s="16" t="s">
+      <c r="A147" s="13" t="s">
         <v>298</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C147" s="51">
+      <c r="C147" s="38">
         <v>21</v>
       </c>
-      <c r="D147" s="51">
+      <c r="D147" s="38">
         <v>28</v>
       </c>
-      <c r="E147" s="18"/>
-      <c r="F147" s="27"/>
-      <c r="G147" s="40"/>
-      <c r="H147" s="48">
+      <c r="E147" s="15"/>
+      <c r="F147" s="24"/>
+      <c r="G147" s="53"/>
+      <c r="H147" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="148" spans="1:8">
-      <c r="A148" s="16" t="s">
+      <c r="A148" s="13" t="s">
         <v>300</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C148" s="51">
+      <c r="C148" s="38">
         <v>47</v>
       </c>
-      <c r="D148" s="51">
+      <c r="D148" s="38">
         <v>73</v>
       </c>
-      <c r="E148" s="18"/>
-      <c r="F148" s="27"/>
-      <c r="G148" s="40"/>
-      <c r="H148" s="48">
+      <c r="E148" s="15"/>
+      <c r="F148" s="24"/>
+      <c r="G148" s="53"/>
+      <c r="H148" s="35">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="149" spans="1:8">
-      <c r="A149" s="16" t="s">
+      <c r="A149" s="13" t="s">
         <v>302</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C149" s="51">
+      <c r="C149" s="38">
         <v>67</v>
       </c>
-      <c r="D149" s="53">
+      <c r="D149" s="40">
         <v>52</v>
       </c>
-      <c r="E149" s="18"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="40"/>
-      <c r="H149" s="48">
+      <c r="E149" s="15"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="53"/>
+      <c r="H149" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" s="16" t="s">
+      <c r="A150" s="13" t="s">
         <v>304</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C150" s="51" t="s">
+      <c r="C150" s="38" t="s">
         <v>382</v>
       </c>
-      <c r="D150" s="53">
+      <c r="D150" s="40">
         <v>48</v>
       </c>
-      <c r="E150" s="19"/>
-      <c r="F150" s="29"/>
-      <c r="G150" s="41"/>
-      <c r="H150" s="48">
+      <c r="E150" s="16"/>
+      <c r="F150" s="26"/>
+      <c r="G150" s="54"/>
+      <c r="H150" s="35">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="151" spans="1:8">
-      <c r="A151" s="16" t="s">
+      <c r="A151" s="13" t="s">
         <v>306</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C151" s="51">
+      <c r="C151" s="38">
         <v>52</v>
       </c>
-      <c r="D151" s="51">
+      <c r="D151" s="38">
         <v>43</v>
       </c>
-      <c r="E151" s="18"/>
-      <c r="F151" s="27"/>
-      <c r="G151" s="40"/>
-      <c r="H151" s="48">
+      <c r="E151" s="15"/>
+      <c r="F151" s="24"/>
+      <c r="G151" s="53"/>
+      <c r="H151" s="35">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="152" spans="1:8">
-      <c r="A152" s="16" t="s">
+      <c r="A152" s="13" t="s">
         <v>308</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C152" s="51">
+      <c r="C152" s="38">
         <v>36</v>
       </c>
-      <c r="D152" s="51">
+      <c r="D152" s="38">
         <v>51</v>
       </c>
-      <c r="E152" s="18"/>
-      <c r="F152" s="27"/>
-      <c r="G152" s="40"/>
-      <c r="H152" s="48">
+      <c r="E152" s="15"/>
+      <c r="F152" s="24"/>
+      <c r="G152" s="53"/>
+      <c r="H152" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="153" spans="1:8">
-      <c r="A153" s="16" t="s">
+      <c r="A153" s="13" t="s">
         <v>310</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C153" s="51">
+      <c r="C153" s="38">
         <v>78</v>
       </c>
-      <c r="D153" s="53">
+      <c r="D153" s="40">
         <v>46</v>
       </c>
-      <c r="E153" s="18"/>
-      <c r="F153" s="27"/>
-      <c r="G153" s="40"/>
-      <c r="H153" s="48">
+      <c r="E153" s="15"/>
+      <c r="F153" s="24"/>
+      <c r="G153" s="53"/>
+      <c r="H153" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="154" spans="1:8">
-      <c r="A154" s="16" t="s">
+      <c r="A154" s="13" t="s">
         <v>312</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C154" s="51">
+      <c r="C154" s="38">
         <v>31</v>
       </c>
-      <c r="D154" s="52">
+      <c r="D154" s="39">
         <v>78</v>
       </c>
-      <c r="E154" s="18"/>
-      <c r="F154" s="27"/>
-      <c r="G154" s="40"/>
-      <c r="H154" s="48">
+      <c r="E154" s="15"/>
+      <c r="F154" s="24"/>
+      <c r="G154" s="53"/>
+      <c r="H154" s="35">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="155" spans="1:8">
-      <c r="A155" s="16" t="s">
+      <c r="A155" s="13" t="s">
         <v>314</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C155" s="51">
+      <c r="C155" s="38">
         <v>60</v>
       </c>
-      <c r="D155" s="52">
+      <c r="D155" s="39">
         <v>85</v>
       </c>
-      <c r="E155" s="18"/>
-      <c r="F155" s="27"/>
-      <c r="G155" s="40"/>
-      <c r="H155" s="48">
+      <c r="E155" s="15"/>
+      <c r="F155" s="24"/>
+      <c r="G155" s="53"/>
+      <c r="H155" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="156" spans="1:8">
-      <c r="A156" s="16" t="s">
+      <c r="A156" s="13" t="s">
         <v>316</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C156" s="51">
+      <c r="C156" s="38">
         <v>95</v>
       </c>
-      <c r="D156" s="51">
+      <c r="D156" s="38">
         <v>89</v>
       </c>
-      <c r="E156" s="19"/>
-      <c r="F156" s="29"/>
-      <c r="G156" s="41"/>
-      <c r="H156" s="48">
+      <c r="E156" s="16"/>
+      <c r="F156" s="26"/>
+      <c r="G156" s="54"/>
+      <c r="H156" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" s="16" t="s">
+      <c r="A157" s="13" t="s">
         <v>318</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C157" s="51">
+      <c r="C157" s="38">
         <v>69</v>
       </c>
-      <c r="D157" s="51">
+      <c r="D157" s="38">
         <v>89</v>
       </c>
-      <c r="E157" s="18"/>
-      <c r="F157" s="27"/>
-      <c r="G157" s="40"/>
-      <c r="H157" s="48">
+      <c r="E157" s="15"/>
+      <c r="F157" s="24"/>
+      <c r="G157" s="53"/>
+      <c r="H157" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" s="16" t="s">
+      <c r="A158" s="13" t="s">
         <v>320</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C158" s="51">
+      <c r="C158" s="38">
         <v>47</v>
       </c>
-      <c r="D158" s="51">
+      <c r="D158" s="38">
         <v>86</v>
       </c>
-      <c r="E158" s="18"/>
-      <c r="F158" s="27"/>
-      <c r="G158" s="40"/>
-      <c r="H158" s="48">
+      <c r="E158" s="15"/>
+      <c r="F158" s="24"/>
+      <c r="G158" s="53"/>
+      <c r="H158" s="35">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" s="16" t="s">
+      <c r="A159" s="13" t="s">
         <v>322</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C159" s="51">
+      <c r="C159" s="38">
         <v>58</v>
       </c>
-      <c r="D159" s="52">
+      <c r="D159" s="39">
         <v>56</v>
       </c>
-      <c r="E159" s="20"/>
-      <c r="F159" s="27"/>
-      <c r="G159" s="40"/>
-      <c r="H159" s="48">
+      <c r="E159" s="17"/>
+      <c r="F159" s="24"/>
+      <c r="G159" s="53"/>
+      <c r="H159" s="35">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="16" t="s">
+      <c r="A160" s="13" t="s">
         <v>324</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C160" s="51">
+      <c r="C160" s="38">
         <v>25</v>
       </c>
-      <c r="D160" s="52">
+      <c r="D160" s="39">
         <v>76</v>
       </c>
-      <c r="E160" s="18"/>
-      <c r="F160" s="27"/>
-      <c r="G160" s="40"/>
-      <c r="H160" s="48">
+      <c r="E160" s="15"/>
+      <c r="F160" s="24"/>
+      <c r="G160" s="53"/>
+      <c r="H160" s="35">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="16" t="s">
+      <c r="A161" s="13" t="s">
         <v>326</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C161" s="51">
+      <c r="C161" s="38">
         <v>44</v>
       </c>
-      <c r="D161" s="51">
+      <c r="D161" s="38">
         <v>34</v>
       </c>
-      <c r="E161" s="18"/>
-      <c r="F161" s="27"/>
-      <c r="G161" s="40"/>
-      <c r="H161" s="48">
+      <c r="E161" s="15"/>
+      <c r="F161" s="24"/>
+      <c r="G161" s="53"/>
+      <c r="H161" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="162" spans="1:8">
-      <c r="A162" s="16" t="s">
+      <c r="A162" s="13" t="s">
         <v>328</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C162" s="51">
+      <c r="C162" s="38">
         <v>31</v>
       </c>
-      <c r="D162" s="52">
+      <c r="D162" s="39">
         <v>38</v>
       </c>
-      <c r="E162" s="18"/>
-      <c r="F162" s="27"/>
-      <c r="G162" s="40"/>
-      <c r="H162" s="48">
+      <c r="E162" s="15"/>
+      <c r="F162" s="24"/>
+      <c r="G162" s="53"/>
+      <c r="H162" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="163" spans="1:8">
-      <c r="A163" s="16" t="s">
+      <c r="A163" s="13" t="s">
         <v>330</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C163" s="52">
+      <c r="C163" s="39">
         <v>40</v>
       </c>
-      <c r="D163" s="51">
+      <c r="D163" s="38">
         <v>55</v>
       </c>
-      <c r="E163" s="18"/>
-      <c r="F163" s="27"/>
-      <c r="G163" s="40"/>
-      <c r="H163" s="48">
+      <c r="E163" s="15"/>
+      <c r="F163" s="24"/>
+      <c r="G163" s="53"/>
+      <c r="H163" s="35">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="164" spans="1:8">
-      <c r="A164" s="16" t="s">
+      <c r="A164" s="13" t="s">
         <v>332</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C164" s="52">
+      <c r="C164" s="39">
         <v>19</v>
       </c>
-      <c r="D164" s="52">
+      <c r="D164" s="39">
         <v>63</v>
       </c>
-      <c r="E164" s="18"/>
-      <c r="F164" s="27"/>
-      <c r="G164" s="43"/>
-      <c r="H164" s="48">
+      <c r="E164" s="15"/>
+      <c r="F164" s="24"/>
+      <c r="G164" s="56"/>
+      <c r="H164" s="35">
         <v>47.826087000000001</v>
       </c>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="16" t="s">
+      <c r="A165" s="13" t="s">
         <v>334</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C165" s="52" t="s">
+      <c r="C165" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="D165" s="51">
+      <c r="D165" s="38">
         <v>74</v>
       </c>
-      <c r="E165" s="18"/>
-      <c r="F165" s="27"/>
-      <c r="G165" s="38"/>
-      <c r="H165" s="48">
+      <c r="E165" s="15"/>
+      <c r="F165" s="24"/>
+      <c r="G165" s="51"/>
+      <c r="H165" s="35">
         <v>65.217391300000003</v>
       </c>
     </row>
     <row r="166" spans="1:8">
-      <c r="A166" s="16" t="s">
+      <c r="A166" s="13" t="s">
         <v>336</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C166" s="52">
+      <c r="C166" s="39">
         <v>18</v>
       </c>
-      <c r="D166" s="51">
+      <c r="D166" s="38">
         <v>44</v>
       </c>
-      <c r="E166" s="18"/>
-      <c r="F166" s="27"/>
-      <c r="G166" s="38"/>
-      <c r="H166" s="48">
+      <c r="E166" s="15"/>
+      <c r="F166" s="24"/>
+      <c r="G166" s="51"/>
+      <c r="H166" s="35">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" s="16" t="s">
+      <c r="A167" s="13" t="s">
         <v>338</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C167" s="52">
+      <c r="C167" s="39">
         <v>44</v>
       </c>
-      <c r="D167" s="52">
+      <c r="D167" s="39">
         <v>69</v>
       </c>
-      <c r="E167" s="18"/>
-      <c r="F167" s="27"/>
-      <c r="G167" s="38"/>
-      <c r="H167" s="48">
+      <c r="E167" s="15"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="51"/>
+      <c r="H167" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="16" t="s">
+      <c r="A168" s="13" t="s">
         <v>340</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C168" s="52">
+      <c r="C168" s="39">
         <v>82</v>
       </c>
-      <c r="D168" s="51">
+      <c r="D168" s="38">
         <v>93</v>
       </c>
-      <c r="E168" s="18"/>
-      <c r="F168" s="27"/>
-      <c r="G168" s="38"/>
-      <c r="H168" s="48">
+      <c r="E168" s="15"/>
+      <c r="F168" s="24"/>
+      <c r="G168" s="51"/>
+      <c r="H168" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="169" spans="1:8">
-      <c r="A169" s="16" t="s">
+      <c r="A169" s="13" t="s">
         <v>342</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C169" s="52">
+      <c r="C169" s="39">
         <v>55</v>
       </c>
-      <c r="D169" s="52">
+      <c r="D169" s="39">
         <v>55</v>
       </c>
-      <c r="E169" s="18"/>
-      <c r="F169" s="27"/>
-      <c r="G169" s="38"/>
-      <c r="H169" s="48">
+      <c r="E169" s="15"/>
+      <c r="F169" s="24"/>
+      <c r="G169" s="51"/>
+      <c r="H169" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="170" spans="1:8">
-      <c r="A170" s="16" t="s">
+      <c r="A170" s="13" t="s">
         <v>344</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C170" s="52">
+      <c r="C170" s="39">
         <v>24</v>
       </c>
-      <c r="D170" s="52">
+      <c r="D170" s="39">
         <v>25</v>
       </c>
-      <c r="E170" s="21"/>
-      <c r="F170" s="30"/>
-      <c r="G170" s="45"/>
-      <c r="H170" s="48">
+      <c r="E170" s="18"/>
+      <c r="F170" s="27"/>
+      <c r="G170" s="58"/>
+      <c r="H170" s="35">
         <v>47.826087000000001</v>
       </c>
     </row>
     <row r="171" spans="1:8">
-      <c r="A171" s="16" t="s">
+      <c r="A171" s="13" t="s">
         <v>346</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C171" s="52">
+      <c r="C171" s="39">
         <v>36</v>
       </c>
-      <c r="D171" s="52">
+      <c r="D171" s="39">
         <v>50</v>
       </c>
-      <c r="E171" s="18"/>
-      <c r="F171" s="31"/>
-      <c r="G171" s="46"/>
-      <c r="H171" s="48">
+      <c r="E171" s="15"/>
+      <c r="F171" s="28"/>
+      <c r="G171" s="59"/>
+      <c r="H171" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="172" spans="1:8">
-      <c r="A172" s="16" t="s">
+      <c r="A172" s="13" t="s">
         <v>348</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C172" s="52">
+      <c r="C172" s="39">
         <v>55</v>
       </c>
-      <c r="D172" s="52">
+      <c r="D172" s="39">
         <v>58</v>
       </c>
-      <c r="E172" s="18"/>
-      <c r="F172" s="31"/>
-      <c r="G172" s="46"/>
-      <c r="H172" s="48">
+      <c r="E172" s="15"/>
+      <c r="F172" s="28"/>
+      <c r="G172" s="59"/>
+      <c r="H172" s="35">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="173" spans="1:8">
-      <c r="A173" s="16" t="s">
+      <c r="A173" s="13" t="s">
         <v>350</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C173" s="52">
+      <c r="C173" s="39">
         <v>27</v>
       </c>
-      <c r="D173" s="51">
+      <c r="D173" s="38">
         <v>65</v>
       </c>
-      <c r="E173" s="18"/>
-      <c r="F173" s="31"/>
-      <c r="G173" s="46"/>
-      <c r="H173" s="48">
+      <c r="E173" s="15"/>
+      <c r="F173" s="28"/>
+      <c r="G173" s="59"/>
+      <c r="H173" s="35">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="174" spans="1:8">
-      <c r="A174" s="16" t="s">
+      <c r="A174" s="13" t="s">
         <v>352</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C174" s="52">
+      <c r="C174" s="39">
         <v>14</v>
       </c>
-      <c r="D174" s="51">
+      <c r="D174" s="38">
         <v>22</v>
       </c>
-      <c r="E174" s="18"/>
-      <c r="F174" s="31"/>
-      <c r="G174" s="46"/>
-      <c r="H174" s="48">
+      <c r="E174" s="15"/>
+      <c r="F174" s="28"/>
+      <c r="G174" s="59"/>
+      <c r="H174" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="175" spans="1:8">
-      <c r="A175" s="16" t="s">
+      <c r="A175" s="13" t="s">
         <v>354</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C175" s="52">
+      <c r="C175" s="39">
         <v>17</v>
       </c>
-      <c r="D175" s="52">
+      <c r="D175" s="39">
         <v>40</v>
       </c>
-      <c r="E175" s="18"/>
-      <c r="F175" s="31"/>
-      <c r="G175" s="46"/>
-      <c r="H175" s="48">
+      <c r="E175" s="15"/>
+      <c r="F175" s="28"/>
+      <c r="G175" s="59"/>
+      <c r="H175" s="35">
         <v>30.434782599999998</v>
       </c>
     </row>
     <row r="176" spans="1:8">
-      <c r="A176" s="16" t="s">
+      <c r="A176" s="13" t="s">
         <v>356</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C176" s="52">
+      <c r="C176" s="39">
         <v>33</v>
       </c>
-      <c r="D176" s="51">
+      <c r="D176" s="38">
         <v>23</v>
       </c>
-      <c r="E176" s="18"/>
-      <c r="F176" s="31"/>
-      <c r="G176" s="46"/>
-      <c r="H176" s="48">
+      <c r="E176" s="15"/>
+      <c r="F176" s="28"/>
+      <c r="G176" s="59"/>
+      <c r="H176" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="177" spans="1:8">
-      <c r="A177" s="16" t="s">
+      <c r="A177" s="13" t="s">
         <v>358</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C177" s="52">
+      <c r="C177" s="39">
         <v>64</v>
       </c>
-      <c r="D177" s="51">
+      <c r="D177" s="38">
         <v>81</v>
       </c>
-      <c r="E177" s="18"/>
-      <c r="F177" s="31"/>
-      <c r="G177" s="46"/>
-      <c r="H177" s="48">
+      <c r="E177" s="15"/>
+      <c r="F177" s="28"/>
+      <c r="G177" s="59"/>
+      <c r="H177" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="178" spans="1:8">
-      <c r="A178" s="16" t="s">
+      <c r="A178" s="13" t="s">
         <v>360</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C178" s="52">
+      <c r="C178" s="39">
         <v>32</v>
       </c>
-      <c r="D178" s="51">
+      <c r="D178" s="38">
         <v>94</v>
       </c>
-      <c r="E178" s="18"/>
-      <c r="F178" s="31"/>
-      <c r="G178" s="46"/>
-      <c r="H178" s="48">
+      <c r="E178" s="15"/>
+      <c r="F178" s="28"/>
+      <c r="G178" s="59"/>
+      <c r="H178" s="35">
         <v>100</v>
       </c>
     </row>
     <row r="179" spans="1:8">
-      <c r="A179" s="16" t="s">
+      <c r="A179" s="13" t="s">
         <v>362</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C179" s="52">
+      <c r="C179" s="39">
         <v>64</v>
       </c>
-      <c r="D179" s="51">
+      <c r="D179" s="38">
         <v>92</v>
       </c>
-      <c r="E179" s="18"/>
-      <c r="F179" s="31"/>
-      <c r="G179" s="46"/>
-      <c r="H179" s="48">
+      <c r="E179" s="15"/>
+      <c r="F179" s="28"/>
+      <c r="G179" s="59"/>
+      <c r="H179" s="35">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="180" spans="1:8">
-      <c r="A180" s="16" t="s">
+      <c r="A180" s="13" t="s">
         <v>364</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C180" s="52">
+      <c r="C180" s="39">
         <v>12</v>
       </c>
-      <c r="D180" s="51">
+      <c r="D180" s="38">
         <v>25</v>
       </c>
-      <c r="E180" s="18"/>
-      <c r="F180" s="31"/>
-      <c r="G180" s="46"/>
-      <c r="H180" s="48">
+      <c r="E180" s="15"/>
+      <c r="F180" s="28"/>
+      <c r="G180" s="59"/>
+      <c r="H180" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="181" spans="1:8">
-      <c r="A181" s="16" t="s">
+      <c r="A181" s="13" t="s">
         <v>366</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C181" s="52">
+      <c r="C181" s="39">
         <v>36</v>
       </c>
-      <c r="D181" s="52">
+      <c r="D181" s="39">
         <v>70</v>
       </c>
-      <c r="E181" s="18"/>
-      <c r="F181" s="31"/>
-      <c r="G181" s="46"/>
-      <c r="H181" s="48">
+      <c r="E181" s="15"/>
+      <c r="F181" s="28"/>
+      <c r="G181" s="59"/>
+      <c r="H181" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="182" spans="1:8">
-      <c r="A182" s="16" t="s">
+      <c r="A182" s="13" t="s">
         <v>368</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C182" s="52">
+      <c r="C182" s="39">
         <v>1</v>
       </c>
-      <c r="D182" s="52">
+      <c r="D182" s="39">
         <v>40</v>
       </c>
-      <c r="E182" s="22"/>
-      <c r="F182" s="31"/>
-      <c r="G182" s="46"/>
-      <c r="H182" s="48">
+      <c r="E182" s="19"/>
+      <c r="F182" s="28"/>
+      <c r="G182" s="59"/>
+      <c r="H182" s="35">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="183" spans="1:8">
-      <c r="A183" s="16" t="s">
+      <c r="A183" s="13" t="s">
         <v>370</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C183" s="52">
+      <c r="C183" s="39">
         <v>38</v>
       </c>
-      <c r="D183" s="52">
+      <c r="D183" s="39">
         <v>66</v>
       </c>
-      <c r="E183" s="22"/>
-      <c r="F183" s="31"/>
-      <c r="G183" s="46"/>
-      <c r="H183" s="48">
+      <c r="E183" s="19"/>
+      <c r="F183" s="28"/>
+      <c r="G183" s="59"/>
+      <c r="H183" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="184" spans="1:8">
-      <c r="A184" s="16" t="s">
+      <c r="A184" s="13" t="s">
         <v>372</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C184" s="52">
+      <c r="C184" s="39">
         <v>41</v>
       </c>
-      <c r="D184" s="52">
+      <c r="D184" s="39">
         <v>62</v>
       </c>
-      <c r="E184" s="18"/>
-      <c r="F184" s="31"/>
-      <c r="G184" s="46"/>
-      <c r="H184" s="48">
+      <c r="E184" s="15"/>
+      <c r="F184" s="28"/>
+      <c r="G184" s="59"/>
+      <c r="H184" s="35">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="185" spans="1:8">
-      <c r="A185" s="16" t="s">
+      <c r="A185" s="13" t="s">
         <v>374</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C185" s="52">
+      <c r="C185" s="39">
         <v>77</v>
       </c>
-      <c r="D185" s="52">
+      <c r="D185" s="39">
         <v>57</v>
       </c>
-      <c r="E185" s="18"/>
-      <c r="F185" s="31"/>
-      <c r="G185" s="46"/>
-      <c r="H185" s="48">
+      <c r="E185" s="15"/>
+      <c r="F185" s="28"/>
+      <c r="G185" s="59"/>
+      <c r="H185" s="35">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="186" spans="1:8">
-      <c r="A186" s="16" t="s">
+      <c r="A186" s="13" t="s">
         <v>376</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C186" s="52">
+      <c r="C186" s="39">
         <v>74</v>
       </c>
-      <c r="D186" s="52">
+      <c r="D186" s="39">
         <v>44</v>
       </c>
-      <c r="E186" s="18"/>
-      <c r="F186" s="31"/>
-      <c r="G186" s="46"/>
-      <c r="H186" s="48">
+      <c r="E186" s="15"/>
+      <c r="F186" s="28"/>
+      <c r="G186" s="59"/>
+      <c r="H186" s="35">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="49" t="s">
+      <c r="A187" s="36" t="s">
         <v>380</v>
       </c>
-      <c r="B187" s="50" t="s">
+      <c r="B187" s="37" t="s">
         <v>381</v>
       </c>
-      <c r="C187" s="52">
+      <c r="C187" s="39">
         <v>37</v>
       </c>
-      <c r="D187" s="52">
+      <c r="D187" s="39">
         <v>32</v>
       </c>
-      <c r="E187" s="23"/>
-      <c r="F187" s="31"/>
-      <c r="G187" s="47"/>
-      <c r="H187" s="48">
+      <c r="E187" s="20"/>
+      <c r="F187" s="28"/>
+      <c r="G187" s="60">
+        <v>47</v>
+      </c>
+      <c r="H187" s="35">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="36" t="s">
+      <c r="A188" s="33" t="s">
         <v>378</v>
       </c>
-      <c r="B188" s="37" t="s">
+      <c r="B188" s="34" t="s">
         <v>379</v>
       </c>
-      <c r="C188" s="52">
+      <c r="C188" s="39">
         <v>0</v>
       </c>
-      <c r="D188" s="52">
+      <c r="D188" s="39">
         <v>24</v>
       </c>
-      <c r="E188" s="22"/>
-      <c r="F188" s="31"/>
-      <c r="G188" s="13"/>
-      <c r="H188" s="48">
+      <c r="E188" s="19"/>
+      <c r="F188" s="28"/>
+      <c r="G188" s="61">
+        <v>29</v>
+      </c>
+      <c r="H188" s="35">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="15.75">
-      <c r="A189" s="16" t="s">
+      <c r="A189" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="B189" s="63" t="s">
+      <c r="B189" s="49" t="s">
         <v>399</v>
       </c>
-      <c r="C189" s="52">
+      <c r="C189" s="39">
         <v>38</v>
       </c>
-      <c r="D189" s="51">
+      <c r="D189" s="38">
         <v>56</v>
       </c>
-      <c r="E189" s="20"/>
-      <c r="F189" s="31"/>
-      <c r="G189" s="13"/>
-      <c r="H189" s="48"/>
+      <c r="E189" s="17"/>
+      <c r="F189" s="28"/>
+      <c r="G189" s="61">
+        <v>60</v>
+      </c>
+      <c r="H189" s="35"/>
     </row>
     <row r="190" spans="1:8" ht="15.75">
-      <c r="A190" s="61" t="s">
+      <c r="A190" s="47" t="s">
         <v>384</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C190" s="52">
+      <c r="C190" s="39">
         <v>53</v>
       </c>
-      <c r="D190" s="51">
+      <c r="D190" s="38">
         <v>72</v>
       </c>
       <c r="E190" s="11"/>
-      <c r="F190" s="32"/>
-      <c r="G190" s="14"/>
-      <c r="H190" s="48"/>
+      <c r="F190" s="29"/>
+      <c r="G190" s="62">
+        <v>60</v>
+      </c>
+      <c r="H190" s="35"/>
     </row>
     <row r="191" spans="1:8" ht="15.75">
-      <c r="A191" s="61" t="s">
+      <c r="A191" s="47" t="s">
         <v>385</v>
       </c>
-      <c r="B191" s="63" t="s">
+      <c r="B191" s="49" t="s">
         <v>400</v>
       </c>
-      <c r="C191" s="52">
+      <c r="C191" s="39">
         <v>75</v>
       </c>
-      <c r="D191" s="51">
+      <c r="D191" s="38">
         <v>69</v>
       </c>
-      <c r="E191" s="59"/>
-      <c r="F191" s="32"/>
-      <c r="G191" s="15"/>
-      <c r="H191" s="48"/>
+      <c r="E191" s="45"/>
+      <c r="F191" s="29"/>
+      <c r="G191" s="63">
+        <v>51</v>
+      </c>
+      <c r="H191" s="35"/>
     </row>
     <row r="192" spans="1:8" ht="15.75">
-      <c r="A192" s="62" t="s">
+      <c r="A192" s="48" t="s">
         <v>391</v>
       </c>
-      <c r="B192" s="63" t="s">
+      <c r="B192" s="49" t="s">
         <v>401</v>
       </c>
-      <c r="C192" s="52" t="s">
+      <c r="C192" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="D192" s="51">
+      <c r="D192" s="38">
         <v>71</v>
       </c>
       <c r="E192" s="10"/>
-      <c r="F192" s="34"/>
-      <c r="G192" s="15"/>
-      <c r="H192" s="48"/>
+      <c r="F192" s="31"/>
+      <c r="G192" s="63"/>
+      <c r="H192" s="35"/>
     </row>
     <row r="193" spans="1:8" ht="15.75">
-      <c r="A193" s="61" t="s">
+      <c r="A193" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="B193" s="63" t="s">
+      <c r="B193" s="49" t="s">
         <v>402</v>
       </c>
-      <c r="C193" s="52">
+      <c r="C193" s="39">
         <v>22</v>
       </c>
-      <c r="D193" s="51">
+      <c r="D193" s="38">
         <v>54</v>
       </c>
-      <c r="E193" s="22"/>
-      <c r="F193" s="33"/>
-      <c r="G193" s="15"/>
-      <c r="H193" s="48"/>
+      <c r="E193" s="19"/>
+      <c r="F193" s="30"/>
+      <c r="G193" s="63">
+        <v>62</v>
+      </c>
+      <c r="H193" s="35"/>
     </row>
     <row r="194" spans="1:8" ht="15.75">
-      <c r="A194" s="61" t="s">
+      <c r="A194" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="B194" s="63" t="s">
+      <c r="B194" s="49" t="s">
         <v>397</v>
       </c>
-      <c r="C194" s="52">
+      <c r="C194" s="39">
         <v>7</v>
       </c>
-      <c r="D194" s="51">
+      <c r="D194" s="38">
         <v>31</v>
       </c>
       <c r="E194" s="11"/>
-      <c r="F194" s="32"/>
-      <c r="G194" s="15"/>
-      <c r="H194" s="48"/>
+      <c r="F194" s="29"/>
+      <c r="G194" s="63">
+        <v>16</v>
+      </c>
+      <c r="H194" s="35"/>
     </row>
     <row r="195" spans="1:8" ht="15.75">
-      <c r="A195" s="61" t="s">
+      <c r="A195" s="47" t="s">
         <v>388</v>
       </c>
-      <c r="B195" s="63" t="s">
+      <c r="B195" s="49" t="s">
         <v>403</v>
       </c>
-      <c r="C195" s="52">
+      <c r="C195" s="39">
         <v>41</v>
       </c>
-      <c r="D195" s="52" t="s">
+      <c r="D195" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="E195" s="24"/>
-      <c r="F195" s="34"/>
-      <c r="G195" s="15"/>
-      <c r="H195" s="48"/>
+      <c r="E195" s="21"/>
+      <c r="F195" s="31"/>
+      <c r="G195" s="63"/>
+      <c r="H195" s="35"/>
     </row>
     <row r="196" spans="1:8" ht="15.75">
-      <c r="A196" s="61" t="s">
+      <c r="A196" s="47" t="s">
         <v>389</v>
       </c>
-      <c r="B196" s="63" t="s">
+      <c r="B196" s="49" t="s">
         <v>398</v>
       </c>
-      <c r="C196" s="52">
+      <c r="C196" s="39">
         <v>35</v>
       </c>
-      <c r="D196" s="52">
+      <c r="D196" s="39">
         <v>84</v>
       </c>
-      <c r="E196" s="59"/>
-      <c r="F196" s="35"/>
-      <c r="G196" s="15"/>
-      <c r="H196" s="48"/>
+      <c r="E196" s="45"/>
+      <c r="F196" s="32"/>
+      <c r="G196" s="63">
+        <v>76</v>
+      </c>
+      <c r="H196" s="35"/>
     </row>
     <row r="197" spans="1:8" ht="15.75">
-      <c r="A197" s="62" t="s">
+      <c r="A197" s="48" t="s">
         <v>392</v>
       </c>
-      <c r="B197" s="63" t="s">
+      <c r="B197" s="49" t="s">
         <v>404</v>
       </c>
-      <c r="C197" s="52" t="s">
+      <c r="C197" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="D197" s="52">
+      <c r="D197" s="39">
         <v>42</v>
       </c>
       <c r="E197" s="10"/>
-      <c r="F197" s="35"/>
-      <c r="G197" s="15"/>
-      <c r="H197" s="48"/>
+      <c r="F197" s="32"/>
+      <c r="G197" s="63"/>
+      <c r="H197" s="35"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="62" t="s">
+      <c r="A198" s="48" t="s">
         <v>393</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="C198" s="52" t="s">
+      <c r="C198" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="D198" s="60" t="s">
+      <c r="D198" s="46" t="s">
         <v>382</v>
       </c>
       <c r="E198" s="10"/>
-      <c r="F198" s="35"/>
-      <c r="G198" s="15"/>
-      <c r="H198" s="48"/>
+      <c r="F198" s="32"/>
+      <c r="G198" s="63"/>
+      <c r="H198" s="35"/>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="61" t="s">
+      <c r="A199" s="47" t="s">
         <v>390</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="C199" s="54">
+      <c r="C199" s="41">
         <v>37</v>
       </c>
-      <c r="D199" s="54" t="s">
+      <c r="D199" s="41" t="s">
         <v>382</v>
       </c>
       <c r="E199" s="10"/>
-      <c r="F199" s="55"/>
-      <c r="G199" s="56"/>
-      <c r="H199" s="48"/>
+      <c r="F199" s="42"/>
+      <c r="G199" s="64">
+        <v>37</v>
+      </c>
+      <c r="H199" s="35"/>
     </row>
     <row r="200" spans="1:8" ht="15.75">
-      <c r="A200" s="62" t="s">
+      <c r="A200" s="48" t="s">
         <v>394</v>
       </c>
-      <c r="B200" s="64" t="s">
+      <c r="B200" s="50" t="s">
         <v>407</v>
       </c>
       <c r="C200" s="5" t="s">
@@ -6210,12 +6229,12 @@
         <v>382</v>
       </c>
       <c r="E200" s="10"/>
-      <c r="F200" s="58"/>
-      <c r="G200" s="15"/>
-      <c r="H200" s="48"/>
+      <c r="F200" s="44"/>
+      <c r="G200" s="63"/>
+      <c r="H200" s="35"/>
     </row>
     <row r="201" spans="1:8" ht="15.75">
-      <c r="A201" s="62" t="s">
+      <c r="A201" s="48" t="s">
         <v>395</v>
       </c>
       <c r="B201" s="1" t="s">
@@ -6228,8 +6247,10 @@
         <v>382</v>
       </c>
       <c r="E201" s="10"/>
-      <c r="F201" s="57"/>
-      <c r="G201" s="15"/>
+      <c r="F201" s="43"/>
+      <c r="G201" s="63">
+        <v>14</v>
+      </c>
       <c r="H201" s="8"/>
     </row>
   </sheetData>
@@ -6239,6 +6260,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -6382,15 +6412,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -6398,13 +6419,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>

--- a/MC3020_E24.xlsx
+++ b/MC3020_E24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0750CB54-5456-40D3-B875-49C42517A11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F82B06-FBC7-48A4-8CE8-D126A3C213A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="409">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1256,7 +1256,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1307,11 +1307,6 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Palatino Linotype"/>
       <family val="1"/>
@@ -1344,65 +1339,37 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <name val="Palatino Linotype"/>
+      <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Palatino Linotype"/>
-      <family val="1"/>
+      <sz val="11"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1755,184 +1722,173 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="10" borderId="10" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="20" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="14" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2260,3981 +2216,4361 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="38">
+      <c r="C2" s="31">
         <v>24</v>
       </c>
-      <c r="D2" s="39">
+      <c r="D2" s="32">
         <v>54</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="35">
+      <c r="E2" s="33"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="34">
+        <v>77</v>
+      </c>
+      <c r="H2" s="61">
         <v>65.217391300000003</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="38">
+      <c r="C3" s="31">
         <v>39</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="32">
         <v>75</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="35">
+      <c r="E3" s="35"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="36">
+        <v>76</v>
+      </c>
+      <c r="H3" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="38">
+      <c r="C4" s="31">
         <v>43</v>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="31">
         <v>71</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="35">
+      <c r="E4" s="37"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="38">
+        <v>57</v>
+      </c>
+      <c r="H4" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="31">
         <v>30</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="31">
         <v>38</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="35">
+      <c r="E5" s="35"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="38">
+        <v>34</v>
+      </c>
+      <c r="H5" s="61">
         <v>30.434782599999998</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="31">
         <v>18</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="31">
         <v>37</v>
       </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="35">
+      <c r="E6" s="35"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="38">
+        <v>48</v>
+      </c>
+      <c r="H6" s="61">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="31">
         <v>12</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="32">
         <v>34</v>
       </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="35">
+      <c r="E7" s="35"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="38">
+        <v>54</v>
+      </c>
+      <c r="H7" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="31">
         <v>69</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="32">
         <v>83</v>
       </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="35">
+      <c r="E8" s="35"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="38">
+        <v>76</v>
+      </c>
+      <c r="H8" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="31">
         <v>43</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="32">
         <v>68</v>
       </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="35">
+      <c r="E9" s="35"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="38">
+        <v>59</v>
+      </c>
+      <c r="H9" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="10" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="31">
         <v>38</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="31">
         <v>55</v>
       </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="35">
+      <c r="E10" s="35"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="38">
+        <v>61</v>
+      </c>
+      <c r="H10" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="10" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="31">
         <v>16</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="32">
         <v>28</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="35">
+      <c r="E11" s="35"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="38">
+        <v>24</v>
+      </c>
+      <c r="H11" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="31">
         <v>84</v>
       </c>
-      <c r="D12" s="38">
+      <c r="D12" s="31">
         <v>59</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="35">
+      <c r="E12" s="35"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="38">
+        <v>60</v>
+      </c>
+      <c r="H12" s="61">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="10" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="31">
         <v>39</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="32">
         <v>43</v>
       </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="35">
+      <c r="E13" s="35"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="38">
+        <v>55</v>
+      </c>
+      <c r="H13" s="61">
         <v>90.909090899999995</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="10" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="31">
         <v>61</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="31">
         <v>89</v>
       </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="35">
+      <c r="E14" s="35"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="38">
+        <v>76</v>
+      </c>
+      <c r="H14" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="31">
         <v>80</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="32">
         <v>42</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="35">
+      <c r="E15" s="35"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="38">
+        <v>55</v>
+      </c>
+      <c r="H15" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="10" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="31">
         <v>33</v>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="31">
         <v>46</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="35">
+      <c r="E16" s="33"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="39">
+        <v>56</v>
+      </c>
+      <c r="H16" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="10" t="s">
         <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="31">
         <v>45</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="32">
         <v>68</v>
       </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="53"/>
-      <c r="H17" s="35">
+      <c r="E17" s="35"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="38">
+        <v>87</v>
+      </c>
+      <c r="H17" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="38">
+      <c r="C18" s="31">
         <v>52</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="31">
         <v>54</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="35">
+      <c r="E18" s="35"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="38">
+        <v>75</v>
+      </c>
+      <c r="H18" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="10" t="s">
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="31">
         <v>86</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="31">
         <v>94</v>
       </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="35">
+      <c r="E19" s="35"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="38">
+        <v>83</v>
+      </c>
+      <c r="H19" s="61">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="10" t="s">
         <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="38">
+      <c r="C20" s="31">
         <v>76</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="31">
         <v>78</v>
       </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="35">
+      <c r="E20" s="35"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="38">
+        <v>63</v>
+      </c>
+      <c r="H20" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="38">
+      <c r="C21" s="31">
         <v>99</v>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="31">
         <v>84</v>
       </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="35">
+      <c r="E21" s="35"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="38">
+        <v>74</v>
+      </c>
+      <c r="H21" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="10" t="s">
         <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="31">
         <v>34</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="32">
         <v>51</v>
       </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="35">
+      <c r="E22" s="35"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="38">
+        <v>38</v>
+      </c>
+      <c r="H22" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="10" t="s">
         <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="38">
+      <c r="C23" s="31">
         <v>71</v>
       </c>
-      <c r="D23" s="39">
+      <c r="D23" s="32">
         <v>87</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="35">
+      <c r="E23" s="35"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="38">
+        <v>76</v>
+      </c>
+      <c r="H23" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="38">
+      <c r="C24" s="31">
         <v>64</v>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="32">
         <v>40</v>
       </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="35">
+      <c r="E24" s="35"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="38">
+        <v>44</v>
+      </c>
+      <c r="H24" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="31" t="s">
         <v>382</v>
       </c>
-      <c r="D25" s="39">
+      <c r="D25" s="32">
         <v>63</v>
       </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="35">
+      <c r="E25" s="35"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="38">
+        <v>67</v>
+      </c>
+      <c r="H25" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="10" t="s">
         <v>57</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="38">
+      <c r="C26" s="31">
         <v>68</v>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="32">
         <v>73</v>
       </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="35">
+      <c r="E26" s="35"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="38">
+        <v>71</v>
+      </c>
+      <c r="H26" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="38">
+      <c r="C27" s="31">
         <v>43</v>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="31">
         <v>72</v>
       </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="35">
+      <c r="E27" s="35"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="38">
+        <v>82</v>
+      </c>
+      <c r="H27" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="10" t="s">
         <v>61</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="38">
+      <c r="C28" s="31">
         <v>30</v>
       </c>
-      <c r="D28" s="39">
+      <c r="D28" s="32">
         <v>85</v>
       </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="35">
+      <c r="E28" s="35"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="38">
+        <v>62</v>
+      </c>
+      <c r="H28" s="61">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="10" t="s">
         <v>63</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="38">
+      <c r="C29" s="31">
         <v>65</v>
       </c>
-      <c r="D29" s="39">
+      <c r="D29" s="32">
         <v>84</v>
       </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="35">
+      <c r="E29" s="35"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="38">
+        <v>75</v>
+      </c>
+      <c r="H29" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="38">
+      <c r="C30" s="31">
         <v>69</v>
       </c>
-      <c r="D30" s="39">
+      <c r="D30" s="32">
         <v>25</v>
       </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="35">
+      <c r="E30" s="35"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="38">
+        <v>63</v>
+      </c>
+      <c r="H30" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="10" t="s">
         <v>67</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="38">
+      <c r="C31" s="31">
         <v>44</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="32">
         <v>34</v>
       </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="35">
+      <c r="E31" s="35"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="40">
+        <v>61</v>
+      </c>
+      <c r="H31" s="61">
         <v>47.826087000000001</v>
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="10" t="s">
         <v>69</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="38">
+      <c r="C32" s="31">
         <v>61</v>
       </c>
-      <c r="D32" s="39">
+      <c r="D32" s="32">
         <v>85</v>
       </c>
-      <c r="E32" s="15"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="35">
+      <c r="E32" s="35"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="38">
+        <v>81</v>
+      </c>
+      <c r="H32" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="38">
+      <c r="C33" s="31">
         <v>49</v>
       </c>
-      <c r="D33" s="39">
+      <c r="D33" s="32">
         <v>67</v>
       </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="35">
+      <c r="E33" s="35"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="38">
+        <v>71</v>
+      </c>
+      <c r="H33" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="10" t="s">
         <v>73</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="38">
+      <c r="C34" s="31">
         <v>50</v>
       </c>
-      <c r="D34" s="39">
+      <c r="D34" s="32">
         <v>45</v>
       </c>
-      <c r="E34" s="15"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="35">
+      <c r="E34" s="35"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="38">
+        <v>43</v>
+      </c>
+      <c r="H34" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="10" t="s">
         <v>75</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="38">
+      <c r="C35" s="31">
         <v>48</v>
       </c>
-      <c r="D35" s="38">
+      <c r="D35" s="31">
         <v>55</v>
       </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="35">
+      <c r="E35" s="35"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="38">
+        <v>56</v>
+      </c>
+      <c r="H35" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="10" t="s">
         <v>77</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="38">
+      <c r="C36" s="31">
         <v>49</v>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="32">
         <v>57</v>
       </c>
-      <c r="E36" s="15"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="53"/>
-      <c r="H36" s="35">
+      <c r="E36" s="35"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="38">
+        <v>49</v>
+      </c>
+      <c r="H36" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="10" t="s">
         <v>79</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="38">
+      <c r="C37" s="31">
         <v>58</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="32">
         <v>41</v>
       </c>
-      <c r="E37" s="15"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="35">
+      <c r="E37" s="35"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="38">
+        <v>54</v>
+      </c>
+      <c r="H37" s="61">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="10" t="s">
         <v>81</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="38">
+      <c r="C38" s="31">
         <v>81</v>
       </c>
-      <c r="D38" s="39">
+      <c r="D38" s="32">
         <v>84</v>
       </c>
-      <c r="E38" s="15"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="35">
+      <c r="E38" s="35"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="38">
+        <v>72</v>
+      </c>
+      <c r="H38" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="10" t="s">
         <v>83</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="38">
+      <c r="C39" s="31">
         <v>23</v>
       </c>
-      <c r="D39" s="39">
+      <c r="D39" s="32">
         <v>61</v>
       </c>
-      <c r="E39" s="15"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="53"/>
-      <c r="H39" s="35">
+      <c r="E39" s="35"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="38">
+        <v>58</v>
+      </c>
+      <c r="H39" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="10" t="s">
         <v>85</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="38">
+      <c r="C40" s="31">
         <v>32</v>
       </c>
-      <c r="D40" s="38">
+      <c r="D40" s="31">
         <v>37</v>
       </c>
-      <c r="E40" s="15"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="53"/>
-      <c r="H40" s="35">
+      <c r="E40" s="35"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="38">
+        <v>57</v>
+      </c>
+      <c r="H40" s="61">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="10" t="s">
         <v>87</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="38">
+      <c r="C41" s="31">
         <v>18</v>
       </c>
-      <c r="D41" s="38">
+      <c r="D41" s="31">
         <v>52</v>
       </c>
-      <c r="E41" s="15"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="53"/>
-      <c r="H41" s="35">
+      <c r="E41" s="35"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="38">
+        <v>37</v>
+      </c>
+      <c r="H41" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="10" t="s">
         <v>89</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="38">
+      <c r="C42" s="31">
         <v>46</v>
       </c>
-      <c r="D42" s="39">
+      <c r="D42" s="32">
         <v>75</v>
       </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="35">
+      <c r="E42" s="35"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="38">
+        <v>67</v>
+      </c>
+      <c r="H42" s="61">
         <v>56.521739100000005</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="10" t="s">
         <v>91</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="38">
+      <c r="C43" s="31">
         <v>53</v>
       </c>
-      <c r="D43" s="38">
+      <c r="D43" s="31">
         <v>50</v>
       </c>
-      <c r="E43" s="15"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="53"/>
-      <c r="H43" s="35">
+      <c r="E43" s="35"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="38">
+        <v>69</v>
+      </c>
+      <c r="H43" s="61">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="10" t="s">
         <v>93</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="38">
+      <c r="C44" s="31">
         <v>60</v>
       </c>
-      <c r="D44" s="38">
+      <c r="D44" s="31">
         <v>39</v>
       </c>
-      <c r="E44" s="15"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="35">
+      <c r="E44" s="35"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="38">
+        <v>35</v>
+      </c>
+      <c r="H44" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="10" t="s">
         <v>95</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C45" s="38">
+      <c r="C45" s="31">
         <v>58</v>
       </c>
-      <c r="D45" s="39">
+      <c r="D45" s="32">
         <v>79</v>
       </c>
-      <c r="E45" s="15"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="35">
+      <c r="E45" s="35"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="38">
+        <v>72</v>
+      </c>
+      <c r="H45" s="61">
         <v>56.521739100000005</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="10" t="s">
         <v>97</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C46" s="38">
+      <c r="C46" s="31">
         <v>60</v>
       </c>
-      <c r="D46" s="38">
+      <c r="D46" s="31">
         <v>70</v>
       </c>
-      <c r="E46" s="15"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="53"/>
-      <c r="H46" s="35">
+      <c r="E46" s="35"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="38">
+        <v>45</v>
+      </c>
+      <c r="H46" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="10" t="s">
         <v>99</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="38">
+      <c r="C47" s="31">
         <v>18</v>
       </c>
-      <c r="D47" s="39">
+      <c r="D47" s="32">
         <v>64</v>
       </c>
-      <c r="E47" s="15"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="35">
+      <c r="E47" s="35"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="38">
+        <v>55</v>
+      </c>
+      <c r="H47" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="10" t="s">
         <v>101</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="38">
+      <c r="C48" s="31">
         <v>77</v>
       </c>
-      <c r="D48" s="39">
+      <c r="D48" s="32">
         <v>64</v>
       </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="55"/>
-      <c r="H48" s="35">
+      <c r="E48" s="35"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="40">
+        <v>64</v>
+      </c>
+      <c r="H48" s="61">
         <v>21.739130400000001</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="10" t="s">
         <v>103</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="38">
+      <c r="C49" s="31">
         <v>36</v>
       </c>
-      <c r="D49" s="39">
+      <c r="D49" s="32">
         <v>81</v>
       </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="35">
+      <c r="E49" s="35"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="38">
+        <v>39</v>
+      </c>
+      <c r="H49" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="10" t="s">
         <v>105</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="38">
+      <c r="C50" s="31">
         <v>47</v>
       </c>
-      <c r="D50" s="39">
+      <c r="D50" s="32">
         <v>63</v>
       </c>
-      <c r="E50" s="15"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="35">
+      <c r="E50" s="35"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="38">
+        <v>68</v>
+      </c>
+      <c r="H50" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="10" t="s">
         <v>107</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="38">
+      <c r="C51" s="31">
         <v>59</v>
       </c>
-      <c r="D51" s="38">
+      <c r="D51" s="31">
         <v>90</v>
       </c>
-      <c r="E51" s="15"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="53"/>
-      <c r="H51" s="35">
+      <c r="E51" s="35"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="38">
+        <v>67</v>
+      </c>
+      <c r="H51" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="10" t="s">
         <v>109</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="38">
+      <c r="C52" s="31">
         <v>68</v>
       </c>
-      <c r="D52" s="38">
+      <c r="D52" s="31">
         <v>42</v>
       </c>
-      <c r="E52" s="15"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="53"/>
-      <c r="H52" s="35">
+      <c r="E52" s="35"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="38">
+        <v>41</v>
+      </c>
+      <c r="H52" s="61">
         <v>47.826087000000001</v>
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="10" t="s">
         <v>111</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C53" s="38">
+      <c r="C53" s="31">
         <v>41</v>
       </c>
-      <c r="D53" s="39">
+      <c r="D53" s="32">
         <v>60</v>
       </c>
-      <c r="E53" s="15"/>
-      <c r="F53" s="24"/>
-      <c r="G53" s="53"/>
-      <c r="H53" s="35">
+      <c r="E53" s="35"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="38">
+        <v>39</v>
+      </c>
+      <c r="H53" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="10" t="s">
         <v>113</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="38">
+      <c r="C54" s="31">
         <v>54</v>
       </c>
-      <c r="D54" s="38">
+      <c r="D54" s="31">
         <v>76</v>
       </c>
-      <c r="E54" s="15"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="53"/>
-      <c r="H54" s="35">
+      <c r="E54" s="35"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="38">
+        <v>68</v>
+      </c>
+      <c r="H54" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="10" t="s">
         <v>115</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="38">
+      <c r="C55" s="31">
         <v>51</v>
       </c>
-      <c r="D55" s="39">
+      <c r="D55" s="32">
         <v>89</v>
       </c>
-      <c r="E55" s="15"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="55"/>
-      <c r="H55" s="35">
+      <c r="E55" s="35"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="40">
+        <v>84</v>
+      </c>
+      <c r="H55" s="61">
         <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="10" t="s">
         <v>117</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C56" s="38">
+      <c r="C56" s="31">
         <v>100</v>
       </c>
-      <c r="D56" s="39">
+      <c r="D56" s="32">
         <v>96</v>
       </c>
-      <c r="E56" s="15"/>
-      <c r="F56" s="24"/>
-      <c r="G56" s="53"/>
-      <c r="H56" s="35">
+      <c r="E56" s="35"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="38">
+        <v>63</v>
+      </c>
+      <c r="H56" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="10" t="s">
         <v>119</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="38">
+      <c r="C57" s="31">
         <v>21</v>
       </c>
-      <c r="D57" s="39">
+      <c r="D57" s="32">
         <v>37</v>
       </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="53"/>
-      <c r="H57" s="35">
+      <c r="E57" s="35"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="38">
+        <v>49</v>
+      </c>
+      <c r="H57" s="61">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="10" t="s">
         <v>121</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C58" s="38">
+      <c r="C58" s="31">
         <v>32</v>
       </c>
-      <c r="D58" s="38">
+      <c r="D58" s="31">
         <v>20</v>
       </c>
-      <c r="E58" s="15"/>
-      <c r="F58" s="24"/>
-      <c r="G58" s="53"/>
-      <c r="H58" s="35">
+      <c r="E58" s="35"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="38">
+        <v>28</v>
+      </c>
+      <c r="H58" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="10" t="s">
         <v>123</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="38">
+      <c r="C59" s="31">
         <v>23</v>
       </c>
-      <c r="D59" s="39">
+      <c r="D59" s="32">
         <v>36</v>
       </c>
-      <c r="E59" s="15"/>
-      <c r="F59" s="24"/>
-      <c r="G59" s="53"/>
-      <c r="H59" s="35">
+      <c r="E59" s="35"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="38">
+        <v>44</v>
+      </c>
+      <c r="H59" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="10" t="s">
         <v>125</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C60" s="38">
+      <c r="C60" s="31">
         <v>42</v>
       </c>
-      <c r="D60" s="39">
+      <c r="D60" s="32">
         <v>28</v>
       </c>
-      <c r="E60" s="16"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="54"/>
-      <c r="H60" s="35">
+      <c r="E60" s="33"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="39">
+        <v>60</v>
+      </c>
+      <c r="H60" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="38">
+      <c r="C61" s="31">
         <v>58</v>
       </c>
-      <c r="D61" s="39">
+      <c r="D61" s="32">
         <v>68</v>
       </c>
-      <c r="E61" s="15"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="53"/>
-      <c r="H61" s="35">
+      <c r="E61" s="35"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="38">
+        <v>86</v>
+      </c>
+      <c r="H61" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="10" t="s">
         <v>129</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C62" s="38">
+      <c r="C62" s="31">
         <v>64</v>
       </c>
-      <c r="D62" s="39" t="s">
+      <c r="D62" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="E62" s="15"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="53"/>
-      <c r="H62" s="35">
+      <c r="E62" s="35"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="38">
+        <v>52</v>
+      </c>
+      <c r="H62" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="10" t="s">
         <v>131</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C63" s="38">
+      <c r="C63" s="31">
         <v>54</v>
       </c>
-      <c r="D63" s="39">
+      <c r="D63" s="32">
         <v>57</v>
       </c>
-      <c r="E63" s="15"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="53"/>
-      <c r="H63" s="35">
+      <c r="E63" s="35"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="38">
+        <v>64</v>
+      </c>
+      <c r="H63" s="61">
         <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C64" s="38">
+      <c r="C64" s="31">
         <v>30</v>
       </c>
-      <c r="D64" s="39">
+      <c r="D64" s="32">
         <v>40</v>
       </c>
-      <c r="E64" s="15"/>
-      <c r="F64" s="24"/>
-      <c r="G64" s="53"/>
-      <c r="H64" s="35">
+      <c r="E64" s="35"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="38">
+        <v>46</v>
+      </c>
+      <c r="H64" s="61">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="38">
+      <c r="C65" s="31">
         <v>30</v>
       </c>
-      <c r="D65" s="39">
+      <c r="D65" s="32">
         <v>48</v>
       </c>
-      <c r="E65" s="15"/>
-      <c r="F65" s="24"/>
-      <c r="G65" s="53"/>
-      <c r="H65" s="35">
+      <c r="E65" s="35"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="38">
+        <v>47</v>
+      </c>
+      <c r="H65" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C66" s="38">
+      <c r="C66" s="31">
         <v>47</v>
       </c>
-      <c r="D66" s="39">
+      <c r="D66" s="32">
         <v>84</v>
       </c>
-      <c r="E66" s="15"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="53"/>
-      <c r="H66" s="35">
+      <c r="E66" s="35"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="38">
+        <v>54</v>
+      </c>
+      <c r="H66" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C67" s="38">
+      <c r="C67" s="31">
         <v>38</v>
       </c>
-      <c r="D67" s="39">
+      <c r="D67" s="32">
         <v>50</v>
       </c>
-      <c r="E67" s="15"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="53"/>
-      <c r="H67" s="35">
+      <c r="E67" s="35"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="38">
+        <v>27</v>
+      </c>
+      <c r="H67" s="61">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="10" t="s">
         <v>141</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C68" s="38">
+      <c r="C68" s="31">
         <v>47</v>
       </c>
-      <c r="D68" s="39">
+      <c r="D68" s="32">
         <v>73</v>
       </c>
-      <c r="E68" s="15"/>
-      <c r="F68" s="24"/>
-      <c r="G68" s="55"/>
-      <c r="H68" s="35">
+      <c r="E68" s="35"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="40">
+        <v>62</v>
+      </c>
+      <c r="H68" s="61">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="10" t="s">
         <v>143</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C69" s="38">
+      <c r="C69" s="31">
         <v>36</v>
       </c>
-      <c r="D69" s="38">
+      <c r="D69" s="31">
         <v>17</v>
       </c>
-      <c r="E69" s="15"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="53"/>
-      <c r="H69" s="35">
+      <c r="E69" s="35"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="38">
+        <v>28</v>
+      </c>
+      <c r="H69" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="10" t="s">
         <v>145</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C70" s="38">
+      <c r="C70" s="31">
         <v>47</v>
       </c>
-      <c r="D70" s="39">
+      <c r="D70" s="32">
         <v>60</v>
       </c>
-      <c r="E70" s="15"/>
-      <c r="F70" s="24"/>
-      <c r="G70" s="53"/>
-      <c r="H70" s="35">
+      <c r="E70" s="35"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="38">
+        <v>37</v>
+      </c>
+      <c r="H70" s="61">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="10" t="s">
         <v>147</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C71" s="38">
+      <c r="C71" s="31">
         <v>43</v>
       </c>
-      <c r="D71" s="38">
+      <c r="D71" s="31">
         <v>74</v>
       </c>
-      <c r="E71" s="15"/>
-      <c r="F71" s="24"/>
-      <c r="G71" s="53"/>
-      <c r="H71" s="35">
+      <c r="E71" s="35"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="38">
+        <v>58</v>
+      </c>
+      <c r="H71" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="10" t="s">
         <v>149</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C72" s="38">
+      <c r="C72" s="31">
         <v>46</v>
       </c>
-      <c r="D72" s="38">
+      <c r="D72" s="31">
         <v>68</v>
       </c>
-      <c r="E72" s="15"/>
-      <c r="F72" s="24"/>
-      <c r="G72" s="53"/>
-      <c r="H72" s="35">
+      <c r="E72" s="35"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="38">
+        <v>26</v>
+      </c>
+      <c r="H72" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="10" t="s">
         <v>151</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C73" s="38">
+      <c r="C73" s="31">
         <v>51</v>
       </c>
-      <c r="D73" s="39">
+      <c r="D73" s="32">
         <v>80</v>
       </c>
-      <c r="E73" s="15"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="55"/>
-      <c r="H73" s="35">
+      <c r="E73" s="35"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="40">
+        <v>77</v>
+      </c>
+      <c r="H73" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="10" t="s">
         <v>153</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C74" s="38">
+      <c r="C74" s="31">
         <v>73</v>
       </c>
-      <c r="D74" s="39">
+      <c r="D74" s="32">
         <v>58</v>
       </c>
-      <c r="E74" s="15"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="53"/>
-      <c r="H74" s="35">
+      <c r="E74" s="35"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="38">
+        <v>60</v>
+      </c>
+      <c r="H74" s="61">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="10" t="s">
         <v>155</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C75" s="38">
+      <c r="C75" s="31">
         <v>0</v>
       </c>
-      <c r="D75" s="38">
+      <c r="D75" s="31">
         <v>60</v>
       </c>
-      <c r="E75" s="15"/>
-      <c r="F75" s="24"/>
-      <c r="G75" s="53"/>
-      <c r="H75" s="35">
+      <c r="E75" s="35"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="38">
+        <v>58</v>
+      </c>
+      <c r="H75" s="61">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="10" t="s">
         <v>157</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C76" s="38">
+      <c r="C76" s="31">
         <v>55</v>
       </c>
-      <c r="D76" s="39">
+      <c r="D76" s="32">
         <v>44</v>
       </c>
-      <c r="E76" s="15"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="53"/>
-      <c r="H76" s="35">
+      <c r="E76" s="35"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="38">
+        <v>47</v>
+      </c>
+      <c r="H76" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="10" t="s">
         <v>159</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C77" s="38">
+      <c r="C77" s="31">
         <v>56</v>
       </c>
-      <c r="D77" s="39">
+      <c r="D77" s="32">
         <v>48</v>
       </c>
-      <c r="E77" s="15"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="53"/>
-      <c r="H77" s="35">
+      <c r="E77" s="35"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="38">
+        <v>59</v>
+      </c>
+      <c r="H77" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="10" t="s">
         <v>161</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C78" s="38">
+      <c r="C78" s="31">
         <v>35</v>
       </c>
-      <c r="D78" s="38">
+      <c r="D78" s="31">
         <v>68</v>
       </c>
-      <c r="E78" s="15"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="53"/>
-      <c r="H78" s="35">
+      <c r="E78" s="35"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="38">
+        <v>77</v>
+      </c>
+      <c r="H78" s="61">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="10" t="s">
         <v>163</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C79" s="38">
+      <c r="C79" s="31">
         <v>32</v>
       </c>
-      <c r="D79" s="39">
+      <c r="D79" s="32">
         <v>41</v>
       </c>
-      <c r="E79" s="15"/>
-      <c r="F79" s="24"/>
-      <c r="G79" s="53"/>
-      <c r="H79" s="35">
+      <c r="E79" s="35"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="38">
+        <v>49</v>
+      </c>
+      <c r="H79" s="61">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="10" t="s">
         <v>165</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C80" s="38">
+      <c r="C80" s="31">
         <v>71</v>
       </c>
-      <c r="D80" s="39">
+      <c r="D80" s="32">
         <v>56</v>
       </c>
-      <c r="E80" s="15"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="35">
+      <c r="E80" s="35"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="38">
+        <v>51</v>
+      </c>
+      <c r="H80" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="13" t="s">
+      <c r="A81" s="10" t="s">
         <v>167</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C81" s="38">
+      <c r="C81" s="31">
         <v>56</v>
       </c>
-      <c r="D81" s="39">
+      <c r="D81" s="32">
         <v>63</v>
       </c>
-      <c r="E81" s="15"/>
-      <c r="F81" s="24"/>
-      <c r="G81" s="53"/>
-      <c r="H81" s="35">
+      <c r="E81" s="35"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="38">
+        <v>64</v>
+      </c>
+      <c r="H81" s="61">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="13" t="s">
+      <c r="A82" s="10" t="s">
         <v>169</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C82" s="38">
+      <c r="C82" s="31">
         <v>52</v>
       </c>
-      <c r="D82" s="39">
+      <c r="D82" s="32">
         <v>30</v>
       </c>
-      <c r="E82" s="15"/>
-      <c r="F82" s="24"/>
-      <c r="G82" s="53"/>
-      <c r="H82" s="35">
+      <c r="E82" s="35"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="38">
+        <v>32</v>
+      </c>
+      <c r="H82" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="10" t="s">
         <v>171</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C83" s="38">
+      <c r="C83" s="31">
         <v>34</v>
       </c>
-      <c r="D83" s="39">
+      <c r="D83" s="32">
         <v>85</v>
       </c>
-      <c r="E83" s="15"/>
-      <c r="F83" s="24"/>
-      <c r="G83" s="55"/>
-      <c r="H83" s="35">
+      <c r="E83" s="35"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="40">
+        <v>57</v>
+      </c>
+      <c r="H83" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="10" t="s">
         <v>173</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C84" s="38">
+      <c r="C84" s="31">
         <v>42</v>
       </c>
-      <c r="D84" s="38">
+      <c r="D84" s="31">
         <v>34</v>
       </c>
-      <c r="E84" s="15"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="53"/>
-      <c r="H84" s="35">
+      <c r="E84" s="35"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="38">
+        <v>44</v>
+      </c>
+      <c r="H84" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="13" t="s">
+      <c r="A85" s="10" t="s">
         <v>175</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C85" s="38">
+      <c r="C85" s="31">
         <v>51</v>
       </c>
-      <c r="D85" s="38">
+      <c r="D85" s="31">
         <v>67</v>
       </c>
-      <c r="E85" s="16"/>
-      <c r="F85" s="25"/>
-      <c r="G85" s="54"/>
-      <c r="H85" s="35">
+      <c r="E85" s="33"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="39">
+        <v>58</v>
+      </c>
+      <c r="H85" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="13" t="s">
+      <c r="A86" s="10" t="s">
         <v>177</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C86" s="38">
+      <c r="C86" s="31">
         <v>17</v>
       </c>
-      <c r="D86" s="39">
+      <c r="D86" s="32">
         <v>49</v>
       </c>
-      <c r="E86" s="15"/>
-      <c r="F86" s="24"/>
-      <c r="G86" s="53"/>
-      <c r="H86" s="35">
+      <c r="E86" s="35"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="38">
+        <v>64</v>
+      </c>
+      <c r="H86" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="13" t="s">
+      <c r="A87" s="10" t="s">
         <v>179</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C87" s="38">
+      <c r="C87" s="31">
         <v>34</v>
       </c>
-      <c r="D87" s="39">
+      <c r="D87" s="32">
         <v>58</v>
       </c>
-      <c r="E87" s="15"/>
-      <c r="F87" s="24"/>
-      <c r="G87" s="53"/>
-      <c r="H87" s="35">
+      <c r="E87" s="35"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="38">
+        <v>58</v>
+      </c>
+      <c r="H87" s="61">
         <v>56.521739100000005</v>
       </c>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="10" t="s">
         <v>181</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="38">
+      <c r="C88" s="31">
         <v>60</v>
       </c>
-      <c r="D88" s="39">
+      <c r="D88" s="32">
         <v>47</v>
       </c>
-      <c r="E88" s="15"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="53"/>
-      <c r="H88" s="35">
+      <c r="E88" s="35"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="38">
+        <v>81</v>
+      </c>
+      <c r="H88" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="10" t="s">
         <v>183</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C89" s="38">
+      <c r="C89" s="31">
         <v>29</v>
       </c>
-      <c r="D89" s="39">
+      <c r="D89" s="32">
         <v>58</v>
       </c>
-      <c r="E89" s="15"/>
-      <c r="F89" s="24"/>
-      <c r="G89" s="53"/>
-      <c r="H89" s="35">
+      <c r="E89" s="35"/>
+      <c r="F89" s="13"/>
+      <c r="G89" s="38">
+        <v>75</v>
+      </c>
+      <c r="H89" s="61">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="10" t="s">
         <v>185</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C90" s="38">
+      <c r="C90" s="31">
         <v>25</v>
       </c>
-      <c r="D90" s="39">
+      <c r="D90" s="32">
         <v>84</v>
       </c>
-      <c r="E90" s="15"/>
-      <c r="F90" s="24"/>
-      <c r="G90" s="55"/>
-      <c r="H90" s="35">
+      <c r="E90" s="35"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="40">
+        <v>54</v>
+      </c>
+      <c r="H90" s="61">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="13" t="s">
+      <c r="A91" s="10" t="s">
         <v>187</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C91" s="38">
+      <c r="C91" s="31">
         <v>33</v>
       </c>
-      <c r="D91" s="38">
+      <c r="D91" s="31">
         <v>66</v>
       </c>
-      <c r="E91" s="15"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="53"/>
-      <c r="H91" s="35">
+      <c r="E91" s="35"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="38">
+        <v>58</v>
+      </c>
+      <c r="H91" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="13" t="s">
+      <c r="A92" s="10" t="s">
         <v>189</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="38">
+      <c r="C92" s="31">
         <v>43</v>
       </c>
-      <c r="D92" s="38">
+      <c r="D92" s="31">
         <v>48</v>
       </c>
-      <c r="E92" s="15"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="53"/>
-      <c r="H92" s="35">
+      <c r="E92" s="35"/>
+      <c r="F92" s="13"/>
+      <c r="G92" s="38">
+        <v>40</v>
+      </c>
+      <c r="H92" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="13" t="s">
+      <c r="A93" s="10" t="s">
         <v>191</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C93" s="38">
+      <c r="C93" s="31">
         <v>24</v>
       </c>
-      <c r="D93" s="39" t="s">
+      <c r="D93" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="E93" s="15"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="53"/>
-      <c r="H93" s="35">
+      <c r="E93" s="35"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="38">
+        <v>46</v>
+      </c>
+      <c r="H93" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="13" t="s">
+      <c r="A94" s="10" t="s">
         <v>193</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C94" s="38">
+      <c r="C94" s="31">
         <v>57</v>
       </c>
-      <c r="D94" s="38">
+      <c r="D94" s="31">
         <v>55</v>
       </c>
-      <c r="E94" s="15"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="53"/>
-      <c r="H94" s="35">
+      <c r="E94" s="35"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="38">
+        <v>41</v>
+      </c>
+      <c r="H94" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="13" t="s">
+      <c r="A95" s="10" t="s">
         <v>195</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C95" s="38">
+      <c r="C95" s="31">
         <v>93</v>
       </c>
-      <c r="D95" s="39">
+      <c r="D95" s="32">
         <v>87</v>
       </c>
-      <c r="E95" s="15"/>
-      <c r="F95" s="24"/>
-      <c r="G95" s="53"/>
-      <c r="H95" s="35">
+      <c r="E95" s="35"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="38">
+        <v>84</v>
+      </c>
+      <c r="H95" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="13" t="s">
+      <c r="A96" s="10" t="s">
         <v>197</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="38">
+      <c r="C96" s="31">
         <v>65</v>
       </c>
-      <c r="D96" s="39">
+      <c r="D96" s="32">
         <v>79</v>
       </c>
-      <c r="E96" s="16"/>
-      <c r="F96" s="25"/>
-      <c r="G96" s="54"/>
-      <c r="H96" s="35">
+      <c r="E96" s="33"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="39">
+        <v>75</v>
+      </c>
+      <c r="H96" s="61">
         <v>65.217391300000003</v>
       </c>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="13" t="s">
+      <c r="A97" s="10" t="s">
         <v>199</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="38">
+      <c r="C97" s="31">
         <v>26</v>
       </c>
-      <c r="D97" s="39">
+      <c r="D97" s="32">
         <v>63</v>
       </c>
-      <c r="E97" s="15"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="53"/>
-      <c r="H97" s="35">
+      <c r="E97" s="35"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="38">
+        <v>46</v>
+      </c>
+      <c r="H97" s="61">
         <v>56.521739100000005</v>
       </c>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="13" t="s">
+      <c r="A98" s="10" t="s">
         <v>201</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="38">
+      <c r="C98" s="31">
         <v>13</v>
       </c>
-      <c r="D98" s="40">
+      <c r="D98" s="41">
         <v>52</v>
       </c>
-      <c r="E98" s="15"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="53"/>
-      <c r="H98" s="35">
+      <c r="E98" s="35"/>
+      <c r="F98" s="13"/>
+      <c r="G98" s="38">
+        <v>61</v>
+      </c>
+      <c r="H98" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="13" t="s">
+      <c r="A99" s="10" t="s">
         <v>203</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C99" s="38">
+      <c r="C99" s="31">
         <v>60</v>
       </c>
-      <c r="D99" s="40">
+      <c r="D99" s="41">
         <v>83</v>
       </c>
-      <c r="E99" s="15"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="55"/>
-      <c r="H99" s="35">
+      <c r="E99" s="35"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="40">
+        <v>75</v>
+      </c>
+      <c r="H99" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="13" t="s">
+      <c r="A100" s="10" t="s">
         <v>205</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="38">
+      <c r="C100" s="31">
         <v>42</v>
       </c>
-      <c r="D100" s="40">
+      <c r="D100" s="41">
         <v>48</v>
       </c>
-      <c r="E100" s="15"/>
-      <c r="F100" s="24"/>
-      <c r="G100" s="53"/>
-      <c r="H100" s="35">
+      <c r="E100" s="35"/>
+      <c r="F100" s="13"/>
+      <c r="G100" s="38">
+        <v>50</v>
+      </c>
+      <c r="H100" s="61">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="13" t="s">
+      <c r="A101" s="10" t="s">
         <v>207</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="38">
+      <c r="C101" s="31">
         <v>52</v>
       </c>
-      <c r="D101" s="40">
+      <c r="D101" s="41">
         <v>79</v>
       </c>
-      <c r="E101" s="15"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="53"/>
-      <c r="H101" s="35">
+      <c r="E101" s="35"/>
+      <c r="F101" s="13"/>
+      <c r="G101" s="38">
+        <v>47</v>
+      </c>
+      <c r="H101" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="13" t="s">
+      <c r="A102" s="10" t="s">
         <v>209</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="38">
+      <c r="C102" s="31">
         <v>60</v>
       </c>
-      <c r="D102" s="38">
+      <c r="D102" s="31">
         <v>85</v>
       </c>
-      <c r="E102" s="15"/>
-      <c r="F102" s="24"/>
-      <c r="G102" s="53"/>
-      <c r="H102" s="35">
+      <c r="E102" s="35"/>
+      <c r="F102" s="13"/>
+      <c r="G102" s="38">
+        <v>76</v>
+      </c>
+      <c r="H102" s="61">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="13" t="s">
+      <c r="A103" s="10" t="s">
         <v>211</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="38">
+      <c r="C103" s="31">
         <v>28</v>
       </c>
-      <c r="D103" s="40">
+      <c r="D103" s="41">
         <v>41</v>
       </c>
-      <c r="E103" s="15"/>
-      <c r="F103" s="24"/>
-      <c r="G103" s="53"/>
-      <c r="H103" s="35">
+      <c r="E103" s="35"/>
+      <c r="F103" s="13"/>
+      <c r="G103" s="38">
+        <v>51</v>
+      </c>
+      <c r="H103" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="13" t="s">
+      <c r="A104" s="10" t="s">
         <v>213</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C104" s="38">
+      <c r="C104" s="31">
         <v>27</v>
       </c>
-      <c r="D104" s="40">
+      <c r="D104" s="41">
         <v>74</v>
       </c>
-      <c r="E104" s="15"/>
-      <c r="F104" s="24"/>
-      <c r="G104" s="53"/>
-      <c r="H104" s="35">
+      <c r="E104" s="35"/>
+      <c r="F104" s="13"/>
+      <c r="G104" s="38">
+        <v>69</v>
+      </c>
+      <c r="H104" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="13" t="s">
+      <c r="A105" s="10" t="s">
         <v>215</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="38">
+      <c r="C105" s="31">
         <v>36</v>
       </c>
-      <c r="D105" s="40">
+      <c r="D105" s="41">
         <v>60</v>
       </c>
-      <c r="E105" s="15"/>
-      <c r="F105" s="24"/>
-      <c r="G105" s="53"/>
-      <c r="H105" s="35">
+      <c r="E105" s="35"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="38">
+        <v>72</v>
+      </c>
+      <c r="H105" s="61">
         <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="13" t="s">
+      <c r="A106" s="10" t="s">
         <v>217</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="38">
+      <c r="C106" s="31">
         <v>19</v>
       </c>
-      <c r="D106" s="40">
+      <c r="D106" s="41">
         <v>43</v>
       </c>
-      <c r="E106" s="15"/>
-      <c r="F106" s="24"/>
-      <c r="G106" s="53"/>
-      <c r="H106" s="35">
+      <c r="E106" s="35"/>
+      <c r="F106" s="13"/>
+      <c r="G106" s="38">
+        <v>9</v>
+      </c>
+      <c r="H106" s="61">
         <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="13" t="s">
+      <c r="A107" s="10" t="s">
         <v>219</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="38">
+      <c r="C107" s="31">
         <v>54</v>
       </c>
-      <c r="D107" s="40">
+      <c r="D107" s="41">
         <v>47</v>
       </c>
-      <c r="E107" s="15"/>
-      <c r="F107" s="24"/>
-      <c r="G107" s="53"/>
-      <c r="H107" s="35">
+      <c r="E107" s="35"/>
+      <c r="F107" s="13"/>
+      <c r="G107" s="38">
+        <v>49</v>
+      </c>
+      <c r="H107" s="61">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="13" t="s">
+      <c r="A108" s="10" t="s">
         <v>221</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C108" s="38">
+      <c r="C108" s="31">
         <v>46</v>
       </c>
-      <c r="D108" s="40">
+      <c r="D108" s="41">
         <v>12</v>
       </c>
-      <c r="E108" s="15"/>
-      <c r="F108" s="24"/>
-      <c r="G108" s="53"/>
-      <c r="H108" s="35">
+      <c r="E108" s="35"/>
+      <c r="F108" s="13"/>
+      <c r="G108" s="38">
+        <v>56</v>
+      </c>
+      <c r="H108" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="13" t="s">
+      <c r="A109" s="10" t="s">
         <v>223</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C109" s="38" t="s">
+      <c r="C109" s="31" t="s">
         <v>382</v>
       </c>
-      <c r="D109" s="38">
+      <c r="D109" s="31">
         <v>35</v>
       </c>
-      <c r="E109" s="15"/>
-      <c r="F109" s="24"/>
-      <c r="G109" s="53"/>
-      <c r="H109" s="35">
+      <c r="E109" s="35"/>
+      <c r="F109" s="13"/>
+      <c r="G109" s="38">
+        <v>62</v>
+      </c>
+      <c r="H109" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="13" t="s">
+      <c r="A110" s="10" t="s">
         <v>224</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C110" s="38">
+      <c r="C110" s="31">
         <v>53</v>
       </c>
-      <c r="D110" s="38" t="s">
+      <c r="D110" s="31" t="s">
         <v>382</v>
       </c>
-      <c r="E110" s="15"/>
-      <c r="F110" s="24"/>
-      <c r="G110" s="53"/>
-      <c r="H110" s="35">
+      <c r="E110" s="35"/>
+      <c r="F110" s="13"/>
+      <c r="G110" s="38">
+        <v>60</v>
+      </c>
+      <c r="H110" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="13" t="s">
+      <c r="A111" s="10" t="s">
         <v>226</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C111" s="38">
+      <c r="C111" s="31">
         <v>4</v>
       </c>
-      <c r="D111" s="38">
+      <c r="D111" s="31">
         <v>12</v>
       </c>
-      <c r="E111" s="15"/>
-      <c r="F111" s="24"/>
-      <c r="G111" s="53"/>
-      <c r="H111" s="35">
+      <c r="E111" s="35"/>
+      <c r="F111" s="13"/>
+      <c r="G111" s="38">
+        <v>11</v>
+      </c>
+      <c r="H111" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="13" t="s">
+      <c r="A112" s="10" t="s">
         <v>228</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C112" s="38">
+      <c r="C112" s="31">
         <v>71</v>
       </c>
-      <c r="D112" s="40">
+      <c r="D112" s="41">
         <v>85</v>
       </c>
-      <c r="E112" s="15"/>
-      <c r="F112" s="24"/>
-      <c r="G112" s="53"/>
-      <c r="H112" s="35">
+      <c r="E112" s="35"/>
+      <c r="F112" s="13"/>
+      <c r="G112" s="38">
+        <v>70</v>
+      </c>
+      <c r="H112" s="61">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="13" t="s">
+      <c r="A113" s="10" t="s">
         <v>230</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C113" s="38">
+      <c r="C113" s="31">
         <v>29</v>
       </c>
-      <c r="D113" s="40">
+      <c r="D113" s="41">
         <v>19</v>
       </c>
-      <c r="E113" s="15"/>
-      <c r="F113" s="24"/>
-      <c r="G113" s="53"/>
-      <c r="H113" s="35">
+      <c r="E113" s="35"/>
+      <c r="F113" s="13"/>
+      <c r="G113" s="38">
+        <v>50</v>
+      </c>
+      <c r="H113" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="13" t="s">
+      <c r="A114" s="10" t="s">
         <v>232</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C114" s="38">
+      <c r="C114" s="31">
         <v>45</v>
       </c>
-      <c r="D114" s="38">
+      <c r="D114" s="31">
         <v>75</v>
       </c>
-      <c r="E114" s="15"/>
-      <c r="F114" s="24"/>
-      <c r="G114" s="53"/>
-      <c r="H114" s="35">
+      <c r="E114" s="35"/>
+      <c r="F114" s="13"/>
+      <c r="G114" s="38">
+        <v>63</v>
+      </c>
+      <c r="H114" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="13" t="s">
+      <c r="A115" s="10" t="s">
         <v>234</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C115" s="38">
+      <c r="C115" s="31">
         <v>75</v>
       </c>
-      <c r="D115" s="38">
+      <c r="D115" s="31">
         <v>79</v>
       </c>
-      <c r="E115" s="15"/>
-      <c r="F115" s="24"/>
-      <c r="G115" s="53"/>
-      <c r="H115" s="35">
+      <c r="E115" s="35"/>
+      <c r="F115" s="13"/>
+      <c r="G115" s="38">
+        <v>67</v>
+      </c>
+      <c r="H115" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="13" t="s">
+      <c r="A116" s="10" t="s">
         <v>236</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C116" s="38">
+      <c r="C116" s="31">
         <v>53</v>
       </c>
-      <c r="D116" s="40">
+      <c r="D116" s="41">
         <v>47</v>
       </c>
-      <c r="E116" s="15"/>
-      <c r="F116" s="24"/>
-      <c r="G116" s="53"/>
-      <c r="H116" s="35">
+      <c r="E116" s="35"/>
+      <c r="F116" s="13"/>
+      <c r="G116" s="38">
+        <v>72</v>
+      </c>
+      <c r="H116" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.25" customHeight="1">
-      <c r="A117" s="13" t="s">
+      <c r="A117" s="10" t="s">
         <v>238</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C117" s="38">
+      <c r="C117" s="31">
         <v>44</v>
       </c>
-      <c r="D117" s="40">
+      <c r="D117" s="41">
         <v>60</v>
       </c>
-      <c r="E117" s="15"/>
-      <c r="F117" s="24"/>
-      <c r="G117" s="53"/>
-      <c r="H117" s="35">
+      <c r="E117" s="35"/>
+      <c r="F117" s="13"/>
+      <c r="G117" s="38">
+        <v>28</v>
+      </c>
+      <c r="H117" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="13" t="s">
+      <c r="A118" s="10" t="s">
         <v>240</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C118" s="38">
+      <c r="C118" s="31">
         <v>64</v>
       </c>
-      <c r="D118" s="38">
+      <c r="D118" s="31">
         <v>57</v>
       </c>
-      <c r="E118" s="15"/>
-      <c r="F118" s="24"/>
-      <c r="G118" s="53"/>
-      <c r="H118" s="35">
+      <c r="E118" s="35"/>
+      <c r="F118" s="13"/>
+      <c r="G118" s="38">
+        <v>54</v>
+      </c>
+      <c r="H118" s="61">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="13" t="s">
+      <c r="A119" s="10" t="s">
         <v>242</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C119" s="38">
+      <c r="C119" s="31">
         <v>83</v>
       </c>
-      <c r="D119" s="38">
+      <c r="D119" s="31">
         <v>52</v>
       </c>
-      <c r="E119" s="15"/>
-      <c r="F119" s="24"/>
-      <c r="G119" s="53"/>
-      <c r="H119" s="35">
+      <c r="E119" s="35"/>
+      <c r="F119" s="13"/>
+      <c r="G119" s="38">
+        <v>76</v>
+      </c>
+      <c r="H119" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="13" t="s">
+      <c r="A120" s="10" t="s">
         <v>244</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C120" s="38">
+      <c r="C120" s="31">
         <v>17</v>
       </c>
-      <c r="D120" s="40">
+      <c r="D120" s="41">
         <v>31</v>
       </c>
-      <c r="E120" s="15"/>
-      <c r="F120" s="24"/>
-      <c r="G120" s="53"/>
-      <c r="H120" s="35">
+      <c r="E120" s="35"/>
+      <c r="F120" s="13"/>
+      <c r="G120" s="38">
+        <v>52</v>
+      </c>
+      <c r="H120" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="13" t="s">
+      <c r="A121" s="10" t="s">
         <v>246</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C121" s="38" t="s">
+      <c r="C121" s="31" t="s">
         <v>382</v>
       </c>
-      <c r="D121" s="38">
+      <c r="D121" s="31">
         <v>16</v>
       </c>
-      <c r="E121" s="15"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="53"/>
-      <c r="H121" s="35">
+      <c r="E121" s="35"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="38">
+        <v>59</v>
+      </c>
+      <c r="H121" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="13" t="s">
+      <c r="A122" s="10" t="s">
         <v>248</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C122" s="38">
+      <c r="C122" s="31">
         <v>25</v>
       </c>
-      <c r="D122" s="38">
+      <c r="D122" s="31">
         <v>36</v>
       </c>
-      <c r="E122" s="15"/>
-      <c r="F122" s="24"/>
-      <c r="G122" s="53"/>
-      <c r="H122" s="35">
+      <c r="E122" s="35"/>
+      <c r="F122" s="13"/>
+      <c r="G122" s="38">
+        <v>32</v>
+      </c>
+      <c r="H122" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="13" t="s">
+      <c r="A123" s="10" t="s">
         <v>250</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C123" s="38" t="s">
+      <c r="C123" s="31" t="s">
         <v>382</v>
       </c>
-      <c r="D123" s="40" t="s">
+      <c r="D123" s="41" t="s">
         <v>382</v>
       </c>
-      <c r="E123" s="15"/>
-      <c r="F123" s="24"/>
-      <c r="G123" s="53"/>
-      <c r="H123" s="35">
+      <c r="E123" s="35"/>
+      <c r="F123" s="13"/>
+      <c r="G123" s="38" t="s">
+        <v>382</v>
+      </c>
+      <c r="H123" s="61">
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="13" t="s">
+      <c r="A124" s="10" t="s">
         <v>252</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C124" s="38">
+      <c r="C124" s="31">
         <v>58</v>
       </c>
-      <c r="D124" s="38">
+      <c r="D124" s="31">
         <v>72</v>
       </c>
-      <c r="E124" s="15"/>
-      <c r="F124" s="24"/>
-      <c r="G124" s="53"/>
-      <c r="H124" s="35">
+      <c r="E124" s="35"/>
+      <c r="F124" s="13"/>
+      <c r="G124" s="38">
+        <v>60</v>
+      </c>
+      <c r="H124" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="13" t="s">
+      <c r="A125" s="10" t="s">
         <v>254</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C125" s="38">
+      <c r="C125" s="31">
         <v>28</v>
       </c>
-      <c r="D125" s="40">
+      <c r="D125" s="41">
         <v>41</v>
       </c>
-      <c r="E125" s="15"/>
-      <c r="F125" s="24"/>
-      <c r="G125" s="53"/>
-      <c r="H125" s="35">
+      <c r="E125" s="35"/>
+      <c r="F125" s="13"/>
+      <c r="G125" s="38">
+        <v>55</v>
+      </c>
+      <c r="H125" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="10" t="s">
         <v>256</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C126" s="38">
+      <c r="C126" s="31">
         <v>44</v>
       </c>
-      <c r="D126" s="38">
+      <c r="D126" s="31">
         <v>53</v>
       </c>
-      <c r="E126" s="15"/>
-      <c r="F126" s="24"/>
-      <c r="G126" s="53"/>
-      <c r="H126" s="35">
+      <c r="E126" s="35"/>
+      <c r="F126" s="13"/>
+      <c r="G126" s="38">
+        <v>68</v>
+      </c>
+      <c r="H126" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="13" t="s">
+      <c r="A127" s="10" t="s">
         <v>258</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C127" s="38">
+      <c r="C127" s="31">
         <v>54</v>
       </c>
-      <c r="D127" s="40">
+      <c r="D127" s="41">
         <v>32</v>
       </c>
-      <c r="E127" s="15"/>
-      <c r="F127" s="24"/>
-      <c r="G127" s="53"/>
-      <c r="H127" s="35">
+      <c r="E127" s="35"/>
+      <c r="F127" s="13"/>
+      <c r="G127" s="38">
+        <v>68</v>
+      </c>
+      <c r="H127" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="13" t="s">
+      <c r="A128" s="10" t="s">
         <v>260</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C128" s="38">
+      <c r="C128" s="31">
         <v>21</v>
       </c>
-      <c r="D128" s="40">
+      <c r="D128" s="41">
         <v>56</v>
       </c>
-      <c r="E128" s="15"/>
-      <c r="F128" s="24"/>
-      <c r="G128" s="53"/>
-      <c r="H128" s="35">
+      <c r="E128" s="35"/>
+      <c r="F128" s="13"/>
+      <c r="G128" s="38">
+        <v>48</v>
+      </c>
+      <c r="H128" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="13" t="s">
+      <c r="A129" s="10" t="s">
         <v>262</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C129" s="38">
+      <c r="C129" s="31">
         <v>26</v>
       </c>
-      <c r="D129" s="40">
+      <c r="D129" s="41">
         <v>49</v>
       </c>
-      <c r="E129" s="15"/>
-      <c r="F129" s="24"/>
-      <c r="G129" s="53"/>
-      <c r="H129" s="35">
+      <c r="E129" s="35"/>
+      <c r="F129" s="13"/>
+      <c r="G129" s="38">
+        <v>50</v>
+      </c>
+      <c r="H129" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="13" t="s">
+      <c r="A130" s="10" t="s">
         <v>264</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C130" s="38">
+      <c r="C130" s="31">
         <v>15</v>
       </c>
-      <c r="D130" s="40">
+      <c r="D130" s="41">
         <v>26</v>
       </c>
-      <c r="E130" s="15"/>
-      <c r="F130" s="24"/>
-      <c r="G130" s="53"/>
-      <c r="H130" s="35">
+      <c r="E130" s="35"/>
+      <c r="F130" s="13"/>
+      <c r="G130" s="38">
+        <v>22</v>
+      </c>
+      <c r="H130" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="13" t="s">
+      <c r="A131" s="10" t="s">
         <v>266</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C131" s="38">
+      <c r="C131" s="31">
         <v>51</v>
       </c>
-      <c r="D131" s="40">
+      <c r="D131" s="41">
         <v>23</v>
       </c>
-      <c r="E131" s="15"/>
-      <c r="F131" s="24"/>
-      <c r="G131" s="53"/>
-      <c r="H131" s="35">
+      <c r="E131" s="35"/>
+      <c r="F131" s="13"/>
+      <c r="G131" s="38">
+        <v>63</v>
+      </c>
+      <c r="H131" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="13" t="s">
+      <c r="A132" s="10" t="s">
         <v>268</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C132" s="38">
+      <c r="C132" s="31">
         <v>50</v>
       </c>
-      <c r="D132" s="40">
+      <c r="D132" s="41">
         <v>81</v>
       </c>
-      <c r="E132" s="16"/>
-      <c r="F132" s="25"/>
-      <c r="G132" s="54"/>
-      <c r="H132" s="35">
+      <c r="E132" s="33"/>
+      <c r="F132" s="14"/>
+      <c r="G132" s="39">
+        <v>66</v>
+      </c>
+      <c r="H132" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="13" t="s">
+      <c r="A133" s="10" t="s">
         <v>270</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C133" s="38">
+      <c r="C133" s="31">
         <v>18</v>
       </c>
-      <c r="D133" s="40">
+      <c r="D133" s="41">
         <v>13</v>
       </c>
-      <c r="E133" s="15"/>
-      <c r="F133" s="24"/>
-      <c r="G133" s="53"/>
-      <c r="H133" s="35">
+      <c r="E133" s="35"/>
+      <c r="F133" s="13"/>
+      <c r="G133" s="38">
+        <v>23</v>
+      </c>
+      <c r="H133" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="13" t="s">
+      <c r="A134" s="10" t="s">
         <v>272</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C134" s="38">
+      <c r="C134" s="31">
         <v>53</v>
       </c>
-      <c r="D134" s="40">
+      <c r="D134" s="41">
         <v>49</v>
       </c>
-      <c r="E134" s="15"/>
-      <c r="F134" s="24"/>
-      <c r="G134" s="56"/>
-      <c r="H134" s="35">
+      <c r="E134" s="35"/>
+      <c r="F134" s="13"/>
+      <c r="G134" s="42">
+        <v>65</v>
+      </c>
+      <c r="H134" s="61">
         <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="13" t="s">
+      <c r="A135" s="10" t="s">
         <v>274</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C135" s="38">
+      <c r="C135" s="31">
         <v>8</v>
       </c>
-      <c r="D135" s="40">
+      <c r="D135" s="41">
         <v>42</v>
       </c>
-      <c r="E135" s="15"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="57"/>
-      <c r="H135" s="35">
+      <c r="E135" s="35"/>
+      <c r="F135" s="13"/>
+      <c r="G135" s="43">
+        <v>45</v>
+      </c>
+      <c r="H135" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="13" t="s">
+      <c r="A136" s="10" t="s">
         <v>276</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C136" s="38">
+      <c r="C136" s="31">
         <v>42</v>
       </c>
-      <c r="D136" s="38">
+      <c r="D136" s="31">
         <v>58</v>
       </c>
-      <c r="E136" s="15"/>
-      <c r="F136" s="24"/>
-      <c r="G136" s="52"/>
-      <c r="H136" s="35">
+      <c r="E136" s="35"/>
+      <c r="F136" s="13"/>
+      <c r="G136" s="36">
+        <v>58</v>
+      </c>
+      <c r="H136" s="61">
         <v>100</v>
       </c>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="13" t="s">
+      <c r="A137" s="10" t="s">
         <v>278</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C137" s="38">
+      <c r="C137" s="31">
         <v>37</v>
       </c>
-      <c r="D137" s="38">
+      <c r="D137" s="31">
         <v>45</v>
       </c>
-      <c r="E137" s="16"/>
-      <c r="F137" s="25"/>
-      <c r="G137" s="54"/>
-      <c r="H137" s="35">
+      <c r="E137" s="33"/>
+      <c r="F137" s="14"/>
+      <c r="G137" s="39">
+        <v>53</v>
+      </c>
+      <c r="H137" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="13" t="s">
+      <c r="A138" s="10" t="s">
         <v>280</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C138" s="38">
+      <c r="C138" s="31">
         <v>46</v>
       </c>
-      <c r="D138" s="38">
+      <c r="D138" s="31">
         <v>29</v>
       </c>
-      <c r="E138" s="15"/>
-      <c r="F138" s="24"/>
-      <c r="G138" s="53"/>
-      <c r="H138" s="35">
+      <c r="E138" s="35"/>
+      <c r="F138" s="13"/>
+      <c r="G138" s="38">
+        <v>64</v>
+      </c>
+      <c r="H138" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="13" t="s">
+      <c r="A139" s="10" t="s">
         <v>282</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C139" s="38">
+      <c r="C139" s="31">
         <v>43</v>
       </c>
-      <c r="D139" s="40">
+      <c r="D139" s="41">
         <v>38</v>
       </c>
-      <c r="E139" s="15"/>
-      <c r="F139" s="24"/>
-      <c r="G139" s="53"/>
-      <c r="H139" s="35">
+      <c r="E139" s="35"/>
+      <c r="F139" s="13"/>
+      <c r="G139" s="38">
+        <v>41</v>
+      </c>
+      <c r="H139" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="13" t="s">
+      <c r="A140" s="10" t="s">
         <v>284</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C140" s="38">
+      <c r="C140" s="31">
         <v>40</v>
       </c>
-      <c r="D140" s="38">
+      <c r="D140" s="31">
         <v>66</v>
       </c>
-      <c r="E140" s="15"/>
-      <c r="F140" s="24"/>
-      <c r="G140" s="53"/>
-      <c r="H140" s="35">
+      <c r="E140" s="35"/>
+      <c r="F140" s="13"/>
+      <c r="G140" s="38">
+        <v>70</v>
+      </c>
+      <c r="H140" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="13" t="s">
+      <c r="A141" s="10" t="s">
         <v>286</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C141" s="38">
+      <c r="C141" s="31">
         <v>32</v>
       </c>
-      <c r="D141" s="38">
+      <c r="D141" s="31">
         <v>17</v>
       </c>
-      <c r="E141" s="15"/>
-      <c r="F141" s="24"/>
-      <c r="G141" s="53"/>
-      <c r="H141" s="35">
+      <c r="E141" s="35"/>
+      <c r="F141" s="13"/>
+      <c r="G141" s="38">
+        <v>34</v>
+      </c>
+      <c r="H141" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="13" t="s">
+      <c r="A142" s="10" t="s">
         <v>288</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C142" s="38">
+      <c r="C142" s="31">
         <v>32</v>
       </c>
-      <c r="D142" s="38">
+      <c r="D142" s="31">
         <v>45</v>
       </c>
-      <c r="E142" s="15"/>
-      <c r="F142" s="24"/>
-      <c r="G142" s="53"/>
-      <c r="H142" s="35">
+      <c r="E142" s="35"/>
+      <c r="F142" s="13"/>
+      <c r="G142" s="38">
+        <v>65</v>
+      </c>
+      <c r="H142" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="143" spans="1:8">
-      <c r="A143" s="13" t="s">
+      <c r="A143" s="10" t="s">
         <v>290</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C143" s="38">
+      <c r="C143" s="31">
         <v>67</v>
       </c>
-      <c r="D143" s="40">
+      <c r="D143" s="41">
         <v>89</v>
       </c>
-      <c r="E143" s="15"/>
-      <c r="F143" s="24"/>
-      <c r="G143" s="53"/>
-      <c r="H143" s="35">
+      <c r="E143" s="35"/>
+      <c r="F143" s="13"/>
+      <c r="G143" s="38">
+        <v>72</v>
+      </c>
+      <c r="H143" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="13" t="s">
+      <c r="A144" s="10" t="s">
         <v>292</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C144" s="38">
+      <c r="C144" s="31">
         <v>61</v>
       </c>
-      <c r="D144" s="40">
+      <c r="D144" s="41">
         <v>76</v>
       </c>
-      <c r="E144" s="15"/>
-      <c r="F144" s="24"/>
-      <c r="G144" s="53"/>
-      <c r="H144" s="35">
+      <c r="E144" s="35"/>
+      <c r="F144" s="13"/>
+      <c r="G144" s="38">
+        <v>59</v>
+      </c>
+      <c r="H144" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="145" spans="1:8">
-      <c r="A145" s="13" t="s">
+      <c r="A145" s="10" t="s">
         <v>294</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C145" s="38">
+      <c r="C145" s="31">
         <v>71</v>
       </c>
-      <c r="D145" s="40">
+      <c r="D145" s="41">
         <v>76</v>
       </c>
-      <c r="E145" s="15"/>
-      <c r="F145" s="24"/>
-      <c r="G145" s="53"/>
-      <c r="H145" s="35">
+      <c r="E145" s="35"/>
+      <c r="F145" s="13"/>
+      <c r="G145" s="38">
+        <v>68</v>
+      </c>
+      <c r="H145" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="146" spans="1:8">
-      <c r="A146" s="13" t="s">
+      <c r="A146" s="10" t="s">
         <v>296</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C146" s="38">
+      <c r="C146" s="31">
         <v>96</v>
       </c>
-      <c r="D146" s="40">
+      <c r="D146" s="41">
         <v>86</v>
       </c>
-      <c r="E146" s="15"/>
-      <c r="F146" s="24"/>
-      <c r="G146" s="53"/>
-      <c r="H146" s="35">
+      <c r="E146" s="35"/>
+      <c r="F146" s="13"/>
+      <c r="G146" s="38">
+        <v>66</v>
+      </c>
+      <c r="H146" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" s="13" t="s">
+      <c r="A147" s="10" t="s">
         <v>298</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C147" s="38">
+      <c r="C147" s="31">
         <v>21</v>
       </c>
-      <c r="D147" s="38">
+      <c r="D147" s="31">
         <v>28</v>
       </c>
-      <c r="E147" s="15"/>
-      <c r="F147" s="24"/>
-      <c r="G147" s="53"/>
-      <c r="H147" s="35">
+      <c r="E147" s="35"/>
+      <c r="F147" s="13"/>
+      <c r="G147" s="38">
+        <v>12</v>
+      </c>
+      <c r="H147" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="148" spans="1:8">
-      <c r="A148" s="13" t="s">
+      <c r="A148" s="10" t="s">
         <v>300</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C148" s="38">
+      <c r="C148" s="31">
         <v>47</v>
       </c>
-      <c r="D148" s="38">
+      <c r="D148" s="31">
         <v>73</v>
       </c>
-      <c r="E148" s="15"/>
-      <c r="F148" s="24"/>
-      <c r="G148" s="53"/>
-      <c r="H148" s="35">
+      <c r="E148" s="35"/>
+      <c r="F148" s="13"/>
+      <c r="G148" s="38">
+        <v>52</v>
+      </c>
+      <c r="H148" s="61">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="149" spans="1:8">
-      <c r="A149" s="13" t="s">
+      <c r="A149" s="10" t="s">
         <v>302</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C149" s="38">
+      <c r="C149" s="31">
         <v>67</v>
       </c>
-      <c r="D149" s="40">
+      <c r="D149" s="41">
         <v>52</v>
       </c>
-      <c r="E149" s="15"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="53"/>
-      <c r="H149" s="35">
+      <c r="E149" s="35"/>
+      <c r="F149" s="13"/>
+      <c r="G149" s="38">
+        <v>28</v>
+      </c>
+      <c r="H149" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" s="13" t="s">
+      <c r="A150" s="10" t="s">
         <v>304</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C150" s="38" t="s">
+      <c r="C150" s="31" t="s">
         <v>382</v>
       </c>
-      <c r="D150" s="40">
+      <c r="D150" s="41">
         <v>48</v>
       </c>
-      <c r="E150" s="16"/>
-      <c r="F150" s="26"/>
-      <c r="G150" s="54"/>
-      <c r="H150" s="35">
+      <c r="E150" s="33"/>
+      <c r="F150" s="44"/>
+      <c r="G150" s="39">
+        <v>44</v>
+      </c>
+      <c r="H150" s="61">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="151" spans="1:8">
-      <c r="A151" s="13" t="s">
+      <c r="A151" s="10" t="s">
         <v>306</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C151" s="38">
+      <c r="C151" s="31">
         <v>52</v>
       </c>
-      <c r="D151" s="38">
+      <c r="D151" s="31">
         <v>43</v>
       </c>
-      <c r="E151" s="15"/>
-      <c r="F151" s="24"/>
-      <c r="G151" s="53"/>
-      <c r="H151" s="35">
+      <c r="E151" s="35"/>
+      <c r="F151" s="13"/>
+      <c r="G151" s="38">
+        <v>64</v>
+      </c>
+      <c r="H151" s="61">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="152" spans="1:8">
-      <c r="A152" s="13" t="s">
+      <c r="A152" s="10" t="s">
         <v>308</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C152" s="38">
+      <c r="C152" s="31">
         <v>36</v>
       </c>
-      <c r="D152" s="38">
+      <c r="D152" s="31">
         <v>51</v>
       </c>
-      <c r="E152" s="15"/>
-      <c r="F152" s="24"/>
-      <c r="G152" s="53"/>
-      <c r="H152" s="35">
+      <c r="E152" s="35"/>
+      <c r="F152" s="13"/>
+      <c r="G152" s="38">
+        <v>44</v>
+      </c>
+      <c r="H152" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="153" spans="1:8">
-      <c r="A153" s="13" t="s">
+      <c r="A153" s="10" t="s">
         <v>310</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C153" s="38">
+      <c r="C153" s="31">
         <v>78</v>
       </c>
-      <c r="D153" s="40">
+      <c r="D153" s="41">
         <v>46</v>
       </c>
-      <c r="E153" s="15"/>
-      <c r="F153" s="24"/>
-      <c r="G153" s="53"/>
-      <c r="H153" s="35">
+      <c r="E153" s="35"/>
+      <c r="F153" s="13"/>
+      <c r="G153" s="38">
+        <v>59</v>
+      </c>
+      <c r="H153" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="154" spans="1:8">
-      <c r="A154" s="13" t="s">
+      <c r="A154" s="10" t="s">
         <v>312</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C154" s="38">
+      <c r="C154" s="31">
         <v>31</v>
       </c>
-      <c r="D154" s="39">
+      <c r="D154" s="32">
         <v>78</v>
       </c>
-      <c r="E154" s="15"/>
-      <c r="F154" s="24"/>
-      <c r="G154" s="53"/>
-      <c r="H154" s="35">
+      <c r="E154" s="35"/>
+      <c r="F154" s="13"/>
+      <c r="G154" s="38">
+        <v>72</v>
+      </c>
+      <c r="H154" s="61">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="155" spans="1:8">
-      <c r="A155" s="13" t="s">
+      <c r="A155" s="10" t="s">
         <v>314</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C155" s="38">
+      <c r="C155" s="31">
         <v>60</v>
       </c>
-      <c r="D155" s="39">
+      <c r="D155" s="32">
         <v>85</v>
       </c>
-      <c r="E155" s="15"/>
-      <c r="F155" s="24"/>
-      <c r="G155" s="53"/>
-      <c r="H155" s="35">
+      <c r="E155" s="35"/>
+      <c r="F155" s="13"/>
+      <c r="G155" s="38">
+        <v>64</v>
+      </c>
+      <c r="H155" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="156" spans="1:8">
-      <c r="A156" s="13" t="s">
+      <c r="A156" s="10" t="s">
         <v>316</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C156" s="38">
+      <c r="C156" s="31">
         <v>95</v>
       </c>
-      <c r="D156" s="38">
+      <c r="D156" s="31">
         <v>89</v>
       </c>
-      <c r="E156" s="16"/>
-      <c r="F156" s="26"/>
-      <c r="G156" s="54"/>
-      <c r="H156" s="35">
+      <c r="E156" s="33"/>
+      <c r="F156" s="44"/>
+      <c r="G156" s="39">
+        <v>80</v>
+      </c>
+      <c r="H156" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" s="13" t="s">
+      <c r="A157" s="10" t="s">
         <v>318</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C157" s="38">
+      <c r="C157" s="31">
         <v>69</v>
       </c>
-      <c r="D157" s="38">
+      <c r="D157" s="31">
         <v>89</v>
       </c>
-      <c r="E157" s="15"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="53"/>
-      <c r="H157" s="35">
+      <c r="E157" s="35"/>
+      <c r="F157" s="13"/>
+      <c r="G157" s="38">
+        <v>67</v>
+      </c>
+      <c r="H157" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" s="13" t="s">
+      <c r="A158" s="10" t="s">
         <v>320</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C158" s="38">
+      <c r="C158" s="31">
         <v>47</v>
       </c>
-      <c r="D158" s="38">
+      <c r="D158" s="31">
         <v>86</v>
       </c>
-      <c r="E158" s="15"/>
-      <c r="F158" s="24"/>
-      <c r="G158" s="53"/>
-      <c r="H158" s="35">
+      <c r="E158" s="35"/>
+      <c r="F158" s="13"/>
+      <c r="G158" s="38">
+        <v>57</v>
+      </c>
+      <c r="H158" s="61">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" s="13" t="s">
+      <c r="A159" s="10" t="s">
         <v>322</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C159" s="38">
+      <c r="C159" s="31">
         <v>58</v>
       </c>
-      <c r="D159" s="39">
+      <c r="D159" s="32">
         <v>56</v>
       </c>
-      <c r="E159" s="17"/>
-      <c r="F159" s="24"/>
-      <c r="G159" s="53"/>
-      <c r="H159" s="35">
+      <c r="E159" s="45"/>
+      <c r="F159" s="13"/>
+      <c r="G159" s="38">
+        <v>70</v>
+      </c>
+      <c r="H159" s="61">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="13" t="s">
+      <c r="A160" s="10" t="s">
         <v>324</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C160" s="38">
+      <c r="C160" s="31">
         <v>25</v>
       </c>
-      <c r="D160" s="39">
+      <c r="D160" s="32">
         <v>76</v>
       </c>
-      <c r="E160" s="15"/>
-      <c r="F160" s="24"/>
-      <c r="G160" s="53"/>
-      <c r="H160" s="35">
+      <c r="E160" s="35"/>
+      <c r="F160" s="13"/>
+      <c r="G160" s="38">
+        <v>70</v>
+      </c>
+      <c r="H160" s="61">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="13" t="s">
+      <c r="A161" s="10" t="s">
         <v>326</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C161" s="38">
+      <c r="C161" s="31">
         <v>44</v>
       </c>
-      <c r="D161" s="38">
+      <c r="D161" s="31">
         <v>34</v>
       </c>
-      <c r="E161" s="15"/>
-      <c r="F161" s="24"/>
-      <c r="G161" s="53"/>
-      <c r="H161" s="35">
+      <c r="E161" s="35"/>
+      <c r="F161" s="13"/>
+      <c r="G161" s="38">
+        <v>57</v>
+      </c>
+      <c r="H161" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="162" spans="1:8">
-      <c r="A162" s="13" t="s">
+      <c r="A162" s="10" t="s">
         <v>328</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C162" s="38">
+      <c r="C162" s="31">
         <v>31</v>
       </c>
-      <c r="D162" s="39">
+      <c r="D162" s="32">
         <v>38</v>
       </c>
-      <c r="E162" s="15"/>
-      <c r="F162" s="24"/>
-      <c r="G162" s="53"/>
-      <c r="H162" s="35">
+      <c r="E162" s="35"/>
+      <c r="F162" s="13"/>
+      <c r="G162" s="38">
+        <v>52</v>
+      </c>
+      <c r="H162" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="163" spans="1:8">
-      <c r="A163" s="13" t="s">
+      <c r="A163" s="10" t="s">
         <v>330</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C163" s="39">
+      <c r="C163" s="32">
         <v>40</v>
       </c>
-      <c r="D163" s="38">
+      <c r="D163" s="31">
         <v>55</v>
       </c>
-      <c r="E163" s="15"/>
-      <c r="F163" s="24"/>
-      <c r="G163" s="53"/>
-      <c r="H163" s="35">
+      <c r="E163" s="35"/>
+      <c r="F163" s="13"/>
+      <c r="G163" s="38">
+        <v>42</v>
+      </c>
+      <c r="H163" s="61">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="164" spans="1:8">
-      <c r="A164" s="13" t="s">
+      <c r="A164" s="10" t="s">
         <v>332</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C164" s="39">
+      <c r="C164" s="32">
         <v>19</v>
       </c>
-      <c r="D164" s="39">
+      <c r="D164" s="32">
         <v>63</v>
       </c>
-      <c r="E164" s="15"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="56"/>
-      <c r="H164" s="35">
+      <c r="E164" s="35"/>
+      <c r="F164" s="13"/>
+      <c r="G164" s="42">
+        <v>49</v>
+      </c>
+      <c r="H164" s="61">
         <v>47.826087000000001</v>
       </c>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="13" t="s">
+      <c r="A165" s="10" t="s">
         <v>334</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C165" s="39" t="s">
+      <c r="C165" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="D165" s="38">
+      <c r="D165" s="31">
         <v>74</v>
       </c>
-      <c r="E165" s="15"/>
-      <c r="F165" s="24"/>
-      <c r="G165" s="51"/>
-      <c r="H165" s="35">
+      <c r="E165" s="35"/>
+      <c r="F165" s="13"/>
+      <c r="G165" s="34">
+        <v>61</v>
+      </c>
+      <c r="H165" s="61">
         <v>65.217391300000003</v>
       </c>
     </row>
     <row r="166" spans="1:8">
-      <c r="A166" s="13" t="s">
+      <c r="A166" s="10" t="s">
         <v>336</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C166" s="39">
+      <c r="C166" s="32">
         <v>18</v>
       </c>
-      <c r="D166" s="38">
+      <c r="D166" s="31">
         <v>44</v>
       </c>
-      <c r="E166" s="15"/>
-      <c r="F166" s="24"/>
-      <c r="G166" s="51"/>
-      <c r="H166" s="35">
+      <c r="E166" s="35"/>
+      <c r="F166" s="13"/>
+      <c r="G166" s="34">
+        <v>47</v>
+      </c>
+      <c r="H166" s="61">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" s="13" t="s">
+      <c r="A167" s="10" t="s">
         <v>338</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C167" s="39">
+      <c r="C167" s="32">
         <v>44</v>
       </c>
-      <c r="D167" s="39">
+      <c r="D167" s="32">
         <v>69</v>
       </c>
-      <c r="E167" s="15"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="51"/>
-      <c r="H167" s="35">
+      <c r="E167" s="35"/>
+      <c r="F167" s="13"/>
+      <c r="G167" s="34">
+        <v>65</v>
+      </c>
+      <c r="H167" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="13" t="s">
+      <c r="A168" s="10" t="s">
         <v>340</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C168" s="39">
+      <c r="C168" s="32">
         <v>82</v>
       </c>
-      <c r="D168" s="38">
+      <c r="D168" s="31">
         <v>93</v>
       </c>
-      <c r="E168" s="15"/>
-      <c r="F168" s="24"/>
-      <c r="G168" s="51"/>
-      <c r="H168" s="35">
+      <c r="E168" s="35"/>
+      <c r="F168" s="13"/>
+      <c r="G168" s="34">
+        <v>45</v>
+      </c>
+      <c r="H168" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="169" spans="1:8">
-      <c r="A169" s="13" t="s">
+      <c r="A169" s="10" t="s">
         <v>342</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C169" s="39">
+      <c r="C169" s="32">
         <v>55</v>
       </c>
-      <c r="D169" s="39">
+      <c r="D169" s="32">
         <v>55</v>
       </c>
-      <c r="E169" s="15"/>
-      <c r="F169" s="24"/>
-      <c r="G169" s="51"/>
-      <c r="H169" s="35">
+      <c r="E169" s="35"/>
+      <c r="F169" s="13"/>
+      <c r="G169" s="34">
+        <v>69</v>
+      </c>
+      <c r="H169" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="170" spans="1:8">
-      <c r="A170" s="13" t="s">
+      <c r="A170" s="10" t="s">
         <v>344</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C170" s="39">
+      <c r="C170" s="32">
         <v>24</v>
       </c>
-      <c r="D170" s="39">
+      <c r="D170" s="32">
         <v>25</v>
       </c>
-      <c r="E170" s="18"/>
-      <c r="F170" s="27"/>
-      <c r="G170" s="58"/>
-      <c r="H170" s="35">
+      <c r="E170" s="46"/>
+      <c r="F170" s="47"/>
+      <c r="G170" s="48">
+        <v>33</v>
+      </c>
+      <c r="H170" s="61">
         <v>47.826087000000001</v>
       </c>
     </row>
     <row r="171" spans="1:8">
-      <c r="A171" s="13" t="s">
+      <c r="A171" s="10" t="s">
         <v>346</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C171" s="39">
+      <c r="C171" s="32">
         <v>36</v>
       </c>
-      <c r="D171" s="39">
+      <c r="D171" s="32">
         <v>50</v>
       </c>
-      <c r="E171" s="15"/>
-      <c r="F171" s="28"/>
-      <c r="G171" s="59"/>
-      <c r="H171" s="35">
+      <c r="E171" s="35"/>
+      <c r="F171" s="15"/>
+      <c r="G171" s="49">
+        <v>46</v>
+      </c>
+      <c r="H171" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="172" spans="1:8">
-      <c r="A172" s="13" t="s">
+      <c r="A172" s="10" t="s">
         <v>348</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C172" s="39">
+      <c r="C172" s="32">
         <v>55</v>
       </c>
-      <c r="D172" s="39">
+      <c r="D172" s="32">
         <v>58</v>
       </c>
-      <c r="E172" s="15"/>
-      <c r="F172" s="28"/>
-      <c r="G172" s="59"/>
-      <c r="H172" s="35">
+      <c r="E172" s="35"/>
+      <c r="F172" s="15"/>
+      <c r="G172" s="49">
+        <v>26</v>
+      </c>
+      <c r="H172" s="61">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="173" spans="1:8">
-      <c r="A173" s="13" t="s">
+      <c r="A173" s="10" t="s">
         <v>350</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C173" s="39">
+      <c r="C173" s="32">
         <v>27</v>
       </c>
-      <c r="D173" s="38">
+      <c r="D173" s="31">
         <v>65</v>
       </c>
-      <c r="E173" s="15"/>
-      <c r="F173" s="28"/>
-      <c r="G173" s="59"/>
-      <c r="H173" s="35">
+      <c r="E173" s="35"/>
+      <c r="F173" s="15"/>
+      <c r="G173" s="49">
+        <v>50</v>
+      </c>
+      <c r="H173" s="61">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="174" spans="1:8">
-      <c r="A174" s="13" t="s">
+      <c r="A174" s="10" t="s">
         <v>352</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C174" s="39">
+      <c r="C174" s="32">
         <v>14</v>
       </c>
-      <c r="D174" s="38">
+      <c r="D174" s="31">
         <v>22</v>
       </c>
-      <c r="E174" s="15"/>
-      <c r="F174" s="28"/>
-      <c r="G174" s="59"/>
-      <c r="H174" s="35">
+      <c r="E174" s="35"/>
+      <c r="F174" s="15"/>
+      <c r="G174" s="49">
+        <v>51</v>
+      </c>
+      <c r="H174" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="175" spans="1:8">
-      <c r="A175" s="13" t="s">
+      <c r="A175" s="10" t="s">
         <v>354</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C175" s="39">
+      <c r="C175" s="32">
         <v>17</v>
       </c>
-      <c r="D175" s="39">
+      <c r="D175" s="32">
         <v>40</v>
       </c>
-      <c r="E175" s="15"/>
-      <c r="F175" s="28"/>
-      <c r="G175" s="59"/>
-      <c r="H175" s="35">
+      <c r="E175" s="35"/>
+      <c r="F175" s="15"/>
+      <c r="G175" s="49">
+        <v>60</v>
+      </c>
+      <c r="H175" s="61">
         <v>30.434782599999998</v>
       </c>
     </row>
     <row r="176" spans="1:8">
-      <c r="A176" s="13" t="s">
+      <c r="A176" s="10" t="s">
         <v>356</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C176" s="39">
+      <c r="C176" s="32">
         <v>33</v>
       </c>
-      <c r="D176" s="38">
+      <c r="D176" s="31">
         <v>23</v>
       </c>
-      <c r="E176" s="15"/>
-      <c r="F176" s="28"/>
-      <c r="G176" s="59"/>
-      <c r="H176" s="35">
+      <c r="E176" s="35"/>
+      <c r="F176" s="15"/>
+      <c r="G176" s="49">
+        <v>35</v>
+      </c>
+      <c r="H176" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="177" spans="1:8">
-      <c r="A177" s="13" t="s">
+      <c r="A177" s="10" t="s">
         <v>358</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C177" s="39">
+      <c r="C177" s="32">
         <v>64</v>
       </c>
-      <c r="D177" s="38">
+      <c r="D177" s="31">
         <v>81</v>
       </c>
-      <c r="E177" s="15"/>
-      <c r="F177" s="28"/>
-      <c r="G177" s="59"/>
-      <c r="H177" s="35">
+      <c r="E177" s="35"/>
+      <c r="F177" s="15"/>
+      <c r="G177" s="49">
+        <v>54</v>
+      </c>
+      <c r="H177" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="178" spans="1:8">
-      <c r="A178" s="13" t="s">
+      <c r="A178" s="10" t="s">
         <v>360</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C178" s="39">
+      <c r="C178" s="32">
         <v>32</v>
       </c>
-      <c r="D178" s="38">
+      <c r="D178" s="31">
         <v>94</v>
       </c>
-      <c r="E178" s="15"/>
-      <c r="F178" s="28"/>
-      <c r="G178" s="59"/>
-      <c r="H178" s="35">
+      <c r="E178" s="35"/>
+      <c r="F178" s="15"/>
+      <c r="G178" s="49">
+        <v>80</v>
+      </c>
+      <c r="H178" s="61">
         <v>100</v>
       </c>
     </row>
     <row r="179" spans="1:8">
-      <c r="A179" s="13" t="s">
+      <c r="A179" s="10" t="s">
         <v>362</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C179" s="39">
+      <c r="C179" s="32">
         <v>64</v>
       </c>
-      <c r="D179" s="38">
+      <c r="D179" s="31">
         <v>92</v>
       </c>
-      <c r="E179" s="15"/>
-      <c r="F179" s="28"/>
-      <c r="G179" s="59"/>
-      <c r="H179" s="35">
+      <c r="E179" s="35"/>
+      <c r="F179" s="15"/>
+      <c r="G179" s="49">
+        <v>88</v>
+      </c>
+      <c r="H179" s="61">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="180" spans="1:8">
-      <c r="A180" s="13" t="s">
+      <c r="A180" s="10" t="s">
         <v>364</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C180" s="39">
+      <c r="C180" s="32">
         <v>12</v>
       </c>
-      <c r="D180" s="38">
+      <c r="D180" s="31">
         <v>25</v>
       </c>
-      <c r="E180" s="15"/>
-      <c r="F180" s="28"/>
-      <c r="G180" s="59"/>
-      <c r="H180" s="35">
+      <c r="E180" s="35"/>
+      <c r="F180" s="15"/>
+      <c r="G180" s="49">
+        <v>29</v>
+      </c>
+      <c r="H180" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="181" spans="1:8">
-      <c r="A181" s="13" t="s">
+      <c r="A181" s="10" t="s">
         <v>366</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C181" s="39">
+      <c r="C181" s="32">
         <v>36</v>
       </c>
-      <c r="D181" s="39">
+      <c r="D181" s="32">
         <v>70</v>
       </c>
-      <c r="E181" s="15"/>
-      <c r="F181" s="28"/>
-      <c r="G181" s="59"/>
-      <c r="H181" s="35">
+      <c r="E181" s="35"/>
+      <c r="F181" s="15"/>
+      <c r="G181" s="49">
+        <v>63</v>
+      </c>
+      <c r="H181" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="182" spans="1:8">
-      <c r="A182" s="13" t="s">
+      <c r="A182" s="10" t="s">
         <v>368</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C182" s="39">
+      <c r="C182" s="32">
         <v>1</v>
       </c>
-      <c r="D182" s="39">
+      <c r="D182" s="32">
         <v>40</v>
       </c>
-      <c r="E182" s="19"/>
-      <c r="F182" s="28"/>
-      <c r="G182" s="59"/>
-      <c r="H182" s="35">
+      <c r="E182" s="50"/>
+      <c r="F182" s="15"/>
+      <c r="G182" s="49">
+        <v>49</v>
+      </c>
+      <c r="H182" s="61">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="183" spans="1:8">
-      <c r="A183" s="13" t="s">
+      <c r="A183" s="10" t="s">
         <v>370</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C183" s="39">
+      <c r="C183" s="32">
         <v>38</v>
       </c>
-      <c r="D183" s="39">
+      <c r="D183" s="32">
         <v>66</v>
       </c>
-      <c r="E183" s="19"/>
-      <c r="F183" s="28"/>
-      <c r="G183" s="59"/>
-      <c r="H183" s="35">
+      <c r="E183" s="50"/>
+      <c r="F183" s="15"/>
+      <c r="G183" s="49">
+        <v>59</v>
+      </c>
+      <c r="H183" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="184" spans="1:8">
-      <c r="A184" s="13" t="s">
+      <c r="A184" s="10" t="s">
         <v>372</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C184" s="39">
+      <c r="C184" s="32">
         <v>41</v>
       </c>
-      <c r="D184" s="39">
+      <c r="D184" s="32">
         <v>62</v>
       </c>
-      <c r="E184" s="15"/>
-      <c r="F184" s="28"/>
-      <c r="G184" s="59"/>
-      <c r="H184" s="35">
+      <c r="E184" s="35"/>
+      <c r="F184" s="15"/>
+      <c r="G184" s="49">
+        <v>74</v>
+      </c>
+      <c r="H184" s="61">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="185" spans="1:8">
-      <c r="A185" s="13" t="s">
+      <c r="A185" s="10" t="s">
         <v>374</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C185" s="39">
+      <c r="C185" s="32">
         <v>77</v>
       </c>
-      <c r="D185" s="39">
+      <c r="D185" s="32">
         <v>57</v>
       </c>
-      <c r="E185" s="15"/>
-      <c r="F185" s="28"/>
-      <c r="G185" s="59"/>
-      <c r="H185" s="35">
+      <c r="E185" s="35"/>
+      <c r="F185" s="15"/>
+      <c r="G185" s="49">
+        <v>65</v>
+      </c>
+      <c r="H185" s="61">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="186" spans="1:8">
-      <c r="A186" s="13" t="s">
+      <c r="A186" s="10" t="s">
         <v>376</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C186" s="39">
+      <c r="C186" s="32">
         <v>74</v>
       </c>
-      <c r="D186" s="39">
+      <c r="D186" s="32">
         <v>44</v>
       </c>
-      <c r="E186" s="15"/>
-      <c r="F186" s="28"/>
-      <c r="G186" s="59"/>
-      <c r="H186" s="35">
+      <c r="E186" s="35"/>
+      <c r="F186" s="15"/>
+      <c r="G186" s="49">
+        <v>69</v>
+      </c>
+      <c r="H186" s="61">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="36" t="s">
+      <c r="A187" s="23" t="s">
         <v>380</v>
       </c>
-      <c r="B187" s="37" t="s">
+      <c r="B187" s="24" t="s">
         <v>381</v>
       </c>
-      <c r="C187" s="39">
+      <c r="C187" s="32">
         <v>37</v>
       </c>
-      <c r="D187" s="39">
+      <c r="D187" s="32">
         <v>32</v>
       </c>
-      <c r="E187" s="20"/>
-      <c r="F187" s="28"/>
-      <c r="G187" s="60">
+      <c r="E187" s="51"/>
+      <c r="F187" s="15"/>
+      <c r="G187" s="52">
         <v>47</v>
       </c>
-      <c r="H187" s="35">
+      <c r="H187" s="61">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="33" t="s">
+      <c r="A188" s="20" t="s">
         <v>378</v>
       </c>
-      <c r="B188" s="34" t="s">
+      <c r="B188" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="C188" s="39">
+      <c r="C188" s="32">
         <v>0</v>
       </c>
-      <c r="D188" s="39">
+      <c r="D188" s="32">
         <v>24</v>
       </c>
-      <c r="E188" s="19"/>
-      <c r="F188" s="28"/>
-      <c r="G188" s="61">
+      <c r="E188" s="50"/>
+      <c r="F188" s="15"/>
+      <c r="G188" s="53">
         <v>29</v>
       </c>
-      <c r="H188" s="35">
+      <c r="H188" s="61">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="15.75">
-      <c r="A189" s="13" t="s">
+      <c r="A189" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B189" s="49" t="s">
+      <c r="B189" s="29" t="s">
         <v>399</v>
       </c>
-      <c r="C189" s="39">
+      <c r="C189" s="32">
         <v>38</v>
       </c>
-      <c r="D189" s="38">
+      <c r="D189" s="31">
         <v>56</v>
       </c>
-      <c r="E189" s="17"/>
-      <c r="F189" s="28"/>
-      <c r="G189" s="61">
+      <c r="E189" s="45"/>
+      <c r="F189" s="15"/>
+      <c r="G189" s="53">
         <v>60</v>
       </c>
-      <c r="H189" s="35"/>
+      <c r="H189" s="22"/>
     </row>
     <row r="190" spans="1:8" ht="15.75">
-      <c r="A190" s="47" t="s">
+      <c r="A190" s="27" t="s">
         <v>384</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C190" s="39">
+      <c r="C190" s="32">
         <v>53</v>
       </c>
-      <c r="D190" s="38">
+      <c r="D190" s="31">
         <v>72</v>
       </c>
-      <c r="E190" s="11"/>
-      <c r="F190" s="29"/>
-      <c r="G190" s="62">
+      <c r="E190" s="37"/>
+      <c r="F190" s="16"/>
+      <c r="G190" s="31">
         <v>60</v>
       </c>
-      <c r="H190" s="35"/>
+      <c r="H190" s="22"/>
     </row>
     <row r="191" spans="1:8" ht="15.75">
-      <c r="A191" s="47" t="s">
+      <c r="A191" s="27" t="s">
         <v>385</v>
       </c>
-      <c r="B191" s="49" t="s">
+      <c r="B191" s="29" t="s">
         <v>400</v>
       </c>
-      <c r="C191" s="39">
+      <c r="C191" s="32">
         <v>75</v>
       </c>
-      <c r="D191" s="38">
+      <c r="D191" s="31">
         <v>69</v>
       </c>
-      <c r="E191" s="45"/>
-      <c r="F191" s="29"/>
-      <c r="G191" s="63">
+      <c r="E191" s="54"/>
+      <c r="F191" s="16"/>
+      <c r="G191" s="32">
         <v>51</v>
       </c>
-      <c r="H191" s="35"/>
+      <c r="H191" s="22"/>
     </row>
     <row r="192" spans="1:8" ht="15.75">
-      <c r="A192" s="48" t="s">
+      <c r="A192" s="28" t="s">
         <v>391</v>
       </c>
-      <c r="B192" s="49" t="s">
+      <c r="B192" s="29" t="s">
         <v>401</v>
       </c>
-      <c r="C192" s="39" t="s">
+      <c r="C192" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="D192" s="38">
+      <c r="D192" s="31">
         <v>71</v>
       </c>
-      <c r="E192" s="10"/>
-      <c r="F192" s="31"/>
-      <c r="G192" s="63"/>
-      <c r="H192" s="35"/>
+      <c r="E192" s="55"/>
+      <c r="F192" s="18"/>
+      <c r="G192" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="H192" s="22"/>
     </row>
     <row r="193" spans="1:8" ht="15.75">
-      <c r="A193" s="47" t="s">
+      <c r="A193" s="27" t="s">
         <v>386</v>
       </c>
-      <c r="B193" s="49" t="s">
+      <c r="B193" s="29" t="s">
         <v>402</v>
       </c>
-      <c r="C193" s="39">
+      <c r="C193" s="32">
         <v>22</v>
       </c>
-      <c r="D193" s="38">
+      <c r="D193" s="31">
         <v>54</v>
       </c>
-      <c r="E193" s="19"/>
-      <c r="F193" s="30"/>
-      <c r="G193" s="63">
+      <c r="E193" s="50"/>
+      <c r="F193" s="17"/>
+      <c r="G193" s="32">
         <v>62</v>
       </c>
-      <c r="H193" s="35"/>
+      <c r="H193" s="22"/>
     </row>
     <row r="194" spans="1:8" ht="15.75">
-      <c r="A194" s="47" t="s">
+      <c r="A194" s="27" t="s">
         <v>387</v>
       </c>
-      <c r="B194" s="49" t="s">
+      <c r="B194" s="29" t="s">
         <v>397</v>
       </c>
-      <c r="C194" s="39">
+      <c r="C194" s="32">
         <v>7</v>
       </c>
-      <c r="D194" s="38">
+      <c r="D194" s="31">
         <v>31</v>
       </c>
-      <c r="E194" s="11"/>
-      <c r="F194" s="29"/>
-      <c r="G194" s="63">
+      <c r="E194" s="37"/>
+      <c r="F194" s="16"/>
+      <c r="G194" s="32">
         <v>16</v>
       </c>
-      <c r="H194" s="35"/>
+      <c r="H194" s="22"/>
     </row>
     <row r="195" spans="1:8" ht="15.75">
-      <c r="A195" s="47" t="s">
+      <c r="A195" s="27" t="s">
         <v>388</v>
       </c>
-      <c r="B195" s="49" t="s">
+      <c r="B195" s="29" t="s">
         <v>403</v>
       </c>
-      <c r="C195" s="39">
+      <c r="C195" s="32">
         <v>41</v>
       </c>
-      <c r="D195" s="39" t="s">
+      <c r="D195" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="E195" s="21"/>
-      <c r="F195" s="31"/>
-      <c r="G195" s="63"/>
-      <c r="H195" s="35"/>
+      <c r="E195" s="56"/>
+      <c r="F195" s="18"/>
+      <c r="G195" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="H195" s="22"/>
     </row>
     <row r="196" spans="1:8" ht="15.75">
-      <c r="A196" s="47" t="s">
+      <c r="A196" s="27" t="s">
         <v>389</v>
       </c>
-      <c r="B196" s="49" t="s">
+      <c r="B196" s="29" t="s">
         <v>398</v>
       </c>
-      <c r="C196" s="39">
+      <c r="C196" s="32">
         <v>35</v>
       </c>
-      <c r="D196" s="39">
+      <c r="D196" s="32">
         <v>84</v>
       </c>
-      <c r="E196" s="45"/>
-      <c r="F196" s="32"/>
-      <c r="G196" s="63">
+      <c r="E196" s="54"/>
+      <c r="F196" s="19"/>
+      <c r="G196" s="32">
         <v>76</v>
       </c>
-      <c r="H196" s="35"/>
+      <c r="H196" s="22"/>
     </row>
     <row r="197" spans="1:8" ht="15.75">
-      <c r="A197" s="48" t="s">
+      <c r="A197" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="B197" s="49" t="s">
+      <c r="B197" s="29" t="s">
         <v>404</v>
       </c>
-      <c r="C197" s="39" t="s">
+      <c r="C197" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="D197" s="39">
+      <c r="D197" s="32">
         <v>42</v>
       </c>
-      <c r="E197" s="10"/>
-      <c r="F197" s="32"/>
-      <c r="G197" s="63"/>
-      <c r="H197" s="35"/>
+      <c r="E197" s="55"/>
+      <c r="F197" s="19"/>
+      <c r="G197" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="H197" s="22"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="48" t="s">
+      <c r="A198" s="28" t="s">
         <v>393</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="C198" s="39" t="s">
+      <c r="C198" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="D198" s="46" t="s">
+      <c r="D198" s="57" t="s">
         <v>382</v>
       </c>
-      <c r="E198" s="10"/>
-      <c r="F198" s="32"/>
-      <c r="G198" s="63"/>
-      <c r="H198" s="35"/>
+      <c r="E198" s="55"/>
+      <c r="F198" s="19"/>
+      <c r="G198" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="H198" s="22"/>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="47" t="s">
+      <c r="A199" s="27" t="s">
         <v>390</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="C199" s="41">
+      <c r="C199" s="58">
         <v>37</v>
       </c>
-      <c r="D199" s="41" t="s">
+      <c r="D199" s="58" t="s">
         <v>382</v>
       </c>
-      <c r="E199" s="10"/>
-      <c r="F199" s="42"/>
-      <c r="G199" s="64">
+      <c r="E199" s="55"/>
+      <c r="F199" s="25"/>
+      <c r="G199" s="58">
         <v>37</v>
       </c>
-      <c r="H199" s="35"/>
+      <c r="H199" s="22"/>
     </row>
     <row r="200" spans="1:8" ht="15.75">
-      <c r="A200" s="48" t="s">
+      <c r="A200" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="B200" s="50" t="s">
+      <c r="B200" s="30" t="s">
         <v>407</v>
       </c>
       <c r="C200" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="D200" s="12" t="s">
+      <c r="D200" s="59" t="s">
         <v>382</v>
       </c>
-      <c r="E200" s="10"/>
-      <c r="F200" s="44"/>
-      <c r="G200" s="63"/>
-      <c r="H200" s="35"/>
+      <c r="E200" s="55"/>
+      <c r="F200" s="26"/>
+      <c r="G200" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="H200" s="22"/>
     </row>
     <row r="201" spans="1:8" ht="15.75">
-      <c r="A201" s="48" t="s">
+      <c r="A201" s="28" t="s">
         <v>395</v>
       </c>
       <c r="B201" s="1" t="s">
@@ -6243,12 +6579,12 @@
       <c r="C201" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="D201" s="12" t="s">
+      <c r="D201" s="59" t="s">
         <v>382</v>
       </c>
-      <c r="E201" s="10"/>
-      <c r="F201" s="43"/>
-      <c r="G201" s="63">
+      <c r="E201" s="55"/>
+      <c r="F201" s="60"/>
+      <c r="G201" s="32">
         <v>14</v>
       </c>
       <c r="H201" s="8"/>
@@ -6260,12 +6596,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6413,24 +6746,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -6444,4 +6768,16 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>
--- a/MC3020_E24.xlsx
+++ b/MC3020_E24.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F82B06-FBC7-48A4-8CE8-D126A3C213A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E84997-9869-436B-89F7-5DACEEF39641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="409">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1724,7 +1724,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1761,18 +1761,6 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1785,12 +1773,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1860,23 +1842,11 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="14" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1887,8 +1857,37 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2222,18 +2221,18 @@
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="31">
+      <c r="C2" s="25">
         <v>24</v>
       </c>
-      <c r="D2" s="32">
+      <c r="D2" s="26">
         <v>54</v>
       </c>
-      <c r="E2" s="33"/>
+      <c r="E2" s="27"/>
       <c r="F2" s="12"/>
-      <c r="G2" s="34">
+      <c r="G2" s="28">
         <v>77</v>
       </c>
-      <c r="H2" s="61">
+      <c r="H2" s="50">
         <v>65.217391300000003</v>
       </c>
     </row>
@@ -2244,18 +2243,18 @@
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="25">
         <v>39</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="26">
         <v>75</v>
       </c>
-      <c r="E3" s="35"/>
+      <c r="E3" s="29"/>
       <c r="F3" s="13"/>
-      <c r="G3" s="36">
+      <c r="G3" s="30">
         <v>76</v>
       </c>
-      <c r="H3" s="61">
+      <c r="H3" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2266,18 +2265,18 @@
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="25">
         <v>43</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="25">
         <v>71</v>
       </c>
-      <c r="E4" s="37"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="13"/>
-      <c r="G4" s="38">
+      <c r="G4" s="32">
         <v>57</v>
       </c>
-      <c r="H4" s="61">
+      <c r="H4" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2288,18 +2287,18 @@
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="25">
         <v>30</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="25">
         <v>38</v>
       </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="38">
+      <c r="G5" s="32">
         <v>34</v>
       </c>
-      <c r="H5" s="61">
+      <c r="H5" s="50">
         <v>30.434782599999998</v>
       </c>
     </row>
@@ -2310,18 +2309,18 @@
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="25">
         <v>18</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="25">
         <v>37</v>
       </c>
-      <c r="E6" s="35"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="38">
+      <c r="G6" s="32">
         <v>48</v>
       </c>
-      <c r="H6" s="61">
+      <c r="H6" s="50">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -2332,18 +2331,18 @@
       <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="25">
         <v>12</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="26">
         <v>34</v>
       </c>
-      <c r="E7" s="35"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="13"/>
-      <c r="G7" s="38">
+      <c r="G7" s="32">
         <v>54</v>
       </c>
-      <c r="H7" s="61">
+      <c r="H7" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2354,18 +2353,18 @@
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="25">
         <v>69</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="26">
         <v>83</v>
       </c>
-      <c r="E8" s="35"/>
+      <c r="E8" s="29"/>
       <c r="F8" s="13"/>
-      <c r="G8" s="38">
+      <c r="G8" s="32">
         <v>76</v>
       </c>
-      <c r="H8" s="61">
+      <c r="H8" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2376,18 +2375,18 @@
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="25">
         <v>43</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="26">
         <v>68</v>
       </c>
-      <c r="E9" s="35"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="13"/>
-      <c r="G9" s="38">
+      <c r="G9" s="32">
         <v>59</v>
       </c>
-      <c r="H9" s="61">
+      <c r="H9" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -2398,18 +2397,18 @@
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="25">
         <v>38</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="25">
         <v>55</v>
       </c>
-      <c r="E10" s="35"/>
+      <c r="E10" s="29"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="38">
+      <c r="G10" s="32">
         <v>61</v>
       </c>
-      <c r="H10" s="61">
+      <c r="H10" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2420,18 +2419,18 @@
       <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="25">
         <v>16</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="26">
         <v>28</v>
       </c>
-      <c r="E11" s="35"/>
+      <c r="E11" s="29"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="38">
+      <c r="G11" s="32">
         <v>24</v>
       </c>
-      <c r="H11" s="61">
+      <c r="H11" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2442,18 +2441,18 @@
       <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="25">
         <v>84</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="25">
         <v>59</v>
       </c>
-      <c r="E12" s="35"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="13"/>
-      <c r="G12" s="38">
+      <c r="G12" s="32">
         <v>60</v>
       </c>
-      <c r="H12" s="61">
+      <c r="H12" s="50">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -2464,18 +2463,18 @@
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="25">
         <v>39</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="26">
         <v>43</v>
       </c>
-      <c r="E13" s="35"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="13"/>
-      <c r="G13" s="38">
+      <c r="G13" s="32">
         <v>55</v>
       </c>
-      <c r="H13" s="61">
+      <c r="H13" s="50">
         <v>90.909090899999995</v>
       </c>
     </row>
@@ -2486,18 +2485,18 @@
       <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="25">
         <v>61</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="25">
         <v>89</v>
       </c>
-      <c r="E14" s="35"/>
+      <c r="E14" s="29"/>
       <c r="F14" s="13"/>
-      <c r="G14" s="38">
+      <c r="G14" s="32">
         <v>76</v>
       </c>
-      <c r="H14" s="61">
+      <c r="H14" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2508,18 +2507,18 @@
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="25">
         <v>80</v>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="26">
         <v>42</v>
       </c>
-      <c r="E15" s="35"/>
+      <c r="E15" s="29"/>
       <c r="F15" s="13"/>
-      <c r="G15" s="38">
+      <c r="G15" s="32">
         <v>55</v>
       </c>
-      <c r="H15" s="61">
+      <c r="H15" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -2530,18 +2529,18 @@
       <c r="B16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="25">
         <v>33</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="25">
         <v>46</v>
       </c>
-      <c r="E16" s="33"/>
+      <c r="E16" s="27"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="39">
+      <c r="G16" s="33">
         <v>56</v>
       </c>
-      <c r="H16" s="61">
+      <c r="H16" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2552,18 +2551,18 @@
       <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="25">
         <v>45</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="26">
         <v>68</v>
       </c>
-      <c r="E17" s="35"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="38">
+      <c r="G17" s="32">
         <v>87</v>
       </c>
-      <c r="H17" s="61">
+      <c r="H17" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2574,18 +2573,18 @@
       <c r="B18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="25">
         <v>52</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="25">
         <v>54</v>
       </c>
-      <c r="E18" s="35"/>
+      <c r="E18" s="29"/>
       <c r="F18" s="13"/>
-      <c r="G18" s="38">
+      <c r="G18" s="32">
         <v>75</v>
       </c>
-      <c r="H18" s="61">
+      <c r="H18" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -2596,18 +2595,18 @@
       <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="25">
         <v>86</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="25">
         <v>94</v>
       </c>
-      <c r="E19" s="35"/>
+      <c r="E19" s="29"/>
       <c r="F19" s="13"/>
-      <c r="G19" s="38">
+      <c r="G19" s="32">
         <v>83</v>
       </c>
-      <c r="H19" s="61">
+      <c r="H19" s="50">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -2618,18 +2617,18 @@
       <c r="B20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="25">
         <v>76</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="25">
         <v>78</v>
       </c>
-      <c r="E20" s="35"/>
+      <c r="E20" s="29"/>
       <c r="F20" s="13"/>
-      <c r="G20" s="38">
+      <c r="G20" s="32">
         <v>63</v>
       </c>
-      <c r="H20" s="61">
+      <c r="H20" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2640,18 +2639,18 @@
       <c r="B21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="25">
         <v>99</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="25">
         <v>84</v>
       </c>
-      <c r="E21" s="35"/>
+      <c r="E21" s="29"/>
       <c r="F21" s="13"/>
-      <c r="G21" s="38">
+      <c r="G21" s="32">
         <v>74</v>
       </c>
-      <c r="H21" s="61">
+      <c r="H21" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2662,18 +2661,18 @@
       <c r="B22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="25">
         <v>34</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="26">
         <v>51</v>
       </c>
-      <c r="E22" s="35"/>
+      <c r="E22" s="29"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="38">
+      <c r="G22" s="32">
         <v>38</v>
       </c>
-      <c r="H22" s="61">
+      <c r="H22" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2684,18 +2683,18 @@
       <c r="B23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="25">
         <v>71</v>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="26">
         <v>87</v>
       </c>
-      <c r="E23" s="35"/>
+      <c r="E23" s="29"/>
       <c r="F23" s="13"/>
-      <c r="G23" s="38">
+      <c r="G23" s="32">
         <v>76</v>
       </c>
-      <c r="H23" s="61">
+      <c r="H23" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2706,18 +2705,18 @@
       <c r="B24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="25">
         <v>64</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="26">
         <v>40</v>
       </c>
-      <c r="E24" s="35"/>
+      <c r="E24" s="29"/>
       <c r="F24" s="13"/>
-      <c r="G24" s="38">
+      <c r="G24" s="32">
         <v>44</v>
       </c>
-      <c r="H24" s="61">
+      <c r="H24" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2728,18 +2727,18 @@
       <c r="B25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="26">
         <v>63</v>
       </c>
-      <c r="E25" s="35"/>
+      <c r="E25" s="29"/>
       <c r="F25" s="13"/>
-      <c r="G25" s="38">
+      <c r="G25" s="32">
         <v>67</v>
       </c>
-      <c r="H25" s="61">
+      <c r="H25" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2750,18 +2749,18 @@
       <c r="B26" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="25">
         <v>68</v>
       </c>
-      <c r="D26" s="32">
+      <c r="D26" s="26">
         <v>73</v>
       </c>
-      <c r="E26" s="35"/>
+      <c r="E26" s="29"/>
       <c r="F26" s="13"/>
-      <c r="G26" s="38">
+      <c r="G26" s="32">
         <v>71</v>
       </c>
-      <c r="H26" s="61">
+      <c r="H26" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2772,18 +2771,18 @@
       <c r="B27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="25">
         <v>43</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="25">
         <v>72</v>
       </c>
-      <c r="E27" s="35"/>
+      <c r="E27" s="29"/>
       <c r="F27" s="13"/>
-      <c r="G27" s="38">
+      <c r="G27" s="32">
         <v>82</v>
       </c>
-      <c r="H27" s="61">
+      <c r="H27" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2794,18 +2793,18 @@
       <c r="B28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="25">
         <v>30</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="26">
         <v>85</v>
       </c>
-      <c r="E28" s="35"/>
+      <c r="E28" s="29"/>
       <c r="F28" s="13"/>
-      <c r="G28" s="38">
+      <c r="G28" s="32">
         <v>62</v>
       </c>
-      <c r="H28" s="61">
+      <c r="H28" s="50">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -2816,18 +2815,18 @@
       <c r="B29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="25">
         <v>65</v>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="26">
         <v>84</v>
       </c>
-      <c r="E29" s="35"/>
+      <c r="E29" s="29"/>
       <c r="F29" s="13"/>
-      <c r="G29" s="38">
+      <c r="G29" s="32">
         <v>75</v>
       </c>
-      <c r="H29" s="61">
+      <c r="H29" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2838,18 +2837,18 @@
       <c r="B30" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="25">
         <v>69</v>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="26">
         <v>25</v>
       </c>
-      <c r="E30" s="35"/>
+      <c r="E30" s="29"/>
       <c r="F30" s="13"/>
-      <c r="G30" s="38">
+      <c r="G30" s="32">
         <v>63</v>
       </c>
-      <c r="H30" s="61">
+      <c r="H30" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2860,18 +2859,18 @@
       <c r="B31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="25">
         <v>44</v>
       </c>
-      <c r="D31" s="32">
+      <c r="D31" s="26">
         <v>34</v>
       </c>
-      <c r="E31" s="35"/>
+      <c r="E31" s="29"/>
       <c r="F31" s="13"/>
-      <c r="G31" s="40">
+      <c r="G31" s="34">
         <v>61</v>
       </c>
-      <c r="H31" s="61">
+      <c r="H31" s="50">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -2882,18 +2881,18 @@
       <c r="B32" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="25">
         <v>61</v>
       </c>
-      <c r="D32" s="32">
+      <c r="D32" s="26">
         <v>85</v>
       </c>
-      <c r="E32" s="35"/>
+      <c r="E32" s="29"/>
       <c r="F32" s="13"/>
-      <c r="G32" s="38">
+      <c r="G32" s="32">
         <v>81</v>
       </c>
-      <c r="H32" s="61">
+      <c r="H32" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2904,18 +2903,18 @@
       <c r="B33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C33" s="25">
         <v>49</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="26">
         <v>67</v>
       </c>
-      <c r="E33" s="35"/>
+      <c r="E33" s="29"/>
       <c r="F33" s="13"/>
-      <c r="G33" s="38">
+      <c r="G33" s="32">
         <v>71</v>
       </c>
-      <c r="H33" s="61">
+      <c r="H33" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2926,18 +2925,18 @@
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="25">
         <v>50</v>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="26">
         <v>45</v>
       </c>
-      <c r="E34" s="35"/>
+      <c r="E34" s="29"/>
       <c r="F34" s="13"/>
-      <c r="G34" s="38">
+      <c r="G34" s="32">
         <v>43</v>
       </c>
-      <c r="H34" s="61">
+      <c r="H34" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2948,18 +2947,18 @@
       <c r="B35" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="25">
         <v>48</v>
       </c>
-      <c r="D35" s="31">
+      <c r="D35" s="25">
         <v>55</v>
       </c>
-      <c r="E35" s="35"/>
+      <c r="E35" s="29"/>
       <c r="F35" s="13"/>
-      <c r="G35" s="38">
+      <c r="G35" s="32">
         <v>56</v>
       </c>
-      <c r="H35" s="61">
+      <c r="H35" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2970,18 +2969,18 @@
       <c r="B36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="25">
         <v>49</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="26">
         <v>57</v>
       </c>
-      <c r="E36" s="35"/>
+      <c r="E36" s="29"/>
       <c r="F36" s="13"/>
-      <c r="G36" s="38">
+      <c r="G36" s="32">
         <v>49</v>
       </c>
-      <c r="H36" s="61">
+      <c r="H36" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2992,18 +2991,18 @@
       <c r="B37" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="25">
         <v>58</v>
       </c>
-      <c r="D37" s="32">
+      <c r="D37" s="26">
         <v>41</v>
       </c>
-      <c r="E37" s="35"/>
+      <c r="E37" s="29"/>
       <c r="F37" s="13"/>
-      <c r="G37" s="38">
+      <c r="G37" s="32">
         <v>54</v>
       </c>
-      <c r="H37" s="61">
+      <c r="H37" s="50">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -3014,18 +3013,18 @@
       <c r="B38" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="25">
         <v>81</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="26">
         <v>84</v>
       </c>
-      <c r="E38" s="35"/>
+      <c r="E38" s="29"/>
       <c r="F38" s="13"/>
-      <c r="G38" s="38">
+      <c r="G38" s="32">
         <v>72</v>
       </c>
-      <c r="H38" s="61">
+      <c r="H38" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3036,18 +3035,18 @@
       <c r="B39" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="25">
         <v>23</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="26">
         <v>61</v>
       </c>
-      <c r="E39" s="35"/>
+      <c r="E39" s="29"/>
       <c r="F39" s="13"/>
-      <c r="G39" s="38">
+      <c r="G39" s="32">
         <v>58</v>
       </c>
-      <c r="H39" s="61">
+      <c r="H39" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3058,18 +3057,18 @@
       <c r="B40" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="25">
         <v>32</v>
       </c>
-      <c r="D40" s="31">
+      <c r="D40" s="25">
         <v>37</v>
       </c>
-      <c r="E40" s="35"/>
+      <c r="E40" s="29"/>
       <c r="F40" s="13"/>
-      <c r="G40" s="38">
+      <c r="G40" s="32">
         <v>57</v>
       </c>
-      <c r="H40" s="61">
+      <c r="H40" s="50">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3080,18 +3079,18 @@
       <c r="B41" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="25">
         <v>18</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="25">
         <v>52</v>
       </c>
-      <c r="E41" s="35"/>
+      <c r="E41" s="29"/>
       <c r="F41" s="13"/>
-      <c r="G41" s="38">
+      <c r="G41" s="32">
         <v>37</v>
       </c>
-      <c r="H41" s="61">
+      <c r="H41" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3102,18 +3101,18 @@
       <c r="B42" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="25">
         <v>46</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="26">
         <v>75</v>
       </c>
-      <c r="E42" s="35"/>
+      <c r="E42" s="29"/>
       <c r="F42" s="13"/>
-      <c r="G42" s="38">
+      <c r="G42" s="32">
         <v>67</v>
       </c>
-      <c r="H42" s="61">
+      <c r="H42" s="50">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -3124,18 +3123,18 @@
       <c r="B43" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="25">
         <v>53</v>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="25">
         <v>50</v>
       </c>
-      <c r="E43" s="35"/>
+      <c r="E43" s="29"/>
       <c r="F43" s="13"/>
-      <c r="G43" s="38">
+      <c r="G43" s="32">
         <v>69</v>
       </c>
-      <c r="H43" s="61">
+      <c r="H43" s="50">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3146,18 +3145,18 @@
       <c r="B44" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="25">
         <v>60</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="25">
         <v>39</v>
       </c>
-      <c r="E44" s="35"/>
+      <c r="E44" s="29"/>
       <c r="F44" s="13"/>
-      <c r="G44" s="38">
+      <c r="G44" s="32">
         <v>35</v>
       </c>
-      <c r="H44" s="61">
+      <c r="H44" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3168,18 +3167,18 @@
       <c r="B45" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="25">
         <v>58</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="26">
         <v>79</v>
       </c>
-      <c r="E45" s="35"/>
+      <c r="E45" s="29"/>
       <c r="F45" s="13"/>
-      <c r="G45" s="38">
+      <c r="G45" s="32">
         <v>72</v>
       </c>
-      <c r="H45" s="61">
+      <c r="H45" s="50">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -3190,18 +3189,18 @@
       <c r="B46" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="25">
         <v>60</v>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="25">
         <v>70</v>
       </c>
-      <c r="E46" s="35"/>
+      <c r="E46" s="29"/>
       <c r="F46" s="13"/>
-      <c r="G46" s="38">
+      <c r="G46" s="32">
         <v>45</v>
       </c>
-      <c r="H46" s="61">
+      <c r="H46" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3212,18 +3211,18 @@
       <c r="B47" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="25">
         <v>18</v>
       </c>
-      <c r="D47" s="32">
+      <c r="D47" s="26">
         <v>64</v>
       </c>
-      <c r="E47" s="35"/>
+      <c r="E47" s="29"/>
       <c r="F47" s="13"/>
-      <c r="G47" s="38">
+      <c r="G47" s="32">
         <v>55</v>
       </c>
-      <c r="H47" s="61">
+      <c r="H47" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3234,18 +3233,18 @@
       <c r="B48" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="25">
         <v>77</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="26">
         <v>64</v>
       </c>
-      <c r="E48" s="35"/>
+      <c r="E48" s="29"/>
       <c r="F48" s="13"/>
-      <c r="G48" s="40">
+      <c r="G48" s="34">
         <v>64</v>
       </c>
-      <c r="H48" s="61">
+      <c r="H48" s="50">
         <v>21.739130400000001</v>
       </c>
     </row>
@@ -3256,18 +3255,18 @@
       <c r="B49" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="25">
         <v>36</v>
       </c>
-      <c r="D49" s="32">
+      <c r="D49" s="26">
         <v>81</v>
       </c>
-      <c r="E49" s="35"/>
+      <c r="E49" s="29"/>
       <c r="F49" s="13"/>
-      <c r="G49" s="38">
+      <c r="G49" s="32">
         <v>39</v>
       </c>
-      <c r="H49" s="61">
+      <c r="H49" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3278,18 +3277,18 @@
       <c r="B50" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="25">
         <v>47</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="26">
         <v>63</v>
       </c>
-      <c r="E50" s="35"/>
+      <c r="E50" s="29"/>
       <c r="F50" s="13"/>
-      <c r="G50" s="38">
+      <c r="G50" s="32">
         <v>68</v>
       </c>
-      <c r="H50" s="61">
+      <c r="H50" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3300,18 +3299,18 @@
       <c r="B51" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="25">
         <v>59</v>
       </c>
-      <c r="D51" s="31">
+      <c r="D51" s="25">
         <v>90</v>
       </c>
-      <c r="E51" s="35"/>
+      <c r="E51" s="29"/>
       <c r="F51" s="13"/>
-      <c r="G51" s="38">
+      <c r="G51" s="32">
         <v>67</v>
       </c>
-      <c r="H51" s="61">
+      <c r="H51" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3322,18 +3321,18 @@
       <c r="B52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="25">
         <v>68</v>
       </c>
-      <c r="D52" s="31">
+      <c r="D52" s="25">
         <v>42</v>
       </c>
-      <c r="E52" s="35"/>
+      <c r="E52" s="29"/>
       <c r="F52" s="13"/>
-      <c r="G52" s="38">
+      <c r="G52" s="32">
         <v>41</v>
       </c>
-      <c r="H52" s="61">
+      <c r="H52" s="50">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -3344,18 +3343,18 @@
       <c r="B53" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="25">
         <v>41</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="26">
         <v>60</v>
       </c>
-      <c r="E53" s="35"/>
+      <c r="E53" s="29"/>
       <c r="F53" s="13"/>
-      <c r="G53" s="38">
+      <c r="G53" s="32">
         <v>39</v>
       </c>
-      <c r="H53" s="61">
+      <c r="H53" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3366,18 +3365,18 @@
       <c r="B54" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="25">
         <v>54</v>
       </c>
-      <c r="D54" s="31">
+      <c r="D54" s="25">
         <v>76</v>
       </c>
-      <c r="E54" s="35"/>
+      <c r="E54" s="29"/>
       <c r="F54" s="13"/>
-      <c r="G54" s="38">
+      <c r="G54" s="32">
         <v>68</v>
       </c>
-      <c r="H54" s="61">
+      <c r="H54" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3388,18 +3387,18 @@
       <c r="B55" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="25">
         <v>51</v>
       </c>
-      <c r="D55" s="32">
+      <c r="D55" s="26">
         <v>89</v>
       </c>
-      <c r="E55" s="35"/>
+      <c r="E55" s="29"/>
       <c r="F55" s="13"/>
-      <c r="G55" s="40">
+      <c r="G55" s="34">
         <v>84</v>
       </c>
-      <c r="H55" s="61">
+      <c r="H55" s="50">
         <v>100</v>
       </c>
     </row>
@@ -3410,18 +3409,18 @@
       <c r="B56" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="25">
         <v>100</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="26">
         <v>96</v>
       </c>
-      <c r="E56" s="35"/>
+      <c r="E56" s="29"/>
       <c r="F56" s="13"/>
-      <c r="G56" s="38">
+      <c r="G56" s="32">
         <v>63</v>
       </c>
-      <c r="H56" s="61">
+      <c r="H56" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3432,18 +3431,18 @@
       <c r="B57" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="25">
         <v>21</v>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="26">
         <v>37</v>
       </c>
-      <c r="E57" s="35"/>
+      <c r="E57" s="29"/>
       <c r="F57" s="13"/>
-      <c r="G57" s="38">
+      <c r="G57" s="32">
         <v>49</v>
       </c>
-      <c r="H57" s="61">
+      <c r="H57" s="50">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3454,18 +3453,18 @@
       <c r="B58" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="25">
         <v>32</v>
       </c>
-      <c r="D58" s="31">
+      <c r="D58" s="25">
         <v>20</v>
       </c>
-      <c r="E58" s="35"/>
+      <c r="E58" s="29"/>
       <c r="F58" s="13"/>
-      <c r="G58" s="38">
+      <c r="G58" s="32">
         <v>28</v>
       </c>
-      <c r="H58" s="61">
+      <c r="H58" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3476,18 +3475,18 @@
       <c r="B59" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C59" s="25">
         <v>23</v>
       </c>
-      <c r="D59" s="32">
+      <c r="D59" s="26">
         <v>36</v>
       </c>
-      <c r="E59" s="35"/>
+      <c r="E59" s="29"/>
       <c r="F59" s="13"/>
-      <c r="G59" s="38">
+      <c r="G59" s="32">
         <v>44</v>
       </c>
-      <c r="H59" s="61">
+      <c r="H59" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3498,18 +3497,18 @@
       <c r="B60" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C60" s="25">
         <v>42</v>
       </c>
-      <c r="D60" s="32">
+      <c r="D60" s="26">
         <v>28</v>
       </c>
-      <c r="E60" s="33"/>
+      <c r="E60" s="27"/>
       <c r="F60" s="14"/>
-      <c r="G60" s="39">
+      <c r="G60" s="33">
         <v>60</v>
       </c>
-      <c r="H60" s="61">
+      <c r="H60" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3520,18 +3519,18 @@
       <c r="B61" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C61" s="25">
         <v>58</v>
       </c>
-      <c r="D61" s="32">
+      <c r="D61" s="26">
         <v>68</v>
       </c>
-      <c r="E61" s="35"/>
+      <c r="E61" s="29"/>
       <c r="F61" s="13"/>
-      <c r="G61" s="38">
+      <c r="G61" s="32">
         <v>86</v>
       </c>
-      <c r="H61" s="61">
+      <c r="H61" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3542,18 +3541,18 @@
       <c r="B62" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="25">
         <v>64</v>
       </c>
-      <c r="D62" s="32" t="s">
+      <c r="D62" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="E62" s="35"/>
+      <c r="E62" s="29"/>
       <c r="F62" s="13"/>
-      <c r="G62" s="38">
+      <c r="G62" s="32">
         <v>52</v>
       </c>
-      <c r="H62" s="61">
+      <c r="H62" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3564,18 +3563,18 @@
       <c r="B63" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="25">
         <v>54</v>
       </c>
-      <c r="D63" s="32">
+      <c r="D63" s="26">
         <v>57</v>
       </c>
-      <c r="E63" s="35"/>
+      <c r="E63" s="29"/>
       <c r="F63" s="13"/>
-      <c r="G63" s="38">
+      <c r="G63" s="32">
         <v>64</v>
       </c>
-      <c r="H63" s="61">
+      <c r="H63" s="50">
         <v>100</v>
       </c>
     </row>
@@ -3586,18 +3585,18 @@
       <c r="B64" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C64" s="31">
+      <c r="C64" s="25">
         <v>30</v>
       </c>
-      <c r="D64" s="32">
+      <c r="D64" s="26">
         <v>40</v>
       </c>
-      <c r="E64" s="35"/>
+      <c r="E64" s="29"/>
       <c r="F64" s="13"/>
-      <c r="G64" s="38">
+      <c r="G64" s="32">
         <v>46</v>
       </c>
-      <c r="H64" s="61">
+      <c r="H64" s="50">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -3608,18 +3607,18 @@
       <c r="B65" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="25">
         <v>30</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65" s="26">
         <v>48</v>
       </c>
-      <c r="E65" s="35"/>
+      <c r="E65" s="29"/>
       <c r="F65" s="13"/>
-      <c r="G65" s="38">
+      <c r="G65" s="32">
         <v>47</v>
       </c>
-      <c r="H65" s="61">
+      <c r="H65" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3630,18 +3629,18 @@
       <c r="B66" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="25">
         <v>47</v>
       </c>
-      <c r="D66" s="32">
+      <c r="D66" s="26">
         <v>84</v>
       </c>
-      <c r="E66" s="35"/>
+      <c r="E66" s="29"/>
       <c r="F66" s="13"/>
-      <c r="G66" s="38">
+      <c r="G66" s="32">
         <v>54</v>
       </c>
-      <c r="H66" s="61">
+      <c r="H66" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3652,18 +3651,18 @@
       <c r="B67" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C67" s="31">
+      <c r="C67" s="25">
         <v>38</v>
       </c>
-      <c r="D67" s="32">
+      <c r="D67" s="26">
         <v>50</v>
       </c>
-      <c r="E67" s="35"/>
+      <c r="E67" s="29"/>
       <c r="F67" s="13"/>
-      <c r="G67" s="38">
+      <c r="G67" s="32">
         <v>27</v>
       </c>
-      <c r="H67" s="61">
+      <c r="H67" s="50">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3674,18 +3673,18 @@
       <c r="B68" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="25">
         <v>47</v>
       </c>
-      <c r="D68" s="32">
+      <c r="D68" s="26">
         <v>73</v>
       </c>
-      <c r="E68" s="35"/>
+      <c r="E68" s="29"/>
       <c r="F68" s="13"/>
-      <c r="G68" s="40">
+      <c r="G68" s="34">
         <v>62</v>
       </c>
-      <c r="H68" s="61">
+      <c r="H68" s="50">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3696,18 +3695,18 @@
       <c r="B69" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="25">
         <v>36</v>
       </c>
-      <c r="D69" s="31">
+      <c r="D69" s="25">
         <v>17</v>
       </c>
-      <c r="E69" s="35"/>
+      <c r="E69" s="29"/>
       <c r="F69" s="13"/>
-      <c r="G69" s="38">
+      <c r="G69" s="32">
         <v>28</v>
       </c>
-      <c r="H69" s="61">
+      <c r="H69" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3718,18 +3717,18 @@
       <c r="B70" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C70" s="31">
+      <c r="C70" s="25">
         <v>47</v>
       </c>
-      <c r="D70" s="32">
+      <c r="D70" s="26">
         <v>60</v>
       </c>
-      <c r="E70" s="35"/>
+      <c r="E70" s="29"/>
       <c r="F70" s="13"/>
-      <c r="G70" s="38">
+      <c r="G70" s="32">
         <v>37</v>
       </c>
-      <c r="H70" s="61">
+      <c r="H70" s="50">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3740,18 +3739,18 @@
       <c r="B71" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C71" s="31">
+      <c r="C71" s="25">
         <v>43</v>
       </c>
-      <c r="D71" s="31">
+      <c r="D71" s="25">
         <v>74</v>
       </c>
-      <c r="E71" s="35"/>
+      <c r="E71" s="29"/>
       <c r="F71" s="13"/>
-      <c r="G71" s="38">
+      <c r="G71" s="32">
         <v>58</v>
       </c>
-      <c r="H71" s="61">
+      <c r="H71" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3762,18 +3761,18 @@
       <c r="B72" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="25">
         <v>46</v>
       </c>
-      <c r="D72" s="31">
+      <c r="D72" s="25">
         <v>68</v>
       </c>
-      <c r="E72" s="35"/>
+      <c r="E72" s="29"/>
       <c r="F72" s="13"/>
-      <c r="G72" s="38">
+      <c r="G72" s="32">
         <v>26</v>
       </c>
-      <c r="H72" s="61">
+      <c r="H72" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3784,18 +3783,18 @@
       <c r="B73" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C73" s="31">
+      <c r="C73" s="25">
         <v>51</v>
       </c>
-      <c r="D73" s="32">
+      <c r="D73" s="26">
         <v>80</v>
       </c>
-      <c r="E73" s="35"/>
+      <c r="E73" s="29"/>
       <c r="F73" s="13"/>
-      <c r="G73" s="40">
+      <c r="G73" s="34">
         <v>77</v>
       </c>
-      <c r="H73" s="61">
+      <c r="H73" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3806,18 +3805,18 @@
       <c r="B74" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C74" s="31">
+      <c r="C74" s="25">
         <v>73</v>
       </c>
-      <c r="D74" s="32">
+      <c r="D74" s="26">
         <v>58</v>
       </c>
-      <c r="E74" s="35"/>
+      <c r="E74" s="29"/>
       <c r="F74" s="13"/>
-      <c r="G74" s="38">
+      <c r="G74" s="32">
         <v>60</v>
       </c>
-      <c r="H74" s="61">
+      <c r="H74" s="50">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3828,18 +3827,18 @@
       <c r="B75" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C75" s="31">
+      <c r="C75" s="25">
         <v>0</v>
       </c>
-      <c r="D75" s="31">
+      <c r="D75" s="25">
         <v>60</v>
       </c>
-      <c r="E75" s="35"/>
+      <c r="E75" s="29"/>
       <c r="F75" s="13"/>
-      <c r="G75" s="38">
+      <c r="G75" s="32">
         <v>58</v>
       </c>
-      <c r="H75" s="61">
+      <c r="H75" s="50">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3850,18 +3849,18 @@
       <c r="B76" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C76" s="31">
+      <c r="C76" s="25">
         <v>55</v>
       </c>
-      <c r="D76" s="32">
+      <c r="D76" s="26">
         <v>44</v>
       </c>
-      <c r="E76" s="35"/>
+      <c r="E76" s="29"/>
       <c r="F76" s="13"/>
-      <c r="G76" s="38">
+      <c r="G76" s="32">
         <v>47</v>
       </c>
-      <c r="H76" s="61">
+      <c r="H76" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3872,18 +3871,18 @@
       <c r="B77" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C77" s="31">
+      <c r="C77" s="25">
         <v>56</v>
       </c>
-      <c r="D77" s="32">
+      <c r="D77" s="26">
         <v>48</v>
       </c>
-      <c r="E77" s="35"/>
+      <c r="E77" s="29"/>
       <c r="F77" s="13"/>
-      <c r="G77" s="38">
+      <c r="G77" s="32">
         <v>59</v>
       </c>
-      <c r="H77" s="61">
+      <c r="H77" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3894,18 +3893,18 @@
       <c r="B78" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C78" s="31">
+      <c r="C78" s="25">
         <v>35</v>
       </c>
-      <c r="D78" s="31">
+      <c r="D78" s="25">
         <v>68</v>
       </c>
-      <c r="E78" s="35"/>
+      <c r="E78" s="29"/>
       <c r="F78" s="13"/>
-      <c r="G78" s="38">
+      <c r="G78" s="32">
         <v>77</v>
       </c>
-      <c r="H78" s="61">
+      <c r="H78" s="50">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -3916,18 +3915,18 @@
       <c r="B79" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C79" s="31">
+      <c r="C79" s="25">
         <v>32</v>
       </c>
-      <c r="D79" s="32">
+      <c r="D79" s="26">
         <v>41</v>
       </c>
-      <c r="E79" s="35"/>
+      <c r="E79" s="29"/>
       <c r="F79" s="13"/>
-      <c r="G79" s="38">
+      <c r="G79" s="32">
         <v>49</v>
       </c>
-      <c r="H79" s="61">
+      <c r="H79" s="50">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -3938,18 +3937,18 @@
       <c r="B80" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C80" s="31">
+      <c r="C80" s="25">
         <v>71</v>
       </c>
-      <c r="D80" s="32">
+      <c r="D80" s="26">
         <v>56</v>
       </c>
-      <c r="E80" s="35"/>
+      <c r="E80" s="29"/>
       <c r="F80" s="13"/>
-      <c r="G80" s="38">
+      <c r="G80" s="32">
         <v>51</v>
       </c>
-      <c r="H80" s="61">
+      <c r="H80" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3960,18 +3959,18 @@
       <c r="B81" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C81" s="31">
+      <c r="C81" s="25">
         <v>56</v>
       </c>
-      <c r="D81" s="32">
+      <c r="D81" s="26">
         <v>63</v>
       </c>
-      <c r="E81" s="35"/>
+      <c r="E81" s="29"/>
       <c r="F81" s="13"/>
-      <c r="G81" s="38">
+      <c r="G81" s="32">
         <v>64</v>
       </c>
-      <c r="H81" s="61">
+      <c r="H81" s="50">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -3982,18 +3981,18 @@
       <c r="B82" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C82" s="31">
+      <c r="C82" s="25">
         <v>52</v>
       </c>
-      <c r="D82" s="32">
+      <c r="D82" s="26">
         <v>30</v>
       </c>
-      <c r="E82" s="35"/>
+      <c r="E82" s="29"/>
       <c r="F82" s="13"/>
-      <c r="G82" s="38">
+      <c r="G82" s="32">
         <v>32</v>
       </c>
-      <c r="H82" s="61">
+      <c r="H82" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4004,18 +4003,18 @@
       <c r="B83" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C83" s="31">
+      <c r="C83" s="25">
         <v>34</v>
       </c>
-      <c r="D83" s="32">
+      <c r="D83" s="26">
         <v>85</v>
       </c>
-      <c r="E83" s="35"/>
+      <c r="E83" s="29"/>
       <c r="F83" s="13"/>
-      <c r="G83" s="40">
+      <c r="G83" s="34">
         <v>57</v>
       </c>
-      <c r="H83" s="61">
+      <c r="H83" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4026,18 +4025,18 @@
       <c r="B84" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C84" s="31">
+      <c r="C84" s="25">
         <v>42</v>
       </c>
-      <c r="D84" s="31">
+      <c r="D84" s="25">
         <v>34</v>
       </c>
-      <c r="E84" s="35"/>
+      <c r="E84" s="29"/>
       <c r="F84" s="13"/>
-      <c r="G84" s="38">
+      <c r="G84" s="32">
         <v>44</v>
       </c>
-      <c r="H84" s="61">
+      <c r="H84" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4048,18 +4047,18 @@
       <c r="B85" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C85" s="31">
+      <c r="C85" s="25">
         <v>51</v>
       </c>
-      <c r="D85" s="31">
+      <c r="D85" s="25">
         <v>67</v>
       </c>
-      <c r="E85" s="33"/>
+      <c r="E85" s="27"/>
       <c r="F85" s="14"/>
-      <c r="G85" s="39">
+      <c r="G85" s="33">
         <v>58</v>
       </c>
-      <c r="H85" s="61">
+      <c r="H85" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4070,18 +4069,18 @@
       <c r="B86" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C86" s="31">
+      <c r="C86" s="25">
         <v>17</v>
       </c>
-      <c r="D86" s="32">
+      <c r="D86" s="26">
         <v>49</v>
       </c>
-      <c r="E86" s="35"/>
+      <c r="E86" s="29"/>
       <c r="F86" s="13"/>
-      <c r="G86" s="38">
+      <c r="G86" s="32">
         <v>64</v>
       </c>
-      <c r="H86" s="61">
+      <c r="H86" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4092,18 +4091,18 @@
       <c r="B87" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C87" s="31">
+      <c r="C87" s="25">
         <v>34</v>
       </c>
-      <c r="D87" s="32">
+      <c r="D87" s="26">
         <v>58</v>
       </c>
-      <c r="E87" s="35"/>
+      <c r="E87" s="29"/>
       <c r="F87" s="13"/>
-      <c r="G87" s="38">
+      <c r="G87" s="32">
         <v>58</v>
       </c>
-      <c r="H87" s="61">
+      <c r="H87" s="50">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -4114,18 +4113,18 @@
       <c r="B88" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="31">
+      <c r="C88" s="25">
         <v>60</v>
       </c>
-      <c r="D88" s="32">
+      <c r="D88" s="26">
         <v>47</v>
       </c>
-      <c r="E88" s="35"/>
+      <c r="E88" s="29"/>
       <c r="F88" s="13"/>
-      <c r="G88" s="38">
+      <c r="G88" s="32">
         <v>81</v>
       </c>
-      <c r="H88" s="61">
+      <c r="H88" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4136,18 +4135,18 @@
       <c r="B89" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C89" s="31">
+      <c r="C89" s="25">
         <v>29</v>
       </c>
-      <c r="D89" s="32">
+      <c r="D89" s="26">
         <v>58</v>
       </c>
-      <c r="E89" s="35"/>
+      <c r="E89" s="29"/>
       <c r="F89" s="13"/>
-      <c r="G89" s="38">
+      <c r="G89" s="32">
         <v>75</v>
       </c>
-      <c r="H89" s="61">
+      <c r="H89" s="50">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4158,18 +4157,18 @@
       <c r="B90" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C90" s="31">
+      <c r="C90" s="25">
         <v>25</v>
       </c>
-      <c r="D90" s="32">
+      <c r="D90" s="26">
         <v>84</v>
       </c>
-      <c r="E90" s="35"/>
+      <c r="E90" s="29"/>
       <c r="F90" s="13"/>
-      <c r="G90" s="40">
+      <c r="G90" s="34">
         <v>54</v>
       </c>
-      <c r="H90" s="61">
+      <c r="H90" s="50">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -4180,18 +4179,18 @@
       <c r="B91" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C91" s="31">
+      <c r="C91" s="25">
         <v>33</v>
       </c>
-      <c r="D91" s="31">
+      <c r="D91" s="25">
         <v>66</v>
       </c>
-      <c r="E91" s="35"/>
+      <c r="E91" s="29"/>
       <c r="F91" s="13"/>
-      <c r="G91" s="38">
+      <c r="G91" s="32">
         <v>58</v>
       </c>
-      <c r="H91" s="61">
+      <c r="H91" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4202,18 +4201,18 @@
       <c r="B92" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="31">
+      <c r="C92" s="25">
         <v>43</v>
       </c>
-      <c r="D92" s="31">
+      <c r="D92" s="25">
         <v>48</v>
       </c>
-      <c r="E92" s="35"/>
+      <c r="E92" s="29"/>
       <c r="F92" s="13"/>
-      <c r="G92" s="38">
+      <c r="G92" s="32">
         <v>40</v>
       </c>
-      <c r="H92" s="61">
+      <c r="H92" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4224,18 +4223,18 @@
       <c r="B93" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C93" s="31">
+      <c r="C93" s="25">
         <v>24</v>
       </c>
-      <c r="D93" s="32" t="s">
+      <c r="D93" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="E93" s="35"/>
+      <c r="E93" s="29"/>
       <c r="F93" s="13"/>
-      <c r="G93" s="38">
+      <c r="G93" s="32">
         <v>46</v>
       </c>
-      <c r="H93" s="61">
+      <c r="H93" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -4246,18 +4245,18 @@
       <c r="B94" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C94" s="31">
+      <c r="C94" s="25">
         <v>57</v>
       </c>
-      <c r="D94" s="31">
+      <c r="D94" s="25">
         <v>55</v>
       </c>
-      <c r="E94" s="35"/>
+      <c r="E94" s="29"/>
       <c r="F94" s="13"/>
-      <c r="G94" s="38">
+      <c r="G94" s="32">
         <v>41</v>
       </c>
-      <c r="H94" s="61">
+      <c r="H94" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -4268,18 +4267,18 @@
       <c r="B95" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C95" s="31">
+      <c r="C95" s="25">
         <v>93</v>
       </c>
-      <c r="D95" s="32">
+      <c r="D95" s="26">
         <v>87</v>
       </c>
-      <c r="E95" s="35"/>
+      <c r="E95" s="29"/>
       <c r="F95" s="13"/>
-      <c r="G95" s="38">
+      <c r="G95" s="32">
         <v>84</v>
       </c>
-      <c r="H95" s="61">
+      <c r="H95" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4290,18 +4289,18 @@
       <c r="B96" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="31">
+      <c r="C96" s="25">
         <v>65</v>
       </c>
-      <c r="D96" s="32">
+      <c r="D96" s="26">
         <v>79</v>
       </c>
-      <c r="E96" s="33"/>
+      <c r="E96" s="27"/>
       <c r="F96" s="14"/>
-      <c r="G96" s="39">
+      <c r="G96" s="33">
         <v>75</v>
       </c>
-      <c r="H96" s="61">
+      <c r="H96" s="50">
         <v>65.217391300000003</v>
       </c>
     </row>
@@ -4312,18 +4311,18 @@
       <c r="B97" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="31">
+      <c r="C97" s="25">
         <v>26</v>
       </c>
-      <c r="D97" s="32">
+      <c r="D97" s="26">
         <v>63</v>
       </c>
-      <c r="E97" s="35"/>
+      <c r="E97" s="29"/>
       <c r="F97" s="13"/>
-      <c r="G97" s="38">
+      <c r="G97" s="32">
         <v>46</v>
       </c>
-      <c r="H97" s="61">
+      <c r="H97" s="50">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -4334,18 +4333,18 @@
       <c r="B98" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="31">
+      <c r="C98" s="25">
         <v>13</v>
       </c>
-      <c r="D98" s="41">
+      <c r="D98" s="35">
         <v>52</v>
       </c>
-      <c r="E98" s="35"/>
+      <c r="E98" s="29"/>
       <c r="F98" s="13"/>
-      <c r="G98" s="38">
+      <c r="G98" s="32">
         <v>61</v>
       </c>
-      <c r="H98" s="61">
+      <c r="H98" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4356,18 +4355,18 @@
       <c r="B99" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C99" s="31">
+      <c r="C99" s="25">
         <v>60</v>
       </c>
-      <c r="D99" s="41">
+      <c r="D99" s="35">
         <v>83</v>
       </c>
-      <c r="E99" s="35"/>
+      <c r="E99" s="29"/>
       <c r="F99" s="13"/>
-      <c r="G99" s="40">
+      <c r="G99" s="34">
         <v>75</v>
       </c>
-      <c r="H99" s="61">
+      <c r="H99" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4378,18 +4377,18 @@
       <c r="B100" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="31">
+      <c r="C100" s="25">
         <v>42</v>
       </c>
-      <c r="D100" s="41">
+      <c r="D100" s="35">
         <v>48</v>
       </c>
-      <c r="E100" s="35"/>
+      <c r="E100" s="29"/>
       <c r="F100" s="13"/>
-      <c r="G100" s="38">
+      <c r="G100" s="32">
         <v>50</v>
       </c>
-      <c r="H100" s="61">
+      <c r="H100" s="50">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -4400,18 +4399,18 @@
       <c r="B101" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="31">
+      <c r="C101" s="25">
         <v>52</v>
       </c>
-      <c r="D101" s="41">
+      <c r="D101" s="35">
         <v>79</v>
       </c>
-      <c r="E101" s="35"/>
+      <c r="E101" s="29"/>
       <c r="F101" s="13"/>
-      <c r="G101" s="38">
+      <c r="G101" s="32">
         <v>47</v>
       </c>
-      <c r="H101" s="61">
+      <c r="H101" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4422,18 +4421,18 @@
       <c r="B102" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="31">
+      <c r="C102" s="25">
         <v>60</v>
       </c>
-      <c r="D102" s="31">
+      <c r="D102" s="25">
         <v>85</v>
       </c>
-      <c r="E102" s="35"/>
+      <c r="E102" s="29"/>
       <c r="F102" s="13"/>
-      <c r="G102" s="38">
+      <c r="G102" s="32">
         <v>76</v>
       </c>
-      <c r="H102" s="61">
+      <c r="H102" s="50">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -4444,18 +4443,18 @@
       <c r="B103" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="31">
+      <c r="C103" s="25">
         <v>28</v>
       </c>
-      <c r="D103" s="41">
+      <c r="D103" s="35">
         <v>41</v>
       </c>
-      <c r="E103" s="35"/>
+      <c r="E103" s="29"/>
       <c r="F103" s="13"/>
-      <c r="G103" s="38">
+      <c r="G103" s="32">
         <v>51</v>
       </c>
-      <c r="H103" s="61">
+      <c r="H103" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4466,18 +4465,18 @@
       <c r="B104" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C104" s="31">
+      <c r="C104" s="25">
         <v>27</v>
       </c>
-      <c r="D104" s="41">
+      <c r="D104" s="35">
         <v>74</v>
       </c>
-      <c r="E104" s="35"/>
+      <c r="E104" s="29"/>
       <c r="F104" s="13"/>
-      <c r="G104" s="38">
+      <c r="G104" s="32">
         <v>69</v>
       </c>
-      <c r="H104" s="61">
+      <c r="H104" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4488,18 +4487,18 @@
       <c r="B105" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="31">
+      <c r="C105" s="25">
         <v>36</v>
       </c>
-      <c r="D105" s="41">
+      <c r="D105" s="35">
         <v>60</v>
       </c>
-      <c r="E105" s="35"/>
+      <c r="E105" s="29"/>
       <c r="F105" s="13"/>
-      <c r="G105" s="38">
+      <c r="G105" s="32">
         <v>72</v>
       </c>
-      <c r="H105" s="61">
+      <c r="H105" s="50">
         <v>100</v>
       </c>
     </row>
@@ -4510,18 +4509,18 @@
       <c r="B106" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="31">
+      <c r="C106" s="25">
         <v>19</v>
       </c>
-      <c r="D106" s="41">
+      <c r="D106" s="35">
         <v>43</v>
       </c>
-      <c r="E106" s="35"/>
+      <c r="E106" s="29"/>
       <c r="F106" s="13"/>
-      <c r="G106" s="38">
+      <c r="G106" s="32">
         <v>9</v>
       </c>
-      <c r="H106" s="61">
+      <c r="H106" s="50">
         <v>100</v>
       </c>
     </row>
@@ -4532,18 +4531,18 @@
       <c r="B107" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="31">
+      <c r="C107" s="25">
         <v>54</v>
       </c>
-      <c r="D107" s="41">
+      <c r="D107" s="35">
         <v>47</v>
       </c>
-      <c r="E107" s="35"/>
+      <c r="E107" s="29"/>
       <c r="F107" s="13"/>
-      <c r="G107" s="38">
+      <c r="G107" s="32">
         <v>49</v>
       </c>
-      <c r="H107" s="61">
+      <c r="H107" s="50">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4554,18 +4553,18 @@
       <c r="B108" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C108" s="31">
+      <c r="C108" s="25">
         <v>46</v>
       </c>
-      <c r="D108" s="41">
+      <c r="D108" s="35">
         <v>12</v>
       </c>
-      <c r="E108" s="35"/>
+      <c r="E108" s="29"/>
       <c r="F108" s="13"/>
-      <c r="G108" s="38">
+      <c r="G108" s="32">
         <v>56</v>
       </c>
-      <c r="H108" s="61">
+      <c r="H108" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4576,18 +4575,18 @@
       <c r="B109" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C109" s="31" t="s">
+      <c r="C109" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="D109" s="31">
+      <c r="D109" s="25">
         <v>35</v>
       </c>
-      <c r="E109" s="35"/>
+      <c r="E109" s="29"/>
       <c r="F109" s="13"/>
-      <c r="G109" s="38">
+      <c r="G109" s="32">
         <v>62</v>
       </c>
-      <c r="H109" s="61">
+      <c r="H109" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4598,18 +4597,18 @@
       <c r="B110" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C110" s="31">
+      <c r="C110" s="25">
         <v>53</v>
       </c>
-      <c r="D110" s="31" t="s">
+      <c r="D110" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="E110" s="35"/>
+      <c r="E110" s="29"/>
       <c r="F110" s="13"/>
-      <c r="G110" s="38">
+      <c r="G110" s="32">
         <v>60</v>
       </c>
-      <c r="H110" s="61">
+      <c r="H110" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -4620,18 +4619,18 @@
       <c r="B111" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C111" s="31">
+      <c r="C111" s="25">
         <v>4</v>
       </c>
-      <c r="D111" s="31">
+      <c r="D111" s="25">
         <v>12</v>
       </c>
-      <c r="E111" s="35"/>
+      <c r="E111" s="29"/>
       <c r="F111" s="13"/>
-      <c r="G111" s="38">
+      <c r="G111" s="32">
         <v>11</v>
       </c>
-      <c r="H111" s="61">
+      <c r="H111" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4642,18 +4641,18 @@
       <c r="B112" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C112" s="31">
+      <c r="C112" s="25">
         <v>71</v>
       </c>
-      <c r="D112" s="41">
+      <c r="D112" s="35">
         <v>85</v>
       </c>
-      <c r="E112" s="35"/>
+      <c r="E112" s="29"/>
       <c r="F112" s="13"/>
-      <c r="G112" s="38">
+      <c r="G112" s="32">
         <v>70</v>
       </c>
-      <c r="H112" s="61">
+      <c r="H112" s="50">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4664,18 +4663,18 @@
       <c r="B113" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C113" s="31">
+      <c r="C113" s="25">
         <v>29</v>
       </c>
-      <c r="D113" s="41">
+      <c r="D113" s="35">
         <v>19</v>
       </c>
-      <c r="E113" s="35"/>
+      <c r="E113" s="29"/>
       <c r="F113" s="13"/>
-      <c r="G113" s="38">
+      <c r="G113" s="32">
         <v>50</v>
       </c>
-      <c r="H113" s="61">
+      <c r="H113" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -4686,18 +4685,18 @@
       <c r="B114" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C114" s="31">
+      <c r="C114" s="25">
         <v>45</v>
       </c>
-      <c r="D114" s="31">
+      <c r="D114" s="25">
         <v>75</v>
       </c>
-      <c r="E114" s="35"/>
+      <c r="E114" s="29"/>
       <c r="F114" s="13"/>
-      <c r="G114" s="38">
+      <c r="G114" s="32">
         <v>63</v>
       </c>
-      <c r="H114" s="61">
+      <c r="H114" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4708,18 +4707,18 @@
       <c r="B115" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C115" s="31">
+      <c r="C115" s="25">
         <v>75</v>
       </c>
-      <c r="D115" s="31">
+      <c r="D115" s="25">
         <v>79</v>
       </c>
-      <c r="E115" s="35"/>
+      <c r="E115" s="29"/>
       <c r="F115" s="13"/>
-      <c r="G115" s="38">
+      <c r="G115" s="32">
         <v>67</v>
       </c>
-      <c r="H115" s="61">
+      <c r="H115" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4730,18 +4729,18 @@
       <c r="B116" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C116" s="31">
+      <c r="C116" s="25">
         <v>53</v>
       </c>
-      <c r="D116" s="41">
+      <c r="D116" s="35">
         <v>47</v>
       </c>
-      <c r="E116" s="35"/>
+      <c r="E116" s="29"/>
       <c r="F116" s="13"/>
-      <c r="G116" s="38">
+      <c r="G116" s="32">
         <v>72</v>
       </c>
-      <c r="H116" s="61">
+      <c r="H116" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4752,18 +4751,18 @@
       <c r="B117" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C117" s="31">
+      <c r="C117" s="25">
         <v>44</v>
       </c>
-      <c r="D117" s="41">
+      <c r="D117" s="35">
         <v>60</v>
       </c>
-      <c r="E117" s="35"/>
+      <c r="E117" s="29"/>
       <c r="F117" s="13"/>
-      <c r="G117" s="38">
+      <c r="G117" s="32">
         <v>28</v>
       </c>
-      <c r="H117" s="61">
+      <c r="H117" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4774,18 +4773,18 @@
       <c r="B118" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C118" s="31">
+      <c r="C118" s="25">
         <v>64</v>
       </c>
-      <c r="D118" s="31">
+      <c r="D118" s="25">
         <v>57</v>
       </c>
-      <c r="E118" s="35"/>
+      <c r="E118" s="29"/>
       <c r="F118" s="13"/>
-      <c r="G118" s="38">
+      <c r="G118" s="32">
         <v>54</v>
       </c>
-      <c r="H118" s="61">
+      <c r="H118" s="50">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -4796,18 +4795,18 @@
       <c r="B119" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C119" s="31">
+      <c r="C119" s="25">
         <v>83</v>
       </c>
-      <c r="D119" s="31">
+      <c r="D119" s="25">
         <v>52</v>
       </c>
-      <c r="E119" s="35"/>
+      <c r="E119" s="29"/>
       <c r="F119" s="13"/>
-      <c r="G119" s="38">
+      <c r="G119" s="32">
         <v>76</v>
       </c>
-      <c r="H119" s="61">
+      <c r="H119" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4818,18 +4817,18 @@
       <c r="B120" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C120" s="31">
+      <c r="C120" s="25">
         <v>17</v>
       </c>
-      <c r="D120" s="41">
+      <c r="D120" s="35">
         <v>31</v>
       </c>
-      <c r="E120" s="35"/>
+      <c r="E120" s="29"/>
       <c r="F120" s="13"/>
-      <c r="G120" s="38">
+      <c r="G120" s="32">
         <v>52</v>
       </c>
-      <c r="H120" s="61">
+      <c r="H120" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4840,18 +4839,18 @@
       <c r="B121" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C121" s="31" t="s">
+      <c r="C121" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="D121" s="31">
+      <c r="D121" s="25">
         <v>16</v>
       </c>
-      <c r="E121" s="35"/>
+      <c r="E121" s="29"/>
       <c r="F121" s="13"/>
-      <c r="G121" s="38">
+      <c r="G121" s="32">
         <v>59</v>
       </c>
-      <c r="H121" s="61">
+      <c r="H121" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -4862,18 +4861,18 @@
       <c r="B122" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C122" s="31">
+      <c r="C122" s="25">
         <v>25</v>
       </c>
-      <c r="D122" s="31">
+      <c r="D122" s="25">
         <v>36</v>
       </c>
-      <c r="E122" s="35"/>
+      <c r="E122" s="29"/>
       <c r="F122" s="13"/>
-      <c r="G122" s="38">
+      <c r="G122" s="32">
         <v>32</v>
       </c>
-      <c r="H122" s="61">
+      <c r="H122" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4884,18 +4883,18 @@
       <c r="B123" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C123" s="31" t="s">
+      <c r="C123" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="D123" s="41" t="s">
+      <c r="D123" s="35" t="s">
         <v>382</v>
       </c>
-      <c r="E123" s="35"/>
+      <c r="E123" s="29"/>
       <c r="F123" s="13"/>
-      <c r="G123" s="38" t="s">
+      <c r="G123" s="32" t="s">
         <v>382</v>
       </c>
-      <c r="H123" s="61">
+      <c r="H123" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4906,18 +4905,18 @@
       <c r="B124" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C124" s="31">
+      <c r="C124" s="25">
         <v>58</v>
       </c>
-      <c r="D124" s="31">
+      <c r="D124" s="25">
         <v>72</v>
       </c>
-      <c r="E124" s="35"/>
+      <c r="E124" s="29"/>
       <c r="F124" s="13"/>
-      <c r="G124" s="38">
+      <c r="G124" s="32">
         <v>60</v>
       </c>
-      <c r="H124" s="61">
+      <c r="H124" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -4928,18 +4927,18 @@
       <c r="B125" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C125" s="31">
+      <c r="C125" s="25">
         <v>28</v>
       </c>
-      <c r="D125" s="41">
+      <c r="D125" s="35">
         <v>41</v>
       </c>
-      <c r="E125" s="35"/>
+      <c r="E125" s="29"/>
       <c r="F125" s="13"/>
-      <c r="G125" s="38">
+      <c r="G125" s="32">
         <v>55</v>
       </c>
-      <c r="H125" s="61">
+      <c r="H125" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4950,18 +4949,18 @@
       <c r="B126" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C126" s="31">
+      <c r="C126" s="25">
         <v>44</v>
       </c>
-      <c r="D126" s="31">
+      <c r="D126" s="25">
         <v>53</v>
       </c>
-      <c r="E126" s="35"/>
+      <c r="E126" s="29"/>
       <c r="F126" s="13"/>
-      <c r="G126" s="38">
+      <c r="G126" s="32">
         <v>68</v>
       </c>
-      <c r="H126" s="61">
+      <c r="H126" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4972,18 +4971,18 @@
       <c r="B127" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C127" s="31">
+      <c r="C127" s="25">
         <v>54</v>
       </c>
-      <c r="D127" s="41">
+      <c r="D127" s="35">
         <v>32</v>
       </c>
-      <c r="E127" s="35"/>
+      <c r="E127" s="29"/>
       <c r="F127" s="13"/>
-      <c r="G127" s="38">
+      <c r="G127" s="32">
         <v>68</v>
       </c>
-      <c r="H127" s="61">
+      <c r="H127" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4994,18 +4993,18 @@
       <c r="B128" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C128" s="31">
+      <c r="C128" s="25">
         <v>21</v>
       </c>
-      <c r="D128" s="41">
+      <c r="D128" s="35">
         <v>56</v>
       </c>
-      <c r="E128" s="35"/>
+      <c r="E128" s="29"/>
       <c r="F128" s="13"/>
-      <c r="G128" s="38">
+      <c r="G128" s="32">
         <v>48</v>
       </c>
-      <c r="H128" s="61">
+      <c r="H128" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5016,18 +5015,18 @@
       <c r="B129" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C129" s="31">
+      <c r="C129" s="25">
         <v>26</v>
       </c>
-      <c r="D129" s="41">
+      <c r="D129" s="35">
         <v>49</v>
       </c>
-      <c r="E129" s="35"/>
+      <c r="E129" s="29"/>
       <c r="F129" s="13"/>
-      <c r="G129" s="38">
+      <c r="G129" s="32">
         <v>50</v>
       </c>
-      <c r="H129" s="61">
+      <c r="H129" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5038,18 +5037,18 @@
       <c r="B130" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C130" s="31">
+      <c r="C130" s="25">
         <v>15</v>
       </c>
-      <c r="D130" s="41">
+      <c r="D130" s="35">
         <v>26</v>
       </c>
-      <c r="E130" s="35"/>
+      <c r="E130" s="29"/>
       <c r="F130" s="13"/>
-      <c r="G130" s="38">
+      <c r="G130" s="32">
         <v>22</v>
       </c>
-      <c r="H130" s="61">
+      <c r="H130" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5060,18 +5059,18 @@
       <c r="B131" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C131" s="31">
+      <c r="C131" s="25">
         <v>51</v>
       </c>
-      <c r="D131" s="41">
+      <c r="D131" s="35">
         <v>23</v>
       </c>
-      <c r="E131" s="35"/>
+      <c r="E131" s="29"/>
       <c r="F131" s="13"/>
-      <c r="G131" s="38">
+      <c r="G131" s="32">
         <v>63</v>
       </c>
-      <c r="H131" s="61">
+      <c r="H131" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5082,18 +5081,18 @@
       <c r="B132" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C132" s="31">
+      <c r="C132" s="25">
         <v>50</v>
       </c>
-      <c r="D132" s="41">
+      <c r="D132" s="35">
         <v>81</v>
       </c>
-      <c r="E132" s="33"/>
+      <c r="E132" s="27"/>
       <c r="F132" s="14"/>
-      <c r="G132" s="39">
+      <c r="G132" s="33">
         <v>66</v>
       </c>
-      <c r="H132" s="61">
+      <c r="H132" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5104,18 +5103,18 @@
       <c r="B133" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C133" s="31">
+      <c r="C133" s="25">
         <v>18</v>
       </c>
-      <c r="D133" s="41">
+      <c r="D133" s="35">
         <v>13</v>
       </c>
-      <c r="E133" s="35"/>
+      <c r="E133" s="29"/>
       <c r="F133" s="13"/>
-      <c r="G133" s="38">
+      <c r="G133" s="32">
         <v>23</v>
       </c>
-      <c r="H133" s="61">
+      <c r="H133" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5126,18 +5125,18 @@
       <c r="B134" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C134" s="31">
+      <c r="C134" s="25">
         <v>53</v>
       </c>
-      <c r="D134" s="41">
+      <c r="D134" s="35">
         <v>49</v>
       </c>
-      <c r="E134" s="35"/>
+      <c r="E134" s="29"/>
       <c r="F134" s="13"/>
-      <c r="G134" s="42">
+      <c r="G134" s="36">
         <v>65</v>
       </c>
-      <c r="H134" s="61">
+      <c r="H134" s="50">
         <v>100</v>
       </c>
     </row>
@@ -5148,18 +5147,18 @@
       <c r="B135" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C135" s="31">
+      <c r="C135" s="25">
         <v>8</v>
       </c>
-      <c r="D135" s="41">
+      <c r="D135" s="35">
         <v>42</v>
       </c>
-      <c r="E135" s="35"/>
+      <c r="E135" s="29"/>
       <c r="F135" s="13"/>
-      <c r="G135" s="43">
+      <c r="G135" s="37">
         <v>45</v>
       </c>
-      <c r="H135" s="61">
+      <c r="H135" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5170,18 +5169,18 @@
       <c r="B136" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C136" s="31">
+      <c r="C136" s="25">
         <v>42</v>
       </c>
-      <c r="D136" s="31">
+      <c r="D136" s="25">
         <v>58</v>
       </c>
-      <c r="E136" s="35"/>
+      <c r="E136" s="29"/>
       <c r="F136" s="13"/>
-      <c r="G136" s="36">
+      <c r="G136" s="30">
         <v>58</v>
       </c>
-      <c r="H136" s="61">
+      <c r="H136" s="50">
         <v>100</v>
       </c>
     </row>
@@ -5192,18 +5191,18 @@
       <c r="B137" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C137" s="31">
+      <c r="C137" s="25">
         <v>37</v>
       </c>
-      <c r="D137" s="31">
+      <c r="D137" s="25">
         <v>45</v>
       </c>
-      <c r="E137" s="33"/>
+      <c r="E137" s="27"/>
       <c r="F137" s="14"/>
-      <c r="G137" s="39">
+      <c r="G137" s="33">
         <v>53</v>
       </c>
-      <c r="H137" s="61">
+      <c r="H137" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5214,18 +5213,18 @@
       <c r="B138" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C138" s="31">
+      <c r="C138" s="25">
         <v>46</v>
       </c>
-      <c r="D138" s="31">
+      <c r="D138" s="25">
         <v>29</v>
       </c>
-      <c r="E138" s="35"/>
+      <c r="E138" s="29"/>
       <c r="F138" s="13"/>
-      <c r="G138" s="38">
+      <c r="G138" s="32">
         <v>64</v>
       </c>
-      <c r="H138" s="61">
+      <c r="H138" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5236,18 +5235,18 @@
       <c r="B139" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C139" s="31">
+      <c r="C139" s="25">
         <v>43</v>
       </c>
-      <c r="D139" s="41">
+      <c r="D139" s="35">
         <v>38</v>
       </c>
-      <c r="E139" s="35"/>
+      <c r="E139" s="29"/>
       <c r="F139" s="13"/>
-      <c r="G139" s="38">
+      <c r="G139" s="32">
         <v>41</v>
       </c>
-      <c r="H139" s="61">
+      <c r="H139" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5258,18 +5257,18 @@
       <c r="B140" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C140" s="31">
+      <c r="C140" s="25">
         <v>40</v>
       </c>
-      <c r="D140" s="31">
+      <c r="D140" s="25">
         <v>66</v>
       </c>
-      <c r="E140" s="35"/>
+      <c r="E140" s="29"/>
       <c r="F140" s="13"/>
-      <c r="G140" s="38">
+      <c r="G140" s="32">
         <v>70</v>
       </c>
-      <c r="H140" s="61">
+      <c r="H140" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5280,18 +5279,18 @@
       <c r="B141" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C141" s="31">
+      <c r="C141" s="25">
         <v>32</v>
       </c>
-      <c r="D141" s="31">
+      <c r="D141" s="25">
         <v>17</v>
       </c>
-      <c r="E141" s="35"/>
+      <c r="E141" s="29"/>
       <c r="F141" s="13"/>
-      <c r="G141" s="38">
-        <v>34</v>
-      </c>
-      <c r="H141" s="61">
+      <c r="G141" s="32">
+        <v>36</v>
+      </c>
+      <c r="H141" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5302,18 +5301,18 @@
       <c r="B142" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C142" s="31">
+      <c r="C142" s="25">
         <v>32</v>
       </c>
-      <c r="D142" s="31">
+      <c r="D142" s="25">
         <v>45</v>
       </c>
-      <c r="E142" s="35"/>
+      <c r="E142" s="29"/>
       <c r="F142" s="13"/>
-      <c r="G142" s="38">
+      <c r="G142" s="32">
         <v>65</v>
       </c>
-      <c r="H142" s="61">
+      <c r="H142" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5324,18 +5323,18 @@
       <c r="B143" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C143" s="31">
+      <c r="C143" s="25">
         <v>67</v>
       </c>
-      <c r="D143" s="41">
+      <c r="D143" s="35">
         <v>89</v>
       </c>
-      <c r="E143" s="35"/>
+      <c r="E143" s="29"/>
       <c r="F143" s="13"/>
-      <c r="G143" s="38">
+      <c r="G143" s="32">
         <v>72</v>
       </c>
-      <c r="H143" s="61">
+      <c r="H143" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5346,18 +5345,18 @@
       <c r="B144" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C144" s="31">
+      <c r="C144" s="25">
         <v>61</v>
       </c>
-      <c r="D144" s="41">
+      <c r="D144" s="35">
         <v>76</v>
       </c>
-      <c r="E144" s="35"/>
+      <c r="E144" s="29"/>
       <c r="F144" s="13"/>
-      <c r="G144" s="38">
+      <c r="G144" s="32">
         <v>59</v>
       </c>
-      <c r="H144" s="61">
+      <c r="H144" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5368,18 +5367,18 @@
       <c r="B145" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C145" s="31">
+      <c r="C145" s="25">
         <v>71</v>
       </c>
-      <c r="D145" s="41">
+      <c r="D145" s="35">
         <v>76</v>
       </c>
-      <c r="E145" s="35"/>
+      <c r="E145" s="29"/>
       <c r="F145" s="13"/>
-      <c r="G145" s="38">
+      <c r="G145" s="32">
         <v>68</v>
       </c>
-      <c r="H145" s="61">
+      <c r="H145" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5390,18 +5389,18 @@
       <c r="B146" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C146" s="31">
+      <c r="C146" s="25">
         <v>96</v>
       </c>
-      <c r="D146" s="41">
+      <c r="D146" s="35">
         <v>86</v>
       </c>
-      <c r="E146" s="35"/>
+      <c r="E146" s="29"/>
       <c r="F146" s="13"/>
-      <c r="G146" s="38">
+      <c r="G146" s="32">
         <v>66</v>
       </c>
-      <c r="H146" s="61">
+      <c r="H146" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5412,18 +5411,18 @@
       <c r="B147" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C147" s="31">
+      <c r="C147" s="25">
         <v>21</v>
       </c>
-      <c r="D147" s="31">
+      <c r="D147" s="25">
         <v>28</v>
       </c>
-      <c r="E147" s="35"/>
+      <c r="E147" s="29"/>
       <c r="F147" s="13"/>
-      <c r="G147" s="38">
+      <c r="G147" s="32">
         <v>12</v>
       </c>
-      <c r="H147" s="61">
+      <c r="H147" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5434,18 +5433,18 @@
       <c r="B148" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C148" s="31">
+      <c r="C148" s="25">
         <v>47</v>
       </c>
-      <c r="D148" s="31">
+      <c r="D148" s="25">
         <v>73</v>
       </c>
-      <c r="E148" s="35"/>
+      <c r="E148" s="29"/>
       <c r="F148" s="13"/>
-      <c r="G148" s="38">
+      <c r="G148" s="32">
         <v>52</v>
       </c>
-      <c r="H148" s="61">
+      <c r="H148" s="50">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5456,18 +5455,18 @@
       <c r="B149" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C149" s="31">
+      <c r="C149" s="25">
         <v>67</v>
       </c>
-      <c r="D149" s="41">
+      <c r="D149" s="35">
         <v>52</v>
       </c>
-      <c r="E149" s="35"/>
+      <c r="E149" s="29"/>
       <c r="F149" s="13"/>
-      <c r="G149" s="38">
+      <c r="G149" s="32">
         <v>28</v>
       </c>
-      <c r="H149" s="61">
+      <c r="H149" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5478,18 +5477,18 @@
       <c r="B150" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C150" s="31" t="s">
+      <c r="C150" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="D150" s="41">
+      <c r="D150" s="35">
         <v>48</v>
       </c>
-      <c r="E150" s="33"/>
-      <c r="F150" s="44"/>
-      <c r="G150" s="39">
+      <c r="E150" s="27"/>
+      <c r="F150" s="38"/>
+      <c r="G150" s="33">
         <v>44</v>
       </c>
-      <c r="H150" s="61">
+      <c r="H150" s="50">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5500,18 +5499,18 @@
       <c r="B151" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C151" s="31">
+      <c r="C151" s="25">
         <v>52</v>
       </c>
-      <c r="D151" s="31">
+      <c r="D151" s="25">
         <v>43</v>
       </c>
-      <c r="E151" s="35"/>
+      <c r="E151" s="29"/>
       <c r="F151" s="13"/>
-      <c r="G151" s="38">
+      <c r="G151" s="32">
         <v>64</v>
       </c>
-      <c r="H151" s="61">
+      <c r="H151" s="50">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5522,18 +5521,18 @@
       <c r="B152" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C152" s="31">
+      <c r="C152" s="25">
         <v>36</v>
       </c>
-      <c r="D152" s="31">
+      <c r="D152" s="25">
         <v>51</v>
       </c>
-      <c r="E152" s="35"/>
+      <c r="E152" s="29"/>
       <c r="F152" s="13"/>
-      <c r="G152" s="38">
+      <c r="G152" s="32">
         <v>44</v>
       </c>
-      <c r="H152" s="61">
+      <c r="H152" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5544,18 +5543,18 @@
       <c r="B153" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C153" s="31">
+      <c r="C153" s="25">
         <v>78</v>
       </c>
-      <c r="D153" s="41">
+      <c r="D153" s="35">
         <v>46</v>
       </c>
-      <c r="E153" s="35"/>
+      <c r="E153" s="29"/>
       <c r="F153" s="13"/>
-      <c r="G153" s="38">
+      <c r="G153" s="32">
         <v>59</v>
       </c>
-      <c r="H153" s="61">
+      <c r="H153" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5566,18 +5565,18 @@
       <c r="B154" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C154" s="31">
+      <c r="C154" s="25">
         <v>31</v>
       </c>
-      <c r="D154" s="32">
+      <c r="D154" s="26">
         <v>78</v>
       </c>
-      <c r="E154" s="35"/>
+      <c r="E154" s="29"/>
       <c r="F154" s="13"/>
-      <c r="G154" s="38">
+      <c r="G154" s="32">
         <v>72</v>
       </c>
-      <c r="H154" s="61">
+      <c r="H154" s="50">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -5588,18 +5587,18 @@
       <c r="B155" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C155" s="31">
+      <c r="C155" s="25">
         <v>60</v>
       </c>
-      <c r="D155" s="32">
+      <c r="D155" s="26">
         <v>85</v>
       </c>
-      <c r="E155" s="35"/>
+      <c r="E155" s="29"/>
       <c r="F155" s="13"/>
-      <c r="G155" s="38">
+      <c r="G155" s="32">
         <v>64</v>
       </c>
-      <c r="H155" s="61">
+      <c r="H155" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5610,18 +5609,18 @@
       <c r="B156" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C156" s="31">
+      <c r="C156" s="25">
         <v>95</v>
       </c>
-      <c r="D156" s="31">
+      <c r="D156" s="25">
         <v>89</v>
       </c>
-      <c r="E156" s="33"/>
-      <c r="F156" s="44"/>
-      <c r="G156" s="39">
+      <c r="E156" s="27"/>
+      <c r="F156" s="38"/>
+      <c r="G156" s="33">
         <v>80</v>
       </c>
-      <c r="H156" s="61">
+      <c r="H156" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5632,18 +5631,18 @@
       <c r="B157" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C157" s="31">
+      <c r="C157" s="25">
         <v>69</v>
       </c>
-      <c r="D157" s="31">
+      <c r="D157" s="25">
         <v>89</v>
       </c>
-      <c r="E157" s="35"/>
+      <c r="E157" s="29"/>
       <c r="F157" s="13"/>
-      <c r="G157" s="38">
+      <c r="G157" s="32">
         <v>67</v>
       </c>
-      <c r="H157" s="61">
+      <c r="H157" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5654,18 +5653,18 @@
       <c r="B158" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C158" s="31">
+      <c r="C158" s="25">
         <v>47</v>
       </c>
-      <c r="D158" s="31">
+      <c r="D158" s="25">
         <v>86</v>
       </c>
-      <c r="E158" s="35"/>
+      <c r="E158" s="29"/>
       <c r="F158" s="13"/>
-      <c r="G158" s="38">
+      <c r="G158" s="32">
         <v>57</v>
       </c>
-      <c r="H158" s="61">
+      <c r="H158" s="50">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5676,18 +5675,18 @@
       <c r="B159" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C159" s="31">
+      <c r="C159" s="25">
         <v>58</v>
       </c>
-      <c r="D159" s="32">
+      <c r="D159" s="26">
         <v>56</v>
       </c>
-      <c r="E159" s="45"/>
+      <c r="E159" s="39"/>
       <c r="F159" s="13"/>
-      <c r="G159" s="38">
+      <c r="G159" s="32">
         <v>70</v>
       </c>
-      <c r="H159" s="61">
+      <c r="H159" s="50">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -5698,18 +5697,18 @@
       <c r="B160" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C160" s="31">
+      <c r="C160" s="25">
         <v>25</v>
       </c>
-      <c r="D160" s="32">
+      <c r="D160" s="26">
         <v>76</v>
       </c>
-      <c r="E160" s="35"/>
+      <c r="E160" s="29"/>
       <c r="F160" s="13"/>
-      <c r="G160" s="38">
+      <c r="G160" s="32">
         <v>70</v>
       </c>
-      <c r="H160" s="61">
+      <c r="H160" s="50">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5720,18 +5719,18 @@
       <c r="B161" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C161" s="31">
+      <c r="C161" s="25">
         <v>44</v>
       </c>
-      <c r="D161" s="31">
+      <c r="D161" s="25">
         <v>34</v>
       </c>
-      <c r="E161" s="35"/>
+      <c r="E161" s="29"/>
       <c r="F161" s="13"/>
-      <c r="G161" s="38">
+      <c r="G161" s="32">
         <v>57</v>
       </c>
-      <c r="H161" s="61">
+      <c r="H161" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5742,18 +5741,18 @@
       <c r="B162" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C162" s="31">
+      <c r="C162" s="25">
         <v>31</v>
       </c>
-      <c r="D162" s="32">
+      <c r="D162" s="26">
         <v>38</v>
       </c>
-      <c r="E162" s="35"/>
+      <c r="E162" s="29"/>
       <c r="F162" s="13"/>
-      <c r="G162" s="38">
+      <c r="G162" s="32">
         <v>52</v>
       </c>
-      <c r="H162" s="61">
+      <c r="H162" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5764,18 +5763,18 @@
       <c r="B163" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C163" s="32">
+      <c r="C163" s="26">
         <v>40</v>
       </c>
-      <c r="D163" s="31">
+      <c r="D163" s="25">
         <v>55</v>
       </c>
-      <c r="E163" s="35"/>
+      <c r="E163" s="29"/>
       <c r="F163" s="13"/>
-      <c r="G163" s="38">
+      <c r="G163" s="32">
         <v>42</v>
       </c>
-      <c r="H163" s="61">
+      <c r="H163" s="50">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5786,18 +5785,18 @@
       <c r="B164" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C164" s="32">
+      <c r="C164" s="26">
         <v>19</v>
       </c>
-      <c r="D164" s="32">
+      <c r="D164" s="26">
         <v>63</v>
       </c>
-      <c r="E164" s="35"/>
+      <c r="E164" s="29"/>
       <c r="F164" s="13"/>
-      <c r="G164" s="42">
+      <c r="G164" s="36">
         <v>49</v>
       </c>
-      <c r="H164" s="61">
+      <c r="H164" s="50">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -5808,18 +5807,18 @@
       <c r="B165" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C165" s="32" t="s">
+      <c r="C165" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="D165" s="31">
+      <c r="D165" s="25">
         <v>74</v>
       </c>
-      <c r="E165" s="35"/>
+      <c r="E165" s="29"/>
       <c r="F165" s="13"/>
-      <c r="G165" s="34">
+      <c r="G165" s="28">
         <v>61</v>
       </c>
-      <c r="H165" s="61">
+      <c r="H165" s="50">
         <v>65.217391300000003</v>
       </c>
     </row>
@@ -5830,18 +5829,18 @@
       <c r="B166" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C166" s="32">
+      <c r="C166" s="26">
         <v>18</v>
       </c>
-      <c r="D166" s="31">
+      <c r="D166" s="25">
         <v>44</v>
       </c>
-      <c r="E166" s="35"/>
+      <c r="E166" s="29"/>
       <c r="F166" s="13"/>
-      <c r="G166" s="34">
+      <c r="G166" s="28">
         <v>47</v>
       </c>
-      <c r="H166" s="61">
+      <c r="H166" s="50">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -5852,18 +5851,18 @@
       <c r="B167" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C167" s="32">
+      <c r="C167" s="26">
         <v>44</v>
       </c>
-      <c r="D167" s="32">
+      <c r="D167" s="26">
         <v>69</v>
       </c>
-      <c r="E167" s="35"/>
+      <c r="E167" s="29"/>
       <c r="F167" s="13"/>
-      <c r="G167" s="34">
+      <c r="G167" s="28">
         <v>65</v>
       </c>
-      <c r="H167" s="61">
+      <c r="H167" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5874,18 +5873,18 @@
       <c r="B168" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C168" s="32">
+      <c r="C168" s="26">
         <v>82</v>
       </c>
-      <c r="D168" s="31">
+      <c r="D168" s="25">
         <v>93</v>
       </c>
-      <c r="E168" s="35"/>
+      <c r="E168" s="29"/>
       <c r="F168" s="13"/>
-      <c r="G168" s="34">
+      <c r="G168" s="28">
         <v>45</v>
       </c>
-      <c r="H168" s="61">
+      <c r="H168" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5896,18 +5895,18 @@
       <c r="B169" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C169" s="32">
+      <c r="C169" s="26">
         <v>55</v>
       </c>
-      <c r="D169" s="32">
+      <c r="D169" s="26">
         <v>55</v>
       </c>
-      <c r="E169" s="35"/>
+      <c r="E169" s="29"/>
       <c r="F169" s="13"/>
-      <c r="G169" s="34">
+      <c r="G169" s="28">
         <v>69</v>
       </c>
-      <c r="H169" s="61">
+      <c r="H169" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5918,18 +5917,18 @@
       <c r="B170" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C170" s="32">
+      <c r="C170" s="26">
         <v>24</v>
       </c>
-      <c r="D170" s="32">
+      <c r="D170" s="26">
         <v>25</v>
       </c>
-      <c r="E170" s="46"/>
-      <c r="F170" s="47"/>
-      <c r="G170" s="48">
+      <c r="E170" s="40"/>
+      <c r="F170" s="41"/>
+      <c r="G170" s="42">
         <v>33</v>
       </c>
-      <c r="H170" s="61">
+      <c r="H170" s="50">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -5940,18 +5939,18 @@
       <c r="B171" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C171" s="32">
+      <c r="C171" s="26">
         <v>36</v>
       </c>
-      <c r="D171" s="32">
+      <c r="D171" s="26">
         <v>50</v>
       </c>
-      <c r="E171" s="35"/>
+      <c r="E171" s="29"/>
       <c r="F171" s="15"/>
-      <c r="G171" s="49">
+      <c r="G171" s="43">
         <v>46</v>
       </c>
-      <c r="H171" s="61">
+      <c r="H171" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5962,18 +5961,18 @@
       <c r="B172" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C172" s="32">
+      <c r="C172" s="26">
         <v>55</v>
       </c>
-      <c r="D172" s="32">
+      <c r="D172" s="26">
         <v>58</v>
       </c>
-      <c r="E172" s="35"/>
+      <c r="E172" s="29"/>
       <c r="F172" s="15"/>
-      <c r="G172" s="49">
+      <c r="G172" s="43">
         <v>26</v>
       </c>
-      <c r="H172" s="61">
+      <c r="H172" s="50">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -5984,18 +5983,18 @@
       <c r="B173" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C173" s="32">
+      <c r="C173" s="26">
         <v>27</v>
       </c>
-      <c r="D173" s="31">
+      <c r="D173" s="25">
         <v>65</v>
       </c>
-      <c r="E173" s="35"/>
+      <c r="E173" s="29"/>
       <c r="F173" s="15"/>
-      <c r="G173" s="49">
+      <c r="G173" s="43">
         <v>50</v>
       </c>
-      <c r="H173" s="61">
+      <c r="H173" s="50">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -6006,18 +6005,18 @@
       <c r="B174" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C174" s="32">
+      <c r="C174" s="26">
         <v>14</v>
       </c>
-      <c r="D174" s="31">
+      <c r="D174" s="25">
         <v>22</v>
       </c>
-      <c r="E174" s="35"/>
+      <c r="E174" s="29"/>
       <c r="F174" s="15"/>
-      <c r="G174" s="49">
+      <c r="G174" s="43">
         <v>51</v>
       </c>
-      <c r="H174" s="61">
+      <c r="H174" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6028,18 +6027,18 @@
       <c r="B175" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C175" s="32">
+      <c r="C175" s="26">
         <v>17</v>
       </c>
-      <c r="D175" s="32">
+      <c r="D175" s="26">
         <v>40</v>
       </c>
-      <c r="E175" s="35"/>
+      <c r="E175" s="29"/>
       <c r="F175" s="15"/>
-      <c r="G175" s="49">
+      <c r="G175" s="43">
         <v>60</v>
       </c>
-      <c r="H175" s="61">
+      <c r="H175" s="50">
         <v>30.434782599999998</v>
       </c>
     </row>
@@ -6050,18 +6049,18 @@
       <c r="B176" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C176" s="32">
+      <c r="C176" s="26">
         <v>33</v>
       </c>
-      <c r="D176" s="31">
+      <c r="D176" s="25">
         <v>23</v>
       </c>
-      <c r="E176" s="35"/>
+      <c r="E176" s="29"/>
       <c r="F176" s="15"/>
-      <c r="G176" s="49">
+      <c r="G176" s="43">
         <v>35</v>
       </c>
-      <c r="H176" s="61">
+      <c r="H176" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6072,18 +6071,18 @@
       <c r="B177" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C177" s="32">
+      <c r="C177" s="26">
         <v>64</v>
       </c>
-      <c r="D177" s="31">
+      <c r="D177" s="25">
         <v>81</v>
       </c>
-      <c r="E177" s="35"/>
+      <c r="E177" s="29"/>
       <c r="F177" s="15"/>
-      <c r="G177" s="49">
+      <c r="G177" s="43">
         <v>54</v>
       </c>
-      <c r="H177" s="61">
+      <c r="H177" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6094,18 +6093,18 @@
       <c r="B178" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C178" s="32">
+      <c r="C178" s="26">
         <v>32</v>
       </c>
-      <c r="D178" s="31">
+      <c r="D178" s="25">
         <v>94</v>
       </c>
-      <c r="E178" s="35"/>
+      <c r="E178" s="29"/>
       <c r="F178" s="15"/>
-      <c r="G178" s="49">
+      <c r="G178" s="43">
         <v>80</v>
       </c>
-      <c r="H178" s="61">
+      <c r="H178" s="50">
         <v>100</v>
       </c>
     </row>
@@ -6116,18 +6115,18 @@
       <c r="B179" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C179" s="32">
+      <c r="C179" s="26">
         <v>64</v>
       </c>
-      <c r="D179" s="31">
+      <c r="D179" s="25">
         <v>92</v>
       </c>
-      <c r="E179" s="35"/>
+      <c r="E179" s="29"/>
       <c r="F179" s="15"/>
-      <c r="G179" s="49">
+      <c r="G179" s="43">
         <v>88</v>
       </c>
-      <c r="H179" s="61">
+      <c r="H179" s="50">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -6138,18 +6137,18 @@
       <c r="B180" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C180" s="32">
+      <c r="C180" s="26">
         <v>12</v>
       </c>
-      <c r="D180" s="31">
+      <c r="D180" s="25">
         <v>25</v>
       </c>
-      <c r="E180" s="35"/>
+      <c r="E180" s="29"/>
       <c r="F180" s="15"/>
-      <c r="G180" s="49">
+      <c r="G180" s="43">
         <v>29</v>
       </c>
-      <c r="H180" s="61">
+      <c r="H180" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6160,18 +6159,18 @@
       <c r="B181" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C181" s="32">
+      <c r="C181" s="26">
         <v>36</v>
       </c>
-      <c r="D181" s="32">
+      <c r="D181" s="26">
         <v>70</v>
       </c>
-      <c r="E181" s="35"/>
+      <c r="E181" s="29"/>
       <c r="F181" s="15"/>
-      <c r="G181" s="49">
+      <c r="G181" s="43">
         <v>63</v>
       </c>
-      <c r="H181" s="61">
+      <c r="H181" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6182,18 +6181,18 @@
       <c r="B182" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C182" s="32">
+      <c r="C182" s="26">
         <v>1</v>
       </c>
-      <c r="D182" s="32">
+      <c r="D182" s="26">
         <v>40</v>
       </c>
-      <c r="E182" s="50"/>
+      <c r="E182" s="44"/>
       <c r="F182" s="15"/>
-      <c r="G182" s="49">
+      <c r="G182" s="43">
         <v>49</v>
       </c>
-      <c r="H182" s="61">
+      <c r="H182" s="50">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6204,18 +6203,18 @@
       <c r="B183" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C183" s="32">
+      <c r="C183" s="26">
         <v>38</v>
       </c>
-      <c r="D183" s="32">
+      <c r="D183" s="26">
         <v>66</v>
       </c>
-      <c r="E183" s="50"/>
+      <c r="E183" s="44"/>
       <c r="F183" s="15"/>
-      <c r="G183" s="49">
+      <c r="G183" s="43">
         <v>59</v>
       </c>
-      <c r="H183" s="61">
+      <c r="H183" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6226,18 +6225,18 @@
       <c r="B184" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C184" s="32">
+      <c r="C184" s="26">
         <v>41</v>
       </c>
-      <c r="D184" s="32">
+      <c r="D184" s="26">
         <v>62</v>
       </c>
-      <c r="E184" s="35"/>
+      <c r="E184" s="29"/>
       <c r="F184" s="15"/>
-      <c r="G184" s="49">
+      <c r="G184" s="43">
         <v>74</v>
       </c>
-      <c r="H184" s="61">
+      <c r="H184" s="50">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -6248,18 +6247,18 @@
       <c r="B185" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C185" s="32">
+      <c r="C185" s="26">
         <v>77</v>
       </c>
-      <c r="D185" s="32">
+      <c r="D185" s="26">
         <v>57</v>
       </c>
-      <c r="E185" s="35"/>
+      <c r="E185" s="29"/>
       <c r="F185" s="15"/>
-      <c r="G185" s="49">
+      <c r="G185" s="43">
         <v>65</v>
       </c>
-      <c r="H185" s="61">
+      <c r="H185" s="50">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6270,62 +6269,70 @@
       <c r="B186" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C186" s="32">
+      <c r="C186" s="26">
         <v>74</v>
       </c>
-      <c r="D186" s="32">
+      <c r="D186" s="26">
         <v>44</v>
       </c>
-      <c r="E186" s="35"/>
+      <c r="E186" s="29"/>
       <c r="F186" s="15"/>
-      <c r="G186" s="49">
+      <c r="G186" s="43">
         <v>69</v>
       </c>
-      <c r="H186" s="61">
+      <c r="H186" s="50">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="23" t="s">
+      <c r="A187" s="19" t="s">
         <v>380</v>
       </c>
-      <c r="B187" s="24" t="s">
+      <c r="B187" s="20" t="s">
         <v>381</v>
       </c>
-      <c r="C187" s="32">
+      <c r="C187" s="26">
         <v>37</v>
       </c>
-      <c r="D187" s="32">
+      <c r="D187" s="26">
         <v>32</v>
       </c>
-      <c r="E187" s="51"/>
-      <c r="F187" s="15"/>
-      <c r="G187" s="52">
+      <c r="E187" s="51">
+        <v>57</v>
+      </c>
+      <c r="F187" s="52">
+        <v>63</v>
+      </c>
+      <c r="G187" s="45">
         <v>47</v>
       </c>
-      <c r="H187" s="61">
+      <c r="H187" s="50">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="20" t="s">
+      <c r="A188" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="B188" s="21" t="s">
+      <c r="B188" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="C188" s="32">
+      <c r="C188" s="26">
         <v>0</v>
       </c>
-      <c r="D188" s="32">
+      <c r="D188" s="26">
         <v>24</v>
       </c>
-      <c r="E188" s="50"/>
-      <c r="F188" s="15"/>
-      <c r="G188" s="53">
+      <c r="E188" s="35">
+        <v>39</v>
+      </c>
+      <c r="F188" s="52">
+        <v>54</v>
+      </c>
+      <c r="G188" s="46">
         <v>29</v>
       </c>
-      <c r="H188" s="61">
+      <c r="H188" s="50">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -6333,244 +6340,292 @@
       <c r="A189" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B189" s="29" t="s">
+      <c r="B189" s="23" t="s">
         <v>399</v>
       </c>
-      <c r="C189" s="32">
+      <c r="C189" s="26">
         <v>38</v>
       </c>
-      <c r="D189" s="31">
+      <c r="D189" s="25">
         <v>56</v>
       </c>
-      <c r="E189" s="45"/>
-      <c r="F189" s="15"/>
-      <c r="G189" s="53">
+      <c r="E189" s="53">
+        <v>14</v>
+      </c>
+      <c r="F189" s="52">
+        <v>58</v>
+      </c>
+      <c r="G189" s="46">
         <v>60</v>
       </c>
-      <c r="H189" s="22"/>
+      <c r="H189" s="18"/>
     </row>
     <row r="190" spans="1:8" ht="15.75">
-      <c r="A190" s="27" t="s">
+      <c r="A190" s="21" t="s">
         <v>384</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C190" s="32">
+      <c r="C190" s="26">
         <v>53</v>
       </c>
-      <c r="D190" s="31">
+      <c r="D190" s="25">
         <v>72</v>
       </c>
-      <c r="E190" s="37"/>
-      <c r="F190" s="16"/>
-      <c r="G190" s="31">
+      <c r="E190" s="54">
+        <v>65</v>
+      </c>
+      <c r="F190" s="55">
+        <v>71</v>
+      </c>
+      <c r="G190" s="25">
         <v>60</v>
       </c>
-      <c r="H190" s="22"/>
+      <c r="H190" s="18"/>
     </row>
     <row r="191" spans="1:8" ht="15.75">
-      <c r="A191" s="27" t="s">
+      <c r="A191" s="21" t="s">
         <v>385</v>
       </c>
-      <c r="B191" s="29" t="s">
+      <c r="B191" s="23" t="s">
         <v>400</v>
       </c>
-      <c r="C191" s="32">
+      <c r="C191" s="26">
         <v>75</v>
       </c>
-      <c r="D191" s="31">
+      <c r="D191" s="25">
         <v>69</v>
       </c>
-      <c r="E191" s="54"/>
-      <c r="F191" s="16"/>
-      <c r="G191" s="32">
+      <c r="E191" s="56">
+        <v>65</v>
+      </c>
+      <c r="F191" s="55">
+        <v>54</v>
+      </c>
+      <c r="G191" s="26">
         <v>51</v>
       </c>
-      <c r="H191" s="22"/>
+      <c r="H191" s="18"/>
     </row>
     <row r="192" spans="1:8" ht="15.75">
-      <c r="A192" s="28" t="s">
+      <c r="A192" s="22" t="s">
         <v>391</v>
       </c>
-      <c r="B192" s="29" t="s">
+      <c r="B192" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="C192" s="32" t="s">
+      <c r="C192" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="D192" s="31">
+      <c r="D192" s="25">
         <v>71</v>
       </c>
-      <c r="E192" s="55"/>
-      <c r="F192" s="18"/>
-      <c r="G192" s="32" t="s">
+      <c r="E192" s="26">
+        <v>33</v>
+      </c>
+      <c r="F192" s="57" t="s">
         <v>382</v>
       </c>
-      <c r="H192" s="22"/>
+      <c r="G192" s="26" t="s">
+        <v>382</v>
+      </c>
+      <c r="H192" s="18"/>
     </row>
     <row r="193" spans="1:8" ht="15.75">
-      <c r="A193" s="27" t="s">
+      <c r="A193" s="21" t="s">
         <v>386</v>
       </c>
-      <c r="B193" s="29" t="s">
+      <c r="B193" s="23" t="s">
         <v>402</v>
       </c>
-      <c r="C193" s="32">
+      <c r="C193" s="26">
         <v>22</v>
       </c>
-      <c r="D193" s="31">
+      <c r="D193" s="25">
         <v>54</v>
       </c>
-      <c r="E193" s="50"/>
-      <c r="F193" s="17"/>
-      <c r="G193" s="32">
+      <c r="E193" s="35">
+        <v>10</v>
+      </c>
+      <c r="F193" s="58">
+        <v>47</v>
+      </c>
+      <c r="G193" s="26">
         <v>62</v>
       </c>
-      <c r="H193" s="22"/>
+      <c r="H193" s="18"/>
     </row>
     <row r="194" spans="1:8" ht="15.75">
-      <c r="A194" s="27" t="s">
+      <c r="A194" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="B194" s="29" t="s">
+      <c r="B194" s="23" t="s">
         <v>397</v>
       </c>
-      <c r="C194" s="32">
+      <c r="C194" s="26">
         <v>7</v>
       </c>
-      <c r="D194" s="31">
+      <c r="D194" s="25">
         <v>31</v>
       </c>
-      <c r="E194" s="37"/>
-      <c r="F194" s="16"/>
-      <c r="G194" s="32">
+      <c r="E194" s="54" t="s">
+        <v>382</v>
+      </c>
+      <c r="F194" s="55">
+        <v>41</v>
+      </c>
+      <c r="G194" s="26">
         <v>16</v>
       </c>
-      <c r="H194" s="22"/>
+      <c r="H194" s="18"/>
     </row>
     <row r="195" spans="1:8" ht="15.75">
-      <c r="A195" s="27" t="s">
+      <c r="A195" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="B195" s="29" t="s">
+      <c r="B195" s="23" t="s">
         <v>403</v>
       </c>
-      <c r="C195" s="32">
+      <c r="C195" s="26">
         <v>41</v>
       </c>
-      <c r="D195" s="32" t="s">
+      <c r="D195" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="E195" s="56"/>
-      <c r="F195" s="18"/>
-      <c r="G195" s="32" t="s">
+      <c r="E195" s="59">
+        <v>29</v>
+      </c>
+      <c r="F195" s="57">
+        <v>48</v>
+      </c>
+      <c r="G195" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="H195" s="22"/>
+      <c r="H195" s="18"/>
     </row>
     <row r="196" spans="1:8" ht="15.75">
-      <c r="A196" s="27" t="s">
+      <c r="A196" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="B196" s="29" t="s">
+      <c r="B196" s="23" t="s">
         <v>398</v>
       </c>
-      <c r="C196" s="32">
+      <c r="C196" s="26">
         <v>35</v>
       </c>
-      <c r="D196" s="32">
+      <c r="D196" s="26">
         <v>84</v>
       </c>
-      <c r="E196" s="54"/>
-      <c r="F196" s="19"/>
-      <c r="G196" s="32">
+      <c r="E196" s="56">
+        <v>79</v>
+      </c>
+      <c r="F196" s="58">
+        <v>44</v>
+      </c>
+      <c r="G196" s="26">
         <v>76</v>
       </c>
-      <c r="H196" s="22"/>
+      <c r="H196" s="18"/>
     </row>
     <row r="197" spans="1:8" ht="15.75">
-      <c r="A197" s="28" t="s">
+      <c r="A197" s="22" t="s">
         <v>392</v>
       </c>
-      <c r="B197" s="29" t="s">
+      <c r="B197" s="23" t="s">
         <v>404</v>
       </c>
-      <c r="C197" s="32" t="s">
+      <c r="C197" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="D197" s="32">
+      <c r="D197" s="26">
         <v>42</v>
       </c>
-      <c r="E197" s="55"/>
-      <c r="F197" s="19"/>
-      <c r="G197" s="32" t="s">
+      <c r="E197" s="26">
+        <v>11</v>
+      </c>
+      <c r="F197" s="58" t="s">
         <v>382</v>
       </c>
-      <c r="H197" s="22"/>
+      <c r="G197" s="26" t="s">
+        <v>382</v>
+      </c>
+      <c r="H197" s="18"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="28" t="s">
+      <c r="A198" s="22" t="s">
         <v>393</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="C198" s="32" t="s">
+      <c r="C198" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="D198" s="57" t="s">
+      <c r="D198" s="47" t="s">
         <v>382</v>
       </c>
-      <c r="E198" s="55"/>
-      <c r="F198" s="19"/>
-      <c r="G198" s="32" t="s">
+      <c r="E198" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="H198" s="22"/>
+      <c r="F198" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="G198" s="26" t="s">
+        <v>382</v>
+      </c>
+      <c r="H198" s="18"/>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="27" t="s">
+      <c r="A199" s="21" t="s">
         <v>390</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="C199" s="58">
+      <c r="C199" s="48">
         <v>37</v>
       </c>
-      <c r="D199" s="58" t="s">
+      <c r="D199" s="48" t="s">
         <v>382</v>
       </c>
-      <c r="E199" s="55"/>
-      <c r="F199" s="25"/>
-      <c r="G199" s="58">
+      <c r="E199" s="26">
+        <v>7</v>
+      </c>
+      <c r="F199" s="56">
+        <v>13</v>
+      </c>
+      <c r="G199" s="48">
         <v>37</v>
       </c>
-      <c r="H199" s="22"/>
+      <c r="H199" s="18"/>
     </row>
     <row r="200" spans="1:8" ht="15.75">
-      <c r="A200" s="28" t="s">
+      <c r="A200" s="22" t="s">
         <v>394</v>
       </c>
-      <c r="B200" s="30" t="s">
+      <c r="B200" s="24" t="s">
         <v>407</v>
       </c>
       <c r="C200" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="D200" s="59" t="s">
+      <c r="D200" s="49" t="s">
         <v>382</v>
       </c>
-      <c r="E200" s="55"/>
-      <c r="F200" s="26"/>
-      <c r="G200" s="32" t="s">
+      <c r="E200" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="H200" s="22"/>
+      <c r="F200" s="26" t="s">
+        <v>382</v>
+      </c>
+      <c r="G200" s="26" t="s">
+        <v>382</v>
+      </c>
+      <c r="H200" s="18"/>
     </row>
     <row r="201" spans="1:8" ht="15.75">
-      <c r="A201" s="28" t="s">
+      <c r="A201" s="22" t="s">
         <v>395</v>
       </c>
       <c r="B201" s="1" t="s">
@@ -6579,12 +6634,16 @@
       <c r="C201" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="D201" s="59" t="s">
+      <c r="D201" s="49" t="s">
         <v>382</v>
       </c>
-      <c r="E201" s="55"/>
-      <c r="F201" s="60"/>
-      <c r="G201" s="32">
+      <c r="E201" s="26">
+        <v>10</v>
+      </c>
+      <c r="F201" s="60">
+        <v>38</v>
+      </c>
+      <c r="G201" s="26">
         <v>14</v>
       </c>
       <c r="H201" s="8"/>
@@ -6596,12 +6655,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -6745,16 +6813,13 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -6770,14 +6835,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
 </file>
--- a/MC3020_E24.xlsx
+++ b/MC3020_E24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E84997-9869-436B-89F7-5DACEEF39641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A691AFFC-8B0C-4026-ADAB-93D4AF830150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="409">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1256,7 +1256,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1316,13 +1316,6 @@
       <color rgb="FF000000"/>
       <name val="Palatino Linotype"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1722,9 +1715,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1734,7 +1727,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1745,21 +1738,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1774,119 +1752,124 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -2182,9 +2165,8 @@
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="9" customWidth="1"/>
+    <col min="3" max="7" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="9" customWidth="1"/>
     <col min="10" max="10" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2221,18 +2203,20 @@
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="20">
         <v>24</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="21">
         <v>54</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="28">
+      <c r="E2" s="22"/>
+      <c r="F2" s="53">
+        <v>51</v>
+      </c>
+      <c r="G2" s="23">
         <v>77</v>
       </c>
-      <c r="H2" s="50">
+      <c r="H2" s="52">
         <v>65.217391300000003</v>
       </c>
     </row>
@@ -2243,18 +2227,20 @@
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="20">
         <v>39</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="21">
         <v>75</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="30">
+      <c r="E3" s="24"/>
+      <c r="F3" s="54">
+        <v>77</v>
+      </c>
+      <c r="G3" s="25">
         <v>76</v>
       </c>
-      <c r="H3" s="50">
+      <c r="H3" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2265,18 +2251,20 @@
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="20">
         <v>43</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="20">
         <v>71</v>
       </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="32">
+      <c r="E4" s="26"/>
+      <c r="F4" s="54">
+        <v>74</v>
+      </c>
+      <c r="G4" s="27">
         <v>57</v>
       </c>
-      <c r="H4" s="50">
+      <c r="H4" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2287,18 +2275,20 @@
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="20">
         <v>30</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="20">
         <v>38</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="32">
+      <c r="E5" s="24"/>
+      <c r="F5" s="54">
+        <v>65</v>
+      </c>
+      <c r="G5" s="27">
         <v>34</v>
       </c>
-      <c r="H5" s="50">
+      <c r="H5" s="52">
         <v>30.434782599999998</v>
       </c>
     </row>
@@ -2309,18 +2299,20 @@
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="20">
         <v>18</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="20">
         <v>37</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="32">
+      <c r="E6" s="24"/>
+      <c r="F6" s="54">
+        <v>69</v>
+      </c>
+      <c r="G6" s="27">
         <v>48</v>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="52">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -2331,18 +2323,20 @@
       <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="20">
         <v>12</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="21">
         <v>34</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="32">
+      <c r="E7" s="24"/>
+      <c r="F7" s="54">
+        <v>68</v>
+      </c>
+      <c r="G7" s="27">
         <v>54</v>
       </c>
-      <c r="H7" s="50">
+      <c r="H7" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2353,18 +2347,20 @@
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="20">
         <v>69</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="21">
         <v>83</v>
       </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="32">
+      <c r="E8" s="24"/>
+      <c r="F8" s="54">
+        <v>72</v>
+      </c>
+      <c r="G8" s="27">
         <v>76</v>
       </c>
-      <c r="H8" s="50">
+      <c r="H8" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2375,18 +2371,20 @@
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="20">
         <v>43</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="21">
         <v>68</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="32">
+      <c r="E9" s="24"/>
+      <c r="F9" s="54">
+        <v>58</v>
+      </c>
+      <c r="G9" s="27">
         <v>59</v>
       </c>
-      <c r="H9" s="50">
+      <c r="H9" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -2397,18 +2395,20 @@
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="20">
         <v>38</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="20">
         <v>55</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="32">
+      <c r="E10" s="24"/>
+      <c r="F10" s="54">
+        <v>50</v>
+      </c>
+      <c r="G10" s="27">
         <v>61</v>
       </c>
-      <c r="H10" s="50">
+      <c r="H10" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2419,18 +2419,20 @@
       <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="20">
         <v>16</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="21">
         <v>28</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="32">
+      <c r="E11" s="24"/>
+      <c r="F11" s="54">
+        <v>54</v>
+      </c>
+      <c r="G11" s="27">
         <v>24</v>
       </c>
-      <c r="H11" s="50">
+      <c r="H11" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2441,18 +2443,20 @@
       <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="20">
         <v>84</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="20">
         <v>59</v>
       </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="32">
+      <c r="E12" s="24"/>
+      <c r="F12" s="54">
+        <v>67</v>
+      </c>
+      <c r="G12" s="27">
         <v>60</v>
       </c>
-      <c r="H12" s="50">
+      <c r="H12" s="52">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -2463,18 +2467,20 @@
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="20">
         <v>39</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="21">
         <v>43</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="32">
+      <c r="E13" s="24"/>
+      <c r="F13" s="54">
+        <v>63</v>
+      </c>
+      <c r="G13" s="27">
         <v>55</v>
       </c>
-      <c r="H13" s="50">
+      <c r="H13" s="52">
         <v>90.909090899999995</v>
       </c>
     </row>
@@ -2485,18 +2491,20 @@
       <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="20">
         <v>61</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="20">
         <v>89</v>
       </c>
-      <c r="E14" s="29"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="32">
+      <c r="E14" s="24"/>
+      <c r="F14" s="54">
+        <v>74</v>
+      </c>
+      <c r="G14" s="27">
         <v>76</v>
       </c>
-      <c r="H14" s="50">
+      <c r="H14" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2507,18 +2515,20 @@
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="20">
         <v>80</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="21">
         <v>42</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="32">
+      <c r="E15" s="24"/>
+      <c r="F15" s="54">
+        <v>85</v>
+      </c>
+      <c r="G15" s="27">
         <v>55</v>
       </c>
-      <c r="H15" s="50">
+      <c r="H15" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -2529,18 +2539,20 @@
       <c r="B16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="20">
         <v>33</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="20">
         <v>46</v>
       </c>
-      <c r="E16" s="27"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="33">
+      <c r="E16" s="22"/>
+      <c r="F16" s="55">
+        <v>78</v>
+      </c>
+      <c r="G16" s="28">
         <v>56</v>
       </c>
-      <c r="H16" s="50">
+      <c r="H16" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2551,18 +2563,20 @@
       <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="20">
         <v>45</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="21">
         <v>68</v>
       </c>
-      <c r="E17" s="29"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="32">
+      <c r="E17" s="24"/>
+      <c r="F17" s="54">
+        <v>73</v>
+      </c>
+      <c r="G17" s="27">
         <v>87</v>
       </c>
-      <c r="H17" s="50">
+      <c r="H17" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2573,18 +2587,20 @@
       <c r="B18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="20">
         <v>52</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="20">
         <v>54</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="32">
+      <c r="E18" s="24"/>
+      <c r="F18" s="54">
+        <v>58</v>
+      </c>
+      <c r="G18" s="27">
         <v>75</v>
       </c>
-      <c r="H18" s="50">
+      <c r="H18" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -2595,18 +2611,20 @@
       <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="20">
         <v>86</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="20">
         <v>94</v>
       </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="32">
+      <c r="E19" s="24"/>
+      <c r="F19" s="54">
+        <v>61</v>
+      </c>
+      <c r="G19" s="27">
         <v>83</v>
       </c>
-      <c r="H19" s="50">
+      <c r="H19" s="52">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -2617,18 +2635,20 @@
       <c r="B20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="20">
         <v>76</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="20">
         <v>78</v>
       </c>
-      <c r="E20" s="29"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="32">
+      <c r="E20" s="24"/>
+      <c r="F20" s="54">
         <v>63</v>
       </c>
-      <c r="H20" s="50">
+      <c r="G20" s="27">
+        <v>63</v>
+      </c>
+      <c r="H20" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2639,18 +2659,20 @@
       <c r="B21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="20">
         <v>99</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="20">
         <v>84</v>
       </c>
-      <c r="E21" s="29"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="32">
+      <c r="E21" s="24"/>
+      <c r="F21" s="54">
+        <v>81</v>
+      </c>
+      <c r="G21" s="27">
         <v>74</v>
       </c>
-      <c r="H21" s="50">
+      <c r="H21" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2661,18 +2683,20 @@
       <c r="B22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="20">
         <v>34</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="21">
         <v>51</v>
       </c>
-      <c r="E22" s="29"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="32">
+      <c r="E22" s="24"/>
+      <c r="F22" s="54">
+        <v>78</v>
+      </c>
+      <c r="G22" s="27">
         <v>38</v>
       </c>
-      <c r="H22" s="50">
+      <c r="H22" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2683,18 +2707,20 @@
       <c r="B23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="20">
         <v>71</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="21">
         <v>87</v>
       </c>
-      <c r="E23" s="29"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="32">
+      <c r="E23" s="24"/>
+      <c r="F23" s="54">
+        <v>78</v>
+      </c>
+      <c r="G23" s="27">
         <v>76</v>
       </c>
-      <c r="H23" s="50">
+      <c r="H23" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2705,18 +2731,20 @@
       <c r="B24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="20">
         <v>64</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="21">
         <v>40</v>
       </c>
-      <c r="E24" s="29"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="32">
+      <c r="E24" s="24"/>
+      <c r="F24" s="54">
+        <v>71</v>
+      </c>
+      <c r="G24" s="27">
         <v>44</v>
       </c>
-      <c r="H24" s="50">
+      <c r="H24" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2727,18 +2755,20 @@
       <c r="B25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="21">
         <v>63</v>
       </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="32">
+      <c r="E25" s="24"/>
+      <c r="F25" s="54">
         <v>67</v>
       </c>
-      <c r="H25" s="50">
+      <c r="G25" s="27">
+        <v>67</v>
+      </c>
+      <c r="H25" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2749,18 +2779,20 @@
       <c r="B26" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="20">
         <v>68</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="21">
         <v>73</v>
       </c>
-      <c r="E26" s="29"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="32">
+      <c r="E26" s="24"/>
+      <c r="F26" s="54">
+        <v>73</v>
+      </c>
+      <c r="G26" s="27">
         <v>71</v>
       </c>
-      <c r="H26" s="50">
+      <c r="H26" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2771,18 +2803,20 @@
       <c r="B27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="20">
         <v>43</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="20">
         <v>72</v>
       </c>
-      <c r="E27" s="29"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="32">
+      <c r="E27" s="24"/>
+      <c r="F27" s="54">
+        <v>64</v>
+      </c>
+      <c r="G27" s="27">
         <v>82</v>
       </c>
-      <c r="H27" s="50">
+      <c r="H27" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2793,18 +2827,20 @@
       <c r="B28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="20">
         <v>30</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="21">
         <v>85</v>
       </c>
-      <c r="E28" s="29"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="32">
+      <c r="E28" s="24"/>
+      <c r="F28" s="54">
+        <v>63</v>
+      </c>
+      <c r="G28" s="27">
         <v>62</v>
       </c>
-      <c r="H28" s="50">
+      <c r="H28" s="52">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -2815,18 +2851,20 @@
       <c r="B29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="20">
         <v>65</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="21">
         <v>84</v>
       </c>
-      <c r="E29" s="29"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="32">
+      <c r="E29" s="24"/>
+      <c r="F29" s="54">
+        <v>66</v>
+      </c>
+      <c r="G29" s="27">
         <v>75</v>
       </c>
-      <c r="H29" s="50">
+      <c r="H29" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2837,18 +2875,20 @@
       <c r="B30" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="20">
         <v>69</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="21">
         <v>25</v>
       </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="32">
+      <c r="E30" s="24"/>
+      <c r="F30" s="54">
+        <v>84</v>
+      </c>
+      <c r="G30" s="27">
         <v>63</v>
       </c>
-      <c r="H30" s="50">
+      <c r="H30" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2859,18 +2899,20 @@
       <c r="B31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="20">
         <v>44</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="21">
         <v>34</v>
       </c>
-      <c r="E31" s="29"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="34">
+      <c r="E31" s="24"/>
+      <c r="F31" s="54">
+        <v>78</v>
+      </c>
+      <c r="G31" s="29">
         <v>61</v>
       </c>
-      <c r="H31" s="50">
+      <c r="H31" s="52">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -2881,18 +2923,20 @@
       <c r="B32" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="20">
         <v>61</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="21">
         <v>85</v>
       </c>
-      <c r="E32" s="29"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="32">
+      <c r="E32" s="24"/>
+      <c r="F32" s="54">
+        <v>78</v>
+      </c>
+      <c r="G32" s="27">
         <v>81</v>
       </c>
-      <c r="H32" s="50">
+      <c r="H32" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2903,18 +2947,20 @@
       <c r="B33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="20">
         <v>49</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="21">
         <v>67</v>
       </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="32">
+      <c r="E33" s="24"/>
+      <c r="F33" s="54">
+        <v>67</v>
+      </c>
+      <c r="G33" s="27">
         <v>71</v>
       </c>
-      <c r="H33" s="50">
+      <c r="H33" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2925,18 +2971,20 @@
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="20">
         <v>50</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="21">
         <v>45</v>
       </c>
-      <c r="E34" s="29"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="32">
+      <c r="E34" s="24"/>
+      <c r="F34" s="54">
+        <v>51</v>
+      </c>
+      <c r="G34" s="27">
         <v>43</v>
       </c>
-      <c r="H34" s="50">
+      <c r="H34" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2947,18 +2995,20 @@
       <c r="B35" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="20">
         <v>48</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="20">
         <v>55</v>
       </c>
-      <c r="E35" s="29"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="32">
+      <c r="E35" s="24"/>
+      <c r="F35" s="54">
+        <v>67</v>
+      </c>
+      <c r="G35" s="27">
         <v>56</v>
       </c>
-      <c r="H35" s="50">
+      <c r="H35" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2969,18 +3019,20 @@
       <c r="B36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="20">
         <v>49</v>
       </c>
-      <c r="D36" s="26">
+      <c r="D36" s="21">
         <v>57</v>
       </c>
-      <c r="E36" s="29"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="32">
+      <c r="E36" s="24"/>
+      <c r="F36" s="54">
+        <v>60</v>
+      </c>
+      <c r="G36" s="27">
         <v>49</v>
       </c>
-      <c r="H36" s="50">
+      <c r="H36" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2991,18 +3043,20 @@
       <c r="B37" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="20">
         <v>58</v>
       </c>
-      <c r="D37" s="26">
+      <c r="D37" s="21">
         <v>41</v>
       </c>
-      <c r="E37" s="29"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="32">
+      <c r="E37" s="24"/>
+      <c r="F37" s="54">
+        <v>63</v>
+      </c>
+      <c r="G37" s="27">
         <v>54</v>
       </c>
-      <c r="H37" s="50">
+      <c r="H37" s="52">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -3013,18 +3067,20 @@
       <c r="B38" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="20">
         <v>81</v>
       </c>
-      <c r="D38" s="26">
+      <c r="D38" s="21">
         <v>84</v>
       </c>
-      <c r="E38" s="29"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="32">
+      <c r="E38" s="24"/>
+      <c r="F38" s="54">
+        <v>71</v>
+      </c>
+      <c r="G38" s="27">
         <v>72</v>
       </c>
-      <c r="H38" s="50">
+      <c r="H38" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3035,18 +3091,20 @@
       <c r="B39" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="20">
         <v>23</v>
       </c>
-      <c r="D39" s="26">
+      <c r="D39" s="21">
         <v>61</v>
       </c>
-      <c r="E39" s="29"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="32">
+      <c r="E39" s="24"/>
+      <c r="F39" s="54">
+        <v>56</v>
+      </c>
+      <c r="G39" s="27">
         <v>58</v>
       </c>
-      <c r="H39" s="50">
+      <c r="H39" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3057,18 +3115,20 @@
       <c r="B40" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="20">
         <v>32</v>
       </c>
-      <c r="D40" s="25">
+      <c r="D40" s="20">
         <v>37</v>
       </c>
-      <c r="E40" s="29"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="32">
+      <c r="E40" s="24"/>
+      <c r="F40" s="54">
+        <v>70</v>
+      </c>
+      <c r="G40" s="27">
         <v>57</v>
       </c>
-      <c r="H40" s="50">
+      <c r="H40" s="52">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3079,18 +3139,20 @@
       <c r="B41" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="20">
         <v>18</v>
       </c>
-      <c r="D41" s="25">
+      <c r="D41" s="20">
         <v>52</v>
       </c>
-      <c r="E41" s="29"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="32">
+      <c r="E41" s="24"/>
+      <c r="F41" s="54">
+        <v>47</v>
+      </c>
+      <c r="G41" s="27">
         <v>37</v>
       </c>
-      <c r="H41" s="50">
+      <c r="H41" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3101,18 +3163,20 @@
       <c r="B42" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="20">
         <v>46</v>
       </c>
-      <c r="D42" s="26">
+      <c r="D42" s="21">
         <v>75</v>
       </c>
-      <c r="E42" s="29"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="32">
+      <c r="E42" s="24"/>
+      <c r="F42" s="54">
+        <v>63</v>
+      </c>
+      <c r="G42" s="27">
         <v>67</v>
       </c>
-      <c r="H42" s="50">
+      <c r="H42" s="52">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -3123,18 +3187,20 @@
       <c r="B43" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="20">
         <v>53</v>
       </c>
-      <c r="D43" s="25">
+      <c r="D43" s="20">
         <v>50</v>
       </c>
-      <c r="E43" s="29"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="32">
+      <c r="E43" s="24"/>
+      <c r="F43" s="54">
+        <v>75</v>
+      </c>
+      <c r="G43" s="27">
         <v>69</v>
       </c>
-      <c r="H43" s="50">
+      <c r="H43" s="52">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3145,18 +3211,20 @@
       <c r="B44" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="25">
+      <c r="C44" s="20">
         <v>60</v>
       </c>
-      <c r="D44" s="25">
+      <c r="D44" s="20">
         <v>39</v>
       </c>
-      <c r="E44" s="29"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="32">
+      <c r="E44" s="24"/>
+      <c r="F44" s="54">
+        <v>65</v>
+      </c>
+      <c r="G44" s="27">
         <v>35</v>
       </c>
-      <c r="H44" s="50">
+      <c r="H44" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3167,18 +3235,20 @@
       <c r="B45" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C45" s="25">
+      <c r="C45" s="20">
         <v>58</v>
       </c>
-      <c r="D45" s="26">
+      <c r="D45" s="21">
         <v>79</v>
       </c>
-      <c r="E45" s="29"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="32">
+      <c r="E45" s="24"/>
+      <c r="F45" s="54">
+        <v>59</v>
+      </c>
+      <c r="G45" s="27">
         <v>72</v>
       </c>
-      <c r="H45" s="50">
+      <c r="H45" s="52">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -3189,18 +3259,20 @@
       <c r="B46" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C46" s="25">
+      <c r="C46" s="20">
         <v>60</v>
       </c>
-      <c r="D46" s="25">
+      <c r="D46" s="20">
         <v>70</v>
       </c>
-      <c r="E46" s="29"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="32">
+      <c r="E46" s="24"/>
+      <c r="F46" s="54">
+        <v>49</v>
+      </c>
+      <c r="G46" s="27">
         <v>45</v>
       </c>
-      <c r="H46" s="50">
+      <c r="H46" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3211,18 +3283,20 @@
       <c r="B47" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="25">
+      <c r="C47" s="20">
         <v>18</v>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="21">
         <v>64</v>
       </c>
-      <c r="E47" s="29"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="32">
+      <c r="E47" s="24"/>
+      <c r="F47" s="54">
+        <v>12</v>
+      </c>
+      <c r="G47" s="27">
         <v>55</v>
       </c>
-      <c r="H47" s="50">
+      <c r="H47" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3233,18 +3307,20 @@
       <c r="B48" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="25">
+      <c r="C48" s="20">
         <v>77</v>
       </c>
-      <c r="D48" s="26">
+      <c r="D48" s="21">
         <v>64</v>
       </c>
-      <c r="E48" s="29"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="34">
+      <c r="E48" s="24"/>
+      <c r="F48" s="54">
+        <v>76</v>
+      </c>
+      <c r="G48" s="29">
         <v>64</v>
       </c>
-      <c r="H48" s="50">
+      <c r="H48" s="52">
         <v>21.739130400000001</v>
       </c>
     </row>
@@ -3255,18 +3331,20 @@
       <c r="B49" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="25">
+      <c r="C49" s="20">
         <v>36</v>
       </c>
-      <c r="D49" s="26">
+      <c r="D49" s="21">
         <v>81</v>
       </c>
-      <c r="E49" s="29"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="32">
+      <c r="E49" s="24"/>
+      <c r="F49" s="54">
+        <v>83</v>
+      </c>
+      <c r="G49" s="27">
         <v>39</v>
       </c>
-      <c r="H49" s="50">
+      <c r="H49" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3277,18 +3355,20 @@
       <c r="B50" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="25">
+      <c r="C50" s="20">
         <v>47</v>
       </c>
-      <c r="D50" s="26">
+      <c r="D50" s="21">
         <v>63</v>
       </c>
-      <c r="E50" s="29"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="32">
+      <c r="E50" s="24"/>
+      <c r="F50" s="54">
+        <v>74</v>
+      </c>
+      <c r="G50" s="27">
         <v>68</v>
       </c>
-      <c r="H50" s="50">
+      <c r="H50" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3299,18 +3379,20 @@
       <c r="B51" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="25">
+      <c r="C51" s="20">
         <v>59</v>
       </c>
-      <c r="D51" s="25">
+      <c r="D51" s="20">
         <v>90</v>
       </c>
-      <c r="E51" s="29"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="32">
+      <c r="E51" s="24"/>
+      <c r="F51" s="54">
+        <v>72</v>
+      </c>
+      <c r="G51" s="27">
         <v>67</v>
       </c>
-      <c r="H51" s="50">
+      <c r="H51" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3321,18 +3403,20 @@
       <c r="B52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="25">
+      <c r="C52" s="20">
         <v>68</v>
       </c>
-      <c r="D52" s="25">
+      <c r="D52" s="20">
         <v>42</v>
       </c>
-      <c r="E52" s="29"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="32">
+      <c r="E52" s="24"/>
+      <c r="F52" s="54">
+        <v>58</v>
+      </c>
+      <c r="G52" s="27">
         <v>41</v>
       </c>
-      <c r="H52" s="50">
+      <c r="H52" s="52">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -3343,18 +3427,20 @@
       <c r="B53" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C53" s="25">
+      <c r="C53" s="20">
         <v>41</v>
       </c>
-      <c r="D53" s="26">
+      <c r="D53" s="21">
         <v>60</v>
       </c>
-      <c r="E53" s="29"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="32">
+      <c r="E53" s="24"/>
+      <c r="F53" s="54">
+        <v>60</v>
+      </c>
+      <c r="G53" s="27">
         <v>39</v>
       </c>
-      <c r="H53" s="50">
+      <c r="H53" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3365,18 +3451,20 @@
       <c r="B54" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="25">
+      <c r="C54" s="20">
         <v>54</v>
       </c>
-      <c r="D54" s="25">
+      <c r="D54" s="20">
         <v>76</v>
       </c>
-      <c r="E54" s="29"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="32">
+      <c r="E54" s="24"/>
+      <c r="F54" s="54">
+        <v>59</v>
+      </c>
+      <c r="G54" s="27">
         <v>68</v>
       </c>
-      <c r="H54" s="50">
+      <c r="H54" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3387,18 +3475,20 @@
       <c r="B55" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="25">
+      <c r="C55" s="20">
         <v>51</v>
       </c>
-      <c r="D55" s="26">
+      <c r="D55" s="21">
         <v>89</v>
       </c>
-      <c r="E55" s="29"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="34">
+      <c r="E55" s="24"/>
+      <c r="F55" s="54">
+        <v>76</v>
+      </c>
+      <c r="G55" s="29">
         <v>84</v>
       </c>
-      <c r="H55" s="50">
+      <c r="H55" s="52">
         <v>100</v>
       </c>
     </row>
@@ -3409,18 +3499,20 @@
       <c r="B56" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="20">
         <v>100</v>
       </c>
-      <c r="D56" s="26">
+      <c r="D56" s="21">
         <v>96</v>
       </c>
-      <c r="E56" s="29"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="32">
+      <c r="E56" s="24"/>
+      <c r="F56" s="54">
+        <v>54</v>
+      </c>
+      <c r="G56" s="27">
         <v>63</v>
       </c>
-      <c r="H56" s="50">
+      <c r="H56" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3431,18 +3523,20 @@
       <c r="B57" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="25">
+      <c r="C57" s="20">
         <v>21</v>
       </c>
-      <c r="D57" s="26">
+      <c r="D57" s="21">
         <v>37</v>
       </c>
-      <c r="E57" s="29"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="32">
+      <c r="E57" s="24"/>
+      <c r="F57" s="54">
+        <v>53</v>
+      </c>
+      <c r="G57" s="27">
         <v>49</v>
       </c>
-      <c r="H57" s="50">
+      <c r="H57" s="52">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3453,18 +3547,20 @@
       <c r="B58" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C58" s="25">
+      <c r="C58" s="20">
         <v>32</v>
       </c>
-      <c r="D58" s="25">
+      <c r="D58" s="20">
         <v>20</v>
       </c>
-      <c r="E58" s="29"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="32">
+      <c r="E58" s="24"/>
+      <c r="F58" s="54">
+        <v>43</v>
+      </c>
+      <c r="G58" s="27">
         <v>28</v>
       </c>
-      <c r="H58" s="50">
+      <c r="H58" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3475,18 +3571,20 @@
       <c r="B59" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="25">
+      <c r="C59" s="20">
         <v>23</v>
       </c>
-      <c r="D59" s="26">
+      <c r="D59" s="21">
         <v>36</v>
       </c>
-      <c r="E59" s="29"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="32">
+      <c r="E59" s="24"/>
+      <c r="F59" s="54">
+        <v>72</v>
+      </c>
+      <c r="G59" s="27">
         <v>44</v>
       </c>
-      <c r="H59" s="50">
+      <c r="H59" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3497,18 +3595,20 @@
       <c r="B60" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C60" s="25">
+      <c r="C60" s="20">
         <v>42</v>
       </c>
-      <c r="D60" s="26">
+      <c r="D60" s="21">
         <v>28</v>
       </c>
-      <c r="E60" s="27"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="33">
+      <c r="E60" s="22"/>
+      <c r="F60" s="55">
+        <v>68</v>
+      </c>
+      <c r="G60" s="28">
         <v>60</v>
       </c>
-      <c r="H60" s="50">
+      <c r="H60" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3519,18 +3619,20 @@
       <c r="B61" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="25">
+      <c r="C61" s="20">
         <v>58</v>
       </c>
-      <c r="D61" s="26">
+      <c r="D61" s="21">
         <v>68</v>
       </c>
-      <c r="E61" s="29"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="32">
+      <c r="E61" s="24"/>
+      <c r="F61" s="54">
+        <v>64</v>
+      </c>
+      <c r="G61" s="27">
         <v>86</v>
       </c>
-      <c r="H61" s="50">
+      <c r="H61" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3541,18 +3643,20 @@
       <c r="B62" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C62" s="25">
+      <c r="C62" s="20">
         <v>64</v>
       </c>
-      <c r="D62" s="26" t="s">
+      <c r="D62" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="E62" s="29"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="32">
+      <c r="E62" s="24"/>
+      <c r="F62" s="54">
         <v>52</v>
       </c>
-      <c r="H62" s="50">
+      <c r="G62" s="27">
+        <v>52</v>
+      </c>
+      <c r="H62" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3563,18 +3667,20 @@
       <c r="B63" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C63" s="25">
+      <c r="C63" s="20">
         <v>54</v>
       </c>
-      <c r="D63" s="26">
+      <c r="D63" s="21">
         <v>57</v>
       </c>
-      <c r="E63" s="29"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="32">
+      <c r="E63" s="24"/>
+      <c r="F63" s="54">
+        <v>61</v>
+      </c>
+      <c r="G63" s="27">
         <v>64</v>
       </c>
-      <c r="H63" s="50">
+      <c r="H63" s="52">
         <v>100</v>
       </c>
     </row>
@@ -3585,18 +3691,20 @@
       <c r="B64" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C64" s="25">
+      <c r="C64" s="20">
         <v>30</v>
       </c>
-      <c r="D64" s="26">
+      <c r="D64" s="21">
         <v>40</v>
       </c>
-      <c r="E64" s="29"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="32">
+      <c r="E64" s="24"/>
+      <c r="F64" s="54">
+        <v>65</v>
+      </c>
+      <c r="G64" s="27">
         <v>46</v>
       </c>
-      <c r="H64" s="50">
+      <c r="H64" s="52">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -3607,18 +3715,20 @@
       <c r="B65" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="25">
+      <c r="C65" s="20">
         <v>30</v>
       </c>
-      <c r="D65" s="26">
+      <c r="D65" s="21">
         <v>48</v>
       </c>
-      <c r="E65" s="29"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="32">
+      <c r="E65" s="24"/>
+      <c r="F65" s="54">
+        <v>58</v>
+      </c>
+      <c r="G65" s="27">
         <v>47</v>
       </c>
-      <c r="H65" s="50">
+      <c r="H65" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3629,18 +3739,20 @@
       <c r="B66" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C66" s="25">
+      <c r="C66" s="20">
         <v>47</v>
       </c>
-      <c r="D66" s="26">
+      <c r="D66" s="21">
         <v>84</v>
       </c>
-      <c r="E66" s="29"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="32">
+      <c r="E66" s="24"/>
+      <c r="F66" s="54">
+        <v>73</v>
+      </c>
+      <c r="G66" s="27">
         <v>54</v>
       </c>
-      <c r="H66" s="50">
+      <c r="H66" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3651,18 +3763,20 @@
       <c r="B67" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C67" s="25">
+      <c r="C67" s="20">
         <v>38</v>
       </c>
-      <c r="D67" s="26">
+      <c r="D67" s="21">
         <v>50</v>
       </c>
-      <c r="E67" s="29"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="32">
+      <c r="E67" s="24"/>
+      <c r="F67" s="54">
+        <v>60</v>
+      </c>
+      <c r="G67" s="27">
         <v>27</v>
       </c>
-      <c r="H67" s="50">
+      <c r="H67" s="52">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3673,18 +3787,20 @@
       <c r="B68" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C68" s="25">
+      <c r="C68" s="20">
         <v>47</v>
       </c>
-      <c r="D68" s="26">
+      <c r="D68" s="21">
         <v>73</v>
       </c>
-      <c r="E68" s="29"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="34">
+      <c r="E68" s="24"/>
+      <c r="F68" s="54">
+        <v>76</v>
+      </c>
+      <c r="G68" s="29">
         <v>62</v>
       </c>
-      <c r="H68" s="50">
+      <c r="H68" s="52">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3695,18 +3811,20 @@
       <c r="B69" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C69" s="25">
+      <c r="C69" s="20">
         <v>36</v>
       </c>
-      <c r="D69" s="25">
+      <c r="D69" s="20">
         <v>17</v>
       </c>
-      <c r="E69" s="29"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="32">
+      <c r="E69" s="24"/>
+      <c r="F69" s="54">
+        <v>66</v>
+      </c>
+      <c r="G69" s="27">
         <v>28</v>
       </c>
-      <c r="H69" s="50">
+      <c r="H69" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3717,18 +3835,20 @@
       <c r="B70" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C70" s="25">
+      <c r="C70" s="20">
         <v>47</v>
       </c>
-      <c r="D70" s="26">
+      <c r="D70" s="21">
         <v>60</v>
       </c>
-      <c r="E70" s="29"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="32">
+      <c r="E70" s="24"/>
+      <c r="F70" s="54">
+        <v>61</v>
+      </c>
+      <c r="G70" s="27">
         <v>37</v>
       </c>
-      <c r="H70" s="50">
+      <c r="H70" s="52">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3739,18 +3859,20 @@
       <c r="B71" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C71" s="25">
+      <c r="C71" s="20">
         <v>43</v>
       </c>
-      <c r="D71" s="25">
+      <c r="D71" s="20">
         <v>74</v>
       </c>
-      <c r="E71" s="29"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="32">
+      <c r="E71" s="24"/>
+      <c r="F71" s="54">
+        <v>54</v>
+      </c>
+      <c r="G71" s="27">
         <v>58</v>
       </c>
-      <c r="H71" s="50">
+      <c r="H71" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3761,18 +3883,20 @@
       <c r="B72" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C72" s="25">
+      <c r="C72" s="20">
         <v>46</v>
       </c>
-      <c r="D72" s="25">
+      <c r="D72" s="20">
         <v>68</v>
       </c>
-      <c r="E72" s="29"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="32">
+      <c r="E72" s="24"/>
+      <c r="F72" s="54">
+        <v>54</v>
+      </c>
+      <c r="G72" s="27">
         <v>26</v>
       </c>
-      <c r="H72" s="50">
+      <c r="H72" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3783,18 +3907,20 @@
       <c r="B73" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C73" s="25">
+      <c r="C73" s="20">
         <v>51</v>
       </c>
-      <c r="D73" s="26">
+      <c r="D73" s="21">
         <v>80</v>
       </c>
-      <c r="E73" s="29"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="34">
+      <c r="E73" s="24"/>
+      <c r="F73" s="54">
+        <v>71</v>
+      </c>
+      <c r="G73" s="29">
         <v>77</v>
       </c>
-      <c r="H73" s="50">
+      <c r="H73" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3805,18 +3931,20 @@
       <c r="B74" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C74" s="25">
+      <c r="C74" s="20">
         <v>73</v>
       </c>
-      <c r="D74" s="26">
+      <c r="D74" s="21">
         <v>58</v>
       </c>
-      <c r="E74" s="29"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="32">
+      <c r="E74" s="24"/>
+      <c r="F74" s="54">
+        <v>66</v>
+      </c>
+      <c r="G74" s="27">
         <v>60</v>
       </c>
-      <c r="H74" s="50">
+      <c r="H74" s="52">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3827,18 +3955,20 @@
       <c r="B75" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C75" s="25">
+      <c r="C75" s="20">
         <v>0</v>
       </c>
-      <c r="D75" s="25">
+      <c r="D75" s="20">
         <v>60</v>
       </c>
-      <c r="E75" s="29"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="32">
+      <c r="E75" s="24"/>
+      <c r="F75" s="54">
+        <v>55</v>
+      </c>
+      <c r="G75" s="27">
         <v>58</v>
       </c>
-      <c r="H75" s="50">
+      <c r="H75" s="52">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3849,18 +3979,20 @@
       <c r="B76" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C76" s="25">
+      <c r="C76" s="20">
         <v>55</v>
       </c>
-      <c r="D76" s="26">
+      <c r="D76" s="21">
         <v>44</v>
       </c>
-      <c r="E76" s="29"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="32">
+      <c r="E76" s="24"/>
+      <c r="F76" s="54">
+        <v>58</v>
+      </c>
+      <c r="G76" s="27">
         <v>47</v>
       </c>
-      <c r="H76" s="50">
+      <c r="H76" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3871,18 +4003,20 @@
       <c r="B77" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C77" s="25">
+      <c r="C77" s="20">
         <v>56</v>
       </c>
-      <c r="D77" s="26">
+      <c r="D77" s="21">
         <v>48</v>
       </c>
-      <c r="E77" s="29"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="32">
+      <c r="E77" s="24"/>
+      <c r="F77" s="54">
+        <v>71</v>
+      </c>
+      <c r="G77" s="27">
         <v>59</v>
       </c>
-      <c r="H77" s="50">
+      <c r="H77" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3893,18 +4027,20 @@
       <c r="B78" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C78" s="25">
+      <c r="C78" s="20">
         <v>35</v>
       </c>
-      <c r="D78" s="25">
+      <c r="D78" s="20">
         <v>68</v>
       </c>
-      <c r="E78" s="29"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="32">
+      <c r="E78" s="24"/>
+      <c r="F78" s="54">
+        <v>54</v>
+      </c>
+      <c r="G78" s="27">
         <v>77</v>
       </c>
-      <c r="H78" s="50">
+      <c r="H78" s="52">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -3915,18 +4051,20 @@
       <c r="B79" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C79" s="25">
+      <c r="C79" s="20">
         <v>32</v>
       </c>
-      <c r="D79" s="26">
+      <c r="D79" s="21">
         <v>41</v>
       </c>
-      <c r="E79" s="29"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="32">
+      <c r="E79" s="24"/>
+      <c r="F79" s="54">
+        <v>43</v>
+      </c>
+      <c r="G79" s="27">
         <v>49</v>
       </c>
-      <c r="H79" s="50">
+      <c r="H79" s="52">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -3937,18 +4075,20 @@
       <c r="B80" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C80" s="25">
+      <c r="C80" s="20">
         <v>71</v>
       </c>
-      <c r="D80" s="26">
+      <c r="D80" s="21">
         <v>56</v>
       </c>
-      <c r="E80" s="29"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="32">
+      <c r="E80" s="24"/>
+      <c r="F80" s="54">
+        <v>56</v>
+      </c>
+      <c r="G80" s="27">
         <v>51</v>
       </c>
-      <c r="H80" s="50">
+      <c r="H80" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3959,18 +4099,20 @@
       <c r="B81" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C81" s="25">
+      <c r="C81" s="20">
         <v>56</v>
       </c>
-      <c r="D81" s="26">
+      <c r="D81" s="21">
         <v>63</v>
       </c>
-      <c r="E81" s="29"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="32">
+      <c r="E81" s="24"/>
+      <c r="F81" s="54">
+        <v>79</v>
+      </c>
+      <c r="G81" s="27">
         <v>64</v>
       </c>
-      <c r="H81" s="50">
+      <c r="H81" s="52">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -3981,18 +4123,20 @@
       <c r="B82" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C82" s="25">
+      <c r="C82" s="20">
         <v>52</v>
       </c>
-      <c r="D82" s="26">
+      <c r="D82" s="21">
         <v>30</v>
       </c>
-      <c r="E82" s="29"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="32">
+      <c r="E82" s="24"/>
+      <c r="F82" s="54">
+        <v>63</v>
+      </c>
+      <c r="G82" s="27">
         <v>32</v>
       </c>
-      <c r="H82" s="50">
+      <c r="H82" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4003,18 +4147,20 @@
       <c r="B83" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C83" s="25">
+      <c r="C83" s="20">
         <v>34</v>
       </c>
-      <c r="D83" s="26">
+      <c r="D83" s="21">
         <v>85</v>
       </c>
-      <c r="E83" s="29"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="34">
+      <c r="E83" s="24"/>
+      <c r="F83" s="54">
+        <v>32</v>
+      </c>
+      <c r="G83" s="29">
         <v>57</v>
       </c>
-      <c r="H83" s="50">
+      <c r="H83" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4025,18 +4171,20 @@
       <c r="B84" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C84" s="25">
+      <c r="C84" s="20">
         <v>42</v>
       </c>
-      <c r="D84" s="25">
+      <c r="D84" s="20">
         <v>34</v>
       </c>
-      <c r="E84" s="29"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="32">
+      <c r="E84" s="24"/>
+      <c r="F84" s="54">
+        <v>56</v>
+      </c>
+      <c r="G84" s="27">
         <v>44</v>
       </c>
-      <c r="H84" s="50">
+      <c r="H84" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4047,18 +4195,20 @@
       <c r="B85" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C85" s="25">
+      <c r="C85" s="20">
         <v>51</v>
       </c>
-      <c r="D85" s="25">
+      <c r="D85" s="20">
         <v>67</v>
       </c>
-      <c r="E85" s="27"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="33">
+      <c r="E85" s="22"/>
+      <c r="F85" s="55">
+        <v>51</v>
+      </c>
+      <c r="G85" s="28">
         <v>58</v>
       </c>
-      <c r="H85" s="50">
+      <c r="H85" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4069,18 +4219,20 @@
       <c r="B86" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C86" s="25">
+      <c r="C86" s="20">
         <v>17</v>
       </c>
-      <c r="D86" s="26">
+      <c r="D86" s="21">
         <v>49</v>
       </c>
-      <c r="E86" s="29"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="32">
+      <c r="E86" s="24"/>
+      <c r="F86" s="54">
+        <v>35</v>
+      </c>
+      <c r="G86" s="27">
         <v>64</v>
       </c>
-      <c r="H86" s="50">
+      <c r="H86" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4091,18 +4243,20 @@
       <c r="B87" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C87" s="25">
+      <c r="C87" s="20">
         <v>34</v>
       </c>
-      <c r="D87" s="26">
+      <c r="D87" s="21">
         <v>58</v>
       </c>
-      <c r="E87" s="29"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="32">
+      <c r="E87" s="24"/>
+      <c r="F87" s="54">
+        <v>41</v>
+      </c>
+      <c r="G87" s="27">
         <v>58</v>
       </c>
-      <c r="H87" s="50">
+      <c r="H87" s="52">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -4113,18 +4267,20 @@
       <c r="B88" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="25">
+      <c r="C88" s="20">
         <v>60</v>
       </c>
-      <c r="D88" s="26">
+      <c r="D88" s="21">
         <v>47</v>
       </c>
-      <c r="E88" s="29"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="32">
+      <c r="E88" s="24"/>
+      <c r="F88" s="54">
+        <v>78</v>
+      </c>
+      <c r="G88" s="27">
         <v>81</v>
       </c>
-      <c r="H88" s="50">
+      <c r="H88" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4135,18 +4291,20 @@
       <c r="B89" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C89" s="25">
+      <c r="C89" s="20">
         <v>29</v>
       </c>
-      <c r="D89" s="26">
+      <c r="D89" s="21">
         <v>58</v>
       </c>
-      <c r="E89" s="29"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="32">
+      <c r="E89" s="24"/>
+      <c r="F89" s="54">
+        <v>54</v>
+      </c>
+      <c r="G89" s="27">
         <v>75</v>
       </c>
-      <c r="H89" s="50">
+      <c r="H89" s="52">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4157,18 +4315,20 @@
       <c r="B90" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C90" s="25">
+      <c r="C90" s="20">
         <v>25</v>
       </c>
-      <c r="D90" s="26">
+      <c r="D90" s="21">
         <v>84</v>
       </c>
-      <c r="E90" s="29"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="34">
+      <c r="E90" s="24"/>
+      <c r="F90" s="54">
+        <v>66</v>
+      </c>
+      <c r="G90" s="29">
         <v>54</v>
       </c>
-      <c r="H90" s="50">
+      <c r="H90" s="52">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -4179,18 +4339,20 @@
       <c r="B91" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C91" s="25">
+      <c r="C91" s="20">
         <v>33</v>
       </c>
-      <c r="D91" s="25">
+      <c r="D91" s="20">
         <v>66</v>
       </c>
-      <c r="E91" s="29"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="32">
+      <c r="E91" s="24"/>
+      <c r="F91" s="54">
+        <v>51</v>
+      </c>
+      <c r="G91" s="27">
         <v>58</v>
       </c>
-      <c r="H91" s="50">
+      <c r="H91" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4201,18 +4363,20 @@
       <c r="B92" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="25">
+      <c r="C92" s="20">
         <v>43</v>
       </c>
-      <c r="D92" s="25">
+      <c r="D92" s="20">
         <v>48</v>
       </c>
-      <c r="E92" s="29"/>
-      <c r="F92" s="13"/>
-      <c r="G92" s="32">
+      <c r="E92" s="24"/>
+      <c r="F92" s="54">
+        <v>64</v>
+      </c>
+      <c r="G92" s="27">
         <v>40</v>
       </c>
-      <c r="H92" s="50">
+      <c r="H92" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4223,18 +4387,20 @@
       <c r="B93" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C93" s="25">
+      <c r="C93" s="20">
         <v>24</v>
       </c>
-      <c r="D93" s="26" t="s">
+      <c r="D93" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="E93" s="29"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="32">
+      <c r="E93" s="24"/>
+      <c r="F93" s="54">
+        <v>66</v>
+      </c>
+      <c r="G93" s="27">
         <v>46</v>
       </c>
-      <c r="H93" s="50">
+      <c r="H93" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -4245,18 +4411,20 @@
       <c r="B94" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C94" s="25">
+      <c r="C94" s="20">
         <v>57</v>
       </c>
-      <c r="D94" s="25">
+      <c r="D94" s="20">
         <v>55</v>
       </c>
-      <c r="E94" s="29"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="32">
+      <c r="E94" s="24"/>
+      <c r="F94" s="54">
+        <v>63</v>
+      </c>
+      <c r="G94" s="27">
         <v>41</v>
       </c>
-      <c r="H94" s="50">
+      <c r="H94" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -4267,18 +4435,20 @@
       <c r="B95" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C95" s="25">
+      <c r="C95" s="20">
         <v>93</v>
       </c>
-      <c r="D95" s="26">
+      <c r="D95" s="21">
         <v>87</v>
       </c>
-      <c r="E95" s="29"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="32">
+      <c r="E95" s="24"/>
+      <c r="F95" s="54">
+        <v>75</v>
+      </c>
+      <c r="G95" s="27">
         <v>84</v>
       </c>
-      <c r="H95" s="50">
+      <c r="H95" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4289,18 +4459,20 @@
       <c r="B96" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="25">
+      <c r="C96" s="20">
         <v>65</v>
       </c>
-      <c r="D96" s="26">
+      <c r="D96" s="21">
         <v>79</v>
       </c>
-      <c r="E96" s="27"/>
-      <c r="F96" s="14"/>
-      <c r="G96" s="33">
+      <c r="E96" s="22"/>
+      <c r="F96" s="55">
+        <v>57</v>
+      </c>
+      <c r="G96" s="28">
         <v>75</v>
       </c>
-      <c r="H96" s="50">
+      <c r="H96" s="52">
         <v>65.217391300000003</v>
       </c>
     </row>
@@ -4311,18 +4483,20 @@
       <c r="B97" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="25">
+      <c r="C97" s="20">
         <v>26</v>
       </c>
-      <c r="D97" s="26">
+      <c r="D97" s="21">
         <v>63</v>
       </c>
-      <c r="E97" s="29"/>
-      <c r="F97" s="13"/>
-      <c r="G97" s="32">
+      <c r="E97" s="24"/>
+      <c r="F97" s="54">
+        <v>44</v>
+      </c>
+      <c r="G97" s="27">
         <v>46</v>
       </c>
-      <c r="H97" s="50">
+      <c r="H97" s="52">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -4333,18 +4507,20 @@
       <c r="B98" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="25">
+      <c r="C98" s="20">
         <v>13</v>
       </c>
-      <c r="D98" s="35">
+      <c r="D98" s="30">
         <v>52</v>
       </c>
-      <c r="E98" s="29"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="32">
+      <c r="E98" s="24"/>
+      <c r="F98" s="54">
+        <v>67</v>
+      </c>
+      <c r="G98" s="27">
         <v>61</v>
       </c>
-      <c r="H98" s="50">
+      <c r="H98" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4355,18 +4531,20 @@
       <c r="B99" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C99" s="25">
+      <c r="C99" s="20">
         <v>60</v>
       </c>
-      <c r="D99" s="35">
+      <c r="D99" s="30">
         <v>83</v>
       </c>
-      <c r="E99" s="29"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="34">
+      <c r="E99" s="24"/>
+      <c r="F99" s="54">
+        <v>79</v>
+      </c>
+      <c r="G99" s="29">
         <v>75</v>
       </c>
-      <c r="H99" s="50">
+      <c r="H99" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4377,18 +4555,20 @@
       <c r="B100" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="25">
+      <c r="C100" s="20">
         <v>42</v>
       </c>
-      <c r="D100" s="35">
+      <c r="D100" s="30">
         <v>48</v>
       </c>
-      <c r="E100" s="29"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="32">
+      <c r="E100" s="24"/>
+      <c r="F100" s="54">
+        <v>74</v>
+      </c>
+      <c r="G100" s="27">
         <v>50</v>
       </c>
-      <c r="H100" s="50">
+      <c r="H100" s="52">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -4399,18 +4579,20 @@
       <c r="B101" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="25">
+      <c r="C101" s="20">
         <v>52</v>
       </c>
-      <c r="D101" s="35">
+      <c r="D101" s="30">
         <v>79</v>
       </c>
-      <c r="E101" s="29"/>
-      <c r="F101" s="13"/>
-      <c r="G101" s="32">
+      <c r="E101" s="24"/>
+      <c r="F101" s="54">
+        <v>61</v>
+      </c>
+      <c r="G101" s="27">
         <v>47</v>
       </c>
-      <c r="H101" s="50">
+      <c r="H101" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4421,18 +4603,20 @@
       <c r="B102" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="25">
+      <c r="C102" s="20">
         <v>60</v>
       </c>
-      <c r="D102" s="25">
+      <c r="D102" s="20">
         <v>85</v>
       </c>
-      <c r="E102" s="29"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="32">
+      <c r="E102" s="24"/>
+      <c r="F102" s="54">
         <v>76</v>
       </c>
-      <c r="H102" s="50">
+      <c r="G102" s="27">
+        <v>76</v>
+      </c>
+      <c r="H102" s="52">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -4443,18 +4627,20 @@
       <c r="B103" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="25">
+      <c r="C103" s="20">
         <v>28</v>
       </c>
-      <c r="D103" s="35">
+      <c r="D103" s="30">
         <v>41</v>
       </c>
-      <c r="E103" s="29"/>
-      <c r="F103" s="13"/>
-      <c r="G103" s="32">
+      <c r="E103" s="24"/>
+      <c r="F103" s="54">
+        <v>53</v>
+      </c>
+      <c r="G103" s="27">
         <v>51</v>
       </c>
-      <c r="H103" s="50">
+      <c r="H103" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4465,18 +4651,20 @@
       <c r="B104" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C104" s="25">
+      <c r="C104" s="20">
         <v>27</v>
       </c>
-      <c r="D104" s="35">
+      <c r="D104" s="30">
         <v>74</v>
       </c>
-      <c r="E104" s="29"/>
-      <c r="F104" s="13"/>
-      <c r="G104" s="32">
+      <c r="E104" s="24"/>
+      <c r="F104" s="54">
+        <v>67</v>
+      </c>
+      <c r="G104" s="27">
         <v>69</v>
       </c>
-      <c r="H104" s="50">
+      <c r="H104" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4487,18 +4675,20 @@
       <c r="B105" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="25">
+      <c r="C105" s="20">
         <v>36</v>
       </c>
-      <c r="D105" s="35">
+      <c r="D105" s="30">
         <v>60</v>
       </c>
-      <c r="E105" s="29"/>
-      <c r="F105" s="13"/>
-      <c r="G105" s="32">
+      <c r="E105" s="24"/>
+      <c r="F105" s="54">
+        <v>66</v>
+      </c>
+      <c r="G105" s="27">
         <v>72</v>
       </c>
-      <c r="H105" s="50">
+      <c r="H105" s="52">
         <v>100</v>
       </c>
     </row>
@@ -4509,18 +4699,20 @@
       <c r="B106" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="25">
+      <c r="C106" s="20">
         <v>19</v>
       </c>
-      <c r="D106" s="35">
+      <c r="D106" s="30">
         <v>43</v>
       </c>
-      <c r="E106" s="29"/>
-      <c r="F106" s="13"/>
-      <c r="G106" s="32">
+      <c r="E106" s="24"/>
+      <c r="F106" s="54">
+        <v>55</v>
+      </c>
+      <c r="G106" s="27">
         <v>9</v>
       </c>
-      <c r="H106" s="50">
+      <c r="H106" s="52">
         <v>100</v>
       </c>
     </row>
@@ -4531,18 +4723,20 @@
       <c r="B107" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="25">
+      <c r="C107" s="20">
         <v>54</v>
       </c>
-      <c r="D107" s="35">
+      <c r="D107" s="30">
         <v>47</v>
       </c>
-      <c r="E107" s="29"/>
-      <c r="F107" s="13"/>
-      <c r="G107" s="32">
+      <c r="E107" s="24"/>
+      <c r="F107" s="54">
+        <v>64</v>
+      </c>
+      <c r="G107" s="27">
         <v>49</v>
       </c>
-      <c r="H107" s="50">
+      <c r="H107" s="52">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4553,18 +4747,20 @@
       <c r="B108" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C108" s="25">
+      <c r="C108" s="20">
         <v>46</v>
       </c>
-      <c r="D108" s="35">
+      <c r="D108" s="30">
         <v>12</v>
       </c>
-      <c r="E108" s="29"/>
-      <c r="F108" s="13"/>
-      <c r="G108" s="32">
+      <c r="E108" s="24"/>
+      <c r="F108" s="54">
+        <v>79</v>
+      </c>
+      <c r="G108" s="27">
         <v>56</v>
       </c>
-      <c r="H108" s="50">
+      <c r="H108" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4575,18 +4771,20 @@
       <c r="B109" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C109" s="25" t="s">
+      <c r="C109" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="D109" s="25">
+      <c r="D109" s="20">
         <v>35</v>
       </c>
-      <c r="E109" s="29"/>
-      <c r="F109" s="13"/>
-      <c r="G109" s="32">
+      <c r="E109" s="24"/>
+      <c r="F109" s="54">
+        <v>58</v>
+      </c>
+      <c r="G109" s="27">
         <v>62</v>
       </c>
-      <c r="H109" s="50">
+      <c r="H109" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4597,18 +4795,20 @@
       <c r="B110" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C110" s="25">
+      <c r="C110" s="20">
         <v>53</v>
       </c>
-      <c r="D110" s="25" t="s">
+      <c r="D110" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="E110" s="29"/>
-      <c r="F110" s="13"/>
-      <c r="G110" s="32">
+      <c r="E110" s="24"/>
+      <c r="F110" s="54">
+        <v>65</v>
+      </c>
+      <c r="G110" s="27">
         <v>60</v>
       </c>
-      <c r="H110" s="50">
+      <c r="H110" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -4619,18 +4819,20 @@
       <c r="B111" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C111" s="25">
+      <c r="C111" s="20">
         <v>4</v>
       </c>
-      <c r="D111" s="25">
+      <c r="D111" s="20">
         <v>12</v>
       </c>
-      <c r="E111" s="29"/>
-      <c r="F111" s="13"/>
-      <c r="G111" s="32">
+      <c r="E111" s="24"/>
+      <c r="F111" s="54">
+        <v>42</v>
+      </c>
+      <c r="G111" s="27">
         <v>11</v>
       </c>
-      <c r="H111" s="50">
+      <c r="H111" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4641,18 +4843,20 @@
       <c r="B112" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C112" s="25">
+      <c r="C112" s="20">
         <v>71</v>
       </c>
-      <c r="D112" s="35">
+      <c r="D112" s="30">
         <v>85</v>
       </c>
-      <c r="E112" s="29"/>
-      <c r="F112" s="13"/>
-      <c r="G112" s="32">
+      <c r="E112" s="24"/>
+      <c r="F112" s="54">
+        <v>75</v>
+      </c>
+      <c r="G112" s="27">
         <v>70</v>
       </c>
-      <c r="H112" s="50">
+      <c r="H112" s="52">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4663,18 +4867,20 @@
       <c r="B113" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C113" s="25">
+      <c r="C113" s="20">
         <v>29</v>
       </c>
-      <c r="D113" s="35">
+      <c r="D113" s="30">
         <v>19</v>
       </c>
-      <c r="E113" s="29"/>
-      <c r="F113" s="13"/>
-      <c r="G113" s="32">
+      <c r="E113" s="24"/>
+      <c r="F113" s="54">
+        <v>73</v>
+      </c>
+      <c r="G113" s="27">
         <v>50</v>
       </c>
-      <c r="H113" s="50">
+      <c r="H113" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -4685,18 +4891,20 @@
       <c r="B114" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C114" s="25">
+      <c r="C114" s="20">
         <v>45</v>
       </c>
-      <c r="D114" s="25">
+      <c r="D114" s="20">
         <v>75</v>
       </c>
-      <c r="E114" s="29"/>
-      <c r="F114" s="13"/>
-      <c r="G114" s="32">
+      <c r="E114" s="24"/>
+      <c r="F114" s="54">
+        <v>62</v>
+      </c>
+      <c r="G114" s="27">
         <v>63</v>
       </c>
-      <c r="H114" s="50">
+      <c r="H114" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4707,18 +4915,20 @@
       <c r="B115" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C115" s="25">
+      <c r="C115" s="20">
         <v>75</v>
       </c>
-      <c r="D115" s="25">
+      <c r="D115" s="20">
         <v>79</v>
       </c>
-      <c r="E115" s="29"/>
-      <c r="F115" s="13"/>
-      <c r="G115" s="32">
+      <c r="E115" s="24"/>
+      <c r="F115" s="54">
+        <v>71</v>
+      </c>
+      <c r="G115" s="27">
         <v>67</v>
       </c>
-      <c r="H115" s="50">
+      <c r="H115" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4729,18 +4939,20 @@
       <c r="B116" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C116" s="25">
+      <c r="C116" s="20">
         <v>53</v>
       </c>
-      <c r="D116" s="35">
+      <c r="D116" s="30">
         <v>47</v>
       </c>
-      <c r="E116" s="29"/>
-      <c r="F116" s="13"/>
-      <c r="G116" s="32">
+      <c r="E116" s="24"/>
+      <c r="F116" s="54">
+        <v>66</v>
+      </c>
+      <c r="G116" s="27">
         <v>72</v>
       </c>
-      <c r="H116" s="50">
+      <c r="H116" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4751,18 +4963,20 @@
       <c r="B117" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C117" s="25">
+      <c r="C117" s="20">
         <v>44</v>
       </c>
-      <c r="D117" s="35">
+      <c r="D117" s="30">
         <v>60</v>
       </c>
-      <c r="E117" s="29"/>
-      <c r="F117" s="13"/>
-      <c r="G117" s="32">
+      <c r="E117" s="24"/>
+      <c r="F117" s="54">
+        <v>61</v>
+      </c>
+      <c r="G117" s="27">
         <v>28</v>
       </c>
-      <c r="H117" s="50">
+      <c r="H117" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4773,18 +4987,20 @@
       <c r="B118" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C118" s="25">
+      <c r="C118" s="20">
         <v>64</v>
       </c>
-      <c r="D118" s="25">
+      <c r="D118" s="20">
         <v>57</v>
       </c>
-      <c r="E118" s="29"/>
-      <c r="F118" s="13"/>
-      <c r="G118" s="32">
+      <c r="E118" s="24"/>
+      <c r="F118" s="54">
+        <v>39</v>
+      </c>
+      <c r="G118" s="27">
         <v>54</v>
       </c>
-      <c r="H118" s="50">
+      <c r="H118" s="52">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -4795,18 +5011,20 @@
       <c r="B119" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C119" s="25">
+      <c r="C119" s="20">
         <v>83</v>
       </c>
-      <c r="D119" s="25">
+      <c r="D119" s="20">
         <v>52</v>
       </c>
-      <c r="E119" s="29"/>
-      <c r="F119" s="13"/>
-      <c r="G119" s="32">
+      <c r="E119" s="24"/>
+      <c r="F119" s="54">
+        <v>73</v>
+      </c>
+      <c r="G119" s="27">
         <v>76</v>
       </c>
-      <c r="H119" s="50">
+      <c r="H119" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4817,18 +5035,20 @@
       <c r="B120" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C120" s="25">
+      <c r="C120" s="20">
         <v>17</v>
       </c>
-      <c r="D120" s="35">
+      <c r="D120" s="30">
         <v>31</v>
       </c>
-      <c r="E120" s="29"/>
-      <c r="F120" s="13"/>
-      <c r="G120" s="32">
+      <c r="E120" s="24"/>
+      <c r="F120" s="54">
+        <v>70</v>
+      </c>
+      <c r="G120" s="27">
         <v>52</v>
       </c>
-      <c r="H120" s="50">
+      <c r="H120" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4839,18 +5059,20 @@
       <c r="B121" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C121" s="25" t="s">
+      <c r="C121" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="D121" s="25">
+      <c r="D121" s="20">
         <v>16</v>
       </c>
-      <c r="E121" s="29"/>
-      <c r="F121" s="13"/>
-      <c r="G121" s="32">
+      <c r="E121" s="24"/>
+      <c r="F121" s="54">
+        <v>67</v>
+      </c>
+      <c r="G121" s="27">
         <v>59</v>
       </c>
-      <c r="H121" s="50">
+      <c r="H121" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -4861,18 +5083,20 @@
       <c r="B122" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C122" s="25">
+      <c r="C122" s="20">
         <v>25</v>
       </c>
-      <c r="D122" s="25">
+      <c r="D122" s="20">
         <v>36</v>
       </c>
-      <c r="E122" s="29"/>
-      <c r="F122" s="13"/>
-      <c r="G122" s="32">
+      <c r="E122" s="24"/>
+      <c r="F122" s="54">
+        <v>53</v>
+      </c>
+      <c r="G122" s="27">
         <v>32</v>
       </c>
-      <c r="H122" s="50">
+      <c r="H122" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4883,18 +5107,20 @@
       <c r="B123" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C123" s="25" t="s">
+      <c r="C123" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="D123" s="35" t="s">
+      <c r="D123" s="30" t="s">
         <v>382</v>
       </c>
-      <c r="E123" s="29"/>
-      <c r="F123" s="13"/>
-      <c r="G123" s="32" t="s">
+      <c r="E123" s="24"/>
+      <c r="F123" s="54" t="s">
         <v>382</v>
       </c>
-      <c r="H123" s="50">
+      <c r="G123" s="27" t="s">
+        <v>382</v>
+      </c>
+      <c r="H123" s="52">
         <v>0</v>
       </c>
     </row>
@@ -4905,18 +5131,20 @@
       <c r="B124" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C124" s="25">
+      <c r="C124" s="20">
         <v>58</v>
       </c>
-      <c r="D124" s="25">
+      <c r="D124" s="20">
         <v>72</v>
       </c>
-      <c r="E124" s="29"/>
-      <c r="F124" s="13"/>
-      <c r="G124" s="32">
+      <c r="E124" s="24"/>
+      <c r="F124" s="54">
+        <v>66</v>
+      </c>
+      <c r="G124" s="27">
         <v>60</v>
       </c>
-      <c r="H124" s="50">
+      <c r="H124" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -4927,18 +5155,20 @@
       <c r="B125" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C125" s="25">
+      <c r="C125" s="20">
         <v>28</v>
       </c>
-      <c r="D125" s="35">
+      <c r="D125" s="30">
         <v>41</v>
       </c>
-      <c r="E125" s="29"/>
-      <c r="F125" s="13"/>
-      <c r="G125" s="32">
+      <c r="E125" s="24"/>
+      <c r="F125" s="54">
+        <v>79</v>
+      </c>
+      <c r="G125" s="27">
         <v>55</v>
       </c>
-      <c r="H125" s="50">
+      <c r="H125" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4949,18 +5179,20 @@
       <c r="B126" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C126" s="25">
+      <c r="C126" s="20">
         <v>44</v>
       </c>
-      <c r="D126" s="25">
+      <c r="D126" s="20">
         <v>53</v>
       </c>
-      <c r="E126" s="29"/>
-      <c r="F126" s="13"/>
-      <c r="G126" s="32">
+      <c r="E126" s="24"/>
+      <c r="F126" s="54">
+        <v>80</v>
+      </c>
+      <c r="G126" s="27">
         <v>68</v>
       </c>
-      <c r="H126" s="50">
+      <c r="H126" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4971,18 +5203,20 @@
       <c r="B127" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C127" s="25">
+      <c r="C127" s="20">
         <v>54</v>
       </c>
-      <c r="D127" s="35">
+      <c r="D127" s="30">
         <v>32</v>
       </c>
-      <c r="E127" s="29"/>
-      <c r="F127" s="13"/>
-      <c r="G127" s="32">
+      <c r="E127" s="24"/>
+      <c r="F127" s="54">
+        <v>61</v>
+      </c>
+      <c r="G127" s="27">
         <v>68</v>
       </c>
-      <c r="H127" s="50">
+      <c r="H127" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4993,18 +5227,20 @@
       <c r="B128" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C128" s="25">
+      <c r="C128" s="20">
         <v>21</v>
       </c>
-      <c r="D128" s="35">
+      <c r="D128" s="30">
         <v>56</v>
       </c>
-      <c r="E128" s="29"/>
-      <c r="F128" s="13"/>
-      <c r="G128" s="32">
+      <c r="E128" s="24"/>
+      <c r="F128" s="54">
+        <v>51</v>
+      </c>
+      <c r="G128" s="27">
         <v>48</v>
       </c>
-      <c r="H128" s="50">
+      <c r="H128" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5015,18 +5251,20 @@
       <c r="B129" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C129" s="25">
+      <c r="C129" s="20">
         <v>26</v>
       </c>
-      <c r="D129" s="35">
+      <c r="D129" s="30">
         <v>49</v>
       </c>
-      <c r="E129" s="29"/>
-      <c r="F129" s="13"/>
-      <c r="G129" s="32">
+      <c r="E129" s="24"/>
+      <c r="F129" s="54">
+        <v>46</v>
+      </c>
+      <c r="G129" s="27">
         <v>50</v>
       </c>
-      <c r="H129" s="50">
+      <c r="H129" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5037,18 +5275,20 @@
       <c r="B130" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C130" s="25">
+      <c r="C130" s="20">
         <v>15</v>
       </c>
-      <c r="D130" s="35">
+      <c r="D130" s="30">
         <v>26</v>
       </c>
-      <c r="E130" s="29"/>
-      <c r="F130" s="13"/>
-      <c r="G130" s="32">
+      <c r="E130" s="24"/>
+      <c r="F130" s="54">
+        <v>64</v>
+      </c>
+      <c r="G130" s="27">
         <v>22</v>
       </c>
-      <c r="H130" s="50">
+      <c r="H130" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5059,18 +5299,20 @@
       <c r="B131" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C131" s="25">
+      <c r="C131" s="20">
         <v>51</v>
       </c>
-      <c r="D131" s="35">
+      <c r="D131" s="30">
         <v>23</v>
       </c>
-      <c r="E131" s="29"/>
-      <c r="F131" s="13"/>
-      <c r="G131" s="32">
+      <c r="E131" s="24"/>
+      <c r="F131" s="54">
+        <v>64</v>
+      </c>
+      <c r="G131" s="27">
         <v>63</v>
       </c>
-      <c r="H131" s="50">
+      <c r="H131" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5081,18 +5323,20 @@
       <c r="B132" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C132" s="25">
+      <c r="C132" s="20">
         <v>50</v>
       </c>
-      <c r="D132" s="35">
+      <c r="D132" s="30">
         <v>81</v>
       </c>
-      <c r="E132" s="27"/>
-      <c r="F132" s="14"/>
-      <c r="G132" s="33">
+      <c r="E132" s="22"/>
+      <c r="F132" s="55">
+        <v>70</v>
+      </c>
+      <c r="G132" s="28">
         <v>66</v>
       </c>
-      <c r="H132" s="50">
+      <c r="H132" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5103,18 +5347,20 @@
       <c r="B133" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C133" s="25">
+      <c r="C133" s="20">
         <v>18</v>
       </c>
-      <c r="D133" s="35">
+      <c r="D133" s="30">
         <v>13</v>
       </c>
-      <c r="E133" s="29"/>
-      <c r="F133" s="13"/>
-      <c r="G133" s="32">
+      <c r="E133" s="24"/>
+      <c r="F133" s="54">
+        <v>63</v>
+      </c>
+      <c r="G133" s="27">
         <v>23</v>
       </c>
-      <c r="H133" s="50">
+      <c r="H133" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5125,18 +5371,20 @@
       <c r="B134" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C134" s="25">
+      <c r="C134" s="20">
         <v>53</v>
       </c>
-      <c r="D134" s="35">
+      <c r="D134" s="30">
         <v>49</v>
       </c>
-      <c r="E134" s="29"/>
-      <c r="F134" s="13"/>
-      <c r="G134" s="36">
+      <c r="E134" s="24"/>
+      <c r="F134" s="54">
+        <v>81</v>
+      </c>
+      <c r="G134" s="31">
         <v>65</v>
       </c>
-      <c r="H134" s="50">
+      <c r="H134" s="52">
         <v>100</v>
       </c>
     </row>
@@ -5147,18 +5395,20 @@
       <c r="B135" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C135" s="25">
+      <c r="C135" s="20">
         <v>8</v>
       </c>
-      <c r="D135" s="35">
+      <c r="D135" s="30">
         <v>42</v>
       </c>
-      <c r="E135" s="29"/>
-      <c r="F135" s="13"/>
-      <c r="G135" s="37">
+      <c r="E135" s="24"/>
+      <c r="F135" s="54">
+        <v>71</v>
+      </c>
+      <c r="G135" s="32">
         <v>45</v>
       </c>
-      <c r="H135" s="50">
+      <c r="H135" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5169,18 +5419,20 @@
       <c r="B136" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C136" s="25">
+      <c r="C136" s="20">
         <v>42</v>
       </c>
-      <c r="D136" s="25">
+      <c r="D136" s="20">
         <v>58</v>
       </c>
-      <c r="E136" s="29"/>
-      <c r="F136" s="13"/>
-      <c r="G136" s="30">
+      <c r="E136" s="24"/>
+      <c r="F136" s="54">
+        <v>66</v>
+      </c>
+      <c r="G136" s="25">
         <v>58</v>
       </c>
-      <c r="H136" s="50">
+      <c r="H136" s="52">
         <v>100</v>
       </c>
     </row>
@@ -5191,18 +5443,20 @@
       <c r="B137" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C137" s="25">
+      <c r="C137" s="20">
         <v>37</v>
       </c>
-      <c r="D137" s="25">
+      <c r="D137" s="20">
         <v>45</v>
       </c>
-      <c r="E137" s="27"/>
-      <c r="F137" s="14"/>
-      <c r="G137" s="33">
+      <c r="E137" s="22"/>
+      <c r="F137" s="55">
+        <v>67</v>
+      </c>
+      <c r="G137" s="28">
         <v>53</v>
       </c>
-      <c r="H137" s="50">
+      <c r="H137" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5213,18 +5467,20 @@
       <c r="B138" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C138" s="25">
+      <c r="C138" s="20">
         <v>46</v>
       </c>
-      <c r="D138" s="25">
+      <c r="D138" s="20">
         <v>29</v>
       </c>
-      <c r="E138" s="29"/>
-      <c r="F138" s="13"/>
-      <c r="G138" s="32">
+      <c r="E138" s="24"/>
+      <c r="F138" s="54">
+        <v>58</v>
+      </c>
+      <c r="G138" s="27">
         <v>64</v>
       </c>
-      <c r="H138" s="50">
+      <c r="H138" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5235,18 +5491,20 @@
       <c r="B139" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C139" s="25">
+      <c r="C139" s="20">
         <v>43</v>
       </c>
-      <c r="D139" s="35">
+      <c r="D139" s="30">
         <v>38</v>
       </c>
-      <c r="E139" s="29"/>
-      <c r="F139" s="13"/>
-      <c r="G139" s="32">
+      <c r="E139" s="24"/>
+      <c r="F139" s="54">
+        <v>45</v>
+      </c>
+      <c r="G139" s="27">
         <v>41</v>
       </c>
-      <c r="H139" s="50">
+      <c r="H139" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5257,18 +5515,20 @@
       <c r="B140" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C140" s="25">
+      <c r="C140" s="20">
         <v>40</v>
       </c>
-      <c r="D140" s="25">
+      <c r="D140" s="20">
         <v>66</v>
       </c>
-      <c r="E140" s="29"/>
-      <c r="F140" s="13"/>
-      <c r="G140" s="32">
+      <c r="E140" s="24"/>
+      <c r="F140" s="54">
+        <v>71</v>
+      </c>
+      <c r="G140" s="27">
         <v>70</v>
       </c>
-      <c r="H140" s="50">
+      <c r="H140" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5279,18 +5539,20 @@
       <c r="B141" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C141" s="25">
+      <c r="C141" s="20">
         <v>32</v>
       </c>
-      <c r="D141" s="25">
+      <c r="D141" s="20">
         <v>17</v>
       </c>
-      <c r="E141" s="29"/>
-      <c r="F141" s="13"/>
-      <c r="G141" s="32">
+      <c r="E141" s="24"/>
+      <c r="F141" s="54">
+        <v>32</v>
+      </c>
+      <c r="G141" s="27">
         <v>36</v>
       </c>
-      <c r="H141" s="50">
+      <c r="H141" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5301,18 +5563,20 @@
       <c r="B142" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C142" s="25">
+      <c r="C142" s="20">
         <v>32</v>
       </c>
-      <c r="D142" s="25">
+      <c r="D142" s="20">
         <v>45</v>
       </c>
-      <c r="E142" s="29"/>
-      <c r="F142" s="13"/>
-      <c r="G142" s="32">
+      <c r="E142" s="24"/>
+      <c r="F142" s="54">
+        <v>61</v>
+      </c>
+      <c r="G142" s="27">
         <v>65</v>
       </c>
-      <c r="H142" s="50">
+      <c r="H142" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5323,18 +5587,20 @@
       <c r="B143" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C143" s="25">
+      <c r="C143" s="20">
         <v>67</v>
       </c>
-      <c r="D143" s="35">
+      <c r="D143" s="30">
         <v>89</v>
       </c>
-      <c r="E143" s="29"/>
-      <c r="F143" s="13"/>
-      <c r="G143" s="32">
+      <c r="E143" s="24"/>
+      <c r="F143" s="54">
+        <v>65</v>
+      </c>
+      <c r="G143" s="27">
         <v>72</v>
       </c>
-      <c r="H143" s="50">
+      <c r="H143" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5345,18 +5611,20 @@
       <c r="B144" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C144" s="25">
+      <c r="C144" s="20">
         <v>61</v>
       </c>
-      <c r="D144" s="35">
+      <c r="D144" s="30">
         <v>76</v>
       </c>
-      <c r="E144" s="29"/>
-      <c r="F144" s="13"/>
-      <c r="G144" s="32">
+      <c r="E144" s="24"/>
+      <c r="F144" s="54">
+        <v>79</v>
+      </c>
+      <c r="G144" s="27">
         <v>59</v>
       </c>
-      <c r="H144" s="50">
+      <c r="H144" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5367,18 +5635,20 @@
       <c r="B145" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C145" s="25">
+      <c r="C145" s="20">
         <v>71</v>
       </c>
-      <c r="D145" s="35">
+      <c r="D145" s="30">
         <v>76</v>
       </c>
-      <c r="E145" s="29"/>
-      <c r="F145" s="13"/>
-      <c r="G145" s="32">
+      <c r="E145" s="24"/>
+      <c r="F145" s="54">
+        <v>63</v>
+      </c>
+      <c r="G145" s="27">
         <v>68</v>
       </c>
-      <c r="H145" s="50">
+      <c r="H145" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5389,18 +5659,20 @@
       <c r="B146" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C146" s="25">
+      <c r="C146" s="20">
         <v>96</v>
       </c>
-      <c r="D146" s="35">
+      <c r="D146" s="30">
         <v>86</v>
       </c>
-      <c r="E146" s="29"/>
-      <c r="F146" s="13"/>
-      <c r="G146" s="32">
+      <c r="E146" s="24"/>
+      <c r="F146" s="54">
+        <v>74</v>
+      </c>
+      <c r="G146" s="27">
         <v>66</v>
       </c>
-      <c r="H146" s="50">
+      <c r="H146" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5411,18 +5683,20 @@
       <c r="B147" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C147" s="25">
+      <c r="C147" s="20">
         <v>21</v>
       </c>
-      <c r="D147" s="25">
+      <c r="D147" s="20">
         <v>28</v>
       </c>
-      <c r="E147" s="29"/>
-      <c r="F147" s="13"/>
-      <c r="G147" s="32">
+      <c r="E147" s="24"/>
+      <c r="F147" s="54">
+        <v>57</v>
+      </c>
+      <c r="G147" s="27">
         <v>12</v>
       </c>
-      <c r="H147" s="50">
+      <c r="H147" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5433,18 +5707,20 @@
       <c r="B148" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C148" s="25">
+      <c r="C148" s="20">
         <v>47</v>
       </c>
-      <c r="D148" s="25">
+      <c r="D148" s="20">
         <v>73</v>
       </c>
-      <c r="E148" s="29"/>
-      <c r="F148" s="13"/>
-      <c r="G148" s="32">
+      <c r="E148" s="24"/>
+      <c r="F148" s="54">
+        <v>71</v>
+      </c>
+      <c r="G148" s="27">
         <v>52</v>
       </c>
-      <c r="H148" s="50">
+      <c r="H148" s="52">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5455,18 +5731,20 @@
       <c r="B149" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C149" s="25">
+      <c r="C149" s="20">
         <v>67</v>
       </c>
-      <c r="D149" s="35">
+      <c r="D149" s="30">
         <v>52</v>
       </c>
-      <c r="E149" s="29"/>
-      <c r="F149" s="13"/>
-      <c r="G149" s="32">
+      <c r="E149" s="24"/>
+      <c r="F149" s="54">
+        <v>69</v>
+      </c>
+      <c r="G149" s="27">
         <v>28</v>
       </c>
-      <c r="H149" s="50">
+      <c r="H149" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5477,18 +5755,20 @@
       <c r="B150" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C150" s="25" t="s">
+      <c r="C150" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="D150" s="35">
+      <c r="D150" s="30">
         <v>48</v>
       </c>
-      <c r="E150" s="27"/>
-      <c r="F150" s="38"/>
-      <c r="G150" s="33">
+      <c r="E150" s="22"/>
+      <c r="F150" s="20">
+        <v>68</v>
+      </c>
+      <c r="G150" s="28">
         <v>44</v>
       </c>
-      <c r="H150" s="50">
+      <c r="H150" s="52">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5499,18 +5779,20 @@
       <c r="B151" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C151" s="25">
+      <c r="C151" s="20">
         <v>52</v>
       </c>
-      <c r="D151" s="25">
+      <c r="D151" s="20">
         <v>43</v>
       </c>
-      <c r="E151" s="29"/>
-      <c r="F151" s="13"/>
-      <c r="G151" s="32">
+      <c r="E151" s="24"/>
+      <c r="F151" s="54">
+        <v>73</v>
+      </c>
+      <c r="G151" s="27">
         <v>64</v>
       </c>
-      <c r="H151" s="50">
+      <c r="H151" s="52">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5521,18 +5803,20 @@
       <c r="B152" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C152" s="25">
+      <c r="C152" s="20">
         <v>36</v>
       </c>
-      <c r="D152" s="25">
+      <c r="D152" s="20">
         <v>51</v>
       </c>
-      <c r="E152" s="29"/>
-      <c r="F152" s="13"/>
-      <c r="G152" s="32">
+      <c r="E152" s="24"/>
+      <c r="F152" s="54">
+        <v>54</v>
+      </c>
+      <c r="G152" s="27">
         <v>44</v>
       </c>
-      <c r="H152" s="50">
+      <c r="H152" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5543,18 +5827,20 @@
       <c r="B153" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C153" s="25">
+      <c r="C153" s="20">
         <v>78</v>
       </c>
-      <c r="D153" s="35">
+      <c r="D153" s="30">
         <v>46</v>
       </c>
-      <c r="E153" s="29"/>
-      <c r="F153" s="13"/>
-      <c r="G153" s="32">
+      <c r="E153" s="24"/>
+      <c r="F153" s="54">
+        <v>77</v>
+      </c>
+      <c r="G153" s="27">
         <v>59</v>
       </c>
-      <c r="H153" s="50">
+      <c r="H153" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5565,18 +5851,20 @@
       <c r="B154" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C154" s="25">
+      <c r="C154" s="20">
         <v>31</v>
       </c>
-      <c r="D154" s="26">
+      <c r="D154" s="21">
         <v>78</v>
       </c>
-      <c r="E154" s="29"/>
-      <c r="F154" s="13"/>
-      <c r="G154" s="32">
+      <c r="E154" s="24"/>
+      <c r="F154" s="54">
+        <v>65</v>
+      </c>
+      <c r="G154" s="27">
         <v>72</v>
       </c>
-      <c r="H154" s="50">
+      <c r="H154" s="52">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -5587,18 +5875,20 @@
       <c r="B155" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C155" s="25">
+      <c r="C155" s="20">
         <v>60</v>
       </c>
-      <c r="D155" s="26">
+      <c r="D155" s="21">
         <v>85</v>
       </c>
-      <c r="E155" s="29"/>
-      <c r="F155" s="13"/>
-      <c r="G155" s="32">
+      <c r="E155" s="24"/>
+      <c r="F155" s="54">
+        <v>72</v>
+      </c>
+      <c r="G155" s="27">
         <v>64</v>
       </c>
-      <c r="H155" s="50">
+      <c r="H155" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5609,18 +5899,20 @@
       <c r="B156" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C156" s="25">
+      <c r="C156" s="20">
         <v>95</v>
       </c>
-      <c r="D156" s="25">
+      <c r="D156" s="20">
         <v>89</v>
       </c>
-      <c r="E156" s="27"/>
-      <c r="F156" s="38"/>
-      <c r="G156" s="33">
+      <c r="E156" s="22"/>
+      <c r="F156" s="20">
+        <v>76</v>
+      </c>
+      <c r="G156" s="28">
         <v>80</v>
       </c>
-      <c r="H156" s="50">
+      <c r="H156" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5631,18 +5923,20 @@
       <c r="B157" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C157" s="25">
+      <c r="C157" s="20">
         <v>69</v>
       </c>
-      <c r="D157" s="25">
+      <c r="D157" s="20">
         <v>89</v>
       </c>
-      <c r="E157" s="29"/>
-      <c r="F157" s="13"/>
-      <c r="G157" s="32">
+      <c r="E157" s="24"/>
+      <c r="F157" s="54">
+        <v>72</v>
+      </c>
+      <c r="G157" s="27">
         <v>67</v>
       </c>
-      <c r="H157" s="50">
+      <c r="H157" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5653,18 +5947,20 @@
       <c r="B158" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C158" s="25">
+      <c r="C158" s="20">
         <v>47</v>
       </c>
-      <c r="D158" s="25">
+      <c r="D158" s="20">
         <v>86</v>
       </c>
-      <c r="E158" s="29"/>
-      <c r="F158" s="13"/>
-      <c r="G158" s="32">
+      <c r="E158" s="24"/>
+      <c r="F158" s="54">
+        <v>79</v>
+      </c>
+      <c r="G158" s="27">
         <v>57</v>
       </c>
-      <c r="H158" s="50">
+      <c r="H158" s="52">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5675,18 +5971,20 @@
       <c r="B159" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C159" s="25">
+      <c r="C159" s="20">
         <v>58</v>
       </c>
-      <c r="D159" s="26">
+      <c r="D159" s="21">
         <v>56</v>
       </c>
-      <c r="E159" s="39"/>
-      <c r="F159" s="13"/>
-      <c r="G159" s="32">
+      <c r="E159" s="33"/>
+      <c r="F159" s="54">
+        <v>62</v>
+      </c>
+      <c r="G159" s="27">
         <v>70</v>
       </c>
-      <c r="H159" s="50">
+      <c r="H159" s="52">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -5697,18 +5995,20 @@
       <c r="B160" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C160" s="25">
+      <c r="C160" s="20">
         <v>25</v>
       </c>
-      <c r="D160" s="26">
+      <c r="D160" s="21">
         <v>76</v>
       </c>
-      <c r="E160" s="29"/>
-      <c r="F160" s="13"/>
-      <c r="G160" s="32">
+      <c r="E160" s="24"/>
+      <c r="F160" s="54">
+        <v>52</v>
+      </c>
+      <c r="G160" s="27">
         <v>70</v>
       </c>
-      <c r="H160" s="50">
+      <c r="H160" s="52">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5719,18 +6019,20 @@
       <c r="B161" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C161" s="25">
+      <c r="C161" s="20">
         <v>44</v>
       </c>
-      <c r="D161" s="25">
+      <c r="D161" s="20">
         <v>34</v>
       </c>
-      <c r="E161" s="29"/>
-      <c r="F161" s="13"/>
-      <c r="G161" s="32">
+      <c r="E161" s="24"/>
+      <c r="F161" s="54">
+        <v>58</v>
+      </c>
+      <c r="G161" s="27">
         <v>57</v>
       </c>
-      <c r="H161" s="50">
+      <c r="H161" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5741,18 +6043,20 @@
       <c r="B162" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C162" s="25">
+      <c r="C162" s="20">
         <v>31</v>
       </c>
-      <c r="D162" s="26">
+      <c r="D162" s="21">
         <v>38</v>
       </c>
-      <c r="E162" s="29"/>
-      <c r="F162" s="13"/>
-      <c r="G162" s="32">
+      <c r="E162" s="24"/>
+      <c r="F162" s="54">
+        <v>73</v>
+      </c>
+      <c r="G162" s="27">
         <v>52</v>
       </c>
-      <c r="H162" s="50">
+      <c r="H162" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5763,18 +6067,20 @@
       <c r="B163" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C163" s="26">
+      <c r="C163" s="21">
         <v>40</v>
       </c>
-      <c r="D163" s="25">
+      <c r="D163" s="20">
         <v>55</v>
       </c>
-      <c r="E163" s="29"/>
-      <c r="F163" s="13"/>
-      <c r="G163" s="32">
+      <c r="E163" s="24"/>
+      <c r="F163" s="54">
+        <v>69</v>
+      </c>
+      <c r="G163" s="27">
         <v>42</v>
       </c>
-      <c r="H163" s="50">
+      <c r="H163" s="52">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5785,18 +6091,20 @@
       <c r="B164" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C164" s="26">
+      <c r="C164" s="21">
         <v>19</v>
       </c>
-      <c r="D164" s="26">
+      <c r="D164" s="21">
         <v>63</v>
       </c>
-      <c r="E164" s="29"/>
-      <c r="F164" s="13"/>
-      <c r="G164" s="36">
+      <c r="E164" s="24"/>
+      <c r="F164" s="54">
+        <v>60</v>
+      </c>
+      <c r="G164" s="31">
         <v>49</v>
       </c>
-      <c r="H164" s="50">
+      <c r="H164" s="52">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -5807,18 +6115,20 @@
       <c r="B165" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C165" s="26" t="s">
+      <c r="C165" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="D165" s="25">
+      <c r="D165" s="20">
         <v>74</v>
       </c>
-      <c r="E165" s="29"/>
-      <c r="F165" s="13"/>
-      <c r="G165" s="28">
+      <c r="E165" s="24"/>
+      <c r="F165" s="54">
+        <v>51</v>
+      </c>
+      <c r="G165" s="23">
         <v>61</v>
       </c>
-      <c r="H165" s="50">
+      <c r="H165" s="52">
         <v>65.217391300000003</v>
       </c>
     </row>
@@ -5829,18 +6139,20 @@
       <c r="B166" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C166" s="26">
+      <c r="C166" s="21">
         <v>18</v>
       </c>
-      <c r="D166" s="25">
+      <c r="D166" s="20">
         <v>44</v>
       </c>
-      <c r="E166" s="29"/>
-      <c r="F166" s="13"/>
-      <c r="G166" s="28">
+      <c r="E166" s="24"/>
+      <c r="F166" s="54">
+        <v>65</v>
+      </c>
+      <c r="G166" s="23">
         <v>47</v>
       </c>
-      <c r="H166" s="50">
+      <c r="H166" s="52">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -5851,18 +6163,20 @@
       <c r="B167" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C167" s="26">
+      <c r="C167" s="21">
         <v>44</v>
       </c>
-      <c r="D167" s="26">
+      <c r="D167" s="21">
         <v>69</v>
       </c>
-      <c r="E167" s="29"/>
-      <c r="F167" s="13"/>
-      <c r="G167" s="28">
+      <c r="E167" s="24"/>
+      <c r="F167" s="54">
+        <v>66</v>
+      </c>
+      <c r="G167" s="23">
         <v>65</v>
       </c>
-      <c r="H167" s="50">
+      <c r="H167" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5873,18 +6187,20 @@
       <c r="B168" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C168" s="26">
+      <c r="C168" s="21">
         <v>82</v>
       </c>
-      <c r="D168" s="25">
+      <c r="D168" s="20">
         <v>93</v>
       </c>
-      <c r="E168" s="29"/>
-      <c r="F168" s="13"/>
-      <c r="G168" s="28">
+      <c r="E168" s="24"/>
+      <c r="F168" s="54">
+        <v>79</v>
+      </c>
+      <c r="G168" s="23">
         <v>45</v>
       </c>
-      <c r="H168" s="50">
+      <c r="H168" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5895,18 +6211,20 @@
       <c r="B169" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C169" s="26">
+      <c r="C169" s="21">
         <v>55</v>
       </c>
-      <c r="D169" s="26">
+      <c r="D169" s="21">
         <v>55</v>
       </c>
-      <c r="E169" s="29"/>
-      <c r="F169" s="13"/>
-      <c r="G169" s="28">
+      <c r="E169" s="24"/>
+      <c r="F169" s="54">
+        <v>75</v>
+      </c>
+      <c r="G169" s="23">
         <v>69</v>
       </c>
-      <c r="H169" s="50">
+      <c r="H169" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5917,18 +6235,20 @@
       <c r="B170" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C170" s="26">
+      <c r="C170" s="21">
         <v>24</v>
       </c>
-      <c r="D170" s="26">
+      <c r="D170" s="21">
         <v>25</v>
       </c>
-      <c r="E170" s="40"/>
-      <c r="F170" s="41"/>
-      <c r="G170" s="42">
+      <c r="E170" s="34"/>
+      <c r="F170" s="56">
+        <v>51</v>
+      </c>
+      <c r="G170" s="35">
         <v>33</v>
       </c>
-      <c r="H170" s="50">
+      <c r="H170" s="52">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -5939,18 +6259,20 @@
       <c r="B171" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C171" s="26">
+      <c r="C171" s="21">
         <v>36</v>
       </c>
-      <c r="D171" s="26">
+      <c r="D171" s="21">
         <v>50</v>
       </c>
-      <c r="E171" s="29"/>
-      <c r="F171" s="15"/>
-      <c r="G171" s="43">
+      <c r="E171" s="24"/>
+      <c r="F171" s="44">
+        <v>53</v>
+      </c>
+      <c r="G171" s="36">
         <v>46</v>
       </c>
-      <c r="H171" s="50">
+      <c r="H171" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5961,18 +6283,20 @@
       <c r="B172" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C172" s="26">
+      <c r="C172" s="21">
         <v>55</v>
       </c>
-      <c r="D172" s="26">
+      <c r="D172" s="21">
         <v>58</v>
       </c>
-      <c r="E172" s="29"/>
-      <c r="F172" s="15"/>
-      <c r="G172" s="43">
+      <c r="E172" s="24"/>
+      <c r="F172" s="44">
+        <v>62</v>
+      </c>
+      <c r="G172" s="36">
         <v>26</v>
       </c>
-      <c r="H172" s="50">
+      <c r="H172" s="52">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -5983,18 +6307,20 @@
       <c r="B173" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C173" s="26">
+      <c r="C173" s="21">
         <v>27</v>
       </c>
-      <c r="D173" s="25">
+      <c r="D173" s="20">
         <v>65</v>
       </c>
-      <c r="E173" s="29"/>
-      <c r="F173" s="15"/>
-      <c r="G173" s="43">
+      <c r="E173" s="24"/>
+      <c r="F173" s="44">
+        <v>69</v>
+      </c>
+      <c r="G173" s="36">
         <v>50</v>
       </c>
-      <c r="H173" s="50">
+      <c r="H173" s="52">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -6005,18 +6331,20 @@
       <c r="B174" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C174" s="26">
+      <c r="C174" s="21">
         <v>14</v>
       </c>
-      <c r="D174" s="25">
+      <c r="D174" s="20">
         <v>22</v>
       </c>
-      <c r="E174" s="29"/>
-      <c r="F174" s="15"/>
-      <c r="G174" s="43">
+      <c r="E174" s="24"/>
+      <c r="F174" s="44">
+        <v>54</v>
+      </c>
+      <c r="G174" s="36">
         <v>51</v>
       </c>
-      <c r="H174" s="50">
+      <c r="H174" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6027,18 +6355,20 @@
       <c r="B175" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C175" s="26">
+      <c r="C175" s="21">
         <v>17</v>
       </c>
-      <c r="D175" s="26">
+      <c r="D175" s="21">
         <v>40</v>
       </c>
-      <c r="E175" s="29"/>
-      <c r="F175" s="15"/>
-      <c r="G175" s="43">
+      <c r="E175" s="24"/>
+      <c r="F175" s="44">
+        <v>44</v>
+      </c>
+      <c r="G175" s="36">
         <v>60</v>
       </c>
-      <c r="H175" s="50">
+      <c r="H175" s="52">
         <v>30.434782599999998</v>
       </c>
     </row>
@@ -6049,18 +6379,20 @@
       <c r="B176" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C176" s="26">
+      <c r="C176" s="21">
         <v>33</v>
       </c>
-      <c r="D176" s="25">
+      <c r="D176" s="20">
         <v>23</v>
       </c>
-      <c r="E176" s="29"/>
-      <c r="F176" s="15"/>
-      <c r="G176" s="43">
+      <c r="E176" s="24"/>
+      <c r="F176" s="44">
+        <v>62</v>
+      </c>
+      <c r="G176" s="36">
         <v>35</v>
       </c>
-      <c r="H176" s="50">
+      <c r="H176" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6071,18 +6403,20 @@
       <c r="B177" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C177" s="26">
+      <c r="C177" s="21">
         <v>64</v>
       </c>
-      <c r="D177" s="25">
+      <c r="D177" s="20">
         <v>81</v>
       </c>
-      <c r="E177" s="29"/>
-      <c r="F177" s="15"/>
-      <c r="G177" s="43">
+      <c r="E177" s="24"/>
+      <c r="F177" s="44">
+        <v>73</v>
+      </c>
+      <c r="G177" s="36">
         <v>54</v>
       </c>
-      <c r="H177" s="50">
+      <c r="H177" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6093,18 +6427,20 @@
       <c r="B178" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C178" s="26">
+      <c r="C178" s="21">
         <v>32</v>
       </c>
-      <c r="D178" s="25">
+      <c r="D178" s="20">
         <v>94</v>
       </c>
-      <c r="E178" s="29"/>
-      <c r="F178" s="15"/>
-      <c r="G178" s="43">
+      <c r="E178" s="24"/>
+      <c r="F178" s="44">
+        <v>62</v>
+      </c>
+      <c r="G178" s="36">
         <v>80</v>
       </c>
-      <c r="H178" s="50">
+      <c r="H178" s="52">
         <v>100</v>
       </c>
     </row>
@@ -6115,18 +6451,20 @@
       <c r="B179" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C179" s="26">
+      <c r="C179" s="21">
         <v>64</v>
       </c>
-      <c r="D179" s="25">
+      <c r="D179" s="20">
         <v>92</v>
       </c>
-      <c r="E179" s="29"/>
-      <c r="F179" s="15"/>
-      <c r="G179" s="43">
+      <c r="E179" s="24"/>
+      <c r="F179" s="44">
+        <v>84</v>
+      </c>
+      <c r="G179" s="36">
         <v>88</v>
       </c>
-      <c r="H179" s="50">
+      <c r="H179" s="52">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -6137,18 +6475,20 @@
       <c r="B180" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C180" s="26">
+      <c r="C180" s="21">
         <v>12</v>
       </c>
-      <c r="D180" s="25">
+      <c r="D180" s="20">
         <v>25</v>
       </c>
-      <c r="E180" s="29"/>
-      <c r="F180" s="15"/>
-      <c r="G180" s="43">
+      <c r="E180" s="24"/>
+      <c r="F180" s="44">
+        <v>53</v>
+      </c>
+      <c r="G180" s="36">
         <v>29</v>
       </c>
-      <c r="H180" s="50">
+      <c r="H180" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6159,18 +6499,20 @@
       <c r="B181" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C181" s="26">
+      <c r="C181" s="21">
         <v>36</v>
       </c>
-      <c r="D181" s="26">
+      <c r="D181" s="21">
         <v>70</v>
       </c>
-      <c r="E181" s="29"/>
-      <c r="F181" s="15"/>
-      <c r="G181" s="43">
+      <c r="E181" s="24"/>
+      <c r="F181" s="44">
+        <v>50</v>
+      </c>
+      <c r="G181" s="36">
         <v>63</v>
       </c>
-      <c r="H181" s="50">
+      <c r="H181" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6181,18 +6523,20 @@
       <c r="B182" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C182" s="26">
+      <c r="C182" s="21">
         <v>1</v>
       </c>
-      <c r="D182" s="26">
+      <c r="D182" s="21">
         <v>40</v>
       </c>
-      <c r="E182" s="44"/>
-      <c r="F182" s="15"/>
-      <c r="G182" s="43">
+      <c r="E182" s="37"/>
+      <c r="F182" s="44">
+        <v>58</v>
+      </c>
+      <c r="G182" s="36">
         <v>49</v>
       </c>
-      <c r="H182" s="50">
+      <c r="H182" s="52">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6203,18 +6547,20 @@
       <c r="B183" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C183" s="26">
+      <c r="C183" s="21">
         <v>38</v>
       </c>
-      <c r="D183" s="26">
+      <c r="D183" s="21">
         <v>66</v>
       </c>
-      <c r="E183" s="44"/>
-      <c r="F183" s="15"/>
-      <c r="G183" s="43">
+      <c r="E183" s="37"/>
+      <c r="F183" s="44">
+        <v>73</v>
+      </c>
+      <c r="G183" s="36">
         <v>59</v>
       </c>
-      <c r="H183" s="50">
+      <c r="H183" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6225,18 +6571,20 @@
       <c r="B184" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C184" s="26">
+      <c r="C184" s="21">
         <v>41</v>
       </c>
-      <c r="D184" s="26">
+      <c r="D184" s="21">
         <v>62</v>
       </c>
-      <c r="E184" s="29"/>
-      <c r="F184" s="15"/>
-      <c r="G184" s="43">
+      <c r="E184" s="24"/>
+      <c r="F184" s="44">
+        <v>54</v>
+      </c>
+      <c r="G184" s="36">
         <v>74</v>
       </c>
-      <c r="H184" s="50">
+      <c r="H184" s="52">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -6247,18 +6595,20 @@
       <c r="B185" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C185" s="26">
+      <c r="C185" s="21">
         <v>77</v>
       </c>
-      <c r="D185" s="26">
+      <c r="D185" s="21">
         <v>57</v>
       </c>
-      <c r="E185" s="29"/>
-      <c r="F185" s="15"/>
-      <c r="G185" s="43">
+      <c r="E185" s="24"/>
+      <c r="F185" s="44">
+        <v>57</v>
+      </c>
+      <c r="G185" s="36">
         <v>65</v>
       </c>
-      <c r="H185" s="50">
+      <c r="H185" s="52">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6269,70 +6619,72 @@
       <c r="B186" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C186" s="26">
+      <c r="C186" s="21">
         <v>74</v>
       </c>
-      <c r="D186" s="26">
+      <c r="D186" s="21">
         <v>44</v>
       </c>
-      <c r="E186" s="29"/>
-      <c r="F186" s="15"/>
-      <c r="G186" s="43">
+      <c r="E186" s="24"/>
+      <c r="F186" s="44">
+        <v>71</v>
+      </c>
+      <c r="G186" s="36">
         <v>69</v>
       </c>
-      <c r="H186" s="50">
+      <c r="H186" s="52">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="19" t="s">
+      <c r="A187" s="14" t="s">
         <v>380</v>
       </c>
-      <c r="B187" s="20" t="s">
+      <c r="B187" s="15" t="s">
         <v>381</v>
       </c>
-      <c r="C187" s="26">
+      <c r="C187" s="21">
         <v>37</v>
       </c>
-      <c r="D187" s="26">
+      <c r="D187" s="21">
         <v>32</v>
       </c>
-      <c r="E187" s="51">
+      <c r="E187" s="43">
         <v>57</v>
       </c>
-      <c r="F187" s="52">
+      <c r="F187" s="44">
         <v>63</v>
       </c>
-      <c r="G187" s="45">
+      <c r="G187" s="38">
         <v>47</v>
       </c>
-      <c r="H187" s="50">
+      <c r="H187" s="52">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="16" t="s">
+      <c r="A188" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="B188" s="17" t="s">
+      <c r="B188" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="C188" s="26">
+      <c r="C188" s="21">
         <v>0</v>
       </c>
-      <c r="D188" s="26">
+      <c r="D188" s="21">
         <v>24</v>
       </c>
-      <c r="E188" s="35">
+      <c r="E188" s="30">
         <v>39</v>
       </c>
-      <c r="F188" s="52">
+      <c r="F188" s="44">
         <v>54</v>
       </c>
-      <c r="G188" s="46">
+      <c r="G188" s="39">
         <v>29</v>
       </c>
-      <c r="H188" s="50">
+      <c r="H188" s="52">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -6340,292 +6692,292 @@
       <c r="A189" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B189" s="23" t="s">
+      <c r="B189" s="18" t="s">
         <v>399</v>
       </c>
-      <c r="C189" s="26">
+      <c r="C189" s="21">
         <v>38</v>
       </c>
-      <c r="D189" s="25">
+      <c r="D189" s="20">
         <v>56</v>
       </c>
-      <c r="E189" s="53">
+      <c r="E189" s="45">
         <v>14</v>
       </c>
-      <c r="F189" s="52">
+      <c r="F189" s="44">
         <v>58</v>
       </c>
-      <c r="G189" s="46">
+      <c r="G189" s="39">
         <v>60</v>
       </c>
-      <c r="H189" s="18"/>
+      <c r="H189" s="13"/>
     </row>
     <row r="190" spans="1:8" ht="15.75">
-      <c r="A190" s="21" t="s">
+      <c r="A190" s="16" t="s">
         <v>384</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C190" s="26">
+      <c r="C190" s="21">
         <v>53</v>
       </c>
-      <c r="D190" s="25">
+      <c r="D190" s="20">
         <v>72</v>
       </c>
-      <c r="E190" s="54">
+      <c r="E190" s="46">
         <v>65</v>
       </c>
-      <c r="F190" s="55">
+      <c r="F190" s="47">
         <v>71</v>
       </c>
-      <c r="G190" s="25">
+      <c r="G190" s="20">
         <v>60</v>
       </c>
-      <c r="H190" s="18"/>
+      <c r="H190" s="13"/>
     </row>
     <row r="191" spans="1:8" ht="15.75">
-      <c r="A191" s="21" t="s">
+      <c r="A191" s="16" t="s">
         <v>385</v>
       </c>
-      <c r="B191" s="23" t="s">
+      <c r="B191" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="C191" s="26">
+      <c r="C191" s="21">
         <v>75</v>
       </c>
-      <c r="D191" s="25">
+      <c r="D191" s="20">
         <v>69</v>
       </c>
-      <c r="E191" s="56">
+      <c r="E191" s="48">
         <v>65</v>
       </c>
-      <c r="F191" s="55">
+      <c r="F191" s="47">
         <v>54</v>
       </c>
-      <c r="G191" s="26">
+      <c r="G191" s="21">
         <v>51</v>
       </c>
-      <c r="H191" s="18"/>
+      <c r="H191" s="13"/>
     </row>
     <row r="192" spans="1:8" ht="15.75">
-      <c r="A192" s="22" t="s">
+      <c r="A192" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="B192" s="23" t="s">
+      <c r="B192" s="18" t="s">
         <v>401</v>
       </c>
-      <c r="C192" s="26" t="s">
+      <c r="C192" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="D192" s="25">
+      <c r="D192" s="20">
         <v>71</v>
       </c>
-      <c r="E192" s="26">
+      <c r="E192" s="21">
         <v>33</v>
       </c>
-      <c r="F192" s="57" t="s">
+      <c r="F192" s="49" t="s">
         <v>382</v>
       </c>
-      <c r="G192" s="26" t="s">
+      <c r="G192" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="H192" s="18"/>
+      <c r="H192" s="13"/>
     </row>
     <row r="193" spans="1:8" ht="15.75">
-      <c r="A193" s="21" t="s">
+      <c r="A193" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="B193" s="23" t="s">
+      <c r="B193" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="C193" s="26">
+      <c r="C193" s="21">
         <v>22</v>
       </c>
-      <c r="D193" s="25">
+      <c r="D193" s="20">
         <v>54</v>
       </c>
-      <c r="E193" s="35">
+      <c r="E193" s="30">
         <v>10</v>
       </c>
-      <c r="F193" s="58">
+      <c r="F193" s="50">
         <v>47</v>
       </c>
-      <c r="G193" s="26">
+      <c r="G193" s="21">
         <v>62</v>
       </c>
-      <c r="H193" s="18"/>
+      <c r="H193" s="13"/>
     </row>
     <row r="194" spans="1:8" ht="15.75">
-      <c r="A194" s="21" t="s">
+      <c r="A194" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="B194" s="23" t="s">
+      <c r="B194" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="C194" s="26">
+      <c r="C194" s="21">
         <v>7</v>
       </c>
-      <c r="D194" s="25">
+      <c r="D194" s="20">
         <v>31</v>
       </c>
-      <c r="E194" s="54" t="s">
+      <c r="E194" s="46" t="s">
         <v>382</v>
       </c>
-      <c r="F194" s="55">
+      <c r="F194" s="47">
         <v>41</v>
       </c>
-      <c r="G194" s="26">
+      <c r="G194" s="21">
         <v>16</v>
       </c>
-      <c r="H194" s="18"/>
+      <c r="H194" s="13"/>
     </row>
     <row r="195" spans="1:8" ht="15.75">
-      <c r="A195" s="21" t="s">
+      <c r="A195" s="16" t="s">
         <v>388</v>
       </c>
-      <c r="B195" s="23" t="s">
+      <c r="B195" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="C195" s="26">
+      <c r="C195" s="21">
         <v>41</v>
       </c>
-      <c r="D195" s="26" t="s">
+      <c r="D195" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="E195" s="59">
+      <c r="E195" s="51">
         <v>29</v>
       </c>
-      <c r="F195" s="57">
+      <c r="F195" s="49">
         <v>48</v>
       </c>
-      <c r="G195" s="26" t="s">
+      <c r="G195" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="H195" s="18"/>
+      <c r="H195" s="13"/>
     </row>
     <row r="196" spans="1:8" ht="15.75">
-      <c r="A196" s="21" t="s">
+      <c r="A196" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="B196" s="23" t="s">
+      <c r="B196" s="18" t="s">
         <v>398</v>
       </c>
-      <c r="C196" s="26">
+      <c r="C196" s="21">
         <v>35</v>
       </c>
-      <c r="D196" s="26">
+      <c r="D196" s="21">
         <v>84</v>
       </c>
-      <c r="E196" s="56">
+      <c r="E196" s="48">
         <v>79</v>
       </c>
-      <c r="F196" s="58">
+      <c r="F196" s="50">
         <v>44</v>
       </c>
-      <c r="G196" s="26">
+      <c r="G196" s="21">
         <v>76</v>
       </c>
-      <c r="H196" s="18"/>
+      <c r="H196" s="13"/>
     </row>
     <row r="197" spans="1:8" ht="15.75">
-      <c r="A197" s="22" t="s">
+      <c r="A197" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B197" s="23" t="s">
+      <c r="B197" s="18" t="s">
         <v>404</v>
       </c>
-      <c r="C197" s="26" t="s">
+      <c r="C197" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="D197" s="26">
+      <c r="D197" s="21">
         <v>42</v>
       </c>
-      <c r="E197" s="26">
+      <c r="E197" s="21">
         <v>11</v>
       </c>
-      <c r="F197" s="58" t="s">
+      <c r="F197" s="50" t="s">
         <v>382</v>
       </c>
-      <c r="G197" s="26" t="s">
+      <c r="G197" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="H197" s="18"/>
+      <c r="H197" s="13"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="22" t="s">
+      <c r="A198" s="17" t="s">
         <v>393</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="C198" s="26" t="s">
+      <c r="C198" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="D198" s="47" t="s">
+      <c r="D198" s="40" t="s">
         <v>382</v>
       </c>
-      <c r="E198" s="26" t="s">
+      <c r="E198" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="F198" s="58" t="s">
+      <c r="F198" s="50" t="s">
         <v>382</v>
       </c>
-      <c r="G198" s="26" t="s">
+      <c r="G198" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="H198" s="18"/>
+      <c r="H198" s="13"/>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="21" t="s">
+      <c r="A199" s="16" t="s">
         <v>390</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="C199" s="48">
+      <c r="C199" s="41">
         <v>37</v>
       </c>
-      <c r="D199" s="48" t="s">
+      <c r="D199" s="41" t="s">
         <v>382</v>
       </c>
-      <c r="E199" s="26">
+      <c r="E199" s="21">
         <v>7</v>
       </c>
-      <c r="F199" s="56">
+      <c r="F199" s="48">
         <v>13</v>
       </c>
-      <c r="G199" s="48">
+      <c r="G199" s="41">
         <v>37</v>
       </c>
-      <c r="H199" s="18"/>
+      <c r="H199" s="13"/>
     </row>
     <row r="200" spans="1:8" ht="15.75">
-      <c r="A200" s="22" t="s">
+      <c r="A200" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="B200" s="24" t="s">
+      <c r="B200" s="19" t="s">
         <v>407</v>
       </c>
       <c r="C200" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="D200" s="49" t="s">
+      <c r="D200" s="42" t="s">
         <v>382</v>
       </c>
-      <c r="E200" s="26" t="s">
+      <c r="E200" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="F200" s="26" t="s">
+      <c r="F200" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="G200" s="26" t="s">
+      <c r="G200" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="H200" s="18"/>
+      <c r="H200" s="13"/>
     </row>
     <row r="201" spans="1:8" ht="15.75">
-      <c r="A201" s="22" t="s">
+      <c r="A201" s="17" t="s">
         <v>395</v>
       </c>
       <c r="B201" s="1" t="s">
@@ -6634,16 +6986,16 @@
       <c r="C201" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="D201" s="49" t="s">
+      <c r="D201" s="42" t="s">
         <v>382</v>
       </c>
-      <c r="E201" s="26">
+      <c r="E201" s="21">
         <v>10</v>
       </c>
-      <c r="F201" s="60">
+      <c r="F201" s="52">
         <v>38</v>
       </c>
-      <c r="G201" s="26">
+      <c r="G201" s="21">
         <v>14</v>
       </c>
       <c r="H201" s="8"/>

--- a/MC3020_E24.xlsx
+++ b/MC3020_E24.xlsx
@@ -8,19 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A691AFFC-8B0C-4026-ADAB-93D4AF830150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103E7DD9-33D6-4517-8636-AAE00F17CC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="409">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1256,7 +1267,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1350,19 +1361,8 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1717,7 +1717,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1766,53 +1766,35 @@
     <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1829,13 +1811,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1853,24 +1835,31 @@
     <xf numFmtId="2" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2165,7 +2154,9 @@
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="7" width="13.5703125" customWidth="1"/>
+    <col min="3" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="53" customWidth="1"/>
+    <col min="6" max="7" width="13.5703125" customWidth="1"/>
     <col min="8" max="8" width="13.5703125" style="9" customWidth="1"/>
     <col min="10" max="10" width="12.28515625" customWidth="1"/>
   </cols>
@@ -2209,14 +2200,16 @@
       <c r="D2" s="21">
         <v>54</v>
       </c>
-      <c r="E2" s="22"/>
-      <c r="F2" s="53">
+      <c r="E2" s="49">
+        <v>45</v>
+      </c>
+      <c r="F2" s="47">
         <v>51</v>
       </c>
-      <c r="G2" s="23">
+      <c r="G2" s="22">
         <v>77</v>
       </c>
-      <c r="H2" s="52">
+      <c r="H2" s="46">
         <v>65.217391300000003</v>
       </c>
     </row>
@@ -2233,14 +2226,16 @@
       <c r="D3" s="21">
         <v>75</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="54">
+      <c r="E3" s="51">
+        <v>99</v>
+      </c>
+      <c r="F3" s="48">
         <v>77</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="23">
         <v>76</v>
       </c>
-      <c r="H3" s="52">
+      <c r="H3" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2257,14 +2252,16 @@
       <c r="D4" s="20">
         <v>71</v>
       </c>
-      <c r="E4" s="26"/>
-      <c r="F4" s="54">
+      <c r="E4" s="40">
+        <v>50</v>
+      </c>
+      <c r="F4" s="48">
         <v>74</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="24">
         <v>57</v>
       </c>
-      <c r="H4" s="52">
+      <c r="H4" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2281,14 +2278,16 @@
       <c r="D5" s="20">
         <v>38</v>
       </c>
-      <c r="E5" s="24"/>
-      <c r="F5" s="54">
+      <c r="E5" s="51">
+        <v>21</v>
+      </c>
+      <c r="F5" s="48">
         <v>65</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="24">
         <v>34</v>
       </c>
-      <c r="H5" s="52">
+      <c r="H5" s="46">
         <v>30.434782599999998</v>
       </c>
     </row>
@@ -2305,14 +2304,16 @@
       <c r="D6" s="20">
         <v>37</v>
       </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="54">
+      <c r="E6" s="51">
+        <v>40</v>
+      </c>
+      <c r="F6" s="48">
         <v>69</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="24">
         <v>48</v>
       </c>
-      <c r="H6" s="52">
+      <c r="H6" s="46">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -2329,14 +2330,16 @@
       <c r="D7" s="21">
         <v>34</v>
       </c>
-      <c r="E7" s="24"/>
-      <c r="F7" s="54">
+      <c r="E7" s="51">
+        <v>16</v>
+      </c>
+      <c r="F7" s="48">
         <v>68</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="24">
         <v>54</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2353,14 +2356,16 @@
       <c r="D8" s="21">
         <v>83</v>
       </c>
-      <c r="E8" s="24"/>
-      <c r="F8" s="54">
+      <c r="E8" s="51">
+        <v>51</v>
+      </c>
+      <c r="F8" s="48">
         <v>72</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="24">
         <v>76</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2377,14 +2382,16 @@
       <c r="D9" s="21">
         <v>68</v>
       </c>
-      <c r="E9" s="24"/>
-      <c r="F9" s="54">
+      <c r="E9" s="51">
+        <v>66</v>
+      </c>
+      <c r="F9" s="48">
         <v>58</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="24">
         <v>59</v>
       </c>
-      <c r="H9" s="52">
+      <c r="H9" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -2401,14 +2408,16 @@
       <c r="D10" s="20">
         <v>55</v>
       </c>
-      <c r="E10" s="24"/>
-      <c r="F10" s="54">
+      <c r="E10" s="51">
+        <v>47</v>
+      </c>
+      <c r="F10" s="48">
         <v>50</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="24">
         <v>61</v>
       </c>
-      <c r="H10" s="52">
+      <c r="H10" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2425,14 +2434,16 @@
       <c r="D11" s="21">
         <v>28</v>
       </c>
-      <c r="E11" s="24"/>
-      <c r="F11" s="54">
+      <c r="E11" s="51">
+        <v>45</v>
+      </c>
+      <c r="F11" s="48">
         <v>54</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="24">
         <v>24</v>
       </c>
-      <c r="H11" s="52">
+      <c r="H11" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2449,14 +2460,16 @@
       <c r="D12" s="20">
         <v>59</v>
       </c>
-      <c r="E12" s="24"/>
-      <c r="F12" s="54">
+      <c r="E12" s="51">
+        <v>76</v>
+      </c>
+      <c r="F12" s="48">
         <v>67</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="24">
         <v>60</v>
       </c>
-      <c r="H12" s="52">
+      <c r="H12" s="46">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -2473,14 +2486,16 @@
       <c r="D13" s="21">
         <v>43</v>
       </c>
-      <c r="E13" s="24"/>
-      <c r="F13" s="54">
+      <c r="E13" s="51">
+        <v>30</v>
+      </c>
+      <c r="F13" s="48">
         <v>63</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="24">
         <v>55</v>
       </c>
-      <c r="H13" s="52">
+      <c r="H13" s="46">
         <v>90.909090899999995</v>
       </c>
     </row>
@@ -2497,14 +2512,16 @@
       <c r="D14" s="20">
         <v>89</v>
       </c>
-      <c r="E14" s="24"/>
-      <c r="F14" s="54">
+      <c r="E14" s="51">
+        <v>88</v>
+      </c>
+      <c r="F14" s="48">
         <v>74</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="24">
         <v>76</v>
       </c>
-      <c r="H14" s="52">
+      <c r="H14" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2521,14 +2538,16 @@
       <c r="D15" s="21">
         <v>42</v>
       </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="54">
+      <c r="E15" s="51">
+        <v>82</v>
+      </c>
+      <c r="F15" s="48">
         <v>85</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="24">
         <v>55</v>
       </c>
-      <c r="H15" s="52">
+      <c r="H15" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -2545,14 +2564,16 @@
       <c r="D16" s="20">
         <v>46</v>
       </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="55">
+      <c r="E16" s="49">
+        <v>57</v>
+      </c>
+      <c r="F16" s="49">
         <v>78</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="25">
         <v>56</v>
       </c>
-      <c r="H16" s="52">
+      <c r="H16" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2569,14 +2590,16 @@
       <c r="D17" s="21">
         <v>68</v>
       </c>
-      <c r="E17" s="24"/>
-      <c r="F17" s="54">
+      <c r="E17" s="51">
+        <v>78</v>
+      </c>
+      <c r="F17" s="48">
         <v>73</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="24">
         <v>87</v>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2593,14 +2616,16 @@
       <c r="D18" s="20">
         <v>54</v>
       </c>
-      <c r="E18" s="24"/>
-      <c r="F18" s="54">
+      <c r="E18" s="51">
+        <v>52</v>
+      </c>
+      <c r="F18" s="48">
         <v>58</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="24">
         <v>75</v>
       </c>
-      <c r="H18" s="52">
+      <c r="H18" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -2617,14 +2642,16 @@
       <c r="D19" s="20">
         <v>94</v>
       </c>
-      <c r="E19" s="24"/>
-      <c r="F19" s="54">
+      <c r="E19" s="51">
+        <v>88</v>
+      </c>
+      <c r="F19" s="48">
         <v>61</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="24">
         <v>83</v>
       </c>
-      <c r="H19" s="52">
+      <c r="H19" s="46">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -2641,14 +2668,16 @@
       <c r="D20" s="20">
         <v>78</v>
       </c>
-      <c r="E20" s="24"/>
-      <c r="F20" s="54">
+      <c r="E20" s="51">
+        <v>55</v>
+      </c>
+      <c r="F20" s="48">
         <v>63</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="24">
         <v>63</v>
       </c>
-      <c r="H20" s="52">
+      <c r="H20" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2665,14 +2694,16 @@
       <c r="D21" s="20">
         <v>84</v>
       </c>
-      <c r="E21" s="24"/>
-      <c r="F21" s="54">
+      <c r="E21" s="51">
+        <v>71</v>
+      </c>
+      <c r="F21" s="48">
         <v>81</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="24">
         <v>74</v>
       </c>
-      <c r="H21" s="52">
+      <c r="H21" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2689,14 +2720,16 @@
       <c r="D22" s="21">
         <v>51</v>
       </c>
-      <c r="E22" s="24"/>
-      <c r="F22" s="54">
+      <c r="E22" s="51">
+        <v>58</v>
+      </c>
+      <c r="F22" s="48">
         <v>78</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="24">
         <v>38</v>
       </c>
-      <c r="H22" s="52">
+      <c r="H22" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2713,14 +2746,16 @@
       <c r="D23" s="21">
         <v>87</v>
       </c>
-      <c r="E23" s="24"/>
-      <c r="F23" s="54">
+      <c r="E23" s="51">
+        <v>65</v>
+      </c>
+      <c r="F23" s="48">
         <v>78</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="24">
         <v>76</v>
       </c>
-      <c r="H23" s="52">
+      <c r="H23" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2737,14 +2772,16 @@
       <c r="D24" s="21">
         <v>40</v>
       </c>
-      <c r="E24" s="24"/>
-      <c r="F24" s="54">
+      <c r="E24" s="51">
+        <v>48</v>
+      </c>
+      <c r="F24" s="48">
         <v>71</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="24">
         <v>44</v>
       </c>
-      <c r="H24" s="52">
+      <c r="H24" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2761,14 +2798,16 @@
       <c r="D25" s="21">
         <v>63</v>
       </c>
-      <c r="E25" s="24"/>
-      <c r="F25" s="54">
+      <c r="E25" s="51">
+        <v>92</v>
+      </c>
+      <c r="F25" s="48">
         <v>67</v>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="24">
         <v>67</v>
       </c>
-      <c r="H25" s="52">
+      <c r="H25" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2785,14 +2824,16 @@
       <c r="D26" s="21">
         <v>73</v>
       </c>
-      <c r="E26" s="24"/>
-      <c r="F26" s="54">
+      <c r="E26" s="51">
+        <v>77</v>
+      </c>
+      <c r="F26" s="48">
         <v>73</v>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="24">
         <v>71</v>
       </c>
-      <c r="H26" s="52">
+      <c r="H26" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2809,14 +2850,16 @@
       <c r="D27" s="20">
         <v>72</v>
       </c>
-      <c r="E27" s="24"/>
-      <c r="F27" s="54">
+      <c r="E27" s="51">
+        <v>81</v>
+      </c>
+      <c r="F27" s="48">
         <v>64</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="24">
         <v>82</v>
       </c>
-      <c r="H27" s="52">
+      <c r="H27" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2833,14 +2876,16 @@
       <c r="D28" s="21">
         <v>85</v>
       </c>
-      <c r="E28" s="24"/>
-      <c r="F28" s="54">
+      <c r="E28" s="51">
         <v>63</v>
       </c>
-      <c r="G28" s="27">
+      <c r="F28" s="48">
+        <v>63</v>
+      </c>
+      <c r="G28" s="24">
         <v>62</v>
       </c>
-      <c r="H28" s="52">
+      <c r="H28" s="46">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -2857,14 +2902,16 @@
       <c r="D29" s="21">
         <v>84</v>
       </c>
-      <c r="E29" s="24"/>
-      <c r="F29" s="54">
+      <c r="E29" s="51">
+        <v>35</v>
+      </c>
+      <c r="F29" s="48">
         <v>66</v>
       </c>
-      <c r="G29" s="27">
+      <c r="G29" s="24">
         <v>75</v>
       </c>
-      <c r="H29" s="52">
+      <c r="H29" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2881,14 +2928,16 @@
       <c r="D30" s="21">
         <v>25</v>
       </c>
-      <c r="E30" s="24"/>
-      <c r="F30" s="54">
+      <c r="E30" s="51">
+        <v>69</v>
+      </c>
+      <c r="F30" s="48">
         <v>84</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="24">
         <v>63</v>
       </c>
-      <c r="H30" s="52">
+      <c r="H30" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2905,14 +2954,16 @@
       <c r="D31" s="21">
         <v>34</v>
       </c>
-      <c r="E31" s="24"/>
-      <c r="F31" s="54">
+      <c r="E31" s="51">
+        <v>38</v>
+      </c>
+      <c r="F31" s="48">
         <v>78</v>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="26">
         <v>61</v>
       </c>
-      <c r="H31" s="52">
+      <c r="H31" s="46">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -2929,14 +2980,16 @@
       <c r="D32" s="21">
         <v>85</v>
       </c>
-      <c r="E32" s="24"/>
-      <c r="F32" s="54">
+      <c r="E32" s="51">
+        <v>61</v>
+      </c>
+      <c r="F32" s="48">
         <v>78</v>
       </c>
-      <c r="G32" s="27">
+      <c r="G32" s="24">
         <v>81</v>
       </c>
-      <c r="H32" s="52">
+      <c r="H32" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2953,14 +3006,16 @@
       <c r="D33" s="21">
         <v>67</v>
       </c>
-      <c r="E33" s="24"/>
-      <c r="F33" s="54">
+      <c r="E33" s="51">
         <v>67</v>
       </c>
-      <c r="G33" s="27">
+      <c r="F33" s="48">
+        <v>67</v>
+      </c>
+      <c r="G33" s="24">
         <v>71</v>
       </c>
-      <c r="H33" s="52">
+      <c r="H33" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2977,14 +3032,16 @@
       <c r="D34" s="21">
         <v>45</v>
       </c>
-      <c r="E34" s="24"/>
-      <c r="F34" s="54">
+      <c r="E34" s="51">
+        <v>27</v>
+      </c>
+      <c r="F34" s="48">
         <v>51</v>
       </c>
-      <c r="G34" s="27">
+      <c r="G34" s="24">
         <v>43</v>
       </c>
-      <c r="H34" s="52">
+      <c r="H34" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3001,14 +3058,16 @@
       <c r="D35" s="20">
         <v>55</v>
       </c>
-      <c r="E35" s="24"/>
-      <c r="F35" s="54">
+      <c r="E35" s="51">
+        <v>74</v>
+      </c>
+      <c r="F35" s="48">
         <v>67</v>
       </c>
-      <c r="G35" s="27">
+      <c r="G35" s="24">
         <v>56</v>
       </c>
-      <c r="H35" s="52">
+      <c r="H35" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3025,14 +3084,16 @@
       <c r="D36" s="21">
         <v>57</v>
       </c>
-      <c r="E36" s="24"/>
-      <c r="F36" s="54">
+      <c r="E36" s="51">
+        <v>65</v>
+      </c>
+      <c r="F36" s="48">
         <v>60</v>
       </c>
-      <c r="G36" s="27">
+      <c r="G36" s="24">
         <v>49</v>
       </c>
-      <c r="H36" s="52">
+      <c r="H36" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3049,14 +3110,16 @@
       <c r="D37" s="21">
         <v>41</v>
       </c>
-      <c r="E37" s="24"/>
-      <c r="F37" s="54">
+      <c r="E37" s="51">
+        <v>28</v>
+      </c>
+      <c r="F37" s="48">
         <v>63</v>
       </c>
-      <c r="G37" s="27">
+      <c r="G37" s="24">
         <v>54</v>
       </c>
-      <c r="H37" s="52">
+      <c r="H37" s="46">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -3073,14 +3136,16 @@
       <c r="D38" s="21">
         <v>84</v>
       </c>
-      <c r="E38" s="24"/>
-      <c r="F38" s="54">
+      <c r="E38" s="51">
+        <v>73</v>
+      </c>
+      <c r="F38" s="48">
         <v>71</v>
       </c>
-      <c r="G38" s="27">
+      <c r="G38" s="24">
         <v>72</v>
       </c>
-      <c r="H38" s="52">
+      <c r="H38" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3097,14 +3162,16 @@
       <c r="D39" s="21">
         <v>61</v>
       </c>
-      <c r="E39" s="24"/>
-      <c r="F39" s="54">
+      <c r="E39" s="51">
+        <v>75</v>
+      </c>
+      <c r="F39" s="48">
         <v>56</v>
       </c>
-      <c r="G39" s="27">
+      <c r="G39" s="24">
         <v>58</v>
       </c>
-      <c r="H39" s="52">
+      <c r="H39" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3121,14 +3188,16 @@
       <c r="D40" s="20">
         <v>37</v>
       </c>
-      <c r="E40" s="24"/>
-      <c r="F40" s="54">
+      <c r="E40" s="51">
+        <v>80</v>
+      </c>
+      <c r="F40" s="48">
         <v>70</v>
       </c>
-      <c r="G40" s="27">
+      <c r="G40" s="24">
         <v>57</v>
       </c>
-      <c r="H40" s="52">
+      <c r="H40" s="46">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3145,14 +3214,16 @@
       <c r="D41" s="20">
         <v>52</v>
       </c>
-      <c r="E41" s="24"/>
-      <c r="F41" s="54">
+      <c r="E41" s="51">
+        <v>59</v>
+      </c>
+      <c r="F41" s="48">
         <v>47</v>
       </c>
-      <c r="G41" s="27">
+      <c r="G41" s="24">
         <v>37</v>
       </c>
-      <c r="H41" s="52">
+      <c r="H41" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3169,14 +3240,16 @@
       <c r="D42" s="21">
         <v>75</v>
       </c>
-      <c r="E42" s="24"/>
-      <c r="F42" s="54">
+      <c r="E42" s="51">
+        <v>41</v>
+      </c>
+      <c r="F42" s="48">
         <v>63</v>
       </c>
-      <c r="G42" s="27">
+      <c r="G42" s="24">
         <v>67</v>
       </c>
-      <c r="H42" s="52">
+      <c r="H42" s="46">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -3193,14 +3266,16 @@
       <c r="D43" s="20">
         <v>50</v>
       </c>
-      <c r="E43" s="24"/>
-      <c r="F43" s="54">
+      <c r="E43" s="51">
+        <v>59</v>
+      </c>
+      <c r="F43" s="48">
         <v>75</v>
       </c>
-      <c r="G43" s="27">
+      <c r="G43" s="24">
         <v>69</v>
       </c>
-      <c r="H43" s="52">
+      <c r="H43" s="46">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3217,14 +3292,16 @@
       <c r="D44" s="20">
         <v>39</v>
       </c>
-      <c r="E44" s="24"/>
-      <c r="F44" s="54">
+      <c r="E44" s="51">
+        <v>31</v>
+      </c>
+      <c r="F44" s="48">
         <v>65</v>
       </c>
-      <c r="G44" s="27">
+      <c r="G44" s="24">
         <v>35</v>
       </c>
-      <c r="H44" s="52">
+      <c r="H44" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3241,14 +3318,16 @@
       <c r="D45" s="21">
         <v>79</v>
       </c>
-      <c r="E45" s="24"/>
-      <c r="F45" s="54">
+      <c r="E45" s="51">
+        <v>56</v>
+      </c>
+      <c r="F45" s="48">
         <v>59</v>
       </c>
-      <c r="G45" s="27">
+      <c r="G45" s="24">
         <v>72</v>
       </c>
-      <c r="H45" s="52">
+      <c r="H45" s="46">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -3265,14 +3344,16 @@
       <c r="D46" s="20">
         <v>70</v>
       </c>
-      <c r="E46" s="24"/>
-      <c r="F46" s="54">
+      <c r="E46" s="51">
+        <v>56</v>
+      </c>
+      <c r="F46" s="48">
         <v>49</v>
       </c>
-      <c r="G46" s="27">
+      <c r="G46" s="24">
         <v>45</v>
       </c>
-      <c r="H46" s="52">
+      <c r="H46" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3289,14 +3370,16 @@
       <c r="D47" s="21">
         <v>64</v>
       </c>
-      <c r="E47" s="24"/>
-      <c r="F47" s="54">
+      <c r="E47" s="51">
+        <v>91</v>
+      </c>
+      <c r="F47" s="48">
         <v>12</v>
       </c>
-      <c r="G47" s="27">
+      <c r="G47" s="24">
         <v>55</v>
       </c>
-      <c r="H47" s="52">
+      <c r="H47" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3313,14 +3396,16 @@
       <c r="D48" s="21">
         <v>64</v>
       </c>
-      <c r="E48" s="24"/>
-      <c r="F48" s="54">
+      <c r="E48" s="51">
+        <v>71</v>
+      </c>
+      <c r="F48" s="48">
         <v>76</v>
       </c>
-      <c r="G48" s="29">
+      <c r="G48" s="26">
         <v>64</v>
       </c>
-      <c r="H48" s="52">
+      <c r="H48" s="46">
         <v>21.739130400000001</v>
       </c>
     </row>
@@ -3337,14 +3422,16 @@
       <c r="D49" s="21">
         <v>81</v>
       </c>
-      <c r="E49" s="24"/>
-      <c r="F49" s="54">
+      <c r="E49" s="51">
+        <v>79</v>
+      </c>
+      <c r="F49" s="48">
         <v>83</v>
       </c>
-      <c r="G49" s="27">
+      <c r="G49" s="24">
         <v>39</v>
       </c>
-      <c r="H49" s="52">
+      <c r="H49" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3361,14 +3448,16 @@
       <c r="D50" s="21">
         <v>63</v>
       </c>
-      <c r="E50" s="24"/>
-      <c r="F50" s="54">
+      <c r="E50" s="51">
+        <v>41</v>
+      </c>
+      <c r="F50" s="48">
         <v>74</v>
       </c>
-      <c r="G50" s="27">
+      <c r="G50" s="24">
         <v>68</v>
       </c>
-      <c r="H50" s="52">
+      <c r="H50" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3385,14 +3474,16 @@
       <c r="D51" s="20">
         <v>90</v>
       </c>
-      <c r="E51" s="24"/>
-      <c r="F51" s="54">
+      <c r="E51" s="51">
+        <v>53</v>
+      </c>
+      <c r="F51" s="48">
         <v>72</v>
       </c>
-      <c r="G51" s="27">
+      <c r="G51" s="24">
         <v>67</v>
       </c>
-      <c r="H51" s="52">
+      <c r="H51" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3409,14 +3500,16 @@
       <c r="D52" s="20">
         <v>42</v>
       </c>
-      <c r="E52" s="24"/>
-      <c r="F52" s="54">
+      <c r="E52" s="51">
+        <v>52</v>
+      </c>
+      <c r="F52" s="48">
         <v>58</v>
       </c>
-      <c r="G52" s="27">
+      <c r="G52" s="24">
         <v>41</v>
       </c>
-      <c r="H52" s="52">
+      <c r="H52" s="46">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -3433,14 +3526,16 @@
       <c r="D53" s="21">
         <v>60</v>
       </c>
-      <c r="E53" s="24"/>
-      <c r="F53" s="54">
+      <c r="E53" s="51">
+        <v>24</v>
+      </c>
+      <c r="F53" s="48">
         <v>60</v>
       </c>
-      <c r="G53" s="27">
+      <c r="G53" s="24">
         <v>39</v>
       </c>
-      <c r="H53" s="52">
+      <c r="H53" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3457,14 +3552,16 @@
       <c r="D54" s="20">
         <v>76</v>
       </c>
-      <c r="E54" s="24"/>
-      <c r="F54" s="54">
+      <c r="E54" s="51">
+        <v>97</v>
+      </c>
+      <c r="F54" s="48">
         <v>59</v>
       </c>
-      <c r="G54" s="27">
+      <c r="G54" s="24">
         <v>68</v>
       </c>
-      <c r="H54" s="52">
+      <c r="H54" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3481,14 +3578,16 @@
       <c r="D55" s="21">
         <v>89</v>
       </c>
-      <c r="E55" s="24"/>
-      <c r="F55" s="54">
+      <c r="E55" s="51">
+        <v>85</v>
+      </c>
+      <c r="F55" s="48">
         <v>76</v>
       </c>
-      <c r="G55" s="29">
+      <c r="G55" s="26">
         <v>84</v>
       </c>
-      <c r="H55" s="52">
+      <c r="H55" s="46">
         <v>100</v>
       </c>
     </row>
@@ -3505,14 +3604,16 @@
       <c r="D56" s="21">
         <v>96</v>
       </c>
-      <c r="E56" s="24"/>
-      <c r="F56" s="54">
+      <c r="E56" s="51">
+        <v>67</v>
+      </c>
+      <c r="F56" s="48">
         <v>54</v>
       </c>
-      <c r="G56" s="27">
+      <c r="G56" s="24">
         <v>63</v>
       </c>
-      <c r="H56" s="52">
+      <c r="H56" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3529,14 +3630,16 @@
       <c r="D57" s="21">
         <v>37</v>
       </c>
-      <c r="E57" s="24"/>
-      <c r="F57" s="54">
+      <c r="E57" s="51">
+        <v>45</v>
+      </c>
+      <c r="F57" s="48">
         <v>53</v>
       </c>
-      <c r="G57" s="27">
+      <c r="G57" s="24">
         <v>49</v>
       </c>
-      <c r="H57" s="52">
+      <c r="H57" s="46">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3553,14 +3656,16 @@
       <c r="D58" s="20">
         <v>20</v>
       </c>
-      <c r="E58" s="24"/>
-      <c r="F58" s="54">
+      <c r="E58" s="51">
+        <v>38</v>
+      </c>
+      <c r="F58" s="48">
         <v>43</v>
       </c>
-      <c r="G58" s="27">
+      <c r="G58" s="24">
         <v>28</v>
       </c>
-      <c r="H58" s="52">
+      <c r="H58" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3577,14 +3682,16 @@
       <c r="D59" s="21">
         <v>36</v>
       </c>
-      <c r="E59" s="24"/>
-      <c r="F59" s="54">
+      <c r="E59" s="51">
+        <v>36</v>
+      </c>
+      <c r="F59" s="48">
         <v>72</v>
       </c>
-      <c r="G59" s="27">
+      <c r="G59" s="24">
         <v>44</v>
       </c>
-      <c r="H59" s="52">
+      <c r="H59" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3601,14 +3708,16 @@
       <c r="D60" s="21">
         <v>28</v>
       </c>
-      <c r="E60" s="22"/>
-      <c r="F60" s="55">
+      <c r="E60" s="49" t="s">
+        <v>382</v>
+      </c>
+      <c r="F60" s="49">
         <v>68</v>
       </c>
-      <c r="G60" s="28">
+      <c r="G60" s="25">
         <v>60</v>
       </c>
-      <c r="H60" s="52">
+      <c r="H60" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3625,14 +3734,16 @@
       <c r="D61" s="21">
         <v>68</v>
       </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="54">
+      <c r="E61" s="51">
+        <v>81</v>
+      </c>
+      <c r="F61" s="48">
         <v>64</v>
       </c>
-      <c r="G61" s="27">
+      <c r="G61" s="24">
         <v>86</v>
       </c>
-      <c r="H61" s="52">
+      <c r="H61" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3649,14 +3760,16 @@
       <c r="D62" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="54">
+      <c r="E62" s="51">
+        <v>55</v>
+      </c>
+      <c r="F62" s="48">
         <v>52</v>
       </c>
-      <c r="G62" s="27">
+      <c r="G62" s="24">
         <v>52</v>
       </c>
-      <c r="H62" s="52">
+      <c r="H62" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3673,14 +3786,16 @@
       <c r="D63" s="21">
         <v>57</v>
       </c>
-      <c r="E63" s="24"/>
-      <c r="F63" s="54">
+      <c r="E63" s="51">
+        <v>76</v>
+      </c>
+      <c r="F63" s="48">
         <v>61</v>
       </c>
-      <c r="G63" s="27">
+      <c r="G63" s="24">
         <v>64</v>
       </c>
-      <c r="H63" s="52">
+      <c r="H63" s="46">
         <v>100</v>
       </c>
     </row>
@@ -3697,14 +3812,16 @@
       <c r="D64" s="21">
         <v>40</v>
       </c>
-      <c r="E64" s="24"/>
-      <c r="F64" s="54">
+      <c r="E64" s="51">
+        <v>53</v>
+      </c>
+      <c r="F64" s="48">
         <v>65</v>
       </c>
-      <c r="G64" s="27">
+      <c r="G64" s="24">
         <v>46</v>
       </c>
-      <c r="H64" s="52">
+      <c r="H64" s="46">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -3721,14 +3838,16 @@
       <c r="D65" s="21">
         <v>48</v>
       </c>
-      <c r="E65" s="24"/>
-      <c r="F65" s="54">
+      <c r="E65" s="51">
+        <v>49</v>
+      </c>
+      <c r="F65" s="48">
         <v>58</v>
       </c>
-      <c r="G65" s="27">
+      <c r="G65" s="24">
         <v>47</v>
       </c>
-      <c r="H65" s="52">
+      <c r="H65" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3745,14 +3864,16 @@
       <c r="D66" s="21">
         <v>84</v>
       </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="54">
+      <c r="E66" s="51">
+        <v>23</v>
+      </c>
+      <c r="F66" s="48">
         <v>73</v>
       </c>
-      <c r="G66" s="27">
+      <c r="G66" s="24">
         <v>54</v>
       </c>
-      <c r="H66" s="52">
+      <c r="H66" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3769,14 +3890,16 @@
       <c r="D67" s="21">
         <v>50</v>
       </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="54">
+      <c r="E67" s="51">
+        <v>30</v>
+      </c>
+      <c r="F67" s="48">
         <v>60</v>
       </c>
-      <c r="G67" s="27">
+      <c r="G67" s="24">
         <v>27</v>
       </c>
-      <c r="H67" s="52">
+      <c r="H67" s="46">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3793,14 +3916,16 @@
       <c r="D68" s="21">
         <v>73</v>
       </c>
-      <c r="E68" s="24"/>
-      <c r="F68" s="54">
+      <c r="E68" s="51">
+        <v>61</v>
+      </c>
+      <c r="F68" s="48">
         <v>76</v>
       </c>
-      <c r="G68" s="29">
+      <c r="G68" s="26">
         <v>62</v>
       </c>
-      <c r="H68" s="52">
+      <c r="H68" s="46">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3817,14 +3942,16 @@
       <c r="D69" s="20">
         <v>17</v>
       </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="54">
+      <c r="E69" s="51">
+        <v>36</v>
+      </c>
+      <c r="F69" s="48">
         <v>66</v>
       </c>
-      <c r="G69" s="27">
+      <c r="G69" s="24">
         <v>28</v>
       </c>
-      <c r="H69" s="52">
+      <c r="H69" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3841,14 +3968,16 @@
       <c r="D70" s="21">
         <v>60</v>
       </c>
-      <c r="E70" s="24"/>
-      <c r="F70" s="54">
+      <c r="E70" s="51">
+        <v>46</v>
+      </c>
+      <c r="F70" s="48">
         <v>61</v>
       </c>
-      <c r="G70" s="27">
+      <c r="G70" s="24">
         <v>37</v>
       </c>
-      <c r="H70" s="52">
+      <c r="H70" s="46">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3865,14 +3994,16 @@
       <c r="D71" s="20">
         <v>74</v>
       </c>
-      <c r="E71" s="24"/>
-      <c r="F71" s="54">
+      <c r="E71" s="51">
+        <v>51</v>
+      </c>
+      <c r="F71" s="48">
         <v>54</v>
       </c>
-      <c r="G71" s="27">
+      <c r="G71" s="24">
         <v>58</v>
       </c>
-      <c r="H71" s="52">
+      <c r="H71" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3889,14 +4020,16 @@
       <c r="D72" s="20">
         <v>68</v>
       </c>
-      <c r="E72" s="24"/>
-      <c r="F72" s="54">
+      <c r="E72" s="51">
+        <v>29</v>
+      </c>
+      <c r="F72" s="48">
         <v>54</v>
       </c>
-      <c r="G72" s="27">
+      <c r="G72" s="24">
         <v>26</v>
       </c>
-      <c r="H72" s="52">
+      <c r="H72" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3913,14 +4046,16 @@
       <c r="D73" s="21">
         <v>80</v>
       </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="54">
+      <c r="E73" s="51">
+        <v>83</v>
+      </c>
+      <c r="F73" s="48">
         <v>71</v>
       </c>
-      <c r="G73" s="29">
+      <c r="G73" s="26">
         <v>77</v>
       </c>
-      <c r="H73" s="52">
+      <c r="H73" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3937,14 +4072,16 @@
       <c r="D74" s="21">
         <v>58</v>
       </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="54">
+      <c r="E74" s="51">
+        <v>32</v>
+      </c>
+      <c r="F74" s="48">
         <v>66</v>
       </c>
-      <c r="G74" s="27">
+      <c r="G74" s="24">
         <v>60</v>
       </c>
-      <c r="H74" s="52">
+      <c r="H74" s="46">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3961,14 +4098,16 @@
       <c r="D75" s="20">
         <v>60</v>
       </c>
-      <c r="E75" s="24"/>
-      <c r="F75" s="54">
+      <c r="E75" s="51">
+        <v>33</v>
+      </c>
+      <c r="F75" s="48">
         <v>55</v>
       </c>
-      <c r="G75" s="27">
+      <c r="G75" s="24">
         <v>58</v>
       </c>
-      <c r="H75" s="52">
+      <c r="H75" s="46">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3985,14 +4124,16 @@
       <c r="D76" s="21">
         <v>44</v>
       </c>
-      <c r="E76" s="24"/>
-      <c r="F76" s="54">
+      <c r="E76" s="51">
+        <v>11</v>
+      </c>
+      <c r="F76" s="48">
         <v>58</v>
       </c>
-      <c r="G76" s="27">
+      <c r="G76" s="24">
         <v>47</v>
       </c>
-      <c r="H76" s="52">
+      <c r="H76" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4009,14 +4150,16 @@
       <c r="D77" s="21">
         <v>48</v>
       </c>
-      <c r="E77" s="24"/>
-      <c r="F77" s="54">
+      <c r="E77" s="51">
+        <v>33</v>
+      </c>
+      <c r="F77" s="48">
         <v>71</v>
       </c>
-      <c r="G77" s="27">
+      <c r="G77" s="24">
         <v>59</v>
       </c>
-      <c r="H77" s="52">
+      <c r="H77" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4033,14 +4176,16 @@
       <c r="D78" s="20">
         <v>68</v>
       </c>
-      <c r="E78" s="24"/>
-      <c r="F78" s="54">
+      <c r="E78" s="51">
+        <v>24</v>
+      </c>
+      <c r="F78" s="48">
         <v>54</v>
       </c>
-      <c r="G78" s="27">
+      <c r="G78" s="24">
         <v>77</v>
       </c>
-      <c r="H78" s="52">
+      <c r="H78" s="46">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -4057,14 +4202,16 @@
       <c r="D79" s="21">
         <v>41</v>
       </c>
-      <c r="E79" s="24"/>
-      <c r="F79" s="54">
+      <c r="E79" s="51">
+        <v>27</v>
+      </c>
+      <c r="F79" s="48">
         <v>43</v>
       </c>
-      <c r="G79" s="27">
+      <c r="G79" s="24">
         <v>49</v>
       </c>
-      <c r="H79" s="52">
+      <c r="H79" s="46">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4081,14 +4228,16 @@
       <c r="D80" s="21">
         <v>56</v>
       </c>
-      <c r="E80" s="24"/>
-      <c r="F80" s="54">
+      <c r="E80" s="51">
+        <v>72</v>
+      </c>
+      <c r="F80" s="48">
         <v>56</v>
       </c>
-      <c r="G80" s="27">
+      <c r="G80" s="24">
         <v>51</v>
       </c>
-      <c r="H80" s="52">
+      <c r="H80" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4105,14 +4254,16 @@
       <c r="D81" s="21">
         <v>63</v>
       </c>
-      <c r="E81" s="24"/>
-      <c r="F81" s="54">
+      <c r="E81" s="51">
+        <v>64</v>
+      </c>
+      <c r="F81" s="48">
         <v>79</v>
       </c>
-      <c r="G81" s="27">
+      <c r="G81" s="24">
         <v>64</v>
       </c>
-      <c r="H81" s="52">
+      <c r="H81" s="46">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -4129,14 +4280,16 @@
       <c r="D82" s="21">
         <v>30</v>
       </c>
-      <c r="E82" s="24"/>
-      <c r="F82" s="54">
+      <c r="E82" s="51">
+        <v>27</v>
+      </c>
+      <c r="F82" s="48">
         <v>63</v>
       </c>
-      <c r="G82" s="27">
+      <c r="G82" s="24">
         <v>32</v>
       </c>
-      <c r="H82" s="52">
+      <c r="H82" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4153,14 +4306,16 @@
       <c r="D83" s="21">
         <v>85</v>
       </c>
-      <c r="E83" s="24"/>
-      <c r="F83" s="54">
+      <c r="E83" s="51">
+        <v>42</v>
+      </c>
+      <c r="F83" s="48">
         <v>32</v>
       </c>
-      <c r="G83" s="29">
+      <c r="G83" s="26">
         <v>57</v>
       </c>
-      <c r="H83" s="52">
+      <c r="H83" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4177,14 +4332,16 @@
       <c r="D84" s="20">
         <v>34</v>
       </c>
-      <c r="E84" s="24"/>
-      <c r="F84" s="54">
+      <c r="E84" s="51">
+        <v>24</v>
+      </c>
+      <c r="F84" s="48">
         <v>56</v>
       </c>
-      <c r="G84" s="27">
+      <c r="G84" s="24">
         <v>44</v>
       </c>
-      <c r="H84" s="52">
+      <c r="H84" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4201,14 +4358,16 @@
       <c r="D85" s="20">
         <v>67</v>
       </c>
-      <c r="E85" s="22"/>
-      <c r="F85" s="55">
+      <c r="E85" s="49">
+        <v>45</v>
+      </c>
+      <c r="F85" s="49">
         <v>51</v>
       </c>
-      <c r="G85" s="28">
+      <c r="G85" s="25">
         <v>58</v>
       </c>
-      <c r="H85" s="52">
+      <c r="H85" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4225,14 +4384,16 @@
       <c r="D86" s="21">
         <v>49</v>
       </c>
-      <c r="E86" s="24"/>
-      <c r="F86" s="54">
+      <c r="E86" s="51">
+        <v>24</v>
+      </c>
+      <c r="F86" s="48">
         <v>35</v>
       </c>
-      <c r="G86" s="27">
+      <c r="G86" s="24">
         <v>64</v>
       </c>
-      <c r="H86" s="52">
+      <c r="H86" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4249,14 +4410,16 @@
       <c r="D87" s="21">
         <v>58</v>
       </c>
-      <c r="E87" s="24"/>
-      <c r="F87" s="54">
+      <c r="E87" s="51">
+        <v>34</v>
+      </c>
+      <c r="F87" s="48">
         <v>41</v>
       </c>
-      <c r="G87" s="27">
+      <c r="G87" s="24">
         <v>58</v>
       </c>
-      <c r="H87" s="52">
+      <c r="H87" s="46">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -4273,14 +4436,16 @@
       <c r="D88" s="21">
         <v>47</v>
       </c>
-      <c r="E88" s="24"/>
-      <c r="F88" s="54">
+      <c r="E88" s="51">
+        <v>41</v>
+      </c>
+      <c r="F88" s="48">
         <v>78</v>
       </c>
-      <c r="G88" s="27">
+      <c r="G88" s="24">
         <v>81</v>
       </c>
-      <c r="H88" s="52">
+      <c r="H88" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4297,14 +4462,16 @@
       <c r="D89" s="21">
         <v>58</v>
       </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="54">
+      <c r="E89" s="51">
+        <v>61</v>
+      </c>
+      <c r="F89" s="48">
         <v>54</v>
       </c>
-      <c r="G89" s="27">
+      <c r="G89" s="24">
         <v>75</v>
       </c>
-      <c r="H89" s="52">
+      <c r="H89" s="46">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4321,14 +4488,16 @@
       <c r="D90" s="21">
         <v>84</v>
       </c>
-      <c r="E90" s="24"/>
-      <c r="F90" s="54">
+      <c r="E90" s="51">
+        <v>48</v>
+      </c>
+      <c r="F90" s="48">
         <v>66</v>
       </c>
-      <c r="G90" s="29">
+      <c r="G90" s="26">
         <v>54</v>
       </c>
-      <c r="H90" s="52">
+      <c r="H90" s="46">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -4345,14 +4514,16 @@
       <c r="D91" s="20">
         <v>66</v>
       </c>
-      <c r="E91" s="24"/>
-      <c r="F91" s="54">
+      <c r="E91" s="51">
+        <v>48</v>
+      </c>
+      <c r="F91" s="48">
         <v>51</v>
       </c>
-      <c r="G91" s="27">
+      <c r="G91" s="24">
         <v>58</v>
       </c>
-      <c r="H91" s="52">
+      <c r="H91" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4369,14 +4540,16 @@
       <c r="D92" s="20">
         <v>48</v>
       </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="54">
+      <c r="E92" s="51">
+        <v>33</v>
+      </c>
+      <c r="F92" s="48">
         <v>64</v>
       </c>
-      <c r="G92" s="27">
+      <c r="G92" s="24">
         <v>40</v>
       </c>
-      <c r="H92" s="52">
+      <c r="H92" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4393,14 +4566,16 @@
       <c r="D93" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="54">
+      <c r="E93" s="51">
+        <v>70</v>
+      </c>
+      <c r="F93" s="48">
         <v>66</v>
       </c>
-      <c r="G93" s="27">
+      <c r="G93" s="24">
         <v>46</v>
       </c>
-      <c r="H93" s="52">
+      <c r="H93" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -4417,14 +4592,16 @@
       <c r="D94" s="20">
         <v>55</v>
       </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="54">
+      <c r="E94" s="51">
+        <v>29</v>
+      </c>
+      <c r="F94" s="48">
         <v>63</v>
       </c>
-      <c r="G94" s="27">
+      <c r="G94" s="24">
         <v>41</v>
       </c>
-      <c r="H94" s="52">
+      <c r="H94" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -4441,14 +4618,16 @@
       <c r="D95" s="21">
         <v>87</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="54">
+      <c r="E95" s="51">
+        <v>65</v>
+      </c>
+      <c r="F95" s="48">
         <v>75</v>
       </c>
-      <c r="G95" s="27">
+      <c r="G95" s="24">
         <v>84</v>
       </c>
-      <c r="H95" s="52">
+      <c r="H95" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4465,14 +4644,16 @@
       <c r="D96" s="21">
         <v>79</v>
       </c>
-      <c r="E96" s="22"/>
-      <c r="F96" s="55">
+      <c r="E96" s="49">
+        <v>31</v>
+      </c>
+      <c r="F96" s="49">
         <v>57</v>
       </c>
-      <c r="G96" s="28">
+      <c r="G96" s="25">
         <v>75</v>
       </c>
-      <c r="H96" s="52">
+      <c r="H96" s="46">
         <v>65.217391300000003</v>
       </c>
     </row>
@@ -4489,14 +4670,16 @@
       <c r="D97" s="21">
         <v>63</v>
       </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="54">
+      <c r="E97" s="51">
+        <v>27</v>
+      </c>
+      <c r="F97" s="48">
         <v>44</v>
       </c>
-      <c r="G97" s="27">
+      <c r="G97" s="24">
         <v>46</v>
       </c>
-      <c r="H97" s="52">
+      <c r="H97" s="46">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -4510,17 +4693,19 @@
       <c r="C98" s="20">
         <v>13</v>
       </c>
-      <c r="D98" s="30">
+      <c r="D98" s="27">
         <v>52</v>
       </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="54">
+      <c r="E98" s="51">
+        <v>44</v>
+      </c>
+      <c r="F98" s="48">
         <v>67</v>
       </c>
-      <c r="G98" s="27">
+      <c r="G98" s="24">
         <v>61</v>
       </c>
-      <c r="H98" s="52">
+      <c r="H98" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4534,17 +4719,19 @@
       <c r="C99" s="20">
         <v>60</v>
       </c>
-      <c r="D99" s="30">
+      <c r="D99" s="27">
         <v>83</v>
       </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="54">
+      <c r="E99" s="51">
+        <v>62</v>
+      </c>
+      <c r="F99" s="48">
         <v>79</v>
       </c>
-      <c r="G99" s="29">
+      <c r="G99" s="26">
         <v>75</v>
       </c>
-      <c r="H99" s="52">
+      <c r="H99" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4558,17 +4745,19 @@
       <c r="C100" s="20">
         <v>42</v>
       </c>
-      <c r="D100" s="30">
+      <c r="D100" s="27">
         <v>48</v>
       </c>
-      <c r="E100" s="24"/>
-      <c r="F100" s="54">
+      <c r="E100" s="51">
+        <v>49</v>
+      </c>
+      <c r="F100" s="48">
         <v>74</v>
       </c>
-      <c r="G100" s="27">
+      <c r="G100" s="24">
         <v>50</v>
       </c>
-      <c r="H100" s="52">
+      <c r="H100" s="46">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -4582,17 +4771,19 @@
       <c r="C101" s="20">
         <v>52</v>
       </c>
-      <c r="D101" s="30">
+      <c r="D101" s="27">
         <v>79</v>
       </c>
-      <c r="E101" s="24"/>
-      <c r="F101" s="54">
+      <c r="E101" s="51">
+        <v>50</v>
+      </c>
+      <c r="F101" s="48">
         <v>61</v>
       </c>
-      <c r="G101" s="27">
+      <c r="G101" s="24">
         <v>47</v>
       </c>
-      <c r="H101" s="52">
+      <c r="H101" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4609,14 +4800,16 @@
       <c r="D102" s="20">
         <v>85</v>
       </c>
-      <c r="E102" s="24"/>
-      <c r="F102" s="54">
+      <c r="E102" s="51">
+        <v>42</v>
+      </c>
+      <c r="F102" s="48">
         <v>76</v>
       </c>
-      <c r="G102" s="27">
+      <c r="G102" s="24">
         <v>76</v>
       </c>
-      <c r="H102" s="52">
+      <c r="H102" s="46">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -4630,17 +4823,19 @@
       <c r="C103" s="20">
         <v>28</v>
       </c>
-      <c r="D103" s="30">
+      <c r="D103" s="27">
         <v>41</v>
       </c>
-      <c r="E103" s="24"/>
-      <c r="F103" s="54">
+      <c r="E103" s="51">
+        <v>20</v>
+      </c>
+      <c r="F103" s="48">
         <v>53</v>
       </c>
-      <c r="G103" s="27">
+      <c r="G103" s="24">
         <v>51</v>
       </c>
-      <c r="H103" s="52">
+      <c r="H103" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4654,17 +4849,19 @@
       <c r="C104" s="20">
         <v>27</v>
       </c>
-      <c r="D104" s="30">
+      <c r="D104" s="27">
         <v>74</v>
       </c>
-      <c r="E104" s="24"/>
-      <c r="F104" s="54">
+      <c r="E104" s="51">
         <v>67</v>
       </c>
-      <c r="G104" s="27">
+      <c r="F104" s="48">
+        <v>67</v>
+      </c>
+      <c r="G104" s="24">
         <v>69</v>
       </c>
-      <c r="H104" s="52">
+      <c r="H104" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4678,17 +4875,19 @@
       <c r="C105" s="20">
         <v>36</v>
       </c>
-      <c r="D105" s="30">
+      <c r="D105" s="27">
         <v>60</v>
       </c>
-      <c r="E105" s="24"/>
-      <c r="F105" s="54">
+      <c r="E105" s="51">
+        <v>57</v>
+      </c>
+      <c r="F105" s="48">
         <v>66</v>
       </c>
-      <c r="G105" s="27">
+      <c r="G105" s="24">
         <v>72</v>
       </c>
-      <c r="H105" s="52">
+      <c r="H105" s="46">
         <v>100</v>
       </c>
     </row>
@@ -4702,17 +4901,19 @@
       <c r="C106" s="20">
         <v>19</v>
       </c>
-      <c r="D106" s="30">
+      <c r="D106" s="27">
         <v>43</v>
       </c>
-      <c r="E106" s="24"/>
-      <c r="F106" s="54">
+      <c r="E106" s="51">
+        <v>35</v>
+      </c>
+      <c r="F106" s="48">
         <v>55</v>
       </c>
-      <c r="G106" s="27">
+      <c r="G106" s="24">
         <v>9</v>
       </c>
-      <c r="H106" s="52">
+      <c r="H106" s="46">
         <v>100</v>
       </c>
     </row>
@@ -4726,17 +4927,19 @@
       <c r="C107" s="20">
         <v>54</v>
       </c>
-      <c r="D107" s="30">
+      <c r="D107" s="27">
         <v>47</v>
       </c>
-      <c r="E107" s="24"/>
-      <c r="F107" s="54">
+      <c r="E107" s="51">
+        <v>34</v>
+      </c>
+      <c r="F107" s="48">
         <v>64</v>
       </c>
-      <c r="G107" s="27">
+      <c r="G107" s="24">
         <v>49</v>
       </c>
-      <c r="H107" s="52">
+      <c r="H107" s="46">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4750,17 +4953,19 @@
       <c r="C108" s="20">
         <v>46</v>
       </c>
-      <c r="D108" s="30">
+      <c r="D108" s="27">
         <v>12</v>
       </c>
-      <c r="E108" s="24"/>
-      <c r="F108" s="54">
+      <c r="E108" s="51">
+        <v>41</v>
+      </c>
+      <c r="F108" s="48">
         <v>79</v>
       </c>
-      <c r="G108" s="27">
+      <c r="G108" s="24">
         <v>56</v>
       </c>
-      <c r="H108" s="52">
+      <c r="H108" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4777,14 +4982,16 @@
       <c r="D109" s="20">
         <v>35</v>
       </c>
-      <c r="E109" s="24"/>
-      <c r="F109" s="54">
+      <c r="E109" s="51">
+        <v>50</v>
+      </c>
+      <c r="F109" s="48">
         <v>58</v>
       </c>
-      <c r="G109" s="27">
+      <c r="G109" s="24">
         <v>62</v>
       </c>
-      <c r="H109" s="52">
+      <c r="H109" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4801,14 +5008,16 @@
       <c r="D110" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="E110" s="24"/>
-      <c r="F110" s="54">
+      <c r="E110" s="51">
+        <v>51</v>
+      </c>
+      <c r="F110" s="48">
         <v>65</v>
       </c>
-      <c r="G110" s="27">
+      <c r="G110" s="24">
         <v>60</v>
       </c>
-      <c r="H110" s="52">
+      <c r="H110" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -4825,14 +5034,16 @@
       <c r="D111" s="20">
         <v>12</v>
       </c>
-      <c r="E111" s="24"/>
-      <c r="F111" s="54">
+      <c r="E111" s="51" t="s">
+        <v>382</v>
+      </c>
+      <c r="F111" s="48">
         <v>42</v>
       </c>
-      <c r="G111" s="27">
+      <c r="G111" s="24">
         <v>11</v>
       </c>
-      <c r="H111" s="52">
+      <c r="H111" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4846,17 +5057,19 @@
       <c r="C112" s="20">
         <v>71</v>
       </c>
-      <c r="D112" s="30">
+      <c r="D112" s="27">
         <v>85</v>
       </c>
-      <c r="E112" s="24"/>
-      <c r="F112" s="54">
+      <c r="E112" s="51">
+        <v>44</v>
+      </c>
+      <c r="F112" s="48">
         <v>75</v>
       </c>
-      <c r="G112" s="27">
+      <c r="G112" s="24">
         <v>70</v>
       </c>
-      <c r="H112" s="52">
+      <c r="H112" s="46">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4870,17 +5083,19 @@
       <c r="C113" s="20">
         <v>29</v>
       </c>
-      <c r="D113" s="30">
+      <c r="D113" s="27">
         <v>19</v>
       </c>
-      <c r="E113" s="24"/>
-      <c r="F113" s="54">
+      <c r="E113" s="51">
+        <v>24</v>
+      </c>
+      <c r="F113" s="48">
         <v>73</v>
       </c>
-      <c r="G113" s="27">
+      <c r="G113" s="24">
         <v>50</v>
       </c>
-      <c r="H113" s="52">
+      <c r="H113" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -4897,14 +5112,16 @@
       <c r="D114" s="20">
         <v>75</v>
       </c>
-      <c r="E114" s="24"/>
-      <c r="F114" s="54">
+      <c r="E114" s="51">
+        <v>64</v>
+      </c>
+      <c r="F114" s="48">
         <v>62</v>
       </c>
-      <c r="G114" s="27">
+      <c r="G114" s="24">
         <v>63</v>
       </c>
-      <c r="H114" s="52">
+      <c r="H114" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4921,14 +5138,16 @@
       <c r="D115" s="20">
         <v>79</v>
       </c>
-      <c r="E115" s="24"/>
-      <c r="F115" s="54">
+      <c r="E115" s="51">
+        <v>72</v>
+      </c>
+      <c r="F115" s="48">
         <v>71</v>
       </c>
-      <c r="G115" s="27">
+      <c r="G115" s="24">
         <v>67</v>
       </c>
-      <c r="H115" s="52">
+      <c r="H115" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4942,17 +5161,19 @@
       <c r="C116" s="20">
         <v>53</v>
       </c>
-      <c r="D116" s="30">
+      <c r="D116" s="27">
         <v>47</v>
       </c>
-      <c r="E116" s="24"/>
-      <c r="F116" s="54">
+      <c r="E116" s="51">
+        <v>78</v>
+      </c>
+      <c r="F116" s="48">
         <v>66</v>
       </c>
-      <c r="G116" s="27">
+      <c r="G116" s="24">
         <v>72</v>
       </c>
-      <c r="H116" s="52">
+      <c r="H116" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4966,17 +5187,19 @@
       <c r="C117" s="20">
         <v>44</v>
       </c>
-      <c r="D117" s="30">
+      <c r="D117" s="27">
         <v>60</v>
       </c>
-      <c r="E117" s="24"/>
-      <c r="F117" s="54">
+      <c r="E117" s="51">
+        <v>39</v>
+      </c>
+      <c r="F117" s="48">
         <v>61</v>
       </c>
-      <c r="G117" s="27">
+      <c r="G117" s="24">
         <v>28</v>
       </c>
-      <c r="H117" s="52">
+      <c r="H117" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4993,14 +5216,16 @@
       <c r="D118" s="20">
         <v>57</v>
       </c>
-      <c r="E118" s="24"/>
-      <c r="F118" s="54">
+      <c r="E118" s="51">
+        <v>62</v>
+      </c>
+      <c r="F118" s="48">
         <v>39</v>
       </c>
-      <c r="G118" s="27">
+      <c r="G118" s="24">
         <v>54</v>
       </c>
-      <c r="H118" s="52">
+      <c r="H118" s="46">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -5017,14 +5242,16 @@
       <c r="D119" s="20">
         <v>52</v>
       </c>
-      <c r="E119" s="24"/>
-      <c r="F119" s="54">
+      <c r="E119" s="51">
+        <v>92</v>
+      </c>
+      <c r="F119" s="48">
         <v>73</v>
       </c>
-      <c r="G119" s="27">
+      <c r="G119" s="24">
         <v>76</v>
       </c>
-      <c r="H119" s="52">
+      <c r="H119" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5038,17 +5265,19 @@
       <c r="C120" s="20">
         <v>17</v>
       </c>
-      <c r="D120" s="30">
+      <c r="D120" s="27">
         <v>31</v>
       </c>
-      <c r="E120" s="24"/>
-      <c r="F120" s="54">
+      <c r="E120" s="51">
+        <v>82</v>
+      </c>
+      <c r="F120" s="48">
         <v>70</v>
       </c>
-      <c r="G120" s="27">
+      <c r="G120" s="24">
         <v>52</v>
       </c>
-      <c r="H120" s="52">
+      <c r="H120" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5065,14 +5294,16 @@
       <c r="D121" s="20">
         <v>16</v>
       </c>
-      <c r="E121" s="24"/>
-      <c r="F121" s="54">
+      <c r="E121" s="51">
+        <v>32</v>
+      </c>
+      <c r="F121" s="48">
         <v>67</v>
       </c>
-      <c r="G121" s="27">
+      <c r="G121" s="24">
         <v>59</v>
       </c>
-      <c r="H121" s="52">
+      <c r="H121" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5089,14 +5320,16 @@
       <c r="D122" s="20">
         <v>36</v>
       </c>
-      <c r="E122" s="24"/>
-      <c r="F122" s="54">
+      <c r="E122" s="51">
+        <v>31</v>
+      </c>
+      <c r="F122" s="48">
         <v>53</v>
       </c>
-      <c r="G122" s="27">
+      <c r="G122" s="24">
         <v>32</v>
       </c>
-      <c r="H122" s="52">
+      <c r="H122" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5110,17 +5343,19 @@
       <c r="C123" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="D123" s="30" t="s">
+      <c r="D123" s="27" t="s">
         <v>382</v>
       </c>
-      <c r="E123" s="24"/>
-      <c r="F123" s="54" t="s">
+      <c r="E123" s="51" t="s">
         <v>382</v>
       </c>
-      <c r="G123" s="27" t="s">
+      <c r="F123" s="48" t="s">
         <v>382</v>
       </c>
-      <c r="H123" s="52">
+      <c r="G123" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="H123" s="46">
         <v>0</v>
       </c>
     </row>
@@ -5137,14 +5372,16 @@
       <c r="D124" s="20">
         <v>72</v>
       </c>
-      <c r="E124" s="24"/>
-      <c r="F124" s="54">
+      <c r="E124" s="51">
+        <v>64</v>
+      </c>
+      <c r="F124" s="48">
         <v>66</v>
       </c>
-      <c r="G124" s="27">
+      <c r="G124" s="24">
         <v>60</v>
       </c>
-      <c r="H124" s="52">
+      <c r="H124" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5158,17 +5395,19 @@
       <c r="C125" s="20">
         <v>28</v>
       </c>
-      <c r="D125" s="30">
+      <c r="D125" s="27">
         <v>41</v>
       </c>
-      <c r="E125" s="24"/>
-      <c r="F125" s="54">
+      <c r="E125" s="51">
+        <v>50</v>
+      </c>
+      <c r="F125" s="48">
         <v>79</v>
       </c>
-      <c r="G125" s="27">
+      <c r="G125" s="24">
         <v>55</v>
       </c>
-      <c r="H125" s="52">
+      <c r="H125" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5185,14 +5424,16 @@
       <c r="D126" s="20">
         <v>53</v>
       </c>
-      <c r="E126" s="24"/>
-      <c r="F126" s="54">
+      <c r="E126" s="51">
+        <v>88</v>
+      </c>
+      <c r="F126" s="48">
         <v>80</v>
       </c>
-      <c r="G126" s="27">
+      <c r="G126" s="24">
         <v>68</v>
       </c>
-      <c r="H126" s="52">
+      <c r="H126" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5206,17 +5447,19 @@
       <c r="C127" s="20">
         <v>54</v>
       </c>
-      <c r="D127" s="30">
+      <c r="D127" s="27">
         <v>32</v>
       </c>
-      <c r="E127" s="24"/>
-      <c r="F127" s="54">
+      <c r="E127" s="51">
+        <v>51</v>
+      </c>
+      <c r="F127" s="48">
         <v>61</v>
       </c>
-      <c r="G127" s="27">
+      <c r="G127" s="24">
         <v>68</v>
       </c>
-      <c r="H127" s="52">
+      <c r="H127" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5230,17 +5473,19 @@
       <c r="C128" s="20">
         <v>21</v>
       </c>
-      <c r="D128" s="30">
+      <c r="D128" s="27">
         <v>56</v>
       </c>
-      <c r="E128" s="24"/>
-      <c r="F128" s="54">
+      <c r="E128" s="51">
+        <v>38</v>
+      </c>
+      <c r="F128" s="48">
         <v>51</v>
       </c>
-      <c r="G128" s="27">
+      <c r="G128" s="24">
         <v>48</v>
       </c>
-      <c r="H128" s="52">
+      <c r="H128" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5254,17 +5499,19 @@
       <c r="C129" s="20">
         <v>26</v>
       </c>
-      <c r="D129" s="30">
+      <c r="D129" s="27">
         <v>49</v>
       </c>
-      <c r="E129" s="24"/>
-      <c r="F129" s="54">
+      <c r="E129" s="51">
+        <v>4</v>
+      </c>
+      <c r="F129" s="48">
         <v>46</v>
       </c>
-      <c r="G129" s="27">
+      <c r="G129" s="24">
         <v>50</v>
       </c>
-      <c r="H129" s="52">
+      <c r="H129" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5278,17 +5525,19 @@
       <c r="C130" s="20">
         <v>15</v>
       </c>
-      <c r="D130" s="30">
+      <c r="D130" s="27">
         <v>26</v>
       </c>
-      <c r="E130" s="24"/>
-      <c r="F130" s="54">
+      <c r="E130" s="51">
+        <v>37</v>
+      </c>
+      <c r="F130" s="48">
         <v>64</v>
       </c>
-      <c r="G130" s="27">
+      <c r="G130" s="24">
         <v>22</v>
       </c>
-      <c r="H130" s="52">
+      <c r="H130" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5302,17 +5551,19 @@
       <c r="C131" s="20">
         <v>51</v>
       </c>
-      <c r="D131" s="30">
+      <c r="D131" s="27">
         <v>23</v>
       </c>
-      <c r="E131" s="24"/>
-      <c r="F131" s="54">
+      <c r="E131" s="51">
+        <v>37</v>
+      </c>
+      <c r="F131" s="48">
         <v>64</v>
       </c>
-      <c r="G131" s="27">
+      <c r="G131" s="24">
         <v>63</v>
       </c>
-      <c r="H131" s="52">
+      <c r="H131" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5326,17 +5577,19 @@
       <c r="C132" s="20">
         <v>50</v>
       </c>
-      <c r="D132" s="30">
+      <c r="D132" s="27">
         <v>81</v>
       </c>
-      <c r="E132" s="22"/>
-      <c r="F132" s="55">
+      <c r="E132" s="49">
+        <v>14</v>
+      </c>
+      <c r="F132" s="49">
         <v>70</v>
       </c>
-      <c r="G132" s="28">
+      <c r="G132" s="25">
         <v>66</v>
       </c>
-      <c r="H132" s="52">
+      <c r="H132" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5350,17 +5603,19 @@
       <c r="C133" s="20">
         <v>18</v>
       </c>
-      <c r="D133" s="30">
+      <c r="D133" s="27">
         <v>13</v>
       </c>
-      <c r="E133" s="24"/>
-      <c r="F133" s="54">
+      <c r="E133" s="51">
+        <v>42</v>
+      </c>
+      <c r="F133" s="48">
         <v>63</v>
       </c>
-      <c r="G133" s="27">
+      <c r="G133" s="24">
         <v>23</v>
       </c>
-      <c r="H133" s="52">
+      <c r="H133" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5374,17 +5629,19 @@
       <c r="C134" s="20">
         <v>53</v>
       </c>
-      <c r="D134" s="30">
+      <c r="D134" s="27">
         <v>49</v>
       </c>
-      <c r="E134" s="24"/>
-      <c r="F134" s="54">
+      <c r="E134" s="51">
+        <v>66</v>
+      </c>
+      <c r="F134" s="48">
         <v>81</v>
       </c>
-      <c r="G134" s="31">
+      <c r="G134" s="28">
         <v>65</v>
       </c>
-      <c r="H134" s="52">
+      <c r="H134" s="46">
         <v>100</v>
       </c>
     </row>
@@ -5398,17 +5655,19 @@
       <c r="C135" s="20">
         <v>8</v>
       </c>
-      <c r="D135" s="30">
+      <c r="D135" s="27">
         <v>42</v>
       </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="54">
+      <c r="E135" s="51">
+        <v>12</v>
+      </c>
+      <c r="F135" s="48">
         <v>71</v>
       </c>
-      <c r="G135" s="32">
+      <c r="G135" s="29">
         <v>45</v>
       </c>
-      <c r="H135" s="52">
+      <c r="H135" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5425,14 +5684,16 @@
       <c r="D136" s="20">
         <v>58</v>
       </c>
-      <c r="E136" s="24"/>
-      <c r="F136" s="54">
+      <c r="E136" s="51">
+        <v>21</v>
+      </c>
+      <c r="F136" s="48">
         <v>66</v>
       </c>
-      <c r="G136" s="25">
+      <c r="G136" s="23">
         <v>58</v>
       </c>
-      <c r="H136" s="52">
+      <c r="H136" s="46">
         <v>100</v>
       </c>
     </row>
@@ -5449,14 +5710,16 @@
       <c r="D137" s="20">
         <v>45</v>
       </c>
-      <c r="E137" s="22"/>
-      <c r="F137" s="55">
+      <c r="E137" s="49">
+        <v>26</v>
+      </c>
+      <c r="F137" s="49">
         <v>67</v>
       </c>
-      <c r="G137" s="28">
+      <c r="G137" s="25">
         <v>53</v>
       </c>
-      <c r="H137" s="52">
+      <c r="H137" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5473,14 +5736,16 @@
       <c r="D138" s="20">
         <v>29</v>
       </c>
-      <c r="E138" s="24"/>
-      <c r="F138" s="54">
+      <c r="E138" s="51">
+        <v>38</v>
+      </c>
+      <c r="F138" s="48">
         <v>58</v>
       </c>
-      <c r="G138" s="27">
+      <c r="G138" s="24">
         <v>64</v>
       </c>
-      <c r="H138" s="52">
+      <c r="H138" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5494,17 +5759,19 @@
       <c r="C139" s="20">
         <v>43</v>
       </c>
-      <c r="D139" s="30">
+      <c r="D139" s="27">
         <v>38</v>
       </c>
-      <c r="E139" s="24"/>
-      <c r="F139" s="54">
+      <c r="E139" s="51">
+        <v>37</v>
+      </c>
+      <c r="F139" s="48">
         <v>45</v>
       </c>
-      <c r="G139" s="27">
+      <c r="G139" s="24">
         <v>41</v>
       </c>
-      <c r="H139" s="52">
+      <c r="H139" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5521,14 +5788,16 @@
       <c r="D140" s="20">
         <v>66</v>
       </c>
-      <c r="E140" s="24"/>
-      <c r="F140" s="54">
+      <c r="E140" s="51">
+        <v>80</v>
+      </c>
+      <c r="F140" s="48">
         <v>71</v>
       </c>
-      <c r="G140" s="27">
+      <c r="G140" s="24">
         <v>70</v>
       </c>
-      <c r="H140" s="52">
+      <c r="H140" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5545,14 +5814,16 @@
       <c r="D141" s="20">
         <v>17</v>
       </c>
-      <c r="E141" s="24"/>
-      <c r="F141" s="54">
+      <c r="E141" s="51">
         <v>32</v>
       </c>
-      <c r="G141" s="27">
+      <c r="F141" s="48">
+        <v>32</v>
+      </c>
+      <c r="G141" s="24">
         <v>36</v>
       </c>
-      <c r="H141" s="52">
+      <c r="H141" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5569,14 +5840,16 @@
       <c r="D142" s="20">
         <v>45</v>
       </c>
-      <c r="E142" s="24"/>
-      <c r="F142" s="54">
+      <c r="E142" s="51">
+        <v>67</v>
+      </c>
+      <c r="F142" s="48">
         <v>61</v>
       </c>
-      <c r="G142" s="27">
+      <c r="G142" s="24">
         <v>65</v>
       </c>
-      <c r="H142" s="52">
+      <c r="H142" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5590,17 +5863,19 @@
       <c r="C143" s="20">
         <v>67</v>
       </c>
-      <c r="D143" s="30">
+      <c r="D143" s="27">
         <v>89</v>
       </c>
-      <c r="E143" s="24"/>
-      <c r="F143" s="54">
+      <c r="E143" s="51">
+        <v>91</v>
+      </c>
+      <c r="F143" s="48">
         <v>65</v>
       </c>
-      <c r="G143" s="27">
+      <c r="G143" s="24">
         <v>72</v>
       </c>
-      <c r="H143" s="52">
+      <c r="H143" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5614,17 +5889,19 @@
       <c r="C144" s="20">
         <v>61</v>
       </c>
-      <c r="D144" s="30">
+      <c r="D144" s="27">
         <v>76</v>
       </c>
-      <c r="E144" s="24"/>
-      <c r="F144" s="54">
+      <c r="E144" s="51">
+        <v>32</v>
+      </c>
+      <c r="F144" s="48">
         <v>79</v>
       </c>
-      <c r="G144" s="27">
+      <c r="G144" s="24">
         <v>59</v>
       </c>
-      <c r="H144" s="52">
+      <c r="H144" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5638,17 +5915,19 @@
       <c r="C145" s="20">
         <v>71</v>
       </c>
-      <c r="D145" s="30">
+      <c r="D145" s="27">
         <v>76</v>
       </c>
-      <c r="E145" s="24"/>
-      <c r="F145" s="54">
+      <c r="E145" s="51">
+        <v>71</v>
+      </c>
+      <c r="F145" s="48">
         <v>63</v>
       </c>
-      <c r="G145" s="27">
+      <c r="G145" s="24">
         <v>68</v>
       </c>
-      <c r="H145" s="52">
+      <c r="H145" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5662,17 +5941,19 @@
       <c r="C146" s="20">
         <v>96</v>
       </c>
-      <c r="D146" s="30">
+      <c r="D146" s="27">
         <v>86</v>
       </c>
-      <c r="E146" s="24"/>
-      <c r="F146" s="54">
+      <c r="E146" s="51">
+        <v>60</v>
+      </c>
+      <c r="F146" s="48">
         <v>74</v>
       </c>
-      <c r="G146" s="27">
+      <c r="G146" s="24">
         <v>66</v>
       </c>
-      <c r="H146" s="52">
+      <c r="H146" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5689,14 +5970,16 @@
       <c r="D147" s="20">
         <v>28</v>
       </c>
-      <c r="E147" s="24"/>
-      <c r="F147" s="54">
+      <c r="E147" s="51">
+        <v>40</v>
+      </c>
+      <c r="F147" s="48">
         <v>57</v>
       </c>
-      <c r="G147" s="27">
+      <c r="G147" s="24">
         <v>12</v>
       </c>
-      <c r="H147" s="52">
+      <c r="H147" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5713,14 +5996,16 @@
       <c r="D148" s="20">
         <v>73</v>
       </c>
-      <c r="E148" s="24"/>
-      <c r="F148" s="54">
+      <c r="E148" s="51">
+        <v>38</v>
+      </c>
+      <c r="F148" s="48">
         <v>71</v>
       </c>
-      <c r="G148" s="27">
+      <c r="G148" s="24">
         <v>52</v>
       </c>
-      <c r="H148" s="52">
+      <c r="H148" s="46">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5734,17 +6019,19 @@
       <c r="C149" s="20">
         <v>67</v>
       </c>
-      <c r="D149" s="30">
+      <c r="D149" s="27">
         <v>52</v>
       </c>
-      <c r="E149" s="24"/>
-      <c r="F149" s="54">
+      <c r="E149" s="51">
+        <v>72</v>
+      </c>
+      <c r="F149" s="48">
         <v>69</v>
       </c>
-      <c r="G149" s="27">
+      <c r="G149" s="24">
         <v>28</v>
       </c>
-      <c r="H149" s="52">
+      <c r="H149" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5758,17 +6045,19 @@
       <c r="C150" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="D150" s="30">
+      <c r="D150" s="27">
         <v>48</v>
       </c>
-      <c r="E150" s="22"/>
+      <c r="E150" s="49">
+        <v>18</v>
+      </c>
       <c r="F150" s="20">
         <v>68</v>
       </c>
-      <c r="G150" s="28">
+      <c r="G150" s="25">
         <v>44</v>
       </c>
-      <c r="H150" s="52">
+      <c r="H150" s="46">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5785,14 +6074,16 @@
       <c r="D151" s="20">
         <v>43</v>
       </c>
-      <c r="E151" s="24"/>
-      <c r="F151" s="54">
+      <c r="E151" s="51">
+        <v>43</v>
+      </c>
+      <c r="F151" s="48">
         <v>73</v>
       </c>
-      <c r="G151" s="27">
+      <c r="G151" s="24">
         <v>64</v>
       </c>
-      <c r="H151" s="52">
+      <c r="H151" s="46">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5809,14 +6100,16 @@
       <c r="D152" s="20">
         <v>51</v>
       </c>
-      <c r="E152" s="24"/>
-      <c r="F152" s="54">
+      <c r="E152" s="51">
+        <v>27</v>
+      </c>
+      <c r="F152" s="48">
         <v>54</v>
       </c>
-      <c r="G152" s="27">
+      <c r="G152" s="24">
         <v>44</v>
       </c>
-      <c r="H152" s="52">
+      <c r="H152" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5830,17 +6123,19 @@
       <c r="C153" s="20">
         <v>78</v>
       </c>
-      <c r="D153" s="30">
+      <c r="D153" s="27">
         <v>46</v>
       </c>
-      <c r="E153" s="24"/>
-      <c r="F153" s="54">
+      <c r="E153" s="51">
+        <v>67</v>
+      </c>
+      <c r="F153" s="48">
         <v>77</v>
       </c>
-      <c r="G153" s="27">
+      <c r="G153" s="24">
         <v>59</v>
       </c>
-      <c r="H153" s="52">
+      <c r="H153" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5857,14 +6152,16 @@
       <c r="D154" s="21">
         <v>78</v>
       </c>
-      <c r="E154" s="24"/>
-      <c r="F154" s="54">
+      <c r="E154" s="51">
+        <v>67</v>
+      </c>
+      <c r="F154" s="48">
         <v>65</v>
       </c>
-      <c r="G154" s="27">
+      <c r="G154" s="24">
         <v>72</v>
       </c>
-      <c r="H154" s="52">
+      <c r="H154" s="46">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -5881,14 +6178,16 @@
       <c r="D155" s="21">
         <v>85</v>
       </c>
-      <c r="E155" s="24"/>
-      <c r="F155" s="54">
+      <c r="E155" s="51">
+        <v>56</v>
+      </c>
+      <c r="F155" s="48">
         <v>72</v>
       </c>
-      <c r="G155" s="27">
+      <c r="G155" s="24">
         <v>64</v>
       </c>
-      <c r="H155" s="52">
+      <c r="H155" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5905,14 +6204,16 @@
       <c r="D156" s="20">
         <v>89</v>
       </c>
-      <c r="E156" s="22"/>
+      <c r="E156" s="49">
+        <v>59</v>
+      </c>
       <c r="F156" s="20">
         <v>76</v>
       </c>
-      <c r="G156" s="28">
+      <c r="G156" s="25">
         <v>80</v>
       </c>
-      <c r="H156" s="52">
+      <c r="H156" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5929,14 +6230,16 @@
       <c r="D157" s="20">
         <v>89</v>
       </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="54">
+      <c r="E157" s="51">
+        <v>53</v>
+      </c>
+      <c r="F157" s="48">
         <v>72</v>
       </c>
-      <c r="G157" s="27">
+      <c r="G157" s="24">
         <v>67</v>
       </c>
-      <c r="H157" s="52">
+      <c r="H157" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5953,14 +6256,16 @@
       <c r="D158" s="20">
         <v>86</v>
       </c>
-      <c r="E158" s="24"/>
-      <c r="F158" s="54">
+      <c r="E158" s="51">
+        <v>67</v>
+      </c>
+      <c r="F158" s="48">
         <v>79</v>
       </c>
-      <c r="G158" s="27">
+      <c r="G158" s="24">
         <v>57</v>
       </c>
-      <c r="H158" s="52">
+      <c r="H158" s="46">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5977,14 +6282,16 @@
       <c r="D159" s="21">
         <v>56</v>
       </c>
-      <c r="E159" s="33"/>
-      <c r="F159" s="54">
+      <c r="E159" s="39">
+        <v>71</v>
+      </c>
+      <c r="F159" s="48">
         <v>62</v>
       </c>
-      <c r="G159" s="27">
+      <c r="G159" s="24">
         <v>70</v>
       </c>
-      <c r="H159" s="52">
+      <c r="H159" s="46">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -6001,14 +6308,16 @@
       <c r="D160" s="21">
         <v>76</v>
       </c>
-      <c r="E160" s="24"/>
-      <c r="F160" s="54">
+      <c r="E160" s="51" t="s">
+        <v>382</v>
+      </c>
+      <c r="F160" s="48">
         <v>52</v>
       </c>
-      <c r="G160" s="27">
+      <c r="G160" s="24">
         <v>70</v>
       </c>
-      <c r="H160" s="52">
+      <c r="H160" s="46">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -6025,14 +6334,16 @@
       <c r="D161" s="20">
         <v>34</v>
       </c>
-      <c r="E161" s="24"/>
-      <c r="F161" s="54">
+      <c r="E161" s="51">
+        <v>49</v>
+      </c>
+      <c r="F161" s="48">
         <v>58</v>
       </c>
-      <c r="G161" s="27">
+      <c r="G161" s="24">
         <v>57</v>
       </c>
-      <c r="H161" s="52">
+      <c r="H161" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6049,14 +6360,16 @@
       <c r="D162" s="21">
         <v>38</v>
       </c>
-      <c r="E162" s="24"/>
-      <c r="F162" s="54">
+      <c r="E162" s="51">
+        <v>57</v>
+      </c>
+      <c r="F162" s="48">
         <v>73</v>
       </c>
-      <c r="G162" s="27">
+      <c r="G162" s="24">
         <v>52</v>
       </c>
-      <c r="H162" s="52">
+      <c r="H162" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6073,14 +6386,16 @@
       <c r="D163" s="20">
         <v>55</v>
       </c>
-      <c r="E163" s="24"/>
-      <c r="F163" s="54">
+      <c r="E163" s="51">
+        <v>45</v>
+      </c>
+      <c r="F163" s="48">
         <v>69</v>
       </c>
-      <c r="G163" s="27">
+      <c r="G163" s="24">
         <v>42</v>
       </c>
-      <c r="H163" s="52">
+      <c r="H163" s="46">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -6097,14 +6412,16 @@
       <c r="D164" s="21">
         <v>63</v>
       </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="54">
+      <c r="E164" s="51">
+        <v>27</v>
+      </c>
+      <c r="F164" s="48">
         <v>60</v>
       </c>
-      <c r="G164" s="31">
+      <c r="G164" s="28">
         <v>49</v>
       </c>
-      <c r="H164" s="52">
+      <c r="H164" s="46">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -6121,14 +6438,16 @@
       <c r="D165" s="20">
         <v>74</v>
       </c>
-      <c r="E165" s="24"/>
-      <c r="F165" s="54">
+      <c r="E165" s="51" t="s">
+        <v>382</v>
+      </c>
+      <c r="F165" s="48">
         <v>51</v>
       </c>
-      <c r="G165" s="23">
+      <c r="G165" s="22">
         <v>61</v>
       </c>
-      <c r="H165" s="52">
+      <c r="H165" s="46">
         <v>65.217391300000003</v>
       </c>
     </row>
@@ -6145,14 +6464,16 @@
       <c r="D166" s="20">
         <v>44</v>
       </c>
-      <c r="E166" s="24"/>
-      <c r="F166" s="54">
+      <c r="E166" s="51" t="s">
+        <v>382</v>
+      </c>
+      <c r="F166" s="48">
         <v>65</v>
       </c>
-      <c r="G166" s="23">
+      <c r="G166" s="22">
         <v>47</v>
       </c>
-      <c r="H166" s="52">
+      <c r="H166" s="46">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -6169,14 +6490,16 @@
       <c r="D167" s="21">
         <v>69</v>
       </c>
-      <c r="E167" s="24"/>
-      <c r="F167" s="54">
+      <c r="E167" s="51">
+        <v>62</v>
+      </c>
+      <c r="F167" s="48">
         <v>66</v>
       </c>
-      <c r="G167" s="23">
+      <c r="G167" s="22">
         <v>65</v>
       </c>
-      <c r="H167" s="52">
+      <c r="H167" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6193,14 +6516,16 @@
       <c r="D168" s="20">
         <v>93</v>
       </c>
-      <c r="E168" s="24"/>
-      <c r="F168" s="54">
+      <c r="E168" s="51">
+        <v>39</v>
+      </c>
+      <c r="F168" s="48">
         <v>79</v>
       </c>
-      <c r="G168" s="23">
+      <c r="G168" s="22">
         <v>45</v>
       </c>
-      <c r="H168" s="52">
+      <c r="H168" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6217,14 +6542,16 @@
       <c r="D169" s="21">
         <v>55</v>
       </c>
-      <c r="E169" s="24"/>
-      <c r="F169" s="54">
+      <c r="E169" s="51">
+        <v>54</v>
+      </c>
+      <c r="F169" s="48">
         <v>75</v>
       </c>
-      <c r="G169" s="23">
+      <c r="G169" s="22">
         <v>69</v>
       </c>
-      <c r="H169" s="52">
+      <c r="H169" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -6241,14 +6568,16 @@
       <c r="D170" s="21">
         <v>25</v>
       </c>
-      <c r="E170" s="34"/>
-      <c r="F170" s="56">
+      <c r="E170" s="52">
+        <v>26</v>
+      </c>
+      <c r="F170" s="50">
         <v>51</v>
       </c>
-      <c r="G170" s="35">
+      <c r="G170" s="30">
         <v>33</v>
       </c>
-      <c r="H170" s="52">
+      <c r="H170" s="46">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -6265,14 +6594,16 @@
       <c r="D171" s="21">
         <v>50</v>
       </c>
-      <c r="E171" s="24"/>
-      <c r="F171" s="44">
+      <c r="E171" s="51">
+        <v>14</v>
+      </c>
+      <c r="F171" s="38">
         <v>53</v>
       </c>
-      <c r="G171" s="36">
+      <c r="G171" s="31">
         <v>46</v>
       </c>
-      <c r="H171" s="52">
+      <c r="H171" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -6289,14 +6620,16 @@
       <c r="D172" s="21">
         <v>58</v>
       </c>
-      <c r="E172" s="24"/>
-      <c r="F172" s="44">
+      <c r="E172" s="51">
+        <v>29</v>
+      </c>
+      <c r="F172" s="38">
         <v>62</v>
       </c>
-      <c r="G172" s="36">
+      <c r="G172" s="31">
         <v>26</v>
       </c>
-      <c r="H172" s="52">
+      <c r="H172" s="46">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -6313,14 +6646,16 @@
       <c r="D173" s="20">
         <v>65</v>
       </c>
-      <c r="E173" s="24"/>
-      <c r="F173" s="44">
+      <c r="E173" s="51">
+        <v>32</v>
+      </c>
+      <c r="F173" s="38">
         <v>69</v>
       </c>
-      <c r="G173" s="36">
+      <c r="G173" s="31">
         <v>50</v>
       </c>
-      <c r="H173" s="52">
+      <c r="H173" s="46">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -6337,14 +6672,16 @@
       <c r="D174" s="20">
         <v>22</v>
       </c>
-      <c r="E174" s="24"/>
-      <c r="F174" s="44">
+      <c r="E174" s="51">
+        <v>22</v>
+      </c>
+      <c r="F174" s="38">
         <v>54</v>
       </c>
-      <c r="G174" s="36">
+      <c r="G174" s="31">
         <v>51</v>
       </c>
-      <c r="H174" s="52">
+      <c r="H174" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6361,14 +6698,16 @@
       <c r="D175" s="21">
         <v>40</v>
       </c>
-      <c r="E175" s="24"/>
-      <c r="F175" s="44">
+      <c r="E175" s="51">
+        <v>34</v>
+      </c>
+      <c r="F175" s="38">
         <v>44</v>
       </c>
-      <c r="G175" s="36">
+      <c r="G175" s="31">
         <v>60</v>
       </c>
-      <c r="H175" s="52">
+      <c r="H175" s="46">
         <v>30.434782599999998</v>
       </c>
     </row>
@@ -6385,14 +6724,16 @@
       <c r="D176" s="20">
         <v>23</v>
       </c>
-      <c r="E176" s="24"/>
-      <c r="F176" s="44">
+      <c r="E176" s="51">
+        <v>19</v>
+      </c>
+      <c r="F176" s="38">
         <v>62</v>
       </c>
-      <c r="G176" s="36">
+      <c r="G176" s="31">
         <v>35</v>
       </c>
-      <c r="H176" s="52">
+      <c r="H176" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6409,14 +6750,16 @@
       <c r="D177" s="20">
         <v>81</v>
       </c>
-      <c r="E177" s="24"/>
-      <c r="F177" s="44">
+      <c r="E177" s="51">
+        <v>57</v>
+      </c>
+      <c r="F177" s="38">
         <v>73</v>
       </c>
-      <c r="G177" s="36">
+      <c r="G177" s="31">
         <v>54</v>
       </c>
-      <c r="H177" s="52">
+      <c r="H177" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6433,14 +6776,16 @@
       <c r="D178" s="20">
         <v>94</v>
       </c>
-      <c r="E178" s="24"/>
-      <c r="F178" s="44">
+      <c r="E178" s="51">
+        <v>49</v>
+      </c>
+      <c r="F178" s="38">
         <v>62</v>
       </c>
-      <c r="G178" s="36">
+      <c r="G178" s="31">
         <v>80</v>
       </c>
-      <c r="H178" s="52">
+      <c r="H178" s="46">
         <v>100</v>
       </c>
     </row>
@@ -6457,14 +6802,16 @@
       <c r="D179" s="20">
         <v>92</v>
       </c>
-      <c r="E179" s="24"/>
-      <c r="F179" s="44">
+      <c r="E179" s="51">
+        <v>92</v>
+      </c>
+      <c r="F179" s="38">
         <v>84</v>
       </c>
-      <c r="G179" s="36">
+      <c r="G179" s="31">
         <v>88</v>
       </c>
-      <c r="H179" s="52">
+      <c r="H179" s="46">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -6481,14 +6828,16 @@
       <c r="D180" s="20">
         <v>25</v>
       </c>
-      <c r="E180" s="24"/>
-      <c r="F180" s="44">
+      <c r="E180" s="51">
+        <v>12</v>
+      </c>
+      <c r="F180" s="38">
         <v>53</v>
       </c>
-      <c r="G180" s="36">
+      <c r="G180" s="31">
         <v>29</v>
       </c>
-      <c r="H180" s="52">
+      <c r="H180" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6505,14 +6854,16 @@
       <c r="D181" s="21">
         <v>70</v>
       </c>
-      <c r="E181" s="24"/>
-      <c r="F181" s="44">
+      <c r="E181" s="51">
+        <v>43</v>
+      </c>
+      <c r="F181" s="38">
         <v>50</v>
       </c>
-      <c r="G181" s="36">
+      <c r="G181" s="31">
         <v>63</v>
       </c>
-      <c r="H181" s="52">
+      <c r="H181" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6529,14 +6880,16 @@
       <c r="D182" s="21">
         <v>40</v>
       </c>
-      <c r="E182" s="37"/>
-      <c r="F182" s="44">
+      <c r="E182" s="27">
+        <v>37</v>
+      </c>
+      <c r="F182" s="38">
         <v>58</v>
       </c>
-      <c r="G182" s="36">
+      <c r="G182" s="31">
         <v>49</v>
       </c>
-      <c r="H182" s="52">
+      <c r="H182" s="46">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6553,14 +6906,16 @@
       <c r="D183" s="21">
         <v>66</v>
       </c>
-      <c r="E183" s="37"/>
-      <c r="F183" s="44">
+      <c r="E183" s="27">
+        <v>29</v>
+      </c>
+      <c r="F183" s="38">
         <v>73</v>
       </c>
-      <c r="G183" s="36">
+      <c r="G183" s="31">
         <v>59</v>
       </c>
-      <c r="H183" s="52">
+      <c r="H183" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6577,14 +6932,16 @@
       <c r="D184" s="21">
         <v>62</v>
       </c>
-      <c r="E184" s="24"/>
-      <c r="F184" s="44">
+      <c r="E184" s="51">
+        <v>31</v>
+      </c>
+      <c r="F184" s="38">
         <v>54</v>
       </c>
-      <c r="G184" s="36">
+      <c r="G184" s="31">
         <v>74</v>
       </c>
-      <c r="H184" s="52">
+      <c r="H184" s="46">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -6601,14 +6958,16 @@
       <c r="D185" s="21">
         <v>57</v>
       </c>
-      <c r="E185" s="24"/>
-      <c r="F185" s="44">
+      <c r="E185" s="51">
+        <v>61</v>
+      </c>
+      <c r="F185" s="38">
         <v>57</v>
       </c>
-      <c r="G185" s="36">
+      <c r="G185" s="31">
         <v>65</v>
       </c>
-      <c r="H185" s="52">
+      <c r="H185" s="46">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6625,14 +6984,16 @@
       <c r="D186" s="21">
         <v>44</v>
       </c>
-      <c r="E186" s="24"/>
-      <c r="F186" s="44">
+      <c r="E186" s="51">
+        <v>60</v>
+      </c>
+      <c r="F186" s="38">
         <v>71</v>
       </c>
-      <c r="G186" s="36">
+      <c r="G186" s="31">
         <v>69</v>
       </c>
-      <c r="H186" s="52">
+      <c r="H186" s="46">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -6649,16 +7010,16 @@
       <c r="D187" s="21">
         <v>32</v>
       </c>
-      <c r="E187" s="43">
+      <c r="E187" s="37">
         <v>57</v>
       </c>
-      <c r="F187" s="44">
+      <c r="F187" s="38">
         <v>63</v>
       </c>
-      <c r="G187" s="38">
+      <c r="G187" s="32">
         <v>47</v>
       </c>
-      <c r="H187" s="52">
+      <c r="H187" s="46">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -6675,16 +7036,16 @@
       <c r="D188" s="21">
         <v>24</v>
       </c>
-      <c r="E188" s="30">
+      <c r="E188" s="27">
         <v>39</v>
       </c>
-      <c r="F188" s="44">
+      <c r="F188" s="38">
         <v>54</v>
       </c>
-      <c r="G188" s="39">
+      <c r="G188" s="33">
         <v>29</v>
       </c>
-      <c r="H188" s="52">
+      <c r="H188" s="46">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -6701,13 +7062,13 @@
       <c r="D189" s="20">
         <v>56</v>
       </c>
-      <c r="E189" s="45">
+      <c r="E189" s="39">
         <v>14</v>
       </c>
-      <c r="F189" s="44">
+      <c r="F189" s="38">
         <v>58</v>
       </c>
-      <c r="G189" s="39">
+      <c r="G189" s="33">
         <v>60</v>
       </c>
       <c r="H189" s="13"/>
@@ -6725,10 +7086,10 @@
       <c r="D190" s="20">
         <v>72</v>
       </c>
-      <c r="E190" s="46">
+      <c r="E190" s="40">
         <v>65</v>
       </c>
-      <c r="F190" s="47">
+      <c r="F190" s="41">
         <v>71</v>
       </c>
       <c r="G190" s="20">
@@ -6749,10 +7110,10 @@
       <c r="D191" s="20">
         <v>69</v>
       </c>
-      <c r="E191" s="48">
+      <c r="E191" s="42">
         <v>65</v>
       </c>
-      <c r="F191" s="47">
+      <c r="F191" s="41">
         <v>54</v>
       </c>
       <c r="G191" s="21">
@@ -6776,7 +7137,7 @@
       <c r="E192" s="21">
         <v>33</v>
       </c>
-      <c r="F192" s="49" t="s">
+      <c r="F192" s="43" t="s">
         <v>382</v>
       </c>
       <c r="G192" s="21" t="s">
@@ -6797,10 +7158,10 @@
       <c r="D193" s="20">
         <v>54</v>
       </c>
-      <c r="E193" s="30">
+      <c r="E193" s="27">
         <v>10</v>
       </c>
-      <c r="F193" s="50">
+      <c r="F193" s="44">
         <v>47</v>
       </c>
       <c r="G193" s="21">
@@ -6821,10 +7182,10 @@
       <c r="D194" s="20">
         <v>31</v>
       </c>
-      <c r="E194" s="46" t="s">
+      <c r="E194" s="40" t="s">
         <v>382</v>
       </c>
-      <c r="F194" s="47">
+      <c r="F194" s="41">
         <v>41</v>
       </c>
       <c r="G194" s="21">
@@ -6845,10 +7206,10 @@
       <c r="D195" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="E195" s="51">
+      <c r="E195" s="45">
         <v>29</v>
       </c>
-      <c r="F195" s="49">
+      <c r="F195" s="43">
         <v>48</v>
       </c>
       <c r="G195" s="21" t="s">
@@ -6869,10 +7230,10 @@
       <c r="D196" s="21">
         <v>84</v>
       </c>
-      <c r="E196" s="48">
+      <c r="E196" s="42">
         <v>79</v>
       </c>
-      <c r="F196" s="50">
+      <c r="F196" s="44">
         <v>44</v>
       </c>
       <c r="G196" s="21">
@@ -6896,7 +7257,7 @@
       <c r="E197" s="21">
         <v>11</v>
       </c>
-      <c r="F197" s="50" t="s">
+      <c r="F197" s="44" t="s">
         <v>382</v>
       </c>
       <c r="G197" s="21" t="s">
@@ -6914,13 +7275,13 @@
       <c r="C198" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="D198" s="40" t="s">
+      <c r="D198" s="34" t="s">
         <v>382</v>
       </c>
       <c r="E198" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="F198" s="50" t="s">
+      <c r="F198" s="44" t="s">
         <v>382</v>
       </c>
       <c r="G198" s="21" t="s">
@@ -6935,19 +7296,19 @@
       <c r="B199" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="C199" s="41">
+      <c r="C199" s="35">
         <v>37</v>
       </c>
-      <c r="D199" s="41" t="s">
+      <c r="D199" s="35" t="s">
         <v>382</v>
       </c>
       <c r="E199" s="21">
         <v>7</v>
       </c>
-      <c r="F199" s="48">
+      <c r="F199" s="42">
         <v>13</v>
       </c>
-      <c r="G199" s="41">
+      <c r="G199" s="35">
         <v>37</v>
       </c>
       <c r="H199" s="13"/>
@@ -6962,7 +7323,7 @@
       <c r="C200" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="D200" s="42" t="s">
+      <c r="D200" s="36" t="s">
         <v>382</v>
       </c>
       <c r="E200" s="21" t="s">
@@ -6986,13 +7347,13 @@
       <c r="C201" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="D201" s="42" t="s">
+      <c r="D201" s="36" t="s">
         <v>382</v>
       </c>
       <c r="E201" s="21">
         <v>10</v>
       </c>
-      <c r="F201" s="52">
+      <c r="F201" s="46">
         <v>38</v>
       </c>
       <c r="G201" s="21">
@@ -7007,21 +7368,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -7165,8 +7511,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
@@ -7188,7 +7549,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
--- a/MC3020_E24.xlsx
+++ b/MC3020_E24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103E7DD9-33D6-4517-8636-AAE00F17CC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9DBB36-F5D5-4470-9EA1-7410A1F7B494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="409">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1814,9 +1814,6 @@
     <xf numFmtId="2" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1841,12 +1838,6 @@
     <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1860,6 +1851,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2155,8 +2155,9 @@
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
     <col min="3" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="53" customWidth="1"/>
-    <col min="6" max="7" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="50" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="53" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
     <col min="8" max="8" width="13.5703125" style="9" customWidth="1"/>
     <col min="10" max="10" width="12.28515625" customWidth="1"/>
   </cols>
@@ -2177,7 +2178,7 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="52" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
@@ -2200,16 +2201,16 @@
       <c r="D2" s="21">
         <v>54</v>
       </c>
-      <c r="E2" s="49">
+      <c r="E2" s="46">
         <v>45</v>
       </c>
-      <c r="F2" s="47">
+      <c r="F2" s="27">
         <v>51</v>
       </c>
       <c r="G2" s="22">
         <v>77</v>
       </c>
-      <c r="H2" s="46">
+      <c r="H2" s="45">
         <v>65.217391300000003</v>
       </c>
     </row>
@@ -2226,16 +2227,16 @@
       <c r="D3" s="21">
         <v>75</v>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="48">
         <v>99</v>
       </c>
-      <c r="F3" s="48">
+      <c r="F3" s="38">
         <v>77</v>
       </c>
       <c r="G3" s="23">
         <v>76</v>
       </c>
-      <c r="H3" s="46">
+      <c r="H3" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2252,16 +2253,16 @@
       <c r="D4" s="20">
         <v>71</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="39">
         <v>50</v>
       </c>
-      <c r="F4" s="48">
+      <c r="F4" s="38">
         <v>74</v>
       </c>
       <c r="G4" s="24">
         <v>57</v>
       </c>
-      <c r="H4" s="46">
+      <c r="H4" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2278,16 +2279,16 @@
       <c r="D5" s="20">
         <v>38</v>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="48">
         <v>21</v>
       </c>
-      <c r="F5" s="48">
+      <c r="F5" s="38">
         <v>65</v>
       </c>
       <c r="G5" s="24">
         <v>34</v>
       </c>
-      <c r="H5" s="46">
+      <c r="H5" s="45">
         <v>30.434782599999998</v>
       </c>
     </row>
@@ -2304,16 +2305,16 @@
       <c r="D6" s="20">
         <v>37</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="48">
         <v>40</v>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="38">
         <v>69</v>
       </c>
       <c r="G6" s="24">
         <v>48</v>
       </c>
-      <c r="H6" s="46">
+      <c r="H6" s="45">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -2330,16 +2331,16 @@
       <c r="D7" s="21">
         <v>34</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="48">
         <v>16</v>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="38">
         <v>68</v>
       </c>
       <c r="G7" s="24">
         <v>54</v>
       </c>
-      <c r="H7" s="46">
+      <c r="H7" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2356,16 +2357,16 @@
       <c r="D8" s="21">
         <v>83</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="48">
         <v>51</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="38">
         <v>72</v>
       </c>
       <c r="G8" s="24">
         <v>76</v>
       </c>
-      <c r="H8" s="46">
+      <c r="H8" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2382,16 +2383,16 @@
       <c r="D9" s="21">
         <v>68</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="48">
         <v>66</v>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="38">
         <v>58</v>
       </c>
       <c r="G9" s="24">
         <v>59</v>
       </c>
-      <c r="H9" s="46">
+      <c r="H9" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -2408,16 +2409,16 @@
       <c r="D10" s="20">
         <v>55</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="48">
         <v>47</v>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="38">
         <v>50</v>
       </c>
       <c r="G10" s="24">
         <v>61</v>
       </c>
-      <c r="H10" s="46">
+      <c r="H10" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2434,16 +2435,16 @@
       <c r="D11" s="21">
         <v>28</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="48">
         <v>45</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="38">
         <v>54</v>
       </c>
       <c r="G11" s="24">
         <v>24</v>
       </c>
-      <c r="H11" s="46">
+      <c r="H11" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2460,16 +2461,16 @@
       <c r="D12" s="20">
         <v>59</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="48">
         <v>76</v>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="38">
         <v>67</v>
       </c>
       <c r="G12" s="24">
         <v>60</v>
       </c>
-      <c r="H12" s="46">
+      <c r="H12" s="45">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -2486,16 +2487,16 @@
       <c r="D13" s="21">
         <v>43</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="48">
         <v>30</v>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="38">
         <v>63</v>
       </c>
       <c r="G13" s="24">
         <v>55</v>
       </c>
-      <c r="H13" s="46">
+      <c r="H13" s="45">
         <v>90.909090899999995</v>
       </c>
     </row>
@@ -2512,16 +2513,16 @@
       <c r="D14" s="20">
         <v>89</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="48">
         <v>88</v>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="38">
         <v>74</v>
       </c>
       <c r="G14" s="24">
         <v>76</v>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2538,16 +2539,16 @@
       <c r="D15" s="21">
         <v>42</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="48">
         <v>82</v>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="38">
         <v>85</v>
       </c>
       <c r="G15" s="24">
         <v>55</v>
       </c>
-      <c r="H15" s="46">
+      <c r="H15" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -2564,16 +2565,16 @@
       <c r="D16" s="20">
         <v>46</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="46">
         <v>57</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="46">
         <v>78</v>
       </c>
       <c r="G16" s="25">
         <v>56</v>
       </c>
-      <c r="H16" s="46">
+      <c r="H16" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2590,16 +2591,16 @@
       <c r="D17" s="21">
         <v>68</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="48">
         <v>78</v>
       </c>
-      <c r="F17" s="48">
+      <c r="F17" s="38">
         <v>73</v>
       </c>
       <c r="G17" s="24">
         <v>87</v>
       </c>
-      <c r="H17" s="46">
+      <c r="H17" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2616,16 +2617,16 @@
       <c r="D18" s="20">
         <v>54</v>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="48">
         <v>52</v>
       </c>
-      <c r="F18" s="48">
+      <c r="F18" s="38">
         <v>58</v>
       </c>
       <c r="G18" s="24">
         <v>75</v>
       </c>
-      <c r="H18" s="46">
+      <c r="H18" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -2642,16 +2643,16 @@
       <c r="D19" s="20">
         <v>94</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="48">
         <v>88</v>
       </c>
-      <c r="F19" s="48">
+      <c r="F19" s="38">
         <v>61</v>
       </c>
       <c r="G19" s="24">
         <v>83</v>
       </c>
-      <c r="H19" s="46">
+      <c r="H19" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -2668,16 +2669,16 @@
       <c r="D20" s="20">
         <v>78</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="48">
         <v>55</v>
       </c>
-      <c r="F20" s="48">
+      <c r="F20" s="38">
         <v>63</v>
       </c>
       <c r="G20" s="24">
         <v>63</v>
       </c>
-      <c r="H20" s="46">
+      <c r="H20" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2694,16 +2695,16 @@
       <c r="D21" s="20">
         <v>84</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="48">
         <v>71</v>
       </c>
-      <c r="F21" s="48">
+      <c r="F21" s="38">
         <v>81</v>
       </c>
       <c r="G21" s="24">
         <v>74</v>
       </c>
-      <c r="H21" s="46">
+      <c r="H21" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2720,16 +2721,16 @@
       <c r="D22" s="21">
         <v>51</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="48">
         <v>58</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="38">
         <v>78</v>
       </c>
       <c r="G22" s="24">
         <v>38</v>
       </c>
-      <c r="H22" s="46">
+      <c r="H22" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2746,16 +2747,16 @@
       <c r="D23" s="21">
         <v>87</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="48">
         <v>65</v>
       </c>
-      <c r="F23" s="48">
+      <c r="F23" s="38">
         <v>78</v>
       </c>
       <c r="G23" s="24">
         <v>76</v>
       </c>
-      <c r="H23" s="46">
+      <c r="H23" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2772,16 +2773,16 @@
       <c r="D24" s="21">
         <v>40</v>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="48">
         <v>48</v>
       </c>
-      <c r="F24" s="48">
+      <c r="F24" s="38">
         <v>71</v>
       </c>
       <c r="G24" s="24">
         <v>44</v>
       </c>
-      <c r="H24" s="46">
+      <c r="H24" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2792,22 +2793,22 @@
       <c r="B25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>382</v>
+      <c r="C25" s="20">
+        <v>100</v>
       </c>
       <c r="D25" s="21">
         <v>63</v>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="48">
         <v>92</v>
       </c>
-      <c r="F25" s="48">
+      <c r="F25" s="38">
         <v>67</v>
       </c>
       <c r="G25" s="24">
         <v>67</v>
       </c>
-      <c r="H25" s="46">
+      <c r="H25" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2824,16 +2825,16 @@
       <c r="D26" s="21">
         <v>73</v>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="48">
         <v>77</v>
       </c>
-      <c r="F26" s="48">
+      <c r="F26" s="38">
         <v>73</v>
       </c>
       <c r="G26" s="24">
         <v>71</v>
       </c>
-      <c r="H26" s="46">
+      <c r="H26" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -2850,16 +2851,16 @@
       <c r="D27" s="20">
         <v>72</v>
       </c>
-      <c r="E27" s="51">
+      <c r="E27" s="48">
         <v>81</v>
       </c>
-      <c r="F27" s="48">
+      <c r="F27" s="38">
         <v>64</v>
       </c>
       <c r="G27" s="24">
         <v>82</v>
       </c>
-      <c r="H27" s="46">
+      <c r="H27" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -2876,16 +2877,16 @@
       <c r="D28" s="21">
         <v>85</v>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="48">
         <v>63</v>
       </c>
-      <c r="F28" s="48">
+      <c r="F28" s="38">
         <v>63</v>
       </c>
       <c r="G28" s="24">
         <v>62</v>
       </c>
-      <c r="H28" s="46">
+      <c r="H28" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -2902,16 +2903,16 @@
       <c r="D29" s="21">
         <v>84</v>
       </c>
-      <c r="E29" s="51">
+      <c r="E29" s="48">
         <v>35</v>
       </c>
-      <c r="F29" s="48">
+      <c r="F29" s="38">
         <v>66</v>
       </c>
       <c r="G29" s="24">
         <v>75</v>
       </c>
-      <c r="H29" s="46">
+      <c r="H29" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -2928,16 +2929,16 @@
       <c r="D30" s="21">
         <v>25</v>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="48">
         <v>69</v>
       </c>
-      <c r="F30" s="48">
+      <c r="F30" s="38">
         <v>84</v>
       </c>
       <c r="G30" s="24">
         <v>63</v>
       </c>
-      <c r="H30" s="46">
+      <c r="H30" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -2954,16 +2955,16 @@
       <c r="D31" s="21">
         <v>34</v>
       </c>
-      <c r="E31" s="51">
+      <c r="E31" s="48">
         <v>38</v>
       </c>
-      <c r="F31" s="48">
+      <c r="F31" s="38">
         <v>78</v>
       </c>
       <c r="G31" s="26">
         <v>61</v>
       </c>
-      <c r="H31" s="46">
+      <c r="H31" s="45">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -2980,16 +2981,16 @@
       <c r="D32" s="21">
         <v>85</v>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="48">
         <v>61</v>
       </c>
-      <c r="F32" s="48">
+      <c r="F32" s="38">
         <v>78</v>
       </c>
       <c r="G32" s="24">
         <v>81</v>
       </c>
-      <c r="H32" s="46">
+      <c r="H32" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3006,16 +3007,16 @@
       <c r="D33" s="21">
         <v>67</v>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="48">
         <v>67</v>
       </c>
-      <c r="F33" s="48">
+      <c r="F33" s="38">
         <v>67</v>
       </c>
       <c r="G33" s="24">
         <v>71</v>
       </c>
-      <c r="H33" s="46">
+      <c r="H33" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3032,16 +3033,16 @@
       <c r="D34" s="21">
         <v>45</v>
       </c>
-      <c r="E34" s="51">
+      <c r="E34" s="48">
         <v>27</v>
       </c>
-      <c r="F34" s="48">
+      <c r="F34" s="38">
         <v>51</v>
       </c>
       <c r="G34" s="24">
         <v>43</v>
       </c>
-      <c r="H34" s="46">
+      <c r="H34" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3058,16 +3059,16 @@
       <c r="D35" s="20">
         <v>55</v>
       </c>
-      <c r="E35" s="51">
+      <c r="E35" s="48">
         <v>74</v>
       </c>
-      <c r="F35" s="48">
+      <c r="F35" s="38">
         <v>67</v>
       </c>
       <c r="G35" s="24">
         <v>56</v>
       </c>
-      <c r="H35" s="46">
+      <c r="H35" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3084,16 +3085,16 @@
       <c r="D36" s="21">
         <v>57</v>
       </c>
-      <c r="E36" s="51">
+      <c r="E36" s="48">
         <v>65</v>
       </c>
-      <c r="F36" s="48">
+      <c r="F36" s="38">
         <v>60</v>
       </c>
       <c r="G36" s="24">
         <v>49</v>
       </c>
-      <c r="H36" s="46">
+      <c r="H36" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3110,16 +3111,16 @@
       <c r="D37" s="21">
         <v>41</v>
       </c>
-      <c r="E37" s="51">
+      <c r="E37" s="48">
         <v>28</v>
       </c>
-      <c r="F37" s="48">
+      <c r="F37" s="38">
         <v>63</v>
       </c>
       <c r="G37" s="24">
         <v>54</v>
       </c>
-      <c r="H37" s="46">
+      <c r="H37" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -3136,16 +3137,16 @@
       <c r="D38" s="21">
         <v>84</v>
       </c>
-      <c r="E38" s="51">
+      <c r="E38" s="48">
         <v>73</v>
       </c>
-      <c r="F38" s="48">
+      <c r="F38" s="38">
         <v>71</v>
       </c>
       <c r="G38" s="24">
         <v>72</v>
       </c>
-      <c r="H38" s="46">
+      <c r="H38" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3162,16 +3163,16 @@
       <c r="D39" s="21">
         <v>61</v>
       </c>
-      <c r="E39" s="51">
+      <c r="E39" s="48">
         <v>75</v>
       </c>
-      <c r="F39" s="48">
+      <c r="F39" s="38">
         <v>56</v>
       </c>
       <c r="G39" s="24">
         <v>58</v>
       </c>
-      <c r="H39" s="46">
+      <c r="H39" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3188,16 +3189,16 @@
       <c r="D40" s="20">
         <v>37</v>
       </c>
-      <c r="E40" s="51">
+      <c r="E40" s="48">
         <v>80</v>
       </c>
-      <c r="F40" s="48">
+      <c r="F40" s="38">
         <v>70</v>
       </c>
       <c r="G40" s="24">
         <v>57</v>
       </c>
-      <c r="H40" s="46">
+      <c r="H40" s="45">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3214,16 +3215,16 @@
       <c r="D41" s="20">
         <v>52</v>
       </c>
-      <c r="E41" s="51">
+      <c r="E41" s="48">
         <v>59</v>
       </c>
-      <c r="F41" s="48">
+      <c r="F41" s="38">
         <v>47</v>
       </c>
       <c r="G41" s="24">
         <v>37</v>
       </c>
-      <c r="H41" s="46">
+      <c r="H41" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3240,16 +3241,16 @@
       <c r="D42" s="21">
         <v>75</v>
       </c>
-      <c r="E42" s="51">
+      <c r="E42" s="48">
         <v>41</v>
       </c>
-      <c r="F42" s="48">
+      <c r="F42" s="38">
         <v>63</v>
       </c>
       <c r="G42" s="24">
         <v>67</v>
       </c>
-      <c r="H42" s="46">
+      <c r="H42" s="45">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -3266,16 +3267,16 @@
       <c r="D43" s="20">
         <v>50</v>
       </c>
-      <c r="E43" s="51">
+      <c r="E43" s="48">
         <v>59</v>
       </c>
-      <c r="F43" s="48">
+      <c r="F43" s="38">
         <v>75</v>
       </c>
       <c r="G43" s="24">
         <v>69</v>
       </c>
-      <c r="H43" s="46">
+      <c r="H43" s="45">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3292,16 +3293,16 @@
       <c r="D44" s="20">
         <v>39</v>
       </c>
-      <c r="E44" s="51">
+      <c r="E44" s="48">
         <v>31</v>
       </c>
-      <c r="F44" s="48">
+      <c r="F44" s="38">
         <v>65</v>
       </c>
       <c r="G44" s="24">
         <v>35</v>
       </c>
-      <c r="H44" s="46">
+      <c r="H44" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3318,16 +3319,16 @@
       <c r="D45" s="21">
         <v>79</v>
       </c>
-      <c r="E45" s="51">
+      <c r="E45" s="48">
         <v>56</v>
       </c>
-      <c r="F45" s="48">
+      <c r="F45" s="38">
         <v>59</v>
       </c>
       <c r="G45" s="24">
         <v>72</v>
       </c>
-      <c r="H45" s="46">
+      <c r="H45" s="45">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -3344,16 +3345,16 @@
       <c r="D46" s="20">
         <v>70</v>
       </c>
-      <c r="E46" s="51">
+      <c r="E46" s="48">
         <v>56</v>
       </c>
-      <c r="F46" s="48">
+      <c r="F46" s="38">
         <v>49</v>
       </c>
       <c r="G46" s="24">
         <v>45</v>
       </c>
-      <c r="H46" s="46">
+      <c r="H46" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3370,16 +3371,16 @@
       <c r="D47" s="21">
         <v>64</v>
       </c>
-      <c r="E47" s="51">
+      <c r="E47" s="48">
         <v>91</v>
       </c>
-      <c r="F47" s="48">
+      <c r="F47" s="38">
         <v>12</v>
       </c>
       <c r="G47" s="24">
         <v>55</v>
       </c>
-      <c r="H47" s="46">
+      <c r="H47" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3396,16 +3397,16 @@
       <c r="D48" s="21">
         <v>64</v>
       </c>
-      <c r="E48" s="51">
+      <c r="E48" s="48">
         <v>71</v>
       </c>
-      <c r="F48" s="48">
+      <c r="F48" s="38">
         <v>76</v>
       </c>
       <c r="G48" s="26">
         <v>64</v>
       </c>
-      <c r="H48" s="46">
+      <c r="H48" s="45">
         <v>21.739130400000001</v>
       </c>
     </row>
@@ -3422,16 +3423,16 @@
       <c r="D49" s="21">
         <v>81</v>
       </c>
-      <c r="E49" s="51">
+      <c r="E49" s="48">
         <v>79</v>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="38">
         <v>83</v>
       </c>
       <c r="G49" s="24">
         <v>39</v>
       </c>
-      <c r="H49" s="46">
+      <c r="H49" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3448,16 +3449,16 @@
       <c r="D50" s="21">
         <v>63</v>
       </c>
-      <c r="E50" s="51">
+      <c r="E50" s="48">
         <v>41</v>
       </c>
-      <c r="F50" s="48">
+      <c r="F50" s="38">
         <v>74</v>
       </c>
       <c r="G50" s="24">
         <v>68</v>
       </c>
-      <c r="H50" s="46">
+      <c r="H50" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3474,16 +3475,16 @@
       <c r="D51" s="20">
         <v>90</v>
       </c>
-      <c r="E51" s="51">
+      <c r="E51" s="48">
         <v>53</v>
       </c>
-      <c r="F51" s="48">
+      <c r="F51" s="38">
         <v>72</v>
       </c>
       <c r="G51" s="24">
         <v>67</v>
       </c>
-      <c r="H51" s="46">
+      <c r="H51" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3500,16 +3501,16 @@
       <c r="D52" s="20">
         <v>42</v>
       </c>
-      <c r="E52" s="51">
+      <c r="E52" s="48">
         <v>52</v>
       </c>
-      <c r="F52" s="48">
+      <c r="F52" s="38">
         <v>58</v>
       </c>
       <c r="G52" s="24">
         <v>41</v>
       </c>
-      <c r="H52" s="46">
+      <c r="H52" s="45">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -3526,16 +3527,16 @@
       <c r="D53" s="21">
         <v>60</v>
       </c>
-      <c r="E53" s="51">
+      <c r="E53" s="48">
         <v>24</v>
       </c>
-      <c r="F53" s="48">
+      <c r="F53" s="38">
         <v>60</v>
       </c>
       <c r="G53" s="24">
         <v>39</v>
       </c>
-      <c r="H53" s="46">
+      <c r="H53" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3552,16 +3553,16 @@
       <c r="D54" s="20">
         <v>76</v>
       </c>
-      <c r="E54" s="51">
+      <c r="E54" s="48">
         <v>97</v>
       </c>
-      <c r="F54" s="48">
+      <c r="F54" s="38">
         <v>59</v>
       </c>
       <c r="G54" s="24">
         <v>68</v>
       </c>
-      <c r="H54" s="46">
+      <c r="H54" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3578,16 +3579,16 @@
       <c r="D55" s="21">
         <v>89</v>
       </c>
-      <c r="E55" s="51">
+      <c r="E55" s="48">
         <v>85</v>
       </c>
-      <c r="F55" s="48">
+      <c r="F55" s="38">
         <v>76</v>
       </c>
       <c r="G55" s="26">
         <v>84</v>
       </c>
-      <c r="H55" s="46">
+      <c r="H55" s="45">
         <v>100</v>
       </c>
     </row>
@@ -3604,16 +3605,16 @@
       <c r="D56" s="21">
         <v>96</v>
       </c>
-      <c r="E56" s="51">
+      <c r="E56" s="48">
         <v>67</v>
       </c>
-      <c r="F56" s="48">
+      <c r="F56" s="38">
         <v>54</v>
       </c>
       <c r="G56" s="24">
         <v>63</v>
       </c>
-      <c r="H56" s="46">
+      <c r="H56" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3630,16 +3631,16 @@
       <c r="D57" s="21">
         <v>37</v>
       </c>
-      <c r="E57" s="51">
+      <c r="E57" s="48">
         <v>45</v>
       </c>
-      <c r="F57" s="48">
+      <c r="F57" s="38">
         <v>53</v>
       </c>
       <c r="G57" s="24">
         <v>49</v>
       </c>
-      <c r="H57" s="46">
+      <c r="H57" s="45">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3656,16 +3657,16 @@
       <c r="D58" s="20">
         <v>20</v>
       </c>
-      <c r="E58" s="51">
+      <c r="E58" s="48">
         <v>38</v>
       </c>
-      <c r="F58" s="48">
+      <c r="F58" s="38">
         <v>43</v>
       </c>
       <c r="G58" s="24">
         <v>28</v>
       </c>
-      <c r="H58" s="46">
+      <c r="H58" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3682,16 +3683,16 @@
       <c r="D59" s="21">
         <v>36</v>
       </c>
-      <c r="E59" s="51">
+      <c r="E59" s="48">
         <v>36</v>
       </c>
-      <c r="F59" s="48">
+      <c r="F59" s="38">
         <v>72</v>
       </c>
       <c r="G59" s="24">
         <v>44</v>
       </c>
-      <c r="H59" s="46">
+      <c r="H59" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3708,16 +3709,16 @@
       <c r="D60" s="21">
         <v>28</v>
       </c>
-      <c r="E60" s="49" t="s">
-        <v>382</v>
-      </c>
-      <c r="F60" s="49">
+      <c r="E60" s="46">
+        <v>62</v>
+      </c>
+      <c r="F60" s="46">
         <v>68</v>
       </c>
       <c r="G60" s="25">
         <v>60</v>
       </c>
-      <c r="H60" s="46">
+      <c r="H60" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3734,16 +3735,16 @@
       <c r="D61" s="21">
         <v>68</v>
       </c>
-      <c r="E61" s="51">
+      <c r="E61" s="48">
         <v>81</v>
       </c>
-      <c r="F61" s="48">
+      <c r="F61" s="38">
         <v>64</v>
       </c>
       <c r="G61" s="24">
         <v>86</v>
       </c>
-      <c r="H61" s="46">
+      <c r="H61" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -3757,19 +3758,19 @@
       <c r="C62" s="20">
         <v>64</v>
       </c>
-      <c r="D62" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="E62" s="51">
+      <c r="D62" s="21">
+        <v>76</v>
+      </c>
+      <c r="E62" s="48">
         <v>55</v>
       </c>
-      <c r="F62" s="48">
+      <c r="F62" s="38">
         <v>52</v>
       </c>
       <c r="G62" s="24">
         <v>52</v>
       </c>
-      <c r="H62" s="46">
+      <c r="H62" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -3786,16 +3787,16 @@
       <c r="D63" s="21">
         <v>57</v>
       </c>
-      <c r="E63" s="51">
+      <c r="E63" s="48">
         <v>76</v>
       </c>
-      <c r="F63" s="48">
+      <c r="F63" s="38">
         <v>61</v>
       </c>
       <c r="G63" s="24">
         <v>64</v>
       </c>
-      <c r="H63" s="46">
+      <c r="H63" s="45">
         <v>100</v>
       </c>
     </row>
@@ -3812,16 +3813,16 @@
       <c r="D64" s="21">
         <v>40</v>
       </c>
-      <c r="E64" s="51">
+      <c r="E64" s="48">
         <v>53</v>
       </c>
-      <c r="F64" s="48">
+      <c r="F64" s="38">
         <v>65</v>
       </c>
       <c r="G64" s="24">
         <v>46</v>
       </c>
-      <c r="H64" s="46">
+      <c r="H64" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -3838,16 +3839,16 @@
       <c r="D65" s="21">
         <v>48</v>
       </c>
-      <c r="E65" s="51">
+      <c r="E65" s="48">
         <v>49</v>
       </c>
-      <c r="F65" s="48">
+      <c r="F65" s="38">
         <v>58</v>
       </c>
       <c r="G65" s="24">
         <v>47</v>
       </c>
-      <c r="H65" s="46">
+      <c r="H65" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -3864,16 +3865,16 @@
       <c r="D66" s="21">
         <v>84</v>
       </c>
-      <c r="E66" s="51">
+      <c r="E66" s="48">
         <v>23</v>
       </c>
-      <c r="F66" s="48">
+      <c r="F66" s="38">
         <v>73</v>
       </c>
       <c r="G66" s="24">
         <v>54</v>
       </c>
-      <c r="H66" s="46">
+      <c r="H66" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -3890,16 +3891,16 @@
       <c r="D67" s="21">
         <v>50</v>
       </c>
-      <c r="E67" s="51">
+      <c r="E67" s="48">
         <v>30</v>
       </c>
-      <c r="F67" s="48">
+      <c r="F67" s="38">
         <v>60</v>
       </c>
       <c r="G67" s="24">
         <v>27</v>
       </c>
-      <c r="H67" s="46">
+      <c r="H67" s="45">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3916,16 +3917,16 @@
       <c r="D68" s="21">
         <v>73</v>
       </c>
-      <c r="E68" s="51">
+      <c r="E68" s="48">
         <v>61</v>
       </c>
-      <c r="F68" s="48">
+      <c r="F68" s="38">
         <v>76</v>
       </c>
       <c r="G68" s="26">
         <v>62</v>
       </c>
-      <c r="H68" s="46">
+      <c r="H68" s="45">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -3942,16 +3943,16 @@
       <c r="D69" s="20">
         <v>17</v>
       </c>
-      <c r="E69" s="51">
+      <c r="E69" s="48">
         <v>36</v>
       </c>
-      <c r="F69" s="48">
+      <c r="F69" s="38">
         <v>66</v>
       </c>
       <c r="G69" s="24">
         <v>28</v>
       </c>
-      <c r="H69" s="46">
+      <c r="H69" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -3968,16 +3969,16 @@
       <c r="D70" s="21">
         <v>60</v>
       </c>
-      <c r="E70" s="51">
+      <c r="E70" s="48">
         <v>46</v>
       </c>
-      <c r="F70" s="48">
+      <c r="F70" s="38">
         <v>61</v>
       </c>
       <c r="G70" s="24">
         <v>37</v>
       </c>
-      <c r="H70" s="46">
+      <c r="H70" s="45">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -3994,16 +3995,16 @@
       <c r="D71" s="20">
         <v>74</v>
       </c>
-      <c r="E71" s="51">
+      <c r="E71" s="48">
         <v>51</v>
       </c>
-      <c r="F71" s="48">
+      <c r="F71" s="38">
         <v>54</v>
       </c>
       <c r="G71" s="24">
         <v>58</v>
       </c>
-      <c r="H71" s="46">
+      <c r="H71" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -4020,16 +4021,16 @@
       <c r="D72" s="20">
         <v>68</v>
       </c>
-      <c r="E72" s="51">
+      <c r="E72" s="48">
         <v>29</v>
       </c>
-      <c r="F72" s="48">
+      <c r="F72" s="38">
         <v>54</v>
       </c>
       <c r="G72" s="24">
         <v>26</v>
       </c>
-      <c r="H72" s="46">
+      <c r="H72" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4046,16 +4047,16 @@
       <c r="D73" s="21">
         <v>80</v>
       </c>
-      <c r="E73" s="51">
+      <c r="E73" s="48">
         <v>83</v>
       </c>
-      <c r="F73" s="48">
+      <c r="F73" s="38">
         <v>71</v>
       </c>
       <c r="G73" s="26">
         <v>77</v>
       </c>
-      <c r="H73" s="46">
+      <c r="H73" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -4072,16 +4073,16 @@
       <c r="D74" s="21">
         <v>58</v>
       </c>
-      <c r="E74" s="51">
+      <c r="E74" s="48">
         <v>32</v>
       </c>
-      <c r="F74" s="48">
+      <c r="F74" s="38">
         <v>66</v>
       </c>
       <c r="G74" s="24">
         <v>60</v>
       </c>
-      <c r="H74" s="46">
+      <c r="H74" s="45">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -4098,16 +4099,16 @@
       <c r="D75" s="20">
         <v>60</v>
       </c>
-      <c r="E75" s="51">
+      <c r="E75" s="48">
         <v>33</v>
       </c>
-      <c r="F75" s="48">
+      <c r="F75" s="38">
         <v>55</v>
       </c>
       <c r="G75" s="24">
         <v>58</v>
       </c>
-      <c r="H75" s="46">
+      <c r="H75" s="45">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -4124,16 +4125,16 @@
       <c r="D76" s="21">
         <v>44</v>
       </c>
-      <c r="E76" s="51">
+      <c r="E76" s="48">
         <v>11</v>
       </c>
-      <c r="F76" s="48">
+      <c r="F76" s="38">
         <v>58</v>
       </c>
       <c r="G76" s="24">
         <v>47</v>
       </c>
-      <c r="H76" s="46">
+      <c r="H76" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4150,16 +4151,16 @@
       <c r="D77" s="21">
         <v>48</v>
       </c>
-      <c r="E77" s="51">
+      <c r="E77" s="48">
         <v>33</v>
       </c>
-      <c r="F77" s="48">
+      <c r="F77" s="38">
         <v>71</v>
       </c>
       <c r="G77" s="24">
         <v>59</v>
       </c>
-      <c r="H77" s="46">
+      <c r="H77" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4176,16 +4177,16 @@
       <c r="D78" s="20">
         <v>68</v>
       </c>
-      <c r="E78" s="51">
+      <c r="E78" s="48">
         <v>24</v>
       </c>
-      <c r="F78" s="48">
+      <c r="F78" s="38">
         <v>54</v>
       </c>
       <c r="G78" s="24">
         <v>77</v>
       </c>
-      <c r="H78" s="46">
+      <c r="H78" s="45">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -4202,16 +4203,16 @@
       <c r="D79" s="21">
         <v>41</v>
       </c>
-      <c r="E79" s="51">
+      <c r="E79" s="48">
         <v>27</v>
       </c>
-      <c r="F79" s="48">
+      <c r="F79" s="38">
         <v>43</v>
       </c>
       <c r="G79" s="24">
         <v>49</v>
       </c>
-      <c r="H79" s="46">
+      <c r="H79" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4228,16 +4229,16 @@
       <c r="D80" s="21">
         <v>56</v>
       </c>
-      <c r="E80" s="51">
+      <c r="E80" s="48">
         <v>72</v>
       </c>
-      <c r="F80" s="48">
+      <c r="F80" s="38">
         <v>56</v>
       </c>
       <c r="G80" s="24">
         <v>51</v>
       </c>
-      <c r="H80" s="46">
+      <c r="H80" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4254,16 +4255,16 @@
       <c r="D81" s="21">
         <v>63</v>
       </c>
-      <c r="E81" s="51">
+      <c r="E81" s="48">
         <v>64</v>
       </c>
-      <c r="F81" s="48">
+      <c r="F81" s="38">
         <v>79</v>
       </c>
       <c r="G81" s="24">
         <v>64</v>
       </c>
-      <c r="H81" s="46">
+      <c r="H81" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -4280,16 +4281,16 @@
       <c r="D82" s="21">
         <v>30</v>
       </c>
-      <c r="E82" s="51">
+      <c r="E82" s="48">
         <v>27</v>
       </c>
-      <c r="F82" s="48">
+      <c r="F82" s="38">
         <v>63</v>
       </c>
       <c r="G82" s="24">
         <v>32</v>
       </c>
-      <c r="H82" s="46">
+      <c r="H82" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4306,16 +4307,16 @@
       <c r="D83" s="21">
         <v>85</v>
       </c>
-      <c r="E83" s="51">
+      <c r="E83" s="48">
         <v>42</v>
       </c>
-      <c r="F83" s="48">
+      <c r="F83" s="38">
         <v>32</v>
       </c>
       <c r="G83" s="26">
         <v>57</v>
       </c>
-      <c r="H83" s="46">
+      <c r="H83" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4332,16 +4333,16 @@
       <c r="D84" s="20">
         <v>34</v>
       </c>
-      <c r="E84" s="51">
+      <c r="E84" s="48">
         <v>24</v>
       </c>
-      <c r="F84" s="48">
+      <c r="F84" s="38">
         <v>56</v>
       </c>
       <c r="G84" s="24">
         <v>44</v>
       </c>
-      <c r="H84" s="46">
+      <c r="H84" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4358,16 +4359,16 @@
       <c r="D85" s="20">
         <v>67</v>
       </c>
-      <c r="E85" s="49">
+      <c r="E85" s="46">
         <v>45</v>
       </c>
-      <c r="F85" s="49">
+      <c r="F85" s="46">
         <v>51</v>
       </c>
       <c r="G85" s="25">
         <v>58</v>
       </c>
-      <c r="H85" s="46">
+      <c r="H85" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4384,16 +4385,16 @@
       <c r="D86" s="21">
         <v>49</v>
       </c>
-      <c r="E86" s="51">
+      <c r="E86" s="48">
         <v>24</v>
       </c>
-      <c r="F86" s="48">
+      <c r="F86" s="38">
         <v>35</v>
       </c>
       <c r="G86" s="24">
         <v>64</v>
       </c>
-      <c r="H86" s="46">
+      <c r="H86" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -4410,16 +4411,16 @@
       <c r="D87" s="21">
         <v>58</v>
       </c>
-      <c r="E87" s="51">
+      <c r="E87" s="48">
         <v>34</v>
       </c>
-      <c r="F87" s="48">
+      <c r="F87" s="38">
         <v>41</v>
       </c>
       <c r="G87" s="24">
         <v>58</v>
       </c>
-      <c r="H87" s="46">
+      <c r="H87" s="45">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -4436,16 +4437,16 @@
       <c r="D88" s="21">
         <v>47</v>
       </c>
-      <c r="E88" s="51">
+      <c r="E88" s="48">
         <v>41</v>
       </c>
-      <c r="F88" s="48">
+      <c r="F88" s="38">
         <v>78</v>
       </c>
       <c r="G88" s="24">
         <v>81</v>
       </c>
-      <c r="H88" s="46">
+      <c r="H88" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4462,16 +4463,16 @@
       <c r="D89" s="21">
         <v>58</v>
       </c>
-      <c r="E89" s="51">
+      <c r="E89" s="48">
         <v>61</v>
       </c>
-      <c r="F89" s="48">
+      <c r="F89" s="38">
         <v>54</v>
       </c>
       <c r="G89" s="24">
         <v>75</v>
       </c>
-      <c r="H89" s="46">
+      <c r="H89" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4488,16 +4489,16 @@
       <c r="D90" s="21">
         <v>84</v>
       </c>
-      <c r="E90" s="51">
+      <c r="E90" s="48">
         <v>48</v>
       </c>
-      <c r="F90" s="48">
+      <c r="F90" s="38">
         <v>66</v>
       </c>
       <c r="G90" s="26">
         <v>54</v>
       </c>
-      <c r="H90" s="46">
+      <c r="H90" s="45">
         <v>52.173913000000006</v>
       </c>
     </row>
@@ -4514,16 +4515,16 @@
       <c r="D91" s="20">
         <v>66</v>
       </c>
-      <c r="E91" s="51">
+      <c r="E91" s="48">
         <v>48</v>
       </c>
-      <c r="F91" s="48">
+      <c r="F91" s="38">
         <v>51</v>
       </c>
       <c r="G91" s="24">
         <v>58</v>
       </c>
-      <c r="H91" s="46">
+      <c r="H91" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4540,16 +4541,16 @@
       <c r="D92" s="20">
         <v>48</v>
       </c>
-      <c r="E92" s="51">
+      <c r="E92" s="48">
         <v>33</v>
       </c>
-      <c r="F92" s="48">
+      <c r="F92" s="38">
         <v>64</v>
       </c>
       <c r="G92" s="24">
         <v>40</v>
       </c>
-      <c r="H92" s="46">
+      <c r="H92" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4563,19 +4564,19 @@
       <c r="C93" s="20">
         <v>24</v>
       </c>
-      <c r="D93" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="E93" s="51">
+      <c r="D93" s="21">
+        <v>74</v>
+      </c>
+      <c r="E93" s="48">
         <v>70</v>
       </c>
-      <c r="F93" s="48">
+      <c r="F93" s="38">
         <v>66</v>
       </c>
       <c r="G93" s="24">
         <v>46</v>
       </c>
-      <c r="H93" s="46">
+      <c r="H93" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -4592,16 +4593,16 @@
       <c r="D94" s="20">
         <v>55</v>
       </c>
-      <c r="E94" s="51">
+      <c r="E94" s="48">
         <v>29</v>
       </c>
-      <c r="F94" s="48">
+      <c r="F94" s="38">
         <v>63</v>
       </c>
       <c r="G94" s="24">
         <v>41</v>
       </c>
-      <c r="H94" s="46">
+      <c r="H94" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -4618,16 +4619,16 @@
       <c r="D95" s="21">
         <v>87</v>
       </c>
-      <c r="E95" s="51">
+      <c r="E95" s="48">
         <v>65</v>
       </c>
-      <c r="F95" s="48">
+      <c r="F95" s="38">
         <v>75</v>
       </c>
       <c r="G95" s="24">
         <v>84</v>
       </c>
-      <c r="H95" s="46">
+      <c r="H95" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4644,16 +4645,16 @@
       <c r="D96" s="21">
         <v>79</v>
       </c>
-      <c r="E96" s="49">
+      <c r="E96" s="46">
         <v>31</v>
       </c>
-      <c r="F96" s="49">
+      <c r="F96" s="46">
         <v>57</v>
       </c>
       <c r="G96" s="25">
         <v>75</v>
       </c>
-      <c r="H96" s="46">
+      <c r="H96" s="45">
         <v>65.217391300000003</v>
       </c>
     </row>
@@ -4670,16 +4671,16 @@
       <c r="D97" s="21">
         <v>63</v>
       </c>
-      <c r="E97" s="51">
+      <c r="E97" s="48">
         <v>27</v>
       </c>
-      <c r="F97" s="48">
+      <c r="F97" s="38">
         <v>44</v>
       </c>
       <c r="G97" s="24">
         <v>46</v>
       </c>
-      <c r="H97" s="46">
+      <c r="H97" s="45">
         <v>56.521739100000005</v>
       </c>
     </row>
@@ -4696,16 +4697,16 @@
       <c r="D98" s="27">
         <v>52</v>
       </c>
-      <c r="E98" s="51">
+      <c r="E98" s="48">
         <v>44</v>
       </c>
-      <c r="F98" s="48">
+      <c r="F98" s="38">
         <v>67</v>
       </c>
       <c r="G98" s="24">
         <v>61</v>
       </c>
-      <c r="H98" s="46">
+      <c r="H98" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4722,16 +4723,16 @@
       <c r="D99" s="27">
         <v>83</v>
       </c>
-      <c r="E99" s="51">
+      <c r="E99" s="48">
         <v>62</v>
       </c>
-      <c r="F99" s="48">
+      <c r="F99" s="38">
         <v>79</v>
       </c>
       <c r="G99" s="26">
         <v>75</v>
       </c>
-      <c r="H99" s="46">
+      <c r="H99" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4748,16 +4749,16 @@
       <c r="D100" s="27">
         <v>48</v>
       </c>
-      <c r="E100" s="51">
+      <c r="E100" s="48">
         <v>49</v>
       </c>
-      <c r="F100" s="48">
+      <c r="F100" s="38">
         <v>74</v>
       </c>
       <c r="G100" s="24">
         <v>50</v>
       </c>
-      <c r="H100" s="46">
+      <c r="H100" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -4774,16 +4775,16 @@
       <c r="D101" s="27">
         <v>79</v>
       </c>
-      <c r="E101" s="51">
+      <c r="E101" s="48">
         <v>50</v>
       </c>
-      <c r="F101" s="48">
+      <c r="F101" s="38">
         <v>61</v>
       </c>
       <c r="G101" s="24">
         <v>47</v>
       </c>
-      <c r="H101" s="46">
+      <c r="H101" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4800,16 +4801,16 @@
       <c r="D102" s="20">
         <v>85</v>
       </c>
-      <c r="E102" s="51">
+      <c r="E102" s="48">
         <v>42</v>
       </c>
-      <c r="F102" s="48">
+      <c r="F102" s="38">
         <v>76</v>
       </c>
       <c r="G102" s="24">
         <v>76</v>
       </c>
-      <c r="H102" s="46">
+      <c r="H102" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -4826,16 +4827,16 @@
       <c r="D103" s="27">
         <v>41</v>
       </c>
-      <c r="E103" s="51">
+      <c r="E103" s="48">
         <v>20</v>
       </c>
-      <c r="F103" s="48">
+      <c r="F103" s="38">
         <v>53</v>
       </c>
       <c r="G103" s="24">
         <v>51</v>
       </c>
-      <c r="H103" s="46">
+      <c r="H103" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4852,16 +4853,16 @@
       <c r="D104" s="27">
         <v>74</v>
       </c>
-      <c r="E104" s="51">
+      <c r="E104" s="48">
         <v>67</v>
       </c>
-      <c r="F104" s="48">
+      <c r="F104" s="38">
         <v>67</v>
       </c>
       <c r="G104" s="24">
         <v>69</v>
       </c>
-      <c r="H104" s="46">
+      <c r="H104" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -4878,16 +4879,16 @@
       <c r="D105" s="27">
         <v>60</v>
       </c>
-      <c r="E105" s="51">
+      <c r="E105" s="48">
         <v>57</v>
       </c>
-      <c r="F105" s="48">
+      <c r="F105" s="38">
         <v>66</v>
       </c>
       <c r="G105" s="24">
         <v>72</v>
       </c>
-      <c r="H105" s="46">
+      <c r="H105" s="45">
         <v>100</v>
       </c>
     </row>
@@ -4904,16 +4905,16 @@
       <c r="D106" s="27">
         <v>43</v>
       </c>
-      <c r="E106" s="51">
+      <c r="E106" s="48">
         <v>35</v>
       </c>
-      <c r="F106" s="48">
+      <c r="F106" s="38">
         <v>55</v>
       </c>
       <c r="G106" s="24">
         <v>9</v>
       </c>
-      <c r="H106" s="46">
+      <c r="H106" s="45">
         <v>100</v>
       </c>
     </row>
@@ -4930,16 +4931,16 @@
       <c r="D107" s="27">
         <v>47</v>
       </c>
-      <c r="E107" s="51">
+      <c r="E107" s="48">
         <v>34</v>
       </c>
-      <c r="F107" s="48">
+      <c r="F107" s="38">
         <v>64</v>
       </c>
       <c r="G107" s="24">
         <v>49</v>
       </c>
-      <c r="H107" s="46">
+      <c r="H107" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -4956,16 +4957,16 @@
       <c r="D108" s="27">
         <v>12</v>
       </c>
-      <c r="E108" s="51">
+      <c r="E108" s="48">
         <v>41</v>
       </c>
-      <c r="F108" s="48">
+      <c r="F108" s="38">
         <v>79</v>
       </c>
       <c r="G108" s="24">
         <v>56</v>
       </c>
-      <c r="H108" s="46">
+      <c r="H108" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -4976,22 +4977,22 @@
       <c r="B109" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C109" s="20" t="s">
-        <v>382</v>
+      <c r="C109" s="20">
+        <v>75</v>
       </c>
       <c r="D109" s="20">
         <v>35</v>
       </c>
-      <c r="E109" s="51">
+      <c r="E109" s="48">
         <v>50</v>
       </c>
-      <c r="F109" s="48">
+      <c r="F109" s="38">
         <v>58</v>
       </c>
       <c r="G109" s="24">
         <v>62</v>
       </c>
-      <c r="H109" s="46">
+      <c r="H109" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5005,19 +5006,19 @@
       <c r="C110" s="20">
         <v>53</v>
       </c>
-      <c r="D110" s="20" t="s">
-        <v>382</v>
-      </c>
-      <c r="E110" s="51">
+      <c r="D110" s="20">
+        <v>57</v>
+      </c>
+      <c r="E110" s="48">
         <v>51</v>
       </c>
-      <c r="F110" s="48">
+      <c r="F110" s="38">
         <v>65</v>
       </c>
       <c r="G110" s="24">
         <v>60</v>
       </c>
-      <c r="H110" s="46">
+      <c r="H110" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5034,16 +5035,16 @@
       <c r="D111" s="20">
         <v>12</v>
       </c>
-      <c r="E111" s="51" t="s">
+      <c r="E111" s="48" t="s">
         <v>382</v>
       </c>
-      <c r="F111" s="48">
+      <c r="F111" s="38">
         <v>42</v>
       </c>
       <c r="G111" s="24">
         <v>11</v>
       </c>
-      <c r="H111" s="46">
+      <c r="H111" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5060,16 +5061,16 @@
       <c r="D112" s="27">
         <v>85</v>
       </c>
-      <c r="E112" s="51">
+      <c r="E112" s="48">
         <v>44</v>
       </c>
-      <c r="F112" s="48">
+      <c r="F112" s="38">
         <v>75</v>
       </c>
       <c r="G112" s="24">
         <v>70</v>
       </c>
-      <c r="H112" s="46">
+      <c r="H112" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -5086,16 +5087,16 @@
       <c r="D113" s="27">
         <v>19</v>
       </c>
-      <c r="E113" s="51">
+      <c r="E113" s="48">
         <v>24</v>
       </c>
-      <c r="F113" s="48">
+      <c r="F113" s="38">
         <v>73</v>
       </c>
       <c r="G113" s="24">
         <v>50</v>
       </c>
-      <c r="H113" s="46">
+      <c r="H113" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5112,16 +5113,16 @@
       <c r="D114" s="20">
         <v>75</v>
       </c>
-      <c r="E114" s="51">
+      <c r="E114" s="48">
         <v>64</v>
       </c>
-      <c r="F114" s="48">
+      <c r="F114" s="38">
         <v>62</v>
       </c>
       <c r="G114" s="24">
         <v>63</v>
       </c>
-      <c r="H114" s="46">
+      <c r="H114" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5138,16 +5139,16 @@
       <c r="D115" s="20">
         <v>79</v>
       </c>
-      <c r="E115" s="51">
+      <c r="E115" s="48">
         <v>72</v>
       </c>
-      <c r="F115" s="48">
+      <c r="F115" s="38">
         <v>71</v>
       </c>
       <c r="G115" s="24">
         <v>67</v>
       </c>
-      <c r="H115" s="46">
+      <c r="H115" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5164,16 +5165,16 @@
       <c r="D116" s="27">
         <v>47</v>
       </c>
-      <c r="E116" s="51">
+      <c r="E116" s="48">
         <v>78</v>
       </c>
-      <c r="F116" s="48">
+      <c r="F116" s="38">
         <v>66</v>
       </c>
       <c r="G116" s="24">
         <v>72</v>
       </c>
-      <c r="H116" s="46">
+      <c r="H116" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5190,16 +5191,16 @@
       <c r="D117" s="27">
         <v>60</v>
       </c>
-      <c r="E117" s="51">
+      <c r="E117" s="48">
         <v>39</v>
       </c>
-      <c r="F117" s="48">
+      <c r="F117" s="38">
         <v>61</v>
       </c>
       <c r="G117" s="24">
         <v>28</v>
       </c>
-      <c r="H117" s="46">
+      <c r="H117" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5216,16 +5217,16 @@
       <c r="D118" s="20">
         <v>57</v>
       </c>
-      <c r="E118" s="51">
+      <c r="E118" s="48">
         <v>62</v>
       </c>
-      <c r="F118" s="48">
+      <c r="F118" s="38">
         <v>39</v>
       </c>
       <c r="G118" s="24">
         <v>54</v>
       </c>
-      <c r="H118" s="46">
+      <c r="H118" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -5242,16 +5243,16 @@
       <c r="D119" s="20">
         <v>52</v>
       </c>
-      <c r="E119" s="51">
+      <c r="E119" s="48">
         <v>92</v>
       </c>
-      <c r="F119" s="48">
+      <c r="F119" s="38">
         <v>73</v>
       </c>
       <c r="G119" s="24">
         <v>76</v>
       </c>
-      <c r="H119" s="46">
+      <c r="H119" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5268,16 +5269,16 @@
       <c r="D120" s="27">
         <v>31</v>
       </c>
-      <c r="E120" s="51">
+      <c r="E120" s="48">
         <v>82</v>
       </c>
-      <c r="F120" s="48">
+      <c r="F120" s="38">
         <v>70</v>
       </c>
       <c r="G120" s="24">
         <v>52</v>
       </c>
-      <c r="H120" s="46">
+      <c r="H120" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5294,16 +5295,16 @@
       <c r="D121" s="20">
         <v>16</v>
       </c>
-      <c r="E121" s="51">
+      <c r="E121" s="48">
         <v>32</v>
       </c>
-      <c r="F121" s="48">
+      <c r="F121" s="38">
         <v>67</v>
       </c>
       <c r="G121" s="24">
         <v>59</v>
       </c>
-      <c r="H121" s="46">
+      <c r="H121" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5320,16 +5321,16 @@
       <c r="D122" s="20">
         <v>36</v>
       </c>
-      <c r="E122" s="51">
+      <c r="E122" s="48">
         <v>31</v>
       </c>
-      <c r="F122" s="48">
+      <c r="F122" s="38">
         <v>53</v>
       </c>
       <c r="G122" s="24">
         <v>32</v>
       </c>
-      <c r="H122" s="46">
+      <c r="H122" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5346,16 +5347,16 @@
       <c r="D123" s="27" t="s">
         <v>382</v>
       </c>
-      <c r="E123" s="51" t="s">
+      <c r="E123" s="48" t="s">
         <v>382</v>
       </c>
-      <c r="F123" s="48" t="s">
+      <c r="F123" s="38" t="s">
         <v>382</v>
       </c>
       <c r="G123" s="24" t="s">
         <v>382</v>
       </c>
-      <c r="H123" s="46">
+      <c r="H123" s="45">
         <v>0</v>
       </c>
     </row>
@@ -5372,16 +5373,16 @@
       <c r="D124" s="20">
         <v>72</v>
       </c>
-      <c r="E124" s="51">
+      <c r="E124" s="48">
         <v>64</v>
       </c>
-      <c r="F124" s="48">
+      <c r="F124" s="38">
         <v>66</v>
       </c>
       <c r="G124" s="24">
         <v>60</v>
       </c>
-      <c r="H124" s="46">
+      <c r="H124" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5398,16 +5399,16 @@
       <c r="D125" s="27">
         <v>41</v>
       </c>
-      <c r="E125" s="51">
+      <c r="E125" s="48">
         <v>50</v>
       </c>
-      <c r="F125" s="48">
+      <c r="F125" s="38">
         <v>79</v>
       </c>
       <c r="G125" s="24">
         <v>55</v>
       </c>
-      <c r="H125" s="46">
+      <c r="H125" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5424,16 +5425,16 @@
       <c r="D126" s="20">
         <v>53</v>
       </c>
-      <c r="E126" s="51">
+      <c r="E126" s="48">
         <v>88</v>
       </c>
-      <c r="F126" s="48">
+      <c r="F126" s="38">
         <v>80</v>
       </c>
       <c r="G126" s="24">
         <v>68</v>
       </c>
-      <c r="H126" s="46">
+      <c r="H126" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5450,16 +5451,16 @@
       <c r="D127" s="27">
         <v>32</v>
       </c>
-      <c r="E127" s="51">
+      <c r="E127" s="48">
         <v>51</v>
       </c>
-      <c r="F127" s="48">
+      <c r="F127" s="38">
         <v>61</v>
       </c>
       <c r="G127" s="24">
         <v>68</v>
       </c>
-      <c r="H127" s="46">
+      <c r="H127" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -5476,16 +5477,16 @@
       <c r="D128" s="27">
         <v>56</v>
       </c>
-      <c r="E128" s="51">
+      <c r="E128" s="48">
         <v>38</v>
       </c>
-      <c r="F128" s="48">
+      <c r="F128" s="38">
         <v>51</v>
       </c>
       <c r="G128" s="24">
         <v>48</v>
       </c>
-      <c r="H128" s="46">
+      <c r="H128" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5502,16 +5503,16 @@
       <c r="D129" s="27">
         <v>49</v>
       </c>
-      <c r="E129" s="51">
+      <c r="E129" s="48">
         <v>4</v>
       </c>
-      <c r="F129" s="48">
+      <c r="F129" s="38">
         <v>46</v>
       </c>
       <c r="G129" s="24">
         <v>50</v>
       </c>
-      <c r="H129" s="46">
+      <c r="H129" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5528,16 +5529,16 @@
       <c r="D130" s="27">
         <v>26</v>
       </c>
-      <c r="E130" s="51">
+      <c r="E130" s="48">
         <v>37</v>
       </c>
-      <c r="F130" s="48">
+      <c r="F130" s="38">
         <v>64</v>
       </c>
       <c r="G130" s="24">
         <v>22</v>
       </c>
-      <c r="H130" s="46">
+      <c r="H130" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5554,16 +5555,16 @@
       <c r="D131" s="27">
         <v>23</v>
       </c>
-      <c r="E131" s="51">
+      <c r="E131" s="48">
         <v>37</v>
       </c>
-      <c r="F131" s="48">
+      <c r="F131" s="38">
         <v>64</v>
       </c>
       <c r="G131" s="24">
         <v>63</v>
       </c>
-      <c r="H131" s="46">
+      <c r="H131" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5580,16 +5581,16 @@
       <c r="D132" s="27">
         <v>81</v>
       </c>
-      <c r="E132" s="49">
+      <c r="E132" s="46">
         <v>14</v>
       </c>
-      <c r="F132" s="49">
+      <c r="F132" s="46">
         <v>70</v>
       </c>
       <c r="G132" s="25">
         <v>66</v>
       </c>
-      <c r="H132" s="46">
+      <c r="H132" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5606,16 +5607,16 @@
       <c r="D133" s="27">
         <v>13</v>
       </c>
-      <c r="E133" s="51">
+      <c r="E133" s="48">
         <v>42</v>
       </c>
-      <c r="F133" s="48">
+      <c r="F133" s="38">
         <v>63</v>
       </c>
       <c r="G133" s="24">
         <v>23</v>
       </c>
-      <c r="H133" s="46">
+      <c r="H133" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5632,16 +5633,16 @@
       <c r="D134" s="27">
         <v>49</v>
       </c>
-      <c r="E134" s="51">
+      <c r="E134" s="48">
         <v>66</v>
       </c>
-      <c r="F134" s="48">
+      <c r="F134" s="38">
         <v>81</v>
       </c>
       <c r="G134" s="28">
         <v>65</v>
       </c>
-      <c r="H134" s="46">
+      <c r="H134" s="45">
         <v>100</v>
       </c>
     </row>
@@ -5658,16 +5659,16 @@
       <c r="D135" s="27">
         <v>42</v>
       </c>
-      <c r="E135" s="51">
+      <c r="E135" s="48">
         <v>12</v>
       </c>
-      <c r="F135" s="48">
+      <c r="F135" s="38">
         <v>71</v>
       </c>
       <c r="G135" s="29">
         <v>45</v>
       </c>
-      <c r="H135" s="46">
+      <c r="H135" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5684,16 +5685,16 @@
       <c r="D136" s="20">
         <v>58</v>
       </c>
-      <c r="E136" s="51">
+      <c r="E136" s="48">
         <v>21</v>
       </c>
-      <c r="F136" s="48">
+      <c r="F136" s="38">
         <v>66</v>
       </c>
       <c r="G136" s="23">
         <v>58</v>
       </c>
-      <c r="H136" s="46">
+      <c r="H136" s="45">
         <v>100</v>
       </c>
     </row>
@@ -5710,16 +5711,16 @@
       <c r="D137" s="20">
         <v>45</v>
       </c>
-      <c r="E137" s="49">
+      <c r="E137" s="46">
         <v>26</v>
       </c>
-      <c r="F137" s="49">
+      <c r="F137" s="46">
         <v>67</v>
       </c>
       <c r="G137" s="25">
         <v>53</v>
       </c>
-      <c r="H137" s="46">
+      <c r="H137" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5736,16 +5737,16 @@
       <c r="D138" s="20">
         <v>29</v>
       </c>
-      <c r="E138" s="51">
+      <c r="E138" s="48">
         <v>38</v>
       </c>
-      <c r="F138" s="48">
+      <c r="F138" s="38">
         <v>58</v>
       </c>
       <c r="G138" s="24">
         <v>64</v>
       </c>
-      <c r="H138" s="46">
+      <c r="H138" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5762,16 +5763,16 @@
       <c r="D139" s="27">
         <v>38</v>
       </c>
-      <c r="E139" s="51">
+      <c r="E139" s="48">
         <v>37</v>
       </c>
-      <c r="F139" s="48">
+      <c r="F139" s="38">
         <v>45</v>
       </c>
       <c r="G139" s="24">
         <v>41</v>
       </c>
-      <c r="H139" s="46">
+      <c r="H139" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5788,16 +5789,16 @@
       <c r="D140" s="20">
         <v>66</v>
       </c>
-      <c r="E140" s="51">
+      <c r="E140" s="48">
         <v>80</v>
       </c>
-      <c r="F140" s="48">
+      <c r="F140" s="38">
         <v>71</v>
       </c>
       <c r="G140" s="24">
         <v>70</v>
       </c>
-      <c r="H140" s="46">
+      <c r="H140" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5814,16 +5815,16 @@
       <c r="D141" s="20">
         <v>17</v>
       </c>
-      <c r="E141" s="51">
+      <c r="E141" s="48">
         <v>32</v>
       </c>
-      <c r="F141" s="48">
+      <c r="F141" s="38">
         <v>32</v>
       </c>
       <c r="G141" s="24">
         <v>36</v>
       </c>
-      <c r="H141" s="46">
+      <c r="H141" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5840,16 +5841,16 @@
       <c r="D142" s="20">
         <v>45</v>
       </c>
-      <c r="E142" s="51">
+      <c r="E142" s="48">
         <v>67</v>
       </c>
-      <c r="F142" s="48">
+      <c r="F142" s="38">
         <v>61</v>
       </c>
       <c r="G142" s="24">
         <v>65</v>
       </c>
-      <c r="H142" s="46">
+      <c r="H142" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -5866,16 +5867,16 @@
       <c r="D143" s="27">
         <v>89</v>
       </c>
-      <c r="E143" s="51">
+      <c r="E143" s="48">
         <v>91</v>
       </c>
-      <c r="F143" s="48">
+      <c r="F143" s="38">
         <v>65</v>
       </c>
       <c r="G143" s="24">
         <v>72</v>
       </c>
-      <c r="H143" s="46">
+      <c r="H143" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -5892,16 +5893,16 @@
       <c r="D144" s="27">
         <v>76</v>
       </c>
-      <c r="E144" s="51">
+      <c r="E144" s="48">
         <v>32</v>
       </c>
-      <c r="F144" s="48">
+      <c r="F144" s="38">
         <v>79</v>
       </c>
       <c r="G144" s="24">
         <v>59</v>
       </c>
-      <c r="H144" s="46">
+      <c r="H144" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5918,16 +5919,16 @@
       <c r="D145" s="27">
         <v>76</v>
       </c>
-      <c r="E145" s="51">
+      <c r="E145" s="48">
         <v>71</v>
       </c>
-      <c r="F145" s="48">
+      <c r="F145" s="38">
         <v>63</v>
       </c>
       <c r="G145" s="24">
         <v>68</v>
       </c>
-      <c r="H145" s="46">
+      <c r="H145" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5944,16 +5945,16 @@
       <c r="D146" s="27">
         <v>86</v>
       </c>
-      <c r="E146" s="51">
+      <c r="E146" s="48">
         <v>60</v>
       </c>
-      <c r="F146" s="48">
+      <c r="F146" s="38">
         <v>74</v>
       </c>
       <c r="G146" s="24">
         <v>66</v>
       </c>
-      <c r="H146" s="46">
+      <c r="H146" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -5970,16 +5971,16 @@
       <c r="D147" s="20">
         <v>28</v>
       </c>
-      <c r="E147" s="51">
+      <c r="E147" s="48">
         <v>40</v>
       </c>
-      <c r="F147" s="48">
+      <c r="F147" s="38">
         <v>57</v>
       </c>
       <c r="G147" s="24">
         <v>12</v>
       </c>
-      <c r="H147" s="46">
+      <c r="H147" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -5996,16 +5997,16 @@
       <c r="D148" s="20">
         <v>73</v>
       </c>
-      <c r="E148" s="51">
+      <c r="E148" s="48">
         <v>38</v>
       </c>
-      <c r="F148" s="48">
+      <c r="F148" s="38">
         <v>71</v>
       </c>
       <c r="G148" s="24">
         <v>52</v>
       </c>
-      <c r="H148" s="46">
+      <c r="H148" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -6022,16 +6023,16 @@
       <c r="D149" s="27">
         <v>52</v>
       </c>
-      <c r="E149" s="51">
+      <c r="E149" s="48">
         <v>72</v>
       </c>
-      <c r="F149" s="48">
+      <c r="F149" s="38">
         <v>69</v>
       </c>
       <c r="G149" s="24">
         <v>28</v>
       </c>
-      <c r="H149" s="46">
+      <c r="H149" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -6048,7 +6049,7 @@
       <c r="D150" s="27">
         <v>48</v>
       </c>
-      <c r="E150" s="49">
+      <c r="E150" s="46">
         <v>18</v>
       </c>
       <c r="F150" s="20">
@@ -6057,7 +6058,7 @@
       <c r="G150" s="25">
         <v>44</v>
       </c>
-      <c r="H150" s="46">
+      <c r="H150" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -6074,16 +6075,16 @@
       <c r="D151" s="20">
         <v>43</v>
       </c>
-      <c r="E151" s="51">
+      <c r="E151" s="48">
         <v>43</v>
       </c>
-      <c r="F151" s="48">
+      <c r="F151" s="38">
         <v>73</v>
       </c>
       <c r="G151" s="24">
         <v>64</v>
       </c>
-      <c r="H151" s="46">
+      <c r="H151" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
@@ -6100,16 +6101,16 @@
       <c r="D152" s="20">
         <v>51</v>
       </c>
-      <c r="E152" s="51">
+      <c r="E152" s="48">
         <v>27</v>
       </c>
-      <c r="F152" s="48">
+      <c r="F152" s="38">
         <v>54</v>
       </c>
       <c r="G152" s="24">
         <v>44</v>
       </c>
-      <c r="H152" s="46">
+      <c r="H152" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6126,16 +6127,16 @@
       <c r="D153" s="27">
         <v>46</v>
       </c>
-      <c r="E153" s="51">
+      <c r="E153" s="48">
         <v>67</v>
       </c>
-      <c r="F153" s="48">
+      <c r="F153" s="38">
         <v>77</v>
       </c>
       <c r="G153" s="24">
         <v>59</v>
       </c>
-      <c r="H153" s="46">
+      <c r="H153" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6152,16 +6153,16 @@
       <c r="D154" s="21">
         <v>78</v>
       </c>
-      <c r="E154" s="51">
+      <c r="E154" s="48">
         <v>67</v>
       </c>
-      <c r="F154" s="48">
+      <c r="F154" s="38">
         <v>65</v>
       </c>
       <c r="G154" s="24">
         <v>72</v>
       </c>
-      <c r="H154" s="46">
+      <c r="H154" s="45">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -6178,16 +6179,16 @@
       <c r="D155" s="21">
         <v>85</v>
       </c>
-      <c r="E155" s="51">
+      <c r="E155" s="48">
         <v>56</v>
       </c>
-      <c r="F155" s="48">
+      <c r="F155" s="38">
         <v>72</v>
       </c>
       <c r="G155" s="24">
         <v>64</v>
       </c>
-      <c r="H155" s="46">
+      <c r="H155" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -6204,7 +6205,7 @@
       <c r="D156" s="20">
         <v>89</v>
       </c>
-      <c r="E156" s="49">
+      <c r="E156" s="46">
         <v>59</v>
       </c>
       <c r="F156" s="20">
@@ -6213,7 +6214,7 @@
       <c r="G156" s="25">
         <v>80</v>
       </c>
-      <c r="H156" s="46">
+      <c r="H156" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -6230,16 +6231,16 @@
       <c r="D157" s="20">
         <v>89</v>
       </c>
-      <c r="E157" s="51">
+      <c r="E157" s="48">
         <v>53</v>
       </c>
-      <c r="F157" s="48">
+      <c r="F157" s="38">
         <v>72</v>
       </c>
       <c r="G157" s="24">
         <v>67</v>
       </c>
-      <c r="H157" s="46">
+      <c r="H157" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -6256,16 +6257,16 @@
       <c r="D158" s="20">
         <v>86</v>
       </c>
-      <c r="E158" s="51">
+      <c r="E158" s="48">
         <v>67</v>
       </c>
-      <c r="F158" s="48">
+      <c r="F158" s="38">
         <v>79</v>
       </c>
       <c r="G158" s="24">
         <v>57</v>
       </c>
-      <c r="H158" s="46">
+      <c r="H158" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -6282,16 +6283,16 @@
       <c r="D159" s="21">
         <v>56</v>
       </c>
-      <c r="E159" s="39">
+      <c r="E159" s="38">
         <v>71</v>
       </c>
-      <c r="F159" s="48">
+      <c r="F159" s="38">
         <v>62</v>
       </c>
       <c r="G159" s="24">
         <v>70</v>
       </c>
-      <c r="H159" s="46">
+      <c r="H159" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -6308,16 +6309,16 @@
       <c r="D160" s="21">
         <v>76</v>
       </c>
-      <c r="E160" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="F160" s="48">
+      <c r="E160" s="48">
+        <v>30</v>
+      </c>
+      <c r="F160" s="38">
         <v>52</v>
       </c>
       <c r="G160" s="24">
         <v>70</v>
       </c>
-      <c r="H160" s="46">
+      <c r="H160" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -6334,16 +6335,16 @@
       <c r="D161" s="20">
         <v>34</v>
       </c>
-      <c r="E161" s="51">
+      <c r="E161" s="48">
         <v>49</v>
       </c>
-      <c r="F161" s="48">
+      <c r="F161" s="38">
         <v>58</v>
       </c>
       <c r="G161" s="24">
         <v>57</v>
       </c>
-      <c r="H161" s="46">
+      <c r="H161" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6360,16 +6361,16 @@
       <c r="D162" s="21">
         <v>38</v>
       </c>
-      <c r="E162" s="51">
+      <c r="E162" s="48">
         <v>57</v>
       </c>
-      <c r="F162" s="48">
+      <c r="F162" s="38">
         <v>73</v>
       </c>
       <c r="G162" s="24">
         <v>52</v>
       </c>
-      <c r="H162" s="46">
+      <c r="H162" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6386,16 +6387,16 @@
       <c r="D163" s="20">
         <v>55</v>
       </c>
-      <c r="E163" s="51">
+      <c r="E163" s="48">
         <v>45</v>
       </c>
-      <c r="F163" s="48">
+      <c r="F163" s="38">
         <v>69</v>
       </c>
       <c r="G163" s="24">
         <v>42</v>
       </c>
-      <c r="H163" s="46">
+      <c r="H163" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
@@ -6412,16 +6413,16 @@
       <c r="D164" s="21">
         <v>63</v>
       </c>
-      <c r="E164" s="51">
+      <c r="E164" s="48">
         <v>27</v>
       </c>
-      <c r="F164" s="48">
+      <c r="F164" s="38">
         <v>60</v>
       </c>
       <c r="G164" s="28">
         <v>49</v>
       </c>
-      <c r="H164" s="46">
+      <c r="H164" s="45">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -6432,22 +6433,22 @@
       <c r="B165" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C165" s="21" t="s">
-        <v>382</v>
+      <c r="C165" s="21">
+        <v>12</v>
       </c>
       <c r="D165" s="20">
         <v>74</v>
       </c>
-      <c r="E165" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="F165" s="48">
+      <c r="E165" s="48">
+        <v>19</v>
+      </c>
+      <c r="F165" s="38">
         <v>51</v>
       </c>
       <c r="G165" s="22">
         <v>61</v>
       </c>
-      <c r="H165" s="46">
+      <c r="H165" s="45">
         <v>65.217391300000003</v>
       </c>
     </row>
@@ -6464,16 +6465,16 @@
       <c r="D166" s="20">
         <v>44</v>
       </c>
-      <c r="E166" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="F166" s="48">
+      <c r="E166" s="48">
+        <v>51</v>
+      </c>
+      <c r="F166" s="38">
         <v>65</v>
       </c>
       <c r="G166" s="22">
         <v>47</v>
       </c>
-      <c r="H166" s="46">
+      <c r="H166" s="45">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -6490,16 +6491,16 @@
       <c r="D167" s="21">
         <v>69</v>
       </c>
-      <c r="E167" s="51">
+      <c r="E167" s="48">
         <v>62</v>
       </c>
-      <c r="F167" s="48">
+      <c r="F167" s="38">
         <v>66</v>
       </c>
       <c r="G167" s="22">
         <v>65</v>
       </c>
-      <c r="H167" s="46">
+      <c r="H167" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6516,16 +6517,16 @@
       <c r="D168" s="20">
         <v>93</v>
       </c>
-      <c r="E168" s="51">
+      <c r="E168" s="48">
         <v>39</v>
       </c>
-      <c r="F168" s="48">
+      <c r="F168" s="38">
         <v>79</v>
       </c>
       <c r="G168" s="22">
         <v>45</v>
       </c>
-      <c r="H168" s="46">
+      <c r="H168" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6542,16 +6543,16 @@
       <c r="D169" s="21">
         <v>55</v>
       </c>
-      <c r="E169" s="51">
+      <c r="E169" s="48">
         <v>54</v>
       </c>
-      <c r="F169" s="48">
+      <c r="F169" s="38">
         <v>75</v>
       </c>
       <c r="G169" s="22">
         <v>69</v>
       </c>
-      <c r="H169" s="46">
+      <c r="H169" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -6568,16 +6569,16 @@
       <c r="D170" s="21">
         <v>25</v>
       </c>
-      <c r="E170" s="52">
+      <c r="E170" s="49">
         <v>26</v>
       </c>
-      <c r="F170" s="50">
+      <c r="F170" s="47">
         <v>51</v>
       </c>
       <c r="G170" s="30">
         <v>33</v>
       </c>
-      <c r="H170" s="46">
+      <c r="H170" s="45">
         <v>47.826087000000001</v>
       </c>
     </row>
@@ -6594,16 +6595,16 @@
       <c r="D171" s="21">
         <v>50</v>
       </c>
-      <c r="E171" s="51">
+      <c r="E171" s="48">
         <v>14</v>
       </c>
-      <c r="F171" s="38">
+      <c r="F171" s="39">
         <v>53</v>
       </c>
       <c r="G171" s="31">
         <v>46</v>
       </c>
-      <c r="H171" s="46">
+      <c r="H171" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -6620,16 +6621,16 @@
       <c r="D172" s="21">
         <v>58</v>
       </c>
-      <c r="E172" s="51">
+      <c r="E172" s="48">
         <v>29</v>
       </c>
-      <c r="F172" s="38">
+      <c r="F172" s="39">
         <v>62</v>
       </c>
       <c r="G172" s="31">
         <v>26</v>
       </c>
-      <c r="H172" s="46">
+      <c r="H172" s="45">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -6646,16 +6647,16 @@
       <c r="D173" s="20">
         <v>65</v>
       </c>
-      <c r="E173" s="51">
+      <c r="E173" s="48">
         <v>32</v>
       </c>
-      <c r="F173" s="38">
+      <c r="F173" s="39">
         <v>69</v>
       </c>
       <c r="G173" s="31">
         <v>50</v>
       </c>
-      <c r="H173" s="46">
+      <c r="H173" s="45">
         <v>43.478260899999995</v>
       </c>
     </row>
@@ -6672,16 +6673,16 @@
       <c r="D174" s="20">
         <v>22</v>
       </c>
-      <c r="E174" s="51">
+      <c r="E174" s="48">
         <v>22</v>
       </c>
-      <c r="F174" s="38">
+      <c r="F174" s="39">
         <v>54</v>
       </c>
       <c r="G174" s="31">
         <v>51</v>
       </c>
-      <c r="H174" s="46">
+      <c r="H174" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6698,16 +6699,16 @@
       <c r="D175" s="21">
         <v>40</v>
       </c>
-      <c r="E175" s="51">
+      <c r="E175" s="48">
         <v>34</v>
       </c>
-      <c r="F175" s="38">
+      <c r="F175" s="39">
         <v>44</v>
       </c>
       <c r="G175" s="31">
         <v>60</v>
       </c>
-      <c r="H175" s="46">
+      <c r="H175" s="45">
         <v>30.434782599999998</v>
       </c>
     </row>
@@ -6724,16 +6725,16 @@
       <c r="D176" s="20">
         <v>23</v>
       </c>
-      <c r="E176" s="51">
+      <c r="E176" s="48">
         <v>19</v>
       </c>
-      <c r="F176" s="38">
+      <c r="F176" s="39">
         <v>62</v>
       </c>
       <c r="G176" s="31">
         <v>35</v>
       </c>
-      <c r="H176" s="46">
+      <c r="H176" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6750,16 +6751,16 @@
       <c r="D177" s="20">
         <v>81</v>
       </c>
-      <c r="E177" s="51">
+      <c r="E177" s="48">
         <v>57</v>
       </c>
-      <c r="F177" s="38">
+      <c r="F177" s="39">
         <v>73</v>
       </c>
       <c r="G177" s="31">
         <v>54</v>
       </c>
-      <c r="H177" s="46">
+      <c r="H177" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6776,16 +6777,16 @@
       <c r="D178" s="20">
         <v>94</v>
       </c>
-      <c r="E178" s="51">
+      <c r="E178" s="48">
         <v>49</v>
       </c>
-      <c r="F178" s="38">
+      <c r="F178" s="39">
         <v>62</v>
       </c>
       <c r="G178" s="31">
         <v>80</v>
       </c>
-      <c r="H178" s="46">
+      <c r="H178" s="45">
         <v>100</v>
       </c>
     </row>
@@ -6802,16 +6803,16 @@
       <c r="D179" s="20">
         <v>92</v>
       </c>
-      <c r="E179" s="51">
+      <c r="E179" s="48">
         <v>92</v>
       </c>
-      <c r="F179" s="38">
+      <c r="F179" s="39">
         <v>84</v>
       </c>
       <c r="G179" s="31">
         <v>88</v>
       </c>
-      <c r="H179" s="46">
+      <c r="H179" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -6828,16 +6829,16 @@
       <c r="D180" s="20">
         <v>25</v>
       </c>
-      <c r="E180" s="51">
+      <c r="E180" s="48">
         <v>12</v>
       </c>
-      <c r="F180" s="38">
+      <c r="F180" s="39">
         <v>53</v>
       </c>
       <c r="G180" s="31">
         <v>29</v>
       </c>
-      <c r="H180" s="46">
+      <c r="H180" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6854,16 +6855,16 @@
       <c r="D181" s="21">
         <v>70</v>
       </c>
-      <c r="E181" s="51">
+      <c r="E181" s="48">
         <v>43</v>
       </c>
-      <c r="F181" s="38">
+      <c r="F181" s="39">
         <v>50</v>
       </c>
       <c r="G181" s="31">
         <v>63</v>
       </c>
-      <c r="H181" s="46">
+      <c r="H181" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6883,13 +6884,13 @@
       <c r="E182" s="27">
         <v>37</v>
       </c>
-      <c r="F182" s="38">
+      <c r="F182" s="39">
         <v>58</v>
       </c>
       <c r="G182" s="31">
         <v>49</v>
       </c>
-      <c r="H182" s="46">
+      <c r="H182" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
@@ -6909,13 +6910,13 @@
       <c r="E183" s="27">
         <v>29</v>
       </c>
-      <c r="F183" s="38">
+      <c r="F183" s="39">
         <v>73</v>
       </c>
       <c r="G183" s="31">
         <v>59</v>
       </c>
-      <c r="H183" s="46">
+      <c r="H183" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6932,16 +6933,16 @@
       <c r="D184" s="21">
         <v>62</v>
       </c>
-      <c r="E184" s="51">
+      <c r="E184" s="48">
         <v>31</v>
       </c>
-      <c r="F184" s="38">
+      <c r="F184" s="39">
         <v>54</v>
       </c>
       <c r="G184" s="31">
         <v>74</v>
       </c>
-      <c r="H184" s="46">
+      <c r="H184" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
@@ -6958,16 +6959,16 @@
       <c r="D185" s="21">
         <v>57</v>
       </c>
-      <c r="E185" s="51">
+      <c r="E185" s="48">
         <v>61</v>
       </c>
-      <c r="F185" s="38">
+      <c r="F185" s="39">
         <v>57</v>
       </c>
       <c r="G185" s="31">
         <v>65</v>
       </c>
-      <c r="H185" s="46">
+      <c r="H185" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
@@ -6984,16 +6985,16 @@
       <c r="D186" s="21">
         <v>44</v>
       </c>
-      <c r="E186" s="51">
+      <c r="E186" s="48">
         <v>60</v>
       </c>
-      <c r="F186" s="38">
+      <c r="F186" s="39">
         <v>71</v>
       </c>
       <c r="G186" s="31">
         <v>69</v>
       </c>
-      <c r="H186" s="46">
+      <c r="H186" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
@@ -7013,13 +7014,13 @@
       <c r="E187" s="37">
         <v>57</v>
       </c>
-      <c r="F187" s="38">
+      <c r="F187" s="39">
         <v>63</v>
       </c>
       <c r="G187" s="32">
         <v>47</v>
       </c>
-      <c r="H187" s="46">
+      <c r="H187" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
@@ -7039,13 +7040,13 @@
       <c r="E188" s="27">
         <v>39</v>
       </c>
-      <c r="F188" s="38">
+      <c r="F188" s="39">
         <v>54</v>
       </c>
       <c r="G188" s="33">
         <v>29</v>
       </c>
-      <c r="H188" s="46">
+      <c r="H188" s="45">
         <v>60.869565199999997</v>
       </c>
     </row>
@@ -7062,10 +7063,10 @@
       <c r="D189" s="20">
         <v>56</v>
       </c>
-      <c r="E189" s="39">
+      <c r="E189" s="38">
         <v>14</v>
       </c>
-      <c r="F189" s="38">
+      <c r="F189" s="39">
         <v>58</v>
       </c>
       <c r="G189" s="33">
@@ -7086,10 +7087,10 @@
       <c r="D190" s="20">
         <v>72</v>
       </c>
-      <c r="E190" s="40">
+      <c r="E190" s="39">
         <v>65</v>
       </c>
-      <c r="F190" s="41">
+      <c r="F190" s="40">
         <v>71</v>
       </c>
       <c r="G190" s="20">
@@ -7110,10 +7111,10 @@
       <c r="D191" s="20">
         <v>69</v>
       </c>
-      <c r="E191" s="42">
+      <c r="E191" s="41">
         <v>65</v>
       </c>
-      <c r="F191" s="41">
+      <c r="F191" s="40">
         <v>54</v>
       </c>
       <c r="G191" s="21">
@@ -7137,7 +7138,7 @@
       <c r="E192" s="21">
         <v>33</v>
       </c>
-      <c r="F192" s="43" t="s">
+      <c r="F192" s="42" t="s">
         <v>382</v>
       </c>
       <c r="G192" s="21" t="s">
@@ -7161,7 +7162,7 @@
       <c r="E193" s="27">
         <v>10</v>
       </c>
-      <c r="F193" s="44">
+      <c r="F193" s="43">
         <v>47</v>
       </c>
       <c r="G193" s="21">
@@ -7182,10 +7183,10 @@
       <c r="D194" s="20">
         <v>31</v>
       </c>
-      <c r="E194" s="40" t="s">
+      <c r="E194" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="F194" s="41">
+      <c r="F194" s="40">
         <v>41</v>
       </c>
       <c r="G194" s="21">
@@ -7206,10 +7207,10 @@
       <c r="D195" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="E195" s="45">
+      <c r="E195" s="44">
         <v>29</v>
       </c>
-      <c r="F195" s="43">
+      <c r="F195" s="42">
         <v>48</v>
       </c>
       <c r="G195" s="21" t="s">
@@ -7230,10 +7231,10 @@
       <c r="D196" s="21">
         <v>84</v>
       </c>
-      <c r="E196" s="42">
+      <c r="E196" s="41">
         <v>79</v>
       </c>
-      <c r="F196" s="44">
+      <c r="F196" s="43">
         <v>44</v>
       </c>
       <c r="G196" s="21">
@@ -7257,7 +7258,7 @@
       <c r="E197" s="21">
         <v>11</v>
       </c>
-      <c r="F197" s="44" t="s">
+      <c r="F197" s="43" t="s">
         <v>382</v>
       </c>
       <c r="G197" s="21" t="s">
@@ -7281,7 +7282,7 @@
       <c r="E198" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="F198" s="44" t="s">
+      <c r="F198" s="43" t="s">
         <v>382</v>
       </c>
       <c r="G198" s="21" t="s">
@@ -7299,13 +7300,13 @@
       <c r="C199" s="35">
         <v>37</v>
       </c>
-      <c r="D199" s="35" t="s">
-        <v>382</v>
+      <c r="D199" s="35">
+        <v>30</v>
       </c>
       <c r="E199" s="21">
         <v>7</v>
       </c>
-      <c r="F199" s="42">
+      <c r="F199" s="41">
         <v>13</v>
       </c>
       <c r="G199" s="35">
@@ -7347,13 +7348,13 @@
       <c r="C201" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="D201" s="36" t="s">
-        <v>382</v>
+      <c r="D201" s="51">
+        <v>33</v>
       </c>
       <c r="E201" s="21">
         <v>10</v>
       </c>
-      <c r="F201" s="46">
+      <c r="F201" s="20">
         <v>38</v>
       </c>
       <c r="G201" s="21">
@@ -7368,6 +7369,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -7511,23 +7527,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
@@ -7549,7 +7550,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
--- a/MC3020_E24.xlsx
+++ b/MC3020_E24.xlsx
@@ -1,25 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment marks\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9DBB36-F5D5-4470-9EA1-7410A1F7B494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="409">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1251,11 +1263,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1306,11 +1318,6 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Palatino Linotype"/>
       <family val="1"/>
@@ -1320,13 +1327,6 @@
       <color rgb="FF000000"/>
       <name val="Palatino Linotype"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1343,64 +1343,25 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
+      <name val="Palatino Linotype"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Palatino Linotype"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -1754,197 +1715,164 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="10" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="10" borderId="10" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="20" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
-    <cellStyle name="60% - Accent1 2" xfId="1"/>
-    <cellStyle name="60% - Accent2 2" xfId="2"/>
-    <cellStyle name="60% - Accent3 2" xfId="3"/>
-    <cellStyle name="60% - Accent4 2" xfId="4"/>
-    <cellStyle name="60% - Accent5 2" xfId="5"/>
-    <cellStyle name="60% - Accent6 2" xfId="6"/>
+    <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="60% - Accent2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="60% - Accent3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="60% - Accent4 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="60% - Accent5 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="60% - Accent6 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Comma" xfId="10" builtinId="3"/>
-    <cellStyle name="Neutral 2" xfId="7"/>
+    <cellStyle name="Neutral 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="8"/>
-    <cellStyle name="Title 2" xfId="9"/>
+    <cellStyle name="Normal 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Title 2" xfId="9" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2220,15 +2148,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="9" customWidth="1"/>
+    <col min="3" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="50" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="53" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="9" customWidth="1"/>
     <col min="10" max="10" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2248,7 +2178,7 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="52" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
@@ -2259,3963 +2189,5157 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="51">
+      <c r="C2" s="20">
         <v>24</v>
       </c>
-      <c r="D2" s="52">
+      <c r="D2" s="21">
         <v>54</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="48">
+      <c r="E2" s="46">
+        <v>45</v>
+      </c>
+      <c r="F2" s="27">
+        <v>51</v>
+      </c>
+      <c r="G2" s="22">
+        <v>77</v>
+      </c>
+      <c r="H2" s="45">
         <v>65.217391300000003</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="51">
+      <c r="C3" s="20">
         <v>39</v>
       </c>
-      <c r="D3" s="52">
+      <c r="D3" s="21">
         <v>75</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="48">
+      <c r="E3" s="48">
+        <v>99</v>
+      </c>
+      <c r="F3" s="38">
+        <v>77</v>
+      </c>
+      <c r="G3" s="23">
+        <v>76</v>
+      </c>
+      <c r="H3" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="51">
+      <c r="C4" s="20">
         <v>43</v>
       </c>
-      <c r="D4" s="51">
+      <c r="D4" s="20">
         <v>71</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="48">
+      <c r="E4" s="39">
+        <v>50</v>
+      </c>
+      <c r="F4" s="38">
+        <v>74</v>
+      </c>
+      <c r="G4" s="24">
+        <v>57</v>
+      </c>
+      <c r="H4" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="51">
+      <c r="C5" s="20">
         <v>30</v>
       </c>
-      <c r="D5" s="51">
+      <c r="D5" s="20">
         <v>38</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="48">
+      <c r="E5" s="48">
+        <v>21</v>
+      </c>
+      <c r="F5" s="38">
+        <v>65</v>
+      </c>
+      <c r="G5" s="24">
+        <v>34</v>
+      </c>
+      <c r="H5" s="45">
         <v>30.434782599999998</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="51">
+      <c r="C6" s="20">
         <v>18</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="20">
         <v>37</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="48">
+      <c r="E6" s="48">
+        <v>40</v>
+      </c>
+      <c r="F6" s="38">
+        <v>69</v>
+      </c>
+      <c r="G6" s="24">
+        <v>48</v>
+      </c>
+      <c r="H6" s="45">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="20">
         <v>12</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="21">
         <v>34</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="48">
+      <c r="E7" s="48">
+        <v>16</v>
+      </c>
+      <c r="F7" s="38">
+        <v>68</v>
+      </c>
+      <c r="G7" s="24">
+        <v>54</v>
+      </c>
+      <c r="H7" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="20">
         <v>69</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="21">
         <v>83</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="48">
+      <c r="E8" s="48">
+        <v>51</v>
+      </c>
+      <c r="F8" s="38">
+        <v>72</v>
+      </c>
+      <c r="G8" s="24">
+        <v>76</v>
+      </c>
+      <c r="H8" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="20">
         <v>43</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="21">
         <v>68</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="48">
+      <c r="E9" s="48">
+        <v>66</v>
+      </c>
+      <c r="F9" s="38">
+        <v>58</v>
+      </c>
+      <c r="G9" s="24">
+        <v>59</v>
+      </c>
+      <c r="H9" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="10" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="20">
         <v>38</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="20">
         <v>55</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="48">
+      <c r="E10" s="48">
+        <v>47</v>
+      </c>
+      <c r="F10" s="38">
+        <v>50</v>
+      </c>
+      <c r="G10" s="24">
+        <v>61</v>
+      </c>
+      <c r="H10" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="10" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="51">
+      <c r="C11" s="20">
         <v>16</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="21">
         <v>28</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="48">
+      <c r="E11" s="48">
+        <v>45</v>
+      </c>
+      <c r="F11" s="38">
+        <v>54</v>
+      </c>
+      <c r="G11" s="24">
+        <v>24</v>
+      </c>
+      <c r="H11" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="20">
         <v>84</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="20">
         <v>59</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="48">
+      <c r="E12" s="48">
+        <v>76</v>
+      </c>
+      <c r="F12" s="38">
+        <v>67</v>
+      </c>
+      <c r="G12" s="24">
+        <v>60</v>
+      </c>
+      <c r="H12" s="45">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="10" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="51">
+      <c r="C13" s="20">
         <v>39</v>
       </c>
-      <c r="D13" s="52">
+      <c r="D13" s="21">
         <v>43</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="48">
+      <c r="E13" s="48">
+        <v>30</v>
+      </c>
+      <c r="F13" s="38">
+        <v>63</v>
+      </c>
+      <c r="G13" s="24">
+        <v>55</v>
+      </c>
+      <c r="H13" s="45">
         <v>90.909090899999995</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="10" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="51">
+      <c r="C14" s="20">
         <v>61</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="20">
         <v>89</v>
       </c>
-      <c r="E14" s="18"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="48">
+      <c r="E14" s="48">
+        <v>88</v>
+      </c>
+      <c r="F14" s="38">
+        <v>74</v>
+      </c>
+      <c r="G14" s="24">
+        <v>76</v>
+      </c>
+      <c r="H14" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="10" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="51">
+      <c r="C15" s="20">
         <v>80</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="21">
         <v>42</v>
       </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="48">
+      <c r="E15" s="48">
+        <v>82</v>
+      </c>
+      <c r="F15" s="38">
+        <v>85</v>
+      </c>
+      <c r="G15" s="24">
+        <v>55</v>
+      </c>
+      <c r="H15" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="10" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="51">
+      <c r="C16" s="20">
         <v>33</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="20">
         <v>46</v>
       </c>
-      <c r="E16" s="19"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="48">
+      <c r="E16" s="46">
+        <v>57</v>
+      </c>
+      <c r="F16" s="46">
+        <v>78</v>
+      </c>
+      <c r="G16" s="25">
+        <v>56</v>
+      </c>
+      <c r="H16" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="10" t="s">
         <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="20">
         <v>45</v>
       </c>
-      <c r="D17" s="52">
+      <c r="D17" s="21">
         <v>68</v>
       </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="48">
+      <c r="E17" s="48">
+        <v>78</v>
+      </c>
+      <c r="F17" s="38">
+        <v>73</v>
+      </c>
+      <c r="G17" s="24">
+        <v>87</v>
+      </c>
+      <c r="H17" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="51">
+      <c r="C18" s="20">
         <v>52</v>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="20">
         <v>54</v>
       </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="48">
+      <c r="E18" s="48">
+        <v>52</v>
+      </c>
+      <c r="F18" s="38">
+        <v>58</v>
+      </c>
+      <c r="G18" s="24">
+        <v>75</v>
+      </c>
+      <c r="H18" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="10" t="s">
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="51">
+      <c r="C19" s="20">
         <v>86</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="20">
         <v>94</v>
       </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="48">
+      <c r="E19" s="48">
+        <v>88</v>
+      </c>
+      <c r="F19" s="38">
+        <v>61</v>
+      </c>
+      <c r="G19" s="24">
+        <v>83</v>
+      </c>
+      <c r="H19" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="10" t="s">
         <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="51">
+      <c r="C20" s="20">
         <v>76</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="20">
         <v>78</v>
       </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="48">
+      <c r="E20" s="48">
+        <v>55</v>
+      </c>
+      <c r="F20" s="38">
+        <v>63</v>
+      </c>
+      <c r="G20" s="24">
+        <v>63</v>
+      </c>
+      <c r="H20" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="51">
+      <c r="C21" s="20">
         <v>99</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="20">
         <v>84</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="48">
+      <c r="E21" s="48">
+        <v>71</v>
+      </c>
+      <c r="F21" s="38">
+        <v>81</v>
+      </c>
+      <c r="G21" s="24">
+        <v>74</v>
+      </c>
+      <c r="H21" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="10" t="s">
         <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="51">
+      <c r="C22" s="20">
         <v>34</v>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="21">
         <v>51</v>
       </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="48">
+      <c r="E22" s="48">
+        <v>58</v>
+      </c>
+      <c r="F22" s="38">
+        <v>78</v>
+      </c>
+      <c r="G22" s="24">
+        <v>38</v>
+      </c>
+      <c r="H22" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="10" t="s">
         <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="51">
+      <c r="C23" s="20">
         <v>71</v>
       </c>
-      <c r="D23" s="52">
+      <c r="D23" s="21">
         <v>87</v>
       </c>
-      <c r="E23" s="18"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="48">
+      <c r="E23" s="48">
+        <v>65</v>
+      </c>
+      <c r="F23" s="38">
+        <v>78</v>
+      </c>
+      <c r="G23" s="24">
+        <v>76</v>
+      </c>
+      <c r="H23" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="51">
+      <c r="C24" s="20">
         <v>64</v>
       </c>
-      <c r="D24" s="52">
+      <c r="D24" s="21">
         <v>40</v>
       </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="48">
+      <c r="E24" s="48">
+        <v>48</v>
+      </c>
+      <c r="F24" s="38">
+        <v>71</v>
+      </c>
+      <c r="G24" s="24">
+        <v>44</v>
+      </c>
+      <c r="H24" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="D25" s="52">
+      <c r="C25" s="20">
+        <v>100</v>
+      </c>
+      <c r="D25" s="21">
         <v>63</v>
       </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="48">
+      <c r="E25" s="48">
+        <v>92</v>
+      </c>
+      <c r="F25" s="38">
+        <v>67</v>
+      </c>
+      <c r="G25" s="24">
+        <v>67</v>
+      </c>
+      <c r="H25" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="10" t="s">
         <v>57</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="51">
+      <c r="C26" s="20">
         <v>68</v>
       </c>
-      <c r="D26" s="52">
+      <c r="D26" s="21">
         <v>73</v>
       </c>
-      <c r="E26" s="18"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="48">
+      <c r="E26" s="48">
+        <v>77</v>
+      </c>
+      <c r="F26" s="38">
+        <v>73</v>
+      </c>
+      <c r="G26" s="24">
+        <v>71</v>
+      </c>
+      <c r="H26" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="51">
+      <c r="C27" s="20">
         <v>43</v>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="20">
         <v>72</v>
       </c>
-      <c r="E27" s="18"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="48">
+      <c r="E27" s="48">
+        <v>81</v>
+      </c>
+      <c r="F27" s="38">
+        <v>64</v>
+      </c>
+      <c r="G27" s="24">
+        <v>82</v>
+      </c>
+      <c r="H27" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="10" t="s">
         <v>61</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="51">
+      <c r="C28" s="20">
         <v>30</v>
       </c>
-      <c r="D28" s="52">
+      <c r="D28" s="21">
         <v>85</v>
       </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="48">
+      <c r="E28" s="48">
+        <v>63</v>
+      </c>
+      <c r="F28" s="38">
+        <v>63</v>
+      </c>
+      <c r="G28" s="24">
+        <v>62</v>
+      </c>
+      <c r="H28" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="10" t="s">
         <v>63</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="51">
+      <c r="C29" s="20">
         <v>65</v>
       </c>
-      <c r="D29" s="52">
+      <c r="D29" s="21">
         <v>84</v>
       </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="48">
+      <c r="E29" s="48">
+        <v>35</v>
+      </c>
+      <c r="F29" s="38">
+        <v>66</v>
+      </c>
+      <c r="G29" s="24">
+        <v>75</v>
+      </c>
+      <c r="H29" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="10" t="s">
         <v>65</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="20">
         <v>69</v>
       </c>
-      <c r="D30" s="52">
+      <c r="D30" s="21">
         <v>25</v>
       </c>
-      <c r="E30" s="18"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="48">
+      <c r="E30" s="48">
+        <v>69</v>
+      </c>
+      <c r="F30" s="38">
+        <v>84</v>
+      </c>
+      <c r="G30" s="24">
+        <v>63</v>
+      </c>
+      <c r="H30" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="10" t="s">
         <v>67</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="51">
+      <c r="C31" s="20">
         <v>44</v>
       </c>
-      <c r="D31" s="52">
+      <c r="D31" s="21">
         <v>34</v>
       </c>
-      <c r="E31" s="18"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="48">
+      <c r="E31" s="48">
+        <v>38</v>
+      </c>
+      <c r="F31" s="38">
+        <v>78</v>
+      </c>
+      <c r="G31" s="26">
+        <v>61</v>
+      </c>
+      <c r="H31" s="45">
         <v>47.826087000000001</v>
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="10" t="s">
         <v>69</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="51">
+      <c r="C32" s="20">
         <v>61</v>
       </c>
-      <c r="D32" s="52">
+      <c r="D32" s="21">
         <v>85</v>
       </c>
-      <c r="E32" s="18"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="48">
+      <c r="E32" s="48">
+        <v>61</v>
+      </c>
+      <c r="F32" s="38">
+        <v>78</v>
+      </c>
+      <c r="G32" s="24">
+        <v>81</v>
+      </c>
+      <c r="H32" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="51">
+      <c r="C33" s="20">
         <v>49</v>
       </c>
-      <c r="D33" s="52">
+      <c r="D33" s="21">
         <v>67</v>
       </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="48">
+      <c r="E33" s="48">
+        <v>67</v>
+      </c>
+      <c r="F33" s="38">
+        <v>67</v>
+      </c>
+      <c r="G33" s="24">
+        <v>71</v>
+      </c>
+      <c r="H33" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="10" t="s">
         <v>73</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="51">
+      <c r="C34" s="20">
         <v>50</v>
       </c>
-      <c r="D34" s="52">
+      <c r="D34" s="21">
         <v>45</v>
       </c>
-      <c r="E34" s="18"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="48">
+      <c r="E34" s="48">
+        <v>27</v>
+      </c>
+      <c r="F34" s="38">
+        <v>51</v>
+      </c>
+      <c r="G34" s="24">
+        <v>43</v>
+      </c>
+      <c r="H34" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="10" t="s">
         <v>75</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="51">
+      <c r="C35" s="20">
         <v>48</v>
       </c>
-      <c r="D35" s="51">
+      <c r="D35" s="20">
         <v>55</v>
       </c>
-      <c r="E35" s="18"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="48">
+      <c r="E35" s="48">
+        <v>74</v>
+      </c>
+      <c r="F35" s="38">
+        <v>67</v>
+      </c>
+      <c r="G35" s="24">
+        <v>56</v>
+      </c>
+      <c r="H35" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="10" t="s">
         <v>77</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="51">
+      <c r="C36" s="20">
         <v>49</v>
       </c>
-      <c r="D36" s="52">
+      <c r="D36" s="21">
         <v>57</v>
       </c>
-      <c r="E36" s="18"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="48">
+      <c r="E36" s="48">
+        <v>65</v>
+      </c>
+      <c r="F36" s="38">
+        <v>60</v>
+      </c>
+      <c r="G36" s="24">
+        <v>49</v>
+      </c>
+      <c r="H36" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="10" t="s">
         <v>79</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="51">
+      <c r="C37" s="20">
         <v>58</v>
       </c>
-      <c r="D37" s="52">
+      <c r="D37" s="21">
         <v>41</v>
       </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="48">
+      <c r="E37" s="48">
+        <v>28</v>
+      </c>
+      <c r="F37" s="38">
+        <v>63</v>
+      </c>
+      <c r="G37" s="24">
+        <v>54</v>
+      </c>
+      <c r="H37" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="10" t="s">
         <v>81</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="51">
+      <c r="C38" s="20">
         <v>81</v>
       </c>
-      <c r="D38" s="52">
+      <c r="D38" s="21">
         <v>84</v>
       </c>
-      <c r="E38" s="18"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="48">
+      <c r="E38" s="48">
+        <v>73</v>
+      </c>
+      <c r="F38" s="38">
+        <v>71</v>
+      </c>
+      <c r="G38" s="24">
+        <v>72</v>
+      </c>
+      <c r="H38" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="10" t="s">
         <v>83</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="51">
+      <c r="C39" s="20">
         <v>23</v>
       </c>
-      <c r="D39" s="52">
+      <c r="D39" s="21">
         <v>61</v>
       </c>
-      <c r="E39" s="18"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="48">
+      <c r="E39" s="48">
+        <v>75</v>
+      </c>
+      <c r="F39" s="38">
+        <v>56</v>
+      </c>
+      <c r="G39" s="24">
+        <v>58</v>
+      </c>
+      <c r="H39" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="10" t="s">
         <v>85</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="51">
+      <c r="C40" s="20">
         <v>32</v>
       </c>
-      <c r="D40" s="51">
+      <c r="D40" s="20">
         <v>37</v>
       </c>
-      <c r="E40" s="18"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="48">
+      <c r="E40" s="48">
+        <v>80</v>
+      </c>
+      <c r="F40" s="38">
+        <v>70</v>
+      </c>
+      <c r="G40" s="24">
+        <v>57</v>
+      </c>
+      <c r="H40" s="45">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="10" t="s">
         <v>87</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="51">
+      <c r="C41" s="20">
         <v>18</v>
       </c>
-      <c r="D41" s="51">
+      <c r="D41" s="20">
         <v>52</v>
       </c>
-      <c r="E41" s="18"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="48">
+      <c r="E41" s="48">
+        <v>59</v>
+      </c>
+      <c r="F41" s="38">
+        <v>47</v>
+      </c>
+      <c r="G41" s="24">
+        <v>37</v>
+      </c>
+      <c r="H41" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="10" t="s">
         <v>89</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="51">
+      <c r="C42" s="20">
         <v>46</v>
       </c>
-      <c r="D42" s="52">
+      <c r="D42" s="21">
         <v>75</v>
       </c>
-      <c r="E42" s="18"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="48">
+      <c r="E42" s="48">
+        <v>41</v>
+      </c>
+      <c r="F42" s="38">
+        <v>63</v>
+      </c>
+      <c r="G42" s="24">
+        <v>67</v>
+      </c>
+      <c r="H42" s="45">
         <v>56.521739100000005</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="10" t="s">
         <v>91</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="51">
+      <c r="C43" s="20">
         <v>53</v>
       </c>
-      <c r="D43" s="51">
+      <c r="D43" s="20">
         <v>50</v>
       </c>
-      <c r="E43" s="18"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="48">
+      <c r="E43" s="48">
+        <v>59</v>
+      </c>
+      <c r="F43" s="38">
+        <v>75</v>
+      </c>
+      <c r="G43" s="24">
+        <v>69</v>
+      </c>
+      <c r="H43" s="45">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="10" t="s">
         <v>93</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="51">
+      <c r="C44" s="20">
         <v>60</v>
       </c>
-      <c r="D44" s="51">
+      <c r="D44" s="20">
         <v>39</v>
       </c>
-      <c r="E44" s="18"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="48">
+      <c r="E44" s="48">
+        <v>31</v>
+      </c>
+      <c r="F44" s="38">
+        <v>65</v>
+      </c>
+      <c r="G44" s="24">
+        <v>35</v>
+      </c>
+      <c r="H44" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="10" t="s">
         <v>95</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C45" s="51">
+      <c r="C45" s="20">
         <v>58</v>
       </c>
-      <c r="D45" s="52">
+      <c r="D45" s="21">
         <v>79</v>
       </c>
-      <c r="E45" s="18"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="48">
+      <c r="E45" s="48">
+        <v>56</v>
+      </c>
+      <c r="F45" s="38">
+        <v>59</v>
+      </c>
+      <c r="G45" s="24">
+        <v>72</v>
+      </c>
+      <c r="H45" s="45">
         <v>56.521739100000005</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="10" t="s">
         <v>97</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C46" s="51">
+      <c r="C46" s="20">
         <v>60</v>
       </c>
-      <c r="D46" s="51">
+      <c r="D46" s="20">
         <v>70</v>
       </c>
-      <c r="E46" s="18"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="48">
+      <c r="E46" s="48">
+        <v>56</v>
+      </c>
+      <c r="F46" s="38">
+        <v>49</v>
+      </c>
+      <c r="G46" s="24">
+        <v>45</v>
+      </c>
+      <c r="H46" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="10" t="s">
         <v>99</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="51">
+      <c r="C47" s="20">
         <v>18</v>
       </c>
-      <c r="D47" s="52">
+      <c r="D47" s="21">
         <v>64</v>
       </c>
-      <c r="E47" s="18"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="40"/>
-      <c r="H47" s="48">
+      <c r="E47" s="48">
+        <v>91</v>
+      </c>
+      <c r="F47" s="38">
+        <v>12</v>
+      </c>
+      <c r="G47" s="24">
+        <v>55</v>
+      </c>
+      <c r="H47" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="10" t="s">
         <v>101</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="51">
+      <c r="C48" s="20">
         <v>77</v>
       </c>
-      <c r="D48" s="52">
+      <c r="D48" s="21">
         <v>64</v>
       </c>
-      <c r="E48" s="18"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="42"/>
-      <c r="H48" s="48">
+      <c r="E48" s="48">
+        <v>71</v>
+      </c>
+      <c r="F48" s="38">
+        <v>76</v>
+      </c>
+      <c r="G48" s="26">
+        <v>64</v>
+      </c>
+      <c r="H48" s="45">
         <v>21.739130400000001</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="10" t="s">
         <v>103</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="51">
+      <c r="C49" s="20">
         <v>36</v>
       </c>
-      <c r="D49" s="52">
+      <c r="D49" s="21">
         <v>81</v>
       </c>
-      <c r="E49" s="18"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="48">
+      <c r="E49" s="48">
+        <v>79</v>
+      </c>
+      <c r="F49" s="38">
+        <v>83</v>
+      </c>
+      <c r="G49" s="24">
+        <v>39</v>
+      </c>
+      <c r="H49" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="10" t="s">
         <v>105</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="51">
+      <c r="C50" s="20">
         <v>47</v>
       </c>
-      <c r="D50" s="52">
+      <c r="D50" s="21">
         <v>63</v>
       </c>
-      <c r="E50" s="18"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="48">
+      <c r="E50" s="48">
+        <v>41</v>
+      </c>
+      <c r="F50" s="38">
+        <v>74</v>
+      </c>
+      <c r="G50" s="24">
+        <v>68</v>
+      </c>
+      <c r="H50" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="10" t="s">
         <v>107</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C51" s="51">
+      <c r="C51" s="20">
         <v>59</v>
       </c>
-      <c r="D51" s="51">
+      <c r="D51" s="20">
         <v>90</v>
       </c>
-      <c r="E51" s="18"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="48">
+      <c r="E51" s="48">
+        <v>53</v>
+      </c>
+      <c r="F51" s="38">
+        <v>72</v>
+      </c>
+      <c r="G51" s="24">
+        <v>67</v>
+      </c>
+      <c r="H51" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="10" t="s">
         <v>109</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="51">
+      <c r="C52" s="20">
         <v>68</v>
       </c>
-      <c r="D52" s="51">
+      <c r="D52" s="20">
         <v>42</v>
       </c>
-      <c r="E52" s="18"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="48">
+      <c r="E52" s="48">
+        <v>52</v>
+      </c>
+      <c r="F52" s="38">
+        <v>58</v>
+      </c>
+      <c r="G52" s="24">
+        <v>41</v>
+      </c>
+      <c r="H52" s="45">
         <v>47.826087000000001</v>
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="10" t="s">
         <v>111</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C53" s="51">
+      <c r="C53" s="20">
         <v>41</v>
       </c>
-      <c r="D53" s="52">
+      <c r="D53" s="21">
         <v>60</v>
       </c>
-      <c r="E53" s="18"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="48">
+      <c r="E53" s="48">
+        <v>24</v>
+      </c>
+      <c r="F53" s="38">
+        <v>60</v>
+      </c>
+      <c r="G53" s="24">
+        <v>39</v>
+      </c>
+      <c r="H53" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="10" t="s">
         <v>113</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C54" s="51">
+      <c r="C54" s="20">
         <v>54</v>
       </c>
-      <c r="D54" s="51">
+      <c r="D54" s="20">
         <v>76</v>
       </c>
-      <c r="E54" s="18"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="48">
+      <c r="E54" s="48">
+        <v>97</v>
+      </c>
+      <c r="F54" s="38">
+        <v>59</v>
+      </c>
+      <c r="G54" s="24">
+        <v>68</v>
+      </c>
+      <c r="H54" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="10" t="s">
         <v>115</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="51">
+      <c r="C55" s="20">
         <v>51</v>
       </c>
-      <c r="D55" s="52">
+      <c r="D55" s="21">
         <v>89</v>
       </c>
-      <c r="E55" s="18"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="42"/>
-      <c r="H55" s="48">
+      <c r="E55" s="48">
+        <v>85</v>
+      </c>
+      <c r="F55" s="38">
+        <v>76</v>
+      </c>
+      <c r="G55" s="26">
+        <v>84</v>
+      </c>
+      <c r="H55" s="45">
         <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="10" t="s">
         <v>117</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C56" s="51">
+      <c r="C56" s="20">
         <v>100</v>
       </c>
-      <c r="D56" s="52">
+      <c r="D56" s="21">
         <v>96</v>
       </c>
-      <c r="E56" s="18"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="48">
+      <c r="E56" s="48">
+        <v>67</v>
+      </c>
+      <c r="F56" s="38">
+        <v>54</v>
+      </c>
+      <c r="G56" s="24">
+        <v>63</v>
+      </c>
+      <c r="H56" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="10" t="s">
         <v>119</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C57" s="51">
+      <c r="C57" s="20">
         <v>21</v>
       </c>
-      <c r="D57" s="52">
+      <c r="D57" s="21">
         <v>37</v>
       </c>
-      <c r="E57" s="18"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="48">
+      <c r="E57" s="48">
+        <v>45</v>
+      </c>
+      <c r="F57" s="38">
+        <v>53</v>
+      </c>
+      <c r="G57" s="24">
+        <v>49</v>
+      </c>
+      <c r="H57" s="45">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="10" t="s">
         <v>121</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C58" s="51">
+      <c r="C58" s="20">
         <v>32</v>
       </c>
-      <c r="D58" s="51">
+      <c r="D58" s="20">
         <v>20</v>
       </c>
-      <c r="E58" s="18"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="48">
+      <c r="E58" s="48">
+        <v>38</v>
+      </c>
+      <c r="F58" s="38">
+        <v>43</v>
+      </c>
+      <c r="G58" s="24">
+        <v>28</v>
+      </c>
+      <c r="H58" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="10" t="s">
         <v>123</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="51">
+      <c r="C59" s="20">
         <v>23</v>
       </c>
-      <c r="D59" s="52">
+      <c r="D59" s="21">
         <v>36</v>
       </c>
-      <c r="E59" s="18"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="40"/>
-      <c r="H59" s="48">
+      <c r="E59" s="48">
+        <v>36</v>
+      </c>
+      <c r="F59" s="38">
+        <v>72</v>
+      </c>
+      <c r="G59" s="24">
+        <v>44</v>
+      </c>
+      <c r="H59" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A60" s="16" t="s">
+      <c r="A60" s="10" t="s">
         <v>125</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C60" s="51">
+      <c r="C60" s="20">
         <v>42</v>
       </c>
-      <c r="D60" s="52">
+      <c r="D60" s="21">
         <v>28</v>
       </c>
-      <c r="E60" s="19"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="41"/>
-      <c r="H60" s="48">
+      <c r="E60" s="46">
+        <v>62</v>
+      </c>
+      <c r="F60" s="46">
+        <v>68</v>
+      </c>
+      <c r="G60" s="25">
+        <v>60</v>
+      </c>
+      <c r="H60" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="16" t="s">
+      <c r="A61" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="51">
+      <c r="C61" s="20">
         <v>58</v>
       </c>
-      <c r="D61" s="52">
+      <c r="D61" s="21">
         <v>68</v>
       </c>
-      <c r="E61" s="18"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="40"/>
-      <c r="H61" s="48">
+      <c r="E61" s="48">
+        <v>81</v>
+      </c>
+      <c r="F61" s="38">
+        <v>64</v>
+      </c>
+      <c r="G61" s="24">
+        <v>86</v>
+      </c>
+      <c r="H61" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="10" t="s">
         <v>129</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C62" s="51">
+      <c r="C62" s="20">
         <v>64</v>
       </c>
-      <c r="D62" s="52" t="s">
-        <v>382</v>
-      </c>
-      <c r="E62" s="18"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="40"/>
-      <c r="H62" s="48">
+      <c r="D62" s="21">
+        <v>76</v>
+      </c>
+      <c r="E62" s="48">
+        <v>55</v>
+      </c>
+      <c r="F62" s="38">
+        <v>52</v>
+      </c>
+      <c r="G62" s="24">
+        <v>52</v>
+      </c>
+      <c r="H62" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="10" t="s">
         <v>131</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C63" s="51">
+      <c r="C63" s="20">
         <v>54</v>
       </c>
-      <c r="D63" s="52">
+      <c r="D63" s="21">
         <v>57</v>
       </c>
-      <c r="E63" s="18"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="40"/>
-      <c r="H63" s="48">
+      <c r="E63" s="48">
+        <v>76</v>
+      </c>
+      <c r="F63" s="38">
+        <v>61</v>
+      </c>
+      <c r="G63" s="24">
+        <v>64</v>
+      </c>
+      <c r="H63" s="45">
         <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="10" t="s">
         <v>133</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C64" s="51">
+      <c r="C64" s="20">
         <v>30</v>
       </c>
-      <c r="D64" s="52">
+      <c r="D64" s="21">
         <v>40</v>
       </c>
-      <c r="E64" s="18"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="40"/>
-      <c r="H64" s="48">
+      <c r="E64" s="48">
+        <v>53</v>
+      </c>
+      <c r="F64" s="38">
+        <v>65</v>
+      </c>
+      <c r="G64" s="24">
+        <v>46</v>
+      </c>
+      <c r="H64" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="16" t="s">
+      <c r="A65" s="10" t="s">
         <v>135</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="51">
+      <c r="C65" s="20">
         <v>30</v>
       </c>
-      <c r="D65" s="52">
+      <c r="D65" s="21">
         <v>48</v>
       </c>
-      <c r="E65" s="18"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="40"/>
-      <c r="H65" s="48">
+      <c r="E65" s="48">
+        <v>49</v>
+      </c>
+      <c r="F65" s="38">
+        <v>58</v>
+      </c>
+      <c r="G65" s="24">
+        <v>47</v>
+      </c>
+      <c r="H65" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="16" t="s">
+      <c r="A66" s="10" t="s">
         <v>137</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C66" s="51">
+      <c r="C66" s="20">
         <v>47</v>
       </c>
-      <c r="D66" s="52">
+      <c r="D66" s="21">
         <v>84</v>
       </c>
-      <c r="E66" s="18"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="48">
+      <c r="E66" s="48">
+        <v>23</v>
+      </c>
+      <c r="F66" s="38">
+        <v>73</v>
+      </c>
+      <c r="G66" s="24">
+        <v>54</v>
+      </c>
+      <c r="H66" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="10" t="s">
         <v>139</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C67" s="51">
+      <c r="C67" s="20">
         <v>38</v>
       </c>
-      <c r="D67" s="52">
+      <c r="D67" s="21">
         <v>50</v>
       </c>
-      <c r="E67" s="18"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="40"/>
-      <c r="H67" s="48">
+      <c r="E67" s="48">
+        <v>30</v>
+      </c>
+      <c r="F67" s="38">
+        <v>60</v>
+      </c>
+      <c r="G67" s="24">
+        <v>27</v>
+      </c>
+      <c r="H67" s="45">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="10" t="s">
         <v>141</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C68" s="51">
+      <c r="C68" s="20">
         <v>47</v>
       </c>
-      <c r="D68" s="52">
+      <c r="D68" s="21">
         <v>73</v>
       </c>
-      <c r="E68" s="18"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="42"/>
-      <c r="H68" s="48">
+      <c r="E68" s="48">
+        <v>61</v>
+      </c>
+      <c r="F68" s="38">
+        <v>76</v>
+      </c>
+      <c r="G68" s="26">
+        <v>62</v>
+      </c>
+      <c r="H68" s="45">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="10" t="s">
         <v>143</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C69" s="51">
+      <c r="C69" s="20">
         <v>36</v>
       </c>
-      <c r="D69" s="51">
+      <c r="D69" s="20">
         <v>17</v>
       </c>
-      <c r="E69" s="18"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="40"/>
-      <c r="H69" s="48">
+      <c r="E69" s="48">
+        <v>36</v>
+      </c>
+      <c r="F69" s="38">
+        <v>66</v>
+      </c>
+      <c r="G69" s="24">
+        <v>28</v>
+      </c>
+      <c r="H69" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="10" t="s">
         <v>145</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C70" s="51">
+      <c r="C70" s="20">
         <v>47</v>
       </c>
-      <c r="D70" s="52">
+      <c r="D70" s="21">
         <v>60</v>
       </c>
-      <c r="E70" s="18"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="40"/>
-      <c r="H70" s="48">
+      <c r="E70" s="48">
+        <v>46</v>
+      </c>
+      <c r="F70" s="38">
+        <v>61</v>
+      </c>
+      <c r="G70" s="24">
+        <v>37</v>
+      </c>
+      <c r="H70" s="45">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="10" t="s">
         <v>147</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C71" s="51">
+      <c r="C71" s="20">
         <v>43</v>
       </c>
-      <c r="D71" s="51">
+      <c r="D71" s="20">
         <v>74</v>
       </c>
-      <c r="E71" s="18"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="40"/>
-      <c r="H71" s="48">
+      <c r="E71" s="48">
+        <v>51</v>
+      </c>
+      <c r="F71" s="38">
+        <v>54</v>
+      </c>
+      <c r="G71" s="24">
+        <v>58</v>
+      </c>
+      <c r="H71" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="10" t="s">
         <v>149</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C72" s="51">
+      <c r="C72" s="20">
         <v>46</v>
       </c>
-      <c r="D72" s="51">
+      <c r="D72" s="20">
         <v>68</v>
       </c>
-      <c r="E72" s="18"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="40"/>
-      <c r="H72" s="48">
+      <c r="E72" s="48">
+        <v>29</v>
+      </c>
+      <c r="F72" s="38">
+        <v>54</v>
+      </c>
+      <c r="G72" s="24">
+        <v>26</v>
+      </c>
+      <c r="H72" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="10" t="s">
         <v>151</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C73" s="51">
+      <c r="C73" s="20">
         <v>51</v>
       </c>
-      <c r="D73" s="52">
+      <c r="D73" s="21">
         <v>80</v>
       </c>
-      <c r="E73" s="18"/>
-      <c r="F73" s="27"/>
-      <c r="G73" s="42"/>
-      <c r="H73" s="48">
+      <c r="E73" s="48">
+        <v>83</v>
+      </c>
+      <c r="F73" s="38">
+        <v>71</v>
+      </c>
+      <c r="G73" s="26">
+        <v>77</v>
+      </c>
+      <c r="H73" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="10" t="s">
         <v>153</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C74" s="51">
+      <c r="C74" s="20">
         <v>73</v>
       </c>
-      <c r="D74" s="52">
+      <c r="D74" s="21">
         <v>58</v>
       </c>
-      <c r="E74" s="18"/>
-      <c r="F74" s="27"/>
-      <c r="G74" s="40"/>
-      <c r="H74" s="48">
+      <c r="E74" s="48">
+        <v>32</v>
+      </c>
+      <c r="F74" s="38">
+        <v>66</v>
+      </c>
+      <c r="G74" s="24">
+        <v>60</v>
+      </c>
+      <c r="H74" s="45">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="10" t="s">
         <v>155</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C75" s="51">
+      <c r="C75" s="20">
         <v>0</v>
       </c>
-      <c r="D75" s="51">
+      <c r="D75" s="20">
         <v>60</v>
       </c>
-      <c r="E75" s="18"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="40"/>
-      <c r="H75" s="48">
+      <c r="E75" s="48">
+        <v>33</v>
+      </c>
+      <c r="F75" s="38">
+        <v>55</v>
+      </c>
+      <c r="G75" s="24">
+        <v>58</v>
+      </c>
+      <c r="H75" s="45">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="10" t="s">
         <v>157</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C76" s="51">
+      <c r="C76" s="20">
         <v>55</v>
       </c>
-      <c r="D76" s="52">
+      <c r="D76" s="21">
         <v>44</v>
       </c>
-      <c r="E76" s="18"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="40"/>
-      <c r="H76" s="48">
+      <c r="E76" s="48">
+        <v>11</v>
+      </c>
+      <c r="F76" s="38">
+        <v>58</v>
+      </c>
+      <c r="G76" s="24">
+        <v>47</v>
+      </c>
+      <c r="H76" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="10" t="s">
         <v>159</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C77" s="51">
+      <c r="C77" s="20">
         <v>56</v>
       </c>
-      <c r="D77" s="52">
+      <c r="D77" s="21">
         <v>48</v>
       </c>
-      <c r="E77" s="18"/>
-      <c r="F77" s="27"/>
-      <c r="G77" s="40"/>
-      <c r="H77" s="48">
+      <c r="E77" s="48">
+        <v>33</v>
+      </c>
+      <c r="F77" s="38">
+        <v>71</v>
+      </c>
+      <c r="G77" s="24">
+        <v>59</v>
+      </c>
+      <c r="H77" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="16" t="s">
+      <c r="A78" s="10" t="s">
         <v>161</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C78" s="51">
+      <c r="C78" s="20">
         <v>35</v>
       </c>
-      <c r="D78" s="51">
+      <c r="D78" s="20">
         <v>68</v>
       </c>
-      <c r="E78" s="18"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="40"/>
-      <c r="H78" s="48">
+      <c r="E78" s="48">
+        <v>24</v>
+      </c>
+      <c r="F78" s="38">
+        <v>54</v>
+      </c>
+      <c r="G78" s="24">
+        <v>77</v>
+      </c>
+      <c r="H78" s="45">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="10" t="s">
         <v>163</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C79" s="51">
+      <c r="C79" s="20">
         <v>32</v>
       </c>
-      <c r="D79" s="52">
+      <c r="D79" s="21">
         <v>41</v>
       </c>
-      <c r="E79" s="18"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="40"/>
-      <c r="H79" s="48">
+      <c r="E79" s="48">
+        <v>27</v>
+      </c>
+      <c r="F79" s="38">
+        <v>43</v>
+      </c>
+      <c r="G79" s="24">
+        <v>49</v>
+      </c>
+      <c r="H79" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="16" t="s">
+      <c r="A80" s="10" t="s">
         <v>165</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C80" s="51">
+      <c r="C80" s="20">
         <v>71</v>
       </c>
-      <c r="D80" s="52">
+      <c r="D80" s="21">
         <v>56</v>
       </c>
-      <c r="E80" s="18"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="40"/>
-      <c r="H80" s="48">
+      <c r="E80" s="48">
+        <v>72</v>
+      </c>
+      <c r="F80" s="38">
+        <v>56</v>
+      </c>
+      <c r="G80" s="24">
+        <v>51</v>
+      </c>
+      <c r="H80" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="16" t="s">
+      <c r="A81" s="10" t="s">
         <v>167</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C81" s="51">
+      <c r="C81" s="20">
         <v>56</v>
       </c>
-      <c r="D81" s="52">
+      <c r="D81" s="21">
         <v>63</v>
       </c>
-      <c r="E81" s="18"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="40"/>
-      <c r="H81" s="48">
+      <c r="E81" s="48">
+        <v>64</v>
+      </c>
+      <c r="F81" s="38">
+        <v>79</v>
+      </c>
+      <c r="G81" s="24">
+        <v>64</v>
+      </c>
+      <c r="H81" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="16" t="s">
+      <c r="A82" s="10" t="s">
         <v>169</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C82" s="51">
+      <c r="C82" s="20">
         <v>52</v>
       </c>
-      <c r="D82" s="52">
+      <c r="D82" s="21">
         <v>30</v>
       </c>
-      <c r="E82" s="18"/>
-      <c r="F82" s="27"/>
-      <c r="G82" s="40"/>
-      <c r="H82" s="48">
+      <c r="E82" s="48">
+        <v>27</v>
+      </c>
+      <c r="F82" s="38">
+        <v>63</v>
+      </c>
+      <c r="G82" s="24">
+        <v>32</v>
+      </c>
+      <c r="H82" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="10" t="s">
         <v>171</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C83" s="51">
+      <c r="C83" s="20">
         <v>34</v>
       </c>
-      <c r="D83" s="52">
+      <c r="D83" s="21">
         <v>85</v>
       </c>
-      <c r="E83" s="18"/>
-      <c r="F83" s="27"/>
-      <c r="G83" s="42"/>
-      <c r="H83" s="48">
+      <c r="E83" s="48">
+        <v>42</v>
+      </c>
+      <c r="F83" s="38">
+        <v>32</v>
+      </c>
+      <c r="G83" s="26">
+        <v>57</v>
+      </c>
+      <c r="H83" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="16" t="s">
+      <c r="A84" s="10" t="s">
         <v>173</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C84" s="51">
+      <c r="C84" s="20">
         <v>42</v>
       </c>
-      <c r="D84" s="51">
+      <c r="D84" s="20">
         <v>34</v>
       </c>
-      <c r="E84" s="18"/>
-      <c r="F84" s="27"/>
-      <c r="G84" s="40"/>
-      <c r="H84" s="48">
+      <c r="E84" s="48">
+        <v>24</v>
+      </c>
+      <c r="F84" s="38">
+        <v>56</v>
+      </c>
+      <c r="G84" s="24">
+        <v>44</v>
+      </c>
+      <c r="H84" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="16" t="s">
+      <c r="A85" s="10" t="s">
         <v>175</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C85" s="51">
+      <c r="C85" s="20">
         <v>51</v>
       </c>
-      <c r="D85" s="51">
+      <c r="D85" s="20">
         <v>67</v>
       </c>
-      <c r="E85" s="19"/>
-      <c r="F85" s="28"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="48">
+      <c r="E85" s="46">
+        <v>45</v>
+      </c>
+      <c r="F85" s="46">
+        <v>51</v>
+      </c>
+      <c r="G85" s="25">
+        <v>58</v>
+      </c>
+      <c r="H85" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="16" t="s">
+      <c r="A86" s="10" t="s">
         <v>177</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C86" s="51">
+      <c r="C86" s="20">
         <v>17</v>
       </c>
-      <c r="D86" s="52">
+      <c r="D86" s="21">
         <v>49</v>
       </c>
-      <c r="E86" s="18"/>
-      <c r="F86" s="27"/>
-      <c r="G86" s="40"/>
-      <c r="H86" s="48">
+      <c r="E86" s="48">
+        <v>24</v>
+      </c>
+      <c r="F86" s="38">
+        <v>35</v>
+      </c>
+      <c r="G86" s="24">
+        <v>64</v>
+      </c>
+      <c r="H86" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="16" t="s">
+      <c r="A87" s="10" t="s">
         <v>179</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C87" s="51">
+      <c r="C87" s="20">
         <v>34</v>
       </c>
-      <c r="D87" s="52">
+      <c r="D87" s="21">
         <v>58</v>
       </c>
-      <c r="E87" s="18"/>
-      <c r="F87" s="27"/>
-      <c r="G87" s="40"/>
-      <c r="H87" s="48">
+      <c r="E87" s="48">
+        <v>34</v>
+      </c>
+      <c r="F87" s="38">
+        <v>41</v>
+      </c>
+      <c r="G87" s="24">
+        <v>58</v>
+      </c>
+      <c r="H87" s="45">
         <v>56.521739100000005</v>
       </c>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="16" t="s">
+      <c r="A88" s="10" t="s">
         <v>181</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="51">
+      <c r="C88" s="20">
         <v>60</v>
       </c>
-      <c r="D88" s="52">
+      <c r="D88" s="21">
         <v>47</v>
       </c>
-      <c r="E88" s="18"/>
-      <c r="F88" s="27"/>
-      <c r="G88" s="40"/>
-      <c r="H88" s="48">
+      <c r="E88" s="48">
+        <v>41</v>
+      </c>
+      <c r="F88" s="38">
+        <v>78</v>
+      </c>
+      <c r="G88" s="24">
+        <v>81</v>
+      </c>
+      <c r="H88" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="16" t="s">
+      <c r="A89" s="10" t="s">
         <v>183</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C89" s="51">
+      <c r="C89" s="20">
         <v>29</v>
       </c>
-      <c r="D89" s="52">
+      <c r="D89" s="21">
         <v>58</v>
       </c>
-      <c r="E89" s="18"/>
-      <c r="F89" s="27"/>
-      <c r="G89" s="40"/>
-      <c r="H89" s="48">
+      <c r="E89" s="48">
+        <v>61</v>
+      </c>
+      <c r="F89" s="38">
+        <v>54</v>
+      </c>
+      <c r="G89" s="24">
+        <v>75</v>
+      </c>
+      <c r="H89" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="16" t="s">
+      <c r="A90" s="10" t="s">
         <v>185</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C90" s="51">
+      <c r="C90" s="20">
         <v>25</v>
       </c>
-      <c r="D90" s="52">
+      <c r="D90" s="21">
         <v>84</v>
       </c>
-      <c r="E90" s="18"/>
-      <c r="F90" s="27"/>
-      <c r="G90" s="42"/>
-      <c r="H90" s="48">
+      <c r="E90" s="48">
+        <v>48</v>
+      </c>
+      <c r="F90" s="38">
+        <v>66</v>
+      </c>
+      <c r="G90" s="26">
+        <v>54</v>
+      </c>
+      <c r="H90" s="45">
         <v>52.173913000000006</v>
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="10" t="s">
         <v>187</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C91" s="51">
+      <c r="C91" s="20">
         <v>33</v>
       </c>
-      <c r="D91" s="51">
+      <c r="D91" s="20">
         <v>66</v>
       </c>
-      <c r="E91" s="18"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="40"/>
-      <c r="H91" s="48">
+      <c r="E91" s="48">
+        <v>48</v>
+      </c>
+      <c r="F91" s="38">
+        <v>51</v>
+      </c>
+      <c r="G91" s="24">
+        <v>58</v>
+      </c>
+      <c r="H91" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="16" t="s">
+      <c r="A92" s="10" t="s">
         <v>189</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="51">
+      <c r="C92" s="20">
         <v>43</v>
       </c>
-      <c r="D92" s="51">
+      <c r="D92" s="20">
         <v>48</v>
       </c>
-      <c r="E92" s="18"/>
-      <c r="F92" s="27"/>
-      <c r="G92" s="40"/>
-      <c r="H92" s="48">
+      <c r="E92" s="48">
+        <v>33</v>
+      </c>
+      <c r="F92" s="38">
+        <v>64</v>
+      </c>
+      <c r="G92" s="24">
+        <v>40</v>
+      </c>
+      <c r="H92" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="16" t="s">
+      <c r="A93" s="10" t="s">
         <v>191</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C93" s="51">
+      <c r="C93" s="20">
         <v>24</v>
       </c>
-      <c r="D93" s="52" t="s">
-        <v>382</v>
-      </c>
-      <c r="E93" s="18"/>
-      <c r="F93" s="27"/>
-      <c r="G93" s="40"/>
-      <c r="H93" s="48">
+      <c r="D93" s="21">
+        <v>74</v>
+      </c>
+      <c r="E93" s="48">
+        <v>70</v>
+      </c>
+      <c r="F93" s="38">
+        <v>66</v>
+      </c>
+      <c r="G93" s="24">
+        <v>46</v>
+      </c>
+      <c r="H93" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="16" t="s">
+      <c r="A94" s="10" t="s">
         <v>193</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C94" s="51">
+      <c r="C94" s="20">
         <v>57</v>
       </c>
-      <c r="D94" s="51">
+      <c r="D94" s="20">
         <v>55</v>
       </c>
-      <c r="E94" s="18"/>
-      <c r="F94" s="27"/>
-      <c r="G94" s="40"/>
-      <c r="H94" s="48">
+      <c r="E94" s="48">
+        <v>29</v>
+      </c>
+      <c r="F94" s="38">
+        <v>63</v>
+      </c>
+      <c r="G94" s="24">
+        <v>41</v>
+      </c>
+      <c r="H94" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="16" t="s">
+      <c r="A95" s="10" t="s">
         <v>195</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C95" s="51">
+      <c r="C95" s="20">
         <v>93</v>
       </c>
-      <c r="D95" s="52">
+      <c r="D95" s="21">
         <v>87</v>
       </c>
-      <c r="E95" s="18"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="40"/>
-      <c r="H95" s="48">
+      <c r="E95" s="48">
+        <v>65</v>
+      </c>
+      <c r="F95" s="38">
+        <v>75</v>
+      </c>
+      <c r="G95" s="24">
+        <v>84</v>
+      </c>
+      <c r="H95" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="16" t="s">
+      <c r="A96" s="10" t="s">
         <v>197</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="51">
+      <c r="C96" s="20">
         <v>65</v>
       </c>
-      <c r="D96" s="52">
+      <c r="D96" s="21">
         <v>79</v>
       </c>
-      <c r="E96" s="19"/>
-      <c r="F96" s="28"/>
-      <c r="G96" s="41"/>
-      <c r="H96" s="48">
+      <c r="E96" s="46">
+        <v>31</v>
+      </c>
+      <c r="F96" s="46">
+        <v>57</v>
+      </c>
+      <c r="G96" s="25">
+        <v>75</v>
+      </c>
+      <c r="H96" s="45">
         <v>65.217391300000003</v>
       </c>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="10" t="s">
         <v>199</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="51">
+      <c r="C97" s="20">
         <v>26</v>
       </c>
-      <c r="D97" s="52">
+      <c r="D97" s="21">
         <v>63</v>
       </c>
-      <c r="E97" s="18"/>
-      <c r="F97" s="27"/>
-      <c r="G97" s="40"/>
-      <c r="H97" s="48">
+      <c r="E97" s="48">
+        <v>27</v>
+      </c>
+      <c r="F97" s="38">
+        <v>44</v>
+      </c>
+      <c r="G97" s="24">
+        <v>46</v>
+      </c>
+      <c r="H97" s="45">
         <v>56.521739100000005</v>
       </c>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="16" t="s">
+      <c r="A98" s="10" t="s">
         <v>201</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="51">
+      <c r="C98" s="20">
         <v>13</v>
       </c>
-      <c r="D98" s="53">
+      <c r="D98" s="27">
         <v>52</v>
       </c>
-      <c r="E98" s="18"/>
-      <c r="F98" s="27"/>
-      <c r="G98" s="40"/>
-      <c r="H98" s="48">
+      <c r="E98" s="48">
+        <v>44</v>
+      </c>
+      <c r="F98" s="38">
+        <v>67</v>
+      </c>
+      <c r="G98" s="24">
+        <v>61</v>
+      </c>
+      <c r="H98" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="16" t="s">
+      <c r="A99" s="10" t="s">
         <v>203</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C99" s="51">
+      <c r="C99" s="20">
         <v>60</v>
       </c>
-      <c r="D99" s="53">
+      <c r="D99" s="27">
         <v>83</v>
       </c>
-      <c r="E99" s="18"/>
-      <c r="F99" s="27"/>
-      <c r="G99" s="42"/>
-      <c r="H99" s="48">
+      <c r="E99" s="48">
+        <v>62</v>
+      </c>
+      <c r="F99" s="38">
+        <v>79</v>
+      </c>
+      <c r="G99" s="26">
+        <v>75</v>
+      </c>
+      <c r="H99" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="16" t="s">
+      <c r="A100" s="10" t="s">
         <v>205</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="51">
+      <c r="C100" s="20">
         <v>42</v>
       </c>
-      <c r="D100" s="53">
+      <c r="D100" s="27">
         <v>48</v>
       </c>
-      <c r="E100" s="18"/>
-      <c r="F100" s="27"/>
-      <c r="G100" s="40"/>
-      <c r="H100" s="48">
+      <c r="E100" s="48">
+        <v>49</v>
+      </c>
+      <c r="F100" s="38">
+        <v>74</v>
+      </c>
+      <c r="G100" s="24">
+        <v>50</v>
+      </c>
+      <c r="H100" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="16" t="s">
+      <c r="A101" s="10" t="s">
         <v>207</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="51">
+      <c r="C101" s="20">
         <v>52</v>
       </c>
-      <c r="D101" s="53">
+      <c r="D101" s="27">
         <v>79</v>
       </c>
-      <c r="E101" s="18"/>
-      <c r="F101" s="27"/>
-      <c r="G101" s="40"/>
-      <c r="H101" s="48">
+      <c r="E101" s="48">
+        <v>50</v>
+      </c>
+      <c r="F101" s="38">
+        <v>61</v>
+      </c>
+      <c r="G101" s="24">
+        <v>47</v>
+      </c>
+      <c r="H101" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="16" t="s">
+      <c r="A102" s="10" t="s">
         <v>209</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="51">
+      <c r="C102" s="20">
         <v>60</v>
       </c>
-      <c r="D102" s="51">
+      <c r="D102" s="20">
         <v>85</v>
       </c>
-      <c r="E102" s="18"/>
-      <c r="F102" s="27"/>
-      <c r="G102" s="40"/>
-      <c r="H102" s="48">
+      <c r="E102" s="48">
+        <v>42</v>
+      </c>
+      <c r="F102" s="38">
+        <v>76</v>
+      </c>
+      <c r="G102" s="24">
+        <v>76</v>
+      </c>
+      <c r="H102" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="10" t="s">
         <v>211</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="51">
+      <c r="C103" s="20">
         <v>28</v>
       </c>
-      <c r="D103" s="53">
+      <c r="D103" s="27">
         <v>41</v>
       </c>
-      <c r="E103" s="18"/>
-      <c r="F103" s="27"/>
-      <c r="G103" s="40"/>
-      <c r="H103" s="48">
+      <c r="E103" s="48">
+        <v>20</v>
+      </c>
+      <c r="F103" s="38">
+        <v>53</v>
+      </c>
+      <c r="G103" s="24">
+        <v>51</v>
+      </c>
+      <c r="H103" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="16" t="s">
+      <c r="A104" s="10" t="s">
         <v>213</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C104" s="51">
+      <c r="C104" s="20">
         <v>27</v>
       </c>
-      <c r="D104" s="53">
+      <c r="D104" s="27">
         <v>74</v>
       </c>
-      <c r="E104" s="18"/>
-      <c r="F104" s="27"/>
-      <c r="G104" s="40"/>
-      <c r="H104" s="48">
+      <c r="E104" s="48">
+        <v>67</v>
+      </c>
+      <c r="F104" s="38">
+        <v>67</v>
+      </c>
+      <c r="G104" s="24">
+        <v>69</v>
+      </c>
+      <c r="H104" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="16" t="s">
+      <c r="A105" s="10" t="s">
         <v>215</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="51">
+      <c r="C105" s="20">
         <v>36</v>
       </c>
-      <c r="D105" s="53">
+      <c r="D105" s="27">
         <v>60</v>
       </c>
-      <c r="E105" s="18"/>
-      <c r="F105" s="27"/>
-      <c r="G105" s="40"/>
-      <c r="H105" s="48">
+      <c r="E105" s="48">
+        <v>57</v>
+      </c>
+      <c r="F105" s="38">
+        <v>66</v>
+      </c>
+      <c r="G105" s="24">
+        <v>72</v>
+      </c>
+      <c r="H105" s="45">
         <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="16" t="s">
+      <c r="A106" s="10" t="s">
         <v>217</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="51">
+      <c r="C106" s="20">
         <v>19</v>
       </c>
-      <c r="D106" s="53">
+      <c r="D106" s="27">
         <v>43</v>
       </c>
-      <c r="E106" s="18"/>
-      <c r="F106" s="27"/>
-      <c r="G106" s="40"/>
-      <c r="H106" s="48">
+      <c r="E106" s="48">
+        <v>35</v>
+      </c>
+      <c r="F106" s="38">
+        <v>55</v>
+      </c>
+      <c r="G106" s="24">
+        <v>9</v>
+      </c>
+      <c r="H106" s="45">
         <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="16" t="s">
+      <c r="A107" s="10" t="s">
         <v>219</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="51">
+      <c r="C107" s="20">
         <v>54</v>
       </c>
-      <c r="D107" s="53">
+      <c r="D107" s="27">
         <v>47</v>
       </c>
-      <c r="E107" s="18"/>
-      <c r="F107" s="27"/>
-      <c r="G107" s="40"/>
-      <c r="H107" s="48">
+      <c r="E107" s="48">
+        <v>34</v>
+      </c>
+      <c r="F107" s="38">
+        <v>64</v>
+      </c>
+      <c r="G107" s="24">
+        <v>49</v>
+      </c>
+      <c r="H107" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="16" t="s">
+      <c r="A108" s="10" t="s">
         <v>221</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C108" s="51">
+      <c r="C108" s="20">
         <v>46</v>
       </c>
-      <c r="D108" s="53">
+      <c r="D108" s="27">
         <v>12</v>
       </c>
-      <c r="E108" s="18"/>
-      <c r="F108" s="27"/>
-      <c r="G108" s="40"/>
-      <c r="H108" s="48">
+      <c r="E108" s="48">
+        <v>41</v>
+      </c>
+      <c r="F108" s="38">
+        <v>79</v>
+      </c>
+      <c r="G108" s="24">
+        <v>56</v>
+      </c>
+      <c r="H108" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="16" t="s">
+      <c r="A109" s="10" t="s">
         <v>223</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C109" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="D109" s="51">
+      <c r="C109" s="20">
+        <v>75</v>
+      </c>
+      <c r="D109" s="20">
         <v>35</v>
       </c>
-      <c r="E109" s="18"/>
-      <c r="F109" s="27"/>
-      <c r="G109" s="40"/>
-      <c r="H109" s="48">
+      <c r="E109" s="48">
+        <v>50</v>
+      </c>
+      <c r="F109" s="38">
+        <v>58</v>
+      </c>
+      <c r="G109" s="24">
+        <v>62</v>
+      </c>
+      <c r="H109" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="16" t="s">
+      <c r="A110" s="10" t="s">
         <v>224</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C110" s="51">
+      <c r="C110" s="20">
         <v>53</v>
       </c>
-      <c r="D110" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="E110" s="18"/>
-      <c r="F110" s="27"/>
-      <c r="G110" s="40"/>
-      <c r="H110" s="48">
+      <c r="D110" s="20">
+        <v>57</v>
+      </c>
+      <c r="E110" s="48">
+        <v>51</v>
+      </c>
+      <c r="F110" s="38">
+        <v>65</v>
+      </c>
+      <c r="G110" s="24">
+        <v>60</v>
+      </c>
+      <c r="H110" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="16" t="s">
+      <c r="A111" s="10" t="s">
         <v>226</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C111" s="51">
+      <c r="C111" s="20">
         <v>4</v>
       </c>
-      <c r="D111" s="51">
+      <c r="D111" s="20">
         <v>12</v>
       </c>
-      <c r="E111" s="18"/>
-      <c r="F111" s="27"/>
-      <c r="G111" s="40"/>
-      <c r="H111" s="48">
+      <c r="E111" s="48" t="s">
+        <v>382</v>
+      </c>
+      <c r="F111" s="38">
+        <v>42</v>
+      </c>
+      <c r="G111" s="24">
+        <v>11</v>
+      </c>
+      <c r="H111" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="16" t="s">
+      <c r="A112" s="10" t="s">
         <v>228</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C112" s="51">
+      <c r="C112" s="20">
         <v>71</v>
       </c>
-      <c r="D112" s="53">
+      <c r="D112" s="27">
         <v>85</v>
       </c>
-      <c r="E112" s="18"/>
-      <c r="F112" s="27"/>
-      <c r="G112" s="40"/>
-      <c r="H112" s="48">
+      <c r="E112" s="48">
+        <v>44</v>
+      </c>
+      <c r="F112" s="38">
+        <v>75</v>
+      </c>
+      <c r="G112" s="24">
+        <v>70</v>
+      </c>
+      <c r="H112" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="16" t="s">
+      <c r="A113" s="10" t="s">
         <v>230</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C113" s="51">
+      <c r="C113" s="20">
         <v>29</v>
       </c>
-      <c r="D113" s="53">
+      <c r="D113" s="27">
         <v>19</v>
       </c>
-      <c r="E113" s="18"/>
-      <c r="F113" s="27"/>
-      <c r="G113" s="40"/>
-      <c r="H113" s="48">
+      <c r="E113" s="48">
+        <v>24</v>
+      </c>
+      <c r="F113" s="38">
+        <v>73</v>
+      </c>
+      <c r="G113" s="24">
+        <v>50</v>
+      </c>
+      <c r="H113" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="16" t="s">
+      <c r="A114" s="10" t="s">
         <v>232</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C114" s="51">
+      <c r="C114" s="20">
         <v>45</v>
       </c>
-      <c r="D114" s="51">
+      <c r="D114" s="20">
         <v>75</v>
       </c>
-      <c r="E114" s="18"/>
-      <c r="F114" s="27"/>
-      <c r="G114" s="40"/>
-      <c r="H114" s="48">
+      <c r="E114" s="48">
+        <v>64</v>
+      </c>
+      <c r="F114" s="38">
+        <v>62</v>
+      </c>
+      <c r="G114" s="24">
+        <v>63</v>
+      </c>
+      <c r="H114" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="16" t="s">
+      <c r="A115" s="10" t="s">
         <v>234</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C115" s="51">
+      <c r="C115" s="20">
         <v>75</v>
       </c>
-      <c r="D115" s="51">
+      <c r="D115" s="20">
         <v>79</v>
       </c>
-      <c r="E115" s="18"/>
-      <c r="F115" s="27"/>
-      <c r="G115" s="40"/>
-      <c r="H115" s="48">
+      <c r="E115" s="48">
+        <v>72</v>
+      </c>
+      <c r="F115" s="38">
+        <v>71</v>
+      </c>
+      <c r="G115" s="24">
+        <v>67</v>
+      </c>
+      <c r="H115" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="16" t="s">
+      <c r="A116" s="10" t="s">
         <v>236</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C116" s="51">
+      <c r="C116" s="20">
         <v>53</v>
       </c>
-      <c r="D116" s="53">
+      <c r="D116" s="27">
         <v>47</v>
       </c>
-      <c r="E116" s="18"/>
-      <c r="F116" s="27"/>
-      <c r="G116" s="40"/>
-      <c r="H116" s="48">
+      <c r="E116" s="48">
+        <v>78</v>
+      </c>
+      <c r="F116" s="38">
+        <v>66</v>
+      </c>
+      <c r="G116" s="24">
+        <v>72</v>
+      </c>
+      <c r="H116" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.25" customHeight="1">
-      <c r="A117" s="16" t="s">
+      <c r="A117" s="10" t="s">
         <v>238</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C117" s="51">
+      <c r="C117" s="20">
         <v>44</v>
       </c>
-      <c r="D117" s="53">
+      <c r="D117" s="27">
         <v>60</v>
       </c>
-      <c r="E117" s="18"/>
-      <c r="F117" s="27"/>
-      <c r="G117" s="40"/>
-      <c r="H117" s="48">
+      <c r="E117" s="48">
+        <v>39</v>
+      </c>
+      <c r="F117" s="38">
+        <v>61</v>
+      </c>
+      <c r="G117" s="24">
+        <v>28</v>
+      </c>
+      <c r="H117" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="16" t="s">
+      <c r="A118" s="10" t="s">
         <v>240</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C118" s="51">
+      <c r="C118" s="20">
         <v>64</v>
       </c>
-      <c r="D118" s="51">
+      <c r="D118" s="20">
         <v>57</v>
       </c>
-      <c r="E118" s="18"/>
-      <c r="F118" s="27"/>
-      <c r="G118" s="40"/>
-      <c r="H118" s="48">
+      <c r="E118" s="48">
+        <v>62</v>
+      </c>
+      <c r="F118" s="38">
+        <v>39</v>
+      </c>
+      <c r="G118" s="24">
+        <v>54</v>
+      </c>
+      <c r="H118" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="16" t="s">
+      <c r="A119" s="10" t="s">
         <v>242</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C119" s="51">
+      <c r="C119" s="20">
         <v>83</v>
       </c>
-      <c r="D119" s="51">
+      <c r="D119" s="20">
         <v>52</v>
       </c>
-      <c r="E119" s="18"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="40"/>
-      <c r="H119" s="48">
+      <c r="E119" s="48">
+        <v>92</v>
+      </c>
+      <c r="F119" s="38">
+        <v>73</v>
+      </c>
+      <c r="G119" s="24">
+        <v>76</v>
+      </c>
+      <c r="H119" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="16" t="s">
+      <c r="A120" s="10" t="s">
         <v>244</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C120" s="51">
+      <c r="C120" s="20">
         <v>17</v>
       </c>
-      <c r="D120" s="53">
+      <c r="D120" s="27">
         <v>31</v>
       </c>
-      <c r="E120" s="18"/>
-      <c r="F120" s="27"/>
-      <c r="G120" s="40"/>
-      <c r="H120" s="48">
+      <c r="E120" s="48">
+        <v>82</v>
+      </c>
+      <c r="F120" s="38">
+        <v>70</v>
+      </c>
+      <c r="G120" s="24">
+        <v>52</v>
+      </c>
+      <c r="H120" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="16" t="s">
+      <c r="A121" s="10" t="s">
         <v>246</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C121" s="51" t="s">
+      <c r="C121" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="D121" s="51">
+      <c r="D121" s="20">
         <v>16</v>
       </c>
-      <c r="E121" s="18"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="40"/>
-      <c r="H121" s="48">
+      <c r="E121" s="48">
+        <v>32</v>
+      </c>
+      <c r="F121" s="38">
+        <v>67</v>
+      </c>
+      <c r="G121" s="24">
+        <v>59</v>
+      </c>
+      <c r="H121" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="16" t="s">
+      <c r="A122" s="10" t="s">
         <v>248</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C122" s="51">
+      <c r="C122" s="20">
         <v>25</v>
       </c>
-      <c r="D122" s="51">
+      <c r="D122" s="20">
         <v>36</v>
       </c>
-      <c r="E122" s="18"/>
-      <c r="F122" s="27"/>
-      <c r="G122" s="40"/>
-      <c r="H122" s="48">
+      <c r="E122" s="48">
+        <v>31</v>
+      </c>
+      <c r="F122" s="38">
+        <v>53</v>
+      </c>
+      <c r="G122" s="24">
+        <v>32</v>
+      </c>
+      <c r="H122" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="16" t="s">
+      <c r="A123" s="10" t="s">
         <v>250</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C123" s="51" t="s">
+      <c r="C123" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="D123" s="53" t="s">
+      <c r="D123" s="27" t="s">
         <v>382</v>
       </c>
-      <c r="E123" s="18"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="40"/>
-      <c r="H123" s="48">
+      <c r="E123" s="48" t="s">
+        <v>382</v>
+      </c>
+      <c r="F123" s="38" t="s">
+        <v>382</v>
+      </c>
+      <c r="G123" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="H123" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="16" t="s">
+      <c r="A124" s="10" t="s">
         <v>252</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C124" s="51">
+      <c r="C124" s="20">
         <v>58</v>
       </c>
-      <c r="D124" s="51">
+      <c r="D124" s="20">
         <v>72</v>
       </c>
-      <c r="E124" s="18"/>
-      <c r="F124" s="27"/>
-      <c r="G124" s="40"/>
-      <c r="H124" s="48">
+      <c r="E124" s="48">
+        <v>64</v>
+      </c>
+      <c r="F124" s="38">
+        <v>66</v>
+      </c>
+      <c r="G124" s="24">
+        <v>60</v>
+      </c>
+      <c r="H124" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="16" t="s">
+      <c r="A125" s="10" t="s">
         <v>254</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C125" s="51">
+      <c r="C125" s="20">
         <v>28</v>
       </c>
-      <c r="D125" s="53">
+      <c r="D125" s="27">
         <v>41</v>
       </c>
-      <c r="E125" s="18"/>
-      <c r="F125" s="27"/>
-      <c r="G125" s="40"/>
-      <c r="H125" s="48">
+      <c r="E125" s="48">
+        <v>50</v>
+      </c>
+      <c r="F125" s="38">
+        <v>79</v>
+      </c>
+      <c r="G125" s="24">
+        <v>55</v>
+      </c>
+      <c r="H125" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="16" t="s">
+      <c r="A126" s="10" t="s">
         <v>256</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C126" s="51">
+      <c r="C126" s="20">
         <v>44</v>
       </c>
-      <c r="D126" s="51">
+      <c r="D126" s="20">
         <v>53</v>
       </c>
-      <c r="E126" s="18"/>
-      <c r="F126" s="27"/>
-      <c r="G126" s="40"/>
-      <c r="H126" s="48">
+      <c r="E126" s="48">
+        <v>88</v>
+      </c>
+      <c r="F126" s="38">
+        <v>80</v>
+      </c>
+      <c r="G126" s="24">
+        <v>68</v>
+      </c>
+      <c r="H126" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="16" t="s">
+      <c r="A127" s="10" t="s">
         <v>258</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C127" s="51">
+      <c r="C127" s="20">
         <v>54</v>
       </c>
-      <c r="D127" s="53">
+      <c r="D127" s="27">
         <v>32</v>
       </c>
-      <c r="E127" s="18"/>
-      <c r="F127" s="27"/>
-      <c r="G127" s="40"/>
-      <c r="H127" s="48">
+      <c r="E127" s="48">
+        <v>51</v>
+      </c>
+      <c r="F127" s="38">
+        <v>61</v>
+      </c>
+      <c r="G127" s="24">
+        <v>68</v>
+      </c>
+      <c r="H127" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="16" t="s">
+      <c r="A128" s="10" t="s">
         <v>260</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C128" s="51">
+      <c r="C128" s="20">
         <v>21</v>
       </c>
-      <c r="D128" s="53">
+      <c r="D128" s="27">
         <v>56</v>
       </c>
-      <c r="E128" s="18"/>
-      <c r="F128" s="27"/>
-      <c r="G128" s="40"/>
-      <c r="H128" s="48">
+      <c r="E128" s="48">
+        <v>38</v>
+      </c>
+      <c r="F128" s="38">
+        <v>51</v>
+      </c>
+      <c r="G128" s="24">
+        <v>48</v>
+      </c>
+      <c r="H128" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="16" t="s">
+      <c r="A129" s="10" t="s">
         <v>262</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C129" s="51">
+      <c r="C129" s="20">
         <v>26</v>
       </c>
-      <c r="D129" s="53">
+      <c r="D129" s="27">
         <v>49</v>
       </c>
-      <c r="E129" s="18"/>
-      <c r="F129" s="27"/>
-      <c r="G129" s="40"/>
-      <c r="H129" s="48">
+      <c r="E129" s="48">
+        <v>4</v>
+      </c>
+      <c r="F129" s="38">
+        <v>46</v>
+      </c>
+      <c r="G129" s="24">
+        <v>50</v>
+      </c>
+      <c r="H129" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="16" t="s">
+      <c r="A130" s="10" t="s">
         <v>264</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C130" s="51">
+      <c r="C130" s="20">
         <v>15</v>
       </c>
-      <c r="D130" s="53">
+      <c r="D130" s="27">
         <v>26</v>
       </c>
-      <c r="E130" s="18"/>
-      <c r="F130" s="27"/>
-      <c r="G130" s="40"/>
-      <c r="H130" s="48">
+      <c r="E130" s="48">
+        <v>37</v>
+      </c>
+      <c r="F130" s="38">
+        <v>64</v>
+      </c>
+      <c r="G130" s="24">
+        <v>22</v>
+      </c>
+      <c r="H130" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="16" t="s">
+      <c r="A131" s="10" t="s">
         <v>266</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C131" s="51">
+      <c r="C131" s="20">
         <v>51</v>
       </c>
-      <c r="D131" s="53">
+      <c r="D131" s="27">
         <v>23</v>
       </c>
-      <c r="E131" s="18"/>
-      <c r="F131" s="27"/>
-      <c r="G131" s="40"/>
-      <c r="H131" s="48">
+      <c r="E131" s="48">
+        <v>37</v>
+      </c>
+      <c r="F131" s="38">
+        <v>64</v>
+      </c>
+      <c r="G131" s="24">
+        <v>63</v>
+      </c>
+      <c r="H131" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="16" t="s">
+      <c r="A132" s="10" t="s">
         <v>268</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C132" s="51">
+      <c r="C132" s="20">
         <v>50</v>
       </c>
-      <c r="D132" s="53">
+      <c r="D132" s="27">
         <v>81</v>
       </c>
-      <c r="E132" s="19"/>
-      <c r="F132" s="28"/>
-      <c r="G132" s="41"/>
-      <c r="H132" s="48">
+      <c r="E132" s="46">
+        <v>14</v>
+      </c>
+      <c r="F132" s="46">
+        <v>70</v>
+      </c>
+      <c r="G132" s="25">
+        <v>66</v>
+      </c>
+      <c r="H132" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="16" t="s">
+      <c r="A133" s="10" t="s">
         <v>270</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C133" s="51">
+      <c r="C133" s="20">
         <v>18</v>
       </c>
-      <c r="D133" s="53">
+      <c r="D133" s="27">
         <v>13</v>
       </c>
-      <c r="E133" s="18"/>
-      <c r="F133" s="27"/>
-      <c r="G133" s="40"/>
-      <c r="H133" s="48">
+      <c r="E133" s="48">
+        <v>42</v>
+      </c>
+      <c r="F133" s="38">
+        <v>63</v>
+      </c>
+      <c r="G133" s="24">
+        <v>23</v>
+      </c>
+      <c r="H133" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="16" t="s">
+      <c r="A134" s="10" t="s">
         <v>272</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C134" s="51">
+      <c r="C134" s="20">
         <v>53</v>
       </c>
-      <c r="D134" s="53">
+      <c r="D134" s="27">
         <v>49</v>
       </c>
-      <c r="E134" s="18"/>
-      <c r="F134" s="27"/>
-      <c r="G134" s="43"/>
-      <c r="H134" s="48">
+      <c r="E134" s="48">
+        <v>66</v>
+      </c>
+      <c r="F134" s="38">
+        <v>81</v>
+      </c>
+      <c r="G134" s="28">
+        <v>65</v>
+      </c>
+      <c r="H134" s="45">
         <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="16" t="s">
+      <c r="A135" s="10" t="s">
         <v>274</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C135" s="51">
+      <c r="C135" s="20">
         <v>8</v>
       </c>
-      <c r="D135" s="53">
+      <c r="D135" s="27">
         <v>42</v>
       </c>
-      <c r="E135" s="18"/>
-      <c r="F135" s="27"/>
-      <c r="G135" s="44"/>
-      <c r="H135" s="48">
+      <c r="E135" s="48">
+        <v>12</v>
+      </c>
+      <c r="F135" s="38">
+        <v>71</v>
+      </c>
+      <c r="G135" s="29">
+        <v>45</v>
+      </c>
+      <c r="H135" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="16" t="s">
+      <c r="A136" s="10" t="s">
         <v>276</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C136" s="51">
+      <c r="C136" s="20">
         <v>42</v>
       </c>
-      <c r="D136" s="51">
+      <c r="D136" s="20">
         <v>58</v>
       </c>
-      <c r="E136" s="18"/>
-      <c r="F136" s="27"/>
-      <c r="G136" s="39"/>
-      <c r="H136" s="48">
+      <c r="E136" s="48">
+        <v>21</v>
+      </c>
+      <c r="F136" s="38">
+        <v>66</v>
+      </c>
+      <c r="G136" s="23">
+        <v>58</v>
+      </c>
+      <c r="H136" s="45">
         <v>100</v>
       </c>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="16" t="s">
+      <c r="A137" s="10" t="s">
         <v>278</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C137" s="51">
+      <c r="C137" s="20">
         <v>37</v>
       </c>
-      <c r="D137" s="51">
+      <c r="D137" s="20">
         <v>45</v>
       </c>
-      <c r="E137" s="19"/>
-      <c r="F137" s="28"/>
-      <c r="G137" s="41"/>
-      <c r="H137" s="48">
+      <c r="E137" s="46">
+        <v>26</v>
+      </c>
+      <c r="F137" s="46">
+        <v>67</v>
+      </c>
+      <c r="G137" s="25">
+        <v>53</v>
+      </c>
+      <c r="H137" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="16" t="s">
+      <c r="A138" s="10" t="s">
         <v>280</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C138" s="51">
+      <c r="C138" s="20">
         <v>46</v>
       </c>
-      <c r="D138" s="51">
+      <c r="D138" s="20">
         <v>29</v>
       </c>
-      <c r="E138" s="18"/>
-      <c r="F138" s="27"/>
-      <c r="G138" s="40"/>
-      <c r="H138" s="48">
+      <c r="E138" s="48">
+        <v>38</v>
+      </c>
+      <c r="F138" s="38">
+        <v>58</v>
+      </c>
+      <c r="G138" s="24">
+        <v>64</v>
+      </c>
+      <c r="H138" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="16" t="s">
+      <c r="A139" s="10" t="s">
         <v>282</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C139" s="51">
+      <c r="C139" s="20">
         <v>43</v>
       </c>
-      <c r="D139" s="53">
+      <c r="D139" s="27">
         <v>38</v>
       </c>
-      <c r="E139" s="18"/>
-      <c r="F139" s="27"/>
-      <c r="G139" s="40"/>
-      <c r="H139" s="48">
+      <c r="E139" s="48">
+        <v>37</v>
+      </c>
+      <c r="F139" s="38">
+        <v>45</v>
+      </c>
+      <c r="G139" s="24">
+        <v>41</v>
+      </c>
+      <c r="H139" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="16" t="s">
+      <c r="A140" s="10" t="s">
         <v>284</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C140" s="51">
+      <c r="C140" s="20">
         <v>40</v>
       </c>
-      <c r="D140" s="51">
+      <c r="D140" s="20">
         <v>66</v>
       </c>
-      <c r="E140" s="18"/>
-      <c r="F140" s="27"/>
-      <c r="G140" s="40"/>
-      <c r="H140" s="48">
+      <c r="E140" s="48">
+        <v>80</v>
+      </c>
+      <c r="F140" s="38">
+        <v>71</v>
+      </c>
+      <c r="G140" s="24">
+        <v>70</v>
+      </c>
+      <c r="H140" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="16" t="s">
+      <c r="A141" s="10" t="s">
         <v>286</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C141" s="51">
+      <c r="C141" s="20">
         <v>32</v>
       </c>
-      <c r="D141" s="51">
+      <c r="D141" s="20">
         <v>17</v>
       </c>
-      <c r="E141" s="18"/>
-      <c r="F141" s="27"/>
-      <c r="G141" s="40"/>
-      <c r="H141" s="48">
+      <c r="E141" s="48">
+        <v>32</v>
+      </c>
+      <c r="F141" s="38">
+        <v>32</v>
+      </c>
+      <c r="G141" s="24">
+        <v>36</v>
+      </c>
+      <c r="H141" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="16" t="s">
+      <c r="A142" s="10" t="s">
         <v>288</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C142" s="51">
+      <c r="C142" s="20">
         <v>32</v>
       </c>
-      <c r="D142" s="51">
+      <c r="D142" s="20">
         <v>45</v>
       </c>
-      <c r="E142" s="18"/>
-      <c r="F142" s="27"/>
-      <c r="G142" s="40"/>
-      <c r="H142" s="48">
+      <c r="E142" s="48">
+        <v>67</v>
+      </c>
+      <c r="F142" s="38">
+        <v>61</v>
+      </c>
+      <c r="G142" s="24">
+        <v>65</v>
+      </c>
+      <c r="H142" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="143" spans="1:8">
-      <c r="A143" s="16" t="s">
+      <c r="A143" s="10" t="s">
         <v>290</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C143" s="51">
+      <c r="C143" s="20">
         <v>67</v>
       </c>
-      <c r="D143" s="53">
+      <c r="D143" s="27">
         <v>89</v>
       </c>
-      <c r="E143" s="18"/>
-      <c r="F143" s="27"/>
-      <c r="G143" s="40"/>
-      <c r="H143" s="48">
+      <c r="E143" s="48">
+        <v>91</v>
+      </c>
+      <c r="F143" s="38">
+        <v>65</v>
+      </c>
+      <c r="G143" s="24">
+        <v>72</v>
+      </c>
+      <c r="H143" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="16" t="s">
+      <c r="A144" s="10" t="s">
         <v>292</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C144" s="51">
+      <c r="C144" s="20">
         <v>61</v>
       </c>
-      <c r="D144" s="53">
+      <c r="D144" s="27">
         <v>76</v>
       </c>
-      <c r="E144" s="18"/>
-      <c r="F144" s="27"/>
-      <c r="G144" s="40"/>
-      <c r="H144" s="48">
+      <c r="E144" s="48">
+        <v>32</v>
+      </c>
+      <c r="F144" s="38">
+        <v>79</v>
+      </c>
+      <c r="G144" s="24">
+        <v>59</v>
+      </c>
+      <c r="H144" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="145" spans="1:8">
-      <c r="A145" s="16" t="s">
+      <c r="A145" s="10" t="s">
         <v>294</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C145" s="51">
+      <c r="C145" s="20">
         <v>71</v>
       </c>
-      <c r="D145" s="53">
+      <c r="D145" s="27">
         <v>76</v>
       </c>
-      <c r="E145" s="18"/>
-      <c r="F145" s="27"/>
-      <c r="G145" s="40"/>
-      <c r="H145" s="48">
+      <c r="E145" s="48">
+        <v>71</v>
+      </c>
+      <c r="F145" s="38">
+        <v>63</v>
+      </c>
+      <c r="G145" s="24">
+        <v>68</v>
+      </c>
+      <c r="H145" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="146" spans="1:8">
-      <c r="A146" s="16" t="s">
+      <c r="A146" s="10" t="s">
         <v>296</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C146" s="51">
+      <c r="C146" s="20">
         <v>96</v>
       </c>
-      <c r="D146" s="53">
+      <c r="D146" s="27">
         <v>86</v>
       </c>
-      <c r="E146" s="18"/>
-      <c r="F146" s="27"/>
-      <c r="G146" s="40"/>
-      <c r="H146" s="48">
+      <c r="E146" s="48">
+        <v>60</v>
+      </c>
+      <c r="F146" s="38">
+        <v>74</v>
+      </c>
+      <c r="G146" s="24">
+        <v>66</v>
+      </c>
+      <c r="H146" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" s="16" t="s">
+      <c r="A147" s="10" t="s">
         <v>298</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C147" s="51">
+      <c r="C147" s="20">
         <v>21</v>
       </c>
-      <c r="D147" s="51">
+      <c r="D147" s="20">
         <v>28</v>
       </c>
-      <c r="E147" s="18"/>
-      <c r="F147" s="27"/>
-      <c r="G147" s="40"/>
-      <c r="H147" s="48">
+      <c r="E147" s="48">
+        <v>40</v>
+      </c>
+      <c r="F147" s="38">
+        <v>57</v>
+      </c>
+      <c r="G147" s="24">
+        <v>12</v>
+      </c>
+      <c r="H147" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="148" spans="1:8">
-      <c r="A148" s="16" t="s">
+      <c r="A148" s="10" t="s">
         <v>300</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C148" s="51">
+      <c r="C148" s="20">
         <v>47</v>
       </c>
-      <c r="D148" s="51">
+      <c r="D148" s="20">
         <v>73</v>
       </c>
-      <c r="E148" s="18"/>
-      <c r="F148" s="27"/>
-      <c r="G148" s="40"/>
-      <c r="H148" s="48">
+      <c r="E148" s="48">
+        <v>38</v>
+      </c>
+      <c r="F148" s="38">
+        <v>71</v>
+      </c>
+      <c r="G148" s="24">
+        <v>52</v>
+      </c>
+      <c r="H148" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="149" spans="1:8">
-      <c r="A149" s="16" t="s">
+      <c r="A149" s="10" t="s">
         <v>302</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C149" s="51">
+      <c r="C149" s="20">
         <v>67</v>
       </c>
-      <c r="D149" s="53">
+      <c r="D149" s="27">
         <v>52</v>
       </c>
-      <c r="E149" s="18"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="40"/>
-      <c r="H149" s="48">
+      <c r="E149" s="48">
+        <v>72</v>
+      </c>
+      <c r="F149" s="38">
+        <v>69</v>
+      </c>
+      <c r="G149" s="24">
+        <v>28</v>
+      </c>
+      <c r="H149" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" s="16" t="s">
+      <c r="A150" s="10" t="s">
         <v>304</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C150" s="51" t="s">
+      <c r="C150" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="D150" s="53">
+      <c r="D150" s="27">
         <v>48</v>
       </c>
-      <c r="E150" s="19"/>
-      <c r="F150" s="29"/>
-      <c r="G150" s="41"/>
-      <c r="H150" s="48">
+      <c r="E150" s="46">
+        <v>18</v>
+      </c>
+      <c r="F150" s="20">
+        <v>68</v>
+      </c>
+      <c r="G150" s="25">
+        <v>44</v>
+      </c>
+      <c r="H150" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="151" spans="1:8">
-      <c r="A151" s="16" t="s">
+      <c r="A151" s="10" t="s">
         <v>306</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C151" s="51">
+      <c r="C151" s="20">
         <v>52</v>
       </c>
-      <c r="D151" s="51">
+      <c r="D151" s="20">
         <v>43</v>
       </c>
-      <c r="E151" s="18"/>
-      <c r="F151" s="27"/>
-      <c r="G151" s="40"/>
-      <c r="H151" s="48">
+      <c r="E151" s="48">
+        <v>43</v>
+      </c>
+      <c r="F151" s="38">
+        <v>73</v>
+      </c>
+      <c r="G151" s="24">
+        <v>64</v>
+      </c>
+      <c r="H151" s="45">
         <v>82.608695699999998</v>
       </c>
     </row>
     <row r="152" spans="1:8">
-      <c r="A152" s="16" t="s">
+      <c r="A152" s="10" t="s">
         <v>308</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C152" s="51">
+      <c r="C152" s="20">
         <v>36</v>
       </c>
-      <c r="D152" s="51">
+      <c r="D152" s="20">
         <v>51</v>
       </c>
-      <c r="E152" s="18"/>
-      <c r="F152" s="27"/>
-      <c r="G152" s="40"/>
-      <c r="H152" s="48">
+      <c r="E152" s="48">
+        <v>27</v>
+      </c>
+      <c r="F152" s="38">
+        <v>54</v>
+      </c>
+      <c r="G152" s="24">
+        <v>44</v>
+      </c>
+      <c r="H152" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="153" spans="1:8">
-      <c r="A153" s="16" t="s">
+      <c r="A153" s="10" t="s">
         <v>310</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C153" s="51">
+      <c r="C153" s="20">
         <v>78</v>
       </c>
-      <c r="D153" s="53">
+      <c r="D153" s="27">
         <v>46</v>
       </c>
-      <c r="E153" s="18"/>
-      <c r="F153" s="27"/>
-      <c r="G153" s="40"/>
-      <c r="H153" s="48">
+      <c r="E153" s="48">
+        <v>67</v>
+      </c>
+      <c r="F153" s="38">
+        <v>77</v>
+      </c>
+      <c r="G153" s="24">
+        <v>59</v>
+      </c>
+      <c r="H153" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="154" spans="1:8">
-      <c r="A154" s="16" t="s">
+      <c r="A154" s="10" t="s">
         <v>312</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C154" s="51">
+      <c r="C154" s="20">
         <v>31</v>
       </c>
-      <c r="D154" s="52">
+      <c r="D154" s="21">
         <v>78</v>
       </c>
-      <c r="E154" s="18"/>
-      <c r="F154" s="27"/>
-      <c r="G154" s="40"/>
-      <c r="H154" s="48">
+      <c r="E154" s="48">
+        <v>67</v>
+      </c>
+      <c r="F154" s="38">
+        <v>65</v>
+      </c>
+      <c r="G154" s="24">
+        <v>72</v>
+      </c>
+      <c r="H154" s="45">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="155" spans="1:8">
-      <c r="A155" s="16" t="s">
+      <c r="A155" s="10" t="s">
         <v>314</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C155" s="51">
+      <c r="C155" s="20">
         <v>60</v>
       </c>
-      <c r="D155" s="52">
+      <c r="D155" s="21">
         <v>85</v>
       </c>
-      <c r="E155" s="18"/>
-      <c r="F155" s="27"/>
-      <c r="G155" s="40"/>
-      <c r="H155" s="48">
+      <c r="E155" s="48">
+        <v>56</v>
+      </c>
+      <c r="F155" s="38">
+        <v>72</v>
+      </c>
+      <c r="G155" s="24">
+        <v>64</v>
+      </c>
+      <c r="H155" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="156" spans="1:8">
-      <c r="A156" s="16" t="s">
+      <c r="A156" s="10" t="s">
         <v>316</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C156" s="51">
+      <c r="C156" s="20">
         <v>95</v>
       </c>
-      <c r="D156" s="51">
+      <c r="D156" s="20">
         <v>89</v>
       </c>
-      <c r="E156" s="19"/>
-      <c r="F156" s="29"/>
-      <c r="G156" s="41"/>
-      <c r="H156" s="48">
+      <c r="E156" s="46">
+        <v>59</v>
+      </c>
+      <c r="F156" s="20">
+        <v>76</v>
+      </c>
+      <c r="G156" s="25">
+        <v>80</v>
+      </c>
+      <c r="H156" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" s="16" t="s">
+      <c r="A157" s="10" t="s">
         <v>318</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C157" s="51">
+      <c r="C157" s="20">
         <v>69</v>
       </c>
-      <c r="D157" s="51">
+      <c r="D157" s="20">
         <v>89</v>
       </c>
-      <c r="E157" s="18"/>
-      <c r="F157" s="27"/>
-      <c r="G157" s="40"/>
-      <c r="H157" s="48">
+      <c r="E157" s="48">
+        <v>53</v>
+      </c>
+      <c r="F157" s="38">
+        <v>72</v>
+      </c>
+      <c r="G157" s="24">
+        <v>67</v>
+      </c>
+      <c r="H157" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" s="16" t="s">
+      <c r="A158" s="10" t="s">
         <v>320</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C158" s="51">
+      <c r="C158" s="20">
         <v>47</v>
       </c>
-      <c r="D158" s="51">
+      <c r="D158" s="20">
         <v>86</v>
       </c>
-      <c r="E158" s="18"/>
-      <c r="F158" s="27"/>
-      <c r="G158" s="40"/>
-      <c r="H158" s="48">
+      <c r="E158" s="48">
+        <v>67</v>
+      </c>
+      <c r="F158" s="38">
+        <v>79</v>
+      </c>
+      <c r="G158" s="24">
+        <v>57</v>
+      </c>
+      <c r="H158" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" s="16" t="s">
+      <c r="A159" s="10" t="s">
         <v>322</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C159" s="51">
+      <c r="C159" s="20">
         <v>58</v>
       </c>
-      <c r="D159" s="52">
+      <c r="D159" s="21">
         <v>56</v>
       </c>
-      <c r="E159" s="20"/>
-      <c r="F159" s="27"/>
-      <c r="G159" s="40"/>
-      <c r="H159" s="48">
+      <c r="E159" s="38">
+        <v>71</v>
+      </c>
+      <c r="F159" s="38">
+        <v>62</v>
+      </c>
+      <c r="G159" s="24">
+        <v>70</v>
+      </c>
+      <c r="H159" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="16" t="s">
+      <c r="A160" s="10" t="s">
         <v>324</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C160" s="51">
+      <c r="C160" s="20">
         <v>25</v>
       </c>
-      <c r="D160" s="52">
+      <c r="D160" s="21">
         <v>76</v>
       </c>
-      <c r="E160" s="18"/>
-      <c r="F160" s="27"/>
-      <c r="G160" s="40"/>
-      <c r="H160" s="48">
+      <c r="E160" s="48">
+        <v>30</v>
+      </c>
+      <c r="F160" s="38">
+        <v>52</v>
+      </c>
+      <c r="G160" s="24">
+        <v>70</v>
+      </c>
+      <c r="H160" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="16" t="s">
+      <c r="A161" s="10" t="s">
         <v>326</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C161" s="51">
+      <c r="C161" s="20">
         <v>44</v>
       </c>
-      <c r="D161" s="51">
+      <c r="D161" s="20">
         <v>34</v>
       </c>
-      <c r="E161" s="18"/>
-      <c r="F161" s="27"/>
-      <c r="G161" s="40"/>
-      <c r="H161" s="48">
+      <c r="E161" s="48">
+        <v>49</v>
+      </c>
+      <c r="F161" s="38">
+        <v>58</v>
+      </c>
+      <c r="G161" s="24">
+        <v>57</v>
+      </c>
+      <c r="H161" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="162" spans="1:8">
-      <c r="A162" s="16" t="s">
+      <c r="A162" s="10" t="s">
         <v>328</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C162" s="51">
+      <c r="C162" s="20">
         <v>31</v>
       </c>
-      <c r="D162" s="52">
+      <c r="D162" s="21">
         <v>38</v>
       </c>
-      <c r="E162" s="18"/>
-      <c r="F162" s="27"/>
-      <c r="G162" s="40"/>
-      <c r="H162" s="48">
+      <c r="E162" s="48">
+        <v>57</v>
+      </c>
+      <c r="F162" s="38">
+        <v>73</v>
+      </c>
+      <c r="G162" s="24">
+        <v>52</v>
+      </c>
+      <c r="H162" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="163" spans="1:8">
-      <c r="A163" s="16" t="s">
+      <c r="A163" s="10" t="s">
         <v>330</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C163" s="52">
+      <c r="C163" s="21">
         <v>40</v>
       </c>
-      <c r="D163" s="51">
+      <c r="D163" s="20">
         <v>55</v>
       </c>
-      <c r="E163" s="18"/>
-      <c r="F163" s="27"/>
-      <c r="G163" s="40"/>
-      <c r="H163" s="48">
+      <c r="E163" s="48">
+        <v>45</v>
+      </c>
+      <c r="F163" s="38">
+        <v>69</v>
+      </c>
+      <c r="G163" s="24">
+        <v>42</v>
+      </c>
+      <c r="H163" s="45">
         <v>69.565217399999995</v>
       </c>
     </row>
     <row r="164" spans="1:8">
-      <c r="A164" s="16" t="s">
+      <c r="A164" s="10" t="s">
         <v>332</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C164" s="52">
+      <c r="C164" s="21">
         <v>19</v>
       </c>
-      <c r="D164" s="52">
+      <c r="D164" s="21">
         <v>63</v>
       </c>
-      <c r="E164" s="18"/>
-      <c r="F164" s="27"/>
-      <c r="G164" s="43"/>
-      <c r="H164" s="48">
+      <c r="E164" s="48">
+        <v>27</v>
+      </c>
+      <c r="F164" s="38">
+        <v>60</v>
+      </c>
+      <c r="G164" s="28">
+        <v>49</v>
+      </c>
+      <c r="H164" s="45">
         <v>47.826087000000001</v>
       </c>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="16" t="s">
+      <c r="A165" s="10" t="s">
         <v>334</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C165" s="52" t="s">
-        <v>382</v>
-      </c>
-      <c r="D165" s="51">
+      <c r="C165" s="21">
+        <v>12</v>
+      </c>
+      <c r="D165" s="20">
         <v>74</v>
       </c>
-      <c r="E165" s="18"/>
-      <c r="F165" s="27"/>
-      <c r="G165" s="38"/>
-      <c r="H165" s="48">
+      <c r="E165" s="48">
+        <v>19</v>
+      </c>
+      <c r="F165" s="38">
+        <v>51</v>
+      </c>
+      <c r="G165" s="22">
+        <v>61</v>
+      </c>
+      <c r="H165" s="45">
         <v>65.217391300000003</v>
       </c>
     </row>
     <row r="166" spans="1:8">
-      <c r="A166" s="16" t="s">
+      <c r="A166" s="10" t="s">
         <v>336</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C166" s="52">
+      <c r="C166" s="21">
         <v>18</v>
       </c>
-      <c r="D166" s="51">
+      <c r="D166" s="20">
         <v>44</v>
       </c>
-      <c r="E166" s="18"/>
-      <c r="F166" s="27"/>
-      <c r="G166" s="38"/>
-      <c r="H166" s="48">
+      <c r="E166" s="48">
+        <v>51</v>
+      </c>
+      <c r="F166" s="38">
+        <v>65</v>
+      </c>
+      <c r="G166" s="22">
+        <v>47</v>
+      </c>
+      <c r="H166" s="45">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" s="16" t="s">
+      <c r="A167" s="10" t="s">
         <v>338</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C167" s="52">
+      <c r="C167" s="21">
         <v>44</v>
       </c>
-      <c r="D167" s="52">
+      <c r="D167" s="21">
         <v>69</v>
       </c>
-      <c r="E167" s="18"/>
-      <c r="F167" s="27"/>
-      <c r="G167" s="38"/>
-      <c r="H167" s="48">
+      <c r="E167" s="48">
+        <v>62</v>
+      </c>
+      <c r="F167" s="38">
+        <v>66</v>
+      </c>
+      <c r="G167" s="22">
+        <v>65</v>
+      </c>
+      <c r="H167" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="16" t="s">
+      <c r="A168" s="10" t="s">
         <v>340</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C168" s="52">
+      <c r="C168" s="21">
         <v>82</v>
       </c>
-      <c r="D168" s="51">
+      <c r="D168" s="20">
         <v>93</v>
       </c>
-      <c r="E168" s="18"/>
-      <c r="F168" s="27"/>
-      <c r="G168" s="38"/>
-      <c r="H168" s="48">
+      <c r="E168" s="48">
+        <v>39</v>
+      </c>
+      <c r="F168" s="38">
+        <v>79</v>
+      </c>
+      <c r="G168" s="22">
+        <v>45</v>
+      </c>
+      <c r="H168" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="169" spans="1:8">
-      <c r="A169" s="16" t="s">
+      <c r="A169" s="10" t="s">
         <v>342</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C169" s="52">
+      <c r="C169" s="21">
         <v>55</v>
       </c>
-      <c r="D169" s="52">
+      <c r="D169" s="21">
         <v>55</v>
       </c>
-      <c r="E169" s="18"/>
-      <c r="F169" s="27"/>
-      <c r="G169" s="38"/>
-      <c r="H169" s="48">
+      <c r="E169" s="48">
+        <v>54</v>
+      </c>
+      <c r="F169" s="38">
+        <v>75</v>
+      </c>
+      <c r="G169" s="22">
+        <v>69</v>
+      </c>
+      <c r="H169" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="170" spans="1:8">
-      <c r="A170" s="16" t="s">
+      <c r="A170" s="10" t="s">
         <v>344</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C170" s="52">
+      <c r="C170" s="21">
         <v>24</v>
       </c>
-      <c r="D170" s="52">
+      <c r="D170" s="21">
         <v>25</v>
       </c>
-      <c r="E170" s="21"/>
-      <c r="F170" s="30"/>
-      <c r="G170" s="45"/>
-      <c r="H170" s="48">
+      <c r="E170" s="49">
+        <v>26</v>
+      </c>
+      <c r="F170" s="47">
+        <v>51</v>
+      </c>
+      <c r="G170" s="30">
+        <v>33</v>
+      </c>
+      <c r="H170" s="45">
         <v>47.826087000000001</v>
       </c>
     </row>
     <row r="171" spans="1:8">
-      <c r="A171" s="16" t="s">
+      <c r="A171" s="10" t="s">
         <v>346</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C171" s="52">
+      <c r="C171" s="21">
         <v>36</v>
       </c>
-      <c r="D171" s="52">
+      <c r="D171" s="21">
         <v>50</v>
       </c>
-      <c r="E171" s="18"/>
-      <c r="F171" s="31"/>
-      <c r="G171" s="46"/>
-      <c r="H171" s="48">
+      <c r="E171" s="48">
+        <v>14</v>
+      </c>
+      <c r="F171" s="39">
+        <v>53</v>
+      </c>
+      <c r="G171" s="31">
+        <v>46</v>
+      </c>
+      <c r="H171" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="172" spans="1:8">
-      <c r="A172" s="16" t="s">
+      <c r="A172" s="10" t="s">
         <v>348</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C172" s="52">
+      <c r="C172" s="21">
         <v>55</v>
       </c>
-      <c r="D172" s="52">
+      <c r="D172" s="21">
         <v>58</v>
       </c>
-      <c r="E172" s="18"/>
-      <c r="F172" s="31"/>
-      <c r="G172" s="46"/>
-      <c r="H172" s="48">
+      <c r="E172" s="48">
+        <v>29</v>
+      </c>
+      <c r="F172" s="39">
+        <v>62</v>
+      </c>
+      <c r="G172" s="31">
+        <v>26</v>
+      </c>
+      <c r="H172" s="45">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="173" spans="1:8">
-      <c r="A173" s="16" t="s">
+      <c r="A173" s="10" t="s">
         <v>350</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C173" s="52">
+      <c r="C173" s="21">
         <v>27</v>
       </c>
-      <c r="D173" s="51">
+      <c r="D173" s="20">
         <v>65</v>
       </c>
-      <c r="E173" s="18"/>
-      <c r="F173" s="31"/>
-      <c r="G173" s="46"/>
-      <c r="H173" s="48">
+      <c r="E173" s="48">
+        <v>32</v>
+      </c>
+      <c r="F173" s="39">
+        <v>69</v>
+      </c>
+      <c r="G173" s="31">
+        <v>50</v>
+      </c>
+      <c r="H173" s="45">
         <v>43.478260899999995</v>
       </c>
     </row>
     <row r="174" spans="1:8">
-      <c r="A174" s="16" t="s">
+      <c r="A174" s="10" t="s">
         <v>352</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C174" s="52">
+      <c r="C174" s="21">
         <v>14</v>
       </c>
-      <c r="D174" s="51">
+      <c r="D174" s="20">
         <v>22</v>
       </c>
-      <c r="E174" s="18"/>
-      <c r="F174" s="31"/>
-      <c r="G174" s="46"/>
-      <c r="H174" s="48">
+      <c r="E174" s="48">
+        <v>22</v>
+      </c>
+      <c r="F174" s="39">
+        <v>54</v>
+      </c>
+      <c r="G174" s="31">
+        <v>51</v>
+      </c>
+      <c r="H174" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="175" spans="1:8">
-      <c r="A175" s="16" t="s">
+      <c r="A175" s="10" t="s">
         <v>354</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C175" s="52">
+      <c r="C175" s="21">
         <v>17</v>
       </c>
-      <c r="D175" s="52">
+      <c r="D175" s="21">
         <v>40</v>
       </c>
-      <c r="E175" s="18"/>
-      <c r="F175" s="31"/>
-      <c r="G175" s="46"/>
-      <c r="H175" s="48">
+      <c r="E175" s="48">
+        <v>34</v>
+      </c>
+      <c r="F175" s="39">
+        <v>44</v>
+      </c>
+      <c r="G175" s="31">
+        <v>60</v>
+      </c>
+      <c r="H175" s="45">
         <v>30.434782599999998</v>
       </c>
     </row>
     <row r="176" spans="1:8">
-      <c r="A176" s="16" t="s">
+      <c r="A176" s="10" t="s">
         <v>356</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C176" s="52">
+      <c r="C176" s="21">
         <v>33</v>
       </c>
-      <c r="D176" s="51">
+      <c r="D176" s="20">
         <v>23</v>
       </c>
-      <c r="E176" s="18"/>
-      <c r="F176" s="31"/>
-      <c r="G176" s="46"/>
-      <c r="H176" s="48">
+      <c r="E176" s="48">
+        <v>19</v>
+      </c>
+      <c r="F176" s="39">
+        <v>62</v>
+      </c>
+      <c r="G176" s="31">
+        <v>35</v>
+      </c>
+      <c r="H176" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="177" spans="1:8">
-      <c r="A177" s="16" t="s">
+      <c r="A177" s="10" t="s">
         <v>358</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C177" s="52">
+      <c r="C177" s="21">
         <v>64</v>
       </c>
-      <c r="D177" s="51">
+      <c r="D177" s="20">
         <v>81</v>
       </c>
-      <c r="E177" s="18"/>
-      <c r="F177" s="31"/>
-      <c r="G177" s="46"/>
-      <c r="H177" s="48">
+      <c r="E177" s="48">
+        <v>57</v>
+      </c>
+      <c r="F177" s="39">
+        <v>73</v>
+      </c>
+      <c r="G177" s="31">
+        <v>54</v>
+      </c>
+      <c r="H177" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="178" spans="1:8">
-      <c r="A178" s="16" t="s">
+      <c r="A178" s="10" t="s">
         <v>360</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C178" s="52">
+      <c r="C178" s="21">
         <v>32</v>
       </c>
-      <c r="D178" s="51">
+      <c r="D178" s="20">
         <v>94</v>
       </c>
-      <c r="E178" s="18"/>
-      <c r="F178" s="31"/>
-      <c r="G178" s="46"/>
-      <c r="H178" s="48">
+      <c r="E178" s="48">
+        <v>49</v>
+      </c>
+      <c r="F178" s="39">
+        <v>62</v>
+      </c>
+      <c r="G178" s="31">
+        <v>80</v>
+      </c>
+      <c r="H178" s="45">
         <v>100</v>
       </c>
     </row>
     <row r="179" spans="1:8">
-      <c r="A179" s="16" t="s">
+      <c r="A179" s="10" t="s">
         <v>362</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C179" s="52">
+      <c r="C179" s="21">
         <v>64</v>
       </c>
-      <c r="D179" s="51">
+      <c r="D179" s="20">
         <v>92</v>
       </c>
-      <c r="E179" s="18"/>
-      <c r="F179" s="31"/>
-      <c r="G179" s="46"/>
-      <c r="H179" s="48">
+      <c r="E179" s="48">
+        <v>92</v>
+      </c>
+      <c r="F179" s="39">
+        <v>84</v>
+      </c>
+      <c r="G179" s="31">
+        <v>88</v>
+      </c>
+      <c r="H179" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="180" spans="1:8">
-      <c r="A180" s="16" t="s">
+      <c r="A180" s="10" t="s">
         <v>364</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C180" s="52">
+      <c r="C180" s="21">
         <v>12</v>
       </c>
-      <c r="D180" s="51">
+      <c r="D180" s="20">
         <v>25</v>
       </c>
-      <c r="E180" s="18"/>
-      <c r="F180" s="31"/>
-      <c r="G180" s="46"/>
-      <c r="H180" s="48">
+      <c r="E180" s="48">
+        <v>12</v>
+      </c>
+      <c r="F180" s="39">
+        <v>53</v>
+      </c>
+      <c r="G180" s="31">
+        <v>29</v>
+      </c>
+      <c r="H180" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="181" spans="1:8">
-      <c r="A181" s="16" t="s">
+      <c r="A181" s="10" t="s">
         <v>366</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C181" s="52">
+      <c r="C181" s="21">
         <v>36</v>
       </c>
-      <c r="D181" s="52">
+      <c r="D181" s="21">
         <v>70</v>
       </c>
-      <c r="E181" s="18"/>
-      <c r="F181" s="31"/>
-      <c r="G181" s="46"/>
-      <c r="H181" s="48">
+      <c r="E181" s="48">
+        <v>43</v>
+      </c>
+      <c r="F181" s="39">
+        <v>50</v>
+      </c>
+      <c r="G181" s="31">
+        <v>63</v>
+      </c>
+      <c r="H181" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="182" spans="1:8">
-      <c r="A182" s="16" t="s">
+      <c r="A182" s="10" t="s">
         <v>368</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C182" s="52">
+      <c r="C182" s="21">
         <v>1</v>
       </c>
-      <c r="D182" s="52">
+      <c r="D182" s="21">
         <v>40</v>
       </c>
-      <c r="E182" s="22"/>
-      <c r="F182" s="31"/>
-      <c r="G182" s="46"/>
-      <c r="H182" s="48">
+      <c r="E182" s="27">
+        <v>37</v>
+      </c>
+      <c r="F182" s="39">
+        <v>58</v>
+      </c>
+      <c r="G182" s="31">
+        <v>49</v>
+      </c>
+      <c r="H182" s="45">
         <v>86.956521699999996</v>
       </c>
     </row>
     <row r="183" spans="1:8">
-      <c r="A183" s="16" t="s">
+      <c r="A183" s="10" t="s">
         <v>370</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C183" s="52">
+      <c r="C183" s="21">
         <v>38</v>
       </c>
-      <c r="D183" s="52">
+      <c r="D183" s="21">
         <v>66</v>
       </c>
-      <c r="E183" s="22"/>
-      <c r="F183" s="31"/>
-      <c r="G183" s="46"/>
-      <c r="H183" s="48">
+      <c r="E183" s="27">
+        <v>29</v>
+      </c>
+      <c r="F183" s="39">
+        <v>73</v>
+      </c>
+      <c r="G183" s="31">
+        <v>59</v>
+      </c>
+      <c r="H183" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="184" spans="1:8">
-      <c r="A184" s="16" t="s">
+      <c r="A184" s="10" t="s">
         <v>372</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C184" s="52">
+      <c r="C184" s="21">
         <v>41</v>
       </c>
-      <c r="D184" s="52">
+      <c r="D184" s="21">
         <v>62</v>
       </c>
-      <c r="E184" s="18"/>
-      <c r="F184" s="31"/>
-      <c r="G184" s="46"/>
-      <c r="H184" s="48">
+      <c r="E184" s="48">
+        <v>31</v>
+      </c>
+      <c r="F184" s="39">
+        <v>54</v>
+      </c>
+      <c r="G184" s="31">
+        <v>74</v>
+      </c>
+      <c r="H184" s="45">
         <v>95.652173900000008</v>
       </c>
     </row>
     <row r="185" spans="1:8">
-      <c r="A185" s="16" t="s">
+      <c r="A185" s="10" t="s">
         <v>374</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C185" s="52">
+      <c r="C185" s="21">
         <v>77</v>
       </c>
-      <c r="D185" s="52">
+      <c r="D185" s="21">
         <v>57</v>
       </c>
-      <c r="E185" s="18"/>
-      <c r="F185" s="31"/>
-      <c r="G185" s="46"/>
-      <c r="H185" s="48">
+      <c r="E185" s="48">
+        <v>61</v>
+      </c>
+      <c r="F185" s="39">
+        <v>57</v>
+      </c>
+      <c r="G185" s="31">
+        <v>65</v>
+      </c>
+      <c r="H185" s="45">
         <v>78.260869600000007</v>
       </c>
     </row>
     <row r="186" spans="1:8">
-      <c r="A186" s="16" t="s">
+      <c r="A186" s="10" t="s">
         <v>376</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C186" s="52">
+      <c r="C186" s="21">
         <v>74</v>
       </c>
-      <c r="D186" s="52">
+      <c r="D186" s="21">
         <v>44</v>
       </c>
-      <c r="E186" s="18"/>
-      <c r="F186" s="31"/>
-      <c r="G186" s="46"/>
-      <c r="H186" s="48">
+      <c r="E186" s="48">
+        <v>60</v>
+      </c>
+      <c r="F186" s="39">
+        <v>71</v>
+      </c>
+      <c r="G186" s="31">
+        <v>69</v>
+      </c>
+      <c r="H186" s="45">
         <v>91.304347800000002</v>
       </c>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="49" t="s">
+      <c r="A187" s="14" t="s">
         <v>380</v>
       </c>
-      <c r="B187" s="50" t="s">
+      <c r="B187" s="15" t="s">
         <v>381</v>
       </c>
-      <c r="C187" s="52">
+      <c r="C187" s="21">
         <v>37</v>
       </c>
-      <c r="D187" s="52">
+      <c r="D187" s="21">
         <v>32</v>
       </c>
-      <c r="E187" s="23"/>
-      <c r="F187" s="31"/>
-      <c r="G187" s="47"/>
-      <c r="H187" s="48">
+      <c r="E187" s="37">
+        <v>57</v>
+      </c>
+      <c r="F187" s="39">
+        <v>63</v>
+      </c>
+      <c r="G187" s="32">
+        <v>47</v>
+      </c>
+      <c r="H187" s="45">
         <v>73.913043500000001</v>
       </c>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="36" t="s">
+      <c r="A188" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="B188" s="37" t="s">
+      <c r="B188" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="C188" s="52">
+      <c r="C188" s="21">
         <v>0</v>
       </c>
-      <c r="D188" s="52">
+      <c r="D188" s="21">
         <v>24</v>
       </c>
-      <c r="E188" s="22"/>
-      <c r="F188" s="31"/>
-      <c r="G188" s="13"/>
-      <c r="H188" s="48">
+      <c r="E188" s="27">
+        <v>39</v>
+      </c>
+      <c r="F188" s="39">
+        <v>54</v>
+      </c>
+      <c r="G188" s="33">
+        <v>29</v>
+      </c>
+      <c r="H188" s="45">
         <v>60.869565199999997</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="15.75">
-      <c r="A189" s="16" t="s">
+      <c r="A189" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B189" s="63" t="s">
+      <c r="B189" s="18" t="s">
         <v>399</v>
       </c>
-      <c r="C189" s="52">
+      <c r="C189" s="21">
         <v>38</v>
       </c>
-      <c r="D189" s="51">
+      <c r="D189" s="20">
         <v>56</v>
       </c>
-      <c r="E189" s="20"/>
-      <c r="F189" s="31"/>
-      <c r="G189" s="13"/>
-      <c r="H189" s="48"/>
+      <c r="E189" s="38">
+        <v>14</v>
+      </c>
+      <c r="F189" s="39">
+        <v>58</v>
+      </c>
+      <c r="G189" s="33">
+        <v>60</v>
+      </c>
+      <c r="H189" s="13"/>
     </row>
     <row r="190" spans="1:8" ht="15.75">
-      <c r="A190" s="61" t="s">
+      <c r="A190" s="16" t="s">
         <v>384</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C190" s="52">
+      <c r="C190" s="21">
         <v>53</v>
       </c>
-      <c r="D190" s="51">
+      <c r="D190" s="20">
         <v>72</v>
       </c>
-      <c r="E190" s="11"/>
-      <c r="F190" s="32"/>
-      <c r="G190" s="14"/>
-      <c r="H190" s="48"/>
+      <c r="E190" s="39">
+        <v>65</v>
+      </c>
+      <c r="F190" s="40">
+        <v>71</v>
+      </c>
+      <c r="G190" s="20">
+        <v>60</v>
+      </c>
+      <c r="H190" s="13"/>
     </row>
     <row r="191" spans="1:8" ht="15.75">
-      <c r="A191" s="61" t="s">
+      <c r="A191" s="16" t="s">
         <v>385</v>
       </c>
-      <c r="B191" s="63" t="s">
+      <c r="B191" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="C191" s="52">
+      <c r="C191" s="21">
         <v>75</v>
       </c>
-      <c r="D191" s="51">
+      <c r="D191" s="20">
         <v>69</v>
       </c>
-      <c r="E191" s="59"/>
-      <c r="F191" s="32"/>
-      <c r="G191" s="15"/>
-      <c r="H191" s="48"/>
+      <c r="E191" s="41">
+        <v>65</v>
+      </c>
+      <c r="F191" s="40">
+        <v>54</v>
+      </c>
+      <c r="G191" s="21">
+        <v>51</v>
+      </c>
+      <c r="H191" s="13"/>
     </row>
     <row r="192" spans="1:8" ht="15.75">
-      <c r="A192" s="62" t="s">
+      <c r="A192" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="B192" s="63" t="s">
+      <c r="B192" s="18" t="s">
         <v>401</v>
       </c>
-      <c r="C192" s="52" t="s">
+      <c r="C192" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="D192" s="51">
+      <c r="D192" s="20">
         <v>71</v>
       </c>
-      <c r="E192" s="10"/>
-      <c r="F192" s="34"/>
-      <c r="G192" s="15"/>
-      <c r="H192" s="48"/>
+      <c r="E192" s="21">
+        <v>33</v>
+      </c>
+      <c r="F192" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="G192" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="H192" s="13"/>
     </row>
     <row r="193" spans="1:8" ht="15.75">
-      <c r="A193" s="61" t="s">
+      <c r="A193" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="B193" s="63" t="s">
+      <c r="B193" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="C193" s="52">
+      <c r="C193" s="21">
         <v>22</v>
       </c>
-      <c r="D193" s="51">
+      <c r="D193" s="20">
         <v>54</v>
       </c>
-      <c r="E193" s="22"/>
-      <c r="F193" s="33"/>
-      <c r="G193" s="15"/>
-      <c r="H193" s="48"/>
+      <c r="E193" s="27">
+        <v>10</v>
+      </c>
+      <c r="F193" s="43">
+        <v>47</v>
+      </c>
+      <c r="G193" s="21">
+        <v>62</v>
+      </c>
+      <c r="H193" s="13"/>
     </row>
     <row r="194" spans="1:8" ht="15.75">
-      <c r="A194" s="61" t="s">
+      <c r="A194" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="B194" s="63" t="s">
+      <c r="B194" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="C194" s="52">
+      <c r="C194" s="21">
         <v>7</v>
       </c>
-      <c r="D194" s="51">
+      <c r="D194" s="20">
         <v>31</v>
       </c>
-      <c r="E194" s="11"/>
-      <c r="F194" s="32"/>
-      <c r="G194" s="15"/>
-      <c r="H194" s="48"/>
+      <c r="E194" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="F194" s="40">
+        <v>41</v>
+      </c>
+      <c r="G194" s="21">
+        <v>16</v>
+      </c>
+      <c r="H194" s="13"/>
     </row>
     <row r="195" spans="1:8" ht="15.75">
-      <c r="A195" s="61" t="s">
+      <c r="A195" s="16" t="s">
         <v>388</v>
       </c>
-      <c r="B195" s="63" t="s">
+      <c r="B195" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="C195" s="52">
+      <c r="C195" s="21">
         <v>41</v>
       </c>
-      <c r="D195" s="52" t="s">
+      <c r="D195" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="E195" s="24"/>
-      <c r="F195" s="34"/>
-      <c r="G195" s="15"/>
-      <c r="H195" s="48"/>
+      <c r="E195" s="44">
+        <v>29</v>
+      </c>
+      <c r="F195" s="42">
+        <v>48</v>
+      </c>
+      <c r="G195" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="H195" s="13"/>
     </row>
     <row r="196" spans="1:8" ht="15.75">
-      <c r="A196" s="61" t="s">
+      <c r="A196" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="B196" s="63" t="s">
+      <c r="B196" s="18" t="s">
         <v>398</v>
       </c>
-      <c r="C196" s="52">
+      <c r="C196" s="21">
         <v>35</v>
       </c>
-      <c r="D196" s="52">
+      <c r="D196" s="21">
         <v>84</v>
       </c>
-      <c r="E196" s="59"/>
-      <c r="F196" s="35"/>
-      <c r="G196" s="15"/>
-      <c r="H196" s="48"/>
+      <c r="E196" s="41">
+        <v>79</v>
+      </c>
+      <c r="F196" s="43">
+        <v>44</v>
+      </c>
+      <c r="G196" s="21">
+        <v>76</v>
+      </c>
+      <c r="H196" s="13"/>
     </row>
     <row r="197" spans="1:8" ht="15.75">
-      <c r="A197" s="62" t="s">
+      <c r="A197" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B197" s="63" t="s">
+      <c r="B197" s="18" t="s">
         <v>404</v>
       </c>
-      <c r="C197" s="52" t="s">
+      <c r="C197" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="D197" s="52">
+      <c r="D197" s="21">
         <v>42</v>
       </c>
-      <c r="E197" s="10"/>
-      <c r="F197" s="35"/>
-      <c r="G197" s="15"/>
-      <c r="H197" s="48"/>
+      <c r="E197" s="21">
+        <v>11</v>
+      </c>
+      <c r="F197" s="43" t="s">
+        <v>382</v>
+      </c>
+      <c r="G197" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="H197" s="13"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="62" t="s">
+      <c r="A198" s="17" t="s">
         <v>393</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="C198" s="52" t="s">
+      <c r="C198" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="D198" s="60" t="s">
+      <c r="D198" s="34" t="s">
         <v>382</v>
       </c>
-      <c r="E198" s="10"/>
-      <c r="F198" s="35"/>
-      <c r="G198" s="15"/>
-      <c r="H198" s="48"/>
+      <c r="E198" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="F198" s="43" t="s">
+        <v>382</v>
+      </c>
+      <c r="G198" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="H198" s="13"/>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="61" t="s">
+      <c r="A199" s="16" t="s">
         <v>390</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="C199" s="54">
+      <c r="C199" s="35">
         <v>37</v>
       </c>
-      <c r="D199" s="54" t="s">
-        <v>382</v>
-      </c>
-      <c r="E199" s="10"/>
-      <c r="F199" s="55"/>
-      <c r="G199" s="56"/>
-      <c r="H199" s="48"/>
+      <c r="D199" s="35">
+        <v>30</v>
+      </c>
+      <c r="E199" s="21">
+        <v>7</v>
+      </c>
+      <c r="F199" s="41">
+        <v>13</v>
+      </c>
+      <c r="G199" s="35">
+        <v>37</v>
+      </c>
+      <c r="H199" s="13"/>
     </row>
     <row r="200" spans="1:8" ht="15.75">
-      <c r="A200" s="62" t="s">
+      <c r="A200" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="B200" s="64" t="s">
+      <c r="B200" s="19" t="s">
         <v>407</v>
       </c>
       <c r="C200" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="D200" s="12" t="s">
+      <c r="D200" s="36" t="s">
         <v>382</v>
       </c>
-      <c r="E200" s="10"/>
-      <c r="F200" s="58"/>
-      <c r="G200" s="15"/>
-      <c r="H200" s="48"/>
+      <c r="E200" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="F200" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="G200" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="H200" s="13"/>
     </row>
     <row r="201" spans="1:8" ht="15.75">
-      <c r="A201" s="62" t="s">
+      <c r="A201" s="17" t="s">
         <v>395</v>
       </c>
       <c r="B201" s="1" t="s">
@@ -6224,12 +7348,18 @@
       <c r="C201" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="D201" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="E201" s="10"/>
-      <c r="F201" s="57"/>
-      <c r="G201" s="15"/>
+      <c r="D201" s="51">
+        <v>33</v>
+      </c>
+      <c r="E201" s="21">
+        <v>10</v>
+      </c>
+      <c r="F201" s="20">
+        <v>38</v>
+      </c>
+      <c r="G201" s="21">
+        <v>14</v>
+      </c>
       <c r="H201" s="8"/>
     </row>
   </sheetData>
@@ -6239,6 +7369,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -6382,34 +7527,13 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -6423,4 +7547,10 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>